--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="1256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="1258">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32635235786438</t>
+    <t xml:space="preserve">0.326352328062057</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844811439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323679059743881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980766296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313056260347366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304966062307358</t>
+    <t xml:space="preserve">0.326844841241837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323679089546204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980736494064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313056290149689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304966032505035</t>
   </si>
   <si>
     <t xml:space="preserve">0.29976013302803</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">0.302503794431686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287097215652466</t>
+    <t xml:space="preserve">0.287097275257111</t>
   </si>
   <si>
     <t xml:space="preserve">0.274363934993744</t>
@@ -80,28 +80,28 @@
     <t xml:space="preserve">0.265288770198822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260645717382431</t>
+    <t xml:space="preserve">0.260645747184753</t>
   </si>
   <si>
     <t xml:space="preserve">0.270846426486969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269087702035904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272956907749176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270142942667007</t>
+    <t xml:space="preserve">0.269087672233582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272956937551498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270142912864685</t>
   </si>
   <si>
     <t xml:space="preserve">0.265921950340271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290825724601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288433820009232</t>
+    <t xml:space="preserve">0.290825694799423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288433879613876</t>
   </si>
   <si>
     <t xml:space="preserve">0.294061869382858</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">0.276404052972794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273167997598648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262545198202133</t>
+    <t xml:space="preserve">0.273167967796326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262545168399811</t>
   </si>
   <si>
     <t xml:space="preserve">0.260293990373611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246927514672279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246224045753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239751890301704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240103602409363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271549910306931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276122719049454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274645328521729</t>
+    <t xml:space="preserve">0.246927529573441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24622406065464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239751860499382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240103632211685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271549940109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276122689247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274645268917084</t>
   </si>
   <si>
     <t xml:space="preserve">0.277881413698196</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">0.270987153053284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281539589166641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277177929878235</t>
+    <t xml:space="preserve">0.281539618968964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277177900075912</t>
   </si>
   <si>
     <t xml:space="preserve">0.263319045305252</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">0.268032491207123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28210237622261</t>
+    <t xml:space="preserve">0.282102406024933</t>
   </si>
   <si>
     <t xml:space="preserve">0.295468807220459</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">0.291740298271179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288644909858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504183292389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281469255685806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277248293161392</t>
+    <t xml:space="preserve">0.288644880056381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504213094711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281469225883484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277248233556747</t>
   </si>
   <si>
     <t xml:space="preserve">0.278373837471008</t>
@@ -194,19 +194,19 @@
     <t xml:space="preserve">0.295820623636246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307217299938202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305669575929642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31375977396965</t>
+    <t xml:space="preserve">0.307217240333557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305669546127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313759744167328</t>
   </si>
   <si>
     <t xml:space="preserve">0.320442974567413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317417949438095</t>
+    <t xml:space="preserve">0.317417919635773</t>
   </si>
   <si>
     <t xml:space="preserve">0.316573739051819</t>
@@ -218,34 +218,34 @@
     <t xml:space="preserve">0.310945779085159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311438232660294</t>
+    <t xml:space="preserve">0.311438202857971</t>
   </si>
   <si>
     <t xml:space="preserve">0.301800280809402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288011789321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288082122802734</t>
+    <t xml:space="preserve">0.288011729717255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288082093000412</t>
   </si>
   <si>
     <t xml:space="preserve">0.28055465221405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281328499317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291880995035172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301378220319748</t>
+    <t xml:space="preserve">0.281328558921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291881024837494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301378190517426</t>
   </si>
   <si>
     <t xml:space="preserve">0.311649292707443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310242295265198</t>
+    <t xml:space="preserve">0.310242265462875</t>
   </si>
   <si>
     <t xml:space="preserve">0.311508536338806</t>
@@ -254,58 +254,58 @@
     <t xml:space="preserve">0.314533621072769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316644102334976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318684220314026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330573320388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330643743276596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334161192178726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333528071641922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330432653427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327126204967499</t>
+    <t xml:space="preserve">0.316644072532654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318684250116348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330573350191116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330643683671951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334161162376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3335280418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330432683229446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327126175165176</t>
   </si>
   <si>
     <t xml:space="preserve">0.323538392782211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318543583154678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319247007369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32311624288559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32100573182106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324875056743622</t>
+    <t xml:space="preserve">0.318543523550034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319247037172318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323116272687912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321005791425705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324875026941299</t>
   </si>
   <si>
     <t xml:space="preserve">0.323749423027039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325015723705292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321076154708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326774448156357</t>
+    <t xml:space="preserve">0.325015753507614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32107612490654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326774507761002</t>
   </si>
   <si>
     <t xml:space="preserve">0.331769287586212</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">0.344713658094406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342040330171585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338030397891998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352100372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354914337396622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351678311824799</t>
+    <t xml:space="preserve">0.34204038977623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338030427694321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352100402116776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354914367198944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351678282022476</t>
   </si>
   <si>
     <t xml:space="preserve">0.350341618061066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343306660652161</t>
+    <t xml:space="preserve">0.343306630849838</t>
   </si>
   <si>
     <t xml:space="preserve">0.343165963888168</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">0.341196179389954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34021121263504</t>
+    <t xml:space="preserve">0.340211272239685</t>
   </si>
   <si>
     <t xml:space="preserve">0.337045520544052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323537766933441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309325903654099</t>
+    <t xml:space="preserve">0.323537796735764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309325844049454</t>
   </si>
   <si>
     <t xml:space="preserve">0.3121537566185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308890819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311936259269714</t>
+    <t xml:space="preserve">0.308890849351883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31193619966507</t>
   </si>
   <si>
     <t xml:space="preserve">0.325277984142303</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">0.322232633829117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318607062101364</t>
+    <t xml:space="preserve">0.318607091903687</t>
   </si>
   <si>
     <t xml:space="preserve">0.324190348386765</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">0.299464553594589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313096344470978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320854902267456</t>
+    <t xml:space="preserve">0.3130963742733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320854932069778</t>
   </si>
   <si>
     <t xml:space="preserve">0.318027049303055</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">0.319042146205902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318317025899887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309543401002884</t>
+    <t xml:space="preserve">0.318317085504532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309543430805206</t>
   </si>
   <si>
     <t xml:space="preserve">0.311791211366653</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">0.310558557510376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311066120862961</t>
+    <t xml:space="preserve">0.311066061258316</t>
   </si>
   <si>
     <t xml:space="preserve">0.322087585926056</t>
@@ -419,31 +419,31 @@
     <t xml:space="preserve">0.318172067403793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309978485107422</t>
+    <t xml:space="preserve">0.309978455305099</t>
   </si>
   <si>
     <t xml:space="preserve">0.306715548038483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305627912282944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301784873008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300914764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298739433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298014372587204</t>
+    <t xml:space="preserve">0.305627882480621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30178490281105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300914734601974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298739492893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298014402389526</t>
   </si>
   <si>
     <t xml:space="preserve">0.291488528251648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294316411018372</t>
+    <t xml:space="preserve">0.294316381216049</t>
   </si>
   <si>
     <t xml:space="preserve">0.304467737674713</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">0.301204800605774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302727520465851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30381515622139</t>
+    <t xml:space="preserve">0.302727490663528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303815186023712</t>
   </si>
   <si>
     <t xml:space="preserve">0.30062472820282</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">0.297434329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299682140350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301929891109467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301712393760681</t>
+    <t xml:space="preserve">0.299682110548019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301929861307144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301712363958359</t>
   </si>
   <si>
     <t xml:space="preserve">0.302364975214005</t>
@@ -479,40 +479,40 @@
     <t xml:space="preserve">0.300117135047913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302219957113266</t>
+    <t xml:space="preserve">0.302219927310944</t>
   </si>
   <si>
     <t xml:space="preserve">0.297144263982773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295621544122696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293663829565048</t>
+    <t xml:space="preserve">0.295621573925018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293663769960403</t>
   </si>
   <si>
     <t xml:space="preserve">0.297289282083511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291706025600433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292358636856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29003831744194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287500500679016</t>
+    <t xml:space="preserve">0.291706055402756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292358666658401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290038347244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287500470876694</t>
   </si>
   <si>
     <t xml:space="preserve">0.292648673057556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287645518779755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295041471719742</t>
+    <t xml:space="preserve">0.287645488977432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295041501522064</t>
   </si>
   <si>
     <t xml:space="preserve">0.291561007499695</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.294533938169479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289313167333603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287935584783554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283004879951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287428051233292</t>
+    <t xml:space="preserve">0.289313197135925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287935554981232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283004909753799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287427991628647</t>
   </si>
   <si>
     <t xml:space="preserve">0.282859861850739</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">0.269735664129257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273288637399673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279524445533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282062292098999</t>
+    <t xml:space="preserve">0.273288607597351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279524475336075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282062321901321</t>
   </si>
   <si>
     <t xml:space="preserve">0.283802509307861</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">0.292866200208664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301422297954559</t>
+    <t xml:space="preserve">0.301422327756882</t>
   </si>
   <si>
     <t xml:space="preserve">0.295839101076126</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">0.300262153148651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297071754932404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292938739061356</t>
+    <t xml:space="preserve">0.297071784734726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292938768863678</t>
   </si>
   <si>
     <t xml:space="preserve">0.298812001943588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296056658029556</t>
+    <t xml:space="preserve">0.296056628227234</t>
   </si>
   <si>
     <t xml:space="preserve">0.31019601225853</t>
@@ -605,49 +605,49 @@
     <t xml:space="preserve">0.307078093290329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301639884710312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294098883867264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283077418804169</t>
+    <t xml:space="preserve">0.30163985490799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294098854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283077389001846</t>
   </si>
   <si>
     <t xml:space="preserve">0.287863045930862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289603263139725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285615265369415</t>
+    <t xml:space="preserve">0.289603233337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285615235567093</t>
   </si>
   <si>
     <t xml:space="preserve">0.2839475274086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288805663585663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293736338615417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290835916996002</t>
+    <t xml:space="preserve">0.288805693387985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293736279010773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290835976600647</t>
   </si>
   <si>
     <t xml:space="preserve">0.283512473106384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281409651041031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280684620141983</t>
+    <t xml:space="preserve">0.281409680843353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280684590339661</t>
   </si>
   <si>
     <t xml:space="preserve">0.279016852378845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796200752258</t>
+    <t xml:space="preserve">0.273796230554581</t>
   </si>
   <si>
     <t xml:space="preserve">0.291416019201279</t>
@@ -659,85 +659,85 @@
     <t xml:space="preserve">0.290545910596848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288588136434555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292213618755341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292141169309616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294388890266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29939204454422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296491712331772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303597629070282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309615910053253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307440638542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319187194108963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331513822078705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331368774175644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345000565052032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349786192178726</t>
+    <t xml:space="preserve">0.288588106632233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292213648557663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292141079902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294388860464096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299392074346542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296491682529449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30359759926796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309615880250931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307440608739853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319187223911285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331513851881027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331368803977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345000594854355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349786221981049</t>
   </si>
   <si>
     <t xml:space="preserve">0.358342349529266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354209333658218</t>
+    <t xml:space="preserve">0.354209303855896</t>
   </si>
   <si>
     <t xml:space="preserve">0.34964120388031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352396577596664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355296939611435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359430015087128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352686613798141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346885859966278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343187868595123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346160739660263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346595764160156</t>
+    <t xml:space="preserve">0.352396547794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355296969413757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359429985284805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352686643600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3468858897686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343187898397446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346160769462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346595793962479</t>
   </si>
   <si>
     <t xml:space="preserve">0.346450805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344348013401031</t>
+    <t xml:space="preserve">0.344347983598709</t>
   </si>
   <si>
     <t xml:space="preserve">0.350221306085587</t>
@@ -749,22 +749,22 @@
     <t xml:space="preserve">0.388288795948029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397715091705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379950195550919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382125496864319</t>
+    <t xml:space="preserve">0.397715032100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379950255155563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382125526666641</t>
   </si>
   <si>
     <t xml:space="preserve">0.37487456202507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37342432141304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377412408590317</t>
+    <t xml:space="preserve">0.373424351215363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377412378787994</t>
   </si>
   <si>
     <t xml:space="preserve">0.373061835765839</t>
@@ -773,64 +773,64 @@
     <t xml:space="preserve">0.369798868894577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383575648069382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369436353445053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369073778390884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358197331428528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358052313327789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377049833536148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412579476833344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382488071918488</t>
+    <t xml:space="preserve">0.383575707674026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369436323642731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369073748588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35819736123085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358052343130112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377049803733826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412579506635666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382488042116165</t>
   </si>
   <si>
     <t xml:space="preserve">0.400615483522415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394452184438705</t>
+    <t xml:space="preserve">0.394452154636383</t>
   </si>
   <si>
     <t xml:space="preserve">0.385750979185104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393727034330368</t>
+    <t xml:space="preserve">0.39372706413269</t>
   </si>
   <si>
     <t xml:space="preserve">0.390464097261429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384300768375397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391551822423935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387563705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390826642513275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395177185535431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393364489078522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397352457046509</t>
+    <t xml:space="preserve">0.384300798177719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391551792621613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387563735246658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390826612710953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395177245140076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393364518880844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397352516651154</t>
   </si>
   <si>
     <t xml:space="preserve">0.398802667856216</t>
@@ -842,76 +842,76 @@
     <t xml:space="preserve">0.396627396345139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398440152406693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395902335643768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393001914024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398077607154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401703059673309</t>
+    <t xml:space="preserve">0.39844012260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395902305841446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393001973628998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398077636957169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401703119277954</t>
   </si>
   <si>
     <t xml:space="preserve">0.392276853322983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387201189994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386476069688797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382850587368011</t>
+    <t xml:space="preserve">0.387201130390167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386476099491119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382850557565689</t>
   </si>
   <si>
     <t xml:space="preserve">0.394089609384537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389376491308212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38176292181015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38103786110878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386838644742966</t>
+    <t xml:space="preserve">0.389376431703568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381762951612473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381037831306458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386838614940643</t>
   </si>
   <si>
     <t xml:space="preserve">0.38865140080452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385025888681412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391189247369766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392639338970184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425631284713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419105410575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445208877325058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435057461261749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442308485507965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432611972093582</t>
+    <t xml:space="preserve">0.385025858879089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391189217567444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392639398574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425631314516068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419105380773544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445208847522736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435057550668716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442308455705643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43261194229126</t>
   </si>
   <si>
     <t xml:space="preserve">0.413591980934143</t>
@@ -920,19 +920,19 @@
     <t xml:space="preserve">0.408370792865753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406879037618637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402776718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399047315120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400539070367813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395317822694778</t>
+    <t xml:space="preserve">0.406878978013992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402776688337326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399047285318375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400539040565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395317792892456</t>
   </si>
   <si>
     <t xml:space="preserve">0.396809607744217</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">0.39606374502182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393080174922943</t>
+    <t xml:space="preserve">0.393080204725266</t>
   </si>
   <si>
     <t xml:space="preserve">0.388604938983917</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">0.387859016656876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379654318094254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381146043539047</t>
+    <t xml:space="preserve">0.379654288291931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38114607334137</t>
   </si>
   <si>
     <t xml:space="preserve">0.383010774850845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387486100196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384875506162643</t>
+    <t xml:space="preserve">0.387486159801483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384875476360321</t>
   </si>
   <si>
     <t xml:space="preserve">0.383756697177887</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">0.394944906234741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403522580862045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410235464572906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407251924276352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407624959945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40874370932579</t>
+    <t xml:space="preserve">0.403522610664368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410235494375229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407251954078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407624930143356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408743679523468</t>
   </si>
   <si>
     <t xml:space="preserve">0.406506061553955</t>
@@ -998,22 +998,22 @@
     <t xml:space="preserve">0.40091198682785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394199043512344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398674309253693</t>
+    <t xml:space="preserve">0.394199013710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398674339056015</t>
   </si>
   <si>
     <t xml:space="preserve">0.390842527151108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392334342002869</t>
+    <t xml:space="preserve">0.392334282398224</t>
   </si>
   <si>
     <t xml:space="preserve">0.388231992721558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387113124132156</t>
+    <t xml:space="preserve">0.387113183736801</t>
   </si>
   <si>
     <t xml:space="preserve">0.391588419675827</t>
@@ -1025,55 +1025,55 @@
     <t xml:space="preserve">0.385621428489685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380773186683655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385248452425003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383383721113205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397928416728973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40948960185051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410981357097626</t>
+    <t xml:space="preserve">0.380773156881332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385248422622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383383750915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397928476333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409489631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410981416702271</t>
   </si>
   <si>
     <t xml:space="preserve">0.41433784365654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415083736181259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416575491428375</t>
+    <t xml:space="preserve">0.415083765983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41657555103302</t>
   </si>
   <si>
     <t xml:space="preserve">0.415829628705978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424034297466278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439324945211411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866079568863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428882569074631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420304894447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421796679496765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428509652614594</t>
+    <t xml:space="preserve">0.424034357070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439324975013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866109371185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428882539272308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420304924249649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421796709299088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428509622812271</t>
   </si>
   <si>
     <t xml:space="preserve">0.454988479614258</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">0.445291996002197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444546103477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440443783998489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44976732134819</t>
+    <t xml:space="preserve">0.4445461332798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440443724393845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449767261743546</t>
   </si>
   <si>
     <t xml:space="preserve">0.459463715553284</t>
@@ -1097,91 +1097,91 @@
     <t xml:space="preserve">0.460955500602722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469533205032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466549694538116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474008500576019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474754333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348467826843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485942631959915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482586085796356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4855697453022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50943797826767</t>
+    <t xml:space="preserve">0.469533234834671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466549664735794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474008440971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474754363298416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480348497629166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485942602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482586145401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485569655895233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509437918663025</t>
   </si>
   <si>
     <t xml:space="preserve">0.511302649974823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521744966506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512794375419617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519507348537445</t>
+    <t xml:space="preserve">0.521745026111603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512794435024261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5195072889328</t>
   </si>
   <si>
     <t xml:space="preserve">0.511675536632538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506081402301788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501233160495758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502352058887482</t>
+    <t xml:space="preserve">0.506081342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501233220100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502351999282837</t>
   </si>
   <si>
     <t xml:space="preserve">0.495266109704971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49153670668602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477737873792648</t>
+    <t xml:space="preserve">0.491536736488342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477737843990326</t>
   </si>
   <si>
     <t xml:space="preserve">0.478483766317368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48109433054924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492282629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499741435050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493774354457855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495639055967331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507946133613586</t>
+    <t xml:space="preserve">0.481094390153885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492282658815384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499741464853287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493774324655533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495639085769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507946074008942</t>
   </si>
   <si>
     <t xml:space="preserve">0.500114381313324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493028491735458</t>
+    <t xml:space="preserve">0.493028551340103</t>
   </si>
   <si>
     <t xml:space="preserve">0.508692026138306</t>
@@ -1190,115 +1190,115 @@
     <t xml:space="preserve">0.503470897674561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508319020271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507200181484222</t>
+    <t xml:space="preserve">0.508319079875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507200300693512</t>
   </si>
   <si>
     <t xml:space="preserve">0.510183811187744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513167262077332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500860333442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503097891807556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502725005149841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501606166362762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498249650001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510929644107819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531068503856659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557920336723328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554936707019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559412002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56537914276123</t>
+    <t xml:space="preserve">0.513167381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500860273838043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503097951412201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502724945545197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501606225967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498249709606171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510929584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531068563461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557920277118683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554936766624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559412062168121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565379202365875</t>
   </si>
   <si>
     <t xml:space="preserve">0.593722641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574329674243927</t>
+    <t xml:space="preserve">0.574329733848572</t>
   </si>
   <si>
     <t xml:space="preserve">0.576567351818085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577313244342804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583280324935913</t>
+    <t xml:space="preserve">0.577313303947449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583280265331268</t>
   </si>
   <si>
     <t xml:space="preserve">0.59148496389389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585517942905426</t>
+    <t xml:space="preserve">0.585518002510071</t>
   </si>
   <si>
     <t xml:space="preserve">0.575075566768646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612369656562805</t>
+    <t xml:space="preserve">0.612369775772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.556428551673889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551953196525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548223793506622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53479790687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521372079849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505708456039429</t>
+    <t xml:space="preserve">0.551953256130219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548223853111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534797847270966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521372020244598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505708575248718</t>
   </si>
   <si>
     <t xml:space="preserve">0.528084993362427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54524028301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522863745689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517642617225647</t>
+    <t xml:space="preserve">0.545240342617035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522863686084747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517642557621002</t>
   </si>
   <si>
     <t xml:space="preserve">0.532560288906097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531814336776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523609697818756</t>
+    <t xml:space="preserve">0.531814396381378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523609638214111</t>
   </si>
   <si>
     <t xml:space="preserve">0.516150832176208</t>
@@ -1307,34 +1307,34 @@
     <t xml:space="preserve">0.512421369552612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519134402275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498995572328568</t>
+    <t xml:space="preserve">0.519134342670441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498995631933212</t>
   </si>
   <si>
     <t xml:space="preserve">0.463193148374557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469906121492386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476619094610214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477364927530289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494520217180252</t>
+    <t xml:space="preserve">0.469906151294708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476619064807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477364987134933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494520276784897</t>
   </si>
   <si>
     <t xml:space="preserve">0.490044951438904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478856772184372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47811084985733</t>
+    <t xml:space="preserve">0.478856682777405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478110790252686</t>
   </si>
   <si>
     <t xml:space="preserve">0.468414396047592</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">0.481840282678604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484077870845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475127309560776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473635494709015</t>
+    <t xml:space="preserve">0.484077930450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475127369165421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473635524511337</t>
   </si>
   <si>
     <t xml:space="preserve">0.474381387233734</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">0.487061411142349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483332067728043</t>
+    <t xml:space="preserve">0.48333203792572</t>
   </si>
   <si>
     <t xml:space="preserve">0.50421679019928</t>
@@ -1370,37 +1370,37 @@
     <t xml:space="preserve">0.504962623119354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49675789475441</t>
+    <t xml:space="preserve">0.496757864952087</t>
   </si>
   <si>
     <t xml:space="preserve">0.497503817081451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486315608024597</t>
+    <t xml:space="preserve">0.486315578222275</t>
   </si>
   <si>
     <t xml:space="preserve">0.500487387180328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454242587089539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452004969120026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457226097583771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458717882633209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462447315454483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455734401941299</t>
+    <t xml:space="preserve">0.454242616891861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465430825948715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452004939317703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457226037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458717823028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462447285652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455734312534332</t>
   </si>
   <si>
     <t xml:space="preserve">0.457972019910812</t>
@@ -1409,82 +1409,82 @@
     <t xml:space="preserve">0.485727906227112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48418590426445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474933862686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469536989927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464910984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461055934429169</t>
+    <t xml:space="preserve">0.484185874462128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47493389248848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469536960124969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464910924434662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461055904626846</t>
   </si>
   <si>
     <t xml:space="preserve">0.463368952274323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459514081478119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45797199010849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458743065595627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447949051856995</t>
+    <t xml:space="preserve">0.459513992071152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457971960306168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45874297618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447949022054672</t>
   </si>
   <si>
     <t xml:space="preserve">0.451033025979996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454887986183167</t>
+    <t xml:space="preserve">0.454887956380844</t>
   </si>
   <si>
     <t xml:space="preserve">0.446407049894333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44178107380867</t>
+    <t xml:space="preserve">0.441781044006348</t>
   </si>
   <si>
     <t xml:space="preserve">0.443323045969009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494208812713623</t>
+    <t xml:space="preserve">0.494208782911301</t>
   </si>
   <si>
     <t xml:space="preserve">0.474162876605988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481101870536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489582806825638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476475864648819</t>
+    <t xml:space="preserve">0.481101900339127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48958283662796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476475894451141</t>
   </si>
   <si>
     <t xml:space="preserve">0.464139968156815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461826950311661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456430017948151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454117000102997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466453015804291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467223942279816</t>
+    <t xml:space="preserve">0.461826920509338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456429988145828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454117059707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466452956199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467223972082138</t>
   </si>
   <si>
     <t xml:space="preserve">0.439468055963516</t>
@@ -1496,46 +1496,46 @@
     <t xml:space="preserve">0.45257505774498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45334604382515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4410100877285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437926083803177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433300107717514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430987149477005</t>
+    <t xml:space="preserve">0.453346014022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441010117530823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437926054000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433300137519836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430987119674683</t>
   </si>
   <si>
     <t xml:space="preserve">0.431758135557175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435613095760345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444865107536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284948348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451804041862488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470308005809784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471849918365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465681940317154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457200974225998</t>
+    <t xml:space="preserve">0.435613065958023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444865047931671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460285007953644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45180407166481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470307916402817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471849888563156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465681970119476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45720100402832</t>
   </si>
   <si>
     <t xml:space="preserve">0.46259793639183</t>
@@ -1544,28 +1544,28 @@
     <t xml:space="preserve">0.455659002065659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450262039899826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449491024017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437155038118362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440239012241364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426361083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427903175354004</t>
+    <t xml:space="preserve">0.450262069702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449491053819656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43715512752533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440239071846008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42636114358902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427903115749359</t>
   </si>
   <si>
     <t xml:space="preserve">0.407086193561554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406315237283707</t>
+    <t xml:space="preserve">0.406315207481384</t>
   </si>
   <si>
     <t xml:space="preserve">0.410170197486877</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">0.404002219438553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407857209444046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41094121336937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400147259235382</t>
+    <t xml:space="preserve">0.407857179641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410941183567047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400147289037704</t>
   </si>
   <si>
     <t xml:space="preserve">0.396292269229889</t>
@@ -1598,31 +1598,31 @@
     <t xml:space="preserve">0.38318532705307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387811362743378</t>
+    <t xml:space="preserve">0.387811332941055</t>
   </si>
   <si>
     <t xml:space="preserve">0.388582289218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39475029706955</t>
+    <t xml:space="preserve">0.394750326871872</t>
   </si>
   <si>
     <t xml:space="preserve">0.397063255310059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389353275299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387040317058563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385498315095901</t>
+    <t xml:space="preserve">0.389353305101395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387040287256241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385498285293579</t>
   </si>
   <si>
     <t xml:space="preserve">0.375475317239761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366223394870758</t>
+    <t xml:space="preserve">0.36622342467308</t>
   </si>
   <si>
     <t xml:space="preserve">0.351188957691193</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">0.345406502485275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348875939846039</t>
+    <t xml:space="preserve">0.348875969648361</t>
   </si>
   <si>
     <t xml:space="preserve">0.366994440555573</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">0.372391372919083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36776539683342</t>
+    <t xml:space="preserve">0.367765367031097</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162358999252</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">0.370078384876251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370463937520981</t>
+    <t xml:space="preserve">0.370463877916336</t>
   </si>
   <si>
     <t xml:space="preserve">0.369692862033844</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">0.365837901830673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371620386838913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368536353111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368921875953674</t>
+    <t xml:space="preserve">0.371620327234268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368536382913589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368921905755997</t>
   </si>
   <si>
     <t xml:space="preserve">0.378944844007492</t>
@@ -1676,40 +1676,40 @@
     <t xml:space="preserve">0.377017349004745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382414281368256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399376273155212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416338175535202</t>
+    <t xml:space="preserve">0.382414311170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399376302957535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416338235139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.424048125743866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42481917142868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417109161615372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422506153583527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421735137701035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420964151620865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408628195524216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400918275117874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404773205518723</t>
+    <t xml:space="preserve">0.424819141626358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417109221220016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422506123781204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421735107898712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420964121818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408628165721893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400918245315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4047731757164</t>
   </si>
   <si>
     <t xml:space="preserve">0.405544221401215</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">0.411712169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412483215332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423277109861374</t>
+    <t xml:space="preserve">0.412483245134354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423277169466019</t>
   </si>
   <si>
     <t xml:space="preserve">0.425590127706528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41942223906517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430216133594513</t>
+    <t xml:space="preserve">0.419422209262848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430216163396835</t>
   </si>
   <si>
     <t xml:space="preserve">0.427132159471512</t>
@@ -1739,16 +1739,16 @@
     <t xml:space="preserve">0.414025187492371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414796233177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413254231214523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409399181604385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395521253347397</t>
+    <t xml:space="preserve">0.41479617357254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413254201412201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40939924120903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395521283149719</t>
   </si>
   <si>
     <t xml:space="preserve">0.393208265304565</t>
@@ -1757,19 +1757,19 @@
     <t xml:space="preserve">0.392437279224396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391666293144226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393979281187057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398605287075043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403231203556061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411275923252106</t>
+    <t xml:space="preserve">0.391666322946548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393979251384735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398605316877365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403231233358383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411275893449783</t>
   </si>
   <si>
     <t xml:space="preserve">0.410471081733704</t>
@@ -1781,73 +1781,73 @@
     <t xml:space="preserve">0.415300130844116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41288560628891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41208079457283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399203211069107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401215374469757</t>
+    <t xml:space="preserve">0.412885665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412080824375153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399203240871429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401215344667435</t>
   </si>
   <si>
     <t xml:space="preserve">0.404032319784164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397995978593826</t>
+    <t xml:space="preserve">0.397996008396149</t>
   </si>
   <si>
     <t xml:space="preserve">0.403227478265762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398398369550705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400008112192154</t>
+    <t xml:space="preserve">0.398398399353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400008082389832</t>
   </si>
   <si>
     <t xml:space="preserve">0.40242263674736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400410503149033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395983874797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399605631828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418519556522369</t>
+    <t xml:space="preserve">0.400410532951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395983904600143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39960566163063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418519526720047</t>
   </si>
   <si>
     <t xml:space="preserve">0.417714715003967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416909873485565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404837220907211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401617795228958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407251685857773</t>
+    <t xml:space="preserve">0.416909903287888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404837191104889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401617825031281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40725165605545</t>
   </si>
   <si>
     <t xml:space="preserve">0.408056557178497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405642002820969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397593587636948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391154766082764</t>
+    <t xml:space="preserve">0.405642032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397593557834625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391154795885086</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446844339371</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">0.428177684545517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433006793260574</t>
+    <t xml:space="preserve">0.433006763458252</t>
   </si>
   <si>
     <t xml:space="preserve">0.429787337779999</t>
@@ -1880,16 +1880,16 @@
     <t xml:space="preserve">0.420934051275253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428982526063919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437030971050262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434616446495056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430592238903046</t>
+    <t xml:space="preserve">0.428982496261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437031000852585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434616506099701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430592268705368</t>
   </si>
   <si>
     <t xml:space="preserve">0.4426648914814</t>
@@ -1898,10 +1898,10 @@
     <t xml:space="preserve">0.458761781454086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46681022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473249047994614</t>
+    <t xml:space="preserve">0.466810256242752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473248988389969</t>
   </si>
   <si>
     <t xml:space="preserve">0.476468414068222</t>
@@ -1913,70 +1913,70 @@
     <t xml:space="preserve">0.475663542747498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48129740357399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478078067302704</t>
+    <t xml:space="preserve">0.481297463178635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478078097105026</t>
   </si>
   <si>
     <t xml:space="preserve">0.474858671426773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471639335155487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472444206476212</t>
+    <t xml:space="preserve">0.471639424562454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472444176673889</t>
   </si>
   <si>
     <t xml:space="preserve">0.486126512289047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48049259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494979798793793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511881530284882</t>
+    <t xml:space="preserve">0.480492621660233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494979828596115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511881589889526</t>
   </si>
   <si>
     <t xml:space="preserve">0.513491272926331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520734965801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535222172737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534417271614075</t>
+    <t xml:space="preserve">0.520734906196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535222113132477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53441721200943</t>
   </si>
   <si>
     <t xml:space="preserve">0.523149430751801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51510101556778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516710638999939</t>
+    <t xml:space="preserve">0.515100955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516710698604584</t>
   </si>
   <si>
     <t xml:space="preserve">0.522344589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556148111820221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555343210697174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551319003105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55775773525238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.571440160274506</t>
+    <t xml:space="preserve">0.556148052215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555343270301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551318943500519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557757794857025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.571440100669861</t>
   </si>
   <si>
     <t xml:space="preserve">0.56178206205368</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">0.560977220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552928626537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554538369178772</t>
+    <t xml:space="preserve">0.552928686141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554538428783417</t>
   </si>
   <si>
     <t xml:space="preserve">0.59236615896225</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">0.611682415008545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606853365898132</t>
+    <t xml:space="preserve">0.606853306293488</t>
   </si>
   <si>
     <t xml:space="preserve">0.602024257183075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614901781082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600414514541626</t>
+    <t xml:space="preserve">0.614901840686798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600414574146271</t>
   </si>
   <si>
     <t xml:space="preserve">0.608462989330292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593975782394409</t>
+    <t xml:space="preserve">0.593975722789764</t>
   </si>
   <si>
     <t xml:space="preserve">0.590756475925446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595585525035858</t>
+    <t xml:space="preserve">0.595585465431213</t>
   </si>
   <si>
     <t xml:space="preserve">0.609267890453339</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">0.60604852437973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593170940876007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598804891109467</t>
+    <t xml:space="preserve">0.593171000480652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598804950714111</t>
   </si>
   <si>
     <t xml:space="preserve">0.601219356060028</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">0.594780683517456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603633940219879</t>
+    <t xml:space="preserve">0.603633880615234</t>
   </si>
   <si>
     <t xml:space="preserve">0.610072731971741</t>
@@ -2060,10 +2060,10 @@
     <t xml:space="preserve">0.630193829536438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631803572177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64629077911377</t>
+    <t xml:space="preserve">0.631803512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64629065990448</t>
   </si>
   <si>
     <t xml:space="preserve">0.655948877334595</t>
@@ -2072,37 +2072,37 @@
     <t xml:space="preserve">0.65997314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689752399921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684118509292603</t>
+    <t xml:space="preserve">0.689752280712128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684118449687958</t>
   </si>
   <si>
     <t xml:space="preserve">0.661582827568054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588341891765594</t>
+    <t xml:space="preserve">0.58834183216095</t>
   </si>
   <si>
     <t xml:space="preserve">0.581098258495331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572244942188263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540856003761292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543270587921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518320381641388</t>
+    <t xml:space="preserve">0.572245001792908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540856063365936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543270528316498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518320322036743</t>
   </si>
   <si>
     <t xml:space="preserve">0.526368796825409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490955680608749</t>
+    <t xml:space="preserve">0.490955591201782</t>
   </si>
   <si>
     <t xml:space="preserve">0.439445495605469</t>
@@ -2111,10 +2111,10 @@
     <t xml:space="preserve">0.398800820112228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381496638059616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323145389556885</t>
+    <t xml:space="preserve">0.381496667861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32314532995224</t>
   </si>
   <si>
     <t xml:space="preserve">0.348095595836639</t>
@@ -2126,16 +2126,16 @@
     <t xml:space="preserve">0.282500684261322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288939476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291353970766068</t>
+    <t xml:space="preserve">0.288939446210861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29135400056839</t>
   </si>
   <si>
     <t xml:space="preserve">0.304633945226669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308255761861801</t>
+    <t xml:space="preserve">0.308255732059479</t>
   </si>
   <si>
     <t xml:space="preserve">0.343668937683105</t>
@@ -2147,28 +2147,28 @@
     <t xml:space="preserve">0.37224093079567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355741620063782</t>
+    <t xml:space="preserve">0.355741590261459</t>
   </si>
   <si>
     <t xml:space="preserve">0.373850613832474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391959607601166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37908211350441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375057905912399</t>
+    <t xml:space="preserve">0.391959637403488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379082143306732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375057876110077</t>
   </si>
   <si>
     <t xml:space="preserve">0.384716004133224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386325716972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374253034591675</t>
+    <t xml:space="preserve">0.386325746774673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374253064393997</t>
   </si>
   <si>
     <t xml:space="preserve">0.362180352210999</t>
@@ -2180,16 +2180,16 @@
     <t xml:space="preserve">0.353327065706253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34930282831192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344473779201508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323547810316086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338035017251968</t>
+    <t xml:space="preserve">0.349302798509598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344473749399185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323547780513763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338034987449646</t>
   </si>
   <si>
     <t xml:space="preserve">0.339644700288773</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">0.348497986793518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342864066362381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34527862071991</t>
+    <t xml:space="preserve">0.342864125967026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345278590917587</t>
   </si>
   <si>
     <t xml:space="preserve">0.336425334215164</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">0.326767146587372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321938097476959</t>
+    <t xml:space="preserve">0.321938127279282</t>
   </si>
   <si>
     <t xml:space="preserve">0.331596255302429</t>
@@ -2234,28 +2234,28 @@
     <t xml:space="preserve">0.340449541807175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347693145275116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352522224187851</t>
+    <t xml:space="preserve">0.347693175077438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352522253990173</t>
   </si>
   <si>
     <t xml:space="preserve">0.354936748743057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36942395567894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382301509380341</t>
+    <t xml:space="preserve">0.369423985481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382301479578018</t>
   </si>
   <si>
     <t xml:space="preserve">0.379886984825134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371838510036469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354131937026978</t>
+    <t xml:space="preserve">0.371838539838791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354131907224655</t>
   </si>
   <si>
     <t xml:space="preserve">0.330791413784027</t>
@@ -2264,25 +2264,25 @@
     <t xml:space="preserve">0.356546431779861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357351273298264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350107669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346888333559036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342059254646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337230175733566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328376829624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335620433092117</t>
+    <t xml:space="preserve">0.357351303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350107729434967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346888303756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342059224843979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337230145931244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328376859426498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335620492696762</t>
   </si>
   <si>
     <t xml:space="preserve">0.370228826999664</t>
@@ -2294,13 +2294,13 @@
     <t xml:space="preserve">0.363790035247803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420129239559174</t>
+    <t xml:space="preserve">0.420129269361496</t>
   </si>
   <si>
     <t xml:space="preserve">0.424958288669586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437835901975632</t>
+    <t xml:space="preserve">0.437835842370987</t>
   </si>
   <si>
     <t xml:space="preserve">0.444274574518204</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">0.445884317159653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482907116413116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560172259807587</t>
+    <t xml:space="preserve">0.482907176017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560172319412231</t>
   </si>
   <si>
     <t xml:space="preserve">0.527978479862213</t>
@@ -2321,40 +2321,40 @@
     <t xml:space="preserve">0.521539747714996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529588222503662</t>
+    <t xml:space="preserve">0.529588162899017</t>
   </si>
   <si>
     <t xml:space="preserve">0.519930064678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507052540779114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500613808631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49417507648468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502223432064056</t>
+    <t xml:space="preserve">0.507052481174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500613689422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494175046682358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502223491668701</t>
   </si>
   <si>
     <t xml:space="preserve">0.537636637687683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524759113788605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510271847248077</t>
+    <t xml:space="preserve">0.52475917339325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510271906852722</t>
   </si>
   <si>
     <t xml:space="preserve">0.499004065990448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492565274238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487736225128174</t>
+    <t xml:space="preserve">0.492565244436264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487736254930496</t>
   </si>
   <si>
     <t xml:space="preserve">0.484516859054565</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">0.447493940591812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43139711022377</t>
+    <t xml:space="preserve">0.431397080421448</t>
   </si>
   <si>
     <t xml:space="preserve">0.449103683233261</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">0.378277271986008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375862777233124</t>
+    <t xml:space="preserve">0.375862747430801</t>
   </si>
   <si>
     <t xml:space="preserve">0.367009431123734</t>
@@ -2387,34 +2387,34 @@
     <t xml:space="preserve">0.359765827655792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376667559146881</t>
+    <t xml:space="preserve">0.376667588949203</t>
   </si>
   <si>
     <t xml:space="preserve">0.421738892793655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423348605632782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441055208444595</t>
+    <t xml:space="preserve">0.423348635435104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441055178642273</t>
   </si>
   <si>
     <t xml:space="preserve">0.50544285774231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468419909477234</t>
+    <t xml:space="preserve">0.468419969081879</t>
   </si>
   <si>
     <t xml:space="preserve">0.461981207132339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465200573205948</t>
+    <t xml:space="preserve">0.465200543403625</t>
   </si>
   <si>
     <t xml:space="preserve">0.45232304930687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4555424451828</t>
+    <t xml:space="preserve">0.455542385578156</t>
   </si>
   <si>
     <t xml:space="preserve">0.450713366270065</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">0.457152098417282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453932762145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479687869548798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495784610509872</t>
+    <t xml:space="preserve">0.453932821750641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479687839746475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495784670114517</t>
   </si>
   <si>
     <t xml:space="preserve">0.489345908164978</t>
@@ -2444,46 +2444,46 @@
     <t xml:space="preserve">0.565001368522644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576269268989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575464367866516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569830417633057</t>
+    <t xml:space="preserve">0.576269209384918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575464427471161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569830477237701</t>
   </si>
   <si>
     <t xml:space="preserve">0.549709379673004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567415833473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545685052871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558562636375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544075429439545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531197845935822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559367477893829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573854684829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581903040409088</t>
+    <t xml:space="preserve">0.56741589307785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545685112476349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558562576770782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5440753698349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531197905540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559367418289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573854625225067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581903100013733</t>
   </si>
   <si>
     <t xml:space="preserve">0.579488635063171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544880270957947</t>
+    <t xml:space="preserve">0.544880211353302</t>
   </si>
   <si>
     <t xml:space="preserve">0.552123844623566</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">0.548099637031555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548904478549957</t>
+    <t xml:space="preserve">0.548904418945312</t>
   </si>
   <si>
     <t xml:space="preserve">0.553733587265015</t>
@@ -2507,25 +2507,25 @@
     <t xml:space="preserve">0.573743164539337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567091047763824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574589729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572911620140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561270475387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557944476604462</t>
+    <t xml:space="preserve">0.567091107368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574649333954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57291167974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561270534992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557944416999817</t>
   </si>
   <si>
     <t xml:space="preserve">0.558776021003723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540482640266418</t>
+    <t xml:space="preserve">0.540482699871063</t>
   </si>
   <si>
     <t xml:space="preserve">0.544640243053436</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">0.542977273464203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530504524707794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531336069107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532167613506317</t>
+    <t xml:space="preserve">0.530504584312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531336009502411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532167553901672</t>
   </si>
   <si>
     <t xml:space="preserve">0.516368865966797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511379837989807</t>
+    <t xml:space="preserve">0.511379778385162</t>
   </si>
   <si>
     <t xml:space="preserve">0.505559206008911</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">0.508885264396667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50223308801651</t>
+    <t xml:space="preserve">0.502233147621155</t>
   </si>
   <si>
     <t xml:space="preserve">0.515537321567535</t>
@@ -2564,25 +2564,25 @@
     <t xml:space="preserve">0.498907119035721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493918031454086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494749546051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500570058822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483939915895462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465646624565125</t>
+    <t xml:space="preserve">0.493918001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494749575853348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500570118427277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48393988609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465646594762802</t>
   </si>
   <si>
     <t xml:space="preserve">0.466478109359741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461489111185074</t>
+    <t xml:space="preserve">0.461489081382751</t>
   </si>
   <si>
     <t xml:space="preserve">0.460657566785812</t>
@@ -2591,61 +2591,61 @@
     <t xml:space="preserve">0.473961770534515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473130255937576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486434459686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489760458469391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503064692020416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504727602005005</t>
+    <t xml:space="preserve">0.473130285739899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486434429883957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489760518074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503064632415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50472766160965</t>
   </si>
   <si>
     <t xml:space="preserve">0.506390750408173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51054835319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503896117210388</t>
+    <t xml:space="preserve">0.510548293590546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503896176815033</t>
   </si>
   <si>
     <t xml:space="preserve">0.495581090450287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484771430492401</t>
+    <t xml:space="preserve">0.484771400690079</t>
   </si>
   <si>
     <t xml:space="preserve">0.482276886701584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491423487663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497244089841843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487265974283218</t>
+    <t xml:space="preserve">0.491423547267914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497244030237198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487265944480896</t>
   </si>
   <si>
     <t xml:space="preserve">0.493086487054825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483108371496201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478119224309921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475624829530716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476456314325333</t>
+    <t xml:space="preserve">0.483108341693878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478119283914566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475624799728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47645628452301</t>
   </si>
   <si>
     <t xml:space="preserve">0.529673039913177</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">0.528010010719299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533830642700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527178466320038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547966301441193</t>
+    <t xml:space="preserve">0.533830583095551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527178525924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547966241836548</t>
   </si>
   <si>
     <t xml:space="preserve">0.528841495513916</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">0.52551543712616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526346981525421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554618358612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588710427284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575406134128571</t>
+    <t xml:space="preserve">0.526347041130066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554618418216705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588710367679596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575406193733215</t>
   </si>
   <si>
     <t xml:space="preserve">0.577069222927094</t>
@@ -2690,22 +2690,22 @@
     <t xml:space="preserve">0.570417106151581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583721339702606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58538430929184</t>
+    <t xml:space="preserve">0.583721399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585384368896484</t>
   </si>
   <si>
     <t xml:space="preserve">0.57790070772171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580395221710205</t>
+    <t xml:space="preserve">0.58039528131485</t>
   </si>
   <si>
     <t xml:space="preserve">0.550460815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556281447410583</t>
+    <t xml:space="preserve">0.556281387805939</t>
   </si>
   <si>
     <t xml:space="preserve">0.545471787452698</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">0.567922651767731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566259562969208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5571129322052</t>
+    <t xml:space="preserve">0.566259503364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557112991809845</t>
   </si>
   <si>
     <t xml:space="preserve">0.56459653377533</t>
@@ -2735,64 +2735,64 @@
     <t xml:space="preserve">0.532999098300934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524683892726898</t>
+    <t xml:space="preserve">0.524683952331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.509716749191284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507222294807434</t>
+    <t xml:space="preserve">0.507222175598145</t>
   </si>
   <si>
     <t xml:space="preserve">0.521357893943787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513874232769012</t>
+    <t xml:space="preserve">0.513874351978302</t>
   </si>
   <si>
     <t xml:space="preserve">0.522189497947693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513042807579041</t>
+    <t xml:space="preserve">0.513042747974396</t>
   </si>
   <si>
     <t xml:space="preserve">0.52052640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52302098274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519694864749908</t>
+    <t xml:space="preserve">0.523020923137665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519694924354553</t>
   </si>
   <si>
     <t xml:space="preserve">0.508053779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488097459077835</t>
+    <t xml:space="preserve">0.488097429275513</t>
   </si>
   <si>
     <t xml:space="preserve">0.488928943872452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492255002260208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496412575244904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490591943264008</t>
+    <t xml:space="preserve">0.492255032062531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496412515640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490591913461685</t>
   </si>
   <si>
     <t xml:space="preserve">0.485602915287018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480613887310028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474793285131454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454005479812622</t>
+    <t xml:space="preserve">0.480613857507706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474793195724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4540054500103</t>
   </si>
   <si>
     <t xml:space="preserve">0.478950768709183</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">0.44901642203331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43986976146698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439038276672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419913440942764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422408044338226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424071043729782</t>
+    <t xml:space="preserve">0.439869731664658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439038246870041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419913470745087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422408014535904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42407101392746</t>
   </si>
   <si>
     <t xml:space="preserve">0.411598384380341</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">0.41118261218071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395799666643143</t>
+    <t xml:space="preserve">0.395799607038498</t>
   </si>
   <si>
     <t xml:space="preserve">0.377090603113174</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">0.402035981416702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413677126169205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407440781593323</t>
+    <t xml:space="preserve">0.413677155971527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407440841197968</t>
   </si>
   <si>
     <t xml:space="preserve">0.412429869174957</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">0.431554615497589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429891645908356</t>
+    <t xml:space="preserve">0.429891616106033</t>
   </si>
   <si>
     <t xml:space="preserve">0.432386130094528</t>
@@ -2858,64 +2858,64 @@
     <t xml:space="preserve">0.451510936021805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444027304649353</t>
+    <t xml:space="preserve">0.444027274847031</t>
   </si>
   <si>
     <t xml:space="preserve">0.436543703079224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443195790052414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448184877634048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44652184844017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440701216459274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434880703687668</t>
+    <t xml:space="preserve">0.443195819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448184818029404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.446521908044815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440701276063919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434880673885345</t>
   </si>
   <si>
     <t xml:space="preserve">0.424902558326721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444858849048615</t>
+    <t xml:space="preserve">0.444858878850937</t>
   </si>
   <si>
     <t xml:space="preserve">0.447353363037109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445690363645554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463152140378952</t>
+    <t xml:space="preserve">0.445690333843231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463152080774307</t>
   </si>
   <si>
     <t xml:space="preserve">0.481445372104645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477287769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470635652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437375277280807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429060071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421576499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409935355186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430723160505295</t>
+    <t xml:space="preserve">0.477287858724594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470635682344437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437375247478485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429060101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421576529741287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40993532538414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430723130702972</t>
   </si>
   <si>
     <t xml:space="preserve">0.427397072315216</t>
@@ -2930,28 +2930,28 @@
     <t xml:space="preserve">0.452196657657623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446109414100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439152508974075</t>
+    <t xml:space="preserve">0.446109443902969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439152538776398</t>
   </si>
   <si>
     <t xml:space="preserve">0.431326061487198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423499584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406542181968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403063774108887</t>
+    <t xml:space="preserve">0.423499554395676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406542211771011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403063744306564</t>
   </si>
   <si>
     <t xml:space="preserve">0.414368689060211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3939328789711</t>
+    <t xml:space="preserve">0.393932908773422</t>
   </si>
   <si>
     <t xml:space="preserve">0.391324043273926</t>
@@ -2960,64 +2960,64 @@
     <t xml:space="preserve">0.383932381868362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388715207576752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627934217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380888760089874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387845635414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393498063087463</t>
+    <t xml:space="preserve">0.388715237379074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627964019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380888730287552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387845605611801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393498033285141</t>
   </si>
   <si>
     <t xml:space="preserve">0.379584342241287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384367167949677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378714710474014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373931914567947</t>
+    <t xml:space="preserve">0.384367197751999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378714740276337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373931884765625</t>
   </si>
   <si>
     <t xml:space="preserve">0.372627437114716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373062252998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3782799243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370888203382492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361322551965714</t>
+    <t xml:space="preserve">0.37306222319603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378279894590378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370888233184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361322522163391</t>
   </si>
   <si>
     <t xml:space="preserve">0.366105407476425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371323019266129</t>
+    <t xml:space="preserve">0.371323049068451</t>
   </si>
   <si>
     <t xml:space="preserve">0.375671088695526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374366700649261</t>
+    <t xml:space="preserve">0.374366670846939</t>
   </si>
   <si>
     <t xml:space="preserve">0.370018631219864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367844611406326</t>
+    <t xml:space="preserve">0.367844581604004</t>
   </si>
   <si>
     <t xml:space="preserve">0.366975009441376</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">0.36175736784935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368714183568954</t>
+    <t xml:space="preserve">0.368714213371277</t>
   </si>
   <si>
     <t xml:space="preserve">0.377410292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369583815336227</t>
+    <t xml:space="preserve">0.36958384513855</t>
   </si>
   <si>
     <t xml:space="preserve">0.377845108509064</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">0.374801486730576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37523627281189</t>
+    <t xml:space="preserve">0.375236243009567</t>
   </si>
   <si>
     <t xml:space="preserve">0.372192651033401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365235775709152</t>
+    <t xml:space="preserve">0.36523574590683</t>
   </si>
   <si>
     <t xml:space="preserve">0.376540690660477</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">0.364800959825516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386976033449173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397411286830902</t>
+    <t xml:space="preserve">0.386976003646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397411316633224</t>
   </si>
   <si>
     <t xml:space="preserve">0.402628988027573</t>
@@ -3080,175 +3080,178 @@
     <t xml:space="preserve">0.407846629619598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389584839344025</t>
+    <t xml:space="preserve">0.389584869146347</t>
   </si>
   <si>
     <t xml:space="preserve">0.396106898784637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399150520563126</t>
+    <t xml:space="preserve">0.399150550365448</t>
   </si>
   <si>
     <t xml:space="preserve">0.403498560190201</t>
   </si>
   <si>
+    <t xml:space="preserve">0.396541714668274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392193675041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401759386062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403933376073837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408716231584549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400020152330399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400889724493027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393063247203827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380019158124924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385236769914627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389150023460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390889227390289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395672082901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401324540376663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39697653055191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400454938411713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390454411506653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387410819530487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383497565984726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382193177938461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381758362054825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371757864952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357844114303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366540193557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360887736082077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362626940011978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369149029254913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379149526357651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3861064016819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394367694854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404368221759796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392628461122513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391758888959885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395237267017365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385671585798264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394802510738373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388280391693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398373305797577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399289101362228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400204926729202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403868108987808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406615495681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407531291246414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40936291217804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408447116613388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40478390455246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405699700117111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401120722293854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402952283620834</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.396541684865952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392193675041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401759386062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40393340587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408716231584549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400020152330399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400889754295349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393063277006149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380019158124924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385236769914627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389150023460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390889257192612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395672082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401324540376663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396976500749588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400454938411713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390454441308975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387410819530487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383497565984726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382193148136139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381758332252502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371757835149765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357844084501266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366540193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360887736082077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362626940011978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369148999452591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379149526357651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3861064016819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394367665052414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404368191957474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392628461122513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391758888959885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395237267017365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385671585798264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39480248093605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388280421495438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398373305797577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399289101362228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400204926729202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403868108987808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406615525484085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407531321048737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409362882375717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408447116613388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40478390455246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405699700117111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401120722293854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402952283620834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402036488056183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393794327974319</t>
+    <t xml:space="preserve">0.402036517858505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393794298171997</t>
   </si>
   <si>
     <t xml:space="preserve">0.39104688167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391962707042694</t>
+    <t xml:space="preserve">0.391962677240372</t>
   </si>
   <si>
     <t xml:space="preserve">0.390131086111069</t>
@@ -3257,22 +3260,22 @@
     <t xml:space="preserve">0.394710093736649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3956258893013</t>
+    <t xml:space="preserve">0.395625919103622</t>
   </si>
   <si>
     <t xml:space="preserve">0.397457480430603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392878502607346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388299465179443</t>
+    <t xml:space="preserve">0.392878472805023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388299494981766</t>
   </si>
   <si>
     <t xml:space="preserve">0.384636282920837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389215290546417</t>
+    <t xml:space="preserve">0.38921532034874</t>
   </si>
   <si>
     <t xml:space="preserve">0.386467903852463</t>
@@ -3299,13 +3302,13 @@
     <t xml:space="preserve">0.380973100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375478267669678</t>
+    <t xml:space="preserve">0.375478297472</t>
   </si>
   <si>
     <t xml:space="preserve">0.373646676540375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371815055608749</t>
+    <t xml:space="preserve">0.371815085411072</t>
   </si>
   <si>
     <t xml:space="preserve">0.369067668914795</t>
@@ -3314,7 +3317,7 @@
     <t xml:space="preserve">0.369983494281769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376394093036652</t>
+    <t xml:space="preserve">0.376394122838974</t>
   </si>
   <si>
     <t xml:space="preserve">0.374562501907349</t>
@@ -3323,7 +3326,7 @@
     <t xml:space="preserve">0.37089928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378225684165955</t>
+    <t xml:space="preserve">0.378225654363632</t>
   </si>
   <si>
     <t xml:space="preserve">0.385552108287811</t>
@@ -3341,10 +3344,10 @@
     <t xml:space="preserve">0.420352518558502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421268343925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425847321748734</t>
+    <t xml:space="preserve">0.421268314123154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425847351551056</t>
   </si>
   <si>
     <t xml:space="preserve">0.416689306497574</t>
@@ -3374,7 +3377,7 @@
     <t xml:space="preserve">0.415773510932922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410278707742691</t>
+    <t xml:space="preserve">0.410278737545013</t>
   </si>
   <si>
     <t xml:space="preserve">0.422184109687805</t>
@@ -3392,19 +3395,19 @@
     <t xml:space="preserve">0.456068724393845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445994943380356</t>
+    <t xml:space="preserve">0.445994913578033</t>
   </si>
   <si>
     <t xml:space="preserve">0.494532406330109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48720595240593</t>
+    <t xml:space="preserve">0.487206012010574</t>
   </si>
   <si>
     <t xml:space="preserve">0.492700755596161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481711208820343</t>
+    <t xml:space="preserve">0.481711179018021</t>
   </si>
   <si>
     <t xml:space="preserve">0.489037543535233</t>
@@ -3413,16 +3416,16 @@
     <t xml:space="preserve">0.496363997459412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485374301671982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483542799949646</t>
+    <t xml:space="preserve">0.485374361276627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483542770147324</t>
   </si>
   <si>
     <t xml:space="preserve">0.454237133264542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463395118713379</t>
+    <t xml:space="preserve">0.463395148515701</t>
   </si>
   <si>
     <t xml:space="preserve">0.476216346025467</t>
@@ -3780,6 +3783,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.465000003576279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46000000834465</t>
   </si>
 </sst>
 </file>
@@ -53770,7 +53776,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1910" t="s">
-        <v>1026</v>
+        <v>1075</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53796,7 +53802,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1911" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53848,7 +53854,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1913" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53874,7 +53880,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1914" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53900,7 +53906,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1915" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53926,7 +53932,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1916" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53952,7 +53958,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1917" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53978,7 +53984,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1918" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54004,7 +54010,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1919" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54030,7 +54036,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1920" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54056,7 +54062,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1921" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54082,7 +54088,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1922" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54108,7 +54114,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1923" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54134,7 +54140,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1924" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54160,7 +54166,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1925" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54186,7 +54192,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1926" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54212,7 +54218,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1927" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54264,7 +54270,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1929" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54290,7 +54296,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1930" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54316,7 +54322,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1931" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54342,7 +54348,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1932" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54368,7 +54374,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1933" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54394,7 +54400,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1934" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54420,7 +54426,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1935" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54446,7 +54452,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1936" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54472,7 +54478,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1937" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54498,7 +54504,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1938" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54524,7 +54530,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1939" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54550,7 +54556,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1940" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54576,7 +54582,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1941" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54602,7 +54608,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1942" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54628,7 +54634,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1943" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54654,7 +54660,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1944" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54680,7 +54686,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1945" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54706,7 +54712,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1946" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54732,7 +54738,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1947" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54758,7 +54764,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1948" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54784,7 +54790,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1949" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54940,7 +54946,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1955" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55096,7 +55102,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1961" t="s">
-        <v>1026</v>
+        <v>1075</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55174,7 +55180,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1964" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55200,7 +55206,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1965" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55226,7 +55232,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1966" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55252,7 +55258,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1967" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55278,7 +55284,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1968" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55304,7 +55310,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1969" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55330,7 +55336,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1970" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55356,7 +55362,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -55382,7 +55388,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1972" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55408,7 +55414,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1973" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55434,7 +55440,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1974" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55460,7 +55466,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1975" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55486,7 +55492,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1976" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55512,7 +55518,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1977" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55538,7 +55544,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1978" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55564,7 +55570,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1979" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55590,7 +55596,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1980" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55616,7 +55622,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1981" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55642,7 +55648,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1982" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55668,7 +55674,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1983" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55694,7 +55700,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1984" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55720,7 +55726,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1985" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55746,7 +55752,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1986" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55772,7 +55778,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1987" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55798,7 +55804,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1988" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55824,7 +55830,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1989" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55850,7 +55856,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G1990" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55876,7 +55882,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1991" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55902,7 +55908,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1992" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55928,7 +55934,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1993" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55954,7 +55960,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1994" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55980,7 +55986,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1995" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56006,7 +56012,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1996" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56032,7 +56038,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1997" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56058,7 +56064,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1998" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56084,7 +56090,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1999" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56110,7 +56116,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2000" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56136,7 +56142,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2001" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56162,7 +56168,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2002" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56188,7 +56194,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2003" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56214,7 +56220,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2004" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56240,7 +56246,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2005" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56266,7 +56272,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2006" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56292,7 +56298,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2007" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56318,7 +56324,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2008" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56344,7 +56350,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2009" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56370,7 +56376,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2010" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56396,7 +56402,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2011" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56422,7 +56428,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2012" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56448,7 +56454,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56474,7 +56480,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2014" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56500,7 +56506,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2015" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56526,7 +56532,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2016" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56552,7 +56558,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56604,7 +56610,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56630,7 +56636,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2020" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56656,7 +56662,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2021" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56682,7 +56688,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2022" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56708,7 +56714,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2023" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56734,7 +56740,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2024" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56760,7 +56766,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G2025" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56786,7 +56792,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2026" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56812,7 +56818,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2027" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56838,7 +56844,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2028" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56864,7 +56870,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G2029" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56890,7 +56896,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2030" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56916,7 +56922,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2031" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56942,7 +56948,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2032" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56968,7 +56974,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2033" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56994,7 +57000,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2034" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57020,7 +57026,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2035" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57046,7 +57052,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2036" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57072,7 +57078,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2037" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57098,7 +57104,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2038" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57124,7 +57130,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2039" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57150,7 +57156,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2040" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57176,7 +57182,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57202,7 +57208,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2042" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57228,7 +57234,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2043" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57280,7 +57286,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2045" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57488,7 +57494,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2053" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57514,7 +57520,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2054" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57722,7 +57728,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2062" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57774,7 +57780,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2064" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57800,7 +57806,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2065" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57826,7 +57832,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2066" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57852,7 +57858,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2067" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57904,7 +57910,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2069" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58190,7 +58196,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2080" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58242,7 +58248,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2082" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58268,7 +58274,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G2083" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -58294,7 +58300,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2084" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58320,7 +58326,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2085" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58346,7 +58352,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2086" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58372,7 +58378,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2087" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -58398,7 +58404,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2088" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58554,7 +58560,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2094" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58580,7 +58586,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2095" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58606,7 +58612,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2096" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58632,7 +58638,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2097" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58658,7 +58664,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2098" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58788,7 +58794,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2103" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58814,7 +58820,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2104" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58840,7 +58846,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2105" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58866,7 +58872,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2106" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58892,7 +58898,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2107" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59178,7 +59184,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2118" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59204,7 +59210,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2119" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59230,7 +59236,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G2120" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59256,7 +59262,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2121" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59282,7 +59288,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2122" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59308,7 +59314,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G2123" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59334,7 +59340,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2124" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59360,7 +59366,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2125" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59386,7 +59392,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2126" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59412,7 +59418,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2127" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59438,7 +59444,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2128" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59464,7 +59470,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2129" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59490,7 +59496,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2130" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59516,7 +59522,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2131" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59542,7 +59548,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2132" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59568,7 +59574,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2133" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59594,7 +59600,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2134" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59620,7 +59626,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2135" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59646,7 +59652,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2136" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59672,7 +59678,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2137" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59698,7 +59704,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2138" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59724,7 +59730,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2139" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59750,7 +59756,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2140" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59776,7 +59782,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2141" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59802,7 +59808,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2142" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59828,7 +59834,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2143" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59854,7 +59860,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2144" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59880,7 +59886,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2145" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59906,7 +59912,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2146" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59932,7 +59938,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2147" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59958,7 +59964,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2148" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59984,7 +59990,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2149" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60010,7 +60016,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2150" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60036,7 +60042,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G2151" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60062,7 +60068,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2152" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60088,7 +60094,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2153" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60114,7 +60120,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2154" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60140,7 +60146,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2155" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60166,7 +60172,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60192,7 +60198,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60218,7 +60224,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2158" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60244,7 +60250,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2159" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60270,7 +60276,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2160" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60296,7 +60302,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2161" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60322,7 +60328,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2162" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60348,7 +60354,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2163" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60374,7 +60380,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2164" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60400,7 +60406,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2165" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60426,7 +60432,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2166" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60452,7 +60458,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2167" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60478,7 +60484,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2168" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60504,7 +60510,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2169" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60530,7 +60536,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2170" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60556,7 +60562,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2171" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60582,7 +60588,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2172" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60608,7 +60614,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2173" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60634,7 +60640,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2174" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60660,7 +60666,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2175" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60686,7 +60692,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2176" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60712,7 +60718,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2177" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60738,7 +60744,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2178" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60764,7 +60770,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2179" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60790,7 +60796,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2180" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60816,7 +60822,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2181" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60842,7 +60848,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2182" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60868,7 +60874,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2183" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60894,7 +60900,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2184" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60920,7 +60926,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2185" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60946,7 +60952,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2186" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60972,7 +60978,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2187" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60998,7 +61004,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2188" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61024,7 +61030,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2189" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61050,7 +61056,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61076,7 +61082,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2191" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61102,7 +61108,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2192" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61128,7 +61134,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2193" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61154,7 +61160,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2194" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61180,7 +61186,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2195" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61206,7 +61212,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2196" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61232,7 +61238,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2197" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61258,7 +61264,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2198" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61284,7 +61290,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2199" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61310,7 +61316,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2200" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61336,7 +61342,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2201" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61362,7 +61368,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2202" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61388,7 +61394,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2203" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61414,7 +61420,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2204" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61440,7 +61446,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2205" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61466,7 +61472,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2206" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61492,7 +61498,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2207" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61518,7 +61524,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2208" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61544,7 +61550,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2209" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61570,7 +61576,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2210" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61596,7 +61602,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2211" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61622,7 +61628,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2212" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61648,7 +61654,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2213" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61674,7 +61680,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2214" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61700,7 +61706,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61726,7 +61732,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2216" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61752,7 +61758,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2217" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61778,7 +61784,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2218" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61804,7 +61810,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2219" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61830,7 +61836,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2220" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61856,7 +61862,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2221" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61882,7 +61888,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2222" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61908,7 +61914,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2223" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61934,7 +61940,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2224" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61960,7 +61966,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2225" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61986,7 +61992,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2226" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62012,7 +62018,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2227" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62038,7 +62044,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2228" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62064,7 +62070,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2229" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62090,7 +62096,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2230" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62116,7 +62122,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2231" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62142,7 +62148,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2232" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62168,7 +62174,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2233" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62194,7 +62200,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2234" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62220,7 +62226,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2235" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62246,7 +62252,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2236" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62272,7 +62278,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2237" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62298,7 +62304,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2238" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62324,7 +62330,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2239" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62350,7 +62356,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2240" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62376,7 +62382,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2241" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62402,7 +62408,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2242" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62428,7 +62434,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2243" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62454,7 +62460,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2244" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62480,7 +62486,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2245" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62506,7 +62512,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2246" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62532,7 +62538,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62558,7 +62564,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62584,7 +62590,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2249" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62610,7 +62616,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2250" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62636,7 +62642,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2251" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62662,7 +62668,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2252" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62688,7 +62694,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G2253" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62714,7 +62720,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2254" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62740,7 +62746,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2255" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62766,7 +62772,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2256" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62792,7 +62798,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2257" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62818,7 +62824,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2258" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62844,7 +62850,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2259" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62870,7 +62876,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2260" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62896,7 +62902,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2261" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62922,7 +62928,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2262" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62948,7 +62954,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2263" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62974,7 +62980,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2264" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63000,7 +63006,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2265" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63026,7 +63032,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2266" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63052,7 +63058,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2267" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63078,7 +63084,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2268" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63104,7 +63110,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2269" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63130,7 +63136,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63156,7 +63162,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2271" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63182,7 +63188,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2272" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63208,7 +63214,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2273" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63234,7 +63240,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2274" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63260,7 +63266,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2275" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63286,7 +63292,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2276" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63312,7 +63318,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2277" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63338,7 +63344,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2278" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63364,7 +63370,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2279" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63390,7 +63396,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2280" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63416,7 +63422,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2281" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63442,7 +63448,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2282" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63468,7 +63474,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2283" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63494,7 +63500,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2284" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63520,7 +63526,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2285" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63546,7 +63552,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2286" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63572,7 +63578,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2287" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63598,7 +63604,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2288" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63624,7 +63630,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2289" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63650,7 +63656,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2290" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63676,7 +63682,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63702,7 +63708,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2292" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63728,7 +63734,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2293" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63754,7 +63760,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2294" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63780,7 +63786,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2295" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63806,7 +63812,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2296" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63832,7 +63838,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2297" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63858,7 +63864,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2298" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63884,7 +63890,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2299" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63910,7 +63916,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2300" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63936,7 +63942,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2301" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63962,7 +63968,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2302" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63988,7 +63994,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2303" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64014,7 +64020,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2304" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64040,7 +64046,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2305" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64066,7 +64072,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2306" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64092,7 +64098,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2307" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64118,7 +64124,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2308" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64144,7 +64150,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2309" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64170,7 +64176,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2310" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64196,7 +64202,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2311" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64222,7 +64228,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2312" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64248,7 +64254,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2313" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64274,7 +64280,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2314" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64300,7 +64306,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2315" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64326,7 +64332,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2316" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64352,7 +64358,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2317" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64378,7 +64384,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2318" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64404,7 +64410,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2319" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64430,7 +64436,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2320" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64456,7 +64462,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2321" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64482,7 +64488,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2322" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64508,7 +64514,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2323" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64534,7 +64540,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2324" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64560,7 +64566,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2325" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64586,7 +64592,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64612,7 +64618,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2327" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64638,7 +64644,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2328" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64664,7 +64670,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2329" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64690,7 +64696,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2330" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64716,7 +64722,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2331" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64742,7 +64748,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2332" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64768,7 +64774,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2333" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64794,7 +64800,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2334" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64820,7 +64826,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2335" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64846,7 +64852,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2336" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64872,7 +64878,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2337" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64898,7 +64904,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2338" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64924,7 +64930,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2339" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64950,7 +64956,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2340" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64976,7 +64982,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2341" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65002,7 +65008,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2342" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65028,7 +65034,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2343" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65054,7 +65060,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2344" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65080,7 +65086,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2345" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65106,7 +65112,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2346" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65132,7 +65138,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2347" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65158,7 +65164,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2348" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65184,7 +65190,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2349" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65210,7 +65216,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2350" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65236,7 +65242,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2351" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65262,7 +65268,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2352" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65288,7 +65294,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2353" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65314,7 +65320,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2354" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65340,7 +65346,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2355" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65366,7 +65372,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2356" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65392,7 +65398,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2357" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65418,7 +65424,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2358" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65444,7 +65450,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G2359" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65470,7 +65476,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G2360" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65496,7 +65502,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G2361" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65522,7 +65528,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2362" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65548,7 +65554,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2363" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65574,7 +65580,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2364" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65600,7 +65606,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2365" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65626,7 +65632,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G2366" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65652,7 +65658,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2367" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65678,7 +65684,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2368" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65704,7 +65710,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2369" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65730,7 +65736,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2370" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65756,7 +65762,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2371" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65782,7 +65788,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2372" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65808,7 +65814,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2373" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65834,7 +65840,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2374" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65860,7 +65866,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2375" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65886,7 +65892,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2376" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65912,7 +65918,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G2377" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65938,7 +65944,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2378" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65964,7 +65970,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2379" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65990,7 +65996,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2380" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66016,7 +66022,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2381" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66042,7 +66048,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2382" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66068,7 +66074,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2383" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66094,7 +66100,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2384" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66120,7 +66126,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2385" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66146,7 +66152,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2386" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66172,7 +66178,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2387" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66198,7 +66204,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2388" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66224,7 +66230,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2389" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66250,7 +66256,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2390" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66276,7 +66282,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66302,7 +66308,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2392" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66328,7 +66334,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2393" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66354,7 +66360,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2394" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66380,7 +66386,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2395" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66406,7 +66412,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2396" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66432,7 +66438,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2397" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66458,7 +66464,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2398" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66484,7 +66490,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2399" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66510,7 +66516,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G2400" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66536,7 +66542,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G2401" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66562,7 +66568,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2402" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66588,7 +66594,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2403" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66614,7 +66620,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2404" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66640,7 +66646,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2405" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66666,7 +66672,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2406" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66692,7 +66698,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2407" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66718,7 +66724,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2408" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66744,7 +66750,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2409" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66770,7 +66776,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G2410" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66796,7 +66802,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G2411" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66822,7 +66828,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2412" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66848,7 +66854,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2413" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66874,7 +66880,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2414" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66900,7 +66906,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2415" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66926,7 +66932,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2416" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66952,7 +66958,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2417" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66978,7 +66984,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2418" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67004,7 +67010,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2419" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67030,7 +67036,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2420" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67056,7 +67062,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2421" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67082,7 +67088,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2422" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67108,7 +67114,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2423" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67134,7 +67140,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2424" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67160,7 +67166,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2425" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67186,7 +67192,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2426" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67212,7 +67218,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2427" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67238,7 +67244,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2428" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67264,7 +67270,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2429" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67290,7 +67296,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2430" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67316,7 +67322,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2431" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67342,7 +67348,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2432" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67368,7 +67374,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2433" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67394,7 +67400,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2434" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67420,7 +67426,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2435" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67446,7 +67452,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2436" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67472,7 +67478,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G2437" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67498,7 +67504,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2438" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67524,7 +67530,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2439" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67550,7 +67556,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2440" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67576,7 +67582,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2441" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67602,7 +67608,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2442" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67628,7 +67634,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2443" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67654,7 +67660,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2444" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67680,7 +67686,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2445" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67706,7 +67712,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2446" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67732,7 +67738,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2447" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67758,7 +67764,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2448" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67784,7 +67790,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2449" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67810,7 +67816,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2450" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67836,7 +67842,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2451" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67862,7 +67868,7 @@
         <v>0.5</v>
       </c>
       <c r="G2452" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67888,7 +67894,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G2453" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67914,7 +67920,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2454" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67940,7 +67946,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G2455" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67966,7 +67972,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2456" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67992,7 +67998,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2457" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68018,7 +68024,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2458" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68044,7 +68050,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2459" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68070,7 +68076,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G2460" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68096,7 +68102,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2461" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68122,7 +68128,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G2462" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68148,7 +68154,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2463" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68174,7 +68180,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G2464" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68200,7 +68206,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G2465" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68226,7 +68232,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2466" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68252,7 +68258,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2467" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68278,7 +68284,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2468" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68304,7 +68310,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2469" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68330,7 +68336,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2470" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68356,7 +68362,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2471" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68382,7 +68388,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2472" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68408,7 +68414,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G2473" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68434,7 +68440,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2474" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68460,7 +68466,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2475" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68486,7 +68492,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G2476" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68512,7 +68518,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2477" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68538,7 +68544,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2478" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68564,7 +68570,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2479" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68590,7 +68596,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2480" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68616,7 +68622,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2481" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68642,7 +68648,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2482" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68668,7 +68674,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2483" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68694,7 +68700,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2484" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68720,7 +68726,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G2485" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68746,7 +68752,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G2486" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68754,7 +68760,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6493287037</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>188524</v>
@@ -68772,9 +68778,35 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2487" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6495486111</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>232742</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>0.46900001168251</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>0.46399998664856</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326352328062057</t>
+    <t xml:space="preserve">0.326352387666702</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844841241837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323679089546204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980736494064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313056290149689</t>
+    <t xml:space="preserve">0.326844781637192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323679029941559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980706691742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313056230545044</t>
   </si>
   <si>
     <t xml:space="preserve">0.304966032505035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29976013302803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309538751840591</t>
+    <t xml:space="preserve">0.299760162830353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309538811445236</t>
   </si>
   <si>
     <t xml:space="preserve">0.302503794431686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287097275257111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274363934993744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278655260801315</t>
+    <t xml:space="preserve">0.287097245454788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274363905191422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278655230998993</t>
   </si>
   <si>
     <t xml:space="preserve">0.265288770198822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260645747184753</t>
+    <t xml:space="preserve">0.260645687580109</t>
   </si>
   <si>
     <t xml:space="preserve">0.270846426486969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269087672233582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272956937551498</t>
+    <t xml:space="preserve">0.269087702035904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272956907749176</t>
   </si>
   <si>
     <t xml:space="preserve">0.270142912864685</t>
@@ -98,100 +98,100 @@
     <t xml:space="preserve">0.265921950340271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290825694799423</t>
+    <t xml:space="preserve">0.290825754404068</t>
   </si>
   <si>
     <t xml:space="preserve">0.288433879613876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294061869382858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276404052972794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273167967796326</t>
+    <t xml:space="preserve">0.294061839580536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276404023170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273167997598648</t>
   </si>
   <si>
     <t xml:space="preserve">0.262545168399811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260293990373611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246927529573441</t>
+    <t xml:space="preserve">0.260293960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246927544474602</t>
   </si>
   <si>
     <t xml:space="preserve">0.24622406065464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239751860499382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240103632211685</t>
+    <t xml:space="preserve">0.23975183069706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240103617310524</t>
   </si>
   <si>
     <t xml:space="preserve">0.271549940109253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276122689247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274645268917084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277881413698196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270987153053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281539618968964</t>
+    <t xml:space="preserve">0.276122659444809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274645298719406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277881473302841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270987182855606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281539589166641</t>
   </si>
   <si>
     <t xml:space="preserve">0.277177900075912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263319045305252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268032491207123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282102406024933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295468807220459</t>
+    <t xml:space="preserve">0.263318985700607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268032431602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28210237622261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295468837022781</t>
   </si>
   <si>
     <t xml:space="preserve">0.293358325958252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291740298271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288644880056381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504213094711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281469225883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277248233556747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278373837471008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287026852369308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297368288040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295820623636246</t>
+    <t xml:space="preserve">0.291740328073502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288644909858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504272699356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281469255685806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27724826335907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278373897075653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287026882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297368258237839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295820593833923</t>
   </si>
   <si>
     <t xml:space="preserve">0.307217240333557</t>
@@ -200,25 +200,25 @@
     <t xml:space="preserve">0.305669546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313759744167328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320442974567413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317417919635773</t>
+    <t xml:space="preserve">0.31375977396965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320442944765091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317417979240417</t>
   </si>
   <si>
     <t xml:space="preserve">0.316573739051819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306161969900131</t>
+    <t xml:space="preserve">0.306161940097809</t>
   </si>
   <si>
     <t xml:space="preserve">0.310945779085159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311438202857971</t>
+    <t xml:space="preserve">0.311438232660294</t>
   </si>
   <si>
     <t xml:space="preserve">0.301800280809402</t>
@@ -227,25 +227,25 @@
     <t xml:space="preserve">0.288011729717255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288082093000412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28055465221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281328558921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291881024837494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301378190517426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311649292707443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310242265462875</t>
+    <t xml:space="preserve">0.288082152605057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280554682016373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281328529119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291880995035172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301378220319748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311649262905121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310242295265198</t>
   </si>
   <si>
     <t xml:space="preserve">0.311508536338806</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">0.314533621072769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316644072532654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318684250116348</t>
+    <t xml:space="preserve">0.316644102334976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318684220314026</t>
   </si>
   <si>
     <t xml:space="preserve">0.330573350191116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330643683671951</t>
+    <t xml:space="preserve">0.330643653869629</t>
   </si>
   <si>
     <t xml:space="preserve">0.334161162376404</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">0.3335280418396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330432683229446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327126175165176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323538392782211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318543523550034</t>
+    <t xml:space="preserve">0.330432653427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327126234769821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323538362979889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318543583154678</t>
   </si>
   <si>
     <t xml:space="preserve">0.319247037172318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323116272687912</t>
+    <t xml:space="preserve">0.323116302490234</t>
   </si>
   <si>
     <t xml:space="preserve">0.321005791425705</t>
@@ -299,34 +299,34 @@
     <t xml:space="preserve">0.323749423027039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325015753507614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32107612490654</t>
+    <t xml:space="preserve">0.325015723705292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321076154708862</t>
   </si>
   <si>
     <t xml:space="preserve">0.326774507761002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331769287586212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344713658094406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34204038977623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338030427694321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352100402116776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354914367198944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351678282022476</t>
+    <t xml:space="preserve">0.331769317388535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344713628292084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342040359973907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338030397891998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352100372314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354914337396622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351678311824799</t>
   </si>
   <si>
     <t xml:space="preserve">0.350341618061066</t>
@@ -338,34 +338,34 @@
     <t xml:space="preserve">0.343165963888168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341196179389954</t>
+    <t xml:space="preserve">0.341196149587631</t>
   </si>
   <si>
     <t xml:space="preserve">0.340211272239685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337045520544052</t>
+    <t xml:space="preserve">0.33704549074173</t>
   </si>
   <si>
     <t xml:space="preserve">0.323537796735764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309325844049454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3121537566185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308890849351883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31193619966507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325277984142303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322232633829117</t>
+    <t xml:space="preserve">0.309325873851776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312153726816177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308890789747238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311936229467392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325278013944626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322232574224472</t>
   </si>
   <si>
     <t xml:space="preserve">0.318607091903687</t>
@@ -374,28 +374,28 @@
     <t xml:space="preserve">0.324190348386765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307223111391068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299102038145065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299464553594589</t>
+    <t xml:space="preserve">0.307223081588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299102067947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299464583396912</t>
   </si>
   <si>
     <t xml:space="preserve">0.3130963742733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320854932069778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318027049303055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319042146205902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318317085504532</t>
+    <t xml:space="preserve">0.320854902267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318027019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319042176008224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318317115306854</t>
   </si>
   <si>
     <t xml:space="preserve">0.309543430805206</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">0.311791211366653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310558557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311066061258316</t>
+    <t xml:space="preserve">0.310558527708054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311066120862961</t>
   </si>
   <si>
     <t xml:space="preserve">0.322087585926056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31976729631424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318172067403793</t>
+    <t xml:space="preserve">0.319767266511917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318172037601471</t>
   </si>
   <si>
     <t xml:space="preserve">0.309978455305099</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">0.305627882480621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30178490281105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300914734601974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298739492893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298014402389526</t>
+    <t xml:space="preserve">0.301784932613373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300914764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298739433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298014372587204</t>
   </si>
   <si>
     <t xml:space="preserve">0.291488528251648</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">0.302727490663528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303815186023712</t>
+    <t xml:space="preserve">0.303815126419067</t>
   </si>
   <si>
     <t xml:space="preserve">0.30062472820282</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">0.297434329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299682110548019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301929861307144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301712363958359</t>
+    <t xml:space="preserve">0.299682080745697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301929891109467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301712393760681</t>
   </si>
   <si>
     <t xml:space="preserve">0.302364975214005</t>
@@ -479,16 +479,16 @@
     <t xml:space="preserve">0.300117135047913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302219927310944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297144263982773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295621573925018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293663769960403</t>
+    <t xml:space="preserve">0.302219957113266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297144293785095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295621603727341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293663799762726</t>
   </si>
   <si>
     <t xml:space="preserve">0.297289282083511</t>
@@ -497,94 +497,94 @@
     <t xml:space="preserve">0.291706055402756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292358666658401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290038347244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287500470876694</t>
+    <t xml:space="preserve">0.292358607053757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290038287639618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287500500679016</t>
   </si>
   <si>
     <t xml:space="preserve">0.292648673057556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287645488977432</t>
+    <t xml:space="preserve">0.287645518779755</t>
   </si>
   <si>
     <t xml:space="preserve">0.295041501522064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291561007499695</t>
+    <t xml:space="preserve">0.291561037302017</t>
   </si>
   <si>
     <t xml:space="preserve">0.294533938169479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289313197135925</t>
+    <t xml:space="preserve">0.28931325674057</t>
   </si>
   <si>
     <t xml:space="preserve">0.287935554981232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283004909753799</t>
+    <t xml:space="preserve">0.283004939556122</t>
   </si>
   <si>
     <t xml:space="preserve">0.287427991628647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282859861850739</t>
+    <t xml:space="preserve">0.282859891653061</t>
   </si>
   <si>
     <t xml:space="preserve">0.275826454162598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279161900281906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269735664129257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273288607597351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279524475336075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282062321901321</t>
+    <t xml:space="preserve">0.279161870479584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26973569393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273288637399673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279524445533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282062292098999</t>
   </si>
   <si>
     <t xml:space="preserve">0.283802509307861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282134741544724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287137925624847</t>
+    <t xml:space="preserve">0.282134801149368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28713795542717</t>
   </si>
   <si>
     <t xml:space="preserve">0.292866200208664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301422327756882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295839101076126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296564191579819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300262153148651</t>
+    <t xml:space="preserve">0.301422357559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295839071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296564221382141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300262182950974</t>
   </si>
   <si>
     <t xml:space="preserve">0.297071784734726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292938768863678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298812001943588</t>
+    <t xml:space="preserve">0.292938739061356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298811972141266</t>
   </si>
   <si>
     <t xml:space="preserve">0.296056628227234</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">0.31019601225853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306425511837006</t>
+    <t xml:space="preserve">0.306425482034683</t>
   </si>
   <si>
     <t xml:space="preserve">0.302509963512421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306062936782837</t>
+    <t xml:space="preserve">0.306062966585159</t>
   </si>
   <si>
     <t xml:space="preserve">0.307078093290329</t>
@@ -611,28 +611,28 @@
     <t xml:space="preserve">0.294098854064941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283077389001846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287863045930862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289603233337402</t>
+    <t xml:space="preserve">0.283077418804169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287863075733185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289603263139725</t>
   </si>
   <si>
     <t xml:space="preserve">0.285615235567093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2839475274086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288805693387985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293736279010773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290835976600647</t>
+    <t xml:space="preserve">0.283947557210922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28880563378334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293736308813095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290835946798325</t>
   </si>
   <si>
     <t xml:space="preserve">0.283512473106384</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">0.280684590339661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279016852378845</t>
+    <t xml:space="preserve">0.279016882181168</t>
   </si>
   <si>
     <t xml:space="preserve">0.273796230554581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291416019201279</t>
+    <t xml:space="preserve">0.291415989398956</t>
   </si>
   <si>
     <t xml:space="preserve">0.295114010572433</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.290545910596848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288588106632233</t>
+    <t xml:space="preserve">0.288588136434555</t>
   </si>
   <si>
     <t xml:space="preserve">0.292213648557663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292141079902649</t>
+    <t xml:space="preserve">0.292141109704971</t>
   </si>
   <si>
     <t xml:space="preserve">0.294388860464096</t>
@@ -677,28 +677,28 @@
     <t xml:space="preserve">0.296491682529449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30359759926796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309615880250931</t>
+    <t xml:space="preserve">0.303597629070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309615910053253</t>
   </si>
   <si>
     <t xml:space="preserve">0.307440608739853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319187223911285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331513851881027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331368803977966</t>
+    <t xml:space="preserve">0.319187194108963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331513792276382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331368774175644</t>
   </si>
   <si>
     <t xml:space="preserve">0.345000594854355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349786221981049</t>
+    <t xml:space="preserve">0.349786192178726</t>
   </si>
   <si>
     <t xml:space="preserve">0.358342349529266</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">0.34964120388031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352396547794342</t>
+    <t xml:space="preserve">0.352396607398987</t>
   </si>
   <si>
     <t xml:space="preserve">0.355296969413757</t>
@@ -719,16 +719,16 @@
     <t xml:space="preserve">0.359429985284805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352686643600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3468858897686</t>
+    <t xml:space="preserve">0.352686613798141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346885830163956</t>
   </si>
   <si>
     <t xml:space="preserve">0.343187898397446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346160769462585</t>
+    <t xml:space="preserve">0.346160739660263</t>
   </si>
   <si>
     <t xml:space="preserve">0.346595793962479</t>
@@ -737,34 +737,34 @@
     <t xml:space="preserve">0.346450805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344347983598709</t>
+    <t xml:space="preserve">0.344348013401031</t>
   </si>
   <si>
     <t xml:space="preserve">0.350221306085587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350946366786957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388288795948029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397715032100677</t>
+    <t xml:space="preserve">0.350946396589279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388288825750351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397715061903</t>
   </si>
   <si>
     <t xml:space="preserve">0.379950255155563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382125526666641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37487456202507</t>
+    <t xml:space="preserve">0.382125496864319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374874532222748</t>
   </si>
   <si>
     <t xml:space="preserve">0.373424351215363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377412378787994</t>
+    <t xml:space="preserve">0.377412348985672</t>
   </si>
   <si>
     <t xml:space="preserve">0.373061835765839</t>
@@ -773,139 +773,139 @@
     <t xml:space="preserve">0.369798868894577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383575707674026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369436323642731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369073748588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35819736123085</t>
+    <t xml:space="preserve">0.383575648069382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369436353445053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369073778390884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358197331428528</t>
   </si>
   <si>
     <t xml:space="preserve">0.358052343130112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377049803733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412579506635666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382488042116165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400615483522415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394452154636383</t>
+    <t xml:space="preserve">0.377049833536148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412579536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382488012313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40061542391777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394452184438705</t>
   </si>
   <si>
     <t xml:space="preserve">0.385750979185104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39372706413269</t>
+    <t xml:space="preserve">0.393726974725723</t>
   </si>
   <si>
     <t xml:space="preserve">0.390464097261429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384300798177719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391551792621613</t>
+    <t xml:space="preserve">0.384300768375397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39155176281929</t>
   </si>
   <si>
     <t xml:space="preserve">0.387563735246658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390826612710953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395177245140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393364518880844</t>
+    <t xml:space="preserve">0.39082658290863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395177215337753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393364548683167</t>
   </si>
   <si>
     <t xml:space="preserve">0.397352516651154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398802667856216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3955397605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396627396345139</t>
+    <t xml:space="preserve">0.398802727460861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395539730787277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396627426147461</t>
   </si>
   <si>
     <t xml:space="preserve">0.39844012260437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395902305841446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393001973628998</t>
+    <t xml:space="preserve">0.395902335643768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393001943826675</t>
   </si>
   <si>
     <t xml:space="preserve">0.398077636957169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401703119277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392276853322983</t>
+    <t xml:space="preserve">0.401703089475632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39227682352066</t>
   </si>
   <si>
     <t xml:space="preserve">0.387201130390167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386476099491119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382850557565689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394089609384537</t>
+    <t xml:space="preserve">0.386476010084152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382850587368011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394089579582214</t>
   </si>
   <si>
     <t xml:space="preserve">0.389376431703568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381762951612473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381037831306458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386838614940643</t>
+    <t xml:space="preserve">0.381762981414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38103786110878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386838644742966</t>
   </si>
   <si>
     <t xml:space="preserve">0.38865140080452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385025858879089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391189217567444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392639398574829</t>
+    <t xml:space="preserve">0.385025888681412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391189187765121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392639338970184</t>
   </si>
   <si>
     <t xml:space="preserve">0.425631314516068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419105380773544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445208847522736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435057550668716</t>
+    <t xml:space="preserve">0.419105350971222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445208877325058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435057520866394</t>
   </si>
   <si>
     <t xml:space="preserve">0.442308455705643</t>
@@ -920,37 +920,37 @@
     <t xml:space="preserve">0.408370792865753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406878978013992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402776688337326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399047285318375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400539040565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395317792892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396809607744217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39606374502182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393080204725266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388604938983917</t>
+    <t xml:space="preserve">0.406879007816315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402776658535004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399047255516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400538980960846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395317852497101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396809637546539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396063715219498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393080174922943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388604879379272</t>
   </si>
   <si>
     <t xml:space="preserve">0.387859016656876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379654288291931</t>
+    <t xml:space="preserve">0.379654318094254</t>
   </si>
   <si>
     <t xml:space="preserve">0.38114607334137</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">0.383010774850845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387486159801483</t>
+    <t xml:space="preserve">0.387486070394516</t>
   </si>
   <si>
     <t xml:space="preserve">0.384875476360321</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">0.383756697177887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386740207672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390096664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394944906234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403522610664368</t>
+    <t xml:space="preserve">0.386740148067474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390096634626389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394944936037064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403522551059723</t>
   </si>
   <si>
     <t xml:space="preserve">0.410235494375229</t>
@@ -986,151 +986,151 @@
     <t xml:space="preserve">0.407251954078674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407624930143356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408743679523468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406506061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40091198682785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394199013710022</t>
+    <t xml:space="preserve">0.407624959945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408743768930435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406506091356277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400912016630173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394199043512344</t>
   </si>
   <si>
     <t xml:space="preserve">0.398674339056015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390842527151108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392334282398224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388231992721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387113183736801</t>
+    <t xml:space="preserve">0.39084255695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392334342002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388231962919235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387113153934479</t>
   </si>
   <si>
     <t xml:space="preserve">0.391588419675827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389350801706314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385621428489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380773156881332</t>
+    <t xml:space="preserve">0.389350831508636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38562136888504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380773186683655</t>
   </si>
   <si>
     <t xml:space="preserve">0.385248422622681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383383750915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397928476333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410981416702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41433784365654</t>
+    <t xml:space="preserve">0.383383691310883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397928446531296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409489661455154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410981386899948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414337813854218</t>
   </si>
   <si>
     <t xml:space="preserve">0.415083765983582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41657555103302</t>
+    <t xml:space="preserve">0.416575491428375</t>
   </si>
   <si>
     <t xml:space="preserve">0.415829628705978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424034357070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439324975013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866109371185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428882539272308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420304924249649</t>
+    <t xml:space="preserve">0.4240343272686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439324915409088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866139173508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428882628679276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420304864645004</t>
   </si>
   <si>
     <t xml:space="preserve">0.421796709299088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428509622812271</t>
+    <t xml:space="preserve">0.428509652614594</t>
   </si>
   <si>
     <t xml:space="preserve">0.454988479614258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445291996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4445461332798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440443724393845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449767261743546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459463715553284</t>
+    <t xml:space="preserve">0.445291966199875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444546163082123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440443754196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449767291545868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459463775157928</t>
   </si>
   <si>
     <t xml:space="preserve">0.460955500602722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469533234834671</t>
+    <t xml:space="preserve">0.469533145427704</t>
   </si>
   <si>
     <t xml:space="preserve">0.466549664735794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474008440971375</t>
+    <t xml:space="preserve">0.474008500576019</t>
   </si>
   <si>
     <t xml:space="preserve">0.474754363298416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480348497629166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485942602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482586145401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485569655895233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509437918663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511302649974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521745026111603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512794435024261</t>
+    <t xml:space="preserve">0.480348467826843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485942542552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482586085796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485569685697556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50943797826767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511302709579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521744966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512794375419617</t>
   </si>
   <si>
     <t xml:space="preserve">0.5195072889328</t>
@@ -1139,22 +1139,22 @@
     <t xml:space="preserve">0.511675536632538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506081342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501233220100403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502351999282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495266109704971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491536736488342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477737843990326</t>
+    <t xml:space="preserve">0.506081461906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501233160495758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502352058887482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495266139507294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491536617279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477737873792648</t>
   </si>
   <si>
     <t xml:space="preserve">0.478483766317368</t>
@@ -1163,34 +1163,34 @@
     <t xml:space="preserve">0.481094390153885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492282658815384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499741464853287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493774324655533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495639085769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507946074008942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500114381313324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493028551340103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508692026138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503470897674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508319079875946</t>
+    <t xml:space="preserve">0.492282599210739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49974137544632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493774354457855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495638996362686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507946133613586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500114321708679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493028521537781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508691966533661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503470838069916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508319139480591</t>
   </si>
   <si>
     <t xml:space="preserve">0.507200300693512</t>
@@ -1199,61 +1199,61 @@
     <t xml:space="preserve">0.510183811187744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513167381286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500860273838043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503097951412201</t>
+    <t xml:space="preserve">0.513167440891266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500860333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503097891807556</t>
   </si>
   <si>
     <t xml:space="preserve">0.502724945545197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501606225967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498249709606171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510929584503174</t>
+    <t xml:space="preserve">0.501606166362762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498249679803848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510929644107819</t>
   </si>
   <si>
     <t xml:space="preserve">0.531068563461304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557920277118683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554936766624451</t>
+    <t xml:space="preserve">0.557920336723328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55493688583374</t>
   </si>
   <si>
     <t xml:space="preserve">0.559412062168121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565379202365875</t>
+    <t xml:space="preserve">0.565379083156586</t>
   </si>
   <si>
     <t xml:space="preserve">0.593722641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574329733848572</t>
+    <t xml:space="preserve">0.574329674243927</t>
   </si>
   <si>
     <t xml:space="preserve">0.576567351818085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577313303947449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583280265331268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59148496389389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585518002510071</t>
+    <t xml:space="preserve">0.577313184738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583280324935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591485023498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585517942905426</t>
   </si>
   <si>
     <t xml:space="preserve">0.575075566768646</t>
@@ -1262,34 +1262,34 @@
     <t xml:space="preserve">0.612369775772095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556428551673889</t>
+    <t xml:space="preserve">0.5564284324646</t>
   </si>
   <si>
     <t xml:space="preserve">0.551953256130219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548223853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534797847270966</t>
+    <t xml:space="preserve">0.548223793506622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534797966480255</t>
   </si>
   <si>
     <t xml:space="preserve">0.521372020244598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505708575248718</t>
+    <t xml:space="preserve">0.505708396434784</t>
   </si>
   <si>
     <t xml:space="preserve">0.528084993362427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545240342617035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522863686084747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517642557621002</t>
+    <t xml:space="preserve">0.54524028301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522863745689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517642676830292</t>
   </si>
   <si>
     <t xml:space="preserve">0.532560288906097</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">0.531814396381378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523609638214111</t>
+    <t xml:space="preserve">0.523609697818756</t>
   </si>
   <si>
     <t xml:space="preserve">0.516150832176208</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">0.519134342670441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498995631933212</t>
+    <t xml:space="preserve">0.498995572328568</t>
   </si>
   <si>
     <t xml:space="preserve">0.463193148374557</t>
@@ -1319,34 +1319,34 @@
     <t xml:space="preserve">0.469906151294708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476619064807892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477364987134933</t>
+    <t xml:space="preserve">0.476619124412537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477365016937256</t>
   </si>
   <si>
     <t xml:space="preserve">0.494520276784897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490044951438904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478856682777405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478110790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468414396047592</t>
+    <t xml:space="preserve">0.490044981241226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478856712579727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47811084985733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468414425849915</t>
   </si>
   <si>
     <t xml:space="preserve">0.481840282678604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484077930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475127369165421</t>
+    <t xml:space="preserve">0.484077900648117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475127309560776</t>
   </si>
   <si>
     <t xml:space="preserve">0.473635524511337</t>
@@ -1355,52 +1355,52 @@
     <t xml:space="preserve">0.474381387233734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484823822975159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487061411142349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48333203792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50421679019928</t>
+    <t xml:space="preserve">0.484823763370514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487061440944672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483332008123398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504216730594635</t>
   </si>
   <si>
     <t xml:space="preserve">0.504962623119354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496757864952087</t>
+    <t xml:space="preserve">0.49675789475441</t>
   </si>
   <si>
     <t xml:space="preserve">0.497503817081451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486315578222275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500487387180328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454242616891861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465430825948715</t>
+    <t xml:space="preserve">0.486315608024597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500487327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454242557287216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465430855751038</t>
   </si>
   <si>
     <t xml:space="preserve">0.452004939317703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457226037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458717823028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462447285652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455734312534332</t>
+    <t xml:space="preserve">0.457226127386093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458717912435532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462447255849838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455734342336655</t>
   </si>
   <si>
     <t xml:space="preserve">0.457972019910812</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">0.485727906227112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484185874462128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47493389248848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469536960124969</t>
+    <t xml:space="preserve">0.48418590426445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474933922290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469536930322647</t>
   </si>
   <si>
     <t xml:space="preserve">0.464910924434662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461055904626846</t>
+    <t xml:space="preserve">0.461055934429169</t>
   </si>
   <si>
     <t xml:space="preserve">0.463368952274323</t>
@@ -1430,64 +1430,64 @@
     <t xml:space="preserve">0.459513992071152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457971960306168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45874297618866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447949022054672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451033025979996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454887956380844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.446407049894333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441781044006348</t>
+    <t xml:space="preserve">0.45797199010849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458743005990982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447948962450027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451032996177673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454888045787811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44640702009201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441781103610992</t>
   </si>
   <si>
     <t xml:space="preserve">0.443323045969009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494208782911301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474162876605988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481101900339127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48958283662796</t>
+    <t xml:space="preserve">0.494208872318268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47416290640831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481101930141449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489582777023315</t>
   </si>
   <si>
     <t xml:space="preserve">0.476475894451141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464139968156815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461826920509338</t>
+    <t xml:space="preserve">0.464139938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461827039718628</t>
   </si>
   <si>
     <t xml:space="preserve">0.456429988145828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454117059707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466452956199646</t>
+    <t xml:space="preserve">0.454117000102997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466452926397324</t>
   </si>
   <si>
     <t xml:space="preserve">0.467223972082138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439468055963516</t>
+    <t xml:space="preserve">0.439468085765839</t>
   </si>
   <si>
     <t xml:space="preserve">0.442552089691162</t>
@@ -1496,16 +1496,16 @@
     <t xml:space="preserve">0.45257505774498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453346014022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441010117530823</t>
+    <t xml:space="preserve">0.453345984220505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441010057926178</t>
   </si>
   <si>
     <t xml:space="preserve">0.437926054000854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433300137519836</t>
+    <t xml:space="preserve">0.433300107717514</t>
   </si>
   <si>
     <t xml:space="preserve">0.430987119674683</t>
@@ -1514,61 +1514,61 @@
     <t xml:space="preserve">0.431758135557175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435613065958023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444865047931671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460285007953644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45180407166481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470307916402817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471849888563156</t>
+    <t xml:space="preserve">0.435613095760345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444865107536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284978151321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451804041862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470307976007462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471849977970123</t>
   </si>
   <si>
     <t xml:space="preserve">0.465681970119476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45720100402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46259793639183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455659002065659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450262069702148</t>
+    <t xml:space="preserve">0.457200974225998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462598025798798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455659061670303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450262039899826</t>
   </si>
   <si>
     <t xml:space="preserve">0.449491053819656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43715512752533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440239071846008</t>
+    <t xml:space="preserve">0.437155067920685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440239012241364</t>
   </si>
   <si>
     <t xml:space="preserve">0.42636114358902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427903115749359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407086193561554</t>
+    <t xml:space="preserve">0.427903175354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407086223363876</t>
   </si>
   <si>
     <t xml:space="preserve">0.406315207481384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410170197486877</t>
+    <t xml:space="preserve">0.410170257091522</t>
   </si>
   <si>
     <t xml:space="preserve">0.404002219438553</t>
@@ -1577,22 +1577,22 @@
     <t xml:space="preserve">0.407857179641724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410941183567047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400147289037704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396292269229889</t>
+    <t xml:space="preserve">0.41094121336937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40014722943306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396292239427567</t>
   </si>
   <si>
     <t xml:space="preserve">0.390895307064056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390124261379242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381643295288086</t>
+    <t xml:space="preserve">0.390124291181564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381643354892731</t>
   </si>
   <si>
     <t xml:space="preserve">0.38318532705307</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">0.387811332941055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388582289218903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394750326871872</t>
+    <t xml:space="preserve">0.388582319021225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39475029706955</t>
   </si>
   <si>
     <t xml:space="preserve">0.397063255310059</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">0.389353305101395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387040287256241</t>
+    <t xml:space="preserve">0.387040317058563</t>
   </si>
   <si>
     <t xml:space="preserve">0.385498285293579</t>
@@ -1625,16 +1625,16 @@
     <t xml:space="preserve">0.36622342467308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351188957691193</t>
+    <t xml:space="preserve">0.351189017295837</t>
   </si>
   <si>
     <t xml:space="preserve">0.345406502485275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348875969648361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366994440555573</t>
+    <t xml:space="preserve">0.348875939846039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366994351148605</t>
   </si>
   <si>
     <t xml:space="preserve">0.372391372919083</t>
@@ -1658,85 +1658,85 @@
     <t xml:space="preserve">0.365837901830673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371620327234268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368536382913589</t>
+    <t xml:space="preserve">0.371620386838913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368536353111267</t>
   </si>
   <si>
     <t xml:space="preserve">0.368921905755997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378944844007492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383570820093155</t>
+    <t xml:space="preserve">0.37894481420517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383570849895477</t>
   </si>
   <si>
     <t xml:space="preserve">0.377017349004745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382414311170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399376302957535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416338235139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424048125743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424819141626358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417109221220016</t>
+    <t xml:space="preserve">0.3824143409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399376273155212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416338205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424048155546188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424819111824036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417109161615372</t>
   </si>
   <si>
     <t xml:space="preserve">0.422506123781204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421735107898712</t>
+    <t xml:space="preserve">0.421735167503357</t>
   </si>
   <si>
     <t xml:space="preserve">0.420964121818542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408628165721893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400918245315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4047731757164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405544221401215</t>
+    <t xml:space="preserve">0.408628195524216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400918185710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404773235321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405544281005859</t>
   </si>
   <si>
     <t xml:space="preserve">0.411712169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412483245134354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423277169466019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425590127706528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419422209262848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430216163396835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427132159471512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414025187492371</t>
+    <t xml:space="preserve">0.412483215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423277139663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42559015750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419422179460526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430216133594513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427132129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414025217294693</t>
   </si>
   <si>
     <t xml:space="preserve">0.41479617357254</t>
@@ -1745,34 +1745,34 @@
     <t xml:space="preserve">0.413254201412201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40939924120903</t>
+    <t xml:space="preserve">0.409399211406708</t>
   </si>
   <si>
     <t xml:space="preserve">0.395521283149719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393208265304565</t>
+    <t xml:space="preserve">0.393208235502243</t>
   </si>
   <si>
     <t xml:space="preserve">0.392437279224396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391666322946548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393979251384735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398605316877365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403231233358383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411275893449783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410471081733704</t>
+    <t xml:space="preserve">0.391666263341904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393979281187057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398605287075043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403231263160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411275923252106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410471051931381</t>
   </si>
   <si>
     <t xml:space="preserve">0.409666240215302</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">0.415300130844116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412885665893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412080824375153</t>
+    <t xml:space="preserve">0.412885636091232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41208079457283</t>
   </si>
   <si>
     <t xml:space="preserve">0.399203240871429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401215344667435</t>
+    <t xml:space="preserve">0.401215404272079</t>
   </si>
   <si>
     <t xml:space="preserve">0.404032319784164</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">0.397996008396149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403227478265762</t>
+    <t xml:space="preserve">0.40322744846344</t>
   </si>
   <si>
     <t xml:space="preserve">0.398398399353027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400008082389832</t>
+    <t xml:space="preserve">0.400008112192154</t>
   </si>
   <si>
     <t xml:space="preserve">0.40242263674736</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">0.400410532951355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395983904600143</t>
+    <t xml:space="preserve">0.395983874797821</t>
   </si>
   <si>
     <t xml:space="preserve">0.39960566163063</t>
@@ -1823,52 +1823,52 @@
     <t xml:space="preserve">0.418519526720047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417714715003967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416909903287888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404837191104889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401617825031281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40725165605545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408056557178497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405642032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397593557834625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391154795885086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406446844339371</t>
+    <t xml:space="preserve">0.417714655399323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416909873485565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404837220907211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401617795228958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407251715660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40805658698082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405642002820969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397593587636948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391154766082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406446874141693</t>
   </si>
   <si>
     <t xml:space="preserve">0.42656797170639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433811604976654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424153476953506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43220192193985</t>
+    <t xml:space="preserve">0.433811575174332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424153447151184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432201951742172</t>
   </si>
   <si>
     <t xml:space="preserve">0.425763130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428177684545517</t>
+    <t xml:space="preserve">0.428177714347839</t>
   </si>
   <si>
     <t xml:space="preserve">0.433006763458252</t>
@@ -1877,79 +1877,79 @@
     <t xml:space="preserve">0.429787337779999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420934051275253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428982496261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437031000852585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434616506099701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430592268705368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4426648914814</t>
+    <t xml:space="preserve">0.420934081077576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428982526063919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43703094124794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434616476297379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430592238903046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442664921283722</t>
   </si>
   <si>
     <t xml:space="preserve">0.458761781454086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466810256242752</t>
+    <t xml:space="preserve">0.46681022644043</t>
   </si>
   <si>
     <t xml:space="preserve">0.473248988389969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476468414068222</t>
+    <t xml:space="preserve">0.476468354463577</t>
   </si>
   <si>
     <t xml:space="preserve">0.478882998228073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475663542747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481297463178635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478078097105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474858671426773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471639424562454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472444176673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486126512289047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480492621660233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494979828596115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511881589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513491272926331</t>
+    <t xml:space="preserve">0.475663602352142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48129740357399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478078067302704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474858731031418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471639335155487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472444206476212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486126571893692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48049259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494979798793793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511881530284882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513491332530975</t>
   </si>
   <si>
     <t xml:space="preserve">0.520734906196594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535222113132477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53441721200943</t>
+    <t xml:space="preserve">0.535222172737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534417271614075</t>
   </si>
   <si>
     <t xml:space="preserve">0.523149430751801</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">0.515100955963135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516710698604584</t>
+    <t xml:space="preserve">0.516710638999939</t>
   </si>
   <si>
     <t xml:space="preserve">0.522344589233398</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">0.556148052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555343270301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551318943500519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557757794857025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.571440100669861</t>
+    <t xml:space="preserve">0.555343210697174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551319062709808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55775773525238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.571440160274506</t>
   </si>
   <si>
     <t xml:space="preserve">0.56178206205368</t>
@@ -1994,25 +1994,25 @@
     <t xml:space="preserve">0.59236615896225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596390306949615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599609732627869</t>
+    <t xml:space="preserve">0.59639036655426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599609792232513</t>
   </si>
   <si>
     <t xml:space="preserve">0.611682415008545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606853306293488</t>
+    <t xml:space="preserve">0.606853365898132</t>
   </si>
   <si>
     <t xml:space="preserve">0.602024257183075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614901840686798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600414574146271</t>
+    <t xml:space="preserve">0.614901781082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600414514541626</t>
   </si>
   <si>
     <t xml:space="preserve">0.608462989330292</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">0.590756475925446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595585465431213</t>
+    <t xml:space="preserve">0.595585525035858</t>
   </si>
   <si>
     <t xml:space="preserve">0.609267890453339</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">0.60604852437973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593171000480652</t>
+    <t xml:space="preserve">0.593170940876007</t>
   </si>
   <si>
     <t xml:space="preserve">0.598804950714111</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">0.610072731971741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598000049591064</t>
+    <t xml:space="preserve">0.59799998998642</t>
   </si>
   <si>
     <t xml:space="preserve">0.630193829536438</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">0.631803512573242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64629065990448</t>
+    <t xml:space="preserve">0.646290719509125</t>
   </si>
   <si>
     <t xml:space="preserve">0.655948877334595</t>
@@ -2072,19 +2072,19 @@
     <t xml:space="preserve">0.65997314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689752280712128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684118449687958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661582827568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58834183216095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581098258495331</t>
+    <t xml:space="preserve">0.689752399921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684118509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661582887172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588341951370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581098318099976</t>
   </si>
   <si>
     <t xml:space="preserve">0.572245001792908</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">0.540856063365936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543270528316498</t>
+    <t xml:space="preserve">0.543270587921143</t>
   </si>
   <si>
     <t xml:space="preserve">0.518320322036743</t>
@@ -2102,31 +2102,31 @@
     <t xml:space="preserve">0.526368796825409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490955591201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439445495605469</t>
+    <t xml:space="preserve">0.490955621004105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439445465803146</t>
   </si>
   <si>
     <t xml:space="preserve">0.398800820112228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381496667861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32314532995224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348095595836639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303829103708267</t>
+    <t xml:space="preserve">0.381496638059616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323145359754562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348095625638962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303829073905945</t>
   </si>
   <si>
     <t xml:space="preserve">0.282500684261322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288939446210861</t>
+    <t xml:space="preserve">0.288939476013184</t>
   </si>
   <si>
     <t xml:space="preserve">0.29135400056839</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">0.304633945226669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308255732059479</t>
+    <t xml:space="preserve">0.308255761861801</t>
   </si>
   <si>
     <t xml:space="preserve">0.343668937683105</t>
@@ -2147,16 +2147,16 @@
     <t xml:space="preserve">0.37224093079567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355741590261459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373850613832474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391959637403488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379082143306732</t>
+    <t xml:space="preserve">0.355741620063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373850643634796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391959607601166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37908211350441</t>
   </si>
   <si>
     <t xml:space="preserve">0.375057876110077</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">0.384716004133224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386325746774673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374253064393997</t>
+    <t xml:space="preserve">0.386325716972351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374253034591675</t>
   </si>
   <si>
     <t xml:space="preserve">0.362180352210999</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">0.353327065706253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349302798509598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344473749399185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323547780513763</t>
+    <t xml:space="preserve">0.34930282831192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34447380900383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323547810316086</t>
   </si>
   <si>
     <t xml:space="preserve">0.338034987449646</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">0.339644700288773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341254383325577</t>
+    <t xml:space="preserve">0.341254413127899</t>
   </si>
   <si>
     <t xml:space="preserve">0.346083462238312</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">0.348497986793518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342864125967026</t>
+    <t xml:space="preserve">0.342864096164703</t>
   </si>
   <si>
     <t xml:space="preserve">0.345278590917587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336425334215164</t>
+    <t xml:space="preserve">0.336425304412842</t>
   </si>
   <si>
     <t xml:space="preserve">0.324352651834488</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">0.329986572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326767146587372</t>
+    <t xml:space="preserve">0.326767206192017</t>
   </si>
   <si>
     <t xml:space="preserve">0.321938127279282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331596255302429</t>
+    <t xml:space="preserve">0.331596225500107</t>
   </si>
   <si>
     <t xml:space="preserve">0.340449541807175</t>
@@ -2237,52 +2237,52 @@
     <t xml:space="preserve">0.347693175077438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352522253990173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354936748743057</t>
+    <t xml:space="preserve">0.352522224187851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35493677854538</t>
   </si>
   <si>
     <t xml:space="preserve">0.369423985481262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382301479578018</t>
+    <t xml:space="preserve">0.382301509380341</t>
   </si>
   <si>
     <t xml:space="preserve">0.379886984825134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371838539838791</t>
+    <t xml:space="preserve">0.371838510036469</t>
   </si>
   <si>
     <t xml:space="preserve">0.354131907224655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330791413784027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356546431779861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357351303100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350107729434967</t>
+    <t xml:space="preserve">0.330791443586349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356546461582184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357351273298264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350107669830322</t>
   </si>
   <si>
     <t xml:space="preserve">0.346888303756714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342059224843979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337230145931244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328376859426498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335620492696762</t>
+    <t xml:space="preserve">0.342059254646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337230175733566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328376829624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33562046289444</t>
   </si>
   <si>
     <t xml:space="preserve">0.370228826999664</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">0.363790035247803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420129269361496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424958288669586</t>
+    <t xml:space="preserve">0.420129209756851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424958318471909</t>
   </si>
   <si>
     <t xml:space="preserve">0.437835842370987</t>
@@ -2306,43 +2306,43 @@
     <t xml:space="preserve">0.444274574518204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445884317159653</t>
+    <t xml:space="preserve">0.44588428735733</t>
   </si>
   <si>
     <t xml:space="preserve">0.482907176017761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560172319412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527978479862213</t>
+    <t xml:space="preserve">0.560172259807587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527978539466858</t>
   </si>
   <si>
     <t xml:space="preserve">0.521539747714996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529588162899017</t>
+    <t xml:space="preserve">0.529588222503662</t>
   </si>
   <si>
     <t xml:space="preserve">0.519930064678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507052481174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500613689422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494175046682358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502223491668701</t>
+    <t xml:space="preserve">0.507052540779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500613749027252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494175016880035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502223432064056</t>
   </si>
   <si>
     <t xml:space="preserve">0.537636637687683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52475917339325</t>
+    <t xml:space="preserve">0.524759113788605</t>
   </si>
   <si>
     <t xml:space="preserve">0.510271906852722</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">0.499004065990448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492565244436264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487736254930496</t>
+    <t xml:space="preserve">0.492565333843231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487736225128174</t>
   </si>
   <si>
     <t xml:space="preserve">0.484516859054565</t>
@@ -2369,13 +2369,13 @@
     <t xml:space="preserve">0.449103683233261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436226159334183</t>
+    <t xml:space="preserve">0.436226189136505</t>
   </si>
   <si>
     <t xml:space="preserve">0.393569320440292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378277271986008</t>
+    <t xml:space="preserve">0.37827730178833</t>
   </si>
   <si>
     <t xml:space="preserve">0.375862747430801</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">0.376667588949203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421738892793655</t>
+    <t xml:space="preserve">0.421738922595978</t>
   </si>
   <si>
     <t xml:space="preserve">0.423348635435104</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">0.461981207132339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465200543403625</t>
+    <t xml:space="preserve">0.465200573205948</t>
   </si>
   <si>
     <t xml:space="preserve">0.45232304930687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455542385578156</t>
+    <t xml:space="preserve">0.4555424451828</t>
   </si>
   <si>
     <t xml:space="preserve">0.450713366270065</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">0.457152098417282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453932821750641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479687839746475</t>
+    <t xml:space="preserve">0.453932762145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479687809944153</t>
   </si>
   <si>
     <t xml:space="preserve">0.495784670114517</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">0.576269209384918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575464427471161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569830477237701</t>
+    <t xml:space="preserve">0.575464367866516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569830417633057</t>
   </si>
   <si>
     <t xml:space="preserve">0.549709379673004</t>
@@ -2459,16 +2459,16 @@
     <t xml:space="preserve">0.56741589307785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545685112476349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558562576770782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5440753698349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531197905540466</t>
+    <t xml:space="preserve">0.545685052871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558562636375427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544075429439545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531197845935822</t>
   </si>
   <si>
     <t xml:space="preserve">0.559367418289185</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">0.581903100013733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579488635063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544880211353302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552123844623566</t>
+    <t xml:space="preserve">0.579488575458527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544880270957947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552123785018921</t>
   </si>
   <si>
     <t xml:space="preserve">0.548099637031555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548904418945312</t>
+    <t xml:space="preserve">0.548904478549957</t>
   </si>
   <si>
     <t xml:space="preserve">0.553733587265015</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">0.582058250904083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581226766109467</t>
+    <t xml:space="preserve">0.581226706504822</t>
   </si>
   <si>
     <t xml:space="preserve">0.573743164539337</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">0.567091107368469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574574649333954</t>
+    <t xml:space="preserve">0.574574589729309</t>
   </si>
   <si>
     <t xml:space="preserve">0.57291167974472</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">0.561270534992218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557944416999817</t>
+    <t xml:space="preserve">0.557944476604462</t>
   </si>
   <si>
     <t xml:space="preserve">0.558776021003723</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">0.542977273464203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530504584312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531336009502411</t>
+    <t xml:space="preserve">0.530504524707794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531336069107056</t>
   </si>
   <si>
     <t xml:space="preserve">0.532167553901672</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">0.505559206008911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508885264396667</t>
+    <t xml:space="preserve">0.508885204792023</t>
   </si>
   <si>
     <t xml:space="preserve">0.502233147621155</t>
@@ -2564,19 +2564,19 @@
     <t xml:space="preserve">0.498907119035721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493918001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494749575853348</t>
+    <t xml:space="preserve">0.493918031454086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494749546051025</t>
   </si>
   <si>
     <t xml:space="preserve">0.500570118427277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48393988609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465646594762802</t>
+    <t xml:space="preserve">0.483939915895462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465646624565125</t>
   </si>
   <si>
     <t xml:space="preserve">0.466478109359741</t>
@@ -2591,16 +2591,16 @@
     <t xml:space="preserve">0.473961770534515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473130285739899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486434429883957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489760518074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503064632415771</t>
+    <t xml:space="preserve">0.473130255937576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486434400081635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489760458469391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503064692020416</t>
   </si>
   <si>
     <t xml:space="preserve">0.50472766160965</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">0.495581090450287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484771400690079</t>
+    <t xml:space="preserve">0.484771370887756</t>
   </si>
   <si>
     <t xml:space="preserve">0.482276886701584</t>
@@ -2630,28 +2630,28 @@
     <t xml:space="preserve">0.497244030237198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487265944480896</t>
+    <t xml:space="preserve">0.487265914678574</t>
   </si>
   <si>
     <t xml:space="preserve">0.493086487054825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483108341693878</t>
+    <t xml:space="preserve">0.483108371496201</t>
   </si>
   <si>
     <t xml:space="preserve">0.478119283914566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475624799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47645628452301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529673039913177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523852467536926</t>
+    <t xml:space="preserve">0.475624829530716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476456314325333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529672980308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523852407932281</t>
   </si>
   <si>
     <t xml:space="preserve">0.528010010719299</t>
@@ -2663,34 +2663,34 @@
     <t xml:space="preserve">0.527178525924683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547966241836548</t>
+    <t xml:space="preserve">0.547966301441193</t>
   </si>
   <si>
     <t xml:space="preserve">0.528841495513916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52551543712616</t>
+    <t xml:space="preserve">0.525515496730804</t>
   </si>
   <si>
     <t xml:space="preserve">0.526347041130066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554618418216705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588710367679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575406193733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577069222927094</t>
+    <t xml:space="preserve">0.554618299007416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588710427284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575406134128571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577069163322449</t>
   </si>
   <si>
     <t xml:space="preserve">0.570417106151581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583721399307251</t>
+    <t xml:space="preserve">0.583721339702606</t>
   </si>
   <si>
     <t xml:space="preserve">0.585384368896484</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">0.57790070772171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58039528131485</t>
+    <t xml:space="preserve">0.580395221710205</t>
   </si>
   <si>
     <t xml:space="preserve">0.550460815429688</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">0.567922651767731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566259503364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557112991809845</t>
+    <t xml:space="preserve">0.566259562969208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5571129322052</t>
   </si>
   <si>
     <t xml:space="preserve">0.56459653377533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549629271030426</t>
+    <t xml:space="preserve">0.549629330635071</t>
   </si>
   <si>
     <t xml:space="preserve">0.539651155471802</t>
@@ -2741,58 +2741,58 @@
     <t xml:space="preserve">0.509716749191284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507222175598145</t>
+    <t xml:space="preserve">0.507222235202789</t>
   </si>
   <si>
     <t xml:space="preserve">0.521357893943787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513874351978302</t>
+    <t xml:space="preserve">0.513874292373657</t>
   </si>
   <si>
     <t xml:space="preserve">0.522189497947693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513042747974396</t>
+    <t xml:space="preserve">0.513042807579041</t>
   </si>
   <si>
     <t xml:space="preserve">0.52052640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523020923137665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519694924354553</t>
+    <t xml:space="preserve">0.52302098274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519694864749908</t>
   </si>
   <si>
     <t xml:space="preserve">0.508053779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488097429275513</t>
+    <t xml:space="preserve">0.488097459077835</t>
   </si>
   <si>
     <t xml:space="preserve">0.488928943872452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492255032062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496412515640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490591913461685</t>
+    <t xml:space="preserve">0.492255002260208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496412575244904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490591943264008</t>
   </si>
   <si>
     <t xml:space="preserve">0.485602915287018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480613857507706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474793195724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4540054500103</t>
+    <t xml:space="preserve">0.480613887310028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47479322552681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454005479812622</t>
   </si>
   <si>
     <t xml:space="preserve">0.478950768709183</t>
@@ -2819,28 +2819,28 @@
     <t xml:space="preserve">0.42407101392746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411598384380341</t>
+    <t xml:space="preserve">0.411598354578018</t>
   </si>
   <si>
     <t xml:space="preserve">0.41118261218071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395799607038498</t>
+    <t xml:space="preserve">0.395799666643143</t>
   </si>
   <si>
     <t xml:space="preserve">0.377090603113174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365033686161041</t>
+    <t xml:space="preserve">0.365033715963364</t>
   </si>
   <si>
     <t xml:space="preserve">0.402035981416702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413677155971527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407440841197968</t>
+    <t xml:space="preserve">0.413677126169205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407440811395645</t>
   </si>
   <si>
     <t xml:space="preserve">0.412429869174957</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">0.431554615497589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429891616106033</t>
+    <t xml:space="preserve">0.429891645908356</t>
   </si>
   <si>
     <t xml:space="preserve">0.432386130094528</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">0.451510936021805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444027274847031</t>
+    <t xml:space="preserve">0.444027304649353</t>
   </si>
   <si>
     <t xml:space="preserve">0.436543703079224</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">0.443195819854736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448184818029404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.446521908044815</t>
+    <t xml:space="preserve">0.448184847831726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44652184844017</t>
   </si>
   <si>
     <t xml:space="preserve">0.440701276063919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434880673885345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424902558326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444858878850937</t>
+    <t xml:space="preserve">0.434880703687668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424902528524399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444858849048615</t>
   </si>
   <si>
     <t xml:space="preserve">0.447353363037109</t>
@@ -2894,28 +2894,28 @@
     <t xml:space="preserve">0.463152080774307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481445372104645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477287858724594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470635682344437</t>
+    <t xml:space="preserve">0.48144543170929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477287828922272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470635652542114</t>
   </si>
   <si>
     <t xml:space="preserve">0.437375247478485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429060101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421576529741287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40993532538414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430723130702972</t>
+    <t xml:space="preserve">0.429060071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421576499938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409935355186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430723160505295</t>
   </si>
   <si>
     <t xml:space="preserve">0.427397072315216</t>
@@ -2945,40 +2945,40 @@
     <t xml:space="preserve">0.406542211771011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403063744306564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414368689060211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393932908773422</t>
+    <t xml:space="preserve">0.403063774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414368718862534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3939328789711</t>
   </si>
   <si>
     <t xml:space="preserve">0.391324043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383932381868362</t>
+    <t xml:space="preserve">0.38393235206604</t>
   </si>
   <si>
     <t xml:space="preserve">0.388715237379074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382627964019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380888730287552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387845605611801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393498033285141</t>
+    <t xml:space="preserve">0.382627934217453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380888760089874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387845635414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393498063087463</t>
   </si>
   <si>
     <t xml:space="preserve">0.379584342241287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384367197751999</t>
+    <t xml:space="preserve">0.384367167949677</t>
   </si>
   <si>
     <t xml:space="preserve">0.378714740276337</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">0.372627437114716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37306222319603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378279894590378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370888233184814</t>
+    <t xml:space="preserve">0.373062252998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3782799243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370888203382492</t>
   </si>
   <si>
     <t xml:space="preserve">0.361322522163391</t>
@@ -3005,10 +3005,10 @@
     <t xml:space="preserve">0.366105407476425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371323049068451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375671088695526</t>
+    <t xml:space="preserve">0.371323019266129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375671118497849</t>
   </si>
   <si>
     <t xml:space="preserve">0.374366670846939</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">0.370018631219864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367844581604004</t>
+    <t xml:space="preserve">0.367844611406326</t>
   </si>
   <si>
     <t xml:space="preserve">0.366975009441376</t>
@@ -3038,19 +3038,19 @@
     <t xml:space="preserve">0.36958384513855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377845108509064</t>
+    <t xml:space="preserve">0.377845138311386</t>
   </si>
   <si>
     <t xml:space="preserve">0.374801486730576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375236243009567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372192651033401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36523574590683</t>
+    <t xml:space="preserve">0.37523627281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372192621231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365235775709152</t>
   </si>
   <si>
     <t xml:space="preserve">0.376540690660477</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">0.386976003646851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397411316633224</t>
+    <t xml:space="preserve">0.397411286830902</t>
   </si>
   <si>
     <t xml:space="preserve">0.402628988027573</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">0.396106898784637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399150550365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403498560190201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396541714668274</t>
+    <t xml:space="preserve">0.399150520563126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403498589992523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396541684865952</t>
   </si>
   <si>
     <t xml:space="preserve">0.392193675041199</t>
@@ -3101,19 +3101,19 @@
     <t xml:space="preserve">0.401759386062622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403933376073837</t>
+    <t xml:space="preserve">0.40393340587616</t>
   </si>
   <si>
     <t xml:space="preserve">0.408716231584549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400020152330399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400889724493027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393063247203827</t>
+    <t xml:space="preserve">0.400020122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400889754295349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393063277006149</t>
   </si>
   <si>
     <t xml:space="preserve">0.380019158124924</t>
@@ -3125,22 +3125,22 @@
     <t xml:space="preserve">0.389150023460388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390889227390289</t>
+    <t xml:space="preserve">0.390889257192612</t>
   </si>
   <si>
     <t xml:space="preserve">0.395672082901001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401324540376663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39697653055191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400454938411713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390454411506653</t>
+    <t xml:space="preserve">0.401324570178986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396976500749588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400454968214035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390454441308975</t>
   </si>
   <si>
     <t xml:space="preserve">0.387410819530487</t>
@@ -3149,13 +3149,13 @@
     <t xml:space="preserve">0.383497565984726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382193177938461</t>
+    <t xml:space="preserve">0.382193148136139</t>
   </si>
   <si>
     <t xml:space="preserve">0.381758362054825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371757864952087</t>
+    <t xml:space="preserve">0.371757835149765</t>
   </si>
   <si>
     <t xml:space="preserve">0.357844114303589</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">0.379149526357651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3861064016819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394367694854736</t>
+    <t xml:space="preserve">0.386106371879578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394367665052414</t>
   </si>
   <si>
     <t xml:space="preserve">0.404368221759796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392628461122513</t>
+    <t xml:space="preserve">0.392628490924835</t>
   </si>
   <si>
     <t xml:space="preserve">0.391758888959885</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">0.385671585798264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394802510738373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388280391693115</t>
+    <t xml:space="preserve">0.39480248093605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388280421495438</t>
   </si>
   <si>
     <t xml:space="preserve">0.398373305797577</t>
@@ -3239,9 +3239,6 @@
     <t xml:space="preserve">0.402952283620834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396541684865952</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.402036517858505</t>
   </si>
   <si>
@@ -3786,6 +3783,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.46000000834465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456999987363815</t>
   </si>
 </sst>
 </file>
@@ -53776,7 +53776,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1910" t="s">
-        <v>1075</v>
+        <v>1026</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53802,7 +53802,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1911" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53854,7 +53854,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1913" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53880,7 +53880,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1914" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53906,7 +53906,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1915" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53932,7 +53932,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1916" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53958,7 +53958,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1917" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53984,7 +53984,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1918" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54010,7 +54010,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1919" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54036,7 +54036,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1920" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54062,7 +54062,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1921" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54088,7 +54088,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1922" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54114,7 +54114,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1923" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54140,7 +54140,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1924" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54166,7 +54166,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1925" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54192,7 +54192,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1926" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54218,7 +54218,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1927" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54270,7 +54270,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1929" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54296,7 +54296,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1930" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54322,7 +54322,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1931" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54348,7 +54348,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1932" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54374,7 +54374,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1933" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54400,7 +54400,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1934" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54426,7 +54426,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1935" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54452,7 +54452,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1936" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54478,7 +54478,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1937" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54504,7 +54504,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1938" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54530,7 +54530,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1939" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54556,7 +54556,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1940" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54582,7 +54582,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1941" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54608,7 +54608,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1942" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54634,7 +54634,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1943" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54660,7 +54660,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1944" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54686,7 +54686,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1945" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54712,7 +54712,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1946" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54738,7 +54738,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1947" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54764,7 +54764,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1948" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54790,7 +54790,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1949" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54946,7 +54946,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1955" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55102,7 +55102,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1961" t="s">
-        <v>1075</v>
+        <v>1026</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55180,7 +55180,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1964" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55206,7 +55206,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1965" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55232,7 +55232,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1966" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55258,7 +55258,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1967" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55284,7 +55284,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1968" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55310,7 +55310,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1969" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55336,7 +55336,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1970" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55362,7 +55362,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -55388,7 +55388,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1972" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55414,7 +55414,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1973" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55440,7 +55440,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1974" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55466,7 +55466,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1975" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55492,7 +55492,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1976" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55518,7 +55518,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1977" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55544,7 +55544,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1978" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55570,7 +55570,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1979" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55596,7 +55596,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1980" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55622,7 +55622,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1981" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55648,7 +55648,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1982" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55674,7 +55674,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1983" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55700,7 +55700,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1984" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55726,7 +55726,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1985" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55752,7 +55752,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1986" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55778,7 +55778,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1987" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55804,7 +55804,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1988" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55830,7 +55830,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1989" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55856,7 +55856,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G1990" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55882,7 +55882,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1991" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55908,7 +55908,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1992" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55934,7 +55934,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1993" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55960,7 +55960,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1994" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55986,7 +55986,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1995" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56012,7 +56012,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1996" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56038,7 +56038,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1997" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56064,7 +56064,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1998" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56090,7 +56090,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1999" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56116,7 +56116,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2000" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56142,7 +56142,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2001" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56168,7 +56168,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2002" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56194,7 +56194,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2003" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56220,7 +56220,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2004" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56246,7 +56246,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2005" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56272,7 +56272,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2006" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56298,7 +56298,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2007" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56324,7 +56324,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2008" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56350,7 +56350,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2009" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56376,7 +56376,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2010" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56402,7 +56402,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2011" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56428,7 +56428,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2012" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56454,7 +56454,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56480,7 +56480,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2014" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56506,7 +56506,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2015" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56532,7 +56532,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2016" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56558,7 +56558,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56610,7 +56610,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56636,7 +56636,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2020" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56662,7 +56662,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2021" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56688,7 +56688,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2022" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56714,7 +56714,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2023" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56740,7 +56740,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2024" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56766,7 +56766,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G2025" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56792,7 +56792,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2026" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56818,7 +56818,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2027" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56844,7 +56844,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2028" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56870,7 +56870,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G2029" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56896,7 +56896,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2030" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56922,7 +56922,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2031" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56948,7 +56948,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2032" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56974,7 +56974,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2033" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57000,7 +57000,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2034" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57026,7 +57026,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2035" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57052,7 +57052,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2036" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57078,7 +57078,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2037" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57104,7 +57104,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2038" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57130,7 +57130,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2039" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57156,7 +57156,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2040" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57182,7 +57182,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57208,7 +57208,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2042" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57234,7 +57234,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2043" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57286,7 +57286,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2045" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57494,7 +57494,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2053" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57520,7 +57520,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2054" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57728,7 +57728,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2062" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57780,7 +57780,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2064" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57806,7 +57806,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2065" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57832,7 +57832,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2066" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57858,7 +57858,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2067" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57910,7 +57910,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2069" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58196,7 +58196,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2080" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58248,7 +58248,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2082" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58274,7 +58274,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G2083" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -58300,7 +58300,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2084" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58326,7 +58326,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2085" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58352,7 +58352,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2086" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58378,7 +58378,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2087" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -58404,7 +58404,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2088" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58560,7 +58560,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2094" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58586,7 +58586,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2095" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58612,7 +58612,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2096" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58638,7 +58638,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2097" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58664,7 +58664,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2098" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58794,7 +58794,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2103" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58820,7 +58820,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2104" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58846,7 +58846,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2105" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58872,7 +58872,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2106" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58898,7 +58898,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2107" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59184,7 +59184,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2118" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59210,7 +59210,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2119" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59236,7 +59236,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G2120" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59262,7 +59262,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2121" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59288,7 +59288,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2122" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59314,7 +59314,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G2123" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59340,7 +59340,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2124" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59366,7 +59366,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2125" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59392,7 +59392,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2126" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59418,7 +59418,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2127" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59444,7 +59444,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2128" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59470,7 +59470,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2129" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59496,7 +59496,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2130" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59522,7 +59522,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2131" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59548,7 +59548,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2132" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59574,7 +59574,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2133" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59600,7 +59600,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2134" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59626,7 +59626,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2135" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59652,7 +59652,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2136" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59678,7 +59678,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2137" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59704,7 +59704,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2138" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59730,7 +59730,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2139" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59756,7 +59756,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2140" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59782,7 +59782,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2141" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59808,7 +59808,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2142" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59834,7 +59834,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2143" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59860,7 +59860,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2144" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59886,7 +59886,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2145" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59912,7 +59912,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2146" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59938,7 +59938,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2147" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59964,7 +59964,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2148" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59990,7 +59990,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2149" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60016,7 +60016,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2150" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60042,7 +60042,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G2151" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60068,7 +60068,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2152" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60094,7 +60094,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2153" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60120,7 +60120,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2154" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60146,7 +60146,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2155" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60172,7 +60172,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60198,7 +60198,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60224,7 +60224,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2158" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60250,7 +60250,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2159" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60276,7 +60276,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2160" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60302,7 +60302,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2161" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60328,7 +60328,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2162" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60354,7 +60354,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2163" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60380,7 +60380,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2164" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60406,7 +60406,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2165" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60432,7 +60432,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2166" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60458,7 +60458,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2167" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60484,7 +60484,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2168" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60510,7 +60510,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2169" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60536,7 +60536,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2170" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60562,7 +60562,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2171" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60588,7 +60588,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2172" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60614,7 +60614,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2173" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60640,7 +60640,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2174" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60666,7 +60666,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2175" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60692,7 +60692,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2176" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60718,7 +60718,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2177" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60744,7 +60744,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2178" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60770,7 +60770,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2179" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60796,7 +60796,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2180" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60822,7 +60822,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2181" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60848,7 +60848,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2182" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60874,7 +60874,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2183" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60900,7 +60900,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2184" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60926,7 +60926,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2185" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60952,7 +60952,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2186" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60978,7 +60978,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2187" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61004,7 +61004,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2188" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61030,7 +61030,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2189" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61056,7 +61056,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61082,7 +61082,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2191" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61108,7 +61108,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2192" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61134,7 +61134,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2193" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61160,7 +61160,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2194" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61186,7 +61186,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2195" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61212,7 +61212,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2196" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61238,7 +61238,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2197" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61264,7 +61264,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2198" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61290,7 +61290,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2199" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61316,7 +61316,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2200" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61342,7 +61342,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2201" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61368,7 +61368,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2202" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61394,7 +61394,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2203" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61420,7 +61420,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2204" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61446,7 +61446,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2205" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61472,7 +61472,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2206" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61498,7 +61498,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2207" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61524,7 +61524,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2208" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61550,7 +61550,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2209" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61576,7 +61576,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2210" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61602,7 +61602,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2211" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61628,7 +61628,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2212" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61654,7 +61654,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2213" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61680,7 +61680,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2214" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61706,7 +61706,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61732,7 +61732,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2216" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61758,7 +61758,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2217" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61784,7 +61784,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2218" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61810,7 +61810,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2219" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61836,7 +61836,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2220" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61862,7 +61862,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2221" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61888,7 +61888,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2222" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61914,7 +61914,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2223" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61940,7 +61940,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2224" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61966,7 +61966,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2225" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61992,7 +61992,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2226" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62018,7 +62018,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2227" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62044,7 +62044,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2228" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62070,7 +62070,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2229" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62096,7 +62096,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2230" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62122,7 +62122,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2231" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62148,7 +62148,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2232" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62174,7 +62174,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2233" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62200,7 +62200,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2234" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62226,7 +62226,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2235" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62252,7 +62252,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2236" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62278,7 +62278,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2237" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62304,7 +62304,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2238" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62330,7 +62330,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2239" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62356,7 +62356,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2240" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62382,7 +62382,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2241" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62408,7 +62408,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2242" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62434,7 +62434,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2243" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62460,7 +62460,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2244" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62486,7 +62486,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2245" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62512,7 +62512,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2246" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62538,7 +62538,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62564,7 +62564,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62590,7 +62590,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2249" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62616,7 +62616,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2250" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62642,7 +62642,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2251" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62668,7 +62668,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2252" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62694,7 +62694,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G2253" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62720,7 +62720,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2254" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62746,7 +62746,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2255" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62772,7 +62772,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2256" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62798,7 +62798,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2257" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62824,7 +62824,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2258" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62850,7 +62850,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2259" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62876,7 +62876,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2260" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62902,7 +62902,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2261" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62928,7 +62928,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2262" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62954,7 +62954,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2263" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62980,7 +62980,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2264" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63006,7 +63006,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2265" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63032,7 +63032,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2266" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63058,7 +63058,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2267" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63084,7 +63084,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2268" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63110,7 +63110,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2269" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63136,7 +63136,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63162,7 +63162,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2271" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63188,7 +63188,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2272" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63214,7 +63214,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2273" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63240,7 +63240,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2274" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63266,7 +63266,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2275" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63292,7 +63292,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2276" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63318,7 +63318,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2277" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63344,7 +63344,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2278" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63370,7 +63370,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2279" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63396,7 +63396,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2280" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63422,7 +63422,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2281" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63448,7 +63448,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2282" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63474,7 +63474,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2283" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63500,7 +63500,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2284" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63526,7 +63526,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2285" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63552,7 +63552,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2286" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63578,7 +63578,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2287" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63604,7 +63604,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2288" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63630,7 +63630,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2289" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63656,7 +63656,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2290" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63682,7 +63682,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63708,7 +63708,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2292" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63734,7 +63734,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2293" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63760,7 +63760,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2294" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63786,7 +63786,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2295" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63812,7 +63812,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2296" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63838,7 +63838,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2297" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63864,7 +63864,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2298" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63890,7 +63890,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2299" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63916,7 +63916,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2300" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63942,7 +63942,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2301" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63968,7 +63968,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2302" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63994,7 +63994,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2303" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64020,7 +64020,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2304" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64046,7 +64046,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2305" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64072,7 +64072,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2306" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64098,7 +64098,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2307" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64124,7 +64124,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2308" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64150,7 +64150,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2309" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64176,7 +64176,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2310" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64202,7 +64202,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2311" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64228,7 +64228,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2312" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64254,7 +64254,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2313" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64280,7 +64280,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2314" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64306,7 +64306,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2315" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64332,7 +64332,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2316" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64358,7 +64358,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2317" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64384,7 +64384,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2318" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64410,7 +64410,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2319" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64436,7 +64436,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2320" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64462,7 +64462,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2321" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64488,7 +64488,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2322" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64514,7 +64514,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2323" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64540,7 +64540,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2324" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64566,7 +64566,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2325" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64592,7 +64592,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64618,7 +64618,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2327" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64644,7 +64644,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2328" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64670,7 +64670,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2329" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64696,7 +64696,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2330" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64722,7 +64722,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2331" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64748,7 +64748,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2332" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64774,7 +64774,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2333" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64800,7 +64800,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2334" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64826,7 +64826,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2335" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64852,7 +64852,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2336" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64878,7 +64878,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2337" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64904,7 +64904,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2338" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64930,7 +64930,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2339" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64956,7 +64956,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2340" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64982,7 +64982,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2341" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65008,7 +65008,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2342" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65034,7 +65034,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2343" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65060,7 +65060,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2344" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65086,7 +65086,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2345" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65112,7 +65112,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2346" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65138,7 +65138,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2347" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65164,7 +65164,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2348" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65190,7 +65190,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2349" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65216,7 +65216,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2350" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65242,7 +65242,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2351" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65268,7 +65268,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2352" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65294,7 +65294,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2353" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65320,7 +65320,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2354" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65346,7 +65346,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2355" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65372,7 +65372,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2356" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65398,7 +65398,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2357" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65424,7 +65424,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2358" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65450,7 +65450,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G2359" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65476,7 +65476,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G2360" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65502,7 +65502,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G2361" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65528,7 +65528,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2362" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65554,7 +65554,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2363" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65580,7 +65580,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2364" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65606,7 +65606,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2365" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65632,7 +65632,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G2366" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65658,7 +65658,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2367" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65684,7 +65684,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2368" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65710,7 +65710,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2369" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65736,7 +65736,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2370" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65762,7 +65762,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2371" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65788,7 +65788,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2372" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65814,7 +65814,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2373" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65840,7 +65840,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2374" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65866,7 +65866,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2375" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65892,7 +65892,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2376" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65918,7 +65918,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G2377" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65944,7 +65944,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2378" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65970,7 +65970,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2379" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65996,7 +65996,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2380" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66022,7 +66022,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2381" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66048,7 +66048,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2382" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66074,7 +66074,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2383" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66100,7 +66100,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2384" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66126,7 +66126,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2385" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66152,7 +66152,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2386" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66178,7 +66178,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2387" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66204,7 +66204,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2388" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66230,7 +66230,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2389" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66256,7 +66256,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2390" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66282,7 +66282,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66308,7 +66308,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2392" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66334,7 +66334,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2393" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66360,7 +66360,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2394" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66386,7 +66386,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2395" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66412,7 +66412,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2396" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66438,7 +66438,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2397" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66464,7 +66464,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2398" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66490,7 +66490,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2399" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66516,7 +66516,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G2400" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66542,7 +66542,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G2401" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66568,7 +66568,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2402" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66594,7 +66594,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2403" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66620,7 +66620,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2404" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66646,7 +66646,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2405" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66672,7 +66672,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2406" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66698,7 +66698,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2407" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66724,7 +66724,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2408" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66750,7 +66750,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2409" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66776,7 +66776,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G2410" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66802,7 +66802,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G2411" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66828,7 +66828,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2412" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66854,7 +66854,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2413" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66880,7 +66880,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2414" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66906,7 +66906,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2415" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66932,7 +66932,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2416" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66958,7 +66958,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2417" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66984,7 +66984,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2418" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67010,7 +67010,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2419" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67036,7 +67036,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2420" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67062,7 +67062,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2421" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67088,7 +67088,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2422" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67114,7 +67114,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2423" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67140,7 +67140,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2424" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67166,7 +67166,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2425" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67192,7 +67192,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2426" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67218,7 +67218,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2427" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67244,7 +67244,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2428" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67270,7 +67270,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2429" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67296,7 +67296,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2430" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67322,7 +67322,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2431" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67348,7 +67348,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2432" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67374,7 +67374,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2433" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67400,7 +67400,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2434" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67426,7 +67426,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2435" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67452,7 +67452,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2436" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67478,7 +67478,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G2437" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67504,7 +67504,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2438" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67530,7 +67530,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2439" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67556,7 +67556,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2440" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67582,7 +67582,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2441" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67608,7 +67608,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2442" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67634,7 +67634,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2443" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67660,7 +67660,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2444" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67686,7 +67686,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2445" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67712,7 +67712,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2446" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67738,7 +67738,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2447" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67764,7 +67764,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2448" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67790,7 +67790,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2449" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67816,7 +67816,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2450" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67842,7 +67842,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2451" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67868,7 +67868,7 @@
         <v>0.5</v>
       </c>
       <c r="G2452" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67894,7 +67894,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G2453" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67920,7 +67920,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2454" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67946,7 +67946,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G2455" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67972,7 +67972,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2456" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67998,7 +67998,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2457" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68024,7 +68024,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2458" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68050,7 +68050,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2459" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68076,7 +68076,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G2460" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68102,7 +68102,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2461" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68128,7 +68128,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G2462" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68154,7 +68154,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2463" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68180,7 +68180,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G2464" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68206,7 +68206,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G2465" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68232,7 +68232,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2466" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68258,7 +68258,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2467" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68284,7 +68284,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2468" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68310,7 +68310,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2469" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68336,7 +68336,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2470" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68362,7 +68362,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2471" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68388,7 +68388,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2472" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68414,7 +68414,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G2473" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68440,7 +68440,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2474" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68466,7 +68466,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2475" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68492,7 +68492,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G2476" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68518,7 +68518,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2477" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68544,7 +68544,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2478" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68570,7 +68570,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2479" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68596,7 +68596,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2480" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68622,7 +68622,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2481" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68648,7 +68648,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2482" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68674,7 +68674,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2483" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68700,7 +68700,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2484" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68726,7 +68726,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G2485" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68752,7 +68752,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G2486" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68778,7 +68778,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2487" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68786,7 +68786,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495486111</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>232742</v>
@@ -68804,9 +68804,35 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2488" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6494791667</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>256131</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>0.453000009059906</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>0.456999987363815</v>
+      </c>
+      <c r="G2489" t="s">
         <v>1257</v>
       </c>
-      <c r="H2488" t="s">
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326352328062057</t>
+    <t xml:space="preserve">0.32635235786438</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844841241837</t>
+    <t xml:space="preserve">0.326844811439514</t>
   </si>
   <si>
     <t xml:space="preserve">0.323679089546204</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">0.313056230545044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304966032505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29976013302803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309538751840591</t>
+    <t xml:space="preserve">0.304966062307358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299760162830353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309538781642914</t>
   </si>
   <si>
     <t xml:space="preserve">0.302503824234009</t>
@@ -71,28 +71,28 @@
     <t xml:space="preserve">0.287097215652466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274363875389099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278655260801315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265288770198822</t>
+    <t xml:space="preserve">0.274363905191422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278655290603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265288829803467</t>
   </si>
   <si>
     <t xml:space="preserve">0.260645687580109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270846396684647</t>
+    <t xml:space="preserve">0.270846426486969</t>
   </si>
   <si>
     <t xml:space="preserve">0.269087672233582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272956937551498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270142942667007</t>
+    <t xml:space="preserve">0.272956907749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270142912864685</t>
   </si>
   <si>
     <t xml:space="preserve">0.265921950340271</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">0.290825754404068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288433849811554</t>
+    <t xml:space="preserve">0.288433879613876</t>
   </si>
   <si>
     <t xml:space="preserve">0.294061869382858</t>
@@ -110,79 +110,79 @@
     <t xml:space="preserve">0.276404023170471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273167997598648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262545108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260293990373611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246927544474602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246224045753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239751860499382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240103632211685</t>
+    <t xml:space="preserve">0.273167937994003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262545138597488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260293960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246927559375763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246224015951157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23975183069706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240103602409363</t>
   </si>
   <si>
     <t xml:space="preserve">0.271549940109253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276122629642487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274645298719406</t>
+    <t xml:space="preserve">0.276122689247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274645328521729</t>
   </si>
   <si>
     <t xml:space="preserve">0.277881413698196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270987182855606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281539559364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277177900075912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26331901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2680324614048</t>
+    <t xml:space="preserve">0.270987093448639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281539589166641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27717787027359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263319045305252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268032431602478</t>
   </si>
   <si>
     <t xml:space="preserve">0.28210237622261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295468837022781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293358325958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291740298271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288644909858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504213094711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281469225883484</t>
+    <t xml:space="preserve">0.295468807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293358355760574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291740328073502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288644939661026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504272699356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281469285488129</t>
   </si>
   <si>
     <t xml:space="preserve">0.27724826335907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373807668686</t>
+    <t xml:space="preserve">0.278373837471008</t>
   </si>
   <si>
     <t xml:space="preserve">0.287026852369308</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">0.297368288040161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295820593833923</t>
+    <t xml:space="preserve">0.295820564031601</t>
   </si>
   <si>
     <t xml:space="preserve">0.307217240333557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305669575929642</t>
+    <t xml:space="preserve">0.305669516324997</t>
   </si>
   <si>
     <t xml:space="preserve">0.31375977396965</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">0.320443004369736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317417949438095</t>
+    <t xml:space="preserve">0.317417919635773</t>
   </si>
   <si>
     <t xml:space="preserve">0.316573739051819</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">0.306161999702454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310945779085159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311438262462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301800340414047</t>
+    <t xml:space="preserve">0.310945838689804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311438232660294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301800280809402</t>
   </si>
   <si>
     <t xml:space="preserve">0.288011759519577</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">0.280554682016373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281328499317169</t>
+    <t xml:space="preserve">0.281328558921814</t>
   </si>
   <si>
     <t xml:space="preserve">0.291881024837494</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">0.301378220319748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311649262905121</t>
+    <t xml:space="preserve">0.311649292707443</t>
   </si>
   <si>
     <t xml:space="preserve">0.310242295265198</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">0.314533621072769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316644132137299</t>
+    <t xml:space="preserve">0.316644102334976</t>
   </si>
   <si>
     <t xml:space="preserve">0.318684250116348</t>
@@ -269,22 +269,22 @@
     <t xml:space="preserve">0.334161162376404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333528071641922</t>
+    <t xml:space="preserve">0.3335280418396</t>
   </si>
   <si>
     <t xml:space="preserve">0.330432653427124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327126234769821</t>
+    <t xml:space="preserve">0.327126204967499</t>
   </si>
   <si>
     <t xml:space="preserve">0.323538362979889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318543523550034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319247037172318</t>
+    <t xml:space="preserve">0.318543553352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319247007369995</t>
   </si>
   <si>
     <t xml:space="preserve">0.323116332292557</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.323749423027039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325015723705292</t>
+    <t xml:space="preserve">0.325015753507614</t>
   </si>
   <si>
     <t xml:space="preserve">0.32107612490654</t>
@@ -314,58 +314,58 @@
     <t xml:space="preserve">0.344713658094406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34204038977623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338030427694321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352100372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354914337396622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351678252220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350341618061066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343306601047516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343165934085846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341196179389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340211272239685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33704549074173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323537766933441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309325903654099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312153726816177</t>
+    <t xml:space="preserve">0.342040330171585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338030457496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352100402116776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354914367198944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351678282022476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350341588258743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343306630849838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343165963888168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341196119785309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340211242437363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337045520544052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323537737131119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309325873851776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3121537566185</t>
   </si>
   <si>
     <t xml:space="preserve">0.308890819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311936259269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325278013944626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322232633829117</t>
+    <t xml:space="preserve">0.311936229467392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325277984142303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322232574224472</t>
   </si>
   <si>
     <t xml:space="preserve">0.318607121706009</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">0.307223081588745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299102038145065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299464553594589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313096404075623</t>
+    <t xml:space="preserve">0.299102008342743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299464583396912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3130963742733</t>
   </si>
   <si>
     <t xml:space="preserve">0.320854872465134</t>
@@ -392,25 +392,25 @@
     <t xml:space="preserve">0.318027049303055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319042146205902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318317055702209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309543430805206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311791241168976</t>
+    <t xml:space="preserve">0.319042176008224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318317085504532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309543401002884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311791211366653</t>
   </si>
   <si>
     <t xml:space="preserve">0.310558527708054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311066061258316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322087585926056</t>
+    <t xml:space="preserve">0.311066091060638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322087556123734</t>
   </si>
   <si>
     <t xml:space="preserve">0.319767266511917</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">0.305627912282944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301784873008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300914794206619</t>
+    <t xml:space="preserve">0.301784932613373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">0.298739492893219</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">0.291488528251648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294316381216049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304467707872391</t>
+    <t xml:space="preserve">0.294316411018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304467737674713</t>
   </si>
   <si>
     <t xml:space="preserve">0.301204800605774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302727490663528</t>
+    <t xml:space="preserve">0.302727520465851</t>
   </si>
   <si>
     <t xml:space="preserve">0.30381515622139</t>
@@ -464,31 +464,31 @@
     <t xml:space="preserve">0.29743430018425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299682080745697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301929891109467</t>
+    <t xml:space="preserve">0.299682050943375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301929861307144</t>
   </si>
   <si>
     <t xml:space="preserve">0.301712363958359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302364945411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300117164850235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302219927310944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297144263982773</t>
+    <t xml:space="preserve">0.302364975214005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300117135047913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302219986915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297144293785095</t>
   </si>
   <si>
     <t xml:space="preserve">0.295621573925018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293663829565048</t>
+    <t xml:space="preserve">0.293663769960403</t>
   </si>
   <si>
     <t xml:space="preserve">0.297289311885834</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">0.292358636856079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290038347244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287500470876694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292648673057556</t>
+    <t xml:space="preserve">0.29003831744194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287500500679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292648702859879</t>
   </si>
   <si>
     <t xml:space="preserve">0.287645518779755</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">0.295041501522064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291561007499695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294533878564835</t>
+    <t xml:space="preserve">0.29156106710434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294533908367157</t>
   </si>
   <si>
     <t xml:space="preserve">0.289313226938248</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">0.282859891653061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27582648396492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279161870479584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26973569393158</t>
+    <t xml:space="preserve">0.275826454162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279161900281906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269735634326935</t>
   </si>
   <si>
     <t xml:space="preserve">0.273288607597351</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">0.283802479505539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282134801149368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287137925624847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292866259813309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301422327756882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295839101076126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296564161777496</t>
+    <t xml:space="preserve">0.282134771347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287137866020203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292866200208664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301422297954559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295839071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296564191579819</t>
   </si>
   <si>
     <t xml:space="preserve">0.300262182950974</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">0.297071754932404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292938739061356</t>
+    <t xml:space="preserve">0.292938679456711</t>
   </si>
   <si>
     <t xml:space="preserve">0.298812001943588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296056628227234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31019601225853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306425511837006</t>
+    <t xml:space="preserve">0.296056598424911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310195982456207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306425482034683</t>
   </si>
   <si>
     <t xml:space="preserve">0.302509993314743</t>
@@ -605,46 +605,46 @@
     <t xml:space="preserve">0.307078093290329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301639884710312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294098883867264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283077448606491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28786301612854</t>
+    <t xml:space="preserve">0.30163985490799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294098824262619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283077418804169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287863045930862</t>
   </si>
   <si>
     <t xml:space="preserve">0.289603292942047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285615265369415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2839475274086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288805693387985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293736308813095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290835946798325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283512443304062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281409680843353</t>
+    <t xml:space="preserve">0.285615205764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283947557210922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288805663585663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293736338615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290835976600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283512473106384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281409710645676</t>
   </si>
   <si>
     <t xml:space="preserve">0.280684620141983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279016882181168</t>
+    <t xml:space="preserve">0.27901691198349</t>
   </si>
   <si>
     <t xml:space="preserve">0.273796200752258</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">0.291416019201279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295113980770111</t>
+    <t xml:space="preserve">0.295114010572433</t>
   </si>
   <si>
     <t xml:space="preserve">0.290545880794525</t>
@@ -662,25 +662,25 @@
     <t xml:space="preserve">0.288588136434555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292213618755341</t>
+    <t xml:space="preserve">0.292213588953018</t>
   </si>
   <si>
     <t xml:space="preserve">0.292141109704971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294388920068741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29939204454422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296491652727127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303597658872604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309615969657898</t>
+    <t xml:space="preserve">0.294388860464096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299392074346542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296491682529449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303597629070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309615910053253</t>
   </si>
   <si>
     <t xml:space="preserve">0.307440638542175</t>
@@ -698,52 +698,52 @@
     <t xml:space="preserve">0.345000594854355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349786221981049</t>
+    <t xml:space="preserve">0.349786251783371</t>
   </si>
   <si>
     <t xml:space="preserve">0.358342349529266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354209333658218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349641233682632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352396577596664</t>
+    <t xml:space="preserve">0.354209303855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34964120388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352396547794342</t>
   </si>
   <si>
     <t xml:space="preserve">0.355296969413757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359430015087128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352686613798141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346885830163956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343187868595123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346160739660263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346595764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34645077586174</t>
+    <t xml:space="preserve">0.359429985284805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352686643600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346885859966278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343187838792801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346160769462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346595793962479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346450835466385</t>
   </si>
   <si>
     <t xml:space="preserve">0.344348013401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350221276283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350946366786957</t>
+    <t xml:space="preserve">0.350221306085587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350946396589279</t>
   </si>
   <si>
     <t xml:space="preserve">0.388288825750351</t>
@@ -752,64 +752,64 @@
     <t xml:space="preserve">0.397715061903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379950195550919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382125467061996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37487456202507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373424351215363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377412408590317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373061835765839</t>
+    <t xml:space="preserve">0.379950225353241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382125496864319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374874591827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373424381017685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377412378787994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373061805963516</t>
   </si>
   <si>
     <t xml:space="preserve">0.369798839092255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383575677871704</t>
+    <t xml:space="preserve">0.383575648069382</t>
   </si>
   <si>
     <t xml:space="preserve">0.369436353445053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369073778390884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35819736123085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358052343130112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377049803733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412579596042633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382488042116165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40061542391777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394452184438705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385751008987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393727004528046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390464097261429</t>
+    <t xml:space="preserve">0.369073808193207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358197301626205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358052372932434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377049833536148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412579536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38248798251152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400615453720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394452154636383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385750979185104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393727034330368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390464067459106</t>
   </si>
   <si>
     <t xml:space="preserve">0.384300768375397</t>
@@ -818,40 +818,40 @@
     <t xml:space="preserve">0.391551792621613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387563735246658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390826612710953</t>
+    <t xml:space="preserve">0.387563705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390826642513275</t>
   </si>
   <si>
     <t xml:space="preserve">0.395177215337753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393364518880844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397352486848831</t>
+    <t xml:space="preserve">0.393364489078522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397352516651154</t>
   </si>
   <si>
     <t xml:space="preserve">0.398802727460861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3955397605896</t>
+    <t xml:space="preserve">0.395539790391922</t>
   </si>
   <si>
     <t xml:space="preserve">0.396627426147461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398440182209015</t>
+    <t xml:space="preserve">0.39844024181366</t>
   </si>
   <si>
     <t xml:space="preserve">0.395902305841446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393001973628998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398077607154846</t>
+    <t xml:space="preserve">0.393001943826675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398077577352524</t>
   </si>
   <si>
     <t xml:space="preserve">0.401703059673309</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">0.39227682352066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387201130390167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386476069688797</t>
+    <t xml:space="preserve">0.38720116019249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386476099491119</t>
   </si>
   <si>
     <t xml:space="preserve">0.382850617170334</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">0.38937646150589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381762951612473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38103786110878</t>
+    <t xml:space="preserve">0.38176292181015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381037890911102</t>
   </si>
   <si>
     <t xml:space="preserve">0.386838644742966</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">0.388651371002197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385025888681412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391189277172089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392639368772507</t>
+    <t xml:space="preserve">0.385025918483734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391189187765121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392639398574829</t>
   </si>
   <si>
     <t xml:space="preserve">0.425631284713745</t>
@@ -902,58 +902,58 @@
     <t xml:space="preserve">0.419105380773544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445208817720413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435057520866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442308485507965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432611972093582</t>
+    <t xml:space="preserve">0.445208847522736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435057550668716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442308396100998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43261194229126</t>
   </si>
   <si>
     <t xml:space="preserve">0.413591980934143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408370792865753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406879007816315</t>
+    <t xml:space="preserve">0.408370822668076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406879037618637</t>
   </si>
   <si>
     <t xml:space="preserve">0.402776718139648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399047315120697</t>
+    <t xml:space="preserve">0.399047344923019</t>
   </si>
   <si>
     <t xml:space="preserve">0.400539040565491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395317822694778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396809637546539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39606374502182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393080174922943</t>
+    <t xml:space="preserve">0.395317852497101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396809607744217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396063774824142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393080204725266</t>
   </si>
   <si>
     <t xml:space="preserve">0.388604909181595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387858986854553</t>
+    <t xml:space="preserve">0.387859016656876</t>
   </si>
   <si>
     <t xml:space="preserve">0.379654318094254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38114607334137</t>
+    <t xml:space="preserve">0.381146043539047</t>
   </si>
   <si>
     <t xml:space="preserve">0.383010745048523</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">0.387486100196838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384875476360321</t>
+    <t xml:space="preserve">0.384875416755676</t>
   </si>
   <si>
     <t xml:space="preserve">0.383756697177887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386740148067474</t>
+    <t xml:space="preserve">0.386740177869797</t>
   </si>
   <si>
     <t xml:space="preserve">0.390096694231033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394944965839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403522551059723</t>
+    <t xml:space="preserve">0.394944906234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403522521257401</t>
   </si>
   <si>
     <t xml:space="preserve">0.410235524177551</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">0.407251954078674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407624959945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40874370932579</t>
+    <t xml:space="preserve">0.407624930143356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408743739128113</t>
   </si>
   <si>
     <t xml:space="preserve">0.406506091356277</t>
@@ -998,37 +998,37 @@
     <t xml:space="preserve">0.400912016630173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394199013710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398674339056015</t>
+    <t xml:space="preserve">0.394199073314667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398674309253693</t>
   </si>
   <si>
     <t xml:space="preserve">0.390842527151108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392334371805191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388231992721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387113094329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391588419675827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389350771903992</t>
+    <t xml:space="preserve">0.392334342002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388231962919235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387113124132156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391588389873505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389350801706314</t>
   </si>
   <si>
     <t xml:space="preserve">0.385621398687363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380773156881332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385248422622681</t>
+    <t xml:space="preserve">0.380773186683655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385248452425003</t>
   </si>
   <si>
     <t xml:space="preserve">0.383383721113205</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">0.397928446531296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410981386899948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41433784365654</t>
+    <t xml:space="preserve">0.40948960185051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410981357097626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414337873458862</t>
   </si>
   <si>
     <t xml:space="preserve">0.415083706378937</t>
@@ -1055,139 +1055,139 @@
     <t xml:space="preserve">0.415829658508301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4240343272686</t>
+    <t xml:space="preserve">0.424034357070923</t>
   </si>
   <si>
     <t xml:space="preserve">0.439324915409088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431866049766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428882598876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420304924249649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421796649694443</t>
+    <t xml:space="preserve">0.431866079568863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428882539272308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420304894447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421796679496765</t>
   </si>
   <si>
     <t xml:space="preserve">0.428509622812271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45498850941658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445291996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444546103477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440443754196167</t>
+    <t xml:space="preserve">0.454988449811935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445291966199875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444546192884445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440443783998489</t>
   </si>
   <si>
     <t xml:space="preserve">0.449767291545868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459463775157928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460955530405045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469533175230026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466549724340439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474008500576019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474754393100739</t>
+    <t xml:space="preserve">0.459463715553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460955500602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469533145427704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466549605131149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474008470773697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474754363298416</t>
   </si>
   <si>
     <t xml:space="preserve">0.480348527431488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485942512750626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482586115598679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485569715499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509437918663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511302649974823</t>
+    <t xml:space="preserve">0.485942602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482586145401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4855697453022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50943797826767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511302530765533</t>
   </si>
   <si>
     <t xml:space="preserve">0.521745026111603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512794375419617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5195072889328</t>
+    <t xml:space="preserve">0.512794435024261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519507348537445</t>
   </si>
   <si>
     <t xml:space="preserve">0.511675477027893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506081402301788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501233279705048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502352058887482</t>
+    <t xml:space="preserve">0.506081461906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501233220100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502351999282837</t>
   </si>
   <si>
     <t xml:space="preserve">0.495266109704971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491536617279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477737843990326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478483766317368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48109444975853</t>
+    <t xml:space="preserve">0.49153670668602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477737903594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478483736515045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48109433054924</t>
   </si>
   <si>
     <t xml:space="preserve">0.492282629013062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499741464853287</t>
+    <t xml:space="preserve">0.499741435050964</t>
   </si>
   <si>
     <t xml:space="preserve">0.493774354457855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495639085769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507946193218231</t>
+    <t xml:space="preserve">0.495639026165009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507946133613586</t>
   </si>
   <si>
     <t xml:space="preserve">0.500114381313324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493028491735458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508692026138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503470897674561</t>
+    <t xml:space="preserve">0.493028551340103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508691966533661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503470957279205</t>
   </si>
   <si>
     <t xml:space="preserve">0.508319079875946</t>
@@ -1196,55 +1196,55 @@
     <t xml:space="preserve">0.507200300693512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510183751583099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513167321681976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500860273838043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503097891807556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502725005149841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501606166362762</t>
+    <t xml:space="preserve">0.510183870792389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513167381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500860333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503097951412201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502724945545197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501606106758118</t>
   </si>
   <si>
     <t xml:space="preserve">0.498249650001526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510929703712463</t>
+    <t xml:space="preserve">0.510929763317108</t>
   </si>
   <si>
     <t xml:space="preserve">0.531068503856659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557920217514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554936826229095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559412002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565379023551941</t>
+    <t xml:space="preserve">0.557920336723328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554936766624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559412062168121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56537914276123</t>
   </si>
   <si>
     <t xml:space="preserve">0.593722641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574329674243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576567411422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577313184738159</t>
+    <t xml:space="preserve">0.574329614639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576567351818085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577313244342804</t>
   </si>
   <si>
     <t xml:space="preserve">0.583280265331268</t>
@@ -1253,31 +1253,31 @@
     <t xml:space="preserve">0.59148496389389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585517942905426</t>
+    <t xml:space="preserve">0.585518002510071</t>
   </si>
   <si>
     <t xml:space="preserve">0.575075626373291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61236971616745</t>
+    <t xml:space="preserve">0.612369775772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.556428492069244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551953196525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548223793506622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53479790687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521372079849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505708515644073</t>
+    <t xml:space="preserve">0.551953256130219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548223853111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534797847270966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521372020244598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505708456039429</t>
   </si>
   <si>
     <t xml:space="preserve">0.528084993362427</t>
@@ -1286,22 +1286,22 @@
     <t xml:space="preserve">0.54524028301239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522863745689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517642557621002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532560229301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531814277172089</t>
+    <t xml:space="preserve">0.522863805294037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517642676830292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532560288906097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531814336776733</t>
   </si>
   <si>
     <t xml:space="preserve">0.523609697818756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516150891780853</t>
+    <t xml:space="preserve">0.516150832176208</t>
   </si>
   <si>
     <t xml:space="preserve">0.512421429157257</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">0.519134402275085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498995542526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463193237781525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469906091690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476619064807892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477364867925644</t>
+    <t xml:space="preserve">0.498995572328568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463193148374557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469906121492386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476619154214859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477364927530289</t>
   </si>
   <si>
     <t xml:space="preserve">0.494520306587219</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">0.490044951438904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478856682777405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478110820055008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468414425849915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481840252876282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484077781438828</t>
+    <t xml:space="preserve">0.478856652975082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478110790252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468414306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481840223073959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484077900648117</t>
   </si>
   <si>
     <t xml:space="preserve">0.475127279758453</t>
@@ -1352,142 +1352,142 @@
     <t xml:space="preserve">0.47363555431366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474381357431412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484823763370514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487061381340027</t>
+    <t xml:space="preserve">0.474381417036057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484823703765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487061470746994</t>
   </si>
   <si>
     <t xml:space="preserve">0.48333203792572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50421667098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504962563514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496757864952087</t>
+    <t xml:space="preserve">0.504216730594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504962623119354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49675789475441</t>
   </si>
   <si>
     <t xml:space="preserve">0.497503787279129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48631551861763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500487327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454242616891861</t>
+    <t xml:space="preserve">0.486315488815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500487387180328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454242646694183</t>
   </si>
   <si>
     <t xml:space="preserve">0.465430855751038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452004939317703</t>
+    <t xml:space="preserve">0.452004879713058</t>
   </si>
   <si>
     <t xml:space="preserve">0.457226127386093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458717852830887</t>
+    <t xml:space="preserve">0.458717882633209</t>
   </si>
   <si>
     <t xml:space="preserve">0.462447255849838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455734372138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45797199010849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485727846622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484185963869095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474933922290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469536989927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464910954236984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461055964231491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463368982076645</t>
+    <t xml:space="preserve">0.455734342336655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457972049713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485727876424789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484185844659805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47493389248848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469536930322647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464910984039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461055994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463368952274323</t>
   </si>
   <si>
     <t xml:space="preserve">0.459513992071152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458743005990982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44794899225235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451032996177673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454888015985489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.446406990289688</t>
+    <t xml:space="preserve">0.45874297618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447949051856995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451032966375351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454887926578522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.446407049894333</t>
   </si>
   <si>
     <t xml:space="preserve">0.44178107380867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443323075771332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494208812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47416290640831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481101930141449</t>
+    <t xml:space="preserve">0.443323045969009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494208842515945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474162966012955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481101959943771</t>
   </si>
   <si>
     <t xml:space="preserve">0.489582866430283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476475924253464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46413990855217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461827009916306</t>
+    <t xml:space="preserve">0.476475864648819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464139968156815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461826950311661</t>
   </si>
   <si>
     <t xml:space="preserve">0.456430017948151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454117000102997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466452926397324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467223972082138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439468055963516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442552089691162</t>
+    <t xml:space="preserve">0.454116970300674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466453015804291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467223942279816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439468085765839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44255205988884</t>
   </si>
   <si>
     <t xml:space="preserve">0.45257505774498</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">0.441010057926178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437926113605499</t>
+    <t xml:space="preserve">0.437926083803177</t>
   </si>
   <si>
     <t xml:space="preserve">0.433300107717514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430987119674683</t>
+    <t xml:space="preserve">0.430987179279327</t>
   </si>
   <si>
     <t xml:space="preserve">0.431758135557175</t>
@@ -1514,97 +1514,97 @@
     <t xml:space="preserve">0.435613095760345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444865107536316</t>
+    <t xml:space="preserve">0.444865077733994</t>
   </si>
   <si>
     <t xml:space="preserve">0.460284978151321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45180407166481</t>
+    <t xml:space="preserve">0.451804101467133</t>
   </si>
   <si>
     <t xml:space="preserve">0.470307976007462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471849948167801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465681999921799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457200974225998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462597995996475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455659031867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450262010097504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449490994215012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437155067920685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440239042043686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42636114358902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427903175354004</t>
+    <t xml:space="preserve">0.471849918365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465681910514832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45720100402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462598025798798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455659002065659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450261980295181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449491053819656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437155097723007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440239071846008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426361113786697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427903115749359</t>
   </si>
   <si>
     <t xml:space="preserve">0.407086223363876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406315207481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4101702272892</t>
+    <t xml:space="preserve">0.406315237283707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410170197486877</t>
   </si>
   <si>
     <t xml:space="preserve">0.404002219438553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407857209444046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41094121336937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400147199630737</t>
+    <t xml:space="preserve">0.407857179641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410941243171692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400147259235382</t>
   </si>
   <si>
     <t xml:space="preserve">0.396292269229889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390895307064056</t>
+    <t xml:space="preserve">0.390895366668701</t>
   </si>
   <si>
     <t xml:space="preserve">0.390124291181564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381643354892731</t>
+    <t xml:space="preserve">0.381643325090408</t>
   </si>
   <si>
     <t xml:space="preserve">0.38318532705307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387811332941055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388582319021225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394750326871872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397063255310059</t>
+    <t xml:space="preserve">0.387811303138733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388582289218903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394750267267227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397063285112381</t>
   </si>
   <si>
     <t xml:space="preserve">0.389353275299072</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">0.375475317239761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366223365068436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351188987493515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345406502485275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348875939846039</t>
+    <t xml:space="preserve">0.366223394870758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351188957691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345406532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348875969648361</t>
   </si>
   <si>
     <t xml:space="preserve">0.366994380950928</t>
@@ -1646,25 +1646,25 @@
     <t xml:space="preserve">0.370078384876251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370463907718658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369692832231522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365837872028351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371620386838913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368536353111267</t>
+    <t xml:space="preserve">0.370463877916336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369692891836166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365837901830673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371620357036591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368536382913589</t>
   </si>
   <si>
     <t xml:space="preserve">0.368921875953674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37894481420517</t>
+    <t xml:space="preserve">0.378944844007492</t>
   </si>
   <si>
     <t xml:space="preserve">0.383570820093155</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">0.424819141626358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417109161615372</t>
+    <t xml:space="preserve">0.417109221220016</t>
   </si>
   <si>
     <t xml:space="preserve">0.422506123781204</t>
@@ -1703,64 +1703,64 @@
     <t xml:space="preserve">0.408628195524216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400918215513229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404773205518723</t>
+    <t xml:space="preserve">0.400918245315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4047731757164</t>
   </si>
   <si>
     <t xml:space="preserve">0.405544281005859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411712139844894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412483245134354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423277169466019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425590127706528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419422209262848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430216163396835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427132099866867</t>
+    <t xml:space="preserve">0.411712199449539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412483215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423277139663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42559015750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419422179460526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430216133594513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427132159471512</t>
   </si>
   <si>
     <t xml:space="preserve">0.414025187492371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414796203374863</t>
+    <t xml:space="preserve">0.41479617357254</t>
   </si>
   <si>
     <t xml:space="preserve">0.413254201412201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409399211406708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395521283149719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393208235502243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392437279224396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391666263341904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393979281187057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398605287075043</t>
+    <t xml:space="preserve">0.40939924120903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395521253347397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393208265304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392437249422073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391666293144226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393979251384735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39860525727272</t>
   </si>
   <si>
     <t xml:space="preserve">0.403231263160706</t>
@@ -1769,28 +1769,28 @@
     <t xml:space="preserve">0.411275923252106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410471051931381</t>
+    <t xml:space="preserve">0.410471081733704</t>
   </si>
   <si>
     <t xml:space="preserve">0.409666240215302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415300130844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412885636091232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412080824375153</t>
+    <t xml:space="preserve">0.415300160646439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41288560628891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41208079457283</t>
   </si>
   <si>
     <t xml:space="preserve">0.399203240871429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401215374469757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404032289981842</t>
+    <t xml:space="preserve">0.401215344667435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404032319784164</t>
   </si>
   <si>
     <t xml:space="preserve">0.397996008396149</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">0.403227478265762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39839842915535</t>
+    <t xml:space="preserve">0.398398399353027</t>
   </si>
   <si>
     <t xml:space="preserve">0.400008112192154</t>
@@ -1808,22 +1808,22 @@
     <t xml:space="preserve">0.40242263674736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400410532951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395983874797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39960566163063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418519496917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417714655399323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416909873485565</t>
+    <t xml:space="preserve">0.400410503149033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395983844995499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399605691432953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418519526720047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417714685201645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416909843683243</t>
   </si>
   <si>
     <t xml:space="preserve">0.404837191104889</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">0.397593587636948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391154825687408</t>
+    <t xml:space="preserve">0.391154766082764</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446844339371</t>
@@ -1856,31 +1856,31 @@
     <t xml:space="preserve">0.433811575174332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424153447151184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43220192193985</t>
+    <t xml:space="preserve">0.424153476953506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432201892137527</t>
   </si>
   <si>
     <t xml:space="preserve">0.425763130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428177714347839</t>
+    <t xml:space="preserve">0.428177654743195</t>
   </si>
   <si>
     <t xml:space="preserve">0.433006763458252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429787307977676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420934110879898</t>
+    <t xml:space="preserve">0.429787337779999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420934051275253</t>
   </si>
   <si>
     <t xml:space="preserve">0.428982526063919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437030971050262</t>
+    <t xml:space="preserve">0.437031000852585</t>
   </si>
   <si>
     <t xml:space="preserve">0.434616476297379</t>
@@ -1892,43 +1892,43 @@
     <t xml:space="preserve">0.442664921283722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458761781454086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466810256242752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473249018192291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476468414068222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478882938623428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47566357254982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481297463178635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478078097105026</t>
+    <t xml:space="preserve">0.458761811256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466810286045074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473248988389969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476468354463577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478883028030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475663602352142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481297433376312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478078067302704</t>
   </si>
   <si>
     <t xml:space="preserve">0.474858701229095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471639364957809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472444206476212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486126571893692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480492621660233</t>
+    <t xml:space="preserve">0.471639335155487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472444146871567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48612654209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480492562055588</t>
   </si>
   <si>
     <t xml:space="preserve">0.494979828596115</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">0.513491332530975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520734846591949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535222172737122</t>
+    <t xml:space="preserve">0.520734906196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535222113132477</t>
   </si>
   <si>
     <t xml:space="preserve">0.53441721200943</t>
@@ -1952,13 +1952,13 @@
     <t xml:space="preserve">0.523149430751801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51510089635849</t>
+    <t xml:space="preserve">0.515100955963135</t>
   </si>
   <si>
     <t xml:space="preserve">0.516710638999939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522344470024109</t>
+    <t xml:space="preserve">0.522344589233398</t>
   </si>
   <si>
     <t xml:space="preserve">0.556148052215576</t>
@@ -1967,22 +1967,22 @@
     <t xml:space="preserve">0.555343210697174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551319062709808</t>
+    <t xml:space="preserve">0.551319003105164</t>
   </si>
   <si>
     <t xml:space="preserve">0.55775773525238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571440100669861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56178206205368</t>
+    <t xml:space="preserve">0.571440160274506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561781942844391</t>
   </si>
   <si>
     <t xml:space="preserve">0.560977220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552928686141968</t>
+    <t xml:space="preserve">0.552928745746613</t>
   </si>
   <si>
     <t xml:space="preserve">0.554538428783417</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">0.59236615896225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596390306949615</t>
+    <t xml:space="preserve">0.59639036655426</t>
   </si>
   <si>
     <t xml:space="preserve">0.599609732627869</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">0.606853306293488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60202419757843</t>
+    <t xml:space="preserve">0.602024257183075</t>
   </si>
   <si>
     <t xml:space="preserve">0.614901781082153</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">0.608463048934937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593975782394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590756475925446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595585465431213</t>
+    <t xml:space="preserve">0.593975722789764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590756416320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595585525035858</t>
   </si>
   <si>
     <t xml:space="preserve">0.609267830848694</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">0.593170940876007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598804950714111</t>
+    <t xml:space="preserve">0.598804891109467</t>
   </si>
   <si>
     <t xml:space="preserve">0.601219356060028</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">0.594780683517456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603633880615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610072672367096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598000049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630193829536438</t>
+    <t xml:space="preserve">0.603633940219879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610072791576385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59799998998642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630193889141083</t>
   </si>
   <si>
     <t xml:space="preserve">0.631803512573242</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">0.65594893693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65997314453125</t>
+    <t xml:space="preserve">0.659973084926605</t>
   </si>
   <si>
     <t xml:space="preserve">0.689752399921417</t>
@@ -2078,31 +2078,31 @@
     <t xml:space="preserve">0.661582827568054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588341891765594</t>
+    <t xml:space="preserve">0.588341951370239</t>
   </si>
   <si>
     <t xml:space="preserve">0.581098318099976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572245001792908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540856063365936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543270587921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518320381641388</t>
+    <t xml:space="preserve">0.572244942188263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540856003761292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543270528316498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518320322036743</t>
   </si>
   <si>
     <t xml:space="preserve">0.526368796825409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490955650806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439445495605469</t>
+    <t xml:space="preserve">0.490955621004105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439445465803146</t>
   </si>
   <si>
     <t xml:space="preserve">0.398800820112228</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">0.282500714063644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288939446210861</t>
+    <t xml:space="preserve">0.288939416408539</t>
   </si>
   <si>
     <t xml:space="preserve">0.291353970766068</t>
@@ -2135,10 +2135,10 @@
     <t xml:space="preserve">0.308255761861801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343668967485428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35896098613739</t>
+    <t xml:space="preserve">0.343668907880783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358961015939713</t>
   </si>
   <si>
     <t xml:space="preserve">0.37224093079567</t>
@@ -2147,52 +2147,52 @@
     <t xml:space="preserve">0.355741620063782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373850613832474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391959607601166</t>
+    <t xml:space="preserve">0.373850643634796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391959637403488</t>
   </si>
   <si>
     <t xml:space="preserve">0.37908211350441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375057846307755</t>
+    <t xml:space="preserve">0.375057876110077</t>
   </si>
   <si>
     <t xml:space="preserve">0.384716004133224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386325746774673</t>
+    <t xml:space="preserve">0.386325716972351</t>
   </si>
   <si>
     <t xml:space="preserve">0.374253064393997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362180382013321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351717412471771</t>
+    <t xml:space="preserve">0.362180352210999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351717382669449</t>
   </si>
   <si>
     <t xml:space="preserve">0.353327065706253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349302798509598</t>
+    <t xml:space="preserve">0.349302858114243</t>
   </si>
   <si>
     <t xml:space="preserve">0.344473779201508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323547780513763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338034987449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339644700288773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341254383325577</t>
+    <t xml:space="preserve">0.323547810316086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338035017251968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33964467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341254413127899</t>
   </si>
   <si>
     <t xml:space="preserve">0.346083492040634</t>
@@ -2207,22 +2207,22 @@
     <t xml:space="preserve">0.342864096164703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345278561115265</t>
+    <t xml:space="preserve">0.34527862071991</t>
   </si>
   <si>
     <t xml:space="preserve">0.336425334215164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324352651834488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329986572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326767176389694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321938127279282</t>
+    <t xml:space="preserve">0.324352622032166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329986542463303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326767146587372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321938097476959</t>
   </si>
   <si>
     <t xml:space="preserve">0.331596255302429</t>
@@ -2237,16 +2237,16 @@
     <t xml:space="preserve">0.352522224187851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354936748743057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369424015283585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382301479578018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379886984825134</t>
+    <t xml:space="preserve">0.35493677854538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36942395567894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382301509380341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379886955022812</t>
   </si>
   <si>
     <t xml:space="preserve">0.371838539838791</t>
@@ -2261,10 +2261,10 @@
     <t xml:space="preserve">0.356546431779861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357351273298264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350107699632645</t>
+    <t xml:space="preserve">0.357351303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350107669830322</t>
   </si>
   <si>
     <t xml:space="preserve">0.346888303756714</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">0.342059254646301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337230145931244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328376859426498</t>
+    <t xml:space="preserve">0.337230175733566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328376829624176</t>
   </si>
   <si>
     <t xml:space="preserve">0.33562046289444</t>
@@ -2285,55 +2285,55 @@
     <t xml:space="preserve">0.370228826999664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358156144618988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363790035247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420129209756851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424958318471909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437835872173309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444274574518204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445884257555008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482907176017761</t>
+    <t xml:space="preserve">0.358156114816666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363790065050125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420129239559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424958258867264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437835842370987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444274544715881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44588428735733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482907235622406</t>
   </si>
   <si>
     <t xml:space="preserve">0.560172319412231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527978539466858</t>
+    <t xml:space="preserve">0.527978479862213</t>
   </si>
   <si>
     <t xml:space="preserve">0.521539747714996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529588162899017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519930064678192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507052481174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500613689422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494174987077713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502223491668701</t>
+    <t xml:space="preserve">0.529588222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519930124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507052540779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500613749027252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49417507648468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502223432064056</t>
   </si>
   <si>
     <t xml:space="preserve">0.537636637687683</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">0.524759113788605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510271966457367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499004006385803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492565304040909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487736254930496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484516799449921</t>
+    <t xml:space="preserve">0.510271906852722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49900409579277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492565274238586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487736225128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484516859054565</t>
   </si>
   <si>
     <t xml:space="preserve">0.447493940591812</t>
@@ -2363,13 +2363,13 @@
     <t xml:space="preserve">0.431397080421448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449103713035583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436226159334183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393569320440292</t>
+    <t xml:space="preserve">0.449103683233261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436226099729538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393569350242615</t>
   </si>
   <si>
     <t xml:space="preserve">0.378277271986008</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">0.367009431123734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359765857458115</t>
+    <t xml:space="preserve">0.359765827655792</t>
   </si>
   <si>
     <t xml:space="preserve">0.376667588949203</t>
@@ -2393,46 +2393,46 @@
     <t xml:space="preserve">0.423348665237427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441055178642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505442917346954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468419969081879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461981207132339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465200543403625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45232304930687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455542385578156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450713366270065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460371494293213</t>
+    <t xml:space="preserve">0.441055208444595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50544285774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468419939279556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461981177330017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465200513601303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452323019504547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455542415380478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450713306665421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460371524095535</t>
   </si>
   <si>
     <t xml:space="preserve">0.457152128219604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453932791948318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47968778014183</t>
+    <t xml:space="preserve">0.453932702541351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479687750339508</t>
   </si>
   <si>
     <t xml:space="preserve">0.495784670114517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489345908164978</t>
+    <t xml:space="preserve">0.4893459379673</t>
   </si>
   <si>
     <t xml:space="preserve">0.547294795513153</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">0.575464367866516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569830477237701</t>
+    <t xml:space="preserve">0.569830417633057</t>
   </si>
   <si>
     <t xml:space="preserve">0.549709320068359</t>
@@ -2459,19 +2459,19 @@
     <t xml:space="preserve">0.545685112476349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558562576770782</t>
+    <t xml:space="preserve">0.558562636375427</t>
   </si>
   <si>
     <t xml:space="preserve">0.5440753698349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531197905540466</t>
+    <t xml:space="preserve">0.531197845935822</t>
   </si>
   <si>
     <t xml:space="preserve">0.559367418289185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573854565620422</t>
+    <t xml:space="preserve">0.573854625225067</t>
   </si>
   <si>
     <t xml:space="preserve">0.581903100013733</t>
@@ -2480,250 +2480,253 @@
     <t xml:space="preserve">0.579488635063171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544880211353302</t>
+    <t xml:space="preserve">0.544880270957947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552123844623566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548099637031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548904478549957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553733587265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582058310508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581226766109467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573743164539337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567091107368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574649333954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57291167974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561270475387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557944416999817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558775961399078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540482699871063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544640243053436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542977273464203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530504584312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531336069107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532167553901672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516368806362152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511379778385162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505559206008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508885204792023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502233147621155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51553738117218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498907178640366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493918001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494749635457993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500570118427277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48393988609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465646594762802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466478139162064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461489051580429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460657566785812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473961770534515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473130226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486434429883957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489760458469391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503064632415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50472766160965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506390750408173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51054835319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503896176815033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495581030845642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484771400690079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482276886701584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491423547267914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497244030237198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487265944480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493086487054825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483108371496201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478119343519211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475624799728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476456314325333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529672980308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523852467536926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528010010719299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533830583095551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527178525924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547966241836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528841495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525515496730804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526346981525421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554618418216705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588710367679596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575406193733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577069222927094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570417106151581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583721339702606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585384368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57790070772171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580395221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550460875034332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556281387805939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545471727848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567922592163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566259562969208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5571129322052</t>
   </si>
   <si>
     <t xml:space="preserve">0.552123785018921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548099637031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548904478549957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553733587265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582058310508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581226766109467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573743164539337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567091107368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574589729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57291167974472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561270534992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557944416999817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558775961399078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540482699871063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544640243053436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542977273464203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530504584312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531336069107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532167553901672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516368865966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511379778385162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505559146404266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508885204792023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502233147621155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515537321567535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498907119035721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493918001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494749575853348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500570118427277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48393988609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465646594762802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466478079557419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461489051580429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46065753698349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473961770534515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473130285739899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486434429883957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489760458469391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503064632415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50472766160965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506390690803528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510548293590546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503896176815033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495581090450287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484771400690079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482276886701584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491423547267914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497244030237198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487265944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493086487054825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483108341693878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478119343519211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475624799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476456254720688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529672980308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523852467536926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528010010719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533830583095551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527178525924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547966241836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528841495513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52551543712616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526347041130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554618358612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588710367679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57540625333786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577069222927094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570417106151581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583721339702606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585384428501129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57790070772171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58039528131485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550460815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556281447410583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545471727848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567922592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566259562969208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557112991809845</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.56459653377533</t>
   </si>
   <si>
     <t xml:space="preserve">0.549629330635071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539651155471802</t>
+    <t xml:space="preserve">0.539651215076447</t>
   </si>
   <si>
     <t xml:space="preserve">0.53632515668869</t>
@@ -2747,7 +2750,7 @@
     <t xml:space="preserve">0.513874351978302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522189497947693</t>
+    <t xml:space="preserve">0.522189438343048</t>
   </si>
   <si>
     <t xml:space="preserve">0.513042747974396</t>
@@ -2762,22 +2765,22 @@
     <t xml:space="preserve">0.519694864749908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508053779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488097488880157</t>
+    <t xml:space="preserve">0.508053719997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488097429275513</t>
   </si>
   <si>
     <t xml:space="preserve">0.488928943872452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492255032062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496412575244904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490591913461685</t>
+    <t xml:space="preserve">0.492254972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496412515640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49059197306633</t>
   </si>
   <si>
     <t xml:space="preserve">0.485602915287018</t>
@@ -2786,13 +2789,13 @@
     <t xml:space="preserve">0.480613797903061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474793195724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4540054500103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478950768709183</t>
+    <t xml:space="preserve">0.474793255329132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454005420207977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478950828313828</t>
   </si>
   <si>
     <t xml:space="preserve">0.458163022994995</t>
@@ -2804,7 +2807,7 @@
     <t xml:space="preserve">0.439869731664658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439038246870041</t>
+    <t xml:space="preserve">0.439038217067719</t>
   </si>
   <si>
     <t xml:space="preserve">0.419913470745087</t>
@@ -2816,7 +2819,7 @@
     <t xml:space="preserve">0.424071043729782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411598384380341</t>
+    <t xml:space="preserve">0.411598354578018</t>
   </si>
   <si>
     <t xml:space="preserve">0.41118261218071</t>
@@ -2825,16 +2828,16 @@
     <t xml:space="preserve">0.395799607038498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377090632915497</t>
+    <t xml:space="preserve">0.377090603113174</t>
   </si>
   <si>
     <t xml:space="preserve">0.365033686161041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402035981416702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413677155971527</t>
+    <t xml:space="preserve">0.40203595161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413677126169205</t>
   </si>
   <si>
     <t xml:space="preserve">0.407440811395645</t>
@@ -2843,7 +2846,7 @@
     <t xml:space="preserve">0.412429869174957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431554615497589</t>
+    <t xml:space="preserve">0.431554645299911</t>
   </si>
   <si>
     <t xml:space="preserve">0.429891616106033</t>
@@ -2858,7 +2861,7 @@
     <t xml:space="preserve">0.444027274847031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436543703079224</t>
+    <t xml:space="preserve">0.436543673276901</t>
   </si>
   <si>
     <t xml:space="preserve">0.443195819854736</t>
@@ -2867,7 +2870,7 @@
     <t xml:space="preserve">0.448184847831726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446521908044815</t>
+    <t xml:space="preserve">0.44652184844017</t>
   </si>
   <si>
     <t xml:space="preserve">0.440701246261597</t>
@@ -2885,28 +2888,28 @@
     <t xml:space="preserve">0.447353363037109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445690333843231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46315211057663</t>
+    <t xml:space="preserve">0.445690363645554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463152050971985</t>
   </si>
   <si>
     <t xml:space="preserve">0.481445372104645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477287858724594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470635652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437375247478485</t>
+    <t xml:space="preserve">0.477287799119949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470635682344437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437375277280807</t>
   </si>
   <si>
     <t xml:space="preserve">0.429060101509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421576529741287</t>
+    <t xml:space="preserve">0.421576499938965</t>
   </si>
   <si>
     <t xml:space="preserve">0.40993532538414</t>
@@ -2915,19 +2918,19 @@
     <t xml:space="preserve">0.430723130702972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427397072315216</t>
+    <t xml:space="preserve">0.427397102117538</t>
   </si>
   <si>
     <t xml:space="preserve">0.415755927562714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43321767449379</t>
+    <t xml:space="preserve">0.433217704296112</t>
   </si>
   <si>
     <t xml:space="preserve">0.452196657657623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446109443902969</t>
+    <t xml:space="preserve">0.446109414100647</t>
   </si>
   <si>
     <t xml:space="preserve">0.439152538776398</t>
@@ -2936,7 +2939,7 @@
     <t xml:space="preserve">0.431326061487198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423499554395676</t>
+    <t xml:space="preserve">0.423499584197998</t>
   </si>
   <si>
     <t xml:space="preserve">0.406542211771011</t>
@@ -2957,7 +2960,7 @@
     <t xml:space="preserve">0.383932381868362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388715237379074</t>
+    <t xml:space="preserve">0.388715207576752</t>
   </si>
   <si>
     <t xml:space="preserve">0.382627964019775</t>
@@ -2966,19 +2969,19 @@
     <t xml:space="preserve">0.380888730287552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387845605611801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393498033285141</t>
+    <t xml:space="preserve">0.387845635414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393498063087463</t>
   </si>
   <si>
     <t xml:space="preserve">0.379584342241287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384367197751999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378714740276337</t>
+    <t xml:space="preserve">0.384367167949677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378714710474014</t>
   </si>
   <si>
     <t xml:space="preserve">0.373931884765625</t>
@@ -2987,7 +2990,7 @@
     <t xml:space="preserve">0.372627437114716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37306222319603</t>
+    <t xml:space="preserve">0.373062252998352</t>
   </si>
   <si>
     <t xml:space="preserve">0.378279894590378</t>
@@ -3002,7 +3005,7 @@
     <t xml:space="preserve">0.366105407476425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371323049068451</t>
+    <t xml:space="preserve">0.371323019266129</t>
   </si>
   <si>
     <t xml:space="preserve">0.375671088695526</t>
@@ -3014,10 +3017,10 @@
     <t xml:space="preserve">0.370018631219864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367844581604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366975009441376</t>
+    <t xml:space="preserve">0.367844611406326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366974979639053</t>
   </si>
   <si>
     <t xml:space="preserve">0.364366173744202</t>
@@ -3029,7 +3032,7 @@
     <t xml:space="preserve">0.368714213371277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377410292625427</t>
+    <t xml:space="preserve">0.37741032242775</t>
   </si>
   <si>
     <t xml:space="preserve">0.36958384513855</t>
@@ -3041,10 +3044,10 @@
     <t xml:space="preserve">0.374801486730576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375236243009567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372192651033401</t>
+    <t xml:space="preserve">0.37523627281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372192680835724</t>
   </si>
   <si>
     <t xml:space="preserve">0.36523574590683</t>
@@ -3083,13 +3086,13 @@
     <t xml:space="preserve">0.396106898784637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399150550365448</t>
+    <t xml:space="preserve">0.399150520563126</t>
   </si>
   <si>
     <t xml:space="preserve">0.403498560190201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396541714668274</t>
+    <t xml:space="preserve">0.396541684865952</t>
   </si>
   <si>
     <t xml:space="preserve">0.392193675041199</t>
@@ -3098,13 +3101,13 @@
     <t xml:space="preserve">0.401759386062622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403933376073837</t>
+    <t xml:space="preserve">0.40393340587616</t>
   </si>
   <si>
     <t xml:space="preserve">0.408716231584549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400020152330399</t>
+    <t xml:space="preserve">0.400020182132721</t>
   </si>
   <si>
     <t xml:space="preserve">0.400889724493027</t>
@@ -3125,13 +3128,13 @@
     <t xml:space="preserve">0.390889227390289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395672082901001</t>
+    <t xml:space="preserve">0.395672112703323</t>
   </si>
   <si>
     <t xml:space="preserve">0.401324540376663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39697653055191</t>
+    <t xml:space="preserve">0.396976500749588</t>
   </si>
   <si>
     <t xml:space="preserve">0.400454938411713</t>
@@ -3143,10 +3146,10 @@
     <t xml:space="preserve">0.387410819530487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383497565984726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382193177938461</t>
+    <t xml:space="preserve">0.383497595787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382193148136139</t>
   </si>
   <si>
     <t xml:space="preserve">0.381758362054825</t>
@@ -3161,13 +3164,13 @@
     <t xml:space="preserve">0.366540193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360887736082077</t>
+    <t xml:space="preserve">0.360887706279755</t>
   </si>
   <si>
     <t xml:space="preserve">0.362626940011978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369149029254913</t>
+    <t xml:space="preserve">0.369148999452591</t>
   </si>
   <si>
     <t xml:space="preserve">0.379149526357651</t>
@@ -3176,10 +3179,10 @@
     <t xml:space="preserve">0.3861064016819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394367694854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404368221759796</t>
+    <t xml:space="preserve">0.394367665052414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404368191957474</t>
   </si>
   <si>
     <t xml:space="preserve">0.392628461122513</t>
@@ -3191,10 +3194,10 @@
     <t xml:space="preserve">0.395237267017365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385671585798264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394802510738373</t>
+    <t xml:space="preserve">0.385671615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39480248093605</t>
   </si>
   <si>
     <t xml:space="preserve">0.388280391693115</t>
@@ -3234,9 +3237,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.402952283620834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396541684865952</t>
   </si>
   <si>
     <t xml:space="preserve">0.402036517858505</t>
@@ -42963,7 +42963,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1494" t="s">
-        <v>823</v>
+        <v>901</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -42989,7 +42989,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1495" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43015,7 +43015,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G1496" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43041,7 +43041,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G1497" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43067,7 +43067,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G1498" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43093,7 +43093,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G1499" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43171,7 +43171,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G1502" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43197,7 +43197,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G1503" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43249,7 +43249,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1505" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43275,7 +43275,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G1506" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43301,7 +43301,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1507" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43327,7 +43327,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G1508" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43405,7 +43405,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1511" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43431,7 +43431,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G1512" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43457,7 +43457,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G1513" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43483,7 +43483,7 @@
         <v>0.616999983787537</v>
       </c>
       <c r="G1514" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43509,7 +43509,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1515" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43587,7 +43587,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G1518" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43613,7 +43613,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1519" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43639,7 +43639,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1520" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43665,7 +43665,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1521" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43691,7 +43691,7 @@
         <v>0.616999983787537</v>
       </c>
       <c r="G1522" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43743,7 +43743,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G1524" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43769,7 +43769,7 @@
         <v>0.625</v>
       </c>
       <c r="G1525" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43821,7 +43821,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G1527" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43977,7 +43977,7 @@
         <v>0.616999983787537</v>
       </c>
       <c r="G1533" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44003,7 +44003,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G1534" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44029,7 +44029,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1535" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44081,7 +44081,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G1537" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44133,7 +44133,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1539" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44237,7 +44237,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G1543" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44315,7 +44315,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1546" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44367,7 +44367,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1548" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44393,7 +44393,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1549" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44445,7 +44445,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1551" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44471,7 +44471,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1552" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44497,7 +44497,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1553" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44575,7 +44575,7 @@
         <v>0.570999979972839</v>
       </c>
       <c r="G1556" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44601,7 +44601,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44653,7 +44653,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G1559" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44705,7 +44705,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G1561" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44731,7 +44731,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1562" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44757,7 +44757,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1563" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44783,7 +44783,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G1564" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44809,7 +44809,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1565" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44835,7 +44835,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G1566" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44861,7 +44861,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1567" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44887,7 +44887,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1568" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44913,7 +44913,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G1569" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44939,7 +44939,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1570" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44965,7 +44965,7 @@
         <v>0.453500002622604</v>
       </c>
       <c r="G1571" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44991,7 +44991,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1572" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45017,7 +45017,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45043,7 +45043,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G1574" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45069,7 +45069,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1575" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45095,7 +45095,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1576" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45121,7 +45121,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G1577" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45147,7 +45147,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1578" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45173,7 +45173,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G1579" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45199,7 +45199,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1580" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45225,7 +45225,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G1581" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45251,7 +45251,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1582" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45277,7 +45277,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1583" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45303,7 +45303,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G1584" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45329,7 +45329,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1585" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45355,7 +45355,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45381,7 +45381,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1587" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45407,7 +45407,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G1588" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45433,7 +45433,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1589" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45459,7 +45459,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G1590" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45485,7 +45485,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G1591" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45511,7 +45511,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1592" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -45537,7 +45537,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45563,7 +45563,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1594" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45589,7 +45589,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1595" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45615,7 +45615,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1596" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -45641,7 +45641,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1597" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45667,7 +45667,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1598" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -45693,7 +45693,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1599" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45719,7 +45719,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1600" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45745,7 +45745,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G1601" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45771,7 +45771,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G1602" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45849,7 +45849,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1605" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45875,7 +45875,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G1606" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45901,7 +45901,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1607" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45927,7 +45927,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1608" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45953,7 +45953,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1609" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -45979,7 +45979,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1610" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46005,7 +46005,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1611" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -46031,7 +46031,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1612" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46057,7 +46057,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1613" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -46083,7 +46083,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1614" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -46109,7 +46109,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1615" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46135,7 +46135,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1616" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -46161,7 +46161,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G1617" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46187,7 +46187,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1618" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46213,7 +46213,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G1619" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46239,7 +46239,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1620" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46265,7 +46265,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1621" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46291,7 +46291,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1622" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46317,7 +46317,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1623" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46343,7 +46343,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1624" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46369,7 +46369,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1625" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46395,7 +46395,7 @@
         <v>0.5</v>
       </c>
       <c r="G1626" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46421,7 +46421,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1627" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46447,7 +46447,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1628" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46473,7 +46473,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1629" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46499,7 +46499,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1630" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46525,7 +46525,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1631" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46551,7 +46551,7 @@
         <v>0.521000027656555</v>
       </c>
       <c r="G1632" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46577,7 +46577,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1633" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46603,7 +46603,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1634" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46629,7 +46629,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46655,7 +46655,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1636" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46681,7 +46681,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1637" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46707,7 +46707,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1638" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46733,7 +46733,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G1639" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46759,7 +46759,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1640" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46785,7 +46785,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1641" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46811,7 +46811,7 @@
         <v>0.476500004529953</v>
       </c>
       <c r="G1642" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46837,7 +46837,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G1643" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46863,7 +46863,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1644" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46889,7 +46889,7 @@
         <v>0.441500008106232</v>
       </c>
       <c r="G1645" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46915,7 +46915,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G1646" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46941,7 +46941,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1647" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46967,7 +46967,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1648" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -46993,7 +46993,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1649" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47019,7 +47019,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G1650" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47045,7 +47045,7 @@
         <v>0.452499985694885</v>
       </c>
       <c r="G1651" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47071,7 +47071,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1652" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47097,7 +47097,7 @@
         <v>0.436500012874603</v>
       </c>
       <c r="G1653" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47123,7 +47123,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1654" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47149,7 +47149,7 @@
         <v>0.435499995946884</v>
       </c>
       <c r="G1655" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47175,7 +47175,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1656" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47201,7 +47201,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1657" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47227,7 +47227,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1658" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47253,7 +47253,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1659" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47279,7 +47279,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1660" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47305,7 +47305,7 @@
         <v>0.426499992609024</v>
       </c>
       <c r="G1661" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47331,7 +47331,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1662" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47357,7 +47357,7 @@
         <v>0.415499985218048</v>
       </c>
       <c r="G1663" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47383,7 +47383,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1664" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47409,7 +47409,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1665" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47435,7 +47435,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1666" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47461,7 +47461,7 @@
         <v>0.430500000715256</v>
       </c>
       <c r="G1667" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47487,7 +47487,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1668" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47513,7 +47513,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1669" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47539,7 +47539,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1670" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -47565,7 +47565,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1671" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -47591,7 +47591,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1672" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -47617,7 +47617,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1673" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -47643,7 +47643,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1674" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -47669,7 +47669,7 @@
         <v>0.436500012874603</v>
       </c>
       <c r="G1675" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -47695,7 +47695,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1676" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47721,7 +47721,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1677" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -47747,7 +47747,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1678" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47773,7 +47773,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1679" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -47799,7 +47799,7 @@
         <v>0.430500000715256</v>
       </c>
       <c r="G1680" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47825,7 +47825,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1681" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47851,7 +47851,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1682" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -47877,7 +47877,7 @@
         <v>0.434500008821487</v>
       </c>
       <c r="G1683" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -47903,7 +47903,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1684" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -47929,7 +47929,7 @@
         <v>0.436500012874603</v>
       </c>
       <c r="G1685" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -47955,7 +47955,7 @@
         <v>0.426499992609024</v>
       </c>
       <c r="G1686" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47981,7 +47981,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1687" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48007,7 +48007,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1688" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48033,7 +48033,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1689" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48059,7 +48059,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1690" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48085,7 +48085,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1691" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48111,7 +48111,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1692" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -48137,7 +48137,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1693" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -48163,7 +48163,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1694" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48189,7 +48189,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1695" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48215,7 +48215,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1696" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48241,7 +48241,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1697" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48267,7 +48267,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1698" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48293,7 +48293,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1699" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48319,7 +48319,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1700" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48345,7 +48345,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1701" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48371,7 +48371,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1702" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48397,7 +48397,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1703" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -48423,7 +48423,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1704" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48449,7 +48449,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1705" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48475,7 +48475,7 @@
         <v>0.434500008821487</v>
       </c>
       <c r="G1706" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -48501,7 +48501,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1707" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48527,7 +48527,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1708" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -48553,7 +48553,7 @@
         <v>0.438499987125397</v>
       </c>
       <c r="G1709" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48579,7 +48579,7 @@
         <v>0.438499987125397</v>
       </c>
       <c r="G1710" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -48605,7 +48605,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1711" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48631,7 +48631,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1712" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -48657,7 +48657,7 @@
         <v>0.422500014305115</v>
       </c>
       <c r="G1713" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -48683,7 +48683,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1714" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -48709,7 +48709,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1715" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -48735,7 +48735,7 @@
         <v>0.433499991893768</v>
       </c>
       <c r="G1716" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -48761,7 +48761,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1717" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48787,7 +48787,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1718" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48813,7 +48813,7 @@
         <v>0.41949999332428</v>
       </c>
       <c r="G1719" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48839,7 +48839,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1720" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48865,7 +48865,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1721" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48891,7 +48891,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1722" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48917,7 +48917,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G1723" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48943,7 +48943,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G1724" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48969,7 +48969,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1725" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48995,7 +48995,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1726" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49021,7 +49021,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1727" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49047,7 +49047,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1728" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49073,7 +49073,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G1729" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49099,7 +49099,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1730" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49125,7 +49125,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G1731" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -49151,7 +49151,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1732" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -49177,7 +49177,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1733" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -49203,7 +49203,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1734" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -49229,7 +49229,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1735" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49255,7 +49255,7 @@
         <v>0.46450001001358</v>
       </c>
       <c r="G1736" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49281,7 +49281,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1737" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49307,7 +49307,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1738" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49333,7 +49333,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1739" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49359,7 +49359,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G1740" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49385,7 +49385,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1741" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -49411,7 +49411,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1742" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49437,7 +49437,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1743" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49463,7 +49463,7 @@
         <v>0.447499990463257</v>
       </c>
       <c r="G1744" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -49489,7 +49489,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1745" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49515,7 +49515,7 @@
         <v>0.449499994516373</v>
       </c>
       <c r="G1746" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49541,7 +49541,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G1747" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49567,7 +49567,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1748" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -49593,7 +49593,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1749" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -49619,7 +49619,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G1750" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49645,7 +49645,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1751" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49671,7 +49671,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1752" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49697,7 +49697,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G1753" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49723,7 +49723,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1754" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49749,7 +49749,7 @@
         <v>0.460500001907349</v>
       </c>
       <c r="G1755" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49775,7 +49775,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G1756" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49801,7 +49801,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1757" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49827,7 +49827,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1758" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49853,7 +49853,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1759" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49879,7 +49879,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1760" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49905,7 +49905,7 @@
         <v>0.445499986410141</v>
       </c>
       <c r="G1761" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49931,7 +49931,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1762" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49957,7 +49957,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1763" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49983,7 +49983,7 @@
         <v>0.439500004053116</v>
       </c>
       <c r="G1764" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50009,7 +50009,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1765" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50035,7 +50035,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1766" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50061,7 +50061,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1767" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50087,7 +50087,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1768" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50113,7 +50113,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1769" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50139,7 +50139,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1770" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50165,7 +50165,7 @@
         <v>0.427500009536743</v>
       </c>
       <c r="G1771" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50191,7 +50191,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1772" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -50217,7 +50217,7 @@
         <v>0.411500006914139</v>
       </c>
       <c r="G1773" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50243,7 +50243,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1774" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50269,7 +50269,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1775" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50295,7 +50295,7 @@
         <v>0.41949999332428</v>
       </c>
       <c r="G1776" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50321,7 +50321,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1777" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50347,7 +50347,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1778" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50373,7 +50373,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1779" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50399,7 +50399,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1780" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50425,7 +50425,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1781" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -50451,7 +50451,7 @@
         <v>0.424499988555908</v>
       </c>
       <c r="G1782" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50477,7 +50477,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1783" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50503,7 +50503,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1784" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50529,7 +50529,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1785" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50555,7 +50555,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1786" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50581,7 +50581,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1787" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50607,7 +50607,7 @@
         <v>0.445499986410141</v>
       </c>
       <c r="G1788" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -50633,7 +50633,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1789" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50659,7 +50659,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1790" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50685,7 +50685,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1791" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50711,7 +50711,7 @@
         <v>0.453500002622604</v>
       </c>
       <c r="G1792" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50737,7 +50737,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G1793" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -50763,7 +50763,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1794" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50789,7 +50789,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1795" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50815,7 +50815,7 @@
         <v>0.451499998569489</v>
       </c>
       <c r="G1796" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50841,7 +50841,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1797" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50867,7 +50867,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1798" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50893,7 +50893,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G1799" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50919,7 +50919,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1800" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50945,7 +50945,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G1801" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50971,7 +50971,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1802" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50997,7 +50997,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1803" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51023,7 +51023,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1804" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51049,7 +51049,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1805" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51075,7 +51075,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1806" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51101,7 +51101,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1807" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51127,7 +51127,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1808" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51153,7 +51153,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1809" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51179,7 +51179,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1810" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51205,7 +51205,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G1811" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51231,7 +51231,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1812" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51257,7 +51257,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1813" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51283,7 +51283,7 @@
         <v>0.450500011444092</v>
       </c>
       <c r="G1814" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51309,7 +51309,7 @@
         <v>0.450500011444092</v>
       </c>
       <c r="G1815" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51335,7 +51335,7 @@
         <v>0.454499989748001</v>
       </c>
       <c r="G1816" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51361,7 +51361,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1817" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51387,7 +51387,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1818" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51413,7 +51413,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1819" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51439,7 +51439,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1820" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51465,7 +51465,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1821" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51491,7 +51491,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1822" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51517,7 +51517,7 @@
         <v>0.441500008106232</v>
       </c>
       <c r="G1823" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51543,7 +51543,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1824" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51569,7 +51569,7 @@
         <v>0.443500012159348</v>
       </c>
       <c r="G1825" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51595,7 +51595,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G1826" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51621,7 +51621,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1827" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51647,7 +51647,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1828" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51673,7 +51673,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1829" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51699,7 +51699,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G1830" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51725,7 +51725,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51751,7 +51751,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1832" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51777,7 +51777,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1833" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51803,7 +51803,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1834" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51829,7 +51829,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1835" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51855,7 +51855,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1836" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -51881,7 +51881,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1837" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -51907,7 +51907,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1838" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51933,7 +51933,7 @@
         <v>0.44650000333786</v>
       </c>
       <c r="G1839" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -51959,7 +51959,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1840" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -51985,7 +51985,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1841" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52011,7 +52011,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1842" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52037,7 +52037,7 @@
         <v>0.434500008821487</v>
       </c>
       <c r="G1843" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52063,7 +52063,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1844" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52089,7 +52089,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1845" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52115,7 +52115,7 @@
         <v>0.439500004053116</v>
       </c>
       <c r="G1846" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52141,7 +52141,7 @@
         <v>0.445499986410141</v>
       </c>
       <c r="G1847" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52167,7 +52167,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1848" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52193,7 +52193,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1849" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52219,7 +52219,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1850" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52245,7 +52245,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1851" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52271,7 +52271,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1852" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52297,7 +52297,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1853" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52323,7 +52323,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1854" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52349,7 +52349,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1855" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52375,7 +52375,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1856" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52401,7 +52401,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1857" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52427,7 +52427,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1858" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52453,7 +52453,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G1859" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52479,7 +52479,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1860" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52505,7 +52505,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1861" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52531,7 +52531,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1862" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52557,7 +52557,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G1863" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52583,7 +52583,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G1864" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52609,7 +52609,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1865" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52635,7 +52635,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1866" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52661,7 +52661,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1867" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52687,7 +52687,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1868" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52713,7 +52713,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1869" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52739,7 +52739,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1870" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52765,7 +52765,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1871" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52791,7 +52791,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1872" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52817,7 +52817,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1873" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52843,7 +52843,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1874" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -52869,7 +52869,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1875" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52895,7 +52895,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1876" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52921,7 +52921,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1877" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52947,7 +52947,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1878" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52973,7 +52973,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1879" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52999,7 +52999,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1880" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53025,7 +53025,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1881" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53051,7 +53051,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1882" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53077,7 +53077,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1883" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53103,7 +53103,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1884" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53129,7 +53129,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1885" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53155,7 +53155,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1886" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53181,7 +53181,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1887" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53207,7 +53207,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1888" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53233,7 +53233,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1889" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53259,7 +53259,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1890" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53285,7 +53285,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1891" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -53311,7 +53311,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1892" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53337,7 +53337,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1893" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53363,7 +53363,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1894" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53389,7 +53389,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1895" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53415,7 +53415,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1896" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53441,7 +53441,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1897" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53467,7 +53467,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G1898" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53493,7 +53493,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1899" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53519,7 +53519,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1900" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53545,7 +53545,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1901" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53571,7 +53571,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1902" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53597,7 +53597,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1903" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -53623,7 +53623,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1904" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53649,7 +53649,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1905" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53675,7 +53675,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1906" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -53701,7 +53701,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1907" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -53727,7 +53727,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1908" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -53753,7 +53753,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1909" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53779,7 +53779,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1910" t="s">
-        <v>1074</v>
+        <v>1026</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53831,7 +53831,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1912" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54247,7 +54247,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1928" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -54819,7 +54819,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1950" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54845,7 +54845,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1951" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54871,7 +54871,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1952" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54897,7 +54897,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1953" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54923,7 +54923,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1954" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54975,7 +54975,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1956" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55001,7 +55001,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1957" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -55027,7 +55027,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1958" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -55053,7 +55053,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1959" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -55079,7 +55079,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1960" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -55105,7 +55105,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1961" t="s">
-        <v>1074</v>
+        <v>1026</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55131,7 +55131,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1962" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55157,7 +55157,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1963" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56587,7 +56587,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2018" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57263,7 +57263,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2044" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57315,7 +57315,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2046" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -57341,7 +57341,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2047" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -57367,7 +57367,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2048" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -57393,7 +57393,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2049" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -57419,7 +57419,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2050" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -57445,7 +57445,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2051" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -57471,7 +57471,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2052" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57549,7 +57549,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2055" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -57575,7 +57575,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2056" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -57601,7 +57601,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2057" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57627,7 +57627,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2058" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57653,7 +57653,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2059" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57679,7 +57679,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2060" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57705,7 +57705,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2061" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -57757,7 +57757,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2063" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57887,7 +57887,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2068" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57939,7 +57939,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2070" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57965,7 +57965,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2071" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57991,7 +57991,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2072" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58017,7 +58017,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2073" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58043,7 +58043,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2074" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -58069,7 +58069,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2075" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58095,7 +58095,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2076" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58121,7 +58121,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2077" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -58147,7 +58147,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2078" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -58173,7 +58173,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2079" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58225,7 +58225,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2081" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58433,7 +58433,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2089" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -58459,7 +58459,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2090" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58485,7 +58485,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2091" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58511,7 +58511,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2092" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58537,7 +58537,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2093" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58693,7 +58693,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2099" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -58719,7 +58719,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2100" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -58745,7 +58745,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2101" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -58771,7 +58771,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2102" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58927,7 +58927,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2108" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58953,7 +58953,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2109" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58979,7 +58979,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2110" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59005,7 +59005,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2111" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59031,7 +59031,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2112" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59057,7 +59057,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2113" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59083,7 +59083,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2114" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59109,7 +59109,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2115" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59135,7 +59135,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2116" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59161,7 +59161,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2117" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -68841,7 +68841,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6493287037</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>115953</v>
@@ -68850,7 +68850,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="D2490" t="n">
-        <v>0.453999996185303</v>
+        <v>0.453000009059906</v>
       </c>
       <c r="E2490" t="n">
         <v>0.458000004291534</v>
@@ -68862,6 +68862,32 @@
         <v>1258</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6495486111</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>159494</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>0.458999991416931</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>0.453000009059906</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>0.458999991416931</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>0.456999987363815</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32635235786438</t>
+    <t xml:space="preserve">0.326352387666702</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844811439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323679059743881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980766296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313056290149689</t>
+    <t xml:space="preserve">0.326844781637192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323679089546204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980736494064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313056260347366</t>
   </si>
   <si>
     <t xml:space="preserve">0.304966032505035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299760162830353</t>
+    <t xml:space="preserve">0.299760192632675</t>
   </si>
   <si>
     <t xml:space="preserve">0.309538781642914</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">0.302503824234009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287097185850143</t>
+    <t xml:space="preserve">0.287097215652466</t>
   </si>
   <si>
     <t xml:space="preserve">0.274363905191422</t>
@@ -77,70 +77,70 @@
     <t xml:space="preserve">0.278655260801315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265288770198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260645747184753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270846396684647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269087642431259</t>
+    <t xml:space="preserve">0.265288829803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260645717382431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270846426486969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269087672233582</t>
   </si>
   <si>
     <t xml:space="preserve">0.272956907749176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270142942667007</t>
+    <t xml:space="preserve">0.270142883062363</t>
   </si>
   <si>
     <t xml:space="preserve">0.265921980142593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290825754404068</t>
+    <t xml:space="preserve">0.290825724601746</t>
   </si>
   <si>
     <t xml:space="preserve">0.288433849811554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294061869382858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276404023170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273167937994003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262545138597488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260293990373611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246927514672279</t>
+    <t xml:space="preserve">0.294061839580536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276404052972794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273167967796326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262545168399811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260293960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246927559375763</t>
   </si>
   <si>
     <t xml:space="preserve">0.246224015951157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239751860499382</t>
+    <t xml:space="preserve">0.239751875400543</t>
   </si>
   <si>
     <t xml:space="preserve">0.240103632211685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271549940109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276122719049454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274645328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277881413698196</t>
+    <t xml:space="preserve">0.271549969911575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276122659444809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274645298719406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277881383895874</t>
   </si>
   <si>
     <t xml:space="preserve">0.270987123250961</t>
@@ -152,49 +152,49 @@
     <t xml:space="preserve">0.277177900075912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26331901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2680324614048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282102406024933</t>
+    <t xml:space="preserve">0.263319045305252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268032431602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28210237622261</t>
   </si>
   <si>
     <t xml:space="preserve">0.295468837022781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29335829615593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291740298271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288644939661026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504213094711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281469225883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27724826335907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278373897075653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287026852369308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297368258237839</t>
+    <t xml:space="preserve">0.293358325958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291740268468857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288644880056381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504183292389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281469166278839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277248233556747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278373867273331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287026882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297368288040161</t>
   </si>
   <si>
     <t xml:space="preserve">0.295820564031601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30721727013588</t>
+    <t xml:space="preserve">0.307217210531235</t>
   </si>
   <si>
     <t xml:space="preserve">0.305669546127319</t>
@@ -203,88 +203,88 @@
     <t xml:space="preserve">0.31375977396965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320442974567413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317417979240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316573739051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306161999702454</t>
+    <t xml:space="preserve">0.320443004369736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317417919635773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316573709249496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306161969900131</t>
   </si>
   <si>
     <t xml:space="preserve">0.310945779085159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311438232660294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301800310611725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288011789321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288082093000412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280554711818695</t>
+    <t xml:space="preserve">0.311438202857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301800280809402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288011759519577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288082122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28055465221405</t>
   </si>
   <si>
     <t xml:space="preserve">0.281328529119492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291881024837494</t>
+    <t xml:space="preserve">0.291880965232849</t>
   </si>
   <si>
     <t xml:space="preserve">0.301378220319748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311649262905121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310242265462875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311508536338806</t>
+    <t xml:space="preserve">0.311649233102798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310242295265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311508566141129</t>
   </si>
   <si>
     <t xml:space="preserve">0.314533621072769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316644072532654</t>
+    <t xml:space="preserve">0.316644132137299</t>
   </si>
   <si>
     <t xml:space="preserve">0.318684250116348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330573409795761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330643713474274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334161192178726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333528012037277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330432623624802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327126204967499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323538392782211</t>
+    <t xml:space="preserve">0.330573320388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330643683671951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334161162376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3335280418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330432653427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327126234769821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323538362979889</t>
   </si>
   <si>
     <t xml:space="preserve">0.318543553352356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319247007369995</t>
+    <t xml:space="preserve">0.319247037172318</t>
   </si>
   <si>
     <t xml:space="preserve">0.323116272687912</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">0.324875026941299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323749452829361</t>
+    <t xml:space="preserve">0.323749482631683</t>
   </si>
   <si>
     <t xml:space="preserve">0.325015723705292</t>
@@ -305,43 +305,43 @@
     <t xml:space="preserve">0.321076154708862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326774448156357</t>
+    <t xml:space="preserve">0.326774477958679</t>
   </si>
   <si>
     <t xml:space="preserve">0.331769287586212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344713598489761</t>
+    <t xml:space="preserve">0.344713658094406</t>
   </si>
   <si>
     <t xml:space="preserve">0.342040359973907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338030427694321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352100342512131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354914337396622</t>
+    <t xml:space="preserve">0.338030457496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352100431919098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354914277791977</t>
   </si>
   <si>
     <t xml:space="preserve">0.351678252220154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350341588258743</t>
+    <t xml:space="preserve">0.350341618061066</t>
   </si>
   <si>
     <t xml:space="preserve">0.343306660652161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343165963888168</t>
+    <t xml:space="preserve">0.343165904283524</t>
   </si>
   <si>
     <t xml:space="preserve">0.341196149587631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34021121263504</t>
+    <t xml:space="preserve">0.340211242437363</t>
   </si>
   <si>
     <t xml:space="preserve">0.337045550346375</t>
@@ -359,73 +359,73 @@
     <t xml:space="preserve">0.308890819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31193619966507</t>
+    <t xml:space="preserve">0.311936229467392</t>
   </si>
   <si>
     <t xml:space="preserve">0.325277984142303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322232604026794</t>
+    <t xml:space="preserve">0.322232574224472</t>
   </si>
   <si>
     <t xml:space="preserve">0.318607091903687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324190348386765</t>
+    <t xml:space="preserve">0.324190318584442</t>
   </si>
   <si>
     <t xml:space="preserve">0.30722314119339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299102008342743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299464553594589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313096404075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320854932069778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318027049303055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319042146205902</t>
+    <t xml:space="preserve">0.299102038145065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299464583396912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3130963742733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320854961872101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318027019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319042176008224</t>
   </si>
   <si>
     <t xml:space="preserve">0.318317055702209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309543371200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311791241168976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310558527708054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311066120862961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322087615728378</t>
+    <t xml:space="preserve">0.309543401002884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311791211366653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310558557510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311066091060638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322087585926056</t>
   </si>
   <si>
     <t xml:space="preserve">0.319767266511917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318172067403793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309978485107422</t>
+    <t xml:space="preserve">0.318172037601471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309978455305099</t>
   </si>
   <si>
     <t xml:space="preserve">0.306715548038483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305627912282944</t>
+    <t xml:space="preserve">0.305627882480621</t>
   </si>
   <si>
     <t xml:space="preserve">0.30178490281105</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">0.298014402389526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29148855805397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294316381216049</t>
+    <t xml:space="preserve">0.291488528251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294316411018372</t>
   </si>
   <si>
     <t xml:space="preserve">0.304467737674713</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">0.30381515622139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300624758005142</t>
+    <t xml:space="preserve">0.30062472820282</t>
   </si>
   <si>
     <t xml:space="preserve">0.29743430018425</t>
@@ -476,22 +476,22 @@
     <t xml:space="preserve">0.302364945411682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300117135047913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302219897508621</t>
+    <t xml:space="preserve">0.300117164850235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302219927310944</t>
   </si>
   <si>
     <t xml:space="preserve">0.297144263982773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295621544122696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293663799762726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297289282083511</t>
+    <t xml:space="preserve">0.295621573925018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293663829565048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297289311885834</t>
   </si>
   <si>
     <t xml:space="preserve">0.291706055402756</t>
@@ -500,19 +500,19 @@
     <t xml:space="preserve">0.292358636856079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29003831744194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287500470876694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292648673057556</t>
+    <t xml:space="preserve">0.290038347244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287500500679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292648702859879</t>
   </si>
   <si>
     <t xml:space="preserve">0.287645488977432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295041471719742</t>
+    <t xml:space="preserve">0.295041501522064</t>
   </si>
   <si>
     <t xml:space="preserve">0.291561037302017</t>
@@ -524,25 +524,25 @@
     <t xml:space="preserve">0.289313226938248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287935554981232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283004879951477</t>
+    <t xml:space="preserve">0.287935525178909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283004909753799</t>
   </si>
   <si>
     <t xml:space="preserve">0.287427991628647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282859891653061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275826424360275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279161870479584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26973569393158</t>
+    <t xml:space="preserve">0.282859861850739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27582648396492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279161900281906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269735664129257</t>
   </si>
   <si>
     <t xml:space="preserve">0.273288607597351</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">0.282062262296677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283802479505539</t>
+    <t xml:space="preserve">0.283802509307861</t>
   </si>
   <si>
     <t xml:space="preserve">0.282134771347046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28713795542717</t>
+    <t xml:space="preserve">0.287137925624847</t>
   </si>
   <si>
     <t xml:space="preserve">0.292866200208664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301422327756882</t>
+    <t xml:space="preserve">0.301422387361526</t>
   </si>
   <si>
     <t xml:space="preserve">0.295839101076126</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">0.300262123346329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297071754932404</t>
+    <t xml:space="preserve">0.297071784734726</t>
   </si>
   <si>
     <t xml:space="preserve">0.292938739061356</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">0.296056658029556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31019601225853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306425511837006</t>
+    <t xml:space="preserve">0.310195982456207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306425452232361</t>
   </si>
   <si>
     <t xml:space="preserve">0.302509963512421</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">0.306062936782837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307078152894974</t>
+    <t xml:space="preserve">0.307078093290329</t>
   </si>
   <si>
     <t xml:space="preserve">0.301639884710312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294098883867264</t>
+    <t xml:space="preserve">0.294098854064941</t>
   </si>
   <si>
     <t xml:space="preserve">0.283077418804169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287863045930862</t>
+    <t xml:space="preserve">0.287863105535507</t>
   </si>
   <si>
     <t xml:space="preserve">0.289603263139725</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">0.283947557210922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288805693387985</t>
+    <t xml:space="preserve">0.288805663585663</t>
   </si>
   <si>
     <t xml:space="preserve">0.293736338615417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290835916996002</t>
+    <t xml:space="preserve">0.290835946798325</t>
   </si>
   <si>
     <t xml:space="preserve">0.283512473106384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281409680843353</t>
+    <t xml:space="preserve">0.281409710645676</t>
   </si>
   <si>
     <t xml:space="preserve">0.280684620141983</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">0.279016852378845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796200752258</t>
+    <t xml:space="preserve">0.273796170949936</t>
   </si>
   <si>
     <t xml:space="preserve">0.291416019201279</t>
@@ -656,91 +656,91 @@
     <t xml:space="preserve">0.295113980770111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290545910596848</t>
+    <t xml:space="preserve">0.290545880794525</t>
   </si>
   <si>
     <t xml:space="preserve">0.288588136434555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292213618755341</t>
+    <t xml:space="preserve">0.292213648557663</t>
   </si>
   <si>
     <t xml:space="preserve">0.292141139507294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294388890266418</t>
+    <t xml:space="preserve">0.294388860464096</t>
   </si>
   <si>
     <t xml:space="preserve">0.299392074346542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296491682529449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303597629070282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309615939855576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307440638542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319187134504318</t>
+    <t xml:space="preserve">0.296491652727127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30359759926796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309615910053253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307440608739853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319187194108963</t>
   </si>
   <si>
     <t xml:space="preserve">0.331513792276382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331368774175644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345000594854355</t>
+    <t xml:space="preserve">0.331368803977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345000624656677</t>
   </si>
   <si>
     <t xml:space="preserve">0.349786221981049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358342379331589</t>
+    <t xml:space="preserve">0.358342349529266</t>
   </si>
   <si>
     <t xml:space="preserve">0.354209333658218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349641233682632</t>
+    <t xml:space="preserve">0.34964120388031</t>
   </si>
   <si>
     <t xml:space="preserve">0.352396577596664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355296909809113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35943004488945</t>
+    <t xml:space="preserve">0.355296939611435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359430015087128</t>
   </si>
   <si>
     <t xml:space="preserve">0.352686613798141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346885800361633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343187868595123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346160739660263</t>
+    <t xml:space="preserve">0.346885830163956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343187808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346160769462585</t>
   </si>
   <si>
     <t xml:space="preserve">0.346595793962479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34645077586174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344347983598709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350221276283264</t>
+    <t xml:space="preserve">0.346450805664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344348043203354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350221306085587</t>
   </si>
   <si>
     <t xml:space="preserve">0.350946366786957</t>
@@ -749,22 +749,22 @@
     <t xml:space="preserve">0.388288766145706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397715032100677</t>
+    <t xml:space="preserve">0.397715061903</t>
   </si>
   <si>
     <t xml:space="preserve">0.379950225353241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382125556468964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37487456202507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373424351215363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377412408590317</t>
+    <t xml:space="preserve">0.382125526666641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374874591827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37342432141304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377412378787994</t>
   </si>
   <si>
     <t xml:space="preserve">0.373061835765839</t>
@@ -773,31 +773,31 @@
     <t xml:space="preserve">0.369798868894577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383575677871704</t>
+    <t xml:space="preserve">0.383575707674026</t>
   </si>
   <si>
     <t xml:space="preserve">0.369436353445053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369073778390884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35819736123085</t>
+    <t xml:space="preserve">0.369073808193207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358197331428528</t>
   </si>
   <si>
     <t xml:space="preserve">0.358052343130112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377049833536148</t>
+    <t xml:space="preserve">0.377049803733826</t>
   </si>
   <si>
     <t xml:space="preserve">0.412579566240311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382488071918488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400615483522415</t>
+    <t xml:space="preserve">0.38248798251152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40061542391777</t>
   </si>
   <si>
     <t xml:space="preserve">0.394452124834061</t>
@@ -806,58 +806,58 @@
     <t xml:space="preserve">0.385751008987427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39372706413269</t>
+    <t xml:space="preserve">0.393727034330368</t>
   </si>
   <si>
     <t xml:space="preserve">0.390464097261429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384300768375397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39155176281929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387563705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390826612710953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395177215337753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393364489078522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397352486848831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398802697658539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3955397605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396627396345139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39844012260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395902335643768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393001943826675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398077607154846</t>
+    <t xml:space="preserve">0.384300708770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391551792621613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387563735246658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390826642513275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395177245140076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393364518880844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397352516651154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398802727460861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395539730787277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396627366542816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398440152406693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395902305841446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393001973628998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398077636957169</t>
   </si>
   <si>
     <t xml:space="preserve">0.401703089475632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39227682352066</t>
+    <t xml:space="preserve">0.392276853322983</t>
   </si>
   <si>
     <t xml:space="preserve">0.387201189994812</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">0.386476069688797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382850646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394089579582214</t>
+    <t xml:space="preserve">0.382850617170334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39408951997757</t>
   </si>
   <si>
     <t xml:space="preserve">0.389376431703568</t>
@@ -881,28 +881,28 @@
     <t xml:space="preserve">0.381037890911102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386838644742966</t>
+    <t xml:space="preserve">0.386838614940643</t>
   </si>
   <si>
     <t xml:space="preserve">0.388651341199875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385025888681412</t>
+    <t xml:space="preserve">0.385025858879089</t>
   </si>
   <si>
     <t xml:space="preserve">0.391189217567444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392639368772507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4256312251091</t>
+    <t xml:space="preserve">0.392639398574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425631284713745</t>
   </si>
   <si>
     <t xml:space="preserve">0.419105410575867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445208877325058</t>
+    <t xml:space="preserve">0.445208936929703</t>
   </si>
   <si>
     <t xml:space="preserve">0.435057520866394</t>
@@ -911,28 +911,28 @@
     <t xml:space="preserve">0.442308515310287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432612031698227</t>
+    <t xml:space="preserve">0.432612001895905</t>
   </si>
   <si>
     <t xml:space="preserve">0.413591980934143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408370792865753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406879037618637</t>
+    <t xml:space="preserve">0.408370763063431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406879007816315</t>
   </si>
   <si>
     <t xml:space="preserve">0.402776718139648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399047285318375</t>
+    <t xml:space="preserve">0.399047255516052</t>
   </si>
   <si>
     <t xml:space="preserve">0.400539010763168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395317822694778</t>
+    <t xml:space="preserve">0.395317792892456</t>
   </si>
   <si>
     <t xml:space="preserve">0.396809607744217</t>
@@ -941,16 +941,16 @@
     <t xml:space="preserve">0.39606374502182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39308026432991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388604938983917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387858986854553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379654347896576</t>
+    <t xml:space="preserve">0.393080234527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388604909181595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387859016656876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379654318094254</t>
   </si>
   <si>
     <t xml:space="preserve">0.38114607334137</t>
@@ -959,28 +959,28 @@
     <t xml:space="preserve">0.383010774850845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387486100196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384875476360321</t>
+    <t xml:space="preserve">0.387486070394516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384875446557999</t>
   </si>
   <si>
     <t xml:space="preserve">0.383756697177887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386740177869797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390096664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394944876432419</t>
+    <t xml:space="preserve">0.386740148067474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390096694231033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394944906234741</t>
   </si>
   <si>
     <t xml:space="preserve">0.403522580862045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410235494375229</t>
+    <t xml:space="preserve">0.410235464572906</t>
   </si>
   <si>
     <t xml:space="preserve">0.407251983880997</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">0.406506091356277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40091198682785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394199073314667</t>
+    <t xml:space="preserve">0.400912016630173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394199103116989</t>
   </si>
   <si>
     <t xml:space="preserve">0.398674309253693</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">0.390842527151108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392334342002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388231962919235</t>
+    <t xml:space="preserve">0.392334371805191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388231992721558</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113124132156</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">0.385621398687363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38077312707901</t>
+    <t xml:space="preserve">0.380773156881332</t>
   </si>
   <si>
     <t xml:space="preserve">0.385248422622681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383383691310883</t>
+    <t xml:space="preserve">0.383383721113205</t>
   </si>
   <si>
     <t xml:space="preserve">0.397928446531296</t>
@@ -1049,76 +1049,76 @@
     <t xml:space="preserve">0.415083795785904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416575521230698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415829628705978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4240343272686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439324945211411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866079568863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428882509469986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420304894447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421796679496765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428509682416916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45498850941658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445291966199875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444546163082123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440443754196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449767261743546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459463685750961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460955440998077</t>
+    <t xml:space="preserve">0.416575491428375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415829658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424034357070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439324915409088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866109371185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428882539272308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420304954051971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421796709299088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428509652614594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454988539218903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445291996002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444546103477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440443724393845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449767291545868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459463715553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4609554708004</t>
   </si>
   <si>
     <t xml:space="preserve">0.469533175230026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466549664735794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474008470773697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474754393100739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348527431488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485942631959915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482586145401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4855697453022</t>
+    <t xml:space="preserve">0.466549634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474008440971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474754363298416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48034855723381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485942542552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482586115598679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485569626092911</t>
   </si>
   <si>
     <t xml:space="preserve">0.509437918663025</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">0.521745085716248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512794435024261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5195072889328</t>
+    <t xml:space="preserve">0.512794375419617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519507348537445</t>
   </si>
   <si>
     <t xml:space="preserve">0.511675536632538</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">0.506081402301788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501233160495758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502351999282837</t>
+    <t xml:space="preserve">0.501233220100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502352058887482</t>
   </si>
   <si>
     <t xml:space="preserve">0.495266109704971</t>
@@ -1154,37 +1154,37 @@
     <t xml:space="preserve">0.491536766290665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477737963199615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478483766317368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48109433054924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492282569408417</t>
+    <t xml:space="preserve">0.477737903594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47848379611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481094419956207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492282629013062</t>
   </si>
   <si>
     <t xml:space="preserve">0.499741494655609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4937744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495639055967331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507946193218231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500114321708679</t>
+    <t xml:space="preserve">0.493774354457855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495639085769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507946133613586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500114381313324</t>
   </si>
   <si>
     <t xml:space="preserve">0.493028491735458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508692026138306</t>
+    <t xml:space="preserve">0.508691966533661</t>
   </si>
   <si>
     <t xml:space="preserve">0.503470838069916</t>
@@ -1193,52 +1193,52 @@
     <t xml:space="preserve">0.508319079875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507200241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510183751583099</t>
+    <t xml:space="preserve">0.507200300693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510183811187744</t>
   </si>
   <si>
     <t xml:space="preserve">0.513167321681976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500860333442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503097951412201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502724945545197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501606225967407</t>
+    <t xml:space="preserve">0.500860273838043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503097891807556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502725005149841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501606166362762</t>
   </si>
   <si>
     <t xml:space="preserve">0.498249650001526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510929703712463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531068623065948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557920277118683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554936826229095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559412121772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565379202365875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593722581863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574329733848572</t>
+    <t xml:space="preserve">0.510929763317108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531068563461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557920336723328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554936766624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559412062168121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56537914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593722641468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574329674243927</t>
   </si>
   <si>
     <t xml:space="preserve">0.57656729221344</t>
@@ -1250,25 +1250,25 @@
     <t xml:space="preserve">0.583280324935913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591485023498535</t>
+    <t xml:space="preserve">0.59148496389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.585518002510071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575075566768646</t>
+    <t xml:space="preserve">0.575075685977936</t>
   </si>
   <si>
     <t xml:space="preserve">0.612369656562805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556428551673889</t>
+    <t xml:space="preserve">0.556428492069244</t>
   </si>
   <si>
     <t xml:space="preserve">0.551953256130219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548223793506622</t>
+    <t xml:space="preserve">0.548223853111267</t>
   </si>
   <si>
     <t xml:space="preserve">0.534797966480255</t>
@@ -1286,19 +1286,19 @@
     <t xml:space="preserve">0.545240342617035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522863805294037</t>
+    <t xml:space="preserve">0.522863864898682</t>
   </si>
   <si>
     <t xml:space="preserve">0.517642676830292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532560288906097</t>
+    <t xml:space="preserve">0.532560229301453</t>
   </si>
   <si>
     <t xml:space="preserve">0.531814396381378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523609757423401</t>
+    <t xml:space="preserve">0.523609697818756</t>
   </si>
   <si>
     <t xml:space="preserve">0.516150832176208</t>
@@ -1307,31 +1307,31 @@
     <t xml:space="preserve">0.512421429157257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519134402275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498995631933212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46319317817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469906210899353</t>
+    <t xml:space="preserve">0.51913446187973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498995572328568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463193207979202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469906181097031</t>
   </si>
   <si>
     <t xml:space="preserve">0.476619124412537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477364927530289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494520276784897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490045011043549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478856831789017</t>
+    <t xml:space="preserve">0.477364957332611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49452018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490044891834259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47885674238205</t>
   </si>
   <si>
     <t xml:space="preserve">0.478110760450363</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">0.468414396047592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481840342283249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48407781124115</t>
+    <t xml:space="preserve">0.481840223073959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484077900648117</t>
   </si>
   <si>
     <t xml:space="preserve">0.475127309560776</t>
@@ -1355,85 +1355,85 @@
     <t xml:space="preserve">0.474381357431412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484823763370514</t>
+    <t xml:space="preserve">0.484823703765869</t>
   </si>
   <si>
     <t xml:space="preserve">0.487061411142349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483331948518753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504216730594635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504962563514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49675789475441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497503757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486315488815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500487387180328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454242557287216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465430825948715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452004939317703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457226067781448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458717942237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462447285652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455734372138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457972019910812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485727965831757</t>
+    <t xml:space="preserve">0.483331978321075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50421667098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504962623119354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496757954359055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497503787279129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486315548419952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500487327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454242616891861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452004879713058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457226097583771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458717882633209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462447255849838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45573428273201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457972049713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485727936029434</t>
   </si>
   <si>
     <t xml:space="preserve">0.48418590426445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474933862686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469536930322647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464910954236984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461055994033813</t>
+    <t xml:space="preserve">0.47493389248848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469536960124969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464910984039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461056053638458</t>
   </si>
   <si>
     <t xml:space="preserve">0.463368982076645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459514051675797</t>
+    <t xml:space="preserve">0.459514021873474</t>
   </si>
   <si>
     <t xml:space="preserve">0.45797199010849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458743005990982</t>
+    <t xml:space="preserve">0.45874297618866</t>
   </si>
   <si>
     <t xml:space="preserve">0.447949051856995</t>
@@ -1445,22 +1445,22 @@
     <t xml:space="preserve">0.454887956380844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44640702009201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441781103610992</t>
+    <t xml:space="preserve">0.446407049894333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44178107380867</t>
   </si>
   <si>
     <t xml:space="preserve">0.443322986364365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494208753108978</t>
+    <t xml:space="preserve">0.494208782911301</t>
   </si>
   <si>
     <t xml:space="preserve">0.474162966012955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481101870536804</t>
+    <t xml:space="preserve">0.481101930141449</t>
   </si>
   <si>
     <t xml:space="preserve">0.489582866430283</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">0.476475805044174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46413990855217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461826980113983</t>
+    <t xml:space="preserve">0.464139878749847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461827009916306</t>
   </si>
   <si>
     <t xml:space="preserve">0.456430017948151</t>
@@ -1481,73 +1481,73 @@
     <t xml:space="preserve">0.454117000102997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466452956199646</t>
+    <t xml:space="preserve">0.466453015804291</t>
   </si>
   <si>
     <t xml:space="preserve">0.467223942279816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439468055963516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442552030086517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452575027942657</t>
+    <t xml:space="preserve">0.439468085765839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44255205988884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45257505774498</t>
   </si>
   <si>
     <t xml:space="preserve">0.453345984220505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441010117530823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437926143407822</t>
+    <t xml:space="preserve">0.4410100877285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437926083803177</t>
   </si>
   <si>
     <t xml:space="preserve">0.433300077915192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430987119674683</t>
+    <t xml:space="preserve">0.43098708987236</t>
   </si>
   <si>
     <t xml:space="preserve">0.431758105754852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435613125562668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444865077733994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284948348999</t>
+    <t xml:space="preserve">0.435613065958023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444865018129349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284978151321</t>
   </si>
   <si>
     <t xml:space="preserve">0.45180407166481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470307976007462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471850007772446</t>
+    <t xml:space="preserve">0.470308005809784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471849918365479</t>
   </si>
   <si>
     <t xml:space="preserve">0.465681940317154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457200974225998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462598025798798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455659002065659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450262039899826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449491053819656</t>
+    <t xml:space="preserve">0.45720100402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462597995996475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455658972263336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450262010097504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449491024017334</t>
   </si>
   <si>
     <t xml:space="preserve">0.437155067920685</t>
@@ -1556,49 +1556,49 @@
     <t xml:space="preserve">0.440239071846008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426361113786697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427903175354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407086223363876</t>
+    <t xml:space="preserve">0.42636114358902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427903115749359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407086253166199</t>
   </si>
   <si>
     <t xml:space="preserve">0.406315267086029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410170197486877</t>
+    <t xml:space="preserve">0.4101702272892</t>
   </si>
   <si>
     <t xml:space="preserve">0.404002219438553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407857239246368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41094121336937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40014722943306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396292239427567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390895336866379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39012423157692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381643354892731</t>
+    <t xml:space="preserve">0.407857209444046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410941183567047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400147259235382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396292269229889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390895307064056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390124291181564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381643325090408</t>
   </si>
   <si>
     <t xml:space="preserve">0.383185297250748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387811362743378</t>
+    <t xml:space="preserve">0.387811332941055</t>
   </si>
   <si>
     <t xml:space="preserve">0.388582289218903</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">0.39475029706955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397063255310059</t>
+    <t xml:space="preserve">0.397063225507736</t>
   </si>
   <si>
     <t xml:space="preserve">0.389353275299072</t>
@@ -1616,28 +1616,28 @@
     <t xml:space="preserve">0.387040287256241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385498285293579</t>
+    <t xml:space="preserve">0.385498315095901</t>
   </si>
   <si>
     <t xml:space="preserve">0.375475347042084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366223365068436</t>
+    <t xml:space="preserve">0.366223394870758</t>
   </si>
   <si>
     <t xml:space="preserve">0.351188957691193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345406472682953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348875969648361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366994440555573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37239134311676</t>
+    <t xml:space="preserve">0.345406502485275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348875939846039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366994380950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372391372919083</t>
   </si>
   <si>
     <t xml:space="preserve">0.36776539683342</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">0.369692862033844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365837901830673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371620386838913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368536412715912</t>
+    <t xml:space="preserve">0.365837931632996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371620327234268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368536382913589</t>
   </si>
   <si>
     <t xml:space="preserve">0.368921875953674</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">0.378944844007492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383570820093155</t>
+    <t xml:space="preserve">0.383570849895477</t>
   </si>
   <si>
     <t xml:space="preserve">0.377017349004745</t>
@@ -1679,16 +1679,16 @@
     <t xml:space="preserve">0.382414311170578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39937624335289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416338205337524</t>
+    <t xml:space="preserve">0.399376273155212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416338235139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.424048125743866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42481917142868</t>
+    <t xml:space="preserve">0.424819141626358</t>
   </si>
   <si>
     <t xml:space="preserve">0.417109191417694</t>
@@ -1697,25 +1697,25 @@
     <t xml:space="preserve">0.422506153583527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421735137701035</t>
+    <t xml:space="preserve">0.421735107898712</t>
   </si>
   <si>
     <t xml:space="preserve">0.420964181423187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408628165721893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400918215513229</t>
+    <t xml:space="preserve">0.408628135919571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400918245315552</t>
   </si>
   <si>
     <t xml:space="preserve">0.404773235321045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405544251203537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411712199449539</t>
+    <t xml:space="preserve">0.405544281005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411712169647217</t>
   </si>
   <si>
     <t xml:space="preserve">0.412483215332031</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">0.425590127706528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419422179460526</t>
+    <t xml:space="preserve">0.419422149658203</t>
   </si>
   <si>
     <t xml:space="preserve">0.430216103792191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427132129669189</t>
+    <t xml:space="preserve">0.427132159471512</t>
   </si>
   <si>
     <t xml:space="preserve">0.414025187492371</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">0.413254201412201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409399211406708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395521283149719</t>
+    <t xml:space="preserve">0.409399181604385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395521253347397</t>
   </si>
   <si>
     <t xml:space="preserve">0.393208265304565</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">0.391666293144226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39397931098938</t>
+    <t xml:space="preserve">0.393979281187057</t>
   </si>
   <si>
     <t xml:space="preserve">0.398605287075043</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">0.409666270017624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415300130844116</t>
+    <t xml:space="preserve">0.415300160646439</t>
   </si>
   <si>
     <t xml:space="preserve">0.412885636091232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41208079457283</t>
+    <t xml:space="preserve">0.412080824375153</t>
   </si>
   <si>
     <t xml:space="preserve">0.399203240871429</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">0.401215344667435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404032289981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397995978593826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403227478265762</t>
+    <t xml:space="preserve">0.404032319784164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397996008396149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40322744846344</t>
   </si>
   <si>
     <t xml:space="preserve">0.39839842915535</t>
@@ -1808,22 +1808,22 @@
     <t xml:space="preserve">0.400008082389832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402422606945038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400410532951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395983874797821</t>
+    <t xml:space="preserve">0.40242263674736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400410503149033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395983844995499</t>
   </si>
   <si>
     <t xml:space="preserve">0.39960566163063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418519496917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417714685201645</t>
+    <t xml:space="preserve">0.418519526720047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417714655399323</t>
   </si>
   <si>
     <t xml:space="preserve">0.416909843683243</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">0.401617795228958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40725165605545</t>
+    <t xml:space="preserve">0.407251685857773</t>
   </si>
   <si>
     <t xml:space="preserve">0.40805658698082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405642002820969</t>
+    <t xml:space="preserve">0.405642032623291</t>
   </si>
   <si>
     <t xml:space="preserve">0.397593557834625</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">0.426567941904068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433811575174332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424153506755829</t>
+    <t xml:space="preserve">0.433811604976654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424153476953506</t>
   </si>
   <si>
     <t xml:space="preserve">0.432201892137527</t>
@@ -1868,40 +1868,40 @@
     <t xml:space="preserve">0.425763159990311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428177684545517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43300673365593</t>
+    <t xml:space="preserve">0.428177654743195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433006763458252</t>
   </si>
   <si>
     <t xml:space="preserve">0.429787367582321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420934081077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428982526063919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437031000852585</t>
+    <t xml:space="preserve">0.420934051275253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428982496261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437031030654907</t>
   </si>
   <si>
     <t xml:space="preserve">0.434616476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430592238903046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4426648914814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458761781454086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466810286045074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473248988389969</t>
+    <t xml:space="preserve">0.430592268705368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442664861679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458761811256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466810256242752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473248958587646</t>
   </si>
   <si>
     <t xml:space="preserve">0.476468414068222</t>
@@ -1913,25 +1913,25 @@
     <t xml:space="preserve">0.475663542747498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481297492980957</t>
+    <t xml:space="preserve">0.481297522783279</t>
   </si>
   <si>
     <t xml:space="preserve">0.478078067302704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474858641624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471639364957809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472444176673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486126512289047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48049259185791</t>
+    <t xml:space="preserve">0.474858671426773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471639335155487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472444146871567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486126482486725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480492621660233</t>
   </si>
   <si>
     <t xml:space="preserve">0.49497988820076</t>
@@ -1940,16 +1940,16 @@
     <t xml:space="preserve">0.511881530284882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513491332530975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520734906196594</t>
+    <t xml:space="preserve">0.513491272926331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520734846591949</t>
   </si>
   <si>
     <t xml:space="preserve">0.535222113132477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53441721200943</t>
+    <t xml:space="preserve">0.534417271614075</t>
   </si>
   <si>
     <t xml:space="preserve">0.523149371147156</t>
@@ -1958,34 +1958,34 @@
     <t xml:space="preserve">0.515100955963135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516710758209229</t>
+    <t xml:space="preserve">0.516710698604584</t>
   </si>
   <si>
     <t xml:space="preserve">0.522344529628754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556148052215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555343210697174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551319062709808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557757794857025</t>
+    <t xml:space="preserve">0.556147992610931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555343151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551319003105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55775773525238</t>
   </si>
   <si>
     <t xml:space="preserve">0.571440160274506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561782002449036</t>
+    <t xml:space="preserve">0.561781942844391</t>
   </si>
   <si>
     <t xml:space="preserve">0.560977220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552928686141968</t>
+    <t xml:space="preserve">0.552928745746613</t>
   </si>
   <si>
     <t xml:space="preserve">0.554538369178772</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">0.611682415008545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606853365898132</t>
+    <t xml:space="preserve">0.606853306293488</t>
   </si>
   <si>
     <t xml:space="preserve">0.602024257183075</t>
@@ -2012,13 +2012,13 @@
     <t xml:space="preserve">0.614901721477509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600414574146271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608462989330292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593975782394409</t>
+    <t xml:space="preserve">0.600414514541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608463048934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593975841999054</t>
   </si>
   <si>
     <t xml:space="preserve">0.590756416320801</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">0.593170940876007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598804950714111</t>
+    <t xml:space="preserve">0.598804891109467</t>
   </si>
   <si>
     <t xml:space="preserve">0.601219356060028</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">0.594780623912811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603633999824524</t>
+    <t xml:space="preserve">0.603633940219879</t>
   </si>
   <si>
     <t xml:space="preserve">0.610072791576385</t>
@@ -2057,25 +2057,25 @@
     <t xml:space="preserve">0.59799998998642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.630193829536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631803631782532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64629077911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655948877334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65997314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689752399921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684118449687958</t>
+    <t xml:space="preserve">0.630193889141083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631803572177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646290719509125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65594893693924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.659973084926605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689752340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684118509292603</t>
   </si>
   <si>
     <t xml:space="preserve">0.661582827568054</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">0.588341951370239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581098258495331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572244942188263</t>
+    <t xml:space="preserve">0.581098318099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572245001792908</t>
   </si>
   <si>
     <t xml:space="preserve">0.540856003761292</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">0.526368796825409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490955650806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439445525407791</t>
+    <t xml:space="preserve">0.490955680608749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439445495605469</t>
   </si>
   <si>
     <t xml:space="preserve">0.398800849914551</t>
@@ -2114,10 +2114,10 @@
     <t xml:space="preserve">0.381496697664261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323145389556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348095595836639</t>
+    <t xml:space="preserve">0.323145359754562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348095566034317</t>
   </si>
   <si>
     <t xml:space="preserve">0.303829073905945</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">0.282500714063644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288939446210861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291353970766068</t>
+    <t xml:space="preserve">0.288939416408539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29135400056839</t>
   </si>
   <si>
     <t xml:space="preserve">0.304633945226669</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">0.308255732059479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343668907880783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358961015939713</t>
+    <t xml:space="preserve">0.343668937683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35896098613739</t>
   </si>
   <si>
     <t xml:space="preserve">0.37224093079567</t>
@@ -2159,16 +2159,16 @@
     <t xml:space="preserve">0.37908211350441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375057876110077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384716063737869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386325746774673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374253034591675</t>
+    <t xml:space="preserve">0.375057905912399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384716033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386325716972351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374253064393997</t>
   </si>
   <si>
     <t xml:space="preserve">0.362180352210999</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">0.34930282831192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34447380900383</t>
+    <t xml:space="preserve">0.344473749399185</t>
   </si>
   <si>
     <t xml:space="preserve">0.323547810316086</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">0.346083492040634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350912541151047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348497956991196</t>
+    <t xml:space="preserve">0.350912511348724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348497986793518</t>
   </si>
   <si>
     <t xml:space="preserve">0.342864096164703</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">0.324352622032166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329986572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326767176389694</t>
+    <t xml:space="preserve">0.329986542463303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326767146587372</t>
   </si>
   <si>
     <t xml:space="preserve">0.321938097476959</t>
@@ -2234,25 +2234,25 @@
     <t xml:space="preserve">0.340449541807175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347693145275116</t>
+    <t xml:space="preserve">0.347693115472794</t>
   </si>
   <si>
     <t xml:space="preserve">0.352522253990173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35493677854538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369423985481262</t>
+    <t xml:space="preserve">0.354936748743057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36942395567894</t>
   </si>
   <si>
     <t xml:space="preserve">0.382301479578018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379886984825134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371838539838791</t>
+    <t xml:space="preserve">0.379886955022812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371838510036469</t>
   </si>
   <si>
     <t xml:space="preserve">0.354131907224655</t>
@@ -2267,34 +2267,34 @@
     <t xml:space="preserve">0.357351332902908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350107669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346888273954391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342059224843979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337230145931244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328376889228821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335620433092117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370228856801987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35815617442131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363790065050125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420129209756851</t>
+    <t xml:space="preserve">0.350107699632645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346888303756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342059254646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337230175733566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328376859426498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33562046289444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370228826999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358156144618988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363790094852448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420129239559174</t>
   </si>
   <si>
     <t xml:space="preserve">0.424958318471909</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">0.560172319412231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527978479862213</t>
+    <t xml:space="preserve">0.527978539466858</t>
   </si>
   <si>
     <t xml:space="preserve">0.521539688110352</t>
@@ -2324,40 +2324,40 @@
     <t xml:space="preserve">0.529588222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519930124282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507052600383759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500613749027252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494175016880035</t>
+    <t xml:space="preserve">0.519930064678192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507052540779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500613689422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49417507648468</t>
   </si>
   <si>
     <t xml:space="preserve">0.502223432064056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537636578083038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52475905418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510271906852722</t>
+    <t xml:space="preserve">0.537636637687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524759113788605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510271847248077</t>
   </si>
   <si>
     <t xml:space="preserve">0.499004036188126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492565363645554</t>
+    <t xml:space="preserve">0.492565333843231</t>
   </si>
   <si>
     <t xml:space="preserve">0.487736225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484516799449921</t>
+    <t xml:space="preserve">0.484516859054565</t>
   </si>
   <si>
     <t xml:space="preserve">0.447493970394135</t>
@@ -2381,34 +2381,34 @@
     <t xml:space="preserve">0.375862747430801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009431123734</t>
+    <t xml:space="preserve">0.367009460926056</t>
   </si>
   <si>
     <t xml:space="preserve">0.359765827655792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376667588949203</t>
+    <t xml:space="preserve">0.376667559146881</t>
   </si>
   <si>
     <t xml:space="preserve">0.421738892793655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423348635435104</t>
+    <t xml:space="preserve">0.423348665237427</t>
   </si>
   <si>
     <t xml:space="preserve">0.441055208444595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50544285774231</t>
+    <t xml:space="preserve">0.505442917346954</t>
   </si>
   <si>
     <t xml:space="preserve">0.468419939279556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461981147527695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465200573205948</t>
+    <t xml:space="preserve">0.461981177330017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465200543403625</t>
   </si>
   <si>
     <t xml:space="preserve">0.452323019504547</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">0.460371553897858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457152158021927</t>
+    <t xml:space="preserve">0.457152128219604</t>
   </si>
   <si>
     <t xml:space="preserve">0.453932762145996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479687839746475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495784610509872</t>
+    <t xml:space="preserve">0.479687809944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495784670114517</t>
   </si>
   <si>
     <t xml:space="preserve">0.4893459379673</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">0.565001428127289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576269268989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575464308261871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569830477237701</t>
+    <t xml:space="preserve">0.576269209384918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575464427471161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569830417633057</t>
   </si>
   <si>
     <t xml:space="preserve">0.549709320068359</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">0.558562636375427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5440753698349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531197845935822</t>
+    <t xml:space="preserve">0.544075429439545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531197905540466</t>
   </si>
   <si>
     <t xml:space="preserve">0.559367418289185</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">0.581903100013733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579488575458527</t>
+    <t xml:space="preserve">0.579488635063171</t>
   </si>
   <si>
     <t xml:space="preserve">0.544880211353302</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">0.552123844623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548099637031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548904478549957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55373352766037</t>
+    <t xml:space="preserve">0.54809957742691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548904418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553733587265015</t>
   </si>
   <si>
     <t xml:space="preserve">0.582058250904083</t>
@@ -68925,7 +68925,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6495486111</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>187415</v>
@@ -68946,6 +68946,32 @@
         <v>1260</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6494791667</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>196853</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>0.456000000238419</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>0.446999996900558</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>0.453000009059906</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="1263">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326352387666702</t>
+    <t xml:space="preserve">0.32635235786438</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844781637192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323679089546204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980736494064</t>
+    <t xml:space="preserve">0.326844811439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323679059743881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980766296387</t>
   </si>
   <si>
     <t xml:space="preserve">0.313056260347366</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">0.304966032505035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299760192632675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309538781642914</t>
+    <t xml:space="preserve">0.29976013302803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309538811445236</t>
   </si>
   <si>
     <t xml:space="preserve">0.302503824234009</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">0.274363905191422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278655260801315</t>
+    <t xml:space="preserve">0.278655201196671</t>
   </si>
   <si>
     <t xml:space="preserve">0.265288829803467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260645717382431</t>
+    <t xml:space="preserve">0.260645776987076</t>
   </si>
   <si>
     <t xml:space="preserve">0.270846426486969</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">0.270142883062363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265921980142593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290825724601746</t>
+    <t xml:space="preserve">0.265921920537949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29082578420639</t>
   </si>
   <si>
     <t xml:space="preserve">0.288433849811554</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">0.273167967796326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262545168399811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260293960571289</t>
+    <t xml:space="preserve">0.262545138597488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260293990373611</t>
   </si>
   <si>
     <t xml:space="preserve">0.246927559375763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246224015951157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239751875400543</t>
+    <t xml:space="preserve">0.246224030852318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23975183069706</t>
   </si>
   <si>
     <t xml:space="preserve">0.240103632211685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271549969911575</t>
+    <t xml:space="preserve">0.271549940109253</t>
   </si>
   <si>
     <t xml:space="preserve">0.276122659444809</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">0.274645298719406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277881383895874</t>
+    <t xml:space="preserve">0.277881413698196</t>
   </si>
   <si>
     <t xml:space="preserve">0.270987123250961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281539618968964</t>
+    <t xml:space="preserve">0.281539589166641</t>
   </si>
   <si>
     <t xml:space="preserve">0.277177900075912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263319045305252</t>
+    <t xml:space="preserve">0.26331901550293</t>
   </si>
   <si>
     <t xml:space="preserve">0.268032431602478</t>
@@ -167,31 +167,31 @@
     <t xml:space="preserve">0.293358325958252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291740268468857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288644880056381</t>
+    <t xml:space="preserve">0.291740298271179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288644909858704</t>
   </si>
   <si>
     <t xml:space="preserve">0.288504183292389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281469166278839</t>
+    <t xml:space="preserve">0.281469225883484</t>
   </si>
   <si>
     <t xml:space="preserve">0.277248233556747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373867273331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287026882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297368288040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295820564031601</t>
+    <t xml:space="preserve">0.278373837471008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287026792764664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297368258237839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295820593833923</t>
   </si>
   <si>
     <t xml:space="preserve">0.307217210531235</t>
@@ -200,34 +200,34 @@
     <t xml:space="preserve">0.305669546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31375977396965</t>
+    <t xml:space="preserve">0.313759744167328</t>
   </si>
   <si>
     <t xml:space="preserve">0.320443004369736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317417919635773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316573709249496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306161969900131</t>
+    <t xml:space="preserve">0.317417949438095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316573768854141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306161999702454</t>
   </si>
   <si>
     <t xml:space="preserve">0.310945779085159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311438202857971</t>
+    <t xml:space="preserve">0.311438173055649</t>
   </si>
   <si>
     <t xml:space="preserve">0.301800280809402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288011759519577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288082122802734</t>
+    <t xml:space="preserve">0.288011729717255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288082093000412</t>
   </si>
   <si>
     <t xml:space="preserve">0.28055465221405</t>
@@ -236,67 +236,67 @@
     <t xml:space="preserve">0.281328529119492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291880965232849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301378220319748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311649233102798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310242295265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311508566141129</t>
+    <t xml:space="preserve">0.291881024837494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301378190517426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311649292707443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310242265462875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311508536338806</t>
   </si>
   <si>
     <t xml:space="preserve">0.314533621072769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316644132137299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318684250116348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330573320388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330643683671951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334161162376404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3335280418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330432653427124</t>
+    <t xml:space="preserve">0.316644102334976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318684279918671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330573379993439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330643713474274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334161192178726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333527982234955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330432623624802</t>
   </si>
   <si>
     <t xml:space="preserve">0.327126234769821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323538362979889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318543553352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319247037172318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323116272687912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321005761623383</t>
+    <t xml:space="preserve">0.323538392782211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318543523550034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319247007369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32311624288559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321005791425705</t>
   </si>
   <si>
     <t xml:space="preserve">0.324875026941299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323749482631683</t>
+    <t xml:space="preserve">0.323749393224716</t>
   </si>
   <si>
     <t xml:space="preserve">0.325015723705292</t>
@@ -308,34 +308,34 @@
     <t xml:space="preserve">0.326774477958679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331769287586212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344713658094406</t>
+    <t xml:space="preserve">0.331769317388535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344713687896729</t>
   </si>
   <si>
     <t xml:space="preserve">0.342040359973907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338030457496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352100431919098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354914277791977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351678252220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350341618061066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343306660652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343165904283524</t>
+    <t xml:space="preserve">0.338030427694321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352100342512131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354914337396622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351678282022476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350341588258743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343306601047516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343165963888168</t>
   </si>
   <si>
     <t xml:space="preserve">0.341196149587631</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">0.340211242437363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337045550346375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323537766933441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309325903654099</t>
+    <t xml:space="preserve">0.337045520544052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323537737131119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309325873851776</t>
   </si>
   <si>
     <t xml:space="preserve">0.3121537566185</t>
@@ -362,31 +362,31 @@
     <t xml:space="preserve">0.311936229467392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325277984142303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322232574224472</t>
+    <t xml:space="preserve">0.325278013944626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322232604026794</t>
   </si>
   <si>
     <t xml:space="preserve">0.318607091903687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324190318584442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30722314119339</t>
+    <t xml:space="preserve">0.324190348386765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307223081588745</t>
   </si>
   <si>
     <t xml:space="preserve">0.299102038145065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299464583396912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3130963742733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320854961872101</t>
+    <t xml:space="preserve">0.299464523792267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313096404075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320854902267456</t>
   </si>
   <si>
     <t xml:space="preserve">0.318027019500732</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">0.309543401002884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311791211366653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310558557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311066091060638</t>
+    <t xml:space="preserve">0.311791181564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310558527708054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311066120862961</t>
   </si>
   <si>
     <t xml:space="preserve">0.322087585926056</t>
@@ -422,40 +422,40 @@
     <t xml:space="preserve">0.309978455305099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306715548038483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305627882480621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30178490281105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300914764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298739463090897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298014402389526</t>
+    <t xml:space="preserve">0.30671551823616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305627912282944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301784873008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300914734601974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298739492893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298014372587204</t>
   </si>
   <si>
     <t xml:space="preserve">0.291488528251648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294316411018372</t>
+    <t xml:space="preserve">0.294316381216049</t>
   </si>
   <si>
     <t xml:space="preserve">0.304467737674713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301204800605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302727520465851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30381515622139</t>
+    <t xml:space="preserve">0.301204770803452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302727460861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303815186023712</t>
   </si>
   <si>
     <t xml:space="preserve">0.30062472820282</t>
@@ -464,22 +464,22 @@
     <t xml:space="preserve">0.29743430018425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299682080745697</t>
+    <t xml:space="preserve">0.299682110548019</t>
   </si>
   <si>
     <t xml:space="preserve">0.301929891109467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301712363958359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302364945411682</t>
+    <t xml:space="preserve">0.301712334156036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302364975214005</t>
   </si>
   <si>
     <t xml:space="preserve">0.300117164850235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302219927310944</t>
+    <t xml:space="preserve">0.302219957113266</t>
   </si>
   <si>
     <t xml:space="preserve">0.297144263982773</t>
@@ -488,31 +488,31 @@
     <t xml:space="preserve">0.295621573925018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293663829565048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297289311885834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291706055402756</t>
+    <t xml:space="preserve">0.293663799762726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297289282083511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291706025600433</t>
   </si>
   <si>
     <t xml:space="preserve">0.292358636856079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290038347244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287500500679016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292648702859879</t>
+    <t xml:space="preserve">0.290038377046585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287500470876694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292648643255234</t>
   </si>
   <si>
     <t xml:space="preserve">0.287645488977432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295041501522064</t>
+    <t xml:space="preserve">0.295041471719742</t>
   </si>
   <si>
     <t xml:space="preserve">0.291561037302017</t>
@@ -527,61 +527,61 @@
     <t xml:space="preserve">0.287935525178909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283004909753799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287427991628647</t>
+    <t xml:space="preserve">0.283004939556122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287427961826324</t>
   </si>
   <si>
     <t xml:space="preserve">0.282859861850739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27582648396492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279161900281906</t>
+    <t xml:space="preserve">0.275826454162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279161870479584</t>
   </si>
   <si>
     <t xml:space="preserve">0.269735664129257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273288607597351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279524445533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282062262296677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283802509307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282134771347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287137925624847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292866200208664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301422387361526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295839101076126</t>
+    <t xml:space="preserve">0.273288667201996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279524475336075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282062292098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283802479505539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282134741544724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287137895822525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292866170406342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301422297954559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295839041471481</t>
   </si>
   <si>
     <t xml:space="preserve">0.296564221382141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300262123346329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297071784734726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292938739061356</t>
+    <t xml:space="preserve">0.300262153148651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297071754932404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292938709259033</t>
   </si>
   <si>
     <t xml:space="preserve">0.298812001943588</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">0.310195982456207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306425452232361</t>
+    <t xml:space="preserve">0.306425482034683</t>
   </si>
   <si>
     <t xml:space="preserve">0.302509963512421</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">0.307078093290329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301639884710312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294098854064941</t>
+    <t xml:space="preserve">0.30163985490799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294098883867264</t>
   </si>
   <si>
     <t xml:space="preserve">0.283077418804169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287863105535507</t>
+    <t xml:space="preserve">0.287863045930862</t>
   </si>
   <si>
     <t xml:space="preserve">0.289603263139725</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">0.285615235567093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283947557210922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288805663585663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293736338615417</t>
+    <t xml:space="preserve">0.2839475274086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288805693387985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293736308813095</t>
   </si>
   <si>
     <t xml:space="preserve">0.290835946798325</t>
@@ -638,46 +638,46 @@
     <t xml:space="preserve">0.283512473106384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281409710645676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280684620141983</t>
+    <t xml:space="preserve">0.281409651041031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280684560537338</t>
   </si>
   <si>
     <t xml:space="preserve">0.279016852378845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796170949936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291416019201279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295113980770111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290545880794525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288588136434555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292213648557663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292141139507294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294388860464096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299392074346542</t>
+    <t xml:space="preserve">0.273796200752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291415989398956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295114010572433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290545910596848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288588106632233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292213618755341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292141109704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294388920068741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29939204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.296491652727127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30359759926796</t>
+    <t xml:space="preserve">0.303597629070282</t>
   </si>
   <si>
     <t xml:space="preserve">0.309615910053253</t>
@@ -689,19 +689,19 @@
     <t xml:space="preserve">0.319187194108963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331513792276382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331368803977966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345000624656677</t>
+    <t xml:space="preserve">0.331513822078705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331368774175644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345000594854355</t>
   </si>
   <si>
     <t xml:space="preserve">0.349786221981049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358342349529266</t>
+    <t xml:space="preserve">0.358342379331589</t>
   </si>
   <si>
     <t xml:space="preserve">0.354209333658218</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">0.352396577596664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355296939611435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359430015087128</t>
+    <t xml:space="preserve">0.35529699921608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359429985284805</t>
   </si>
   <si>
     <t xml:space="preserve">0.352686613798141</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">0.346885830163956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343187808990479</t>
+    <t xml:space="preserve">0.343187898397446</t>
   </si>
   <si>
     <t xml:space="preserve">0.346160769462585</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">0.346450805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344348043203354</t>
+    <t xml:space="preserve">0.344348013401031</t>
   </si>
   <si>
     <t xml:space="preserve">0.350221306085587</t>
@@ -746,19 +746,19 @@
     <t xml:space="preserve">0.350946366786957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388288766145706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397715061903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379950225353241</t>
+    <t xml:space="preserve">0.388288795948029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397715032100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379950195550919</t>
   </si>
   <si>
     <t xml:space="preserve">0.382125526666641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374874591827393</t>
+    <t xml:space="preserve">0.374874532222748</t>
   </si>
   <si>
     <t xml:space="preserve">0.37342432141304</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">0.373061835765839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369798868894577</t>
+    <t xml:space="preserve">0.369798898696899</t>
   </si>
   <si>
     <t xml:space="preserve">0.383575707674026</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">0.369436353445053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369073808193207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358197331428528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358052343130112</t>
+    <t xml:space="preserve">0.369073778390884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358197301626205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358052313327789</t>
   </si>
   <si>
     <t xml:space="preserve">0.377049803733826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412579566240311</t>
+    <t xml:space="preserve">0.412579536437988</t>
   </si>
   <si>
     <t xml:space="preserve">0.38248798251152</t>
@@ -800,28 +800,28 @@
     <t xml:space="preserve">0.40061542391777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394452124834061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385751008987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393727034330368</t>
+    <t xml:space="preserve">0.394452154636383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385750979185104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393727004528046</t>
   </si>
   <si>
     <t xml:space="preserve">0.390464097261429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384300708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391551792621613</t>
+    <t xml:space="preserve">0.384300768375397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39155176281929</t>
   </si>
   <si>
     <t xml:space="preserve">0.387563735246658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390826642513275</t>
+    <t xml:space="preserve">0.390826672315598</t>
   </si>
   <si>
     <t xml:space="preserve">0.395177245140076</t>
@@ -830,25 +830,25 @@
     <t xml:space="preserve">0.393364518880844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397352516651154</t>
+    <t xml:space="preserve">0.397352486848831</t>
   </si>
   <si>
     <t xml:space="preserve">0.398802727460861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395539730787277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396627366542816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398440152406693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395902305841446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393001973628998</t>
+    <t xml:space="preserve">0.3955397605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396627426147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398440092802048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395902365446091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393001943826675</t>
   </si>
   <si>
     <t xml:space="preserve">0.398077636957169</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.392276853322983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387201189994812</t>
+    <t xml:space="preserve">0.38720116019249</t>
   </si>
   <si>
     <t xml:space="preserve">0.386476069688797</t>
@@ -869,43 +869,43 @@
     <t xml:space="preserve">0.382850617170334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39408951997757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389376431703568</t>
+    <t xml:space="preserve">0.394089579582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38937646150589</t>
   </si>
   <si>
     <t xml:space="preserve">0.381762951612473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381037890911102</t>
+    <t xml:space="preserve">0.38103786110878</t>
   </si>
   <si>
     <t xml:space="preserve">0.386838614940643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388651341199875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385025858879089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391189217567444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392639398574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425631284713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419105410575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445208936929703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435057520866394</t>
+    <t xml:space="preserve">0.38865140080452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385025888681412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391189157962799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392639368772507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425631254911423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419105350971222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445208847522736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435057491064072</t>
   </si>
   <si>
     <t xml:space="preserve">0.442308515310287</t>
@@ -914,31 +914,31 @@
     <t xml:space="preserve">0.432612001895905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413591980934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408370763063431</t>
+    <t xml:space="preserve">0.413591951131821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408370792865753</t>
   </si>
   <si>
     <t xml:space="preserve">0.406879007816315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402776718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399047255516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400539010763168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395317792892456</t>
+    <t xml:space="preserve">0.402776688337326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399047285318375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400539040565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395317822694778</t>
   </si>
   <si>
     <t xml:space="preserve">0.396809607744217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39606374502182</t>
+    <t xml:space="preserve">0.396063774824142</t>
   </si>
   <si>
     <t xml:space="preserve">0.393080234527588</t>
@@ -953,19 +953,19 @@
     <t xml:space="preserve">0.379654318094254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38114607334137</t>
+    <t xml:space="preserve">0.381146103143692</t>
   </si>
   <si>
     <t xml:space="preserve">0.383010774850845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387486070394516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384875446557999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383756697177887</t>
+    <t xml:space="preserve">0.387486100196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384875476360321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383756726980209</t>
   </si>
   <si>
     <t xml:space="preserve">0.386740148067474</t>
@@ -980,61 +980,61 @@
     <t xml:space="preserve">0.403522580862045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410235464572906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407251983880997</t>
+    <t xml:space="preserve">0.410235524177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407252013683319</t>
   </si>
   <si>
     <t xml:space="preserve">0.407624900341034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408743739128113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406506091356277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400912016630173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394199103116989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398674309253693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390842527151108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392334371805191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388231992721558</t>
+    <t xml:space="preserve">0.40874370932579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406506150960922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400911957025528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394199043512344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39867427945137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39084255695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392334312200546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388231962919235</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113124132156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391588449478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389350771903992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385621398687363</t>
+    <t xml:space="preserve">0.391588419675827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389350801706314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38562136888504</t>
   </si>
   <si>
     <t xml:space="preserve">0.380773156881332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385248422622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383383721113205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397928446531296</t>
+    <t xml:space="preserve">0.385248392820358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383383750915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397928416728973</t>
   </si>
   <si>
     <t xml:space="preserve">0.409489661455154</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">0.410981386899948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41433784365654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415083795785904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416575491428375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415829658508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424034357070923</t>
+    <t xml:space="preserve">0.414337784051895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415083736181259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416575461626053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415829628705978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424034297466278</t>
   </si>
   <si>
     <t xml:space="preserve">0.439324915409088</t>
@@ -1064,10 +1064,10 @@
     <t xml:space="preserve">0.431866109371185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428882539272308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420304954051971</t>
+    <t xml:space="preserve">0.428882569074631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420304894447327</t>
   </si>
   <si>
     <t xml:space="preserve">0.421796709299088</t>
@@ -1079,46 +1079,46 @@
     <t xml:space="preserve">0.454988539218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445291996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444546103477478</t>
+    <t xml:space="preserve">0.445291966199875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4445461332798</t>
   </si>
   <si>
     <t xml:space="preserve">0.440443724393845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449767291545868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459463715553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4609554708004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469533175230026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466549634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474008440971375</t>
+    <t xml:space="preserve">0.449767231941223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459463775157928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460955500602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469533145427704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466549664735794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474008530378342</t>
   </si>
   <si>
     <t xml:space="preserve">0.474754363298416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48034855723381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485942542552948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482586115598679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485569626092911</t>
+    <t xml:space="preserve">0.480348438024521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485942602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482586205005646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485569655895233</t>
   </si>
   <si>
     <t xml:space="preserve">0.509437918663025</t>
@@ -1127,49 +1127,49 @@
     <t xml:space="preserve">0.511302590370178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521745085716248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512794375419617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519507348537445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511675536632538</t>
+    <t xml:space="preserve">0.521745026111603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512794435024261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5195072889328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511675596237183</t>
   </si>
   <si>
     <t xml:space="preserve">0.506081402301788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501233220100403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502352058887482</t>
+    <t xml:space="preserve">0.501233279705048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502351999282837</t>
   </si>
   <si>
     <t xml:space="preserve">0.495266109704971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491536766290665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477737903594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47848379611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481094419956207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492282629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499741494655609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493774354457855</t>
+    <t xml:space="preserve">0.491536796092987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477737873792648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478483766317368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48109433054924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492282658815384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499741405248642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493774384260178</t>
   </si>
   <si>
     <t xml:space="preserve">0.495639085769653</t>
@@ -1190,13 +1190,13 @@
     <t xml:space="preserve">0.503470838069916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508319079875946</t>
+    <t xml:space="preserve">0.508319139480591</t>
   </si>
   <si>
     <t xml:space="preserve">0.507200300693512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510183811187744</t>
+    <t xml:space="preserve">0.510183870792389</t>
   </si>
   <si>
     <t xml:space="preserve">0.513167321681976</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">0.501606166362762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498249650001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510929763317108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531068563461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557920336723328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554936766624451</t>
+    <t xml:space="preserve">0.498249709606171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510929703712463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531068503856659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557920277118683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554936707019806</t>
   </si>
   <si>
     <t xml:space="preserve">0.559412062168121</t>
@@ -1244,22 +1244,22 @@
     <t xml:space="preserve">0.57656729221344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577313303947449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583280324935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59148496389389</t>
+    <t xml:space="preserve">0.577313125133514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583280265331268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591485023498535</t>
   </si>
   <si>
     <t xml:space="preserve">0.585518002510071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575075685977936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612369656562805</t>
+    <t xml:space="preserve">0.575075507164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61236971616745</t>
   </si>
   <si>
     <t xml:space="preserve">0.556428492069244</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">0.534797966480255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521372020244598</t>
+    <t xml:space="preserve">0.521372079849243</t>
   </si>
   <si>
     <t xml:space="preserve">0.505708515644073</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">0.528084993362427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545240342617035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522863864898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517642676830292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532560229301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531814396381378</t>
+    <t xml:space="preserve">0.54524028301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522863745689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517642617225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532560288906097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531814336776733</t>
   </si>
   <si>
     <t xml:space="preserve">0.523609697818756</t>
@@ -1307,136 +1307,136 @@
     <t xml:space="preserve">0.512421429157257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51913446187973</t>
+    <t xml:space="preserve">0.519134402275085</t>
   </si>
   <si>
     <t xml:space="preserve">0.498995572328568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463193207979202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469906181097031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476619124412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477364957332611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49452018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490044891834259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47885674238205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478110760450363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468414396047592</t>
+    <t xml:space="preserve">0.463193148374557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469906151294708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476619094610214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477364927530289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494520276784897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490044951438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478856772184372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478110909461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46841436624527</t>
   </si>
   <si>
     <t xml:space="preserve">0.481840223073959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484077900648117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475127309560776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473635524511337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474381357431412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484823703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487061411142349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483331978321075</t>
+    <t xml:space="preserve">0.484077870845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475127369165421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47363555431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474381417036057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484823763370514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487061470746994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48333203792572</t>
   </si>
   <si>
     <t xml:space="preserve">0.50421667098999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504962623119354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496757954359055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497503787279129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486315548419952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500487327575684</t>
+    <t xml:space="preserve">0.504962563514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496757984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497503817081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486315459012985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500487387180328</t>
   </si>
   <si>
     <t xml:space="preserve">0.454242616891861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452004879713058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457226097583771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458717882633209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462447255849838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45573428273201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457972049713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485727936029434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48418590426445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47493389248848</t>
+    <t xml:space="preserve">0.465430825948715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452004939317703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457226157188416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458717852830887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462447315454483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455734401941299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457972019910812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485727906227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484185874462128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474933952093124</t>
   </si>
   <si>
     <t xml:space="preserve">0.469536960124969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464910984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461056053638458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463368982076645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459514021873474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45797199010849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45874297618866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447949051856995</t>
+    <t xml:space="preserve">0.464910924434662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461056023836136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463369011878967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459513992071152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457971960306168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458743005990982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447949022054672</t>
   </si>
   <si>
     <t xml:space="preserve">0.451033025979996</t>
@@ -1448,34 +1448,34 @@
     <t xml:space="preserve">0.446407049894333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44178107380867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443322986364365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494208782911301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474162966012955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481101930141449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489582866430283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476475805044174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464139878749847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461827009916306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456430017948151</t>
+    <t xml:space="preserve">0.441781133413315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443323075771332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494208872318268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474162876605988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481101900339127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489582896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476475894451141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464139968156815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461826980113983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456430047750473</t>
   </si>
   <si>
     <t xml:space="preserve">0.454117000102997</t>
@@ -1484,31 +1484,31 @@
     <t xml:space="preserve">0.466453015804291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467223942279816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439468085765839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44255205988884</t>
+    <t xml:space="preserve">0.467223972082138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439468115568161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442552089691162</t>
   </si>
   <si>
     <t xml:space="preserve">0.45257505774498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453345984220505</t>
+    <t xml:space="preserve">0.453346014022827</t>
   </si>
   <si>
     <t xml:space="preserve">0.4410100877285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437926083803177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433300077915192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43098708987236</t>
+    <t xml:space="preserve">0.437926113605499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433300107717514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430987119674683</t>
   </si>
   <si>
     <t xml:space="preserve">0.431758105754852</t>
@@ -1517,22 +1517,22 @@
     <t xml:space="preserve">0.435613065958023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444865018129349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284978151321</t>
+    <t xml:space="preserve">0.444865047931671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284948348999</t>
   </si>
   <si>
     <t xml:space="preserve">0.45180407166481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470308005809784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471849918365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465681940317154</t>
+    <t xml:space="preserve">0.470308035612106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471849948167801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465681999921799</t>
   </si>
   <si>
     <t xml:space="preserve">0.45720100402832</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">0.450262010097504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449491024017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437155067920685</t>
+    <t xml:space="preserve">0.449491053819656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43715512752533</t>
   </si>
   <si>
     <t xml:space="preserve">0.440239071846008</t>
@@ -1559,16 +1559,16 @@
     <t xml:space="preserve">0.42636114358902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427903115749359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407086253166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406315267086029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4101702272892</t>
+    <t xml:space="preserve">0.427903145551682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407086223363876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406315237283707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410170197486877</t>
   </si>
   <si>
     <t xml:space="preserve">0.404002219438553</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">0.410941183567047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400147259235382</t>
+    <t xml:space="preserve">0.40014722943306</t>
   </si>
   <si>
     <t xml:space="preserve">0.396292269229889</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">0.390895307064056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390124291181564</t>
+    <t xml:space="preserve">0.390124261379242</t>
   </si>
   <si>
     <t xml:space="preserve">0.381643325090408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383185297250748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387811332941055</t>
+    <t xml:space="preserve">0.38318532705307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387811303138733</t>
   </si>
   <si>
     <t xml:space="preserve">0.388582289218903</t>
@@ -1607,43 +1607,43 @@
     <t xml:space="preserve">0.39475029706955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397063225507736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389353275299072</t>
+    <t xml:space="preserve">0.397063255310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389353305101395</t>
   </si>
   <si>
     <t xml:space="preserve">0.387040287256241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385498315095901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375475347042084</t>
+    <t xml:space="preserve">0.385498285293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375475317239761</t>
   </si>
   <si>
     <t xml:space="preserve">0.366223394870758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351188957691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345406502485275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348875939846039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366994380950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372391372919083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36776539683342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162358999252</t>
+    <t xml:space="preserve">0.351188987493515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345406472682953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348875969648361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36699441075325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372391402721405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367765367031097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162388801575</t>
   </si>
   <si>
     <t xml:space="preserve">0.370078384876251</t>
@@ -1652,88 +1652,88 @@
     <t xml:space="preserve">0.370463907718658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369692862033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365837931632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371620327234268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368536382913589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368921875953674</t>
+    <t xml:space="preserve">0.369692891836166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365837901830673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371620357036591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368536353111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368921905755997</t>
   </si>
   <si>
     <t xml:space="preserve">0.378944844007492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383570849895477</t>
+    <t xml:space="preserve">0.383570820093155</t>
   </si>
   <si>
     <t xml:space="preserve">0.377017349004745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382414311170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399376273155212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416338235139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424048125743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424819141626358</t>
+    <t xml:space="preserve">0.3824143409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39937624335289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416338205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424048155546188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424819111824036</t>
   </si>
   <si>
     <t xml:space="preserve">0.417109191417694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422506153583527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421735107898712</t>
+    <t xml:space="preserve">0.422506123781204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421735137701035</t>
   </si>
   <si>
     <t xml:space="preserve">0.420964181423187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408628135919571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400918245315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404773235321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405544281005859</t>
+    <t xml:space="preserve">0.408628195524216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400918215513229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404773205518723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405544251203537</t>
   </si>
   <si>
     <t xml:space="preserve">0.411712169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412483215332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423277169466019</t>
+    <t xml:space="preserve">0.412483245134354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423277199268341</t>
   </si>
   <si>
     <t xml:space="preserve">0.425590127706528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419422149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430216103792191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427132159471512</t>
+    <t xml:space="preserve">0.41942223906517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430216193199158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427132129669189</t>
   </si>
   <si>
     <t xml:space="preserve">0.414025187492371</t>
@@ -1745,31 +1745,31 @@
     <t xml:space="preserve">0.413254201412201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409399181604385</t>
+    <t xml:space="preserve">0.40939924120903</t>
   </si>
   <si>
     <t xml:space="preserve">0.395521253347397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393208265304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392437309026718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391666293144226</t>
+    <t xml:space="preserve">0.393208295106888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392437279224396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391666322946548</t>
   </si>
   <si>
     <t xml:space="preserve">0.393979281187057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398605287075043</t>
+    <t xml:space="preserve">0.39860525727272</t>
   </si>
   <si>
     <t xml:space="preserve">0.403231233358383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411275953054428</t>
+    <t xml:space="preserve">0.411275893449783</t>
   </si>
   <si>
     <t xml:space="preserve">0.410471081733704</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">0.409666270017624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415300160646439</t>
+    <t xml:space="preserve">0.415300101041794</t>
   </si>
   <si>
     <t xml:space="preserve">0.412885636091232</t>
@@ -1790,31 +1790,31 @@
     <t xml:space="preserve">0.399203240871429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401215344667435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404032319784164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397996008396149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40322744846344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39839842915535</t>
+    <t xml:space="preserve">0.401215374469757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404032289981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397996038198471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403227478265762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398398399353027</t>
   </si>
   <si>
     <t xml:space="preserve">0.400008082389832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40242263674736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400410503149033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395983844995499</t>
+    <t xml:space="preserve">0.402422666549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400410532951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395983874797821</t>
   </si>
   <si>
     <t xml:space="preserve">0.39960566163063</t>
@@ -1823,22 +1823,22 @@
     <t xml:space="preserve">0.418519526720047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417714655399323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416909843683243</t>
+    <t xml:space="preserve">0.417714715003967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416909873485565</t>
   </si>
   <si>
     <t xml:space="preserve">0.404837220907211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401617795228958</t>
+    <t xml:space="preserve">0.401617825031281</t>
   </si>
   <si>
     <t xml:space="preserve">0.407251685857773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40805658698082</t>
+    <t xml:space="preserve">0.408056557178497</t>
   </si>
   <si>
     <t xml:space="preserve">0.405642032623291</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">0.406446844339371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426567941904068</t>
+    <t xml:space="preserve">0.42656797170639</t>
   </si>
   <si>
     <t xml:space="preserve">0.433811604976654</t>
@@ -1862,46 +1862,46 @@
     <t xml:space="preserve">0.424153476953506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432201892137527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425763159990311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428177654743195</t>
+    <t xml:space="preserve">0.43220192193985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425763130187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428177684545517</t>
   </si>
   <si>
     <t xml:space="preserve">0.433006763458252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429787367582321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420934051275253</t>
+    <t xml:space="preserve">0.429787337779999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420934081077576</t>
   </si>
   <si>
     <t xml:space="preserve">0.428982496261597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437031030654907</t>
+    <t xml:space="preserve">0.43703094124794</t>
   </si>
   <si>
     <t xml:space="preserve">0.434616476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430592268705368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442664861679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458761811256409</t>
+    <t xml:space="preserve">0.430592238903046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442664951086044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458761781454086</t>
   </si>
   <si>
     <t xml:space="preserve">0.466810256242752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473248958587646</t>
+    <t xml:space="preserve">0.473249047994614</t>
   </si>
   <si>
     <t xml:space="preserve">0.476468414068222</t>
@@ -1910,25 +1910,25 @@
     <t xml:space="preserve">0.478882938623428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475663542747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481297522783279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478078067302704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474858671426773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471639335155487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472444146871567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486126482486725</t>
+    <t xml:space="preserve">0.475663602352142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481297463178635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478078097105026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474858731031418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471639364957809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472444176673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486126512289047</t>
   </si>
   <si>
     <t xml:space="preserve">0.480492621660233</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">0.49497988820076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511881530284882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513491272926331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520734846591949</t>
+    <t xml:space="preserve">0.511881589889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513491332530975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520734965801239</t>
   </si>
   <si>
     <t xml:space="preserve">0.535222113132477</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">0.534417271614075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523149371147156</t>
+    <t xml:space="preserve">0.523149430751801</t>
   </si>
   <si>
     <t xml:space="preserve">0.515100955963135</t>
@@ -1961,34 +1961,34 @@
     <t xml:space="preserve">0.516710698604584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522344529628754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556147992610931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555343151092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551319003105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55775773525238</t>
+    <t xml:space="preserve">0.522344589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556148111820221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555343270301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551319062709808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557757794857025</t>
   </si>
   <si>
     <t xml:space="preserve">0.571440160274506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561781942844391</t>
+    <t xml:space="preserve">0.561782002449036</t>
   </si>
   <si>
     <t xml:space="preserve">0.560977220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552928745746613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554538369178772</t>
+    <t xml:space="preserve">0.552928686141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554538428783417</t>
   </si>
   <si>
     <t xml:space="preserve">0.592366099357605</t>
@@ -2009,19 +2009,19 @@
     <t xml:space="preserve">0.602024257183075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614901721477509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600414514541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608463048934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593975841999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590756416320801</t>
+    <t xml:space="preserve">0.614901781082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600414633750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608462989330292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593975782394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590756475925446</t>
   </si>
   <si>
     <t xml:space="preserve">0.595585525035858</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">0.614096939563751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60604852437973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593170940876007</t>
+    <t xml:space="preserve">0.606048464775085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593171000480652</t>
   </si>
   <si>
     <t xml:space="preserve">0.598804891109467</t>
@@ -2045,28 +2045,28 @@
     <t xml:space="preserve">0.601219356060028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594780623912811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603633940219879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610072791576385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59799998998642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630193889141083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631803572177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.646290719509125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65594893693924</t>
+    <t xml:space="preserve">0.594780683517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603633880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610072672367096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598000049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630193769931793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631803452968597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64629065990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655948877334595</t>
   </si>
   <si>
     <t xml:space="preserve">0.659973084926605</t>
@@ -2075,22 +2075,22 @@
     <t xml:space="preserve">0.689752340316772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684118509292603</t>
+    <t xml:space="preserve">0.684118449687958</t>
   </si>
   <si>
     <t xml:space="preserve">0.661582827568054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588341951370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581098318099976</t>
+    <t xml:space="preserve">0.588341891765594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581098258495331</t>
   </si>
   <si>
     <t xml:space="preserve">0.572245001792908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540856003761292</t>
+    <t xml:space="preserve">0.540856063365936</t>
   </si>
   <si>
     <t xml:space="preserve">0.543270528316498</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">0.526368796825409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490955680608749</t>
+    <t xml:space="preserve">0.490955591201782</t>
   </si>
   <si>
     <t xml:space="preserve">0.439445495605469</t>
@@ -2111,22 +2111,22 @@
     <t xml:space="preserve">0.398800849914551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381496697664261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323145359754562</t>
+    <t xml:space="preserve">0.381496667861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32314532995224</t>
   </si>
   <si>
     <t xml:space="preserve">0.348095566034317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303829073905945</t>
+    <t xml:space="preserve">0.303829103708267</t>
   </si>
   <si>
     <t xml:space="preserve">0.282500714063644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288939416408539</t>
+    <t xml:space="preserve">0.288939446210861</t>
   </si>
   <si>
     <t xml:space="preserve">0.29135400056839</t>
@@ -2135,37 +2135,37 @@
     <t xml:space="preserve">0.304633945226669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308255732059479</t>
+    <t xml:space="preserve">0.308255702257156</t>
   </si>
   <si>
     <t xml:space="preserve">0.343668937683105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35896098613739</t>
+    <t xml:space="preserve">0.358961015939713</t>
   </si>
   <si>
     <t xml:space="preserve">0.37224093079567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355741620063782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373850643634796</t>
+    <t xml:space="preserve">0.355741590261459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373850613832474</t>
   </si>
   <si>
     <t xml:space="preserve">0.391959637403488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37908211350441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375057905912399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384716033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386325716972351</t>
+    <t xml:space="preserve">0.379082143306732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375057876110077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384716004133224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386325746774673</t>
   </si>
   <si>
     <t xml:space="preserve">0.374253064393997</t>
@@ -2180,28 +2180,28 @@
     <t xml:space="preserve">0.353327065706253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34930282831192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344473749399185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323547810316086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338035017251968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339644730091095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341254383325577</t>
+    <t xml:space="preserve">0.349302798509598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344473779201508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323547780513763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338034987449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33964467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341254353523254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346083492040634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350912511348724</t>
+    <t xml:space="preserve">0.350912541151047</t>
   </si>
   <si>
     <t xml:space="preserve">0.348497986793518</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">0.342864096164703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34527862071991</t>
+    <t xml:space="preserve">0.345278590917587</t>
   </si>
   <si>
     <t xml:space="preserve">0.336425334215164</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">0.340449541807175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347693115472794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352522253990173</t>
+    <t xml:space="preserve">0.347693145275116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352522194385529</t>
   </si>
   <si>
     <t xml:space="preserve">0.354936748743057</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">0.382301479578018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379886955022812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371838510036469</t>
+    <t xml:space="preserve">0.379886984825134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371838539838791</t>
   </si>
   <si>
     <t xml:space="preserve">0.354131907224655</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">0.330791413784027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356546461582184</t>
+    <t xml:space="preserve">0.356546401977539</t>
   </si>
   <si>
     <t xml:space="preserve">0.357351332902908</t>
@@ -2273,28 +2273,28 @@
     <t xml:space="preserve">0.346888303756714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342059254646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337230175733566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328376859426498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33562046289444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370228826999664</t>
+    <t xml:space="preserve">0.342059224843979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337230145931244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328376889228821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335620492696762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370228797197342</t>
   </si>
   <si>
     <t xml:space="preserve">0.358156144618988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363790094852448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420129239559174</t>
+    <t xml:space="preserve">0.363790035247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420129269361496</t>
   </si>
   <si>
     <t xml:space="preserve">0.424958318471909</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">0.444274574518204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44588428735733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482907205820084</t>
+    <t xml:space="preserve">0.445884317159653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482907235622406</t>
   </si>
   <si>
     <t xml:space="preserve">0.560172319412231</t>
@@ -2321,40 +2321,40 @@
     <t xml:space="preserve">0.521539688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529588222503662</t>
+    <t xml:space="preserve">0.529588162899017</t>
   </si>
   <si>
     <t xml:space="preserve">0.519930064678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507052540779114</t>
+    <t xml:space="preserve">0.507052481174469</t>
   </si>
   <si>
     <t xml:space="preserve">0.500613689422607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49417507648468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502223432064056</t>
+    <t xml:space="preserve">0.494175046682358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502223491668701</t>
   </si>
   <si>
     <t xml:space="preserve">0.537636637687683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524759113788605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510271847248077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499004036188126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492565333843231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487736225128174</t>
+    <t xml:space="preserve">0.52475917339325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510271966457367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499004065990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492565304040909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487736254930496</t>
   </si>
   <si>
     <t xml:space="preserve">0.484516859054565</t>
@@ -2366,46 +2366,46 @@
     <t xml:space="preserve">0.431397080421448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449103653430939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436226159334183</t>
+    <t xml:space="preserve">0.449103713035583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436226099729538</t>
   </si>
   <si>
     <t xml:space="preserve">0.393569320440292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37827730178833</t>
+    <t xml:space="preserve">0.378277242183685</t>
   </si>
   <si>
     <t xml:space="preserve">0.375862747430801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009460926056</t>
+    <t xml:space="preserve">0.367009431123734</t>
   </si>
   <si>
     <t xml:space="preserve">0.359765827655792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376667559146881</t>
+    <t xml:space="preserve">0.376667588949203</t>
   </si>
   <si>
     <t xml:space="preserve">0.421738892793655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423348665237427</t>
+    <t xml:space="preserve">0.423348635435104</t>
   </si>
   <si>
     <t xml:space="preserve">0.441055208444595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505442917346954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468419939279556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461981177330017</t>
+    <t xml:space="preserve">0.50544285774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468419969081879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461981207132339</t>
   </si>
   <si>
     <t xml:space="preserve">0.465200543403625</t>
@@ -2417,25 +2417,25 @@
     <t xml:space="preserve">0.455542385578156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450713336467743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460371553897858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457152128219604</t>
+    <t xml:space="preserve">0.450713366270065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460371524095535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457152158021927</t>
   </si>
   <si>
     <t xml:space="preserve">0.453932762145996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479687809944153</t>
+    <t xml:space="preserve">0.479687839746475</t>
   </si>
   <si>
     <t xml:space="preserve">0.495784670114517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4893459379673</t>
+    <t xml:space="preserve">0.489345908164978</t>
   </si>
   <si>
     <t xml:space="preserve">0.547294795513153</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">0.565001428127289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576269209384918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575464427471161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569830417633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549709320068359</t>
+    <t xml:space="preserve">0.576269268989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575464367866516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569830536842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549709379673004</t>
   </si>
   <si>
     <t xml:space="preserve">0.56741589307785</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">0.559367418289185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573854684829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581903100013733</t>
+    <t xml:space="preserve">0.573854625225067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581903159618378</t>
   </si>
   <si>
     <t xml:space="preserve">0.579488635063171</t>
@@ -2489,43 +2489,43 @@
     <t xml:space="preserve">0.552123844623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54809957742691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548904418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553733587265015</t>
+    <t xml:space="preserve">0.5480996966362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548904478549957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553733646869659</t>
   </si>
   <si>
     <t xml:space="preserve">0.582058250904083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581226766109467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573743104934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56709098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574589729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572911620140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561270475387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557944536209106</t>
+    <t xml:space="preserve">0.581226825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573743164539337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567091107368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574649333954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57291167974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561270534992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557944416999817</t>
   </si>
   <si>
     <t xml:space="preserve">0.558775961399078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540482640266418</t>
+    <t xml:space="preserve">0.540482699871063</t>
   </si>
   <si>
     <t xml:space="preserve">0.544640243053436</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">0.542977273464203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530504524707794</t>
+    <t xml:space="preserve">0.530504584312439</t>
   </si>
   <si>
     <t xml:space="preserve">0.531336069107056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532167553901672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516368806362152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511379837989807</t>
+    <t xml:space="preserve">0.532167613506317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516368865966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511379778385162</t>
   </si>
   <si>
     <t xml:space="preserve">0.505559206008911</t>
@@ -2555,19 +2555,19 @@
     <t xml:space="preserve">0.508885264396667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50223308801651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515537321567535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498907148838043</t>
+    <t xml:space="preserve">0.502233147621155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51553738117218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498907119035721</t>
   </si>
   <si>
     <t xml:space="preserve">0.493918001651764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494749546051025</t>
+    <t xml:space="preserve">0.494749575853348</t>
   </si>
   <si>
     <t xml:space="preserve">0.500570118427277</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">0.48393988609314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465646624565125</t>
+    <t xml:space="preserve">0.465646594762802</t>
   </si>
   <si>
     <t xml:space="preserve">0.466478109359741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461489111185074</t>
+    <t xml:space="preserve">0.461489081382751</t>
   </si>
   <si>
     <t xml:space="preserve">0.460657566785812</t>
@@ -2594,10 +2594,10 @@
     <t xml:space="preserve">0.473130285739899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486434459686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489760458469391</t>
+    <t xml:space="preserve">0.486434429883957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489760518074036</t>
   </si>
   <si>
     <t xml:space="preserve">0.503064692020416</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">0.506390750408173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51054835319519</t>
+    <t xml:space="preserve">0.510548293590546</t>
   </si>
   <si>
     <t xml:space="preserve">0.503896176815033</t>
@@ -2618,22 +2618,22 @@
     <t xml:space="preserve">0.495581090450287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484771430492401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482276856899261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491423487663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497244119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487265944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493086516857147</t>
+    <t xml:space="preserve">0.484771460294724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482276886701584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491423547267914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497244089841843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487265974283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493086487054825</t>
   </si>
   <si>
     <t xml:space="preserve">0.483108341693878</t>
@@ -2642,10 +2642,10 @@
     <t xml:space="preserve">0.478119283914566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475624829530716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476456314325333</t>
+    <t xml:space="preserve">0.475624799728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47645628452301</t>
   </si>
   <si>
     <t xml:space="preserve">0.529673039913177</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">0.528010010719299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533830642700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527178466320038</t>
+    <t xml:space="preserve">0.533830583095551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527178525924683</t>
   </si>
   <si>
     <t xml:space="preserve">0.547966301441193</t>
@@ -2669,52 +2669,52 @@
     <t xml:space="preserve">0.528841495513916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52551543712616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526346981525421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554618418216705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588710367679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575406134128571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577069222927094</t>
+    <t xml:space="preserve">0.525515496730804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526347041130066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55461847782135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588710427284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575406193733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577069282531738</t>
   </si>
   <si>
     <t xml:space="preserve">0.570417106151581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583721339702606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58538430929184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57790070772171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580395221710205</t>
+    <t xml:space="preserve">0.583721399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585384368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577900767326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58039528131485</t>
   </si>
   <si>
     <t xml:space="preserve">0.550460875034332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556281507015228</t>
+    <t xml:space="preserve">0.556281447410583</t>
   </si>
   <si>
     <t xml:space="preserve">0.545471787452698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567922592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566259503364563</t>
+    <t xml:space="preserve">0.567922651767731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566259562969208</t>
   </si>
   <si>
     <t xml:space="preserve">0.557112991809845</t>
@@ -2732,22 +2732,22 @@
     <t xml:space="preserve">0.53632515668869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532999038696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524683892726898</t>
+    <t xml:space="preserve">0.532999098300934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524684011936188</t>
   </si>
   <si>
     <t xml:space="preserve">0.509716749191284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507222294807434</t>
+    <t xml:space="preserve">0.507222175598145</t>
   </si>
   <si>
     <t xml:space="preserve">0.521357893943787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513874292373657</t>
+    <t xml:space="preserve">0.513874351978302</t>
   </si>
   <si>
     <t xml:space="preserve">0.522189497947693</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">0.523020923137665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519694864749908</t>
+    <t xml:space="preserve">0.519694983959198</t>
   </si>
   <si>
     <t xml:space="preserve">0.508053779602051</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">0.488097429275513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488928914070129</t>
+    <t xml:space="preserve">0.488928943872452</t>
   </si>
   <si>
     <t xml:space="preserve">0.492255032062531</t>
@@ -2780,22 +2780,22 @@
     <t xml:space="preserve">0.496412575244904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490591943264008</t>
+    <t xml:space="preserve">0.49059197306633</t>
   </si>
   <si>
     <t xml:space="preserve">0.485602915287018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480613827705383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474793285131454</t>
+    <t xml:space="preserve">0.480613857507706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474793255329132</t>
   </si>
   <si>
     <t xml:space="preserve">0.4540054500103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478950798511505</t>
+    <t xml:space="preserve">0.478950828313828</t>
   </si>
   <si>
     <t xml:space="preserve">0.458163022994995</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">0.43986976146698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439038276672363</t>
+    <t xml:space="preserve">0.439038217067719</t>
   </si>
   <si>
     <t xml:space="preserve">0.419913470745087</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">0.422408044338226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424071043729782</t>
+    <t xml:space="preserve">0.42407101392746</t>
   </si>
   <si>
     <t xml:space="preserve">0.411598384380341</t>
@@ -2837,25 +2837,25 @@
     <t xml:space="preserve">0.402035981416702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413677126169205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407440781593323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412429869174957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431554615497589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429891645908356</t>
+    <t xml:space="preserve">0.413677155971527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407440841197968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412429839372635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431554645299911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429891616106033</t>
   </si>
   <si>
     <t xml:space="preserve">0.432386130094528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451510965824127</t>
+    <t xml:space="preserve">0.451510936021805</t>
   </si>
   <si>
     <t xml:space="preserve">0.444027304649353</t>
@@ -2864,16 +2864,16 @@
     <t xml:space="preserve">0.436543703079224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443195790052414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448184877634048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44652184844017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440701216459274</t>
+    <t xml:space="preserve">0.443195819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448184847831726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.446521878242493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440701246261597</t>
   </si>
   <si>
     <t xml:space="preserve">0.434880673885345</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">0.424902558326721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444858878850937</t>
+    <t xml:space="preserve">0.444858849048615</t>
   </si>
   <si>
     <t xml:space="preserve">0.447353363037109</t>
@@ -2891,25 +2891,25 @@
     <t xml:space="preserve">0.445690363645554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46315211057663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4814453125</t>
+    <t xml:space="preserve">0.463152080774307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481445372104645</t>
   </si>
   <si>
     <t xml:space="preserve">0.477287799119949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470635652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437375277280807</t>
+    <t xml:space="preserve">0.470635682344437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437375247478485</t>
   </si>
   <si>
     <t xml:space="preserve">0.429060101509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421576529741287</t>
+    <t xml:space="preserve">0.421576499938965</t>
   </si>
   <si>
     <t xml:space="preserve">0.40993532538414</t>
@@ -2930,28 +2930,28 @@
     <t xml:space="preserve">0.452196657657623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446109414100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439152508974075</t>
+    <t xml:space="preserve">0.446109443902969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439152538776398</t>
   </si>
   <si>
     <t xml:space="preserve">0.431326061487198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423499584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406542181968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403063774108887</t>
+    <t xml:space="preserve">0.423499554395676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406542211771011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403063744306564</t>
   </si>
   <si>
     <t xml:space="preserve">0.414368689060211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3939328789711</t>
+    <t xml:space="preserve">0.393932908773422</t>
   </si>
   <si>
     <t xml:space="preserve">0.391324043273926</t>
@@ -2960,64 +2960,64 @@
     <t xml:space="preserve">0.383932381868362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388715207576752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627934217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380888760089874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387845635414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393498063087463</t>
+    <t xml:space="preserve">0.388715237379074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627964019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380888730287552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387845605611801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393498033285141</t>
   </si>
   <si>
     <t xml:space="preserve">0.379584342241287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384367167949677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378714710474014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373931914567947</t>
+    <t xml:space="preserve">0.384367197751999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378714740276337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373931884765625</t>
   </si>
   <si>
     <t xml:space="preserve">0.372627437114716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373062252998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3782799243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370888203382492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361322551965714</t>
+    <t xml:space="preserve">0.37306222319603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378279894590378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370888233184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361322522163391</t>
   </si>
   <si>
     <t xml:space="preserve">0.366105407476425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371323019266129</t>
+    <t xml:space="preserve">0.371323049068451</t>
   </si>
   <si>
     <t xml:space="preserve">0.375671088695526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374366700649261</t>
+    <t xml:space="preserve">0.374366670846939</t>
   </si>
   <si>
     <t xml:space="preserve">0.370018631219864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367844611406326</t>
+    <t xml:space="preserve">0.367844581604004</t>
   </si>
   <si>
     <t xml:space="preserve">0.366975009441376</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">0.36175736784935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368714183568954</t>
+    <t xml:space="preserve">0.368714213371277</t>
   </si>
   <si>
     <t xml:space="preserve">0.377410292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369583815336227</t>
+    <t xml:space="preserve">0.36958384513855</t>
   </si>
   <si>
     <t xml:space="preserve">0.377845108509064</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">0.374801486730576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37523627281189</t>
+    <t xml:space="preserve">0.375236243009567</t>
   </si>
   <si>
     <t xml:space="preserve">0.372192651033401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365235775709152</t>
+    <t xml:space="preserve">0.36523574590683</t>
   </si>
   <si>
     <t xml:space="preserve">0.376540690660477</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">0.364800959825516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386976033449173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397411286830902</t>
+    <t xml:space="preserve">0.386976003646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397411316633224</t>
   </si>
   <si>
     <t xml:space="preserve">0.402628988027573</t>
@@ -3080,175 +3080,178 @@
     <t xml:space="preserve">0.407846629619598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389584839344025</t>
+    <t xml:space="preserve">0.389584869146347</t>
   </si>
   <si>
     <t xml:space="preserve">0.396106898784637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399150520563126</t>
+    <t xml:space="preserve">0.399150550365448</t>
   </si>
   <si>
     <t xml:space="preserve">0.403498560190201</t>
   </si>
   <si>
+    <t xml:space="preserve">0.396541714668274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392193675041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401759386062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403933376073837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408716231584549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400020152330399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400889724493027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393063247203827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380019158124924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385236769914627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389150023460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390889227390289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395672082901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401324540376663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39697653055191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400454938411713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390454411506653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387410819530487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383497565984726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382193177938461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381758362054825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371757864952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357844114303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366540193557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360887736082077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362626940011978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369149029254913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379149526357651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3861064016819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394367694854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404368221759796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392628461122513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391758888959885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395237267017365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385671585798264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394802510738373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388280391693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398373305797577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399289101362228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400204926729202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403868108987808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406615495681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407531291246414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40936291217804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408447116613388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40478390455246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405699700117111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401120722293854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402952283620834</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.396541684865952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392193675041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401759386062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40393340587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408716231584549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400020152330399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400889754295349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393063277006149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380019158124924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385236769914627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389150023460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390889257192612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395672082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401324540376663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396976500749588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400454938411713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390454441308975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387410819530487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383497565984726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382193148136139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381758332252502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371757835149765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357844084501266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366540193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360887736082077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362626940011978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369148999452591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379149526357651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3861064016819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394367665052414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404368191957474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392628461122513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391758888959885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395237267017365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385671585798264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39480248093605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388280421495438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398373305797577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399289101362228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400204926729202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403868108987808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406615525484085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407531321048737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409362882375717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408447116613388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40478390455246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405699700117111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401120722293854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402952283620834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402036488056183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393794327974319</t>
+    <t xml:space="preserve">0.402036517858505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393794298171997</t>
   </si>
   <si>
     <t xml:space="preserve">0.39104688167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391962707042694</t>
+    <t xml:space="preserve">0.391962677240372</t>
   </si>
   <si>
     <t xml:space="preserve">0.390131086111069</t>
@@ -3257,22 +3260,22 @@
     <t xml:space="preserve">0.394710093736649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3956258893013</t>
+    <t xml:space="preserve">0.395625919103622</t>
   </si>
   <si>
     <t xml:space="preserve">0.397457480430603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392878502607346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388299465179443</t>
+    <t xml:space="preserve">0.392878472805023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388299494981766</t>
   </si>
   <si>
     <t xml:space="preserve">0.384636282920837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389215290546417</t>
+    <t xml:space="preserve">0.38921532034874</t>
   </si>
   <si>
     <t xml:space="preserve">0.386467903852463</t>
@@ -3299,13 +3302,13 @@
     <t xml:space="preserve">0.380973100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375478267669678</t>
+    <t xml:space="preserve">0.375478297472</t>
   </si>
   <si>
     <t xml:space="preserve">0.373646676540375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371815055608749</t>
+    <t xml:space="preserve">0.371815085411072</t>
   </si>
   <si>
     <t xml:space="preserve">0.369067668914795</t>
@@ -3314,7 +3317,7 @@
     <t xml:space="preserve">0.369983494281769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376394093036652</t>
+    <t xml:space="preserve">0.376394122838974</t>
   </si>
   <si>
     <t xml:space="preserve">0.374562501907349</t>
@@ -3323,7 +3326,7 @@
     <t xml:space="preserve">0.37089928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378225684165955</t>
+    <t xml:space="preserve">0.378225654363632</t>
   </si>
   <si>
     <t xml:space="preserve">0.385552108287811</t>
@@ -3341,10 +3344,10 @@
     <t xml:space="preserve">0.420352518558502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421268343925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425847321748734</t>
+    <t xml:space="preserve">0.421268314123154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425847351551056</t>
   </si>
   <si>
     <t xml:space="preserve">0.416689306497574</t>
@@ -3374,7 +3377,7 @@
     <t xml:space="preserve">0.415773510932922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410278707742691</t>
+    <t xml:space="preserve">0.410278737545013</t>
   </si>
   <si>
     <t xml:space="preserve">0.422184109687805</t>
@@ -3392,19 +3395,19 @@
     <t xml:space="preserve">0.456068724393845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445994943380356</t>
+    <t xml:space="preserve">0.445994913578033</t>
   </si>
   <si>
     <t xml:space="preserve">0.494532406330109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48720595240593</t>
+    <t xml:space="preserve">0.487206012010574</t>
   </si>
   <si>
     <t xml:space="preserve">0.492700755596161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481711208820343</t>
+    <t xml:space="preserve">0.481711179018021</t>
   </si>
   <si>
     <t xml:space="preserve">0.489037543535233</t>
@@ -3413,16 +3416,16 @@
     <t xml:space="preserve">0.496363997459412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485374301671982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483542799949646</t>
+    <t xml:space="preserve">0.485374361276627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483542770147324</t>
   </si>
   <si>
     <t xml:space="preserve">0.454237133264542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463395118713379</t>
+    <t xml:space="preserve">0.463395148515701</t>
   </si>
   <si>
     <t xml:space="preserve">0.476216346025467</t>
@@ -3795,6 +3798,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.449999988079071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47299998998642</t>
   </si>
 </sst>
 </file>
@@ -53785,7 +53791,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1910" t="s">
-        <v>1026</v>
+        <v>1075</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53811,7 +53817,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1911" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53863,7 +53869,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1913" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53889,7 +53895,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1914" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53915,7 +53921,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1915" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53941,7 +53947,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1916" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53967,7 +53973,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1917" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53993,7 +53999,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1918" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54019,7 +54025,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1919" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54045,7 +54051,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1920" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54071,7 +54077,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1921" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54097,7 +54103,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1922" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54123,7 +54129,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1923" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54149,7 +54155,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1924" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54175,7 +54181,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1925" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54201,7 +54207,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1926" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54227,7 +54233,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1927" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54279,7 +54285,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1929" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54305,7 +54311,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1930" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54331,7 +54337,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1931" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54357,7 +54363,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1932" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54383,7 +54389,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1933" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54409,7 +54415,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1934" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54435,7 +54441,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1935" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54461,7 +54467,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1936" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54487,7 +54493,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1937" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54513,7 +54519,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1938" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54539,7 +54545,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1939" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54565,7 +54571,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1940" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54591,7 +54597,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1941" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54617,7 +54623,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1942" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54643,7 +54649,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1943" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54669,7 +54675,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1944" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54695,7 +54701,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1945" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54721,7 +54727,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1946" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54747,7 +54753,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1947" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54773,7 +54779,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1948" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54799,7 +54805,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1949" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54955,7 +54961,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1955" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55111,7 +55117,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1961" t="s">
-        <v>1026</v>
+        <v>1075</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55189,7 +55195,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1964" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55215,7 +55221,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1965" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55241,7 +55247,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1966" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55267,7 +55273,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1967" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55293,7 +55299,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1968" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55319,7 +55325,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1969" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55345,7 +55351,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1970" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55371,7 +55377,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -55397,7 +55403,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1972" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55423,7 +55429,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1973" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55449,7 +55455,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1974" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55475,7 +55481,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1975" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55501,7 +55507,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1976" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55527,7 +55533,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1977" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55553,7 +55559,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1978" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55579,7 +55585,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1979" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55605,7 +55611,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1980" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55631,7 +55637,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1981" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55657,7 +55663,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1982" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55683,7 +55689,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1983" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55709,7 +55715,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1984" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55735,7 +55741,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1985" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55761,7 +55767,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1986" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55787,7 +55793,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1987" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55813,7 +55819,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1988" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55839,7 +55845,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1989" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55865,7 +55871,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G1990" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55891,7 +55897,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1991" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55917,7 +55923,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1992" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55943,7 +55949,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1993" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55969,7 +55975,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1994" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55995,7 +56001,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1995" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56021,7 +56027,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1996" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56047,7 +56053,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1997" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56073,7 +56079,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1998" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56099,7 +56105,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1999" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56125,7 +56131,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2000" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56151,7 +56157,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2001" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56177,7 +56183,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2002" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56203,7 +56209,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2003" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56229,7 +56235,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2004" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56255,7 +56261,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2005" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56281,7 +56287,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2006" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56307,7 +56313,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2007" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56333,7 +56339,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2008" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56359,7 +56365,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2009" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56385,7 +56391,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2010" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56411,7 +56417,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2011" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56437,7 +56443,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2012" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56463,7 +56469,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56489,7 +56495,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2014" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56515,7 +56521,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2015" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56541,7 +56547,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2016" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56567,7 +56573,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56619,7 +56625,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56645,7 +56651,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2020" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56671,7 +56677,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2021" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56697,7 +56703,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2022" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56723,7 +56729,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2023" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56749,7 +56755,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2024" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56775,7 +56781,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G2025" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56801,7 +56807,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2026" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56827,7 +56833,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2027" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56853,7 +56859,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2028" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56879,7 +56885,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G2029" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56905,7 +56911,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2030" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56931,7 +56937,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2031" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56957,7 +56963,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2032" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56983,7 +56989,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2033" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57009,7 +57015,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2034" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57035,7 +57041,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2035" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57061,7 +57067,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2036" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57087,7 +57093,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2037" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57113,7 +57119,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2038" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57139,7 +57145,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2039" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57165,7 +57171,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2040" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57191,7 +57197,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57217,7 +57223,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2042" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57243,7 +57249,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2043" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57295,7 +57301,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2045" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57503,7 +57509,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2053" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57529,7 +57535,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2054" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57737,7 +57743,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2062" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57789,7 +57795,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2064" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57815,7 +57821,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2065" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57841,7 +57847,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2066" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57867,7 +57873,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2067" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57919,7 +57925,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2069" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58205,7 +58211,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2080" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58257,7 +58263,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2082" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58283,7 +58289,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G2083" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -58309,7 +58315,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2084" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58335,7 +58341,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2085" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58361,7 +58367,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2086" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58387,7 +58393,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2087" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -58413,7 +58419,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2088" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58569,7 +58575,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2094" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58595,7 +58601,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2095" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58621,7 +58627,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2096" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58647,7 +58653,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2097" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58673,7 +58679,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2098" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58803,7 +58809,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2103" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58829,7 +58835,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2104" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58855,7 +58861,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2105" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58881,7 +58887,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2106" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58907,7 +58913,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2107" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59193,7 +59199,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2118" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59219,7 +59225,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2119" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59245,7 +59251,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G2120" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59271,7 +59277,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2121" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59297,7 +59303,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2122" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59323,7 +59329,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G2123" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59349,7 +59355,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2124" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59375,7 +59381,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2125" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59401,7 +59407,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2126" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59427,7 +59433,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2127" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59453,7 +59459,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2128" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59479,7 +59485,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2129" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59505,7 +59511,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2130" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59531,7 +59537,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2131" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59557,7 +59563,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2132" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59583,7 +59589,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2133" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59609,7 +59615,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2134" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59635,7 +59641,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2135" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59661,7 +59667,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2136" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59687,7 +59693,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2137" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59713,7 +59719,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2138" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59739,7 +59745,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2139" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59765,7 +59771,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2140" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59791,7 +59797,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2141" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59817,7 +59823,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2142" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59843,7 +59849,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2143" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59869,7 +59875,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2144" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59895,7 +59901,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2145" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59921,7 +59927,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2146" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59947,7 +59953,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2147" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59973,7 +59979,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2148" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59999,7 +60005,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2149" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60025,7 +60031,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2150" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60051,7 +60057,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G2151" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60077,7 +60083,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2152" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60103,7 +60109,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2153" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60129,7 +60135,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2154" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60155,7 +60161,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2155" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60181,7 +60187,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60207,7 +60213,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60233,7 +60239,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2158" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60259,7 +60265,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2159" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60285,7 +60291,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2160" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60311,7 +60317,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2161" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60337,7 +60343,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2162" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60363,7 +60369,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2163" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60389,7 +60395,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2164" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60415,7 +60421,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2165" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60441,7 +60447,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2166" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60467,7 +60473,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2167" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60493,7 +60499,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2168" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60519,7 +60525,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2169" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60545,7 +60551,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2170" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60571,7 +60577,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2171" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60597,7 +60603,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2172" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60623,7 +60629,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2173" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60649,7 +60655,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2174" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60675,7 +60681,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2175" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60701,7 +60707,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2176" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60727,7 +60733,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2177" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60753,7 +60759,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2178" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60779,7 +60785,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2179" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60805,7 +60811,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2180" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60831,7 +60837,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2181" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60857,7 +60863,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2182" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60883,7 +60889,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2183" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60909,7 +60915,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2184" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60935,7 +60941,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2185" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60961,7 +60967,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2186" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60987,7 +60993,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2187" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61013,7 +61019,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2188" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61039,7 +61045,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2189" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61065,7 +61071,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61091,7 +61097,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2191" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61117,7 +61123,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2192" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61143,7 +61149,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2193" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61169,7 +61175,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2194" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61195,7 +61201,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2195" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61221,7 +61227,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2196" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61247,7 +61253,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2197" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61273,7 +61279,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2198" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61299,7 +61305,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2199" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61325,7 +61331,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2200" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61351,7 +61357,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2201" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61377,7 +61383,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2202" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61403,7 +61409,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2203" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61429,7 +61435,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2204" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61455,7 +61461,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2205" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61481,7 +61487,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2206" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61507,7 +61513,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2207" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61533,7 +61539,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2208" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61559,7 +61565,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2209" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61585,7 +61591,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2210" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61611,7 +61617,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2211" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61637,7 +61643,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2212" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61663,7 +61669,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2213" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61689,7 +61695,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2214" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61715,7 +61721,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61741,7 +61747,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2216" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61767,7 +61773,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2217" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61793,7 +61799,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2218" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61819,7 +61825,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2219" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61845,7 +61851,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2220" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61871,7 +61877,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2221" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61897,7 +61903,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2222" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61923,7 +61929,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2223" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61949,7 +61955,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2224" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61975,7 +61981,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2225" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62001,7 +62007,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2226" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62027,7 +62033,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2227" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62053,7 +62059,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2228" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62079,7 +62085,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2229" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62105,7 +62111,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2230" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62131,7 +62137,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2231" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62157,7 +62163,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2232" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62183,7 +62189,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2233" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62209,7 +62215,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2234" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62235,7 +62241,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2235" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62261,7 +62267,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2236" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62287,7 +62293,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2237" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62313,7 +62319,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2238" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62339,7 +62345,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2239" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62365,7 +62371,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2240" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62391,7 +62397,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2241" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62417,7 +62423,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2242" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62443,7 +62449,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2243" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62469,7 +62475,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2244" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62495,7 +62501,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2245" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62521,7 +62527,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2246" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62547,7 +62553,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62573,7 +62579,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62599,7 +62605,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2249" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62625,7 +62631,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2250" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62651,7 +62657,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2251" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62677,7 +62683,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2252" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62703,7 +62709,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G2253" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62729,7 +62735,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2254" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62755,7 +62761,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2255" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62781,7 +62787,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2256" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62807,7 +62813,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2257" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62833,7 +62839,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2258" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62859,7 +62865,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2259" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62885,7 +62891,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2260" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62911,7 +62917,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2261" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62937,7 +62943,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2262" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62963,7 +62969,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2263" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62989,7 +62995,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2264" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63015,7 +63021,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2265" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63041,7 +63047,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2266" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63067,7 +63073,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2267" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63093,7 +63099,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2268" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63119,7 +63125,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2269" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63145,7 +63151,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63171,7 +63177,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2271" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63197,7 +63203,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2272" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63223,7 +63229,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2273" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63249,7 +63255,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2274" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63275,7 +63281,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2275" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63301,7 +63307,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2276" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63327,7 +63333,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2277" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63353,7 +63359,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2278" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63379,7 +63385,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2279" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63405,7 +63411,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2280" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63431,7 +63437,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2281" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63457,7 +63463,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2282" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63483,7 +63489,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2283" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63509,7 +63515,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2284" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63535,7 +63541,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2285" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63561,7 +63567,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2286" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63587,7 +63593,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2287" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63613,7 +63619,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2288" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63639,7 +63645,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2289" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63665,7 +63671,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2290" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63691,7 +63697,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63717,7 +63723,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2292" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63743,7 +63749,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2293" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63769,7 +63775,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2294" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63795,7 +63801,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2295" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63821,7 +63827,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2296" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63847,7 +63853,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2297" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63873,7 +63879,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2298" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63899,7 +63905,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2299" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63925,7 +63931,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2300" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63951,7 +63957,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2301" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63977,7 +63983,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2302" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64003,7 +64009,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2303" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64029,7 +64035,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2304" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64055,7 +64061,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2305" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64081,7 +64087,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2306" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64107,7 +64113,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2307" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64133,7 +64139,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2308" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64159,7 +64165,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2309" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64185,7 +64191,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2310" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64211,7 +64217,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2311" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64237,7 +64243,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2312" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64263,7 +64269,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2313" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64289,7 +64295,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2314" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64315,7 +64321,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2315" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64341,7 +64347,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2316" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64367,7 +64373,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2317" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64393,7 +64399,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2318" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64419,7 +64425,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2319" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64445,7 +64451,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2320" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64471,7 +64477,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2321" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64497,7 +64503,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2322" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64523,7 +64529,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2323" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64549,7 +64555,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2324" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64575,7 +64581,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2325" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64601,7 +64607,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64627,7 +64633,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2327" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64653,7 +64659,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2328" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64679,7 +64685,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2329" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64705,7 +64711,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2330" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64731,7 +64737,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2331" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64757,7 +64763,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2332" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64783,7 +64789,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2333" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64809,7 +64815,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2334" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64835,7 +64841,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2335" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64861,7 +64867,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2336" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64887,7 +64893,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2337" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64913,7 +64919,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2338" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64939,7 +64945,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2339" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64965,7 +64971,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2340" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64991,7 +64997,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2341" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65017,7 +65023,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2342" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65043,7 +65049,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2343" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65069,7 +65075,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2344" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65095,7 +65101,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2345" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65121,7 +65127,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2346" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65147,7 +65153,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2347" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65173,7 +65179,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2348" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65199,7 +65205,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2349" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65225,7 +65231,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2350" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65251,7 +65257,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2351" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65277,7 +65283,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2352" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65303,7 +65309,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2353" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65329,7 +65335,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2354" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65355,7 +65361,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2355" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65381,7 +65387,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2356" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65407,7 +65413,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2357" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65433,7 +65439,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2358" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65459,7 +65465,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G2359" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65485,7 +65491,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G2360" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65511,7 +65517,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G2361" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65537,7 +65543,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2362" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65563,7 +65569,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2363" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65589,7 +65595,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2364" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65615,7 +65621,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2365" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65641,7 +65647,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G2366" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65667,7 +65673,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2367" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65693,7 +65699,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2368" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65719,7 +65725,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2369" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65745,7 +65751,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2370" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65771,7 +65777,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2371" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65797,7 +65803,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2372" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65823,7 +65829,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2373" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65849,7 +65855,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2374" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65875,7 +65881,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2375" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65901,7 +65907,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2376" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65927,7 +65933,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G2377" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65953,7 +65959,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2378" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65979,7 +65985,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2379" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66005,7 +66011,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2380" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66031,7 +66037,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2381" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66057,7 +66063,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2382" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66083,7 +66089,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2383" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66109,7 +66115,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2384" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66135,7 +66141,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2385" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66161,7 +66167,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2386" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66187,7 +66193,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2387" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66213,7 +66219,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2388" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66239,7 +66245,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2389" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66265,7 +66271,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2390" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66291,7 +66297,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66317,7 +66323,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2392" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66343,7 +66349,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2393" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66369,7 +66375,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2394" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66395,7 +66401,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2395" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66421,7 +66427,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2396" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66447,7 +66453,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2397" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66473,7 +66479,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2398" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66499,7 +66505,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2399" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66525,7 +66531,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G2400" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66551,7 +66557,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G2401" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66577,7 +66583,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2402" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66603,7 +66609,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2403" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66629,7 +66635,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2404" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66655,7 +66661,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2405" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66681,7 +66687,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2406" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66707,7 +66713,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2407" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66733,7 +66739,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2408" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66759,7 +66765,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2409" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66785,7 +66791,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G2410" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66811,7 +66817,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G2411" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66837,7 +66843,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2412" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66863,7 +66869,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2413" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66889,7 +66895,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2414" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66915,7 +66921,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2415" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66941,7 +66947,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2416" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66967,7 +66973,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2417" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66993,7 +66999,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2418" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67019,7 +67025,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2419" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67045,7 +67051,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2420" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67071,7 +67077,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2421" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67097,7 +67103,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2422" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67123,7 +67129,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2423" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67149,7 +67155,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2424" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67175,7 +67181,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2425" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67201,7 +67207,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2426" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67227,7 +67233,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2427" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67253,7 +67259,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2428" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67279,7 +67285,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2429" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67305,7 +67311,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2430" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67331,7 +67337,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2431" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67357,7 +67363,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2432" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67383,7 +67389,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2433" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67409,7 +67415,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2434" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67435,7 +67441,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2435" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67461,7 +67467,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2436" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67487,7 +67493,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G2437" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67513,7 +67519,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2438" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67539,7 +67545,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2439" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67565,7 +67571,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2440" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67591,7 +67597,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2441" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67617,7 +67623,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2442" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67643,7 +67649,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2443" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67669,7 +67675,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2444" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67695,7 +67701,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2445" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67721,7 +67727,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2446" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67747,7 +67753,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2447" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67773,7 +67779,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2448" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67799,7 +67805,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2449" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67825,7 +67831,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2450" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67851,7 +67857,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2451" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67877,7 +67883,7 @@
         <v>0.5</v>
       </c>
       <c r="G2452" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67903,7 +67909,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G2453" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67929,7 +67935,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2454" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67955,7 +67961,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G2455" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67981,7 +67987,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2456" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68007,7 +68013,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2457" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68033,7 +68039,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2458" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68059,7 +68065,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2459" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68085,7 +68091,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G2460" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68111,7 +68117,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2461" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68137,7 +68143,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G2462" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68163,7 +68169,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2463" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68189,7 +68195,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G2464" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68215,7 +68221,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G2465" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68241,7 +68247,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2466" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68267,7 +68273,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2467" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68293,7 +68299,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2468" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68319,7 +68325,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2469" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68345,7 +68351,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2470" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68371,7 +68377,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2471" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68397,7 +68403,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2472" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68423,7 +68429,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G2473" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68449,7 +68455,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2474" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68475,7 +68481,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2475" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68501,7 +68507,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G2476" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68527,7 +68533,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2477" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68553,7 +68559,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2478" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68579,7 +68585,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2479" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68605,7 +68611,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2480" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68631,7 +68637,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2481" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68657,7 +68663,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2482" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68683,7 +68689,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2483" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68709,7 +68715,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2484" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68735,7 +68741,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G2485" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68761,7 +68767,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G2486" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68787,7 +68793,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2487" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68813,7 +68819,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2488" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68839,7 +68845,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G2489" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68865,7 +68871,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2490" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68891,7 +68897,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G2491" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68917,7 +68923,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2492" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68943,7 +68949,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2493" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68951,7 +68957,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6494791667</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>196853</v>
@@ -68969,9 +68975,35 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2494" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6495949074</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>1632239</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>0.47299998998642</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>0.448000013828278</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>0.448000013828278</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>0.47299998998642</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="1263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="1264">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32635235786438</t>
+    <t xml:space="preserve">0.326352387666702</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844811439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323679059743881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980766296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313056260347366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304966032505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29976013302803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309538811445236</t>
+    <t xml:space="preserve">0.326844781637192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323679089546204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980736494064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313056290149689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304966062307358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299760162830353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309538781642914</t>
   </si>
   <si>
     <t xml:space="preserve">0.302503824234009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287097215652466</t>
+    <t xml:space="preserve">0.287097245454788</t>
   </si>
   <si>
     <t xml:space="preserve">0.274363905191422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278655201196671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265288829803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260645776987076</t>
+    <t xml:space="preserve">0.278655230998993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265288770198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260645717382431</t>
   </si>
   <si>
     <t xml:space="preserve">0.270846426486969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269087672233582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272956907749176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270142883062363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265921920537949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29082578420639</t>
+    <t xml:space="preserve">0.269087702035904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272956877946854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270142912864685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265921950340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290825724601746</t>
   </si>
   <si>
     <t xml:space="preserve">0.288433849811554</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">0.294061839580536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276404052972794</t>
+    <t xml:space="preserve">0.276404082775116</t>
   </si>
   <si>
     <t xml:space="preserve">0.273167967796326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262545138597488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260293990373611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246927559375763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246224030852318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23975183069706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240103632211685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271549940109253</t>
+    <t xml:space="preserve">0.262545168399811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260293960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246927529573441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24622406065464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239751860499382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240103617310524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271549910306931</t>
   </si>
   <si>
     <t xml:space="preserve">0.276122659444809</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">0.274645298719406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277881413698196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270987123250961</t>
+    <t xml:space="preserve">0.277881443500519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270987153053284</t>
   </si>
   <si>
     <t xml:space="preserve">0.281539589166641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277177900075912</t>
+    <t xml:space="preserve">0.27717787027359</t>
   </si>
   <si>
     <t xml:space="preserve">0.26331901550293</t>
@@ -161,31 +161,31 @@
     <t xml:space="preserve">0.28210237622261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295468837022781</t>
+    <t xml:space="preserve">0.295468807220459</t>
   </si>
   <si>
     <t xml:space="preserve">0.293358325958252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291740298271179</t>
+    <t xml:space="preserve">0.291740328073502</t>
   </si>
   <si>
     <t xml:space="preserve">0.288644909858704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288504183292389</t>
+    <t xml:space="preserve">0.288504213094711</t>
   </si>
   <si>
     <t xml:space="preserve">0.281469225883484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277248233556747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278373837471008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287026792764664</t>
+    <t xml:space="preserve">0.277248293161392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278373867273331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287026882171631</t>
   </si>
   <si>
     <t xml:space="preserve">0.297368258237839</t>
@@ -194,19 +194,19 @@
     <t xml:space="preserve">0.295820593833923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307217210531235</t>
+    <t xml:space="preserve">0.307217240333557</t>
   </si>
   <si>
     <t xml:space="preserve">0.305669546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313759744167328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320443004369736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317417949438095</t>
+    <t xml:space="preserve">0.31375977396965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320442974567413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317417979240417</t>
   </si>
   <si>
     <t xml:space="preserve">0.316573768854141</t>
@@ -215,88 +215,88 @@
     <t xml:space="preserve">0.306161999702454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310945779085159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311438173055649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301800280809402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288011729717255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288082093000412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28055465221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281328529119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291881024837494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301378190517426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311649292707443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310242265462875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311508536338806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314533621072769</t>
+    <t xml:space="preserve">0.310945749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311438202857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301800340414047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288011759519577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288082122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280554682016373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281328558921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291880995035172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301378220319748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311649262905121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310242295265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311508566141129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314533591270447</t>
   </si>
   <si>
     <t xml:space="preserve">0.316644102334976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318684279918671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330573379993439</t>
+    <t xml:space="preserve">0.318684220314026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330573350191116</t>
   </si>
   <si>
     <t xml:space="preserve">0.330643713474274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334161192178726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333527982234955</t>
+    <t xml:space="preserve">0.334161162376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3335280418396</t>
   </si>
   <si>
     <t xml:space="preserve">0.330432623624802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327126234769821</t>
+    <t xml:space="preserve">0.327126175165176</t>
   </si>
   <si>
     <t xml:space="preserve">0.323538392782211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318543523550034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319247007369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32311624288559</t>
+    <t xml:space="preserve">0.318543583154678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319247037172318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323116302490234</t>
   </si>
   <si>
     <t xml:space="preserve">0.321005791425705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324875026941299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323749393224716</t>
+    <t xml:space="preserve">0.324874997138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323749452829361</t>
   </si>
   <si>
     <t xml:space="preserve">0.325015723705292</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">0.321076154708862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326774477958679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331769317388535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344713687896729</t>
+    <t xml:space="preserve">0.326774448156357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331769287586212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344713628292084</t>
   </si>
   <si>
     <t xml:space="preserve">0.342040359973907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338030427694321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352100342512131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354914337396622</t>
+    <t xml:space="preserve">0.338030397891998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352100372314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354914367198944</t>
   </si>
   <si>
     <t xml:space="preserve">0.351678282022476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350341588258743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343306601047516</t>
+    <t xml:space="preserve">0.350341618061066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343306660652161</t>
   </si>
   <si>
     <t xml:space="preserve">0.343165963888168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341196149587631</t>
+    <t xml:space="preserve">0.341196209192276</t>
   </si>
   <si>
     <t xml:space="preserve">0.340211242437363</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">0.337045520544052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323537737131119</t>
+    <t xml:space="preserve">0.323537766933441</t>
   </si>
   <si>
     <t xml:space="preserve">0.309325873851776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3121537566185</t>
+    <t xml:space="preserve">0.312153726816177</t>
   </si>
   <si>
     <t xml:space="preserve">0.308890819549561</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">0.311936229467392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325278013944626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322232604026794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318607091903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324190348386765</t>
+    <t xml:space="preserve">0.325277954339981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322232574224472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318607151508331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32419028878212</t>
   </si>
   <si>
     <t xml:space="preserve">0.307223081588745</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">0.299102038145065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299464523792267</t>
+    <t xml:space="preserve">0.299464553594589</t>
   </si>
   <si>
     <t xml:space="preserve">0.313096404075623</t>
@@ -389,58 +389,58 @@
     <t xml:space="preserve">0.320854902267456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318027019500732</t>
+    <t xml:space="preserve">0.318027079105377</t>
   </si>
   <si>
     <t xml:space="preserve">0.319042176008224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318317055702209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309543401002884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311791181564331</t>
+    <t xml:space="preserve">0.318317115306854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309543430805206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311791211366653</t>
   </si>
   <si>
     <t xml:space="preserve">0.310558527708054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311066120862961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322087585926056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319767266511917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318172037601471</t>
+    <t xml:space="preserve">0.311066091060638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322087556123734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31976729631424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318172067403793</t>
   </si>
   <si>
     <t xml:space="preserve">0.309978455305099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30671551823616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305627912282944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301784873008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300914734601974</t>
+    <t xml:space="preserve">0.306715548038483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305627882480621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30178490281105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">0.298739492893219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298014372587204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291488528251648</t>
+    <t xml:space="preserve">0.298014402389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291488498449326</t>
   </si>
   <si>
     <t xml:space="preserve">0.294316381216049</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">0.301204770803452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302727460861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303815186023712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30062472820282</t>
+    <t xml:space="preserve">0.302727490663528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303815126419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300624758005142</t>
   </si>
   <si>
     <t xml:space="preserve">0.29743430018425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299682110548019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301929891109467</t>
+    <t xml:space="preserve">0.299682080745697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301929920911789</t>
   </si>
   <si>
     <t xml:space="preserve">0.301712334156036</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">0.302364975214005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300117164850235</t>
+    <t xml:space="preserve">0.300117135047913</t>
   </si>
   <si>
     <t xml:space="preserve">0.302219957113266</t>
@@ -491,52 +491,52 @@
     <t xml:space="preserve">0.293663799762726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297289282083511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291706025600433</t>
+    <t xml:space="preserve">0.297289311885834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291706055402756</t>
   </si>
   <si>
     <t xml:space="preserve">0.292358636856079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290038377046585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287500470876694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292648643255234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287645488977432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295041471719742</t>
+    <t xml:space="preserve">0.29003831744194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287500500679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292648673057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287645518779755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295041501522064</t>
   </si>
   <si>
     <t xml:space="preserve">0.291561037302017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294533908367157</t>
+    <t xml:space="preserve">0.294533938169479</t>
   </si>
   <si>
     <t xml:space="preserve">0.289313226938248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287935525178909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283004939556122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287427961826324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282859861850739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275826454162598</t>
+    <t xml:space="preserve">0.287935554981232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283004879951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287427991628647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282859891653061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27582648396492</t>
   </si>
   <si>
     <t xml:space="preserve">0.279161870479584</t>
@@ -545,40 +545,40 @@
     <t xml:space="preserve">0.269735664129257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273288667201996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279524475336075</t>
+    <t xml:space="preserve">0.273288607597351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279524445533752</t>
   </si>
   <si>
     <t xml:space="preserve">0.282062292098999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283802479505539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282134741544724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287137895822525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292866170406342</t>
+    <t xml:space="preserve">0.283802509307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282134771347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28713795542717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292866200208664</t>
   </si>
   <si>
     <t xml:space="preserve">0.301422297954559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295839041471481</t>
+    <t xml:space="preserve">0.295839130878448</t>
   </si>
   <si>
     <t xml:space="preserve">0.296564221382141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300262153148651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297071754932404</t>
+    <t xml:space="preserve">0.300262182950974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297071784734726</t>
   </si>
   <si>
     <t xml:space="preserve">0.292938709259033</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">0.298812001943588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296056658029556</t>
+    <t xml:space="preserve">0.296056687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.310195982456207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306425482034683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302509963512421</t>
+    <t xml:space="preserve">0.306425511837006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302509993314743</t>
   </si>
   <si>
     <t xml:space="preserve">0.306062936782837</t>
@@ -608,46 +608,46 @@
     <t xml:space="preserve">0.30163985490799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294098883867264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283077418804169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287863045930862</t>
+    <t xml:space="preserve">0.294098913669586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283077448606491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287863075733185</t>
   </si>
   <si>
     <t xml:space="preserve">0.289603263139725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285615235567093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2839475274086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288805693387985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293736308813095</t>
+    <t xml:space="preserve">0.285615295171738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283947557210922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28880563378334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293736279010773</t>
   </si>
   <si>
     <t xml:space="preserve">0.290835946798325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283512473106384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281409651041031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280684560537338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279016852378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273796200752258</t>
+    <t xml:space="preserve">0.283512502908707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281409680843353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280684590339661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279016822576523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273796170949936</t>
   </si>
   <si>
     <t xml:space="preserve">0.291415989398956</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">0.290545910596848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288588106632233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292213618755341</t>
+    <t xml:space="preserve">0.288588166236877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292213588953018</t>
   </si>
   <si>
     <t xml:space="preserve">0.292141109704971</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">0.29939204454422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296491652727127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303597629070282</t>
+    <t xml:space="preserve">0.296491682529449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303597658872604</t>
   </si>
   <si>
     <t xml:space="preserve">0.309615910053253</t>
@@ -689,19 +689,19 @@
     <t xml:space="preserve">0.319187194108963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331513822078705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331368774175644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345000594854355</t>
+    <t xml:space="preserve">0.331513851881027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331368803977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345000624656677</t>
   </si>
   <si>
     <t xml:space="preserve">0.349786221981049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358342379331589</t>
+    <t xml:space="preserve">0.358342349529266</t>
   </si>
   <si>
     <t xml:space="preserve">0.354209333658218</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">0.34964120388031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352396577596664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35529699921608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359429985284805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352686613798141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346885830163956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343187898397446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346160769462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346595793962479</t>
+    <t xml:space="preserve">0.352396547794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355296939611435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35943004488945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352686643600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346885800361633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343187868595123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346160739660263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346595764160156</t>
   </si>
   <si>
     <t xml:space="preserve">0.346450805664062</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">0.344348013401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350221306085587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350946366786957</t>
+    <t xml:space="preserve">0.350221335887909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350946396589279</t>
   </si>
   <si>
     <t xml:space="preserve">0.388288795948029</t>
@@ -752,85 +752,85 @@
     <t xml:space="preserve">0.397715032100677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379950195550919</t>
+    <t xml:space="preserve">0.379950255155563</t>
   </si>
   <si>
     <t xml:space="preserve">0.382125526666641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374874532222748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37342432141304</t>
+    <t xml:space="preserve">0.37487456202507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373424351215363</t>
   </si>
   <si>
     <t xml:space="preserve">0.377412378787994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373061835765839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369798898696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383575707674026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369436353445053</t>
+    <t xml:space="preserve">0.373061805963516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369798868894577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383575677871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369436323642731</t>
   </si>
   <si>
     <t xml:space="preserve">0.369073778390884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358197301626205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358052313327789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377049803733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412579536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38248798251152</t>
+    <t xml:space="preserve">0.358197331428528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358052343130112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377049833536148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412579566240311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382488042116165</t>
   </si>
   <si>
     <t xml:space="preserve">0.40061542391777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394452154636383</t>
+    <t xml:space="preserve">0.394452124834061</t>
   </si>
   <si>
     <t xml:space="preserve">0.385750979185104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393727004528046</t>
+    <t xml:space="preserve">0.393727034330368</t>
   </si>
   <si>
     <t xml:space="preserve">0.390464097261429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384300768375397</t>
+    <t xml:space="preserve">0.384300738573074</t>
   </si>
   <si>
     <t xml:space="preserve">0.39155176281929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387563735246658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390826672315598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395177245140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393364518880844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397352486848831</t>
+    <t xml:space="preserve">0.387563675642014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390826612710953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395177274942398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393364548683167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397352516651154</t>
   </si>
   <si>
     <t xml:space="preserve">0.398802727460861</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">0.396627426147461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398440092802048</t>
+    <t xml:space="preserve">0.39844012260437</t>
   </si>
   <si>
     <t xml:space="preserve">0.395902365446091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393001943826675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398077636957169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401703089475632</t>
+    <t xml:space="preserve">0.393001973628998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398077607154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401703149080276</t>
   </si>
   <si>
     <t xml:space="preserve">0.392276853322983</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">0.386476069688797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382850617170334</t>
+    <t xml:space="preserve">0.382850587368011</t>
   </si>
   <si>
     <t xml:space="preserve">0.394089579582214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38937646150589</t>
+    <t xml:space="preserve">0.389376431703568</t>
   </si>
   <si>
     <t xml:space="preserve">0.381762951612473</t>
@@ -884,37 +884,37 @@
     <t xml:space="preserve">0.386838614940643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38865140080452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385025888681412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391189157962799</t>
+    <t xml:space="preserve">0.388651371002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385025948286057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391189187765121</t>
   </si>
   <si>
     <t xml:space="preserve">0.392639368772507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425631254911423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419105350971222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445208847522736</t>
+    <t xml:space="preserve">0.425631284713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419105380773544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445208877325058</t>
   </si>
   <si>
     <t xml:space="preserve">0.435057491064072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442308515310287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432612001895905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413591951131821</t>
+    <t xml:space="preserve">0.442308455705643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432611912488937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413591980934143</t>
   </si>
   <si>
     <t xml:space="preserve">0.408370792865753</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">0.406879007816315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402776688337326</t>
+    <t xml:space="preserve">0.402776658535004</t>
   </si>
   <si>
     <t xml:space="preserve">0.399047285318375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400539040565491</t>
+    <t xml:space="preserve">0.400538980960846</t>
   </si>
   <si>
     <t xml:space="preserve">0.395317822694778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396809607744217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396063774824142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393080234527588</t>
+    <t xml:space="preserve">0.396809637546539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39606374502182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393080204725266</t>
   </si>
   <si>
     <t xml:space="preserve">0.388604909181595</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">0.379654318094254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381146103143692</t>
+    <t xml:space="preserve">0.38114607334137</t>
   </si>
   <si>
     <t xml:space="preserve">0.383010774850845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387486100196838</t>
+    <t xml:space="preserve">0.387486070394516</t>
   </si>
   <si>
     <t xml:space="preserve">0.384875476360321</t>
@@ -971,43 +971,43 @@
     <t xml:space="preserve">0.386740148067474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390096694231033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394944906234741</t>
+    <t xml:space="preserve">0.390096664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394944936037064</t>
   </si>
   <si>
     <t xml:space="preserve">0.403522580862045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410235524177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407252013683319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407624900341034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40874370932579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406506150960922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400911957025528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394199043512344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39867427945137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39084255695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392334312200546</t>
+    <t xml:space="preserve">0.410235494375229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407251954078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407624989748001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408743739128113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406506091356277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40091198682785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394199073314667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398674339056015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390842586755753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392334371805191</t>
   </si>
   <si>
     <t xml:space="preserve">0.388231962919235</t>
@@ -1022,46 +1022,46 @@
     <t xml:space="preserve">0.389350801706314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38562136888504</t>
+    <t xml:space="preserve">0.385621398687363</t>
   </si>
   <si>
     <t xml:space="preserve">0.380773156881332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385248392820358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383383750915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397928416728973</t>
+    <t xml:space="preserve">0.385248422622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383383691310883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397928446531296</t>
   </si>
   <si>
     <t xml:space="preserve">0.409489661455154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410981386899948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414337784051895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415083736181259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416575461626053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415829628705978</t>
+    <t xml:space="preserve">0.410981416702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414337813854218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415083765983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416575521230698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415829598903656</t>
   </si>
   <si>
     <t xml:space="preserve">0.424034297466278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439324915409088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866109371185</t>
+    <t xml:space="preserve">0.439324945211411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866139173508</t>
   </si>
   <si>
     <t xml:space="preserve">0.428882569074631</t>
@@ -1079,85 +1079,85 @@
     <t xml:space="preserve">0.454988539218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445291966199875</t>
+    <t xml:space="preserve">0.445291936397552</t>
   </si>
   <si>
     <t xml:space="preserve">0.4445461332798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440443724393845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449767231941223</t>
+    <t xml:space="preserve">0.440443783998489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449767291545868</t>
   </si>
   <si>
     <t xml:space="preserve">0.459463775157928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460955500602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469533145427704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466549664735794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474008530378342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474754363298416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348438024521</t>
+    <t xml:space="preserve">0.4609554708004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469533175230026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466549634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474008500576019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474754333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480348527431488</t>
   </si>
   <si>
     <t xml:space="preserve">0.485942602157593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482586205005646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485569655895233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509437918663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511302590370178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521745026111603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512794435024261</t>
+    <t xml:space="preserve">0.482586145401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485569626092911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50943797826767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511302709579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521744966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512794375419617</t>
   </si>
   <si>
     <t xml:space="preserve">0.5195072889328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511675596237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506081402301788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501233279705048</t>
+    <t xml:space="preserve">0.511675536632538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506081461906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501233160495758</t>
   </si>
   <si>
     <t xml:space="preserve">0.502351999282837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495266109704971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491536796092987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477737873792648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478483766317368</t>
+    <t xml:space="preserve">0.495266139507294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491536736488342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477737933397293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478483706712723</t>
   </si>
   <si>
     <t xml:space="preserve">0.48109433054924</t>
@@ -1166,67 +1166,67 @@
     <t xml:space="preserve">0.492282658815384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499741405248642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493774384260178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495639085769653</t>
+    <t xml:space="preserve">0.49974137544632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493774354457855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495638996362686</t>
   </si>
   <si>
     <t xml:space="preserve">0.507946133613586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500114381313324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493028491735458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508691966533661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503470838069916</t>
+    <t xml:space="preserve">0.500114262104034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493028521537781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508692026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503470897674561</t>
   </si>
   <si>
     <t xml:space="preserve">0.508319139480591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507200300693512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510183870792389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513167321681976</t>
+    <t xml:space="preserve">0.507200241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510183811187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513167381286621</t>
   </si>
   <si>
     <t xml:space="preserve">0.500860273838043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503097891807556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502725005149841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501606166362762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498249709606171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510929703712463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531068503856659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557920277118683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554936707019806</t>
+    <t xml:space="preserve">0.503097951412201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502724945545197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501606106758118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498249590396881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510929644107819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531068563461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557920336723328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554936826229095</t>
   </si>
   <si>
     <t xml:space="preserve">0.559412062168121</t>
@@ -1235,61 +1235,61 @@
     <t xml:space="preserve">0.56537914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593722641468048</t>
+    <t xml:space="preserve">0.593722701072693</t>
   </si>
   <si>
     <t xml:space="preserve">0.574329674243927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57656729221344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577313125133514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583280265331268</t>
+    <t xml:space="preserve">0.576567351818085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577313184738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583280324935913</t>
   </si>
   <si>
     <t xml:space="preserve">0.591485023498535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585518002510071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575075507164001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61236971616745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556428492069244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551953256130219</t>
+    <t xml:space="preserve">0.585517942905426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575075626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612369775772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556428551673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551953196525574</t>
   </si>
   <si>
     <t xml:space="preserve">0.548223853111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534797966480255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521372079849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505708515644073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528084993362427</t>
+    <t xml:space="preserve">0.53479790687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521372020244598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505708456039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528084933757782</t>
   </si>
   <si>
     <t xml:space="preserve">0.54524028301239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522863745689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517642617225647</t>
+    <t xml:space="preserve">0.522863686084747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517642676830292</t>
   </si>
   <si>
     <t xml:space="preserve">0.532560288906097</t>
@@ -1313,160 +1313,160 @@
     <t xml:space="preserve">0.498995572328568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463193148374557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469906151294708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476619094610214</t>
+    <t xml:space="preserve">0.463193207979202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469906121492386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476619064807892</t>
   </si>
   <si>
     <t xml:space="preserve">0.477364927530289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494520276784897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490044951438904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478856772184372</t>
+    <t xml:space="preserve">0.494520217180252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490044981241226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478856712579727</t>
   </si>
   <si>
     <t xml:space="preserve">0.478110909461975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46841436624527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481840223073959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484077870845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475127369165421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47363555431366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474381417036057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484823763370514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487061470746994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48333203792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50421667098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504962563514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496757984161377</t>
+    <t xml:space="preserve">0.468414396047592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481840282678604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484077900648117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475127309560776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47363543510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474381387233734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484823822975159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487061500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483332067728043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504216730594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504962623119354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49675789475441</t>
   </si>
   <si>
     <t xml:space="preserve">0.497503817081451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486315459012985</t>
+    <t xml:space="preserve">0.48631551861763</t>
   </si>
   <si>
     <t xml:space="preserve">0.500487387180328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454242616891861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465430825948715</t>
+    <t xml:space="preserve">0.454242587089539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465430855751038</t>
   </si>
   <si>
     <t xml:space="preserve">0.452004939317703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457226157188416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458717852830887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462447315454483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455734401941299</t>
+    <t xml:space="preserve">0.457226067781448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458717882633209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462447255849838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455734372138977</t>
   </si>
   <si>
     <t xml:space="preserve">0.457972019910812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485727906227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484185874462128</t>
+    <t xml:space="preserve">0.485727846622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484185934066772</t>
   </si>
   <si>
     <t xml:space="preserve">0.474933952093124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469536960124969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464910924434662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461056023836136</t>
+    <t xml:space="preserve">0.469536930322647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464910984039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461055964231491</t>
   </si>
   <si>
     <t xml:space="preserve">0.463369011878967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459513992071152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457971960306168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458743005990982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447949022054672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451033025979996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454887956380844</t>
+    <t xml:space="preserve">0.459514021873474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45797199010849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45874297618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447948962450027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451033055782318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454887986183167</t>
   </si>
   <si>
     <t xml:space="preserve">0.446407049894333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441781133413315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443323075771332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494208872318268</t>
+    <t xml:space="preserve">0.441781044006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443323045969009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494208812713623</t>
   </si>
   <si>
     <t xml:space="preserve">0.474162876605988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481101900339127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489582896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476475894451141</t>
+    <t xml:space="preserve">0.481101930141449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489582866430283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476475924253464</t>
   </si>
   <si>
     <t xml:space="preserve">0.464139968156815</t>
@@ -1475,19 +1475,19 @@
     <t xml:space="preserve">0.461826980113983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456430047750473</t>
+    <t xml:space="preserve">0.456430017948151</t>
   </si>
   <si>
     <t xml:space="preserve">0.454117000102997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466453015804291</t>
+    <t xml:space="preserve">0.466452926397324</t>
   </si>
   <si>
     <t xml:space="preserve">0.467223972082138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439468115568161</t>
+    <t xml:space="preserve">0.439468085765839</t>
   </si>
   <si>
     <t xml:space="preserve">0.442552089691162</t>
@@ -1496,106 +1496,106 @@
     <t xml:space="preserve">0.45257505774498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453346014022827</t>
+    <t xml:space="preserve">0.453345984220505</t>
   </si>
   <si>
     <t xml:space="preserve">0.4410100877285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437926113605499</t>
+    <t xml:space="preserve">0.437926083803177</t>
   </si>
   <si>
     <t xml:space="preserve">0.433300107717514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430987119674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431758105754852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435613065958023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444865047931671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284948348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45180407166481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470308035612106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471849948167801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465681999921799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45720100402832</t>
+    <t xml:space="preserve">0.430987149477005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431758135557175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435613095760345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444865077733994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460285037755966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451804012060165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470307946205139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471849918365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465681940317154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457200974225998</t>
   </si>
   <si>
     <t xml:space="preserve">0.462597995996475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455658972263336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450262010097504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449491053819656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43715512752533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440239071846008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42636114358902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427903145551682</t>
+    <t xml:space="preserve">0.455659031867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450262039899826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449491024017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437155067920685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440239012241364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426361113786697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427903115749359</t>
   </si>
   <si>
     <t xml:space="preserve">0.407086223363876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406315237283707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410170197486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404002219438553</t>
+    <t xml:space="preserve">0.406315177679062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4101702272892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40400218963623</t>
   </si>
   <si>
     <t xml:space="preserve">0.407857209444046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410941183567047</t>
+    <t xml:space="preserve">0.41094121336937</t>
   </si>
   <si>
     <t xml:space="preserve">0.40014722943306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396292269229889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390895307064056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390124261379242</t>
+    <t xml:space="preserve">0.396292239427567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390895336866379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390124320983887</t>
   </si>
   <si>
     <t xml:space="preserve">0.381643325090408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38318532705307</t>
+    <t xml:space="preserve">0.383185356855392</t>
   </si>
   <si>
     <t xml:space="preserve">0.387811303138733</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">0.388582289218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39475029706955</t>
+    <t xml:space="preserve">0.394750326871872</t>
   </si>
   <si>
     <t xml:space="preserve">0.397063255310059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389353305101395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387040287256241</t>
+    <t xml:space="preserve">0.389353275299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387040317058563</t>
   </si>
   <si>
     <t xml:space="preserve">0.385498285293579</t>
@@ -1622,37 +1622,37 @@
     <t xml:space="preserve">0.375475317239761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366223394870758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351188987493515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345406472682953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348875969648361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36699441075325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372391402721405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367765367031097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162388801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370078384876251</t>
+    <t xml:space="preserve">0.36622342467308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351188957691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345406532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348875939846039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366994380950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372391372919083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36776539683342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162358999252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370078414678574</t>
   </si>
   <si>
     <t xml:space="preserve">0.370463907718658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369692891836166</t>
+    <t xml:space="preserve">0.369692862033844</t>
   </si>
   <si>
     <t xml:space="preserve">0.365837901830673</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">0.368536353111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368921905755997</t>
+    <t xml:space="preserve">0.368921846151352</t>
   </si>
   <si>
     <t xml:space="preserve">0.378944844007492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383570820093155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377017349004745</t>
+    <t xml:space="preserve">0.383570849895477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377017378807068</t>
   </si>
   <si>
     <t xml:space="preserve">0.3824143409729</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">0.416338205337524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424048155546188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424819111824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417109191417694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422506123781204</t>
+    <t xml:space="preserve">0.424048185348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424819141626358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417109131813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422506153583527</t>
   </si>
   <si>
     <t xml:space="preserve">0.421735137701035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420964181423187</t>
+    <t xml:space="preserve">0.420964151620865</t>
   </si>
   <si>
     <t xml:space="preserve">0.408628195524216</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">0.400918215513229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404773205518723</t>
+    <t xml:space="preserve">0.404773235321045</t>
   </si>
   <si>
     <t xml:space="preserve">0.405544251203537</t>
@@ -1721,64 +1721,64 @@
     <t xml:space="preserve">0.412483245134354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423277199268341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425590127706528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41942223906517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430216193199158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427132129669189</t>
+    <t xml:space="preserve">0.423277169466019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42559015750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419422149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430216133594513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427132099866867</t>
   </si>
   <si>
     <t xml:space="preserve">0.414025187492371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41479617357254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413254201412201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40939924120903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395521253347397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393208295106888</t>
+    <t xml:space="preserve">0.414796203374863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413254171609879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409399211406708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395521283149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393208235502243</t>
   </si>
   <si>
     <t xml:space="preserve">0.392437279224396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391666322946548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393979281187057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39860525727272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403231233358383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411275893449783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410471081733704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409666270017624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415300101041794</t>
+    <t xml:space="preserve">0.391666293144226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393979251384735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398605287075043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403231263160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411275923252106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410471051931381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409666240215302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415300130844116</t>
   </si>
   <si>
     <t xml:space="preserve">0.412885636091232</t>
@@ -1793,61 +1793,61 @@
     <t xml:space="preserve">0.401215374469757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404032289981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397996038198471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403227478265762</t>
+    <t xml:space="preserve">0.404032319784164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397996008396149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40322744846344</t>
   </si>
   <si>
     <t xml:space="preserve">0.398398399353027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400008082389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402422666549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400410532951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395983874797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39960566163063</t>
+    <t xml:space="preserve">0.400008141994476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40242263674736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400410562753677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395983844995499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399605631828308</t>
   </si>
   <si>
     <t xml:space="preserve">0.418519526720047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417714715003967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416909873485565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404837220907211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401617825031281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407251685857773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408056557178497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405642032623291</t>
+    <t xml:space="preserve">0.417714655399323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416909843683243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404837191104889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401617795228958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407251715660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40805658698082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405642002820969</t>
   </si>
   <si>
     <t xml:space="preserve">0.397593557834625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391154795885086</t>
+    <t xml:space="preserve">0.391154825687408</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446844339371</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">0.42656797170639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433811604976654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424153476953506</t>
+    <t xml:space="preserve">0.433811575174332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424153417348862</t>
   </si>
   <si>
     <t xml:space="preserve">0.43220192193985</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">0.425763130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428177684545517</t>
+    <t xml:space="preserve">0.428177714347839</t>
   </si>
   <si>
     <t xml:space="preserve">0.433006763458252</t>
@@ -1880,28 +1880,28 @@
     <t xml:space="preserve">0.420934081077576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428982496261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43703094124794</t>
+    <t xml:space="preserve">0.428982526063919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437030971050262</t>
   </si>
   <si>
     <t xml:space="preserve">0.434616476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430592238903046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442664951086044</t>
+    <t xml:space="preserve">0.430592268705368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442664921283722</t>
   </si>
   <si>
     <t xml:space="preserve">0.458761781454086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466810256242752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473249047994614</t>
+    <t xml:space="preserve">0.46681022644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473248988389969</t>
   </si>
   <si>
     <t xml:space="preserve">0.476468414068222</t>
@@ -1910,67 +1910,67 @@
     <t xml:space="preserve">0.478882938623428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475663602352142</t>
+    <t xml:space="preserve">0.47566357254982</t>
   </si>
   <si>
     <t xml:space="preserve">0.481297463178635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478078097105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474858731031418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471639364957809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472444176673889</t>
+    <t xml:space="preserve">0.478078067302704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474858671426773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471639305353165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472444206476212</t>
   </si>
   <si>
     <t xml:space="preserve">0.486126512289047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480492621660233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49497988820076</t>
+    <t xml:space="preserve">0.480492651462555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494979798793793</t>
   </si>
   <si>
     <t xml:space="preserve">0.511881589889526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513491332530975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520734965801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535222113132477</t>
+    <t xml:space="preserve">0.513491272926331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520734906196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535222172737122</t>
   </si>
   <si>
     <t xml:space="preserve">0.534417271614075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523149430751801</t>
+    <t xml:space="preserve">0.523149371147156</t>
   </si>
   <si>
     <t xml:space="preserve">0.515100955963135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516710698604584</t>
+    <t xml:space="preserve">0.516710638999939</t>
   </si>
   <si>
     <t xml:space="preserve">0.522344589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556148111820221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555343270301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551319062709808</t>
+    <t xml:space="preserve">0.556148052215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555343210697174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551319003105164</t>
   </si>
   <si>
     <t xml:space="preserve">0.557757794857025</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">0.571440160274506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561782002449036</t>
+    <t xml:space="preserve">0.56178206205368</t>
   </si>
   <si>
     <t xml:space="preserve">0.560977220535278</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">0.554538428783417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592366099357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596390306949615</t>
+    <t xml:space="preserve">0.59236615896225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59639036655426</t>
   </si>
   <si>
     <t xml:space="preserve">0.599609732627869</t>
@@ -2003,13 +2003,13 @@
     <t xml:space="preserve">0.611682415008545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606853306293488</t>
+    <t xml:space="preserve">0.606853365898132</t>
   </si>
   <si>
     <t xml:space="preserve">0.602024257183075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614901781082153</t>
+    <t xml:space="preserve">0.614901840686798</t>
   </si>
   <si>
     <t xml:space="preserve">0.600414633750916</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">0.608462989330292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593975782394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590756475925446</t>
+    <t xml:space="preserve">0.593975722789764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59075653553009</t>
   </si>
   <si>
     <t xml:space="preserve">0.595585525035858</t>
@@ -2030,19 +2030,19 @@
     <t xml:space="preserve">0.609267890453339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614096939563751</t>
+    <t xml:space="preserve">0.614096999168396</t>
   </si>
   <si>
     <t xml:space="preserve">0.606048464775085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593171000480652</t>
+    <t xml:space="preserve">0.593170940876007</t>
   </si>
   <si>
     <t xml:space="preserve">0.598804891109467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601219356060028</t>
+    <t xml:space="preserve">0.601219415664673</t>
   </si>
   <si>
     <t xml:space="preserve">0.594780683517456</t>
@@ -2051,31 +2051,31 @@
     <t xml:space="preserve">0.603633880615234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610072672367096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598000049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630193769931793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631803452968597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64629065990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655948877334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659973084926605</t>
+    <t xml:space="preserve">0.610072731971741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59799998998642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630193829536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631803512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646290719509125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65594893693924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65997314453125</t>
   </si>
   <si>
     <t xml:space="preserve">0.689752340316772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684118449687958</t>
+    <t xml:space="preserve">0.684118568897247</t>
   </si>
   <si>
     <t xml:space="preserve">0.661582827568054</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">0.588341891765594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581098258495331</t>
+    <t xml:space="preserve">0.581098318099976</t>
   </si>
   <si>
     <t xml:space="preserve">0.572245001792908</t>
@@ -2093,70 +2093,70 @@
     <t xml:space="preserve">0.540856063365936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543270528316498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518320381641388</t>
+    <t xml:space="preserve">0.543270587921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518320322036743</t>
   </si>
   <si>
     <t xml:space="preserve">0.526368796825409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490955591201782</t>
+    <t xml:space="preserve">0.490955621004105</t>
   </si>
   <si>
     <t xml:space="preserve">0.439445495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398800849914551</t>
+    <t xml:space="preserve">0.398800820112228</t>
   </si>
   <si>
     <t xml:space="preserve">0.381496667861938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32314532995224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348095566034317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303829103708267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282500714063644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288939446210861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29135400056839</t>
+    <t xml:space="preserve">0.323145359754562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348095595836639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303829073905945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282500684261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288939476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291354030370712</t>
   </si>
   <si>
     <t xml:space="preserve">0.304633945226669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308255702257156</t>
+    <t xml:space="preserve">0.308255732059479</t>
   </si>
   <si>
     <t xml:space="preserve">0.343668937683105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358961015939713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37224093079567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355741590261459</t>
+    <t xml:space="preserve">0.35896098613739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372240960597992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355741620063782</t>
   </si>
   <si>
     <t xml:space="preserve">0.373850613832474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391959637403488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379082143306732</t>
+    <t xml:space="preserve">0.391959607601166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37908211350441</t>
   </si>
   <si>
     <t xml:space="preserve">0.375057876110077</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">0.362180352210999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351717382669449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353327065706253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349302798509598</t>
+    <t xml:space="preserve">0.351717412471771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353327095508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349302858114243</t>
   </si>
   <si>
     <t xml:space="preserve">0.344473779201508</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">0.323547780513763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338034987449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33964467048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341254353523254</t>
+    <t xml:space="preserve">0.338034957647324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339644730091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341254383325577</t>
   </si>
   <si>
     <t xml:space="preserve">0.346083492040634</t>
@@ -2207,31 +2207,31 @@
     <t xml:space="preserve">0.348497986793518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342864096164703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345278590917587</t>
+    <t xml:space="preserve">0.342864066362381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345278561115265</t>
   </si>
   <si>
     <t xml:space="preserve">0.336425334215164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324352622032166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329986542463303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326767146587372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321938097476959</t>
+    <t xml:space="preserve">0.324352651834488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329986572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326767176389694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321938127279282</t>
   </si>
   <si>
     <t xml:space="preserve">0.331596255302429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340449541807175</t>
+    <t xml:space="preserve">0.340449512004852</t>
   </si>
   <si>
     <t xml:space="preserve">0.347693145275116</t>
@@ -2243,85 +2243,85 @@
     <t xml:space="preserve">0.354936748743057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36942395567894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382301479578018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379886984825134</t>
+    <t xml:space="preserve">0.369423985481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382301509380341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379886955022812</t>
   </si>
   <si>
     <t xml:space="preserve">0.371838539838791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354131907224655</t>
+    <t xml:space="preserve">0.354131937026978</t>
   </si>
   <si>
     <t xml:space="preserve">0.330791413784027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356546401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357351332902908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350107699632645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346888303756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342059224843979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337230145931244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328376889228821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335620492696762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370228797197342</t>
+    <t xml:space="preserve">0.356546461582184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357351303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350107669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346888333559036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342059284448624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337230175733566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328376859426498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33562046289444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370228826999664</t>
   </si>
   <si>
     <t xml:space="preserve">0.358156144618988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363790035247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420129269361496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424958318471909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437835842370987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444274574518204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445884317159653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482907235622406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560172319412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527978539466858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521539688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529588162899017</t>
+    <t xml:space="preserve">0.363790065050125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420129209756851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424958288669586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437835812568665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444274604320526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445884257555008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482907176017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560172200202942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527978479862213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521539747714996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529588222503662</t>
   </si>
   <si>
     <t xml:space="preserve">0.519930064678192</t>
@@ -2330,31 +2330,31 @@
     <t xml:space="preserve">0.507052481174469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500613689422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494175046682358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502223491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537636637687683</t>
+    <t xml:space="preserve">0.500613749027252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494175016880035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502223432064056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537636578083038</t>
   </si>
   <si>
     <t xml:space="preserve">0.52475917339325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510271966457367</t>
+    <t xml:space="preserve">0.510271906852722</t>
   </si>
   <si>
     <t xml:space="preserve">0.499004065990448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492565304040909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487736254930496</t>
+    <t xml:space="preserve">0.492565274238586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487736225128174</t>
   </si>
   <si>
     <t xml:space="preserve">0.484516859054565</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">0.447493970394135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431397080421448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449103713035583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436226099729538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393569320440292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378277242183685</t>
+    <t xml:space="preserve">0.431397050619125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449103683233261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436226159334183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393569350242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37827730178833</t>
   </si>
   <si>
     <t xml:space="preserve">0.375862747430801</t>
@@ -2402,16 +2402,16 @@
     <t xml:space="preserve">0.50544285774231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468419969081879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461981207132339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465200543403625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452323019504547</t>
+    <t xml:space="preserve">0.468419939279556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461981236934662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465200573205948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45232304930687</t>
   </si>
   <si>
     <t xml:space="preserve">0.455542385578156</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">0.460371524095535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457152158021927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453932762145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479687839746475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495784670114517</t>
+    <t xml:space="preserve">0.457152128219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453932732343674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479687809944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495784729719162</t>
   </si>
   <si>
     <t xml:space="preserve">0.489345908164978</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">0.547294795513153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565001428127289</t>
+    <t xml:space="preserve">0.565001368522644</t>
   </si>
   <si>
     <t xml:space="preserve">0.576269268989563</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">0.575464367866516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569830536842346</t>
+    <t xml:space="preserve">0.569830417633057</t>
   </si>
   <si>
     <t xml:space="preserve">0.549709379673004</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">0.56741589307785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545685112476349</t>
+    <t xml:space="preserve">0.545685052871704</t>
   </si>
   <si>
     <t xml:space="preserve">0.558562636375427</t>
@@ -2471,37 +2471,37 @@
     <t xml:space="preserve">0.531197905540466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559367418289185</t>
+    <t xml:space="preserve">0.559367477893829</t>
   </si>
   <si>
     <t xml:space="preserve">0.573854625225067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581903159618378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.579488635063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544880211353302</t>
+    <t xml:space="preserve">0.581903100013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579488575458527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544880270957947</t>
   </si>
   <si>
     <t xml:space="preserve">0.552123844623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5480996966362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548904478549957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553733646869659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582058250904083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581226825714111</t>
+    <t xml:space="preserve">0.548099637031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548904538154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553733587265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582058310508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581226766109467</t>
   </si>
   <si>
     <t xml:space="preserve">0.573743164539337</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">0.567091107368469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574574649333954</t>
+    <t xml:space="preserve">0.574574589729309</t>
   </si>
   <si>
     <t xml:space="preserve">0.57291167974472</t>
@@ -2519,28 +2519,28 @@
     <t xml:space="preserve">0.561270534992218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557944416999817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558775961399078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540482699871063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544640243053436</t>
+    <t xml:space="preserve">0.557944476604462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558776021003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540482640266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544640183448792</t>
   </si>
   <si>
     <t xml:space="preserve">0.542977273464203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530504584312439</t>
+    <t xml:space="preserve">0.530504524707794</t>
   </si>
   <si>
     <t xml:space="preserve">0.531336069107056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532167613506317</t>
+    <t xml:space="preserve">0.532167553901672</t>
   </si>
   <si>
     <t xml:space="preserve">0.516368865966797</t>
@@ -2549,34 +2549,34 @@
     <t xml:space="preserve">0.511379778385162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505559206008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508885264396667</t>
+    <t xml:space="preserve">0.505559146404266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508885204792023</t>
   </si>
   <si>
     <t xml:space="preserve">0.502233147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51553738117218</t>
+    <t xml:space="preserve">0.515537321567535</t>
   </si>
   <si>
     <t xml:space="preserve">0.498907119035721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493918001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494749575853348</t>
+    <t xml:space="preserve">0.493918031454086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494749546051025</t>
   </si>
   <si>
     <t xml:space="preserve">0.500570118427277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48393988609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465646594762802</t>
+    <t xml:space="preserve">0.483939915895462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465646624565125</t>
   </si>
   <si>
     <t xml:space="preserve">0.466478109359741</t>
@@ -2585,19 +2585,19 @@
     <t xml:space="preserve">0.461489081382751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460657566785812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473961770534515</t>
+    <t xml:space="preserve">0.46065753698349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473961740732193</t>
   </si>
   <si>
     <t xml:space="preserve">0.473130285739899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486434429883957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489760518074036</t>
+    <t xml:space="preserve">0.486434459686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489760458469391</t>
   </si>
   <si>
     <t xml:space="preserve">0.503064692020416</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">0.50472766160965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506390750408173</t>
+    <t xml:space="preserve">0.506390690803528</t>
   </si>
   <si>
     <t xml:space="preserve">0.510548293590546</t>
@@ -2618,25 +2618,25 @@
     <t xml:space="preserve">0.495581090450287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484771460294724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482276886701584</t>
+    <t xml:space="preserve">0.484771370887756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482276827096939</t>
   </si>
   <si>
     <t xml:space="preserve">0.491423547267914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497244089841843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487265974283218</t>
+    <t xml:space="preserve">0.497244030237198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487265914678574</t>
   </si>
   <si>
     <t xml:space="preserve">0.493086487054825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483108341693878</t>
+    <t xml:space="preserve">0.483108311891556</t>
   </si>
   <si>
     <t xml:space="preserve">0.478119283914566</t>
@@ -2645,13 +2645,13 @@
     <t xml:space="preserve">0.475624799728394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47645628452301</t>
+    <t xml:space="preserve">0.476456254720688</t>
   </si>
   <si>
     <t xml:space="preserve">0.529673039913177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523852467536926</t>
+    <t xml:space="preserve">0.523852407932281</t>
   </si>
   <si>
     <t xml:space="preserve">0.528010010719299</t>
@@ -2669,28 +2669,28 @@
     <t xml:space="preserve">0.528841495513916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525515496730804</t>
+    <t xml:space="preserve">0.52551543712616</t>
   </si>
   <si>
     <t xml:space="preserve">0.526347041130066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55461847782135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588710427284241</t>
+    <t xml:space="preserve">0.554618299007416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588710367679596</t>
   </si>
   <si>
     <t xml:space="preserve">0.575406193733215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577069282531738</t>
+    <t xml:space="preserve">0.577069222927094</t>
   </si>
   <si>
     <t xml:space="preserve">0.570417106151581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583721399307251</t>
+    <t xml:space="preserve">0.583721339702606</t>
   </si>
   <si>
     <t xml:space="preserve">0.585384368896484</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">0.58039528131485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550460875034332</t>
+    <t xml:space="preserve">0.550460755825043</t>
   </si>
   <si>
     <t xml:space="preserve">0.556281447410583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545471787452698</t>
+    <t xml:space="preserve">0.545471727848053</t>
   </si>
   <si>
     <t xml:space="preserve">0.567922651767731</t>
@@ -2720,10 +2720,10 @@
     <t xml:space="preserve">0.557112991809845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56459653377533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549629330635071</t>
+    <t xml:space="preserve">0.564596474170685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549629271030426</t>
   </si>
   <si>
     <t xml:space="preserve">0.539651155471802</t>
@@ -2735,19 +2735,19 @@
     <t xml:space="preserve">0.532999098300934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524684011936188</t>
+    <t xml:space="preserve">0.524683952331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.509716749191284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507222175598145</t>
+    <t xml:space="preserve">0.507222235202789</t>
   </si>
   <si>
     <t xml:space="preserve">0.521357893943787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513874351978302</t>
+    <t xml:space="preserve">0.513874292373657</t>
   </si>
   <si>
     <t xml:space="preserve">0.522189497947693</t>
@@ -2759,43 +2759,43 @@
     <t xml:space="preserve">0.52052640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523020923137665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519694983959198</t>
+    <t xml:space="preserve">0.52302098274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519694864749908</t>
   </si>
   <si>
     <t xml:space="preserve">0.508053779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488097429275513</t>
+    <t xml:space="preserve">0.488097459077835</t>
   </si>
   <si>
     <t xml:space="preserve">0.488928943872452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492255032062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496412575244904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49059197306633</t>
+    <t xml:space="preserve">0.492255002260208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496412634849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490591943264008</t>
   </si>
   <si>
     <t xml:space="preserve">0.485602915287018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480613857507706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474793255329132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4540054500103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478950828313828</t>
+    <t xml:space="preserve">0.480613827705383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474793195724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454005479812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478950768709183</t>
   </si>
   <si>
     <t xml:space="preserve">0.458163022994995</t>
@@ -2804,22 +2804,22 @@
     <t xml:space="preserve">0.44901642203331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43986976146698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439038217067719</t>
+    <t xml:space="preserve">0.439869731664658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439038246870041</t>
   </si>
   <si>
     <t xml:space="preserve">0.419913470745087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422408044338226</t>
+    <t xml:space="preserve">0.422408014535904</t>
   </si>
   <si>
     <t xml:space="preserve">0.42407101392746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411598384380341</t>
+    <t xml:space="preserve">0.411598354578018</t>
   </si>
   <si>
     <t xml:space="preserve">0.41118261218071</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">0.39579963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377090603113174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365033686161041</t>
+    <t xml:space="preserve">0.377090632915497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365033715963364</t>
   </si>
   <si>
     <t xml:space="preserve">0.402035981416702</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">0.413677155971527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407440841197968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412429839372635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431554645299911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429891616106033</t>
+    <t xml:space="preserve">0.407440811395645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412429869174957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431554615497589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429891645908356</t>
   </si>
   <si>
     <t xml:space="preserve">0.432386130094528</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">0.436543703079224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443195819854736</t>
+    <t xml:space="preserve">0.443195790052414</t>
   </si>
   <si>
     <t xml:space="preserve">0.448184847831726</t>
@@ -2876,40 +2876,40 @@
     <t xml:space="preserve">0.440701246261597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434880673885345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424902558326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444858849048615</t>
+    <t xml:space="preserve">0.434880703687668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424902528524399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444858878850937</t>
   </si>
   <si>
     <t xml:space="preserve">0.447353363037109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445690363645554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463152080774307</t>
+    <t xml:space="preserve">0.445690333843231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46315211057663</t>
   </si>
   <si>
     <t xml:space="preserve">0.481445372104645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477287799119949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470635682344437</t>
+    <t xml:space="preserve">0.477287828922272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470635652542114</t>
   </si>
   <si>
     <t xml:space="preserve">0.437375247478485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429060101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421576499938965</t>
+    <t xml:space="preserve">0.429060071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421576529741287</t>
   </si>
   <si>
     <t xml:space="preserve">0.40993532538414</t>
@@ -3801,6 +3801,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.47299998998642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465999990701675</t>
   </si>
 </sst>
 </file>
@@ -68983,7 +68986,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6495949074</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>1632239</v>
@@ -69004,6 +69007,32 @@
         <v>1262</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6493402778</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>278394</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>0.465999990701675</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>0.470999985933304</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>0.465999990701675</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="1265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="1264">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32635235786438</t>
+    <t xml:space="preserve">0.326352328062057</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844841241837</t>
+    <t xml:space="preserve">0.326844811439514</t>
   </si>
   <si>
     <t xml:space="preserve">0.323679089546204</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">0.317980736494064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313056230545044</t>
+    <t xml:space="preserve">0.313056260347366</t>
   </si>
   <si>
     <t xml:space="preserve">0.304966032505035</t>
@@ -65,127 +65,127 @@
     <t xml:space="preserve">0.309538751840591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302503824234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287097245454788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274363905191422</t>
+    <t xml:space="preserve">0.302503854036331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287097215652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274363875389099</t>
   </si>
   <si>
     <t xml:space="preserve">0.278655230998993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265288770198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260645747184753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270846396684647</t>
+    <t xml:space="preserve">0.265288829803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260645717382431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270846426486969</t>
   </si>
   <si>
     <t xml:space="preserve">0.269087672233582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272956967353821</t>
+    <t xml:space="preserve">0.272956937551498</t>
   </si>
   <si>
     <t xml:space="preserve">0.270142942667007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265921950340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290825754404068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288433879613876</t>
+    <t xml:space="preserve">0.265921920537949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290825694799423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288433849811554</t>
   </si>
   <si>
     <t xml:space="preserve">0.294061839580536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276404052972794</t>
+    <t xml:space="preserve">0.276404023170471</t>
   </si>
   <si>
     <t xml:space="preserve">0.273167967796326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262545138597488</t>
+    <t xml:space="preserve">0.262545198202133</t>
   </si>
   <si>
     <t xml:space="preserve">0.260293960571289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246927559375763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24622406065464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239751800894737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240103632211685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271549940109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276122629642487</t>
+    <t xml:space="preserve">0.246927529573441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246224045753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239751875400543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240103602409363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271549910306931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276122689247131</t>
   </si>
   <si>
     <t xml:space="preserve">0.274645298719406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277881443500519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270987153053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281539618968964</t>
+    <t xml:space="preserve">0.277881383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270987123250961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281539589166641</t>
   </si>
   <si>
     <t xml:space="preserve">0.277177900075912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263318985700607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2680324614048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282102406024933</t>
+    <t xml:space="preserve">0.26331901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268032401800156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28210237622261</t>
   </si>
   <si>
     <t xml:space="preserve">0.295468837022781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293358355760574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291740298271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288644880056381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504242897034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281469255685806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27724826335907</t>
+    <t xml:space="preserve">0.293358325958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291740268468857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288644909858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504213094711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281469196081161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277248293161392</t>
   </si>
   <si>
     <t xml:space="preserve">0.278373867273331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287026882171631</t>
+    <t xml:space="preserve">0.287026852369308</t>
   </si>
   <si>
     <t xml:space="preserve">0.297368258237839</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">0.295820593833923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307217210531235</t>
+    <t xml:space="preserve">0.307217240333557</t>
   </si>
   <si>
     <t xml:space="preserve">0.305669575929642</t>
@@ -203,25 +203,25 @@
     <t xml:space="preserve">0.313759744167328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320443004369736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317417949438095</t>
+    <t xml:space="preserve">0.320442974567413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317417919635773</t>
   </si>
   <si>
     <t xml:space="preserve">0.316573768854141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306161969900131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310945808887482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311438202857971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301800280809402</t>
+    <t xml:space="preserve">0.306161999702454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310945779085159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311438232660294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301800310611725</t>
   </si>
   <si>
     <t xml:space="preserve">0.288011729717255</t>
@@ -230,25 +230,25 @@
     <t xml:space="preserve">0.288082093000412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280554682016373</t>
+    <t xml:space="preserve">0.280554711818695</t>
   </si>
   <si>
     <t xml:space="preserve">0.281328529119492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291880965232849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30137825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311649292707443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310242265462875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311508566141129</t>
+    <t xml:space="preserve">0.291880995035172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301378220319748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311649262905121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310242295265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311508536338806</t>
   </si>
   <si>
     <t xml:space="preserve">0.314533650875092</t>
@@ -260,34 +260,34 @@
     <t xml:space="preserve">0.318684250116348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330573350191116</t>
+    <t xml:space="preserve">0.330573379993439</t>
   </si>
   <si>
     <t xml:space="preserve">0.330643713474274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334161192178726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333528071641922</t>
+    <t xml:space="preserve">0.334161162376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3335280418396</t>
   </si>
   <si>
     <t xml:space="preserve">0.330432653427124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327126234769821</t>
+    <t xml:space="preserve">0.327126175165176</t>
   </si>
   <si>
     <t xml:space="preserve">0.323538392782211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318543553352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319247037172318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323116302490234</t>
+    <t xml:space="preserve">0.318543523550034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319247007369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323116272687912</t>
   </si>
   <si>
     <t xml:space="preserve">0.321005791425705</t>
@@ -296,58 +296,58 @@
     <t xml:space="preserve">0.324874997138977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323749452829361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325015753507614</t>
+    <t xml:space="preserve">0.323749393224716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325015783309937</t>
   </si>
   <si>
     <t xml:space="preserve">0.32107612490654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326774477958679</t>
+    <t xml:space="preserve">0.326774448156357</t>
   </si>
   <si>
     <t xml:space="preserve">0.331769287586212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344713658094406</t>
+    <t xml:space="preserve">0.344713628292084</t>
   </si>
   <si>
     <t xml:space="preserve">0.342040359973907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338030427694321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352100342512131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354914307594299</t>
+    <t xml:space="preserve">0.338030457496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352100372314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354914337396622</t>
   </si>
   <si>
     <t xml:space="preserve">0.351678252220154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350341558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343306630849838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343165963888168</t>
+    <t xml:space="preserve">0.350341588258743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343306690454483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343165934085846</t>
   </si>
   <si>
     <t xml:space="preserve">0.341196149587631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34021121263504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337045550346375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323537737131119</t>
+    <t xml:space="preserve">0.340211242437363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337045520544052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323537796735764</t>
   </si>
   <si>
     <t xml:space="preserve">0.309325873851776</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">0.312153726816177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308890849351883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311936259269714</t>
+    <t xml:space="preserve">0.308890819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311936289072037</t>
   </si>
   <si>
     <t xml:space="preserve">0.325278013944626</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">0.322232574224472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318607091903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324190378189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307223081588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299102008342743</t>
+    <t xml:space="preserve">0.318607121706009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324190348386765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307223111391068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299102038145065</t>
   </si>
   <si>
     <t xml:space="preserve">0.299464553594589</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">0.313096404075623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320854902267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318027049303055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319042176008224</t>
+    <t xml:space="preserve">0.320854932069778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318027019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319042146205902</t>
   </si>
   <si>
     <t xml:space="preserve">0.318317085504532</t>
@@ -404,22 +404,22 @@
     <t xml:space="preserve">0.311791211366653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310558557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311066061258316</t>
+    <t xml:space="preserve">0.310558527708054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311066120862961</t>
   </si>
   <si>
     <t xml:space="preserve">0.322087585926056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319767266511917</t>
+    <t xml:space="preserve">0.31976729631424</t>
   </si>
   <si>
     <t xml:space="preserve">0.318172067403793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309978455305099</t>
+    <t xml:space="preserve">0.309978485107422</t>
   </si>
   <si>
     <t xml:space="preserve">0.306715548038483</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">0.305627882480621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301784932613373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300914734601974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298739463090897</t>
+    <t xml:space="preserve">0.301784873008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300914794206619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298739492893219</t>
   </si>
   <si>
     <t xml:space="preserve">0.298014402389526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29148855805397</t>
+    <t xml:space="preserve">0.291488528251648</t>
   </si>
   <si>
     <t xml:space="preserve">0.294316411018372</t>
@@ -452,37 +452,37 @@
     <t xml:space="preserve">0.301204800605774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302727520465851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30381515622139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300624758005142</t>
+    <t xml:space="preserve">0.302727490663528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303815126419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30062472820282</t>
   </si>
   <si>
     <t xml:space="preserve">0.297434329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299682110548019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301929861307144</t>
+    <t xml:space="preserve">0.299682140350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301929891109467</t>
   </si>
   <si>
     <t xml:space="preserve">0.301712363958359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302364975214005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300117164850235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302219927310944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29714423418045</t>
+    <t xml:space="preserve">0.302364945411682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300117194652557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302219897508621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297144263982773</t>
   </si>
   <si>
     <t xml:space="preserve">0.295621573925018</t>
@@ -491,19 +491,19 @@
     <t xml:space="preserve">0.293663799762726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297289282083511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291706085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292358636856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290038377046585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287500530481339</t>
+    <t xml:space="preserve">0.297289252281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291706025600433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292358666658401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290038347244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287500500679016</t>
   </si>
   <si>
     <t xml:space="preserve">0.292648673057556</t>
@@ -512,34 +512,34 @@
     <t xml:space="preserve">0.287645488977432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295041501522064</t>
+    <t xml:space="preserve">0.295041471719742</t>
   </si>
   <si>
     <t xml:space="preserve">0.291561037302017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294533908367157</t>
+    <t xml:space="preserve">0.294533938169479</t>
   </si>
   <si>
     <t xml:space="preserve">0.289313226938248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287935525178909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283004909753799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287428021430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282859861850739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275826454162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279161870479584</t>
+    <t xml:space="preserve">0.287935584783554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283004879951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287427991628647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282859891653061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27582648396492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279161900281906</t>
   </si>
   <si>
     <t xml:space="preserve">0.269735664129257</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">0.273288577795029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279524445533752</t>
+    <t xml:space="preserve">0.279524475336075</t>
   </si>
   <si>
     <t xml:space="preserve">0.282062262296677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283802509307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282134741544724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287137925624847</t>
+    <t xml:space="preserve">0.283802479505539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282134830951691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28713795542717</t>
   </si>
   <si>
     <t xml:space="preserve">0.292866170406342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301422357559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295839071273804</t>
+    <t xml:space="preserve">0.301422327756882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295839130878448</t>
   </si>
   <si>
     <t xml:space="preserve">0.296564191579819</t>
@@ -578,37 +578,37 @@
     <t xml:space="preserve">0.300262182950974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297071784734726</t>
+    <t xml:space="preserve">0.297071754932404</t>
   </si>
   <si>
     <t xml:space="preserve">0.292938739061356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298811972141266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296056598424911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310195982456207</t>
+    <t xml:space="preserve">0.298811942338943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296056628227234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31019601225853</t>
   </si>
   <si>
     <t xml:space="preserve">0.306425511837006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302509963512421</t>
+    <t xml:space="preserve">0.302510023117065</t>
   </si>
   <si>
     <t xml:space="preserve">0.306062966585159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307078063488007</t>
+    <t xml:space="preserve">0.307078093290329</t>
   </si>
   <si>
     <t xml:space="preserve">0.301639884710312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294098854064941</t>
+    <t xml:space="preserve">0.294098913669586</t>
   </si>
   <si>
     <t xml:space="preserve">0.283077418804169</t>
@@ -617,43 +617,43 @@
     <t xml:space="preserve">0.287863045930862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289603263139725</t>
+    <t xml:space="preserve">0.289603292942047</t>
   </si>
   <si>
     <t xml:space="preserve">0.285615265369415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2839475274086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288805693387985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293736279010773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290835946798325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28351241350174</t>
+    <t xml:space="preserve">0.283947557210922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288805663585663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293736338615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290835976600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283512473106384</t>
   </si>
   <si>
     <t xml:space="preserve">0.281409710645676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280684620141983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279016882181168</t>
+    <t xml:space="preserve">0.280684590339661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27901691198349</t>
   </si>
   <si>
     <t xml:space="preserve">0.273796200752258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291416019201279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295113980770111</t>
+    <t xml:space="preserve">0.291416049003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295114010572433</t>
   </si>
   <si>
     <t xml:space="preserve">0.290545880794525</t>
@@ -662,22 +662,22 @@
     <t xml:space="preserve">0.288588136434555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292213618755341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292141079902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294388920068741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299392074346542</t>
+    <t xml:space="preserve">0.292213588953018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292141109704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294388860464096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29939204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.296491682529449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303597629070282</t>
+    <t xml:space="preserve">0.303597658872604</t>
   </si>
   <si>
     <t xml:space="preserve">0.309615910053253</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">0.307440638542175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319187194108963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331513792276382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331368803977966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345000594854355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349786221981049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358342349529266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354209303855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349641233682632</t>
+    <t xml:space="preserve">0.319187164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331513822078705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331368774175644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345000624656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349786251783371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358342319726944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354209333658218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34964120388031</t>
   </si>
   <si>
     <t xml:space="preserve">0.352396577596664</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">0.355296939611435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359430015087128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352686643600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346885859966278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343187838792801</t>
+    <t xml:space="preserve">0.359429985284805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352686613798141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346885830163956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343187898397446</t>
   </si>
   <si>
     <t xml:space="preserve">0.346160769462585</t>
@@ -740,37 +740,37 @@
     <t xml:space="preserve">0.344348013401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350221276283264</t>
+    <t xml:space="preserve">0.350221306085587</t>
   </si>
   <si>
     <t xml:space="preserve">0.350946366786957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388288795948029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397715061903</t>
+    <t xml:space="preserve">0.388288825750351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397715091705322</t>
   </si>
   <si>
     <t xml:space="preserve">0.379950225353241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382125496864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374874591827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373424351215363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377412408590317</t>
+    <t xml:space="preserve">0.382125556468964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37487456202507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37342432141304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377412378787994</t>
   </si>
   <si>
     <t xml:space="preserve">0.373061835765839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369798839092255</t>
+    <t xml:space="preserve">0.369798898696899</t>
   </si>
   <si>
     <t xml:space="preserve">0.383575677871704</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">0.369073778390884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35819736123085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358052313327789</t>
+    <t xml:space="preserve">0.358197391033173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358052343130112</t>
   </si>
   <si>
     <t xml:space="preserve">0.377049803733826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412579566240311</t>
+    <t xml:space="preserve">0.412579506635666</t>
   </si>
   <si>
     <t xml:space="preserve">0.382488042116165</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">0.394452124834061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385750979185104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39372706413269</t>
+    <t xml:space="preserve">0.385750949382782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393727034330368</t>
   </si>
   <si>
     <t xml:space="preserve">0.390464097261429</t>
@@ -818,133 +818,133 @@
     <t xml:space="preserve">0.391551792621613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387563765048981</t>
+    <t xml:space="preserve">0.387563735246658</t>
   </si>
   <si>
     <t xml:space="preserve">0.390826612710953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395177245140076</t>
+    <t xml:space="preserve">0.395177215337753</t>
   </si>
   <si>
     <t xml:space="preserve">0.393364518880844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397352516651154</t>
+    <t xml:space="preserve">0.397352486848831</t>
   </si>
   <si>
     <t xml:space="preserve">0.398802697658539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395539790391922</t>
+    <t xml:space="preserve">0.3955397605896</t>
   </si>
   <si>
     <t xml:space="preserve">0.396627426147461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39844012260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395902305841446</t>
+    <t xml:space="preserve">0.398440152406693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395902335643768</t>
   </si>
   <si>
     <t xml:space="preserve">0.393001943826675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398077607154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401703089475632</t>
+    <t xml:space="preserve">0.398077666759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401703149080276</t>
   </si>
   <si>
     <t xml:space="preserve">0.392276853322983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38720116019249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386476069688797</t>
+    <t xml:space="preserve">0.387201189994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386476099491119</t>
   </si>
   <si>
     <t xml:space="preserve">0.382850587368011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394089579582214</t>
+    <t xml:space="preserve">0.394089549779892</t>
   </si>
   <si>
     <t xml:space="preserve">0.389376491308212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381762951612473</t>
+    <t xml:space="preserve">0.381762981414795</t>
   </si>
   <si>
     <t xml:space="preserve">0.381037890911102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386838614940643</t>
+    <t xml:space="preserve">0.386838674545288</t>
   </si>
   <si>
     <t xml:space="preserve">0.388651371002197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385025918483734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391189217567444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392639368772507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425631254911423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419105440378189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445208847522736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435057520866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442308455705643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432611912488937</t>
+    <t xml:space="preserve">0.385025858879089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391189187765121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392639398574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425631284713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419105410575867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445208877325058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435057550668716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44230842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43261194229126</t>
   </si>
   <si>
     <t xml:space="preserve">0.413591980934143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408370792865753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406879037618637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402776718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399047285318375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400539070367813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395317822694778</t>
+    <t xml:space="preserve">0.408370763063431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406879007816315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402776688337326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399047255516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400539040565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395317792892456</t>
   </si>
   <si>
     <t xml:space="preserve">0.396809637546539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396063774824142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393080174922943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388604909181595</t>
+    <t xml:space="preserve">0.396063715219498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393080204725266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388604938983917</t>
   </si>
   <si>
     <t xml:space="preserve">0.387858986854553</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">0.379654318094254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381146103143692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383010774850845</t>
+    <t xml:space="preserve">0.38114607334137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383010745048523</t>
   </si>
   <si>
     <t xml:space="preserve">0.387486070394516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384875476360321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383756726980209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386740207672119</t>
+    <t xml:space="preserve">0.384875506162643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383756697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386740177869797</t>
   </si>
   <si>
     <t xml:space="preserve">0.390096664428711</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">0.403522580862045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410235494375229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407251983880997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407624930143356</t>
+    <t xml:space="preserve">0.410235524177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407251954078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407624959945679</t>
   </si>
   <si>
     <t xml:space="preserve">0.40874370932579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406506091356277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40091198682785</t>
+    <t xml:space="preserve">0.4065061211586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400911957025528</t>
   </si>
   <si>
     <t xml:space="preserve">0.394199073314667</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">0.39084255695343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392334342002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388231962919235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387113124132156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391588419675827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389350742101669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385621398687363</t>
+    <t xml:space="preserve">0.392334371805191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388231992721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387113153934479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391588449478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389350771903992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38562136888504</t>
   </si>
   <si>
     <t xml:space="preserve">0.380773186683655</t>
@@ -1031,37 +1031,37 @@
     <t xml:space="preserve">0.385248422622681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383383691310883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397928476333618</t>
+    <t xml:space="preserve">0.383383721113205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397928446531296</t>
   </si>
   <si>
     <t xml:space="preserve">0.409489631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410981416702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414337813854218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415083736181259</t>
+    <t xml:space="preserve">0.410981357097626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41433784365654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415083765983582</t>
   </si>
   <si>
     <t xml:space="preserve">0.416575491428375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415829598903656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424034297466278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439324945211411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866139173508</t>
+    <t xml:space="preserve">0.415829658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424034357070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439324885606766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866109371185</t>
   </si>
   <si>
     <t xml:space="preserve">0.428882509469986</t>
@@ -1070,88 +1070,88 @@
     <t xml:space="preserve">0.420304894447327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421796679496765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428509652614594</t>
+    <t xml:space="preserve">0.42179673910141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428509622812271</t>
   </si>
   <si>
     <t xml:space="preserve">0.45498850941658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445291996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444546192884445</t>
+    <t xml:space="preserve">0.44529202580452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444546103477478</t>
   </si>
   <si>
     <t xml:space="preserve">0.440443724393845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449767291545868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459463715553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460955500602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469533145427704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466549664735794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474008530378342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474754363298416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348438024521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485942602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482586145401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485569685697556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50943797826767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511302590370178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521745026111603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512794375419617</t>
+    <t xml:space="preserve">0.449767231941223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459463745355606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460955530405045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469533234834671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466549634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474008470773697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474754333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48034855723381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485942512750626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482586055994034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4855697453022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509437918663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511302649974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521744966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512794435024261</t>
   </si>
   <si>
     <t xml:space="preserve">0.5195072889328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511675536632538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506081461906433</t>
+    <t xml:space="preserve">0.511675596237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506081402301788</t>
   </si>
   <si>
     <t xml:space="preserve">0.501233279705048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502351999282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495266109704971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491536736488342</t>
+    <t xml:space="preserve">0.502352058887482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495266079902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491536766290665</t>
   </si>
   <si>
     <t xml:space="preserve">0.477737903594971</t>
@@ -1160,31 +1160,31 @@
     <t xml:space="preserve">0.478483766317368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48109433054924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492282629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499741405248642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493774324655533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495639085769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507946074008942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500114321708679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493028432130814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508691966533661</t>
+    <t xml:space="preserve">0.48109444975853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492282599210739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499741435050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493774354457855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495639055967331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507946133613586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500114381313324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493028461933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508692026138306</t>
   </si>
   <si>
     <t xml:space="preserve">0.503470838069916</t>
@@ -1199,25 +1199,25 @@
     <t xml:space="preserve">0.510183811187744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513167440891266</t>
+    <t xml:space="preserve">0.513167321681976</t>
   </si>
   <si>
     <t xml:space="preserve">0.500860333442688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503097951412201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502724945545197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501606166362762</t>
+    <t xml:space="preserve">0.503097891807556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502724885940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501606106758118</t>
   </si>
   <si>
     <t xml:space="preserve">0.498249650001526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510929644107819</t>
+    <t xml:space="preserve">0.510929703712463</t>
   </si>
   <si>
     <t xml:space="preserve">0.531068563461304</t>
@@ -1241,16 +1241,16 @@
     <t xml:space="preserve">0.574329674243927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576567411422729</t>
+    <t xml:space="preserve">0.576567351818085</t>
   </si>
   <si>
     <t xml:space="preserve">0.577313244342804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583280205726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59148508310318</t>
+    <t xml:space="preserve">0.583280324935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59148496389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.585517942905426</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">0.61236971616745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556428551673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551953196525574</t>
+    <t xml:space="preserve">0.556428492069244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551953256130219</t>
   </si>
   <si>
     <t xml:space="preserve">0.548223793506622</t>
@@ -1277,82 +1277,82 @@
     <t xml:space="preserve">0.521372020244598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505708456039429</t>
+    <t xml:space="preserve">0.505708396434784</t>
   </si>
   <si>
     <t xml:space="preserve">0.528084933757782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545240342617035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522863686084747</t>
+    <t xml:space="preserve">0.54524028301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522863745689392</t>
   </si>
   <si>
     <t xml:space="preserve">0.517642557621002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532560288906097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531814396381378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523609757423401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516150832176208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512421488761902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519134342670441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498995572328568</t>
+    <t xml:space="preserve">0.532560348510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531814455986023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523609697818756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516150772571564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512421429157257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519134402275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49899560213089</t>
   </si>
   <si>
     <t xml:space="preserve">0.463193148374557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469906061887741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476619064807892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477364927530289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494520217180252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490044951438904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478856712579727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47811084985733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468414396047592</t>
+    <t xml:space="preserve">0.469906091690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476619035005569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477364987134933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494520246982574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490044891834259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47885674238205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478110760450363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468414425849915</t>
   </si>
   <si>
     <t xml:space="preserve">0.481840282678604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48407781124115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475127309560776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473635494709015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474381446838379</t>
+    <t xml:space="preserve">0.484077870845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475127339363098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473635613918304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474381387233734</t>
   </si>
   <si>
     <t xml:space="preserve">0.484823763370514</t>
@@ -1361,46 +1361,46 @@
     <t xml:space="preserve">0.487061470746994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48333203792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50421667098999</t>
+    <t xml:space="preserve">0.483331978321075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504216730594635</t>
   </si>
   <si>
     <t xml:space="preserve">0.504962623119354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496757864952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497503817081451</t>
+    <t xml:space="preserve">0.49675789475441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497503787279129</t>
   </si>
   <si>
     <t xml:space="preserve">0.48631551861763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500487327575684</t>
+    <t xml:space="preserve">0.500487387180328</t>
   </si>
   <si>
     <t xml:space="preserve">0.454242616891861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465430825948715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452004939317703</t>
+    <t xml:space="preserve">0.465430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452004879713058</t>
   </si>
   <si>
     <t xml:space="preserve">0.457226127386093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458717882633209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462447255849838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455734372138977</t>
+    <t xml:space="preserve">0.458717912435532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462447226047516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455734342336655</t>
   </si>
   <si>
     <t xml:space="preserve">0.457972019910812</t>
@@ -1412,37 +1412,37 @@
     <t xml:space="preserve">0.484185874462128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474933952093124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469536930322647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464910984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461055994033813</t>
+    <t xml:space="preserve">0.474933922290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469536989927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464910954236984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461055964231491</t>
   </si>
   <si>
     <t xml:space="preserve">0.463369011878967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459513992071152</t>
+    <t xml:space="preserve">0.459514021873474</t>
   </si>
   <si>
     <t xml:space="preserve">0.457971960306168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458743005990982</t>
+    <t xml:space="preserve">0.458743065595627</t>
   </si>
   <si>
     <t xml:space="preserve">0.44794899225235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451033025979996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454887956380844</t>
+    <t xml:space="preserve">0.451032996177673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454887896776199</t>
   </si>
   <si>
     <t xml:space="preserve">0.446407049894333</t>
@@ -1451,49 +1451,49 @@
     <t xml:space="preserve">0.441781044006348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443323075771332</t>
+    <t xml:space="preserve">0.443323016166687</t>
   </si>
   <si>
     <t xml:space="preserve">0.494208812713623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474162966012955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481101900339127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489582777023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476475924253464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464139997959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461827009916306</t>
+    <t xml:space="preserve">0.474162936210632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481101870536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48958283662796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476475894451141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464139968156815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461826950311661</t>
   </si>
   <si>
     <t xml:space="preserve">0.456430017948151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454117000102997</t>
+    <t xml:space="preserve">0.454116970300674</t>
   </si>
   <si>
     <t xml:space="preserve">0.466452986001968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46722400188446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439468085765839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442552119493484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452575027942657</t>
+    <t xml:space="preserve">0.467223942279816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439468115568161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442552030086517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45257505774498</t>
   </si>
   <si>
     <t xml:space="preserve">0.453345984220505</t>
@@ -1505,70 +1505,70 @@
     <t xml:space="preserve">0.437926113605499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433300137519836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430987119674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43175807595253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435613095760345</t>
+    <t xml:space="preserve">0.433300077915192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43098708987236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431758105754852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435613125562668</t>
   </si>
   <si>
     <t xml:space="preserve">0.444865047931671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460285037755966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451804012060165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470307976007462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471849918365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465681970119476</t>
+    <t xml:space="preserve">0.460285007953644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451804041862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470308005809784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471849948167801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465681940317154</t>
   </si>
   <si>
     <t xml:space="preserve">0.457200944423676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462597995996475</t>
+    <t xml:space="preserve">0.46259805560112</t>
   </si>
   <si>
     <t xml:space="preserve">0.455659002065659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450262010097504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449490994215012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437155067920685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440239042043686</t>
+    <t xml:space="preserve">0.450262039899826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449491053819656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437155097723007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440239101648331</t>
   </si>
   <si>
     <t xml:space="preserve">0.426361113786697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427903085947037</t>
+    <t xml:space="preserve">0.427903175354004</t>
   </si>
   <si>
     <t xml:space="preserve">0.407086223363876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406315177679062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4101702272892</t>
+    <t xml:space="preserve">0.406315267086029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410170197486877</t>
   </si>
   <si>
     <t xml:space="preserve">0.404002219438553</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">0.410941183567047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400147259235382</t>
+    <t xml:space="preserve">0.40014722943306</t>
   </si>
   <si>
     <t xml:space="preserve">0.396292239427567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390895336866379</t>
+    <t xml:space="preserve">0.390895307064056</t>
   </si>
   <si>
     <t xml:space="preserve">0.390124261379242</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">0.381643325090408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383185356855392</t>
+    <t xml:space="preserve">0.38318532705307</t>
   </si>
   <si>
     <t xml:space="preserve">0.387811332941055</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">0.388582289218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394750267267227</t>
+    <t xml:space="preserve">0.39475029706955</t>
   </si>
   <si>
     <t xml:space="preserve">0.397063225507736</t>
@@ -1613,31 +1613,31 @@
     <t xml:space="preserve">0.389353275299072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387040317058563</t>
+    <t xml:space="preserve">0.387040257453918</t>
   </si>
   <si>
     <t xml:space="preserve">0.385498285293579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375475317239761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36622342467308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351188987493515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345406532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348875939846039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36699441075325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372391372919083</t>
+    <t xml:space="preserve">0.375475347042084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366223365068436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351188957691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345406502485275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348875969648361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366994440555573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372391402721405</t>
   </si>
   <si>
     <t xml:space="preserve">0.36776539683342</t>
@@ -1646,55 +1646,55 @@
     <t xml:space="preserve">0.373162358999252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370078414678574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370463877916336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369692862033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365837901830673</t>
+    <t xml:space="preserve">0.370078384876251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370463907718658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369692891836166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365837961435318</t>
   </si>
   <si>
     <t xml:space="preserve">0.371620357036591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368536382913589</t>
+    <t xml:space="preserve">0.368536412715912</t>
   </si>
   <si>
     <t xml:space="preserve">0.368921905755997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378944844007492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383570820093155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377017349004745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382414311170578</t>
+    <t xml:space="preserve">0.37894481420517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383570790290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377017319202423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382414370775223</t>
   </si>
   <si>
     <t xml:space="preserve">0.39937624335289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416338235139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424048155546188</t>
+    <t xml:space="preserve">0.416338205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424048125743866</t>
   </si>
   <si>
     <t xml:space="preserve">0.424819141626358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417109191417694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422506153583527</t>
+    <t xml:space="preserve">0.417109221220016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422506093978882</t>
   </si>
   <si>
     <t xml:space="preserve">0.421735167503357</t>
@@ -1703,22 +1703,22 @@
     <t xml:space="preserve">0.420964151620865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408628195524216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400918245315552</t>
+    <t xml:space="preserve">0.408628165721893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400918215513229</t>
   </si>
   <si>
     <t xml:space="preserve">0.404773235321045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405544251203537</t>
+    <t xml:space="preserve">0.405544281005859</t>
   </si>
   <si>
     <t xml:space="preserve">0.411712169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412483245134354</t>
+    <t xml:space="preserve">0.412483215332031</t>
   </si>
   <si>
     <t xml:space="preserve">0.423277169466019</t>
@@ -1727,34 +1727,34 @@
     <t xml:space="preserve">0.42559015750885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419422179460526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430216163396835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427132129669189</t>
+    <t xml:space="preserve">0.419422149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430216103792191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427132189273834</t>
   </si>
   <si>
     <t xml:space="preserve">0.414025217294693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414796143770218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413254171609879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40939924120903</t>
+    <t xml:space="preserve">0.414796203374863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413254201412201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409399181604385</t>
   </si>
   <si>
     <t xml:space="preserve">0.395521283149719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393208265304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392437249422073</t>
+    <t xml:space="preserve">0.393208295106888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392437279224396</t>
   </si>
   <si>
     <t xml:space="preserve">0.391666293144226</t>
@@ -1763,34 +1763,34 @@
     <t xml:space="preserve">0.393979251384735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39860525727272</t>
+    <t xml:space="preserve">0.398605287075043</t>
   </si>
   <si>
     <t xml:space="preserve">0.403231233358383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411275893449783</t>
+    <t xml:space="preserve">0.411275923252106</t>
   </si>
   <si>
     <t xml:space="preserve">0.410471081733704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409666210412979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415300130844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412885665893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412080824375153</t>
+    <t xml:space="preserve">0.409666240215302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415300160646439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412885636091232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41208079457283</t>
   </si>
   <si>
     <t xml:space="preserve">0.399203270673752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401215374469757</t>
+    <t xml:space="preserve">0.401215344667435</t>
   </si>
   <si>
     <t xml:space="preserve">0.404032319784164</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">0.397996008396149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403227478265762</t>
+    <t xml:space="preserve">0.40322744846344</t>
   </si>
   <si>
     <t xml:space="preserve">0.39839842915535</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">0.40242263674736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400410503149033</t>
+    <t xml:space="preserve">0.400410532951355</t>
   </si>
   <si>
     <t xml:space="preserve">0.395983874797821</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">0.418519496917725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417714655399323</t>
+    <t xml:space="preserve">0.417714685201645</t>
   </si>
   <si>
     <t xml:space="preserve">0.416909873485565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404837161302567</t>
+    <t xml:space="preserve">0.404837191104889</t>
   </si>
   <si>
     <t xml:space="preserve">0.401617795228958</t>
@@ -1841,13 +1841,13 @@
     <t xml:space="preserve">0.40805658698082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405642032623291</t>
+    <t xml:space="preserve">0.405642002820969</t>
   </si>
   <si>
     <t xml:space="preserve">0.397593557834625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391154825687408</t>
+    <t xml:space="preserve">0.391154795885086</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446844339371</t>
@@ -1856,25 +1856,25 @@
     <t xml:space="preserve">0.42656797170639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433811604976654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424153447151184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432201951742172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425763130187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428177714347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43300673365593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429787337779999</t>
+    <t xml:space="preserve">0.433811575174332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424153476953506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432201892137527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425763159990311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428177684545517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433006763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429787307977676</t>
   </si>
   <si>
     <t xml:space="preserve">0.420934081077576</t>
@@ -1883,58 +1883,58 @@
     <t xml:space="preserve">0.428982526063919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437030971050262</t>
+    <t xml:space="preserve">0.437031000852585</t>
   </si>
   <si>
     <t xml:space="preserve">0.434616476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430592268705368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442664921283722</t>
+    <t xml:space="preserve">0.430592238903046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4426648914814</t>
   </si>
   <si>
     <t xml:space="preserve">0.458761811256409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466810256242752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473248988389969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476468443870544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478882938623428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475663602352142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481297433376312</t>
+    <t xml:space="preserve">0.46681022644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473248958587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4764683842659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478882968425751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47566357254982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481297492980957</t>
   </si>
   <si>
     <t xml:space="preserve">0.478078097105026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474858641624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471639335155487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472444206476212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486126571893692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480492621660233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49497988820076</t>
+    <t xml:space="preserve">0.474858701229095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471639364957809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472444146871567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48612654209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48049259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494979828596115</t>
   </si>
   <si>
     <t xml:space="preserve">0.511881589889526</t>
@@ -1943,31 +1943,31 @@
     <t xml:space="preserve">0.513491272926331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520734906196594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535222172737122</t>
+    <t xml:space="preserve">0.520734846591949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535222113132477</t>
   </si>
   <si>
     <t xml:space="preserve">0.53441721200943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523149371147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51510089635849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516710698604584</t>
+    <t xml:space="preserve">0.523149311542511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515100955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516710758209229</t>
   </si>
   <si>
     <t xml:space="preserve">0.522344529628754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556147992610931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555343210697174</t>
+    <t xml:space="preserve">0.556148052215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555343270301819</t>
   </si>
   <si>
     <t xml:space="preserve">0.551319003105164</t>
@@ -1976,13 +1976,13 @@
     <t xml:space="preserve">0.557757794857025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571440160274506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56178206205368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560977220535278</t>
+    <t xml:space="preserve">0.571440100669861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561781942844391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560977101325989</t>
   </si>
   <si>
     <t xml:space="preserve">0.552928686141968</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">0.59639036655426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599609673023224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611682415008545</t>
+    <t xml:space="preserve">0.599609732627869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61168247461319</t>
   </si>
   <si>
     <t xml:space="preserve">0.606853306293488</t>
@@ -2012,61 +2012,61 @@
     <t xml:space="preserve">0.614901781082153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600414574146271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608462989330292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593975722789764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590756475925446</t>
+    <t xml:space="preserve">0.600414633750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608463048934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593975782394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590756416320801</t>
   </si>
   <si>
     <t xml:space="preserve">0.595585525035858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609267830848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614096999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606048464775085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593170940876007</t>
+    <t xml:space="preserve">0.609267890453339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614096939563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60604852437973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593171000480652</t>
   </si>
   <si>
     <t xml:space="preserve">0.598804891109467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601219415664673</t>
+    <t xml:space="preserve">0.601219356060028</t>
   </si>
   <si>
     <t xml:space="preserve">0.594780683517456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603633880615234</t>
+    <t xml:space="preserve">0.603633940219879</t>
   </si>
   <si>
     <t xml:space="preserve">0.610072731971741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.59799998998642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630193889141083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631803452968597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.646290719509125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65594893693924</t>
+    <t xml:space="preserve">0.598000049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630193769931793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631803572177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64629077911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655948877334595</t>
   </si>
   <si>
     <t xml:space="preserve">0.659973084926605</t>
@@ -2078,25 +2078,25 @@
     <t xml:space="preserve">0.684118449687958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661582827568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588341951370239</t>
+    <t xml:space="preserve">0.661582887172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588341891765594</t>
   </si>
   <si>
     <t xml:space="preserve">0.581098258495331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572244942188263</t>
+    <t xml:space="preserve">0.572245001792908</t>
   </si>
   <si>
     <t xml:space="preserve">0.540856003761292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543270587921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518320322036743</t>
+    <t xml:space="preserve">0.543270528316498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518320381641388</t>
   </si>
   <si>
     <t xml:space="preserve">0.526368796825409</t>
@@ -2108,22 +2108,22 @@
     <t xml:space="preserve">0.439445495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398800820112228</t>
+    <t xml:space="preserve">0.398800849914551</t>
   </si>
   <si>
     <t xml:space="preserve">0.381496667861938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323145359754562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348095595836639</t>
+    <t xml:space="preserve">0.323145389556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348095566034317</t>
   </si>
   <si>
     <t xml:space="preserve">0.303829073905945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282500684261322</t>
+    <t xml:space="preserve">0.282500714063644</t>
   </si>
   <si>
     <t xml:space="preserve">0.288939446210861</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">0.29135400056839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304633915424347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308255732059479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343668937683105</t>
+    <t xml:space="preserve">0.304633945226669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308255702257156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343668878078461</t>
   </si>
   <si>
     <t xml:space="preserve">0.35896098613739</t>
@@ -2150,28 +2150,28 @@
     <t xml:space="preserve">0.355741620063782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373850613832474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391959637403488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379082143306732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375057846307755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384716004133224</t>
+    <t xml:space="preserve">0.373850673437119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391959607601166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37908211350441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375057905912399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384716033935547</t>
   </si>
   <si>
     <t xml:space="preserve">0.386325746774673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37425309419632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362180382013321</t>
+    <t xml:space="preserve">0.374253064393997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362180352210999</t>
   </si>
   <si>
     <t xml:space="preserve">0.351717382669449</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">0.34930282831192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344473779201508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323547780513763</t>
+    <t xml:space="preserve">0.34447380900383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323547810316086</t>
   </si>
   <si>
     <t xml:space="preserve">0.338034987449646</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">0.339644730091095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341254383325577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346083492040634</t>
+    <t xml:space="preserve">0.341254353523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346083462238312</t>
   </si>
   <si>
     <t xml:space="preserve">0.350912541151047</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">0.348497986793518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342864096164703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345278590917587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336425364017487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324352651834488</t>
+    <t xml:space="preserve">0.342864066362381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34527862071991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336425304412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324352622032166</t>
   </si>
   <si>
     <t xml:space="preserve">0.329986542463303</t>
@@ -2231,52 +2231,52 @@
     <t xml:space="preserve">0.331596255302429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340449541807175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347693175077438</t>
+    <t xml:space="preserve">0.340449601411819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347693145275116</t>
   </si>
   <si>
     <t xml:space="preserve">0.352522224187851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354936748743057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369424015283585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382301509380341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379886955022812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371838539838791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354131907224655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330791413784027</t>
+    <t xml:space="preserve">0.35493677854538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369423985481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382301449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379886984825134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371838510036469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354131937026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330791443586349</t>
   </si>
   <si>
     <t xml:space="preserve">0.356546431779861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357351332902908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350107669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346888303756714</t>
+    <t xml:space="preserve">0.357351303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350107699632645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346888333559036</t>
   </si>
   <si>
     <t xml:space="preserve">0.342059224843979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337230145931244</t>
+    <t xml:space="preserve">0.337230175733566</t>
   </si>
   <si>
     <t xml:space="preserve">0.328376859426498</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">0.370228826999664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358156114816666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363790035247803</t>
+    <t xml:space="preserve">0.358156144618988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363790065050125</t>
   </si>
   <si>
     <t xml:space="preserve">0.420129239559174</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">0.424958318471909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437835842370987</t>
+    <t xml:space="preserve">0.437835812568665</t>
   </si>
   <si>
     <t xml:space="preserve">0.444274574518204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445884257555008</t>
+    <t xml:space="preserve">0.445884317159653</t>
   </si>
   <si>
     <t xml:space="preserve">0.482907176017761</t>
@@ -2315,64 +2315,64 @@
     <t xml:space="preserve">0.560172319412231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527978479862213</t>
+    <t xml:space="preserve">0.527978539466858</t>
   </si>
   <si>
     <t xml:space="preserve">0.521539688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529588162899017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519930124282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507052481174469</t>
+    <t xml:space="preserve">0.529588222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519930064678192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507052540779114</t>
   </si>
   <si>
     <t xml:space="preserve">0.500613749027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494175046682358</t>
+    <t xml:space="preserve">0.494174987077713</t>
   </si>
   <si>
     <t xml:space="preserve">0.502223491668701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537636578083038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524759113788605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510271966457367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499004006385803</t>
+    <t xml:space="preserve">0.537636637687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52475917339325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510271847248077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499004065990448</t>
   </si>
   <si>
     <t xml:space="preserve">0.492565304040909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487736195325851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484516859054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447493940591812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431397050619125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449103683233261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43622612953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393569320440292</t>
+    <t xml:space="preserve">0.487736254930496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484516769647598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447494000196457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431397080421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449103653430939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436226159334183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393569350242615</t>
   </si>
   <si>
     <t xml:space="preserve">0.378277271986008</t>
@@ -2384,13 +2384,13 @@
     <t xml:space="preserve">0.367009431123734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359765827655792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376667588949203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421738862991333</t>
+    <t xml:space="preserve">0.359765857458115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376667559146881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4217389523983</t>
   </si>
   <si>
     <t xml:space="preserve">0.423348635435104</t>
@@ -2405,46 +2405,46 @@
     <t xml:space="preserve">0.468419939279556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461981236934662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465200513601303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45232304930687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455542385578156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450713336467743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460371524095535</t>
+    <t xml:space="preserve">0.461981207132339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465200573205948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452323019504547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4555424451828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450713366270065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460371553897858</t>
   </si>
   <si>
     <t xml:space="preserve">0.457152128219604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453932762145996</t>
+    <t xml:space="preserve">0.453932702541351</t>
   </si>
   <si>
     <t xml:space="preserve">0.47968778014183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495784670114517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489345848560333</t>
+    <t xml:space="preserve">0.495784640312195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4893459379673</t>
   </si>
   <si>
     <t xml:space="preserve">0.547294795513153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565001368522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576269268989563</t>
+    <t xml:space="preserve">0.565001428127289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576269209384918</t>
   </si>
   <si>
     <t xml:space="preserve">0.575464367866516</t>
@@ -2459,28 +2459,28 @@
     <t xml:space="preserve">0.56741589307785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545685112476349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558562576770782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5440753698349</t>
+    <t xml:space="preserve">0.545685052871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558562636375427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544075429439545</t>
   </si>
   <si>
     <t xml:space="preserve">0.531197905540466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559367418289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573854625225067</t>
+    <t xml:space="preserve">0.559367477893829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573854684829712</t>
   </si>
   <si>
     <t xml:space="preserve">0.581903100013733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579488635063171</t>
+    <t xml:space="preserve">0.579488575458527</t>
   </si>
   <si>
     <t xml:space="preserve">0.544880270957947</t>
@@ -2489,16 +2489,16 @@
     <t xml:space="preserve">0.552123844623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548099637031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548904478549957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553733646869659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582058310508728</t>
+    <t xml:space="preserve">0.54809957742691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548904418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553733587265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582058250904083</t>
   </si>
   <si>
     <t xml:space="preserve">0.581226766109467</t>
@@ -2507,10 +2507,10 @@
     <t xml:space="preserve">0.573743164539337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567091107368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574589729309</t>
+    <t xml:space="preserve">0.567091047763824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574649333954</t>
   </si>
   <si>
     <t xml:space="preserve">0.57291167974472</t>
@@ -2519,19 +2519,19 @@
     <t xml:space="preserve">0.561270534992218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557944416999817</t>
+    <t xml:space="preserve">0.557944476604462</t>
   </si>
   <si>
     <t xml:space="preserve">0.558775961399078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540482699871063</t>
+    <t xml:space="preserve">0.540482640266418</t>
   </si>
   <si>
     <t xml:space="preserve">0.544640243053436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542977273464203</t>
+    <t xml:space="preserve">0.542977213859558</t>
   </si>
   <si>
     <t xml:space="preserve">0.530504584312439</t>
@@ -2543,55 +2543,55 @@
     <t xml:space="preserve">0.532167553901672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516368865966797</t>
+    <t xml:space="preserve">0.516368806362152</t>
   </si>
   <si>
     <t xml:space="preserve">0.511379778385162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505559146404266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508885204792023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502233147621155</t>
+    <t xml:space="preserve">0.505559206008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508885264396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50223308801651</t>
   </si>
   <si>
     <t xml:space="preserve">0.515537321567535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498907119035721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493918001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494749575853348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500570118427277</t>
+    <t xml:space="preserve">0.498907148838043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493918061256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49474960565567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500570058822632</t>
   </si>
   <si>
     <t xml:space="preserve">0.48393988609314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465646594762802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466478079557419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461489051580429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46065753698349</t>
+    <t xml:space="preserve">0.465646624565125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466478109359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461489081382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460657566785812</t>
   </si>
   <si>
     <t xml:space="preserve">0.473961770534515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473130285739899</t>
+    <t xml:space="preserve">0.473130226135254</t>
   </si>
   <si>
     <t xml:space="preserve">0.486434429883957</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">0.489760458469391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503064632415771</t>
+    <t xml:space="preserve">0.503064692020416</t>
   </si>
   <si>
     <t xml:space="preserve">0.50472766160965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506390690803528</t>
+    <t xml:space="preserve">0.506390750408173</t>
   </si>
   <si>
     <t xml:space="preserve">0.510548293590546</t>
@@ -2615,22 +2615,22 @@
     <t xml:space="preserve">0.503896176815033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495581090450287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484771400690079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482276886701584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491423547267914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497244030237198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487265944480896</t>
+    <t xml:space="preserve">0.495581030845642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484771370887756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482276827096939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491423517465591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497244089841843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487265974283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.493086487054825</t>
@@ -2639,49 +2639,49 @@
     <t xml:space="preserve">0.483108341693878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478119343519211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475624799728394</t>
+    <t xml:space="preserve">0.478119283914566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475624829530716</t>
   </si>
   <si>
     <t xml:space="preserve">0.476456254720688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529672980308533</t>
+    <t xml:space="preserve">0.529673099517822</t>
   </si>
   <si>
     <t xml:space="preserve">0.523852467536926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528010010719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533830583095551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527178525924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547966241836548</t>
+    <t xml:space="preserve">0.528009951114655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533830642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527178466320038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547966301441193</t>
   </si>
   <si>
     <t xml:space="preserve">0.528841495513916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52551543712616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526347041130066</t>
+    <t xml:space="preserve">0.525515496730804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526346981525421</t>
   </si>
   <si>
     <t xml:space="preserve">0.554618358612061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588710367679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57540625333786</t>
+    <t xml:space="preserve">0.588710427284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575406134128571</t>
   </si>
   <si>
     <t xml:space="preserve">0.577069222927094</t>
@@ -2693,22 +2693,22 @@
     <t xml:space="preserve">0.583721339702606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585384428501129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57790070772171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58039528131485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550460815429688</t>
+    <t xml:space="preserve">0.58538430929184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577900767326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580395221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550460875034332</t>
   </si>
   <si>
     <t xml:space="preserve">0.556281447410583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545471727848053</t>
+    <t xml:space="preserve">0.545471847057343</t>
   </si>
   <si>
     <t xml:space="preserve">0.567922592163086</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">0.552123785018921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56459653377533</t>
+    <t xml:space="preserve">0.564596593379974</t>
   </si>
   <si>
     <t xml:space="preserve">0.549629330635071</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">0.532999098300934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524683952331543</t>
+    <t xml:space="preserve">0.524683892726898</t>
   </si>
   <si>
     <t xml:space="preserve">0.509716749191284</t>
@@ -2747,10 +2747,10 @@
     <t xml:space="preserve">0.507222235202789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521357893943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513874351978302</t>
+    <t xml:space="preserve">0.521357953548431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513874292373657</t>
   </si>
   <si>
     <t xml:space="preserve">0.522189497947693</t>
@@ -2765,34 +2765,34 @@
     <t xml:space="preserve">0.523020923137665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519694864749908</t>
+    <t xml:space="preserve">0.519694924354553</t>
   </si>
   <si>
     <t xml:space="preserve">0.508053779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488097488880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488928943872452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492255032062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496412575244904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490591913461685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485602915287018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480613797903061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474793195724487</t>
+    <t xml:space="preserve">0.488097429275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488928914070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492255002260208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496412545442581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49059197306633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48560294508934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480613857507706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474793285131454</t>
   </si>
   <si>
     <t xml:space="preserve">0.4540054500103</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">0.458163022994995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44901642203331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439869731664658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439038246870041</t>
+    <t xml:space="preserve">0.449016451835632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43986976146698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439038276672363</t>
   </si>
   <si>
     <t xml:space="preserve">0.419913470745087</t>
@@ -2825,19 +2825,19 @@
     <t xml:space="preserve">0.411598384380341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41118261218071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395799607038498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377090632915497</t>
+    <t xml:space="preserve">0.411182641983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39579963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377090603113174</t>
   </si>
   <si>
     <t xml:space="preserve">0.365033686161041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402035981416702</t>
+    <t xml:space="preserve">0.40203595161438</t>
   </si>
   <si>
     <t xml:space="preserve">0.413677155971527</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">0.431554615497589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429891616106033</t>
+    <t xml:space="preserve">0.429891645908356</t>
   </si>
   <si>
     <t xml:space="preserve">0.432386130094528</t>
@@ -2864,46 +2864,46 @@
     <t xml:space="preserve">0.444027274847031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436543703079224</t>
+    <t xml:space="preserve">0.436543673276901</t>
   </si>
   <si>
     <t xml:space="preserve">0.443195819854736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448184847831726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.446521908044815</t>
+    <t xml:space="preserve">0.448184877634048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44652184844017</t>
   </si>
   <si>
     <t xml:space="preserve">0.440701246261597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434880673885345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424902528524399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444858878850937</t>
+    <t xml:space="preserve">0.43488073348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424902558326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444858849048615</t>
   </si>
   <si>
     <t xml:space="preserve">0.447353363037109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445690333843231</t>
+    <t xml:space="preserve">0.445690363645554</t>
   </si>
   <si>
     <t xml:space="preserve">0.46315211057663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481445372104645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477287858724594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470635652542114</t>
+    <t xml:space="preserve">0.481445342302322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477287799119949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470635712146759</t>
   </si>
   <si>
     <t xml:space="preserve">0.437375247478485</t>
@@ -2921,19 +2921,19 @@
     <t xml:space="preserve">0.430723130702972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427397072315216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415755927562714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43321767449379</t>
+    <t xml:space="preserve">0.427397102117538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415755897760391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433217704296112</t>
   </si>
   <si>
     <t xml:space="preserve">0.452196657657623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446109443902969</t>
+    <t xml:space="preserve">0.446109414100647</t>
   </si>
   <si>
     <t xml:space="preserve">0.439152538776398</t>
@@ -2945,16 +2945,16 @@
     <t xml:space="preserve">0.423499554395676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406542211771011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403063744306564</t>
+    <t xml:space="preserve">0.406542181968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403063774108887</t>
   </si>
   <si>
     <t xml:space="preserve">0.414368689060211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393932908773422</t>
+    <t xml:space="preserve">0.3939328789711</t>
   </si>
   <si>
     <t xml:space="preserve">0.391324043273926</t>
@@ -2963,19 +2963,19 @@
     <t xml:space="preserve">0.383932381868362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388715237379074</t>
+    <t xml:space="preserve">0.388715207576752</t>
   </si>
   <si>
     <t xml:space="preserve">0.382627964019775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380888730287552</t>
+    <t xml:space="preserve">0.380888760089874</t>
   </si>
   <si>
     <t xml:space="preserve">0.387845605611801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393498033285141</t>
+    <t xml:space="preserve">0.393498063087463</t>
   </si>
   <si>
     <t xml:space="preserve">0.379584342241287</t>
@@ -2984,19 +2984,19 @@
     <t xml:space="preserve">0.384367197751999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378714740276337</t>
+    <t xml:space="preserve">0.378714710474014</t>
   </si>
   <si>
     <t xml:space="preserve">0.373931884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372627437114716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37306222319603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378279894590378</t>
+    <t xml:space="preserve">0.372627466917038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373062252998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3782799243927</t>
   </si>
   <si>
     <t xml:space="preserve">0.370888233184814</t>
@@ -3008,22 +3008,22 @@
     <t xml:space="preserve">0.366105407476425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371323049068451</t>
+    <t xml:space="preserve">0.371323019266129</t>
   </si>
   <si>
     <t xml:space="preserve">0.375671088695526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374366670846939</t>
+    <t xml:space="preserve">0.374366700649261</t>
   </si>
   <si>
     <t xml:space="preserve">0.370018631219864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367844581604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366975009441376</t>
+    <t xml:space="preserve">0.367844641208649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366974979639053</t>
   </si>
   <si>
     <t xml:space="preserve">0.364366173744202</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">0.36175736784935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368714213371277</t>
+    <t xml:space="preserve">0.368714183568954</t>
   </si>
   <si>
     <t xml:space="preserve">0.377410292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36958384513855</t>
+    <t xml:space="preserve">0.369583815336227</t>
   </si>
   <si>
     <t xml:space="preserve">0.377845108509064</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">0.375236243009567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372192651033401</t>
+    <t xml:space="preserve">0.372192680835724</t>
   </si>
   <si>
     <t xml:space="preserve">0.36523574590683</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">0.367409825325012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376975506544113</t>
+    <t xml:space="preserve">0.376975476741791</t>
   </si>
   <si>
     <t xml:space="preserve">0.364800959825516</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">0.397411316633224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402628988027573</t>
+    <t xml:space="preserve">0.40262895822525</t>
   </si>
   <si>
     <t xml:space="preserve">0.407846629619598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389584869146347</t>
+    <t xml:space="preserve">0.389584839344025</t>
   </si>
   <si>
     <t xml:space="preserve">0.396106898784637</t>
@@ -3095,31 +3095,31 @@
     <t xml:space="preserve">0.403498560190201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396541714668274</t>
+    <t xml:space="preserve">0.396541684865952</t>
   </si>
   <si>
     <t xml:space="preserve">0.392193675041199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401759386062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403933376073837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408716231584549</t>
+    <t xml:space="preserve">0.4017593562603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40393340587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408716201782227</t>
   </si>
   <si>
     <t xml:space="preserve">0.400020152330399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400889724493027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393063247203827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380019158124924</t>
+    <t xml:space="preserve">0.400889754295349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393063277006149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380019128322601</t>
   </si>
   <si>
     <t xml:space="preserve">0.385236769914627</t>
@@ -3128,22 +3128,22 @@
     <t xml:space="preserve">0.389150023460388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390889227390289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395672082901001</t>
+    <t xml:space="preserve">0.390889257192612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395672112703323</t>
   </si>
   <si>
     <t xml:space="preserve">0.401324540376663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39697653055191</t>
+    <t xml:space="preserve">0.396976500749588</t>
   </si>
   <si>
     <t xml:space="preserve">0.400454938411713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390454411506653</t>
+    <t xml:space="preserve">0.390454441308975</t>
   </si>
   <si>
     <t xml:space="preserve">0.387410819530487</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">0.382193177938461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381758362054825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371757864952087</t>
+    <t xml:space="preserve">0.381758332252502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371757835149765</t>
   </si>
   <si>
     <t xml:space="preserve">0.357844114303589</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">0.362626940011978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369149029254913</t>
+    <t xml:space="preserve">0.369148999452591</t>
   </si>
   <si>
     <t xml:space="preserve">0.379149526357651</t>
@@ -3182,25 +3182,25 @@
     <t xml:space="preserve">0.3861064016819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394367694854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404368221759796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392628461122513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391758888959885</t>
+    <t xml:space="preserve">0.394367665052414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404368191957474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392628490924835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391758859157562</t>
   </si>
   <si>
     <t xml:space="preserve">0.395237267017365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385671585798264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394802510738373</t>
+    <t xml:space="preserve">0.385671615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39480248093605</t>
   </si>
   <si>
     <t xml:space="preserve">0.388280391693115</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">0.403868108987808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406615495681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407531291246414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40936291217804</t>
+    <t xml:space="preserve">0.406615525484085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407531321048737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409362882375717</t>
   </si>
   <si>
     <t xml:space="preserve">0.408447116613388</t>
@@ -3242,19 +3242,16 @@
     <t xml:space="preserve">0.402952283620834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396541684865952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402036517858505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393794298171997</t>
+    <t xml:space="preserve">0.402036488056183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393794327974319</t>
   </si>
   <si>
     <t xml:space="preserve">0.39104688167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391962677240372</t>
+    <t xml:space="preserve">0.391962707042694</t>
   </si>
   <si>
     <t xml:space="preserve">0.390131086111069</t>
@@ -3263,22 +3260,22 @@
     <t xml:space="preserve">0.394710093736649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395625919103622</t>
+    <t xml:space="preserve">0.3956258893013</t>
   </si>
   <si>
     <t xml:space="preserve">0.397457480430603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392878472805023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388299494981766</t>
+    <t xml:space="preserve">0.392878502607346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388299465179443</t>
   </si>
   <si>
     <t xml:space="preserve">0.384636282920837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38921532034874</t>
+    <t xml:space="preserve">0.389215290546417</t>
   </si>
   <si>
     <t xml:space="preserve">0.386467903852463</t>
@@ -3305,13 +3302,13 @@
     <t xml:space="preserve">0.380973100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375478297472</t>
+    <t xml:space="preserve">0.375478267669678</t>
   </si>
   <si>
     <t xml:space="preserve">0.373646676540375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371815085411072</t>
+    <t xml:space="preserve">0.371815055608749</t>
   </si>
   <si>
     <t xml:space="preserve">0.369067668914795</t>
@@ -3320,7 +3317,7 @@
     <t xml:space="preserve">0.369983494281769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376394122838974</t>
+    <t xml:space="preserve">0.376394093036652</t>
   </si>
   <si>
     <t xml:space="preserve">0.374562501907349</t>
@@ -3329,7 +3326,7 @@
     <t xml:space="preserve">0.37089928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378225654363632</t>
+    <t xml:space="preserve">0.378225684165955</t>
   </si>
   <si>
     <t xml:space="preserve">0.385552108287811</t>
@@ -3347,10 +3344,10 @@
     <t xml:space="preserve">0.420352518558502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421268314123154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425847351551056</t>
+    <t xml:space="preserve">0.421268343925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425847321748734</t>
   </si>
   <si>
     <t xml:space="preserve">0.416689306497574</t>
@@ -3380,7 +3377,7 @@
     <t xml:space="preserve">0.415773510932922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410278737545013</t>
+    <t xml:space="preserve">0.410278707742691</t>
   </si>
   <si>
     <t xml:space="preserve">0.422184109687805</t>
@@ -3398,19 +3395,19 @@
     <t xml:space="preserve">0.456068724393845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445994913578033</t>
+    <t xml:space="preserve">0.445994943380356</t>
   </si>
   <si>
     <t xml:space="preserve">0.494532406330109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487206012010574</t>
+    <t xml:space="preserve">0.48720595240593</t>
   </si>
   <si>
     <t xml:space="preserve">0.492700755596161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481711179018021</t>
+    <t xml:space="preserve">0.481711208820343</t>
   </si>
   <si>
     <t xml:space="preserve">0.489037543535233</t>
@@ -3419,16 +3416,16 @@
     <t xml:space="preserve">0.496363997459412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485374361276627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483542770147324</t>
+    <t xml:space="preserve">0.485374301671982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483542799949646</t>
   </si>
   <si>
     <t xml:space="preserve">0.454237133264542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463395148515701</t>
+    <t xml:space="preserve">0.463395118713379</t>
   </si>
   <si>
     <t xml:space="preserve">0.476216346025467</t>
@@ -53797,7 +53794,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1910" t="s">
-        <v>1076</v>
+        <v>1027</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53823,7 +53820,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1911" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53875,7 +53872,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1913" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53901,7 +53898,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1914" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53927,7 +53924,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1915" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53953,7 +53950,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1916" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53979,7 +53976,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1917" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54005,7 +54002,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1918" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54031,7 +54028,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1919" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54057,7 +54054,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1920" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54083,7 +54080,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1921" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54109,7 +54106,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1922" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54135,7 +54132,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1923" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54161,7 +54158,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1924" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54187,7 +54184,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1925" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54213,7 +54210,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1926" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54239,7 +54236,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1927" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54291,7 +54288,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1929" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54317,7 +54314,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1930" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54343,7 +54340,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1931" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54369,7 +54366,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1932" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54395,7 +54392,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1933" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54421,7 +54418,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1934" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54447,7 +54444,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1935" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54473,7 +54470,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1936" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54499,7 +54496,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1937" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54525,7 +54522,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1938" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54551,7 +54548,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1939" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54577,7 +54574,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1940" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54603,7 +54600,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1941" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54629,7 +54626,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1942" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54655,7 +54652,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1943" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54681,7 +54678,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1944" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54707,7 +54704,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1945" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54733,7 +54730,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1946" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54759,7 +54756,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1947" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54785,7 +54782,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1948" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54811,7 +54808,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1949" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54967,7 +54964,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1955" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55123,7 +55120,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1961" t="s">
-        <v>1076</v>
+        <v>1027</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55201,7 +55198,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1964" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55227,7 +55224,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1965" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55253,7 +55250,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1966" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55279,7 +55276,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1967" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55305,7 +55302,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1968" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55331,7 +55328,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1969" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55357,7 +55354,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1970" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55383,7 +55380,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -55409,7 +55406,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1972" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55435,7 +55432,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1973" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55461,7 +55458,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1974" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55487,7 +55484,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1975" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55513,7 +55510,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1976" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55539,7 +55536,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1977" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55565,7 +55562,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1978" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55591,7 +55588,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1979" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55617,7 +55614,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1980" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55643,7 +55640,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1981" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55669,7 +55666,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1982" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55695,7 +55692,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1983" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55721,7 +55718,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1984" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55747,7 +55744,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1985" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55773,7 +55770,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1986" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55799,7 +55796,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1987" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55825,7 +55822,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1988" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55851,7 +55848,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1989" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55877,7 +55874,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G1990" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55903,7 +55900,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1991" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55929,7 +55926,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1992" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55955,7 +55952,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1993" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55981,7 +55978,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1994" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56007,7 +56004,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1995" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56033,7 +56030,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1996" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56059,7 +56056,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1997" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56085,7 +56082,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1998" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56111,7 +56108,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1999" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56137,7 +56134,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2000" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56163,7 +56160,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2001" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56189,7 +56186,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2002" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56215,7 +56212,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2003" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56241,7 +56238,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2004" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56267,7 +56264,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2005" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56293,7 +56290,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2006" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56319,7 +56316,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2007" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56345,7 +56342,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2008" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56371,7 +56368,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2009" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56397,7 +56394,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2010" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56423,7 +56420,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2011" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56449,7 +56446,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2012" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56475,7 +56472,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56501,7 +56498,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2014" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56527,7 +56524,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2015" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56553,7 +56550,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2016" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56579,7 +56576,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56631,7 +56628,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56657,7 +56654,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2020" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56683,7 +56680,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2021" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56709,7 +56706,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2022" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56735,7 +56732,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2023" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56761,7 +56758,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2024" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56787,7 +56784,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G2025" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56813,7 +56810,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2026" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56839,7 +56836,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2027" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56865,7 +56862,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2028" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56891,7 +56888,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G2029" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56917,7 +56914,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2030" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56943,7 +56940,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2031" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56969,7 +56966,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2032" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56995,7 +56992,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2033" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57021,7 +57018,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2034" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57047,7 +57044,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2035" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57073,7 +57070,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2036" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57099,7 +57096,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2037" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57125,7 +57122,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2038" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57151,7 +57148,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2039" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57177,7 +57174,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2040" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57203,7 +57200,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57229,7 +57226,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2042" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57255,7 +57252,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2043" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57307,7 +57304,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2045" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57515,7 +57512,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2053" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57541,7 +57538,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2054" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57749,7 +57746,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2062" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57801,7 +57798,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2064" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57827,7 +57824,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2065" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57853,7 +57850,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2066" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57879,7 +57876,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2067" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57931,7 +57928,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2069" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58217,7 +58214,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2080" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58269,7 +58266,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2082" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58295,7 +58292,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G2083" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -58321,7 +58318,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2084" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58347,7 +58344,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2085" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58373,7 +58370,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2086" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58399,7 +58396,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2087" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -58425,7 +58422,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2088" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58581,7 +58578,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2094" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58607,7 +58604,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2095" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58633,7 +58630,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2096" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58659,7 +58656,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2097" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58685,7 +58682,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2098" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58815,7 +58812,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2103" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58841,7 +58838,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2104" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58867,7 +58864,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2105" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58893,7 +58890,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2106" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58919,7 +58916,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2107" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59205,7 +59202,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2118" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59231,7 +59228,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2119" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59257,7 +59254,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G2120" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59283,7 +59280,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2121" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59309,7 +59306,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2122" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59335,7 +59332,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G2123" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59361,7 +59358,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2124" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59387,7 +59384,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2125" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59413,7 +59410,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2126" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59439,7 +59436,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2127" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59465,7 +59462,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2128" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59491,7 +59488,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2129" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59517,7 +59514,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2130" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59543,7 +59540,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2131" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59569,7 +59566,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2132" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59595,7 +59592,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2133" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59621,7 +59618,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2134" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59647,7 +59644,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2135" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59673,7 +59670,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2136" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59699,7 +59696,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2137" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59725,7 +59722,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2138" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59751,7 +59748,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2139" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59777,7 +59774,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2140" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59803,7 +59800,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2141" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59829,7 +59826,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2142" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59855,7 +59852,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2143" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59881,7 +59878,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2144" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59907,7 +59904,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2145" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59933,7 +59930,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2146" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59959,7 +59956,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2147" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59985,7 +59982,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2148" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60011,7 +60008,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2149" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60037,7 +60034,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2150" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60063,7 +60060,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G2151" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60089,7 +60086,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2152" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60115,7 +60112,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2153" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60141,7 +60138,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2154" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60167,7 +60164,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2155" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60193,7 +60190,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60219,7 +60216,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60245,7 +60242,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2158" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60271,7 +60268,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2159" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60297,7 +60294,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2160" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60323,7 +60320,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2161" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60349,7 +60346,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2162" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60375,7 +60372,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2163" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60401,7 +60398,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2164" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60427,7 +60424,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2165" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60453,7 +60450,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2166" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60479,7 +60476,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2167" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60505,7 +60502,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2168" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60531,7 +60528,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2169" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60557,7 +60554,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2170" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60583,7 +60580,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2171" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60609,7 +60606,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2172" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60635,7 +60632,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2173" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60661,7 +60658,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2174" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60687,7 +60684,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2175" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60713,7 +60710,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2176" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60739,7 +60736,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2177" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60765,7 +60762,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2178" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60791,7 +60788,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2179" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60817,7 +60814,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2180" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60843,7 +60840,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2181" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60869,7 +60866,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2182" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60895,7 +60892,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2183" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60921,7 +60918,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2184" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60947,7 +60944,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2185" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60973,7 +60970,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2186" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60999,7 +60996,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2187" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61025,7 +61022,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2188" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61051,7 +61048,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2189" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61077,7 +61074,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61103,7 +61100,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2191" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61129,7 +61126,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2192" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61155,7 +61152,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2193" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61181,7 +61178,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2194" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61207,7 +61204,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2195" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61233,7 +61230,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2196" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61259,7 +61256,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2197" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61285,7 +61282,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2198" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61311,7 +61308,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2199" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61337,7 +61334,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2200" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61363,7 +61360,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2201" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61389,7 +61386,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2202" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61415,7 +61412,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2203" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61441,7 +61438,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2204" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61467,7 +61464,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2205" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61493,7 +61490,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2206" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61519,7 +61516,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2207" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61545,7 +61542,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2208" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61571,7 +61568,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2209" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61597,7 +61594,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2210" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61623,7 +61620,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2211" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61649,7 +61646,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2212" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61675,7 +61672,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2213" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61701,7 +61698,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2214" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61727,7 +61724,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61753,7 +61750,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2216" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61779,7 +61776,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2217" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61805,7 +61802,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2218" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61831,7 +61828,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2219" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61857,7 +61854,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2220" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61883,7 +61880,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2221" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61909,7 +61906,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2222" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61935,7 +61932,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2223" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61961,7 +61958,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2224" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61987,7 +61984,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2225" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62013,7 +62010,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2226" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62039,7 +62036,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2227" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62065,7 +62062,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2228" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62091,7 +62088,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2229" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62117,7 +62114,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2230" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62143,7 +62140,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2231" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62169,7 +62166,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2232" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62195,7 +62192,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2233" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62221,7 +62218,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2234" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62247,7 +62244,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2235" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62273,7 +62270,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2236" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62299,7 +62296,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2237" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62325,7 +62322,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2238" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62351,7 +62348,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2239" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62377,7 +62374,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2240" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62403,7 +62400,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2241" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62429,7 +62426,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2242" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62455,7 +62452,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2243" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62481,7 +62478,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2244" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62507,7 +62504,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2245" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62533,7 +62530,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2246" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62559,7 +62556,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62585,7 +62582,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62611,7 +62608,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2249" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62637,7 +62634,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2250" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62663,7 +62660,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2251" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62689,7 +62686,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2252" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62715,7 +62712,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G2253" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62741,7 +62738,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2254" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62767,7 +62764,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2255" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62793,7 +62790,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2256" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62819,7 +62816,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2257" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62845,7 +62842,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2258" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62871,7 +62868,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2259" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62897,7 +62894,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2260" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62923,7 +62920,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2261" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62949,7 +62946,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2262" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62975,7 +62972,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2263" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63001,7 +62998,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2264" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63027,7 +63024,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2265" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63053,7 +63050,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2266" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63079,7 +63076,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2267" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63105,7 +63102,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2268" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63131,7 +63128,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2269" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63157,7 +63154,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63183,7 +63180,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2271" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63209,7 +63206,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2272" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63235,7 +63232,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2273" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63261,7 +63258,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2274" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63287,7 +63284,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2275" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63313,7 +63310,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2276" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63339,7 +63336,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2277" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63365,7 +63362,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2278" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63391,7 +63388,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2279" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63417,7 +63414,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2280" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63443,7 +63440,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2281" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63469,7 +63466,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2282" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63495,7 +63492,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2283" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63521,7 +63518,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2284" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63547,7 +63544,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2285" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63573,7 +63570,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2286" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63599,7 +63596,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2287" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63625,7 +63622,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2288" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63651,7 +63648,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2289" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63677,7 +63674,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2290" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63703,7 +63700,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63729,7 +63726,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2292" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63755,7 +63752,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2293" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63781,7 +63778,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2294" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63807,7 +63804,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2295" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63833,7 +63830,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2296" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63859,7 +63856,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2297" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63885,7 +63882,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2298" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63911,7 +63908,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2299" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63937,7 +63934,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2300" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63963,7 +63960,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2301" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63989,7 +63986,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2302" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64015,7 +64012,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2303" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64041,7 +64038,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2304" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64067,7 +64064,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2305" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64093,7 +64090,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2306" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64119,7 +64116,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2307" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64145,7 +64142,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2308" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64171,7 +64168,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2309" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64197,7 +64194,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2310" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64223,7 +64220,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2311" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64249,7 +64246,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2312" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64275,7 +64272,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2313" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64301,7 +64298,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2314" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64327,7 +64324,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2315" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64353,7 +64350,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2316" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64379,7 +64376,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2317" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64405,7 +64402,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2318" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64431,7 +64428,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2319" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64457,7 +64454,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2320" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64483,7 +64480,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2321" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64509,7 +64506,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2322" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64535,7 +64532,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2323" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64561,7 +64558,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2324" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64587,7 +64584,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2325" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64613,7 +64610,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64639,7 +64636,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2327" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64665,7 +64662,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2328" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64691,7 +64688,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2329" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64717,7 +64714,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2330" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64743,7 +64740,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2331" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64769,7 +64766,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2332" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64795,7 +64792,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2333" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64821,7 +64818,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2334" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64847,7 +64844,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2335" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64873,7 +64870,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2336" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64899,7 +64896,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2337" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64925,7 +64922,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2338" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64951,7 +64948,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2339" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64977,7 +64974,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2340" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65003,7 +65000,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2341" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65029,7 +65026,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2342" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65055,7 +65052,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2343" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65081,7 +65078,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2344" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65107,7 +65104,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2345" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65133,7 +65130,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2346" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65159,7 +65156,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2347" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65185,7 +65182,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2348" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65211,7 +65208,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2349" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65237,7 +65234,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2350" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65263,7 +65260,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2351" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65289,7 +65286,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2352" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65315,7 +65312,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2353" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65341,7 +65338,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2354" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65367,7 +65364,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2355" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65393,7 +65390,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2356" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65419,7 +65416,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2357" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65445,7 +65442,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2358" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65471,7 +65468,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G2359" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65497,7 +65494,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G2360" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65523,7 +65520,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G2361" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65549,7 +65546,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2362" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65575,7 +65572,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2363" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65601,7 +65598,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2364" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65627,7 +65624,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2365" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65653,7 +65650,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G2366" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65679,7 +65676,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2367" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65705,7 +65702,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2368" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65731,7 +65728,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2369" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65757,7 +65754,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2370" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65783,7 +65780,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2371" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65809,7 +65806,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2372" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65835,7 +65832,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2373" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65861,7 +65858,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2374" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65887,7 +65884,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2375" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65913,7 +65910,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2376" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65939,7 +65936,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G2377" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65965,7 +65962,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2378" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65991,7 +65988,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2379" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66017,7 +66014,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2380" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66043,7 +66040,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2381" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66069,7 +66066,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2382" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66095,7 +66092,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2383" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66121,7 +66118,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2384" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66147,7 +66144,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2385" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66173,7 +66170,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2386" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66199,7 +66196,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2387" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66225,7 +66222,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2388" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66251,7 +66248,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2389" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66277,7 +66274,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2390" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66303,7 +66300,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66329,7 +66326,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2392" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66355,7 +66352,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2393" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66381,7 +66378,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2394" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66407,7 +66404,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2395" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66433,7 +66430,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2396" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66459,7 +66456,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2397" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66485,7 +66482,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2398" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66511,7 +66508,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2399" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66537,7 +66534,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G2400" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66563,7 +66560,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G2401" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66589,7 +66586,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2402" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66615,7 +66612,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2403" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66641,7 +66638,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2404" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66667,7 +66664,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2405" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66693,7 +66690,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2406" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66719,7 +66716,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2407" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66745,7 +66742,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2408" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66771,7 +66768,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2409" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66797,7 +66794,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G2410" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66823,7 +66820,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G2411" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66849,7 +66846,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2412" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66875,7 +66872,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2413" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66901,7 +66898,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G2414" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66927,7 +66924,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2415" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66953,7 +66950,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2416" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66979,7 +66976,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2417" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67005,7 +67002,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2418" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67031,7 +67028,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2419" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67057,7 +67054,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2420" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67083,7 +67080,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G2421" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67109,7 +67106,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G2422" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67135,7 +67132,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2423" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67161,7 +67158,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2424" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67187,7 +67184,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2425" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67213,7 +67210,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G2426" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67239,7 +67236,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2427" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67265,7 +67262,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2428" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67291,7 +67288,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2429" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67317,7 +67314,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2430" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67343,7 +67340,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2431" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67369,7 +67366,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2432" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67395,7 +67392,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2433" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67421,7 +67418,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2434" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67447,7 +67444,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2435" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67473,7 +67470,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2436" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67499,7 +67496,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G2437" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67525,7 +67522,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2438" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67551,7 +67548,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2439" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67577,7 +67574,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2440" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67603,7 +67600,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2441" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67629,7 +67626,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2442" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67655,7 +67652,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2443" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67681,7 +67678,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2444" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67707,7 +67704,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2445" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67733,7 +67730,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2446" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67759,7 +67756,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2447" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67785,7 +67782,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2448" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67811,7 +67808,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2449" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67837,7 +67834,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2450" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67863,7 +67860,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2451" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67889,7 +67886,7 @@
         <v>0.5</v>
       </c>
       <c r="G2452" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67915,7 +67912,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G2453" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67941,7 +67938,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2454" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67967,7 +67964,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G2455" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67993,7 +67990,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2456" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68019,7 +68016,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2457" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68045,7 +68042,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2458" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68071,7 +68068,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2459" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68097,7 +68094,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G2460" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68123,7 +68120,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2461" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68149,7 +68146,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G2462" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68175,7 +68172,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2463" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68201,7 +68198,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G2464" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68227,7 +68224,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G2465" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68253,7 +68250,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2466" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68279,7 +68276,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2467" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68305,7 +68302,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2468" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68331,7 +68328,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2469" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68357,7 +68354,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2470" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68383,7 +68380,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2471" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68409,7 +68406,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2472" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68435,7 +68432,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G2473" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68461,7 +68458,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2474" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68487,7 +68484,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2475" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68513,7 +68510,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G2476" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68539,7 +68536,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2477" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68565,7 +68562,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2478" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68591,7 +68588,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2479" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68617,7 +68614,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2480" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68643,7 +68640,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2481" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68669,7 +68666,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G2482" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68695,7 +68692,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2483" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68721,7 +68718,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2484" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68747,7 +68744,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G2485" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68773,7 +68770,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G2486" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68799,7 +68796,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2487" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68825,7 +68822,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2488" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68851,7 +68848,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G2489" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68877,7 +68874,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2490" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68903,7 +68900,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G2491" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68929,7 +68926,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2492" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68955,7 +68952,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2493" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68981,7 +68978,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2494" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69007,7 +69004,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G2495" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69033,7 +69030,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G2496" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69041,7 +69038,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6495717593</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>296171</v>
@@ -69059,9 +69056,35 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G2497" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912615741</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>134673</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>0.46900001168251</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>0.467999994754791</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32635235786438</t>
+    <t xml:space="preserve">0.326352387666702</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844841241837</t>
+    <t xml:space="preserve">0.326844811439514</t>
   </si>
   <si>
     <t xml:space="preserve">0.323679059743881</t>
@@ -56,37 +56,37 @@
     <t xml:space="preserve">0.313056260347366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304966002702713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299760162830353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309538811445236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302503824234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287097275257111</t>
+    <t xml:space="preserve">0.304966062307358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299760192632675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309538781642914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302503764629364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287097245454788</t>
   </si>
   <si>
     <t xml:space="preserve">0.274363905191422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278655260801315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265288770198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260645776987076</t>
+    <t xml:space="preserve">0.278655201196671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265288800001144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260645717382431</t>
   </si>
   <si>
     <t xml:space="preserve">0.270846426486969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269087672233582</t>
+    <t xml:space="preserve">0.269087702035904</t>
   </si>
   <si>
     <t xml:space="preserve">0.272956937551498</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">0.270142942667007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265921920537949</t>
+    <t xml:space="preserve">0.265921980142593</t>
   </si>
   <si>
     <t xml:space="preserve">0.290825724601746</t>
@@ -107,28 +107,28 @@
     <t xml:space="preserve">0.294061869382858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276404023170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273167997598648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262545138597488</t>
+    <t xml:space="preserve">0.276404082775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273167967796326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262545168399811</t>
   </si>
   <si>
     <t xml:space="preserve">0.260293960571289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246927514672279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246224045753479</t>
+    <t xml:space="preserve">0.246927544474602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246224030852318</t>
   </si>
   <si>
     <t xml:space="preserve">0.23975183069706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.240103602409363</t>
+    <t xml:space="preserve">0.240103617310524</t>
   </si>
   <si>
     <t xml:space="preserve">0.271549940109253</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">0.276122659444809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274645298719406</t>
+    <t xml:space="preserve">0.274645328521729</t>
   </si>
   <si>
     <t xml:space="preserve">0.277881443500519</t>
@@ -149,100 +149,100 @@
     <t xml:space="preserve">0.281539589166641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277177959680557</t>
+    <t xml:space="preserve">0.277177900075912</t>
   </si>
   <si>
     <t xml:space="preserve">0.263318985700607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268032491207123</t>
+    <t xml:space="preserve">0.268032431602478</t>
   </si>
   <si>
     <t xml:space="preserve">0.28210237622261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295468807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29335829615593</t>
+    <t xml:space="preserve">0.295468837022781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293358355760574</t>
   </si>
   <si>
     <t xml:space="preserve">0.291740298271179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288644850254059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504242897034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281469255685806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27724826335907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278373837471008</t>
+    <t xml:space="preserve">0.288644909858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504213094711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281469196081161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277248233556747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278373897075653</t>
   </si>
   <si>
     <t xml:space="preserve">0.287026882171631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297368228435516</t>
+    <t xml:space="preserve">0.297368258237839</t>
   </si>
   <si>
     <t xml:space="preserve">0.295820593833923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307217240333557</t>
+    <t xml:space="preserve">0.307217210531235</t>
   </si>
   <si>
     <t xml:space="preserve">0.305669546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313759744167328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320443004369736</t>
+    <t xml:space="preserve">0.313759803771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320442944765091</t>
   </si>
   <si>
     <t xml:space="preserve">0.317417979240417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316573798656464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306161999702454</t>
+    <t xml:space="preserve">0.316573768854141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306161969900131</t>
   </si>
   <si>
     <t xml:space="preserve">0.310945779085159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311438262462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301800340414047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288011759519577</t>
+    <t xml:space="preserve">0.311438202857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301800280809402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288011789321899</t>
   </si>
   <si>
     <t xml:space="preserve">0.288082152605057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280554682016373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281328558921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291880965232849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301378220319748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311649292707443</t>
+    <t xml:space="preserve">0.280554711818695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281328529119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291880995035172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30137825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311649262905121</t>
   </si>
   <si>
     <t xml:space="preserve">0.310242295265198</t>
@@ -251,43 +251,43 @@
     <t xml:space="preserve">0.311508566141129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314533650875092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316644102334976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318684220314026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330573320388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330643653869629</t>
+    <t xml:space="preserve">0.314533591270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316644132137299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318684250116348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330573379993439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330643683671951</t>
   </si>
   <si>
     <t xml:space="preserve">0.334161192178726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3335280418396</t>
+    <t xml:space="preserve">0.333528071641922</t>
   </si>
   <si>
     <t xml:space="preserve">0.330432623624802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327126175165176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323538362979889</t>
+    <t xml:space="preserve">0.327126234769821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323538392782211</t>
   </si>
   <si>
     <t xml:space="preserve">0.318543553352356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319247007369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323116272687912</t>
+    <t xml:space="preserve">0.319247037172318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323116302490234</t>
   </si>
   <si>
     <t xml:space="preserve">0.321005761623383</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">0.324875056743622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323749423027039</t>
+    <t xml:space="preserve">0.323749482631683</t>
   </si>
   <si>
     <t xml:space="preserve">0.325015723705292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321076184511185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326774477958679</t>
+    <t xml:space="preserve">0.32107612490654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326774507761002</t>
   </si>
   <si>
     <t xml:space="preserve">0.331769317388535</t>
@@ -314,37 +314,37 @@
     <t xml:space="preserve">0.344713658094406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342040330171585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338030427694321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352100372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354914397001266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351678252220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350341618061066</t>
+    <t xml:space="preserve">0.342040359973907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338030397891998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352100402116776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354914337396622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351678282022476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350341647863388</t>
   </si>
   <si>
     <t xml:space="preserve">0.343306660652161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343165963888168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341196179389954</t>
+    <t xml:space="preserve">0.343165934085846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341196119785309</t>
   </si>
   <si>
     <t xml:space="preserve">0.340211242437363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337045520544052</t>
+    <t xml:space="preserve">0.33704549074173</t>
   </si>
   <si>
     <t xml:space="preserve">0.323537766933441</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">0.309325903654099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3121537566185</t>
+    <t xml:space="preserve">0.312153726816177</t>
   </si>
   <si>
     <t xml:space="preserve">0.308890849351883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311936259269714</t>
+    <t xml:space="preserve">0.31193619966507</t>
   </si>
   <si>
     <t xml:space="preserve">0.325278013944626</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">0.322232604026794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318607091903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324190378189087</t>
+    <t xml:space="preserve">0.318607121706009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324190318584442</t>
   </si>
   <si>
     <t xml:space="preserve">0.307223081588745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299102008342743</t>
+    <t xml:space="preserve">0.299102038145065</t>
   </si>
   <si>
     <t xml:space="preserve">0.299464553594589</t>
@@ -386,22 +386,22 @@
     <t xml:space="preserve">0.3130963742733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320854842662811</t>
+    <t xml:space="preserve">0.320854902267456</t>
   </si>
   <si>
     <t xml:space="preserve">0.318027049303055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319042176008224</t>
+    <t xml:space="preserve">0.319042146205902</t>
   </si>
   <si>
     <t xml:space="preserve">0.318317085504532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309543401002884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311791211366653</t>
+    <t xml:space="preserve">0.309543430805206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311791181564331</t>
   </si>
   <si>
     <t xml:space="preserve">0.310558557510376</t>
@@ -416,46 +416,46 @@
     <t xml:space="preserve">0.319767266511917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318172037601471</t>
+    <t xml:space="preserve">0.318172067403793</t>
   </si>
   <si>
     <t xml:space="preserve">0.309978485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306715548038483</t>
+    <t xml:space="preserve">0.30671551823616</t>
   </si>
   <si>
     <t xml:space="preserve">0.305627882480621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301784873008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300914734601974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298739433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298014402389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29148855805397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294316381216049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304467767477036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301204770803452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302727520465851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30381515622139</t>
+    <t xml:space="preserve">0.30178490281105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300914764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298739492893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298014372587204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291488498449326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294316411018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304467737674713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301204800605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302727460861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303815126419067</t>
   </si>
   <si>
     <t xml:space="preserve">0.30062472820282</t>
@@ -476,76 +476,76 @@
     <t xml:space="preserve">0.302364945411682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300117194652557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302219957113266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29714423418045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295621573925018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293663799762726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297289282083511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291706055402756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292358607053757</t>
+    <t xml:space="preserve">0.300117164850235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302219927310944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297144263982773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295621603727341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293663829565048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297289341688156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291706025600433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292358666658401</t>
   </si>
   <si>
     <t xml:space="preserve">0.29003831744194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287500441074371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292648673057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287645518779755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295041441917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291561037302017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294533878564835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289313197135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287935584783554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283004939556122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287428021430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282859861850739</t>
+    <t xml:space="preserve">0.287500470876694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292648643255234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287645548582077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295041501522064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291561007499695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294533938169479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28931325674057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287935554981232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283004879951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287427991628647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282859891653061</t>
   </si>
   <si>
     <t xml:space="preserve">0.275826454162598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279161900281906</t>
+    <t xml:space="preserve">0.279161870479584</t>
   </si>
   <si>
     <t xml:space="preserve">0.26973569393158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273288637399673</t>
+    <t xml:space="preserve">0.273288607597351</t>
   </si>
   <si>
     <t xml:space="preserve">0.279524445533752</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">0.282134771347046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287137925624847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292866200208664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301422297954559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295839101076126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296564161777496</t>
+    <t xml:space="preserve">0.28713795542717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292866230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301422327756882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295839071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296564221382141</t>
   </si>
   <si>
     <t xml:space="preserve">0.300262182950974</t>
@@ -581,25 +581,25 @@
     <t xml:space="preserve">0.297071754932404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292938768863678</t>
+    <t xml:space="preserve">0.292938739061356</t>
   </si>
   <si>
     <t xml:space="preserve">0.298811972141266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296056628227234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31019601225853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306425511837006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302509993314743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306062936782837</t>
+    <t xml:space="preserve">0.296056658029556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310195982456207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306425452232361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302509963512421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306062966585159</t>
   </si>
   <si>
     <t xml:space="preserve">0.307078093290329</t>
@@ -608,22 +608,22 @@
     <t xml:space="preserve">0.301639884710312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294098883867264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283077418804169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287863075733185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289603263139725</t>
+    <t xml:space="preserve">0.294098913669586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283077389001846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287863045930862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289603292942047</t>
   </si>
   <si>
     <t xml:space="preserve">0.285615235567093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2839475274086</t>
+    <t xml:space="preserve">0.283947557210922</t>
   </si>
   <si>
     <t xml:space="preserve">0.288805663585663</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">0.290835976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283512443304062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281409651041031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280684620141983</t>
+    <t xml:space="preserve">0.283512473106384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281409680843353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280684590339661</t>
   </si>
   <si>
     <t xml:space="preserve">0.279016882181168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796200752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291416019201279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295113980770111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29054594039917</t>
+    <t xml:space="preserve">0.273796170949936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291415989398956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295114010572433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290545910596848</t>
   </si>
   <si>
     <t xml:space="preserve">0.288588136434555</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">0.296491682529449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303597629070282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309615939855576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307440608739853</t>
+    <t xml:space="preserve">0.303597688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309615910053253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307440638542175</t>
   </si>
   <si>
     <t xml:space="preserve">0.319187194108963</t>
@@ -692,10 +692,10 @@
     <t xml:space="preserve">0.331513822078705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331368774175644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345000594854355</t>
+    <t xml:space="preserve">0.331368803977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345000624656677</t>
   </si>
   <si>
     <t xml:space="preserve">0.349786221981049</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">0.358342349529266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354209333658218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34964120388031</t>
+    <t xml:space="preserve">0.354209363460541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349641174077988</t>
   </si>
   <si>
     <t xml:space="preserve">0.352396547794342</t>
@@ -716,31 +716,31 @@
     <t xml:space="preserve">0.355296969413757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359429985284805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352686613798141</t>
+    <t xml:space="preserve">0.359430015087128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352686643600464</t>
   </si>
   <si>
     <t xml:space="preserve">0.346885830163956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343187898397446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346160769462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346595793962479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34645077586174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344348013401031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350221306085587</t>
+    <t xml:space="preserve">0.343187868595123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346160739660263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346595764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346450805664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344348043203354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350221335887909</t>
   </si>
   <si>
     <t xml:space="preserve">0.350946366786957</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">0.388288795948029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397715032100677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379950225353241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382125496864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374874591827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37342432141304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377412438392639</t>
+    <t xml:space="preserve">0.397715061903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379950195550919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382125526666641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37487456202507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373424381017685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377412408590317</t>
   </si>
   <si>
     <t xml:space="preserve">0.373061805963516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369798868894577</t>
+    <t xml:space="preserve">0.369798839092255</t>
   </si>
   <si>
     <t xml:space="preserve">0.383575648069382</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">0.369436323642731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369073748588562</t>
+    <t xml:space="preserve">0.369073778390884</t>
   </si>
   <si>
     <t xml:space="preserve">0.35819736123085</t>
@@ -788,61 +788,61 @@
     <t xml:space="preserve">0.358052343130112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37704986333847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412579536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382488042116165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400615483522415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394452184438705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385751008987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393727034330368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390464127063751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384300798177719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391551822423935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387563705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390826642513275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395177185535431</t>
+    <t xml:space="preserve">0.377049803733826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412579476833344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382488012313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40061542391777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394452154636383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385750979185104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39372706413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390464097261429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384300768375397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391551792621613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387563735246658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390826612710953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395177215337753</t>
   </si>
   <si>
     <t xml:space="preserve">0.393364518880844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397352457046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398802667856216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395539790391922</t>
+    <t xml:space="preserve">0.397352486848831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398802697658539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3955397605896</t>
   </si>
   <si>
     <t xml:space="preserve">0.396627396345139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398440182209015</t>
+    <t xml:space="preserve">0.39844012260437</t>
   </si>
   <si>
     <t xml:space="preserve">0.395902305841446</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">0.398077607154846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401703089475632</t>
+    <t xml:space="preserve">0.401703119277954</t>
   </si>
   <si>
     <t xml:space="preserve">0.392276853322983</t>
@@ -872,16 +872,16 @@
     <t xml:space="preserve">0.394089609384537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38937646150589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38176292181015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381037831306458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386838674545288</t>
+    <t xml:space="preserve">0.389376491308212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381762951612473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381037801504135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386838614940643</t>
   </si>
   <si>
     <t xml:space="preserve">0.388651371002197</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">0.391189217567444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392639398574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425631284713745</t>
+    <t xml:space="preserve">0.392639368772507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425631254911423</t>
   </si>
   <si>
     <t xml:space="preserve">0.419105410575867</t>
@@ -905,37 +905,37 @@
     <t xml:space="preserve">0.445208877325058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435057491064072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442308515310287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432612001895905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413591980934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408370822668076</t>
+    <t xml:space="preserve">0.435057461261749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442308485507965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43261194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413591951131821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408370792865753</t>
   </si>
   <si>
     <t xml:space="preserve">0.406879037618637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402776747941971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399047285318375</t>
+    <t xml:space="preserve">0.402776718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399047315120697</t>
   </si>
   <si>
     <t xml:space="preserve">0.400539040565491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395317852497101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396809637546539</t>
+    <t xml:space="preserve">0.395317822694778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396809607744217</t>
   </si>
   <si>
     <t xml:space="preserve">0.39606374502182</t>
@@ -944,76 +944,76 @@
     <t xml:space="preserve">0.393080204725266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38860496878624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387859046459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379654288291931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381146043539047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383010774850845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387486100196838</t>
+    <t xml:space="preserve">0.388604938983917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387858986854553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379654318094254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38114607334137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383010804653168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387486070394516</t>
   </si>
   <si>
     <t xml:space="preserve">0.384875476360321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383756667375565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386740177869797</t>
+    <t xml:space="preserve">0.383756697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386740207672119</t>
   </si>
   <si>
     <t xml:space="preserve">0.390096634626389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394944906234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403522580862045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410235464572906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407251954078674</t>
+    <t xml:space="preserve">0.394944936037064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403522610664368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410235494375229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407251924276352</t>
   </si>
   <si>
     <t xml:space="preserve">0.407624959945679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408743679523468</t>
+    <t xml:space="preserve">0.40874370932579</t>
   </si>
   <si>
     <t xml:space="preserve">0.406506061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400911957025528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394199043512344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398674309253693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39084255695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392334312200546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38823202252388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387113153934479</t>
+    <t xml:space="preserve">0.400912016630173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394199013710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398674339056015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390842527151108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392334342002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388231992721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387113183736801</t>
   </si>
   <si>
     <t xml:space="preserve">0.391588389873505</t>
@@ -1022,46 +1022,46 @@
     <t xml:space="preserve">0.389350831508636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385621428489685</t>
+    <t xml:space="preserve">0.385621398687363</t>
   </si>
   <si>
     <t xml:space="preserve">0.380773156881332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385248452425003</t>
+    <t xml:space="preserve">0.385248422622681</t>
   </si>
   <si>
     <t xml:space="preserve">0.383383721113205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397928476333618</t>
+    <t xml:space="preserve">0.397928446531296</t>
   </si>
   <si>
     <t xml:space="preserve">0.409489631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410981357097626</t>
+    <t xml:space="preserve">0.410981386899948</t>
   </si>
   <si>
     <t xml:space="preserve">0.41433784365654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415083765983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416575521230698</t>
+    <t xml:space="preserve">0.415083795785904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416575491428375</t>
   </si>
   <si>
     <t xml:space="preserve">0.415829628705978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424034297466278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439324975013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866139173508</t>
+    <t xml:space="preserve">0.4240343272686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439324945211411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866079568863</t>
   </si>
   <si>
     <t xml:space="preserve">0.428882569074631</t>
@@ -1070,25 +1070,25 @@
     <t xml:space="preserve">0.420304894447327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42179673910141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428509652614594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454988539218903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445291966199875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444546073675156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440443813800812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449767291545868</t>
+    <t xml:space="preserve">0.421796709299088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428509622812271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454988479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44529202580452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444546163082123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440443783998489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44976732134819</t>
   </si>
   <si>
     <t xml:space="preserve">0.459463715553284</t>
@@ -1097,115 +1097,115 @@
     <t xml:space="preserve">0.460955530405045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469533145427704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466549694538116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474008470773697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474754393100739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348408222198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485942631959915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482586115598679</t>
+    <t xml:space="preserve">0.469533175230026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466549634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474008440971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474754333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480348467826843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485942661762238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482586145401001</t>
   </si>
   <si>
     <t xml:space="preserve">0.485569685697556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50943785905838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511302590370178</t>
+    <t xml:space="preserve">0.50943797826767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511302649974823</t>
   </si>
   <si>
     <t xml:space="preserve">0.521744966506958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512794375419617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51950740814209</t>
+    <t xml:space="preserve">0.512794435024261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5195072889328</t>
   </si>
   <si>
     <t xml:space="preserve">0.511675536632538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506081342697144</t>
+    <t xml:space="preserve">0.506081402301788</t>
   </si>
   <si>
     <t xml:space="preserve">0.501233220100403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502352058887482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495266050100327</t>
+    <t xml:space="preserve">0.502351999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495266079902649</t>
   </si>
   <si>
     <t xml:space="preserve">0.491536736488342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477737903594971</t>
+    <t xml:space="preserve">0.477737873792648</t>
   </si>
   <si>
     <t xml:space="preserve">0.478483766317368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481094360351562</t>
+    <t xml:space="preserve">0.48109433054924</t>
   </si>
   <si>
     <t xml:space="preserve">0.492282599210739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499741464853287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49377429485321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495639085769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507946133613586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500114381313324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493028491735458</t>
+    <t xml:space="preserve">0.499741435050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493774354457855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495639055967331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507946074008942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500114321708679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493028521537781</t>
   </si>
   <si>
     <t xml:space="preserve">0.508692026138306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503470897674561</t>
+    <t xml:space="preserve">0.503470838069916</t>
   </si>
   <si>
     <t xml:space="preserve">0.508319079875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507200241088867</t>
+    <t xml:space="preserve">0.507200300693512</t>
   </si>
   <si>
     <t xml:space="preserve">0.510183811187744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513167381286621</t>
+    <t xml:space="preserve">0.513167321681976</t>
   </si>
   <si>
     <t xml:space="preserve">0.500860273838043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503097832202911</t>
+    <t xml:space="preserve">0.503097951412201</t>
   </si>
   <si>
     <t xml:space="preserve">0.502725005149841</t>
@@ -1214,22 +1214,22 @@
     <t xml:space="preserve">0.501606166362762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498249620199203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510929703712463</t>
+    <t xml:space="preserve">0.498249650001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510929644107819</t>
   </si>
   <si>
     <t xml:space="preserve">0.531068563461304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557920277118683</t>
+    <t xml:space="preserve">0.557920336723328</t>
   </si>
   <si>
     <t xml:space="preserve">0.554936826229095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559412002563477</t>
+    <t xml:space="preserve">0.559412062168121</t>
   </si>
   <si>
     <t xml:space="preserve">0.56537914276123</t>
@@ -1238,25 +1238,25 @@
     <t xml:space="preserve">0.593722641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574329733848572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576567351818085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577313244342804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583280265331268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591484904289246</t>
+    <t xml:space="preserve">0.574329674243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576567411422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577313184738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583280324935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591485023498535</t>
   </si>
   <si>
     <t xml:space="preserve">0.585517942905426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575075626373291</t>
+    <t xml:space="preserve">0.575075566768646</t>
   </si>
   <si>
     <t xml:space="preserve">0.61236971616745</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">0.551953196525574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548223793506622</t>
+    <t xml:space="preserve">0.548223853111267</t>
   </si>
   <si>
     <t xml:space="preserve">0.534797966480255</t>
@@ -1277,61 +1277,61 @@
     <t xml:space="preserve">0.521372079849243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505708575248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528084874153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54524028301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522863686084747</t>
+    <t xml:space="preserve">0.505708515644073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528084933757782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545240223407745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522863745689392</t>
   </si>
   <si>
     <t xml:space="preserve">0.517642617225647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532560229301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531814396381378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523609697818756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516150891780853</t>
+    <t xml:space="preserve">0.532560288906097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531814336776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523609638214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516150832176208</t>
   </si>
   <si>
     <t xml:space="preserve">0.512421369552612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519134402275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498995542526245</t>
+    <t xml:space="preserve">0.519134342670441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498995572328568</t>
   </si>
   <si>
     <t xml:space="preserve">0.46319317817688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469906151294708</t>
+    <t xml:space="preserve">0.469906121492386</t>
   </si>
   <si>
     <t xml:space="preserve">0.476619064807892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477364927530289</t>
+    <t xml:space="preserve">0.477364987134933</t>
   </si>
   <si>
     <t xml:space="preserve">0.494520217180252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490044921636581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47885674238205</t>
+    <t xml:space="preserve">0.490044981241226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478856712579727</t>
   </si>
   <si>
     <t xml:space="preserve">0.478110790252686</t>
@@ -1340,28 +1340,28 @@
     <t xml:space="preserve">0.468414396047592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481840252876282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484077930450439</t>
+    <t xml:space="preserve">0.481840312480927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484077900648117</t>
   </si>
   <si>
     <t xml:space="preserve">0.475127309560776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473635524511337</t>
+    <t xml:space="preserve">0.47363555431366</t>
   </si>
   <si>
     <t xml:space="preserve">0.474381387233734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484823793172836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487061500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48333203792572</t>
+    <t xml:space="preserve">0.484823822975159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487061440944672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483332067728043</t>
   </si>
   <si>
     <t xml:space="preserve">0.504216730594635</t>
@@ -1370,43 +1370,43 @@
     <t xml:space="preserve">0.504962623119354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496757864952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497503787279129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486315548419952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500487387180328</t>
+    <t xml:space="preserve">0.496757954359055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497503817081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48631551861763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500487327575684</t>
   </si>
   <si>
     <t xml:space="preserve">0.454242616891861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46543088555336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452004909515381</t>
+    <t xml:space="preserve">0.465430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452004939317703</t>
   </si>
   <si>
     <t xml:space="preserve">0.457226067781448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458717823028564</t>
+    <t xml:space="preserve">0.458717882633209</t>
   </si>
   <si>
     <t xml:space="preserve">0.462447255849838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455734401941299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457972049713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485727876424789</t>
+    <t xml:space="preserve">0.455734372138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457972019910812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485727906227112</t>
   </si>
   <si>
     <t xml:space="preserve">0.484185934066772</t>
@@ -1415,31 +1415,31 @@
     <t xml:space="preserve">0.474933922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469536989927292</t>
+    <t xml:space="preserve">0.469536930322647</t>
   </si>
   <si>
     <t xml:space="preserve">0.464910984039307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461055964231491</t>
+    <t xml:space="preserve">0.461055904626846</t>
   </si>
   <si>
     <t xml:space="preserve">0.463368952274323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459513992071152</t>
+    <t xml:space="preserve">0.459514021873474</t>
   </si>
   <si>
     <t xml:space="preserve">0.45797199010849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458743005990982</t>
+    <t xml:space="preserve">0.458743035793304</t>
   </si>
   <si>
     <t xml:space="preserve">0.447949022054672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451032996177673</t>
+    <t xml:space="preserve">0.451033055782318</t>
   </si>
   <si>
     <t xml:space="preserve">0.454887986183167</t>
@@ -1448,22 +1448,22 @@
     <t xml:space="preserve">0.44640702009201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441781044006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443323016166687</t>
+    <t xml:space="preserve">0.44178107380867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443323045969009</t>
   </si>
   <si>
     <t xml:space="preserve">0.494208812713623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474162936210632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481101840734482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489582866430283</t>
+    <t xml:space="preserve">0.474162876605988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481101930141449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48958283662796</t>
   </si>
   <si>
     <t xml:space="preserve">0.476475894451141</t>
@@ -1475,28 +1475,28 @@
     <t xml:space="preserve">0.461826920509338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456430017948151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454117029905319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466453015804291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467224031686783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439468055963516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442552030086517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452575027942657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453346073627472</t>
+    <t xml:space="preserve">0.456429958343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454117000102997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466452986001968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467223972082138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439468085765839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44255205988884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45257505774498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453345984220505</t>
   </si>
   <si>
     <t xml:space="preserve">0.4410100877285</t>
@@ -1514,19 +1514,19 @@
     <t xml:space="preserve">0.431758135557175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43561315536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444865047931671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284948348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45180407166481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470308005809784</t>
+    <t xml:space="preserve">0.435613095760345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444865077733994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284978151321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451804101467133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470307946205139</t>
   </si>
   <si>
     <t xml:space="preserve">0.471849918365479</t>
@@ -1547,76 +1547,76 @@
     <t xml:space="preserve">0.450262039899826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449491053819656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437155097723007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440239071846008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426361083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427903085947037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407086193561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406315237283707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4101702272892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40400218963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407857179641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410941183567047</t>
+    <t xml:space="preserve">0.449491083621979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437155067920685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440239012241364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42636114358902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427903115749359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407086223363876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406315207481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410170197486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404002219438553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407857209444046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41094121336937</t>
   </si>
   <si>
     <t xml:space="preserve">0.400147289037704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396292269229889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390895307064056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390124261379242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381643354892731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383185356855392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387811303138733</t>
+    <t xml:space="preserve">0.396292239427567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390895336866379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390124291181564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381643295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38318532705307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387811332941055</t>
   </si>
   <si>
     <t xml:space="preserve">0.388582289218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394750267267227</t>
+    <t xml:space="preserve">0.39475029706955</t>
   </si>
   <si>
     <t xml:space="preserve">0.397063255310059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38935324549675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387040287256241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385498315095901</t>
+    <t xml:space="preserve">0.389353305101395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387040317058563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385498285293579</t>
   </si>
   <si>
     <t xml:space="preserve">0.375475347042084</t>
@@ -1631,28 +1631,28 @@
     <t xml:space="preserve">0.345406502485275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348875969648361</t>
+    <t xml:space="preserve">0.348875939846039</t>
   </si>
   <si>
     <t xml:space="preserve">0.36699441075325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372391402721405</t>
+    <t xml:space="preserve">0.372391372919083</t>
   </si>
   <si>
     <t xml:space="preserve">0.36776539683342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162358999252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370078355073929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370463877916336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369692862033844</t>
+    <t xml:space="preserve">0.37316232919693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370078384876251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370463937520981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369692891836166</t>
   </si>
   <si>
     <t xml:space="preserve">0.365837901830673</t>
@@ -1661,16 +1661,16 @@
     <t xml:space="preserve">0.371620357036591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368536382913589</t>
+    <t xml:space="preserve">0.368536353111267</t>
   </si>
   <si>
     <t xml:space="preserve">0.368921875953674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37894481420517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383570820093155</t>
+    <t xml:space="preserve">0.378944844007492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383570849895477</t>
   </si>
   <si>
     <t xml:space="preserve">0.377017349004745</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">0.399376273155212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416338235139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424048155546188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424819111824036</t>
+    <t xml:space="preserve">0.416338205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424048185348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424819141626358</t>
   </si>
   <si>
     <t xml:space="preserve">0.417109221220016</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">0.422506123781204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421735137701035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420964151620865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408628165721893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400918275117874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404773205518723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405544251203537</t>
+    <t xml:space="preserve">0.421735107898712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420964121818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408628195524216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400918245315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4047731757164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405544221401215</t>
   </si>
   <si>
     <t xml:space="preserve">0.411712169647217</t>
@@ -1721,19 +1721,19 @@
     <t xml:space="preserve">0.412483215332031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423277139663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425590097904205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419422209262848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430216163396835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427132099866867</t>
+    <t xml:space="preserve">0.423277169466019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425590127706528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419422179460526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430216133594513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427132189273834</t>
   </si>
   <si>
     <t xml:space="preserve">0.414025187492371</t>
@@ -1745,13 +1745,13 @@
     <t xml:space="preserve">0.413254201412201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409399211406708</t>
+    <t xml:space="preserve">0.409399181604385</t>
   </si>
   <si>
     <t xml:space="preserve">0.395521283149719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393208265304565</t>
+    <t xml:space="preserve">0.393208235502243</t>
   </si>
   <si>
     <t xml:space="preserve">0.392437279224396</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">0.391666293144226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393979221582413</t>
+    <t xml:space="preserve">0.393979251384735</t>
   </si>
   <si>
     <t xml:space="preserve">0.398605287075043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403231203556061</t>
+    <t xml:space="preserve">0.403231233358383</t>
   </si>
   <si>
     <t xml:space="preserve">0.411275923252106</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">0.410471051931381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409666270017624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415300160646439</t>
+    <t xml:space="preserve">0.409666240215302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415300130844116</t>
   </si>
   <si>
     <t xml:space="preserve">0.412885636091232</t>
@@ -1793,19 +1793,19 @@
     <t xml:space="preserve">0.401215374469757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404032289981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397995978593826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403227478265762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398398399353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400008082389832</t>
+    <t xml:space="preserve">0.404032319784164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397996008396149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40322744846344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398398369550705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400008112192154</t>
   </si>
   <si>
     <t xml:space="preserve">0.40242263674736</t>
@@ -1814,46 +1814,46 @@
     <t xml:space="preserve">0.400410532951355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395983874797821</t>
+    <t xml:space="preserve">0.395983904600143</t>
   </si>
   <si>
     <t xml:space="preserve">0.39960566163063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418519526720047</t>
+    <t xml:space="preserve">0.418519556522369</t>
   </si>
   <si>
     <t xml:space="preserve">0.417714715003967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416909843683243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404837191104889</t>
+    <t xml:space="preserve">0.416909873485565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404837220907211</t>
   </si>
   <si>
     <t xml:space="preserve">0.401617795228958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40725165605545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408056557178497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405642032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397593557834625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391154795885086</t>
+    <t xml:space="preserve">0.407251685857773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40805658698082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405642002820969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397593587636948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391154766082764</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446874141693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426567941904068</t>
+    <t xml:space="preserve">0.42656797170639</t>
   </si>
   <si>
     <t xml:space="preserve">0.433811604976654</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">0.424153447151184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432201951742172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425763159990311</t>
+    <t xml:space="preserve">0.43220192193985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425763130187988</t>
   </si>
   <si>
     <t xml:space="preserve">0.428177684545517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43300673365593</t>
+    <t xml:space="preserve">0.433006763458252</t>
   </si>
   <si>
     <t xml:space="preserve">0.429787337779999</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">0.428982526063919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437030971050262</t>
+    <t xml:space="preserve">0.437031000852585</t>
   </si>
   <si>
     <t xml:space="preserve">0.434616476297379</t>
@@ -1892,40 +1892,40 @@
     <t xml:space="preserve">0.430592238903046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4426648914814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458761811256409</t>
+    <t xml:space="preserve">0.442664921283722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458761781454086</t>
   </si>
   <si>
     <t xml:space="preserve">0.46681022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473249018192291</t>
+    <t xml:space="preserve">0.473248988389969</t>
   </si>
   <si>
     <t xml:space="preserve">0.476468354463577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478882938623428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47566357254982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481297433376312</t>
+    <t xml:space="preserve">0.478882998228073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475663542747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48129740357399</t>
   </si>
   <si>
     <t xml:space="preserve">0.478078067302704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474858641624451</t>
+    <t xml:space="preserve">0.474858671426773</t>
   </si>
   <si>
     <t xml:space="preserve">0.471639394760132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472444176673889</t>
+    <t xml:space="preserve">0.472444206476212</t>
   </si>
   <si>
     <t xml:space="preserve">0.486126571893692</t>
@@ -1934,31 +1934,31 @@
     <t xml:space="preserve">0.48049259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494979828596115</t>
+    <t xml:space="preserve">0.494979798793793</t>
   </si>
   <si>
     <t xml:space="preserve">0.511881530284882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513491272926331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520734906196594</t>
+    <t xml:space="preserve">0.513491332530975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520734965801239</t>
   </si>
   <si>
     <t xml:space="preserve">0.535222113132477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53441721200943</t>
+    <t xml:space="preserve">0.534417271614075</t>
   </si>
   <si>
     <t xml:space="preserve">0.523149430751801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51510089635849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516710698604584</t>
+    <t xml:space="preserve">0.51510101556778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516710638999939</t>
   </si>
   <si>
     <t xml:space="preserve">0.522344589233398</t>
@@ -1970,34 +1970,34 @@
     <t xml:space="preserve">0.555343210697174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551318943500519</t>
+    <t xml:space="preserve">0.551319003105164</t>
   </si>
   <si>
     <t xml:space="preserve">0.557757794857025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571440100669861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561782002449036</t>
+    <t xml:space="preserve">0.571440160274506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56178206205368</t>
   </si>
   <si>
     <t xml:space="preserve">0.560977220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552928686141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554538369178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592366099357605</t>
+    <t xml:space="preserve">0.552928626537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554538428783417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59236615896225</t>
   </si>
   <si>
     <t xml:space="preserve">0.59639036655426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599609673023224</t>
+    <t xml:space="preserve">0.599609792232513</t>
   </si>
   <si>
     <t xml:space="preserve">0.611682415008545</t>
@@ -2012,31 +2012,31 @@
     <t xml:space="preserve">0.614901781082153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600414574146271</t>
+    <t xml:space="preserve">0.600414514541626</t>
   </si>
   <si>
     <t xml:space="preserve">0.608462989330292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593975841999054</t>
+    <t xml:space="preserve">0.593975722789764</t>
   </si>
   <si>
     <t xml:space="preserve">0.590756475925446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595585465431213</t>
+    <t xml:space="preserve">0.595585525035858</t>
   </si>
   <si>
     <t xml:space="preserve">0.609267950057983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614096999168396</t>
+    <t xml:space="preserve">0.614096939563751</t>
   </si>
   <si>
     <t xml:space="preserve">0.60604852437973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593171000480652</t>
+    <t xml:space="preserve">0.593170940876007</t>
   </si>
   <si>
     <t xml:space="preserve">0.598804950714111</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">0.594780683517456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603633940219879</t>
+    <t xml:space="preserve">0.603633880615234</t>
   </si>
   <si>
     <t xml:space="preserve">0.610072791576385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.59799998998642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630193889141083</t>
+    <t xml:space="preserve">0.598000049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630193829536438</t>
   </si>
   <si>
     <t xml:space="preserve">0.631803572177887</t>
@@ -2072,16 +2072,16 @@
     <t xml:space="preserve">0.65997314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689752399921417</t>
+    <t xml:space="preserve">0.689752340316772</t>
   </si>
   <si>
     <t xml:space="preserve">0.684118509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661582767963409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58834183216095</t>
+    <t xml:space="preserve">0.661582887172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588341891765594</t>
   </si>
   <si>
     <t xml:space="preserve">0.581098318099976</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">0.572245001792908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540856003761292</t>
+    <t xml:space="preserve">0.540856063365936</t>
   </si>
   <si>
     <t xml:space="preserve">0.543270587921143</t>
@@ -2102,43 +2102,43 @@
     <t xml:space="preserve">0.526368796825409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490955650806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439445495605469</t>
+    <t xml:space="preserve">0.490955621004105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439445465803146</t>
   </si>
   <si>
     <t xml:space="preserve">0.398800820112228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381496667861938</t>
+    <t xml:space="preserve">0.381496638059616</t>
   </si>
   <si>
     <t xml:space="preserve">0.323145359754562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348095595836639</t>
+    <t xml:space="preserve">0.348095625638962</t>
   </si>
   <si>
     <t xml:space="preserve">0.303829073905945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282500714063644</t>
+    <t xml:space="preserve">0.282500684261322</t>
   </si>
   <si>
     <t xml:space="preserve">0.288939476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291353940963745</t>
+    <t xml:space="preserve">0.29135400056839</t>
   </si>
   <si>
     <t xml:space="preserve">0.304633975028992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308255732059479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343668907880783</t>
+    <t xml:space="preserve">0.308255761861801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343668937683105</t>
   </si>
   <si>
     <t xml:space="preserve">0.358961015939713</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">0.355741620063782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373850613832474</t>
+    <t xml:space="preserve">0.373850643634796</t>
   </si>
   <si>
     <t xml:space="preserve">0.391959637403488</t>
@@ -2159,22 +2159,22 @@
     <t xml:space="preserve">0.37908211350441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375057905912399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384716033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386325746774673</t>
+    <t xml:space="preserve">0.375057876110077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384716004133224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386325716972351</t>
   </si>
   <si>
     <t xml:space="preserve">0.374253034591675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362180411815643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351717382669449</t>
+    <t xml:space="preserve">0.362180352210999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351717412471771</t>
   </si>
   <si>
     <t xml:space="preserve">0.353327065706253</t>
@@ -2192,19 +2192,19 @@
     <t xml:space="preserve">0.338034987449646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339644730091095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341254383325577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346083492040634</t>
+    <t xml:space="preserve">0.339644700288773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341254413127899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346083462238312</t>
   </si>
   <si>
     <t xml:space="preserve">0.350912541151047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348497986793518</t>
+    <t xml:space="preserve">0.34849801659584</t>
   </si>
   <si>
     <t xml:space="preserve">0.342864096164703</t>
@@ -2213,22 +2213,22 @@
     <t xml:space="preserve">0.345278590917587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336425334215164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324352622032166</t>
+    <t xml:space="preserve">0.336425304412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324352651834488</t>
   </si>
   <si>
     <t xml:space="preserve">0.329986572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326767146587372</t>
+    <t xml:space="preserve">0.326767176389694</t>
   </si>
   <si>
     <t xml:space="preserve">0.321938127279282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331596255302429</t>
+    <t xml:space="preserve">0.331596225500107</t>
   </si>
   <si>
     <t xml:space="preserve">0.340449541807175</t>
@@ -2237,16 +2237,16 @@
     <t xml:space="preserve">0.347693175077438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352522253990173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354936748743057</t>
+    <t xml:space="preserve">0.352522224187851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35493677854538</t>
   </si>
   <si>
     <t xml:space="preserve">0.369423985481262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382301479578018</t>
+    <t xml:space="preserve">0.382301509380341</t>
   </si>
   <si>
     <t xml:space="preserve">0.379886984825134</t>
@@ -2258,34 +2258,34 @@
     <t xml:space="preserve">0.354131907224655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330791383981705</t>
+    <t xml:space="preserve">0.330791443586349</t>
   </si>
   <si>
     <t xml:space="preserve">0.356546461582184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357351303100586</t>
+    <t xml:space="preserve">0.357351273298264</t>
   </si>
   <si>
     <t xml:space="preserve">0.350107669830322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346888273954391</t>
+    <t xml:space="preserve">0.346888303756714</t>
   </si>
   <si>
     <t xml:space="preserve">0.342059254646301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337230116128922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328376859426498</t>
+    <t xml:space="preserve">0.337230175733566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328376829624176</t>
   </si>
   <si>
     <t xml:space="preserve">0.33562046289444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370228856801987</t>
+    <t xml:space="preserve">0.370228826999664</t>
   </si>
   <si>
     <t xml:space="preserve">0.358156144618988</t>
@@ -2294,40 +2294,40 @@
     <t xml:space="preserve">0.363790035247803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420129239559174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424958258867264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437835872173309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444274544715881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445884257555008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482907205820084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560172319412231</t>
+    <t xml:space="preserve">0.420129269361496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424958288669586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437835842370987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444274574518204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445884346961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482907176017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560172259807587</t>
   </si>
   <si>
     <t xml:space="preserve">0.527978479862213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521539688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529588162899017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519930124282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507052600383759</t>
+    <t xml:space="preserve">0.521539747714996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529588222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519930064678192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507052540779114</t>
   </si>
   <si>
     <t xml:space="preserve">0.500613749027252</t>
@@ -2336,22 +2336,22 @@
     <t xml:space="preserve">0.494175016880035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502223372459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537636578083038</t>
+    <t xml:space="preserve">0.502223432064056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537636637687683</t>
   </si>
   <si>
     <t xml:space="preserve">0.524759113788605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510271847248077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49900409579277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492565304040909</t>
+    <t xml:space="preserve">0.510271906852722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499004065990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492565274238586</t>
   </si>
   <si>
     <t xml:space="preserve">0.487736225128174</t>
@@ -2360,22 +2360,22 @@
     <t xml:space="preserve">0.484516859054565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447493970394135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431397050619125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449103713035583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436226159334183</t>
+    <t xml:space="preserve">0.447493940591812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431397080421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449103683233261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436226189136505</t>
   </si>
   <si>
     <t xml:space="preserve">0.393569320440292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378277271986008</t>
+    <t xml:space="preserve">0.37827730178833</t>
   </si>
   <si>
     <t xml:space="preserve">0.375862747430801</t>
@@ -2390,76 +2390,76 @@
     <t xml:space="preserve">0.376667588949203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421738892793655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42334857583046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441055148839951</t>
+    <t xml:space="preserve">0.421738922595978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423348605632782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441055178642273</t>
   </si>
   <si>
     <t xml:space="preserve">0.50544285774231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468419939279556</t>
+    <t xml:space="preserve">0.468419969081879</t>
   </si>
   <si>
     <t xml:space="preserve">0.461981207132339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465200543403625</t>
+    <t xml:space="preserve">0.465200573205948</t>
   </si>
   <si>
     <t xml:space="preserve">0.45232304930687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455542415380478</t>
+    <t xml:space="preserve">0.4555424451828</t>
   </si>
   <si>
     <t xml:space="preserve">0.450713366270065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460371494293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457152038812637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453932732343674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47968778014183</t>
+    <t xml:space="preserve">0.460371524095535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457152098417282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453932762145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479687809944153</t>
   </si>
   <si>
     <t xml:space="preserve">0.495784670114517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489345878362656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547294735908508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565001428127289</t>
+    <t xml:space="preserve">0.489345908164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547294795513153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565001368522644</t>
   </si>
   <si>
     <t xml:space="preserve">0.576269209384918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575464308261871</t>
+    <t xml:space="preserve">0.575464427471161</t>
   </si>
   <si>
     <t xml:space="preserve">0.569830417633057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549709320068359</t>
+    <t xml:space="preserve">0.549709379673004</t>
   </si>
   <si>
     <t xml:space="preserve">0.56741589307785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545685112476349</t>
+    <t xml:space="preserve">0.545685052871704</t>
   </si>
   <si>
     <t xml:space="preserve">0.558562636375427</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">0.544075429439545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531197905540466</t>
+    <t xml:space="preserve">0.531197845935822</t>
   </si>
   <si>
     <t xml:space="preserve">0.559367418289185</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">0.581903100013733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579488635063171</t>
+    <t xml:space="preserve">0.579488575458527</t>
   </si>
   <si>
     <t xml:space="preserve">0.544880270957947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55212390422821</t>
+    <t xml:space="preserve">0.552123785018921</t>
   </si>
   <si>
     <t xml:space="preserve">0.548099637031555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548904418945312</t>
+    <t xml:space="preserve">0.548904478549957</t>
   </si>
   <si>
     <t xml:space="preserve">0.553733587265015</t>
@@ -2501,16 +2501,16 @@
     <t xml:space="preserve">0.582058250904083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581226766109467</t>
+    <t xml:space="preserve">0.581226706504822</t>
   </si>
   <si>
     <t xml:space="preserve">0.573743164539337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567091047763824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574708938599</t>
+    <t xml:space="preserve">0.567091107368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574589729309</t>
   </si>
   <si>
     <t xml:space="preserve">0.57291167974472</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">0.557944476604462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558775961399078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540482640266418</t>
+    <t xml:space="preserve">0.558776021003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540482699871063</t>
   </si>
   <si>
     <t xml:space="preserve">0.544640243053436</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">0.542977273464203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530504584312439</t>
+    <t xml:space="preserve">0.530504524707794</t>
   </si>
   <si>
     <t xml:space="preserve">0.531336069107056</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">0.516368865966797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511379837989807</t>
+    <t xml:space="preserve">0.511379778385162</t>
   </si>
   <si>
     <t xml:space="preserve">0.505559206008911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508885264396667</t>
+    <t xml:space="preserve">0.508885204792023</t>
   </si>
   <si>
     <t xml:space="preserve">0.502233147621155</t>
@@ -2561,10 +2561,10 @@
     <t xml:space="preserve">0.515537321567535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498907148838043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493918061256409</t>
+    <t xml:space="preserve">0.498907119035721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493918031454086</t>
   </si>
   <si>
     <t xml:space="preserve">0.494749546051025</t>
@@ -2573,34 +2573,34 @@
     <t xml:space="preserve">0.500570118427277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48393988609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465646654367447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466478139162064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461489111185074</t>
+    <t xml:space="preserve">0.483939915895462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465646624565125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466478109359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461489081382751</t>
   </si>
   <si>
     <t xml:space="preserve">0.460657566785812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473961740732193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473130285739899</t>
+    <t xml:space="preserve">0.473961770534515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473130255937576</t>
   </si>
   <si>
     <t xml:space="preserve">0.486434400081635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489760518074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503064751625061</t>
+    <t xml:space="preserve">0.489760458469391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503064692020416</t>
   </si>
   <si>
     <t xml:space="preserve">0.50472766160965</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">0.506390750408173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51054835319519</t>
+    <t xml:space="preserve">0.510548293590546</t>
   </si>
   <si>
     <t xml:space="preserve">0.503896176815033</t>
@@ -2618,25 +2618,25 @@
     <t xml:space="preserve">0.495581090450287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484771430492401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482276856899261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491423487663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497244119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487265944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493086516857147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483108341693878</t>
+    <t xml:space="preserve">0.484771370887756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482276886701584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491423547267914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497244030237198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487265914678574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493086487054825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483108371496201</t>
   </si>
   <si>
     <t xml:space="preserve">0.478119283914566</t>
@@ -2645,22 +2645,22 @@
     <t xml:space="preserve">0.475624829530716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476456344127655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529673099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523852467536926</t>
+    <t xml:space="preserve">0.476456314325333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529672980308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523852407932281</t>
   </si>
   <si>
     <t xml:space="preserve">0.528010010719299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533830642700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527178466320038</t>
+    <t xml:space="preserve">0.533830583095551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527178525924683</t>
   </si>
   <si>
     <t xml:space="preserve">0.547966301441193</t>
@@ -2672,19 +2672,19 @@
     <t xml:space="preserve">0.525515496730804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526346981525421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554618418216705</t>
+    <t xml:space="preserve">0.526347041130066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554618299007416</t>
   </si>
   <si>
     <t xml:space="preserve">0.588710427284241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575406193733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577069222927094</t>
+    <t xml:space="preserve">0.575406134128571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577069163322449</t>
   </si>
   <si>
     <t xml:space="preserve">0.570417106151581</t>
@@ -2693,31 +2693,31 @@
     <t xml:space="preserve">0.583721339702606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58538430929184</t>
+    <t xml:space="preserve">0.585384368896484</t>
   </si>
   <si>
     <t xml:space="preserve">0.57790070772171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58039528131485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550460875034332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556281507015228</t>
+    <t xml:space="preserve">0.580395221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550460815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556281387805939</t>
   </si>
   <si>
     <t xml:space="preserve">0.545471787452698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567922592163086</t>
+    <t xml:space="preserve">0.567922651767731</t>
   </si>
   <si>
     <t xml:space="preserve">0.566259562969208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557112991809845</t>
+    <t xml:space="preserve">0.5571129322052</t>
   </si>
   <si>
     <t xml:space="preserve">0.56459653377533</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">0.549629330635071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539651215076447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536325097084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532999038696289</t>
+    <t xml:space="preserve">0.539651155471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53632515668869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532999098300934</t>
   </si>
   <si>
     <t xml:space="preserve">0.524683952331543</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">0.509716749191284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507222294807434</t>
+    <t xml:space="preserve">0.507222235202789</t>
   </si>
   <si>
     <t xml:space="preserve">0.521357893943787</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">0.513874292373657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522189438343048</t>
+    <t xml:space="preserve">0.522189497947693</t>
   </si>
   <si>
     <t xml:space="preserve">0.513042807579041</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">0.52052640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523020923137665</t>
+    <t xml:space="preserve">0.52302098274231</t>
   </si>
   <si>
     <t xml:space="preserve">0.519694864749908</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">0.508053779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488097488880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488928973674774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492255032062531</t>
+    <t xml:space="preserve">0.488097459077835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488928943872452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492255002260208</t>
   </si>
   <si>
     <t xml:space="preserve">0.496412575244904</t>
@@ -2789,13 +2789,13 @@
     <t xml:space="preserve">0.480613887310028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474793285131454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4540054500103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478950798511505</t>
+    <t xml:space="preserve">0.47479322552681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454005479812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478950768709183</t>
   </si>
   <si>
     <t xml:space="preserve">0.458163022994995</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">0.419913470745087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422408044338226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424071043729782</t>
+    <t xml:space="preserve">0.422408014535904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42407101392746</t>
   </si>
   <si>
     <t xml:space="preserve">0.411598354578018</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">0.395799666643143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377090632915497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365033686161041</t>
+    <t xml:space="preserve">0.377090603113174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365033715963364</t>
   </si>
   <si>
     <t xml:space="preserve">0.402035981416702</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">0.407440811395645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412429839372635</t>
+    <t xml:space="preserve">0.412429869174957</t>
   </si>
   <si>
     <t xml:space="preserve">0.431554615497589</t>
@@ -2867,58 +2867,58 @@
     <t xml:space="preserve">0.443195819854736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448184877634048</t>
+    <t xml:space="preserve">0.448184847831726</t>
   </si>
   <si>
     <t xml:space="preserve">0.44652184844017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440701246261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434880673885345</t>
+    <t xml:space="preserve">0.440701276063919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434880703687668</t>
   </si>
   <si>
     <t xml:space="preserve">0.424902528524399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444858878850937</t>
+    <t xml:space="preserve">0.444858849048615</t>
   </si>
   <si>
     <t xml:space="preserve">0.447353363037109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445690363645554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463152050971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477287799119949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470635682344437</t>
+    <t xml:space="preserve">0.445690333843231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463152080774307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48144543170929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477287828922272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470635652542114</t>
   </si>
   <si>
     <t xml:space="preserve">0.437375247478485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429060101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421576529741287</t>
+    <t xml:space="preserve">0.429060071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421576499938965</t>
   </si>
   <si>
     <t xml:space="preserve">0.409935355186462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430723130702972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427397102117538</t>
+    <t xml:space="preserve">0.430723160505295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427397072315216</t>
   </si>
   <si>
     <t xml:space="preserve">0.415755927562714</t>
@@ -2930,25 +2930,25 @@
     <t xml:space="preserve">0.452196657657623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446109414100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439152508974075</t>
+    <t xml:space="preserve">0.446109443902969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439152538776398</t>
   </si>
   <si>
     <t xml:space="preserve">0.431326061487198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423499584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406542181968689</t>
+    <t xml:space="preserve">0.423499554395676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406542211771011</t>
   </si>
   <si>
     <t xml:space="preserve">0.403063774108887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414368689060211</t>
+    <t xml:space="preserve">0.414368718862534</t>
   </si>
   <si>
     <t xml:space="preserve">0.3939328789711</t>
@@ -2957,10 +2957,10 @@
     <t xml:space="preserve">0.391324043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383932381868362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388715207576752</t>
+    <t xml:space="preserve">0.38393235206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388715237379074</t>
   </si>
   <si>
     <t xml:space="preserve">0.382627934217453</t>
@@ -2981,10 +2981,10 @@
     <t xml:space="preserve">0.384367167949677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378714710474014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373931914567947</t>
+    <t xml:space="preserve">0.378714740276337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373931884765625</t>
   </si>
   <si>
     <t xml:space="preserve">0.372627437114716</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">0.370888203382492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361322551965714</t>
+    <t xml:space="preserve">0.361322522163391</t>
   </si>
   <si>
     <t xml:space="preserve">0.366105407476425</t>
@@ -3008,10 +3008,10 @@
     <t xml:space="preserve">0.371323019266129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375671088695526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374366700649261</t>
+    <t xml:space="preserve">0.375671118497849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374366670846939</t>
   </si>
   <si>
     <t xml:space="preserve">0.370018631219864</t>
@@ -3029,16 +3029,16 @@
     <t xml:space="preserve">0.36175736784935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368714183568954</t>
+    <t xml:space="preserve">0.368714213371277</t>
   </si>
   <si>
     <t xml:space="preserve">0.377410292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369583815336227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377845108509064</t>
+    <t xml:space="preserve">0.36958384513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377845138311386</t>
   </si>
   <si>
     <t xml:space="preserve">0.374801486730576</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">0.37523627281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372192651033401</t>
+    <t xml:space="preserve">0.372192621231079</t>
   </si>
   <si>
     <t xml:space="preserve">0.365235775709152</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">0.364800959825516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386976033449173</t>
+    <t xml:space="preserve">0.386976003646851</t>
   </si>
   <si>
     <t xml:space="preserve">0.397411286830902</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">0.407846629619598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389584839344025</t>
+    <t xml:space="preserve">0.389584869146347</t>
   </si>
   <si>
     <t xml:space="preserve">0.396106898784637</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">0.399150520563126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403498560190201</t>
+    <t xml:space="preserve">0.403498589992523</t>
   </si>
   <si>
     <t xml:space="preserve">0.396541684865952</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">0.408716231584549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400020152330399</t>
+    <t xml:space="preserve">0.400020122528076</t>
   </si>
   <si>
     <t xml:space="preserve">0.400889754295349</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">0.395672082901001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401324540376663</t>
+    <t xml:space="preserve">0.401324570178986</t>
   </si>
   <si>
     <t xml:space="preserve">0.396976500749588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400454938411713</t>
+    <t xml:space="preserve">0.400454968214035</t>
   </si>
   <si>
     <t xml:space="preserve">0.390454441308975</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">0.382193148136139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381758332252502</t>
+    <t xml:space="preserve">0.381758362054825</t>
   </si>
   <si>
     <t xml:space="preserve">0.371757835149765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357844084501266</t>
+    <t xml:space="preserve">0.357844114303589</t>
   </si>
   <si>
     <t xml:space="preserve">0.366540193557739</t>
@@ -3170,22 +3170,22 @@
     <t xml:space="preserve">0.362626940011978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369148999452591</t>
+    <t xml:space="preserve">0.369149029254913</t>
   </si>
   <si>
     <t xml:space="preserve">0.379149526357651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3861064016819</t>
+    <t xml:space="preserve">0.386106371879578</t>
   </si>
   <si>
     <t xml:space="preserve">0.394367665052414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404368191957474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392628461122513</t>
+    <t xml:space="preserve">0.404368221759796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392628490924835</t>
   </si>
   <si>
     <t xml:space="preserve">0.391758888959885</t>
@@ -3215,13 +3215,13 @@
     <t xml:space="preserve">0.403868108987808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406615525484085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407531321048737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409362882375717</t>
+    <t xml:space="preserve">0.406615495681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407531291246414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40936291217804</t>
   </si>
   <si>
     <t xml:space="preserve">0.408447116613388</t>
@@ -3239,16 +3239,16 @@
     <t xml:space="preserve">0.402952283620834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402036488056183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393794327974319</t>
+    <t xml:space="preserve">0.402036517858505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393794298171997</t>
   </si>
   <si>
     <t xml:space="preserve">0.39104688167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391962707042694</t>
+    <t xml:space="preserve">0.391962677240372</t>
   </si>
   <si>
     <t xml:space="preserve">0.390131086111069</t>
@@ -3257,22 +3257,22 @@
     <t xml:space="preserve">0.394710093736649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3956258893013</t>
+    <t xml:space="preserve">0.395625919103622</t>
   </si>
   <si>
     <t xml:space="preserve">0.397457480430603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392878502607346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388299465179443</t>
+    <t xml:space="preserve">0.392878472805023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388299494981766</t>
   </si>
   <si>
     <t xml:space="preserve">0.384636282920837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389215290546417</t>
+    <t xml:space="preserve">0.38921532034874</t>
   </si>
   <si>
     <t xml:space="preserve">0.386467903852463</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">0.380973100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375478267669678</t>
+    <t xml:space="preserve">0.375478297472</t>
   </si>
   <si>
     <t xml:space="preserve">0.373646676540375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371815055608749</t>
+    <t xml:space="preserve">0.371815085411072</t>
   </si>
   <si>
     <t xml:space="preserve">0.369067668914795</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">0.369983494281769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376394093036652</t>
+    <t xml:space="preserve">0.376394122838974</t>
   </si>
   <si>
     <t xml:space="preserve">0.374562501907349</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">0.37089928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378225684165955</t>
+    <t xml:space="preserve">0.378225654363632</t>
   </si>
   <si>
     <t xml:space="preserve">0.385552108287811</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">0.420352518558502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421268343925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425847321748734</t>
+    <t xml:space="preserve">0.421268314123154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425847351551056</t>
   </si>
   <si>
     <t xml:space="preserve">0.416689306497574</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">0.415773510932922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410278707742691</t>
+    <t xml:space="preserve">0.410278737545013</t>
   </si>
   <si>
     <t xml:space="preserve">0.422184109687805</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">0.456068724393845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445994943380356</t>
+    <t xml:space="preserve">0.445994913578033</t>
   </si>
   <si>
     <t xml:space="preserve">0.494532406330109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48720595240593</t>
+    <t xml:space="preserve">0.487206012010574</t>
   </si>
   <si>
     <t xml:space="preserve">0.492700755596161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481711208820343</t>
+    <t xml:space="preserve">0.481711179018021</t>
   </si>
   <si>
     <t xml:space="preserve">0.489037543535233</t>
@@ -3413,16 +3413,16 @@
     <t xml:space="preserve">0.496363997459412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485374301671982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483542799949646</t>
+    <t xml:space="preserve">0.485374361276627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483542770147324</t>
   </si>
   <si>
     <t xml:space="preserve">0.454237133264542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463395118713379</t>
+    <t xml:space="preserve">0.463395148515701</t>
   </si>
   <si>
     <t xml:space="preserve">0.476216346025467</t>
@@ -69090,7 +69090,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6912615741</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>287076</v>
@@ -69111,6 +69111,32 @@
         <v>1263</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6909837963</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>154475</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>0.462999999523163</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>0.453999996185303</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>0.456999987363815</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>0.46399998664856</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -44,43 +44,43 @@
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844811439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323679029941559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980736494064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313056260347366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304966062307358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29976013302803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309538751840591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302503824234009</t>
+    <t xml:space="preserve">0.326844841241837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323679089546204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980766296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313056230545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304966032505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299760162830353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309538811445236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302503794431686</t>
   </si>
   <si>
     <t xml:space="preserve">0.287097215652466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274363905191422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278655230998993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265288800001144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260645717382431</t>
+    <t xml:space="preserve">0.274363934993744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278655260801315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265288829803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260645776987076</t>
   </si>
   <si>
     <t xml:space="preserve">0.270846426486969</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">0.269087672233582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272956907749176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270142912864685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265921980142593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290825724601746</t>
+    <t xml:space="preserve">0.272956937551498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270142883062363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265921950340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290825754404068</t>
   </si>
   <si>
     <t xml:space="preserve">0.288433879613876</t>
@@ -107,22 +107,22 @@
     <t xml:space="preserve">0.294061839580536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276404052972794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273167967796326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262545168399811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260293960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246927544474602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24622406065464</t>
+    <t xml:space="preserve">0.276404082775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273167937994003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262545138597488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260293990373611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246927559375763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246224075555801</t>
   </si>
   <si>
     <t xml:space="preserve">0.239751860499382</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">0.240103617310524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271549910306931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276122629642487</t>
+    <t xml:space="preserve">0.271549940109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276122659444809</t>
   </si>
   <si>
     <t xml:space="preserve">0.274645298719406</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">0.277881413698196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270987123250961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281539559364319</t>
+    <t xml:space="preserve">0.270987153053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281539618968964</t>
   </si>
   <si>
     <t xml:space="preserve">0.277177900075912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263319045305252</t>
+    <t xml:space="preserve">0.26331901550293</t>
   </si>
   <si>
     <t xml:space="preserve">0.2680324614048</t>
@@ -161,37 +161,37 @@
     <t xml:space="preserve">0.28210237622261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295468807220459</t>
+    <t xml:space="preserve">0.295468777418137</t>
   </si>
   <si>
     <t xml:space="preserve">0.293358325958252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291740268468857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288644909858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504242897034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281469225883484</t>
+    <t xml:space="preserve">0.291740328073502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288644880056381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504183292389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281469255685806</t>
   </si>
   <si>
     <t xml:space="preserve">0.277248233556747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373837471008</t>
+    <t xml:space="preserve">0.278373897075653</t>
   </si>
   <si>
     <t xml:space="preserve">0.287026882171631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297368288040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295820593833923</t>
+    <t xml:space="preserve">0.297368258237839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295820623636246</t>
   </si>
   <si>
     <t xml:space="preserve">0.307217240333557</t>
@@ -200,88 +200,88 @@
     <t xml:space="preserve">0.305669546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313759744167328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320443034172058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317417979240417</t>
+    <t xml:space="preserve">0.31375977396965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320443004369736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317417949438095</t>
   </si>
   <si>
     <t xml:space="preserve">0.316573739051819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306161969900131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310945808887482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311438262462616</t>
+    <t xml:space="preserve">0.306161999702454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310945779085159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311438202857971</t>
   </si>
   <si>
     <t xml:space="preserve">0.301800280809402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288011729717255</t>
+    <t xml:space="preserve">0.288011759519577</t>
   </si>
   <si>
     <t xml:space="preserve">0.288082122802734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28055465221405</t>
+    <t xml:space="preserve">0.280554682016373</t>
   </si>
   <si>
     <t xml:space="preserve">0.281328529119492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291880965232849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301378190517426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311649262905121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310242265462875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311508566141129</t>
+    <t xml:space="preserve">0.291880995035172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30137825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311649233102798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31024232506752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311508595943451</t>
   </si>
   <si>
     <t xml:space="preserve">0.314533621072769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316644072532654</t>
+    <t xml:space="preserve">0.316644132137299</t>
   </si>
   <si>
     <t xml:space="preserve">0.318684250116348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330573320388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330643683671951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334161192178726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3335280418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330432623624802</t>
+    <t xml:space="preserve">0.330573350191116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330643713474274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334161132574081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333528012037277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330432653427124</t>
   </si>
   <si>
     <t xml:space="preserve">0.327126204967499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323538362979889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318543523550034</t>
+    <t xml:space="preserve">0.323538392782211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318543583154678</t>
   </si>
   <si>
     <t xml:space="preserve">0.319247037172318</t>
@@ -290,49 +290,49 @@
     <t xml:space="preserve">0.323116272687912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321005791425705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324874997138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323749423027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325015723705292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32107612490654</t>
+    <t xml:space="preserve">0.321005761623383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324874967336655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323749452829361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325015753507614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321076154708862</t>
   </si>
   <si>
     <t xml:space="preserve">0.326774477958679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33176925778389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344713658094406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342040300369263</t>
+    <t xml:space="preserve">0.331769287586212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344713687896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34204038977623</t>
   </si>
   <si>
     <t xml:space="preserve">0.338030427694321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352100402116776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354914277791977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351678282022476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350341647863388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343306630849838</t>
+    <t xml:space="preserve">0.352100342512131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354914307594299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351678311824799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350341618061066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343306660652161</t>
   </si>
   <si>
     <t xml:space="preserve">0.343165934085846</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">0.341196149587631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340211242437363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337045520544052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323537796735764</t>
+    <t xml:space="preserve">0.340211272239685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33704549074173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323537766933441</t>
   </si>
   <si>
     <t xml:space="preserve">0.309325873851776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312153726816177</t>
+    <t xml:space="preserve">0.312153786420822</t>
   </si>
   <si>
     <t xml:space="preserve">0.308890819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31193619966507</t>
+    <t xml:space="preserve">0.311936229467392</t>
   </si>
   <si>
     <t xml:space="preserve">0.325277954339981</t>
@@ -368,52 +368,52 @@
     <t xml:space="preserve">0.322232604026794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318607121706009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324190348386765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30722314119339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299102008342743</t>
+    <t xml:space="preserve">0.318607091903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324190378189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307223081588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299102038145065</t>
   </si>
   <si>
     <t xml:space="preserve">0.299464553594589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313096344470978</t>
+    <t xml:space="preserve">0.313096404075623</t>
   </si>
   <si>
     <t xml:space="preserve">0.320854872465134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318027019500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319042146205902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318317055702209</t>
+    <t xml:space="preserve">0.318027049303055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319042176008224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318317085504532</t>
   </si>
   <si>
     <t xml:space="preserve">0.309543401002884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311791211366653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310558557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311066061258316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322087556123734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31976729631424</t>
+    <t xml:space="preserve">0.311791181564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310558587312698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311066091060638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322087585926056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319767266511917</t>
   </si>
   <si>
     <t xml:space="preserve">0.318172037601471</t>
@@ -422,49 +422,49 @@
     <t xml:space="preserve">0.309978455305099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30671551823616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305627852678299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30178490281105</t>
+    <t xml:space="preserve">0.306715548038483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305627912282944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301784932613373</t>
   </si>
   <si>
     <t xml:space="preserve">0.300914764404297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298739492893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298014432191849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291488528251648</t>
+    <t xml:space="preserve">0.298739463090897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298014372587204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291488498449326</t>
   </si>
   <si>
     <t xml:space="preserve">0.294316381216049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304467737674713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301204800605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302727520465851</t>
+    <t xml:space="preserve">0.304467767477036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301204830408096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302727490663528</t>
   </si>
   <si>
     <t xml:space="preserve">0.303815126419067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30062472820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29743430018425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299682110548019</t>
+    <t xml:space="preserve">0.300624758005142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297434329986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299682140350342</t>
   </si>
   <si>
     <t xml:space="preserve">0.301929891109467</t>
@@ -473,94 +473,94 @@
     <t xml:space="preserve">0.301712334156036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302364945411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300117164850235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302219927310944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297144293785095</t>
+    <t xml:space="preserve">0.30236491560936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300117135047913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302219957113266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297144263982773</t>
   </si>
   <si>
     <t xml:space="preserve">0.295621573925018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293663799762726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297289252281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291706055402756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292358607053757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29003831744194</t>
+    <t xml:space="preserve">0.293663829565048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297289282083511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291706085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292358636856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290038347244263</t>
   </si>
   <si>
     <t xml:space="preserve">0.287500470876694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292648673057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287645488977432</t>
+    <t xml:space="preserve">0.292648702859879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287645518779755</t>
   </si>
   <si>
     <t xml:space="preserve">0.295041471719742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291561007499695</t>
+    <t xml:space="preserve">0.29156106710434</t>
   </si>
   <si>
     <t xml:space="preserve">0.294533908367157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289313167333603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287935554981232</t>
+    <t xml:space="preserve">0.289313226938248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287935584783554</t>
   </si>
   <si>
     <t xml:space="preserve">0.283004909753799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287428021430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282859861850739</t>
+    <t xml:space="preserve">0.287427991628647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282859891653061</t>
   </si>
   <si>
     <t xml:space="preserve">0.275826424360275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279161870479584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269735634326935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273288607597351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279524475336075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282062262296677</t>
+    <t xml:space="preserve">0.279161900281906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269735664129257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273288637399673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27952441573143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282062292098999</t>
   </si>
   <si>
     <t xml:space="preserve">0.283802479505539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282134741544724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28713795542717</t>
+    <t xml:space="preserve">0.282134771347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287137985229492</t>
   </si>
   <si>
     <t xml:space="preserve">0.292866200208664</t>
@@ -578,40 +578,40 @@
     <t xml:space="preserve">0.300262182950974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297071754932404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292938739061356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298811972141266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296056658029556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310195982456207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306425511837006</t>
+    <t xml:space="preserve">0.297071784734726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292938709259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298812001943588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296056628227234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31019601225853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306425482034683</t>
   </si>
   <si>
     <t xml:space="preserve">0.302509993314743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306062936782837</t>
+    <t xml:space="preserve">0.306062966585159</t>
   </si>
   <si>
     <t xml:space="preserve">0.307078093290329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30163985490799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294098854064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283077359199524</t>
+    <t xml:space="preserve">0.301639884710312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294098883867264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283077389001846</t>
   </si>
   <si>
     <t xml:space="preserve">0.287863045930862</t>
@@ -623,34 +623,34 @@
     <t xml:space="preserve">0.285615265369415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283947497606277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288805663585663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293736308813095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290835916996002</t>
+    <t xml:space="preserve">0.2839475274086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28880563378334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293736338615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290835946798325</t>
   </si>
   <si>
     <t xml:space="preserve">0.283512473106384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281409651041031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280684590339661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279016882181168</t>
+    <t xml:space="preserve">0.281409710645676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280684620141983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279016852378845</t>
   </si>
   <si>
     <t xml:space="preserve">0.273796200752258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291415989398956</t>
+    <t xml:space="preserve">0.291416019201279</t>
   </si>
   <si>
     <t xml:space="preserve">0.295114010572433</t>
@@ -659,67 +659,67 @@
     <t xml:space="preserve">0.290545910596848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288588106632233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292213588953018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292141079902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294388890266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299392074346542</t>
+    <t xml:space="preserve">0.288588136434555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292213618755341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292141109704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294388920068741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29939204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.296491682529449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303597629070282</t>
+    <t xml:space="preserve">0.303597658872604</t>
   </si>
   <si>
     <t xml:space="preserve">0.309615910053253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307440638542175</t>
+    <t xml:space="preserve">0.307440608739853</t>
   </si>
   <si>
     <t xml:space="preserve">0.319187164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33151376247406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331368774175644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345000624656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349786221981049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358342349529266</t>
+    <t xml:space="preserve">0.331513792276382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331368803977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345000594854355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349786192178726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358342319726944</t>
   </si>
   <si>
     <t xml:space="preserve">0.354209333658218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34964120388031</t>
+    <t xml:space="preserve">0.349641233682632</t>
   </si>
   <si>
     <t xml:space="preserve">0.352396577596664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355296939611435</t>
+    <t xml:space="preserve">0.35529699921608</t>
   </si>
   <si>
     <t xml:space="preserve">0.359430015087128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352686613798141</t>
+    <t xml:space="preserve">0.352686583995819</t>
   </si>
   <si>
     <t xml:space="preserve">0.346885830163956</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">0.346160709857941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346595793962479</t>
+    <t xml:space="preserve">0.346595823764801</t>
   </si>
   <si>
     <t xml:space="preserve">0.346450805664062</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">0.344348043203354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350221276283264</t>
+    <t xml:space="preserve">0.350221306085587</t>
   </si>
   <si>
     <t xml:space="preserve">0.350946366786957</t>
@@ -749,52 +749,52 @@
     <t xml:space="preserve">0.388288795948029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397715002298355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379950165748596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382125526666641</t>
+    <t xml:space="preserve">0.397715091705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379950225353241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382125496864319</t>
   </si>
   <si>
     <t xml:space="preserve">0.374874532222748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373424381017685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377412408590317</t>
+    <t xml:space="preserve">0.37342432141304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377412378787994</t>
   </si>
   <si>
     <t xml:space="preserve">0.373061805963516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369798868894577</t>
+    <t xml:space="preserve">0.369798839092255</t>
   </si>
   <si>
     <t xml:space="preserve">0.383575677871704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369436383247375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369073778390884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358197301626205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358052343130112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377049833536148</t>
+    <t xml:space="preserve">0.369436323642731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369073748588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35819736123085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358052313327789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377049803733826</t>
   </si>
   <si>
     <t xml:space="preserve">0.412579536437988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382488012313843</t>
+    <t xml:space="preserve">0.382488042116165</t>
   </si>
   <si>
     <t xml:space="preserve">0.40061542391777</t>
@@ -803,31 +803,31 @@
     <t xml:space="preserve">0.394452154636383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385750979185104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393727034330368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390464067459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384300798177719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391551733016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387563675642014</t>
+    <t xml:space="preserve">0.385751008987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393726974725723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390464127063751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384300768375397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39155176281929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387563735246658</t>
   </si>
   <si>
     <t xml:space="preserve">0.390826612710953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395177245140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393364459276199</t>
+    <t xml:space="preserve">0.395177215337753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393364518880844</t>
   </si>
   <si>
     <t xml:space="preserve">0.397352516651154</t>
@@ -836,46 +836,46 @@
     <t xml:space="preserve">0.398802697658539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395539730787277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396627396345139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39844012260437</t>
+    <t xml:space="preserve">0.395539700984955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396627426147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398440152406693</t>
   </si>
   <si>
     <t xml:space="preserve">0.395902335643768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393001943826675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398077636957169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401703119277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392276853322983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38720116019249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386476099491119</t>
+    <t xml:space="preserve">0.393001914024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398077696561813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401703089475632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392276793718338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387201130390167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386476039886475</t>
   </si>
   <si>
     <t xml:space="preserve">0.382850617170334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394089579582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389376491308212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38176292181015</t>
+    <t xml:space="preserve">0.394089609384537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389376431703568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381762951612473</t>
   </si>
   <si>
     <t xml:space="preserve">0.381037831306458</t>
@@ -884,100 +884,100 @@
     <t xml:space="preserve">0.386838614940643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388651371002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385025888681412</t>
+    <t xml:space="preserve">0.388651341199875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385025858879089</t>
   </si>
   <si>
     <t xml:space="preserve">0.391189217567444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392639309167862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425631284713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419105410575867</t>
+    <t xml:space="preserve">0.392639368772507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425631254911423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419105350971222</t>
   </si>
   <si>
     <t xml:space="preserve">0.445208877325058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435057491064072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442308485507965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432612001895905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413591921329498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408370792865753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406879007816315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402776718139648</t>
+    <t xml:space="preserve">0.435057550668716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442308455705643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432611972093582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413592010736465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408370822668076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406878978013992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402776688337326</t>
   </si>
   <si>
     <t xml:space="preserve">0.399047255516052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400539070367813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395317822694778</t>
+    <t xml:space="preserve">0.400539010763168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395317852497101</t>
   </si>
   <si>
     <t xml:space="preserve">0.396809637546539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39606374502182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393080234527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388604938983917</t>
+    <t xml:space="preserve">0.396063715219498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393080174922943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388604909181595</t>
   </si>
   <si>
     <t xml:space="preserve">0.387859016656876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379654318094254</t>
+    <t xml:space="preserve">0.379654258489609</t>
   </si>
   <si>
     <t xml:space="preserve">0.381146043539047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383010804653168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387486100196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384875476360321</t>
+    <t xml:space="preserve">0.383010774850845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387486070394516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384875446557999</t>
   </si>
   <si>
     <t xml:space="preserve">0.383756667375565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386740177869797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390096664428711</t>
+    <t xml:space="preserve">0.386740148067474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390096634626389</t>
   </si>
   <si>
     <t xml:space="preserve">0.394944906234741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403522580862045</t>
+    <t xml:space="preserve">0.403522521257401</t>
   </si>
   <si>
     <t xml:space="preserve">0.410235524177551</t>
@@ -986,37 +986,37 @@
     <t xml:space="preserve">0.407251983880997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407624900341034</t>
+    <t xml:space="preserve">0.407624930143356</t>
   </si>
   <si>
     <t xml:space="preserve">0.408743739128113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406506091356277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400911957025528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394199013710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39867427945137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390842527151108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392334342002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388231962919235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387113153934479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391588419675827</t>
+    <t xml:space="preserve">0.406506061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400912016630173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394199073314667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398674309253693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39084255695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392334312200546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388231933116913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387113124132156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391588389873505</t>
   </si>
   <si>
     <t xml:space="preserve">0.389350831508636</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">0.38562136888504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380773156881332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385248452425003</t>
+    <t xml:space="preserve">0.38077312707901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385248422622681</t>
   </si>
   <si>
     <t xml:space="preserve">0.383383721113205</t>
@@ -1037,97 +1037,97 @@
     <t xml:space="preserve">0.397928446531296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410981386899948</t>
+    <t xml:space="preserve">0.409489721059799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410981416702271</t>
   </si>
   <si>
     <t xml:space="preserve">0.414337813854218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415083736181259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416575491428375</t>
+    <t xml:space="preserve">0.415083765983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416575521230698</t>
   </si>
   <si>
     <t xml:space="preserve">0.415829628705978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424034297466278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439324975013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866139173508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428882598876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420304924249649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421796709299088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428509622812271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454988479614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445291996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4445461332798</t>
+    <t xml:space="preserve">0.4240343272686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439324885606766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866109371185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428882539272308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420304864645004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421796649694443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428509712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454988449811935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44529202580452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444546103477478</t>
   </si>
   <si>
     <t xml:space="preserve">0.440443754196167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44976732134819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459463804960251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460955500602722</t>
+    <t xml:space="preserve">0.449767202138901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459463715553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460955530405045</t>
   </si>
   <si>
     <t xml:space="preserve">0.469533145427704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466549634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474008440971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474754363298416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348467826843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485942542552948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482586145401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485569655895233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50943797826767</t>
+    <t xml:space="preserve">0.466549664735794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474008500576019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474754393100739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480348438024521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48594257235527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482586115598679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4855697453022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509437918663025</t>
   </si>
   <si>
     <t xml:space="preserve">0.511302649974823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521745026111603</t>
+    <t xml:space="preserve">0.521744906902313</t>
   </si>
   <si>
     <t xml:space="preserve">0.512794375419617</t>
@@ -1139,22 +1139,22 @@
     <t xml:space="preserve">0.511675536632538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506081402301788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501233279705048</t>
+    <t xml:space="preserve">0.506081342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501233160495758</t>
   </si>
   <si>
     <t xml:space="preserve">0.502352058887482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495266109704971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491536676883698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477737933397293</t>
+    <t xml:space="preserve">0.495266050100327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491536736488342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477737963199615</t>
   </si>
   <si>
     <t xml:space="preserve">0.478483766317368</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">0.481094360351562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492282629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499741524457932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4937744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495639145374298</t>
+    <t xml:space="preserve">0.492282658815384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499741464853287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493774354457855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495639026165009</t>
   </si>
   <si>
     <t xml:space="preserve">0.507946133613586</t>
@@ -1187,22 +1187,22 @@
     <t xml:space="preserve">0.50869208574295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503470897674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508319079875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507200300693512</t>
+    <t xml:space="preserve">0.503470838069916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508319020271301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507200241088867</t>
   </si>
   <si>
     <t xml:space="preserve">0.510183811187744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513167321681976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500860214233398</t>
+    <t xml:space="preserve">0.513167381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500860273838043</t>
   </si>
   <si>
     <t xml:space="preserve">0.503097891807556</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">0.502724945545197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501606106758118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498249650001526</t>
+    <t xml:space="preserve">0.501606166362762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498249679803848</t>
   </si>
   <si>
     <t xml:space="preserve">0.510929703712463</t>
@@ -1226,19 +1226,19 @@
     <t xml:space="preserve">0.557920277118683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554936766624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559412002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565379083156586</t>
+    <t xml:space="preserve">0.554936826229095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559412121772766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56537914276123</t>
   </si>
   <si>
     <t xml:space="preserve">0.593722641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574329614639282</t>
+    <t xml:space="preserve">0.574329733848572</t>
   </si>
   <si>
     <t xml:space="preserve">0.576567351818085</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">0.577313244342804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583280265331268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591485023498535</t>
+    <t xml:space="preserve">0.583280324935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59148496389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.585517883300781</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">0.575075566768646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61236971616745</t>
+    <t xml:space="preserve">0.612369775772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.556428551673889</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">0.548223793506622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534797966480255</t>
+    <t xml:space="preserve">0.53479790687561</t>
   </si>
   <si>
     <t xml:space="preserve">0.521372079849243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505708515644073</t>
+    <t xml:space="preserve">0.505708456039429</t>
   </si>
   <si>
     <t xml:space="preserve">0.528084933757782</t>
@@ -1292,112 +1292,112 @@
     <t xml:space="preserve">0.517642617225647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532560229301453</t>
+    <t xml:space="preserve">0.532560288906097</t>
   </si>
   <si>
     <t xml:space="preserve">0.531814396381378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523609697818756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516150951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512421488761902</t>
+    <t xml:space="preserve">0.523609757423401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516150832176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512421369552612</t>
   </si>
   <si>
     <t xml:space="preserve">0.519134402275085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498995572328568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46319317817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469906181097031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476619094610214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477364987134933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494520306587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490045011043549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478856712579727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47811084985733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46841436624527</t>
+    <t xml:space="preserve">0.498995542526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463193118572235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469906091690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476619124412537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477364927530289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494520246982574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490044921636581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47885674238205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478110790252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468414425849915</t>
   </si>
   <si>
     <t xml:space="preserve">0.481840252876282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484077900648117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475127339363098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473635613918304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474381446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484823763370514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487061381340027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483331978321075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504216730594635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504962682723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496757924556732</t>
+    <t xml:space="preserve">0.484077930450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475127309560776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473635494709015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474381387233734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484823733568192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487061470746994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48333203792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50421667098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504962563514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496757864952087</t>
   </si>
   <si>
     <t xml:space="preserve">0.497503787279129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486315578222275</t>
+    <t xml:space="preserve">0.486315548419952</t>
   </si>
   <si>
     <t xml:space="preserve">0.500487327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454242616891861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46543088555336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452004939317703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457226127386093</t>
+    <t xml:space="preserve">0.454242587089539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465430796146393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452004909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457226037979126</t>
   </si>
   <si>
     <t xml:space="preserve">0.458717852830887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462447345256805</t>
+    <t xml:space="preserve">0.462447285652161</t>
   </si>
   <si>
     <t xml:space="preserve">0.455734342336655</t>
@@ -1406,37 +1406,37 @@
     <t xml:space="preserve">0.457972049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485727936029434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48418590426445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474933952093124</t>
+    <t xml:space="preserve">0.485727876424789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484185934066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474933922290802</t>
   </si>
   <si>
     <t xml:space="preserve">0.469536989927292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464910984039307</t>
+    <t xml:space="preserve">0.464911013841629</t>
   </si>
   <si>
     <t xml:space="preserve">0.461055934429169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463368982076645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459514021873474</t>
+    <t xml:space="preserve">0.463369011878967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459513962268829</t>
   </si>
   <si>
     <t xml:space="preserve">0.45797199010849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458743005990982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447949051856995</t>
+    <t xml:space="preserve">0.458743035793304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447949022054672</t>
   </si>
   <si>
     <t xml:space="preserve">0.451033025979996</t>
@@ -1445,103 +1445,103 @@
     <t xml:space="preserve">0.454887986183167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446407079696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441781103610992</t>
+    <t xml:space="preserve">0.446407049894333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441781044006348</t>
   </si>
   <si>
     <t xml:space="preserve">0.443323075771332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494208842515945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47416290640831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481101959943771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489582926034927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476475894451141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464139938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461826950311661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456429988145828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454117059707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466452926397324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467223972082138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439468055963516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442552119493484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45257505774498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45334604382515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441010117530823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437926113605499</t>
+    <t xml:space="preserve">0.494208812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474162936210632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481101900339127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489582866430283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476475954055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464139968156815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461826920509338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456430017948151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454117029905319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466453015804291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46722400188446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439468085765839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442552030086517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452575027942657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453346014022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4410100877285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437926054000854</t>
   </si>
   <si>
     <t xml:space="preserve">0.433300107717514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430987149477005</t>
+    <t xml:space="preserve">0.430987119674683</t>
   </si>
   <si>
     <t xml:space="preserve">0.431758105754852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435613065958023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444865077733994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284978151321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45180407166481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470307946205139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471849888563156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465681970119476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457200974225998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462597995996475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455659002065659</t>
+    <t xml:space="preserve">0.435613095760345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444865107536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460285007953644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451804041862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470307916402817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471849948167801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465681999921799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45720100402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462597966194153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455659031867981</t>
   </si>
   <si>
     <t xml:space="preserve">0.450262039899826</t>
@@ -1550,22 +1550,22 @@
     <t xml:space="preserve">0.449491083621979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437155097723007</t>
+    <t xml:space="preserve">0.437155038118362</t>
   </si>
   <si>
     <t xml:space="preserve">0.440239042043686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426361113786697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427903115749359</t>
+    <t xml:space="preserve">0.426361083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427903175354004</t>
   </si>
   <si>
     <t xml:space="preserve">0.407086193561554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406315267086029</t>
+    <t xml:space="preserve">0.406315237283707</t>
   </si>
   <si>
     <t xml:space="preserve">0.4101702272892</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">0.41094121336937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400147259235382</t>
+    <t xml:space="preserve">0.40014722943306</t>
   </si>
   <si>
     <t xml:space="preserve">0.396292269229889</t>
@@ -1589,76 +1589,76 @@
     <t xml:space="preserve">0.390895307064056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390124291181564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381643354892731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38318532705307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387811303138733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388582289218903</t>
+    <t xml:space="preserve">0.390124261379242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381643325090408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383185356855392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387811332941055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388582319021225</t>
   </si>
   <si>
     <t xml:space="preserve">0.39475029706955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397063255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389353305101395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387040257453918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385498344898224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375475347042084</t>
+    <t xml:space="preserve">0.397063285112381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389353275299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387040287256241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385498285293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375475376844406</t>
   </si>
   <si>
     <t xml:space="preserve">0.366223394870758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351188957691193</t>
+    <t xml:space="preserve">0.351188987493515</t>
   </si>
   <si>
     <t xml:space="preserve">0.345406502485275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348875910043716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366994351148605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37239134311676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367765367031097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162358999252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370078384876251</t>
+    <t xml:space="preserve">0.348875969648361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36699441075325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372391372919083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36776539683342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162388801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370078355073929</t>
   </si>
   <si>
     <t xml:space="preserve">0.370463877916336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369692832231522</t>
+    <t xml:space="preserve">0.369692891836166</t>
   </si>
   <si>
     <t xml:space="preserve">0.365837901830673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371620357036591</t>
+    <t xml:space="preserve">0.371620327234268</t>
   </si>
   <si>
     <t xml:space="preserve">0.368536353111267</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">0.383570849895477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377017349004745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382414311170578</t>
+    <t xml:space="preserve">0.377017319202423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3824143409729</t>
   </si>
   <si>
     <t xml:space="preserve">0.39937624335289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416338205337524</t>
+    <t xml:space="preserve">0.416338175535202</t>
   </si>
   <si>
     <t xml:space="preserve">0.424048155546188</t>
@@ -1691,40 +1691,40 @@
     <t xml:space="preserve">0.424819141626358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417109191417694</t>
+    <t xml:space="preserve">0.417109161615372</t>
   </si>
   <si>
     <t xml:space="preserve">0.422506153583527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421735197305679</t>
+    <t xml:space="preserve">0.421735107898712</t>
   </si>
   <si>
     <t xml:space="preserve">0.420964181423187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408628195524216</t>
+    <t xml:space="preserve">0.408628165721893</t>
   </si>
   <si>
     <t xml:space="preserve">0.400918245315552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404773205518723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405544251203537</t>
+    <t xml:space="preserve">0.404773235321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405544281005859</t>
   </si>
   <si>
     <t xml:space="preserve">0.411712199449539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412483185529709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423277169466019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42559015750885</t>
+    <t xml:space="preserve">0.412483215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423277199268341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425590127706528</t>
   </si>
   <si>
     <t xml:space="preserve">0.419422209262848</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">0.430216133594513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427132159471512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414025217294693</t>
+    <t xml:space="preserve">0.427132129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414025187492371</t>
   </si>
   <si>
     <t xml:space="preserve">0.41479617357254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413254201412201</t>
+    <t xml:space="preserve">0.413254231214523</t>
   </si>
   <si>
     <t xml:space="preserve">0.409399211406708</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">0.393208295106888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392437279224396</t>
+    <t xml:space="preserve">0.392437309026718</t>
   </si>
   <si>
     <t xml:space="preserve">0.391666293144226</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">0.410471081733704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409666240215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415300160646439</t>
+    <t xml:space="preserve">0.409666270017624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415300130844116</t>
   </si>
   <si>
     <t xml:space="preserve">0.412885636091232</t>
@@ -1796,31 +1796,31 @@
     <t xml:space="preserve">0.404032289981842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397996008396149</t>
+    <t xml:space="preserve">0.397995978593826</t>
   </si>
   <si>
     <t xml:space="preserve">0.403227478265762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39839842915535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400008112192154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40242263674736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400410532951355</t>
+    <t xml:space="preserve">0.398398399353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400008141994476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402422606945038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400410562753677</t>
   </si>
   <si>
     <t xml:space="preserve">0.395983874797821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399605691432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418519556522369</t>
+    <t xml:space="preserve">0.39960566163063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418519526720047</t>
   </si>
   <si>
     <t xml:space="preserve">0.417714685201645</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">0.404837191104889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401617825031281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407251715660095</t>
+    <t xml:space="preserve">0.401617795228958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40725165605545</t>
   </si>
   <si>
     <t xml:space="preserve">0.408056557178497</t>
@@ -1853,10 +1853,10 @@
     <t xml:space="preserve">0.406446844339371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42656797170639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433811575174332</t>
+    <t xml:space="preserve">0.426567941904068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433811604976654</t>
   </si>
   <si>
     <t xml:space="preserve">0.424153476953506</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">0.428177684545517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433006763458252</t>
+    <t xml:space="preserve">0.43300673365593</t>
   </si>
   <si>
     <t xml:space="preserve">0.429787367582321</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">0.420934081077576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428982526063919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437031000852585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434616476297379</t>
+    <t xml:space="preserve">0.428982555866241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437030971050262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434616446495056</t>
   </si>
   <si>
     <t xml:space="preserve">0.430592238903046</t>
@@ -1898,19 +1898,19 @@
     <t xml:space="preserve">0.458761811256409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466810286045074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473249047994614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476468354463577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478882968425751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475663542747498</t>
+    <t xml:space="preserve">0.466810256242752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473249018192291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476468414068222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478882938623428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47566357254982</t>
   </si>
   <si>
     <t xml:space="preserve">0.481297433376312</t>
@@ -1925,19 +1925,19 @@
     <t xml:space="preserve">0.471639364957809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472444206476212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48612654209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480492621660233</t>
+    <t xml:space="preserve">0.472444176673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486126571893692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480492651462555</t>
   </si>
   <si>
     <t xml:space="preserve">0.494979828596115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511881589889526</t>
+    <t xml:space="preserve">0.511881530284882</t>
   </si>
   <si>
     <t xml:space="preserve">0.513491332530975</t>
@@ -1946,46 +1946,46 @@
     <t xml:space="preserve">0.520734906196594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535222172737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534417271614075</t>
+    <t xml:space="preserve">0.535222113132477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53441721200943</t>
   </si>
   <si>
     <t xml:space="preserve">0.523149430751801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51510101556778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516710638999939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522344529628754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556148111820221</t>
+    <t xml:space="preserve">0.515100955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516710698604584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522344589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556148052215576</t>
   </si>
   <si>
     <t xml:space="preserve">0.555343270301819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551319062709808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55775773525238</t>
+    <t xml:space="preserve">0.551319003105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557757794857025</t>
   </si>
   <si>
     <t xml:space="preserve">0.571440160274506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561782002449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560977220535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552928745746613</t>
+    <t xml:space="preserve">0.56178206205368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560977160930634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552928686141968</t>
   </si>
   <si>
     <t xml:space="preserve">0.554538428783417</t>
@@ -2003,19 +2003,19 @@
     <t xml:space="preserve">0.6116823554039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606853306293488</t>
+    <t xml:space="preserve">0.606853365898132</t>
   </si>
   <si>
     <t xml:space="preserve">0.602024257183075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614901721477509</t>
+    <t xml:space="preserve">0.614901781082153</t>
   </si>
   <si>
     <t xml:space="preserve">0.600414574146271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608463048934937</t>
+    <t xml:space="preserve">0.608462989330292</t>
   </si>
   <si>
     <t xml:space="preserve">0.593975841999054</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">0.590756475925446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595585584640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609267830848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614096939563751</t>
+    <t xml:space="preserve">0.595585525035858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609267890453339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614096879959106</t>
   </si>
   <si>
     <t xml:space="preserve">0.60604852437973</t>
@@ -2039,49 +2039,49 @@
     <t xml:space="preserve">0.593171000480652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598804891109467</t>
+    <t xml:space="preserve">0.598804831504822</t>
   </si>
   <si>
     <t xml:space="preserve">0.601219415664673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594780743122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603633880615234</t>
+    <t xml:space="preserve">0.594780683517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603633999824524</t>
   </si>
   <si>
     <t xml:space="preserve">0.610072731971741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598000049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630193829536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631803512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64629065990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65594893693924</t>
+    <t xml:space="preserve">0.59799998998642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630193769931793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631803572177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646290719509125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655948877334595</t>
   </si>
   <si>
     <t xml:space="preserve">0.65997314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689752340316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684118449687958</t>
+    <t xml:space="preserve">0.689752399921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684118509292603</t>
   </si>
   <si>
     <t xml:space="preserve">0.661582827568054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588341951370239</t>
+    <t xml:space="preserve">0.588341891765594</t>
   </si>
   <si>
     <t xml:space="preserve">0.581098318099976</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">0.572245001792908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540856063365936</t>
+    <t xml:space="preserve">0.540855944156647</t>
   </si>
   <si>
     <t xml:space="preserve">0.543270587921143</t>
@@ -2099,22 +2099,22 @@
     <t xml:space="preserve">0.518320322036743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526368737220764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490955621004105</t>
+    <t xml:space="preserve">0.526368856430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490955591201782</t>
   </si>
   <si>
     <t xml:space="preserve">0.439445525407791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398800849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381496697664261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32314532995224</t>
+    <t xml:space="preserve">0.398800820112228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381496667861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323145359754562</t>
   </si>
   <si>
     <t xml:space="preserve">0.348095566034317</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">0.303829044103622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282500714063644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288939446210861</t>
+    <t xml:space="preserve">0.282500743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288939476013184</t>
   </si>
   <si>
     <t xml:space="preserve">0.29135400056839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304633915424347</t>
+    <t xml:space="preserve">0.304633945226669</t>
   </si>
   <si>
     <t xml:space="preserve">0.308255732059479</t>
@@ -2150,28 +2150,28 @@
     <t xml:space="preserve">0.355741620063782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373850643634796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391959607601166</t>
+    <t xml:space="preserve">0.373850613832474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391959637403488</t>
   </si>
   <si>
     <t xml:space="preserve">0.37908211350441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375057876110077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384716004133224</t>
+    <t xml:space="preserve">0.375057905912399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384716033935547</t>
   </si>
   <si>
     <t xml:space="preserve">0.386325716972351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374253064393997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362180322408676</t>
+    <t xml:space="preserve">0.374253034591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362180352210999</t>
   </si>
   <si>
     <t xml:space="preserve">0.351717382669449</t>
@@ -2183,28 +2183,28 @@
     <t xml:space="preserve">0.34930282831192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344473749399185</t>
+    <t xml:space="preserve">0.344473779201508</t>
   </si>
   <si>
     <t xml:space="preserve">0.323547780513763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338035017251968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33964467048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341254383325577</t>
+    <t xml:space="preserve">0.338034987449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339644700288773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341254413127899</t>
   </si>
   <si>
     <t xml:space="preserve">0.346083462238312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350912511348724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348497986793518</t>
+    <t xml:space="preserve">0.350912541151047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348497956991196</t>
   </si>
   <si>
     <t xml:space="preserve">0.342864066362381</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">0.345278590917587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336425304412842</t>
+    <t xml:space="preserve">0.336425334215164</t>
   </si>
   <si>
     <t xml:space="preserve">0.324352622032166</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">0.329986572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326767146587372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321938097476959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331596225500107</t>
+    <t xml:space="preserve">0.326767176389694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321938127279282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331596255302429</t>
   </si>
   <si>
     <t xml:space="preserve">0.340449541807175</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">0.35493677854538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369423925876617</t>
+    <t xml:space="preserve">0.369423985481262</t>
   </si>
   <si>
     <t xml:space="preserve">0.382301479578018</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">0.356546431779861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357351303100586</t>
+    <t xml:space="preserve">0.357351273298264</t>
   </si>
   <si>
     <t xml:space="preserve">0.350107699632645</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">0.346888303756714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342059224843979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337230175733566</t>
+    <t xml:space="preserve">0.342059254646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337230145931244</t>
   </si>
   <si>
     <t xml:space="preserve">0.328376829624176</t>
@@ -2285,31 +2285,31 @@
     <t xml:space="preserve">0.33562046289444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370228797197342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358156144618988</t>
+    <t xml:space="preserve">0.370228856801987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358156114816666</t>
   </si>
   <si>
     <t xml:space="preserve">0.363790065050125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420129269361496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424958258867264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437835872173309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444274604320526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44588428735733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482907176017761</t>
+    <t xml:space="preserve">0.420129239559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424958288669586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437835842370987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444274574518204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445884257555008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482907146215439</t>
   </si>
   <si>
     <t xml:space="preserve">0.560172259807587</t>
@@ -2318,31 +2318,31 @@
     <t xml:space="preserve">0.527978539466858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521539747714996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529588222503662</t>
+    <t xml:space="preserve">0.521539688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529588162899017</t>
   </si>
   <si>
     <t xml:space="preserve">0.519930064678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507052600383759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500613749027252</t>
+    <t xml:space="preserve">0.507052540779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500613689422607</t>
   </si>
   <si>
     <t xml:space="preserve">0.494175016880035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502223491668701</t>
+    <t xml:space="preserve">0.502223432064056</t>
   </si>
   <si>
     <t xml:space="preserve">0.537636637687683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524759113788605</t>
+    <t xml:space="preserve">0.52475917339325</t>
   </si>
   <si>
     <t xml:space="preserve">0.510271906852722</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">0.49900409579277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492565274238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487736225128174</t>
+    <t xml:space="preserve">0.492565304040909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487736284732819</t>
   </si>
   <si>
     <t xml:space="preserve">0.484516859054565</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">0.43622612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393569350242615</t>
+    <t xml:space="preserve">0.393569320440292</t>
   </si>
   <si>
     <t xml:space="preserve">0.378277271986008</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">0.367009431123734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359765857458115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376667588949203</t>
+    <t xml:space="preserve">0.359765827655792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376667559146881</t>
   </si>
   <si>
     <t xml:space="preserve">0.421738892793655</t>
@@ -2399,64 +2399,64 @@
     <t xml:space="preserve">0.441055208444595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505442917346954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468419998884201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461981207132339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465200573205948</t>
+    <t xml:space="preserve">0.50544285774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468419969081879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461981147527695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46520060300827</t>
   </si>
   <si>
     <t xml:space="preserve">0.45232304930687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455542415380478</t>
+    <t xml:space="preserve">0.455542385578156</t>
   </si>
   <si>
     <t xml:space="preserve">0.450713336467743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460371524095535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457152158021927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453932732343674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479687809944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495784729719162</t>
+    <t xml:space="preserve">0.460371494293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457152098417282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453932762145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47968778014183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495784670114517</t>
   </si>
   <si>
     <t xml:space="preserve">0.4893459379673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547294795513153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565001428127289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576269209384918</t>
+    <t xml:space="preserve">0.547294855117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565001487731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576269268989563</t>
   </si>
   <si>
     <t xml:space="preserve">0.575464367866516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569830417633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549709379673004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56741589307785</t>
+    <t xml:space="preserve">0.569830477237701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549709320068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567415952682495</t>
   </si>
   <si>
     <t xml:space="preserve">0.545685112476349</t>
@@ -2474,13 +2474,13 @@
     <t xml:space="preserve">0.559367418289185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573854625225067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581903100013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.579488635063171</t>
+    <t xml:space="preserve">0.573854684829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581903159618378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579488575458527</t>
   </si>
   <si>
     <t xml:space="preserve">0.544880270957947</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">0.552123844623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548099637031555</t>
+    <t xml:space="preserve">0.5480996966362</t>
   </si>
   <si>
     <t xml:space="preserve">0.548904478549957</t>
@@ -2501,16 +2501,16 @@
     <t xml:space="preserve">0.582058250904083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581226825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573743224143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567091107368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574708938599</t>
+    <t xml:space="preserve">0.581226766109467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573743164539337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567091047763824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574649333954</t>
   </si>
   <si>
     <t xml:space="preserve">0.57291167974472</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">0.557944476604462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558776021003723</t>
+    <t xml:space="preserve">0.558775961399078</t>
   </si>
   <si>
     <t xml:space="preserve">0.540482699871063</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">0.544640243053436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542977213859558</t>
+    <t xml:space="preserve">0.542977273464203</t>
   </si>
   <si>
     <t xml:space="preserve">0.530504584312439</t>
@@ -2540,70 +2540,70 @@
     <t xml:space="preserve">0.531336069107056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532167613506317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516368865966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511379778385162</t>
+    <t xml:space="preserve">0.532167553901672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516368806362152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511379837989807</t>
   </si>
   <si>
     <t xml:space="preserve">0.505559206008911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508885204792023</t>
+    <t xml:space="preserve">0.508885264396667</t>
   </si>
   <si>
     <t xml:space="preserve">0.502233147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51553738117218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498907119035721</t>
+    <t xml:space="preserve">0.515537321567535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498907148838043</t>
   </si>
   <si>
     <t xml:space="preserve">0.493918001651764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494749575853348</t>
+    <t xml:space="preserve">0.494749546051025</t>
   </si>
   <si>
     <t xml:space="preserve">0.500570118427277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483939945697784</t>
+    <t xml:space="preserve">0.48393988609314</t>
   </si>
   <si>
     <t xml:space="preserve">0.465646624565125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466478139162064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461489081382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460657566785812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473961740732193</t>
+    <t xml:space="preserve">0.466478109359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461489111185074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46065753698349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473961770534515</t>
   </si>
   <si>
     <t xml:space="preserve">0.473130285739899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486434429883957</t>
+    <t xml:space="preserve">0.486434400081635</t>
   </si>
   <si>
     <t xml:space="preserve">0.489760518074036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503064632415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50472766160965</t>
+    <t xml:space="preserve">0.503064692020416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504727721214294</t>
   </si>
   <si>
     <t xml:space="preserve">0.506390750408173</t>
@@ -2612,61 +2612,61 @@
     <t xml:space="preserve">0.510548293590546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503896176815033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495581090450287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484771460294724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482276886701584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491423487663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497244030237198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487265974283218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493086487054825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483108371496201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478119343519211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475624799728394</t>
+    <t xml:space="preserve">0.503896236419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495581030845642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484771430492401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482276856899261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491423547267914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497244119644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487265944480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493086516857147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483108341693878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478119283914566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475624829530716</t>
   </si>
   <si>
     <t xml:space="preserve">0.476456314325333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529673099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523852527141571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528010070323944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533830583095551</t>
+    <t xml:space="preserve">0.529673039913177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523852407932281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528010010719299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533830642700195</t>
   </si>
   <si>
     <t xml:space="preserve">0.527178525924683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547966241836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528841555118561</t>
+    <t xml:space="preserve">0.547966361045837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528841495513916</t>
   </si>
   <si>
     <t xml:space="preserve">0.525515496730804</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">0.554618418216705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588710367679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57540625333786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577069222927094</t>
+    <t xml:space="preserve">0.588710427284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575406134128571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577069282531738</t>
   </si>
   <si>
     <t xml:space="preserve">0.570417106151581</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">0.585384368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57790070772171</t>
+    <t xml:space="preserve">0.577900767326355</t>
   </si>
   <si>
     <t xml:space="preserve">0.58039528131485</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">0.550460875034332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556281447410583</t>
+    <t xml:space="preserve">0.556281507015228</t>
   </si>
   <si>
     <t xml:space="preserve">0.545471787452698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567922651767731</t>
+    <t xml:space="preserve">0.567922592163086</t>
   </si>
   <si>
     <t xml:space="preserve">0.566259562969208</t>
@@ -2723,19 +2723,19 @@
     <t xml:space="preserve">0.56459653377533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549629330635071</t>
+    <t xml:space="preserve">0.549629390239716</t>
   </si>
   <si>
     <t xml:space="preserve">0.539651155471802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536325097084045</t>
+    <t xml:space="preserve">0.53632515668869</t>
   </si>
   <si>
     <t xml:space="preserve">0.532999098300934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524684011936188</t>
+    <t xml:space="preserve">0.524683952331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.509716749191284</t>
@@ -2747,55 +2747,55 @@
     <t xml:space="preserve">0.521357893943787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513874292373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522189497947693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513042807579041</t>
+    <t xml:space="preserve">0.513874351978302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522189438343048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513042867183685</t>
   </si>
   <si>
     <t xml:space="preserve">0.52052640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52302098274231</t>
+    <t xml:space="preserve">0.523020923137665</t>
   </si>
   <si>
     <t xml:space="preserve">0.519694924354553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508053719997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488097488880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488929003477097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492254972457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496412575244904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49059197306633</t>
+    <t xml:space="preserve">0.508053779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488097429275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488928973674774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492255032062531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496412634849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490592002868652</t>
   </si>
   <si>
     <t xml:space="preserve">0.485602915287018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480613857507706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47479322552681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454005479812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478950828313828</t>
+    <t xml:space="preserve">0.480613827705383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474793285131454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4540054500103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478950798511505</t>
   </si>
   <si>
     <t xml:space="preserve">0.458163022994995</t>
@@ -2804,37 +2804,37 @@
     <t xml:space="preserve">0.44901642203331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439869731664658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439038217067719</t>
+    <t xml:space="preserve">0.43986976146698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439038246870041</t>
   </si>
   <si>
     <t xml:space="preserve">0.419913470745087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422408014535904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424071043729782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411598384380341</t>
+    <t xml:space="preserve">0.422408044338226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42407101392746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411598354578018</t>
   </si>
   <si>
     <t xml:space="preserve">0.41118261218071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395799607038498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377090603113174</t>
+    <t xml:space="preserve">0.395799666643143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377090632915497</t>
   </si>
   <si>
     <t xml:space="preserve">0.365033686161041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40203595161438</t>
+    <t xml:space="preserve">0.402035981416702</t>
   </si>
   <si>
     <t xml:space="preserve">0.413677155971527</t>
@@ -2843,16 +2843,16 @@
     <t xml:space="preserve">0.407440811395645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412429869174957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431554645299911</t>
+    <t xml:space="preserve">0.412429839372635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431554615497589</t>
   </si>
   <si>
     <t xml:space="preserve">0.429891616106033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432386159896851</t>
+    <t xml:space="preserve">0.432386130094528</t>
   </si>
   <si>
     <t xml:space="preserve">0.451510936021805</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">0.443195819854736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448184847831726</t>
+    <t xml:space="preserve">0.448184877634048</t>
   </si>
   <si>
     <t xml:space="preserve">0.446521878242493</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">0.440701246261597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434880703687668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424902528524399</t>
+    <t xml:space="preserve">0.434880673885345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424902558326721</t>
   </si>
   <si>
     <t xml:space="preserve">0.444858849048615</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">0.445690363645554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463152050971985</t>
+    <t xml:space="preserve">0.463152080774307</t>
   </si>
   <si>
     <t xml:space="preserve">0.481445372104645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477287828922272</t>
+    <t xml:space="preserve">0.477287799119949</t>
   </si>
   <si>
     <t xml:space="preserve">0.470635682344437</t>
@@ -2909,10 +2909,10 @@
     <t xml:space="preserve">0.429060101509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421576499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409935355186462</t>
+    <t xml:space="preserve">0.421576529741287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40993532538414</t>
   </si>
   <si>
     <t xml:space="preserve">0.430723130702972</t>
@@ -2921,16 +2921,16 @@
     <t xml:space="preserve">0.427397072315216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415755927562714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433217704296112</t>
+    <t xml:space="preserve">0.415755897760391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43321767449379</t>
   </si>
   <si>
     <t xml:space="preserve">0.452196657657623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446109414100647</t>
+    <t xml:space="preserve">0.446109443902969</t>
   </si>
   <si>
     <t xml:space="preserve">0.439152538776398</t>
@@ -2939,34 +2939,34 @@
     <t xml:space="preserve">0.431326061487198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423499584197998</t>
+    <t xml:space="preserve">0.423499554395676</t>
   </si>
   <si>
     <t xml:space="preserve">0.406542211771011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403063744306564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414368689060211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393932908773422</t>
+    <t xml:space="preserve">0.403063774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414368718862534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3939328789711</t>
   </si>
   <si>
     <t xml:space="preserve">0.391324043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383932381868362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388715207576752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627964019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380888730287552</t>
+    <t xml:space="preserve">0.38393235206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388715237379074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627934217453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380888760089874</t>
   </si>
   <si>
     <t xml:space="preserve">0.387845635414124</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">0.384367167949677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378714710474014</t>
+    <t xml:space="preserve">0.378714740276337</t>
   </si>
   <si>
     <t xml:space="preserve">0.373931884765625</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">0.373062252998352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378279894590378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370888233184814</t>
+    <t xml:space="preserve">0.3782799243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370888203382492</t>
   </si>
   <si>
     <t xml:space="preserve">0.361322522163391</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">0.371323019266129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375671088695526</t>
+    <t xml:space="preserve">0.375671118497849</t>
   </si>
   <si>
     <t xml:space="preserve">0.374366670846939</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">0.367844611406326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366974979639053</t>
+    <t xml:space="preserve">0.366975009441376</t>
   </si>
   <si>
     <t xml:space="preserve">0.364366173744202</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">0.368714213371277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37741032242775</t>
+    <t xml:space="preserve">0.377410292625427</t>
   </si>
   <si>
     <t xml:space="preserve">0.36958384513855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377845108509064</t>
+    <t xml:space="preserve">0.377845138311386</t>
   </si>
   <si>
     <t xml:space="preserve">0.374801486730576</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">0.37523627281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372192680835724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36523574590683</t>
+    <t xml:space="preserve">0.372192621231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365235775709152</t>
   </si>
   <si>
     <t xml:space="preserve">0.376540690660477</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">0.386976003646851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397411316633224</t>
+    <t xml:space="preserve">0.397411286830902</t>
   </si>
   <si>
     <t xml:space="preserve">0.402628988027573</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">0.399150520563126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403498560190201</t>
+    <t xml:space="preserve">0.403498589992523</t>
   </si>
   <si>
     <t xml:space="preserve">0.396541684865952</t>
@@ -3107,13 +3107,13 @@
     <t xml:space="preserve">0.408716231584549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400020182132721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400889724493027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393063247203827</t>
+    <t xml:space="preserve">0.400020122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400889754295349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393063277006149</t>
   </si>
   <si>
     <t xml:space="preserve">0.380019158124924</t>
@@ -3125,28 +3125,28 @@
     <t xml:space="preserve">0.389150023460388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390889227390289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395672112703323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401324540376663</t>
+    <t xml:space="preserve">0.390889257192612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395672082901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401324570178986</t>
   </si>
   <si>
     <t xml:space="preserve">0.396976500749588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400454938411713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390454411506653</t>
+    <t xml:space="preserve">0.400454968214035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390454441308975</t>
   </si>
   <si>
     <t xml:space="preserve">0.387410819530487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383497595787048</t>
+    <t xml:space="preserve">0.383497565984726</t>
   </si>
   <si>
     <t xml:space="preserve">0.382193148136139</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">0.381758362054825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371757864952087</t>
+    <t xml:space="preserve">0.371757835149765</t>
   </si>
   <si>
     <t xml:space="preserve">0.357844114303589</t>
@@ -3164,28 +3164,28 @@
     <t xml:space="preserve">0.366540193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360887706279755</t>
+    <t xml:space="preserve">0.360887736082077</t>
   </si>
   <si>
     <t xml:space="preserve">0.362626940011978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369148999452591</t>
+    <t xml:space="preserve">0.369149029254913</t>
   </si>
   <si>
     <t xml:space="preserve">0.379149526357651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3861064016819</t>
+    <t xml:space="preserve">0.386106371879578</t>
   </si>
   <si>
     <t xml:space="preserve">0.394367665052414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404368191957474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392628461122513</t>
+    <t xml:space="preserve">0.404368221759796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392628490924835</t>
   </si>
   <si>
     <t xml:space="preserve">0.391758888959885</t>
@@ -3194,13 +3194,13 @@
     <t xml:space="preserve">0.395237267017365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385671615600586</t>
+    <t xml:space="preserve">0.385671585798264</t>
   </si>
   <si>
     <t xml:space="preserve">0.39480248093605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388280391693115</t>
+    <t xml:space="preserve">0.388280421495438</t>
   </si>
   <si>
     <t xml:space="preserve">0.398373305797577</t>
@@ -69174,7 +69174,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6912037037</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>326238</v>
@@ -69195,6 +69195,32 @@
         <v>1265</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.691099537</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>61082</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>0.465000003576279</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>0.456999987363815</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>0.458000004291534</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="1266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="1267">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">0.326844841241837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323679089546204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980766296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313056230545044</t>
+    <t xml:space="preserve">0.323679059743881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980736494064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313056260347366</t>
   </si>
   <si>
     <t xml:space="preserve">0.304966032505035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299760162830353</t>
+    <t xml:space="preserve">0.29976013302803</t>
   </si>
   <si>
     <t xml:space="preserve">0.309538811445236</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">0.287097215652466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274363934993744</t>
+    <t xml:space="preserve">0.274363905191422</t>
   </si>
   <si>
     <t xml:space="preserve">0.278655260801315</t>
@@ -80,28 +80,28 @@
     <t xml:space="preserve">0.265288829803467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260645776987076</t>
+    <t xml:space="preserve">0.260645747184753</t>
   </si>
   <si>
     <t xml:space="preserve">0.270846426486969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269087672233582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272956937551498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270142883062363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265921950340271</t>
+    <t xml:space="preserve">0.269087702035904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272956907749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270142912864685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265921920537949</t>
   </si>
   <si>
     <t xml:space="preserve">0.290825754404068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288433879613876</t>
+    <t xml:space="preserve">0.288433820009232</t>
   </si>
   <si>
     <t xml:space="preserve">0.294061839580536</t>
@@ -110,106 +110,106 @@
     <t xml:space="preserve">0.276404082775116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273167937994003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262545138597488</t>
+    <t xml:space="preserve">0.273167997598648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262545168399811</t>
   </si>
   <si>
     <t xml:space="preserve">0.260293990373611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246927559375763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246224075555801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239751860499382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240103617310524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271549940109253</t>
+    <t xml:space="preserve">0.246927499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246224015951157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239751875400543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240103647112846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271549969911575</t>
   </si>
   <si>
     <t xml:space="preserve">0.276122659444809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274645298719406</t>
+    <t xml:space="preserve">0.274645328521729</t>
   </si>
   <si>
     <t xml:space="preserve">0.277881413698196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270987153053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281539618968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277177900075912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26331901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2680324614048</t>
+    <t xml:space="preserve">0.270987093448639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281539559364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277177929878235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263318985700607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268032431602478</t>
   </si>
   <si>
     <t xml:space="preserve">0.28210237622261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295468777418137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293358325958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291740328073502</t>
+    <t xml:space="preserve">0.295468837022781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293358355760574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291740298271179</t>
   </si>
   <si>
     <t xml:space="preserve">0.288644880056381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288504183292389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281469255685806</t>
+    <t xml:space="preserve">0.288504242897034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281469196081161</t>
   </si>
   <si>
     <t xml:space="preserve">0.277248233556747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278373897075653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287026882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297368258237839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295820623636246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307217240333557</t>
+    <t xml:space="preserve">0.278373837471008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287026822566986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297368288040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295820593833923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307217210531235</t>
   </si>
   <si>
     <t xml:space="preserve">0.305669546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31375977396965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320443004369736</t>
+    <t xml:space="preserve">0.313759744167328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320442974567413</t>
   </si>
   <si>
     <t xml:space="preserve">0.317417949438095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316573739051819</t>
+    <t xml:space="preserve">0.316573709249496</t>
   </si>
   <si>
     <t xml:space="preserve">0.306161999702454</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">0.310945779085159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311438202857971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301800280809402</t>
+    <t xml:space="preserve">0.311438232660294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30180025100708</t>
   </si>
   <si>
     <t xml:space="preserve">0.288011759519577</t>
@@ -239,22 +239,22 @@
     <t xml:space="preserve">0.291880995035172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30137825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311649233102798</t>
+    <t xml:space="preserve">0.301378220319748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311649262905121</t>
   </si>
   <si>
     <t xml:space="preserve">0.31024232506752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311508595943451</t>
+    <t xml:space="preserve">0.311508566141129</t>
   </si>
   <si>
     <t xml:space="preserve">0.314533621072769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316644132137299</t>
+    <t xml:space="preserve">0.316644102334976</t>
   </si>
   <si>
     <t xml:space="preserve">0.318684250116348</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">0.330573350191116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330643713474274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334161132574081</t>
+    <t xml:space="preserve">0.330643683671951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334161192178726</t>
   </si>
   <si>
     <t xml:space="preserve">0.333528012037277</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">0.327126204967499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323538392782211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318543583154678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319247037172318</t>
+    <t xml:space="preserve">0.323538333177567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318543553352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319247007369995</t>
   </si>
   <si>
     <t xml:space="preserve">0.323116272687912</t>
@@ -293,52 +293,52 @@
     <t xml:space="preserve">0.321005761623383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324874967336655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323749452829361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325015753507614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321076154708862</t>
+    <t xml:space="preserve">0.324875026941299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323749423027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325015723705292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32107612490654</t>
   </si>
   <si>
     <t xml:space="preserve">0.326774477958679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331769287586212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344713687896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34204038977623</t>
+    <t xml:space="preserve">0.33176925778389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344713628292084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342040330171585</t>
   </si>
   <si>
     <t xml:space="preserve">0.338030427694321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352100342512131</t>
+    <t xml:space="preserve">0.352100372314453</t>
   </si>
   <si>
     <t xml:space="preserve">0.354914307594299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351678311824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350341618061066</t>
+    <t xml:space="preserve">0.351678252220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350341647863388</t>
   </si>
   <si>
     <t xml:space="preserve">0.343306660652161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343165934085846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341196149587631</t>
+    <t xml:space="preserve">0.343165963888168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341196119785309</t>
   </si>
   <si>
     <t xml:space="preserve">0.340211272239685</t>
@@ -350,37 +350,37 @@
     <t xml:space="preserve">0.323537766933441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309325873851776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312153786420822</t>
+    <t xml:space="preserve">0.309325844049454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312153726816177</t>
   </si>
   <si>
     <t xml:space="preserve">0.308890819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311936229467392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325277954339981</t>
+    <t xml:space="preserve">0.31193619966507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325277984142303</t>
   </si>
   <si>
     <t xml:space="preserve">0.322232604026794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318607091903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324190378189087</t>
+    <t xml:space="preserve">0.318607062101364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324190348386765</t>
   </si>
   <si>
     <t xml:space="preserve">0.307223081588745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299102038145065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299464553594589</t>
+    <t xml:space="preserve">0.299102008342743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299464583396912</t>
   </si>
   <si>
     <t xml:space="preserve">0.313096404075623</t>
@@ -389,49 +389,49 @@
     <t xml:space="preserve">0.320854872465134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318027049303055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319042176008224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318317085504532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309543401002884</t>
+    <t xml:space="preserve">0.31802698969841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319042205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318317055702209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309543430805206</t>
   </si>
   <si>
     <t xml:space="preserve">0.311791181564331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310558587312698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311066091060638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322087585926056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319767266511917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318172037601471</t>
+    <t xml:space="preserve">0.310558527708054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311066061258316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322087556123734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31976729631424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318172097206116</t>
   </si>
   <si>
     <t xml:space="preserve">0.309978455305099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306715548038483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305627912282944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301784932613373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300914764404297</t>
+    <t xml:space="preserve">0.306715577840805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305627882480621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301784873008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300914734601974</t>
   </si>
   <si>
     <t xml:space="preserve">0.298739463090897</t>
@@ -440,31 +440,31 @@
     <t xml:space="preserve">0.298014372587204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291488498449326</t>
+    <t xml:space="preserve">0.291488528251648</t>
   </si>
   <si>
     <t xml:space="preserve">0.294316381216049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304467767477036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301204830408096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302727490663528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303815126419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300624758005142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297434329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299682140350342</t>
+    <t xml:space="preserve">0.304467707872391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301204770803452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302727520465851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30381515622139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30062472820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29743430018425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299682080745697</t>
   </si>
   <si>
     <t xml:space="preserve">0.301929891109467</t>
@@ -473,28 +473,28 @@
     <t xml:space="preserve">0.301712334156036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30236491560936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300117135047913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302219957113266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297144263982773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295621573925018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293663829565048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297289282083511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291706085205078</t>
+    <t xml:space="preserve">0.302364975214005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300117164850235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302219927310944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29714423418045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295621544122696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293663769960403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297289252281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291706055402756</t>
   </si>
   <si>
     <t xml:space="preserve">0.292358636856079</t>
@@ -503,28 +503,28 @@
     <t xml:space="preserve">0.290038347244263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287500470876694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292648702859879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287645518779755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295041471719742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29156106710434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294533908367157</t>
+    <t xml:space="preserve">0.287500500679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292648673057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287645488977432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295041531324387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291561007499695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294533878564835</t>
   </si>
   <si>
     <t xml:space="preserve">0.289313226938248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287935584783554</t>
+    <t xml:space="preserve">0.287935554981232</t>
   </si>
   <si>
     <t xml:space="preserve">0.283004909753799</t>
@@ -533,10 +533,10 @@
     <t xml:space="preserve">0.287427991628647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282859891653061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275826424360275</t>
+    <t xml:space="preserve">0.282859861850739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275826454162598</t>
   </si>
   <si>
     <t xml:space="preserve">0.279161900281906</t>
@@ -548,58 +548,58 @@
     <t xml:space="preserve">0.273288637399673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27952441573143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282062292098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283802479505539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282134771347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287137985229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292866200208664</t>
+    <t xml:space="preserve">0.279524445533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282062262296677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283802509307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282134741544724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28713795542717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292866170406342</t>
   </si>
   <si>
     <t xml:space="preserve">0.301422327756882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295839101076126</t>
+    <t xml:space="preserve">0.295839041471481</t>
   </si>
   <si>
     <t xml:space="preserve">0.296564191579819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300262182950974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297071784734726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292938709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298812001943588</t>
+    <t xml:space="preserve">0.300262153148651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297071754932404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292938739061356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298811972141266</t>
   </si>
   <si>
     <t xml:space="preserve">0.296056628227234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31019601225853</t>
+    <t xml:space="preserve">0.310195952653885</t>
   </si>
   <si>
     <t xml:space="preserve">0.306425482034683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302509993314743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306062966585159</t>
+    <t xml:space="preserve">0.302509963512421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306062936782837</t>
   </si>
   <si>
     <t xml:space="preserve">0.307078093290329</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">0.301639884710312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294098883867264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283077389001846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287863045930862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289603263139725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285615265369415</t>
+    <t xml:space="preserve">0.294098854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283077418804169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287863075733185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289603292942047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285615235567093</t>
   </si>
   <si>
     <t xml:space="preserve">0.2839475274086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28880563378334</t>
+    <t xml:space="preserve">0.288805663585663</t>
   </si>
   <si>
     <t xml:space="preserve">0.293736338615417</t>
@@ -635,22 +635,22 @@
     <t xml:space="preserve">0.290835946798325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283512473106384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281409710645676</t>
+    <t xml:space="preserve">0.28351241350174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281409680843353</t>
   </si>
   <si>
     <t xml:space="preserve">0.280684620141983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279016852378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273796200752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291416019201279</t>
+    <t xml:space="preserve">0.279016882181168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273796170949936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291415989398956</t>
   </si>
   <si>
     <t xml:space="preserve">0.295114010572433</t>
@@ -659,28 +659,28 @@
     <t xml:space="preserve">0.290545910596848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288588136434555</t>
+    <t xml:space="preserve">0.288588106632233</t>
   </si>
   <si>
     <t xml:space="preserve">0.292213618755341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292141109704971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294388920068741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29939204454422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296491682529449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303597658872604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309615910053253</t>
+    <t xml:space="preserve">0.292141139507294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294388890266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299392074346542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296491652727127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303597629070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309615880250931</t>
   </si>
   <si>
     <t xml:space="preserve">0.307440608739853</t>
@@ -692,64 +692,64 @@
     <t xml:space="preserve">0.331513792276382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331368803977966</t>
+    <t xml:space="preserve">0.331368774175644</t>
   </si>
   <si>
     <t xml:space="preserve">0.345000594854355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349786192178726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358342319726944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354209333658218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349641233682632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352396577596664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35529699921608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359430015087128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352686583995819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346885830163956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343187868595123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346160709857941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346595823764801</t>
+    <t xml:space="preserve">0.349786221981049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358342379331589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354209303855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34964120388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352396547794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355296939611435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35943004488945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352686613798141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346885859966278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343187838792801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346160769462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346595793962479</t>
   </si>
   <si>
     <t xml:space="preserve">0.346450805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344348043203354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350221306085587</t>
+    <t xml:space="preserve">0.344348013401031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350221246480942</t>
   </si>
   <si>
     <t xml:space="preserve">0.350946366786957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388288795948029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397715091705322</t>
+    <t xml:space="preserve">0.388288766145706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397715061903</t>
   </si>
   <si>
     <t xml:space="preserve">0.379950225353241</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">0.382125496864319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374874532222748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37342432141304</t>
+    <t xml:space="preserve">0.37487456202507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373424381017685</t>
   </si>
   <si>
     <t xml:space="preserve">0.377412378787994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373061805963516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369798839092255</t>
+    <t xml:space="preserve">0.373061835765839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369798868894577</t>
   </si>
   <si>
     <t xml:space="preserve">0.383575677871704</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">0.369436323642731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369073748588562</t>
+    <t xml:space="preserve">0.369073778390884</t>
   </si>
   <si>
     <t xml:space="preserve">0.35819736123085</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">0.377049803733826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412579536437988</t>
+    <t xml:space="preserve">0.412579566240311</t>
   </si>
   <si>
     <t xml:space="preserve">0.382488042116165</t>
@@ -800,124 +800,124 @@
     <t xml:space="preserve">0.40061542391777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394452154636383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385751008987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393726974725723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390464127063751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384300768375397</t>
+    <t xml:space="preserve">0.394452184438705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385750949382782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39372706413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390464097261429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384300738573074</t>
   </si>
   <si>
     <t xml:space="preserve">0.39155176281929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387563735246658</t>
+    <t xml:space="preserve">0.387563705444336</t>
   </si>
   <si>
     <t xml:space="preserve">0.390826612710953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395177215337753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393364518880844</t>
+    <t xml:space="preserve">0.395177274942398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393364489078522</t>
   </si>
   <si>
     <t xml:space="preserve">0.397352516651154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398802697658539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395539700984955</t>
+    <t xml:space="preserve">0.398802727460861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395539730787277</t>
   </si>
   <si>
     <t xml:space="preserve">0.396627426147461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398440152406693</t>
+    <t xml:space="preserve">0.39844012260437</t>
   </si>
   <si>
     <t xml:space="preserve">0.395902335643768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393001914024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398077696561813</t>
+    <t xml:space="preserve">0.393001973628998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398077636957169</t>
   </si>
   <si>
     <t xml:space="preserve">0.401703089475632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392276793718338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387201130390167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386476039886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382850617170334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394089609384537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389376431703568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381762951612473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381037831306458</t>
+    <t xml:space="preserve">0.392276853322983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387201189994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386476069688797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382850587368011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394089579582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38937646150589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38176292181015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38103786110878</t>
   </si>
   <si>
     <t xml:space="preserve">0.386838614940643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388651341199875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385025858879089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391189217567444</t>
+    <t xml:space="preserve">0.38865140080452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385025888681412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391189187765121</t>
   </si>
   <si>
     <t xml:space="preserve">0.392639368772507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425631254911423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419105350971222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445208877325058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435057550668716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442308455705643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432611972093582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413592010736465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408370822668076</t>
+    <t xml:space="preserve">0.425631284713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419105410575867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445208817720413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435057491064072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442308485507965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432612001895905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413591921329498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408370792865753</t>
   </si>
   <si>
     <t xml:space="preserve">0.406878978013992</t>
@@ -926,118 +926,118 @@
     <t xml:space="preserve">0.402776688337326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399047255516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400539010763168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395317852497101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396809637546539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396063715219498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393080174922943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388604909181595</t>
+    <t xml:space="preserve">0.399047285318375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400539040565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395317792892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396809607744217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39606374502182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393080204725266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388604938983917</t>
   </si>
   <si>
     <t xml:space="preserve">0.387859016656876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379654258489609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381146043539047</t>
+    <t xml:space="preserve">0.379654318094254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38114607334137</t>
   </si>
   <si>
     <t xml:space="preserve">0.383010774850845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387486070394516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384875446557999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383756667375565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386740148067474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390096634626389</t>
+    <t xml:space="preserve">0.387486129999161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384875476360321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383756697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386740207672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390096664428711</t>
   </si>
   <si>
     <t xml:space="preserve">0.394944906234741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403522521257401</t>
+    <t xml:space="preserve">0.403522551059723</t>
   </si>
   <si>
     <t xml:space="preserve">0.410235524177551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407251983880997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407624930143356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408743739128113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406506061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400912016630173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394199073314667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398674309253693</t>
+    <t xml:space="preserve">0.407252013683319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407624959945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40874370932579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4065061211586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400911957025528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394199043512344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39867427945137</t>
   </si>
   <si>
     <t xml:space="preserve">0.39084255695343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392334312200546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388231933116913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387113124132156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391588389873505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389350831508636</t>
+    <t xml:space="preserve">0.392334342002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388231962919235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387113153934479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391588419675827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389350801706314</t>
   </si>
   <si>
     <t xml:space="preserve">0.38562136888504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38077312707901</t>
+    <t xml:space="preserve">0.380773156881332</t>
   </si>
   <si>
     <t xml:space="preserve">0.385248422622681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383383721113205</t>
+    <t xml:space="preserve">0.383383750915527</t>
   </si>
   <si>
     <t xml:space="preserve">0.397928446531296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409489721059799</t>
+    <t xml:space="preserve">0.409489661455154</t>
   </si>
   <si>
     <t xml:space="preserve">0.410981416702271</t>
@@ -1046,55 +1046,55 @@
     <t xml:space="preserve">0.414337813854218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415083765983582</t>
+    <t xml:space="preserve">0.415083736181259</t>
   </si>
   <si>
     <t xml:space="preserve">0.416575521230698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415829628705978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4240343272686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439324885606766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866109371185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428882539272308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420304864645004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421796649694443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428509712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454988449811935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44529202580452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444546103477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440443754196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449767202138901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459463715553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460955530405045</t>
+    <t xml:space="preserve">0.415829598903656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424034297466278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439324975013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866139173508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428882569074631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420304894447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421796709299088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428509622812271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454988539218903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445291996002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4445461332798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440443724393845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449767291545868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459463775157928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460955500602722</t>
   </si>
   <si>
     <t xml:space="preserve">0.469533145427704</t>
@@ -1103,31 +1103,31 @@
     <t xml:space="preserve">0.466549664735794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474008500576019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474754393100739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348438024521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48594257235527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482586115598679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4855697453022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509437918663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511302649974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521744906902313</t>
+    <t xml:space="preserve">0.474008470773697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474754363298416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480348497629166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485942602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482586085796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485569685697556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50943797826767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511302590370178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521745026111603</t>
   </si>
   <si>
     <t xml:space="preserve">0.512794375419617</t>
@@ -1139,49 +1139,49 @@
     <t xml:space="preserve">0.511675536632538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506081342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501233160495758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502352058887482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495266050100327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491536736488342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477737963199615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478483766317368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481094360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492282658815384</t>
+    <t xml:space="preserve">0.506081402301788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501233220100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502351999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495266169309616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491536676883698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477737903594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478483825922012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481094270944595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492282629013062</t>
   </si>
   <si>
     <t xml:space="preserve">0.499741464853287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493774354457855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495639026165009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507946133613586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500114321708679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493028491735458</t>
+    <t xml:space="preserve">0.493774443864822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495639085769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507946074008942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500114262104034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493028432130814</t>
   </si>
   <si>
     <t xml:space="preserve">0.50869208574295</t>
@@ -1190,13 +1190,13 @@
     <t xml:space="preserve">0.503470838069916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508319020271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507200241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510183811187744</t>
+    <t xml:space="preserve">0.508319139480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507200300693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510183870792389</t>
   </si>
   <si>
     <t xml:space="preserve">0.513167381286621</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">0.501606166362762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498249679803848</t>
+    <t xml:space="preserve">0.498249650001526</t>
   </si>
   <si>
     <t xml:space="preserve">0.510929703712463</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">0.531068563461304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557920277118683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554936826229095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559412121772766</t>
+    <t xml:space="preserve">0.557920217514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554936766624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559412062168121</t>
   </si>
   <si>
     <t xml:space="preserve">0.56537914276123</t>
@@ -1247,37 +1247,37 @@
     <t xml:space="preserve">0.577313244342804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583280324935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59148496389389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585517883300781</t>
+    <t xml:space="preserve">0.583280205726624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591485023498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585518002510071</t>
   </si>
   <si>
     <t xml:space="preserve">0.575075566768646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612369775772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556428551673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551953256130219</t>
+    <t xml:space="preserve">0.61236971616745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556428492069244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551953315734863</t>
   </si>
   <si>
     <t xml:space="preserve">0.548223793506622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53479790687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521372079849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505708456039429</t>
+    <t xml:space="preserve">0.534797966480255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521372020244598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505708575248718</t>
   </si>
   <si>
     <t xml:space="preserve">0.528084933757782</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">0.545240342617035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522863745689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517642617225647</t>
+    <t xml:space="preserve">0.522863686084747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517642557621002</t>
   </si>
   <si>
     <t xml:space="preserve">0.532560288906097</t>
@@ -1298,127 +1298,127 @@
     <t xml:space="preserve">0.531814396381378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523609757423401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516150832176208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512421369552612</t>
+    <t xml:space="preserve">0.523609697818756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516150891780853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512421488761902</t>
   </si>
   <si>
     <t xml:space="preserve">0.519134402275085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498995542526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463193118572235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469906091690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476619124412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477364927530289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494520246982574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490044921636581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47885674238205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478110790252686</t>
+    <t xml:space="preserve">0.498995631933212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463193207979202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469906181097031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476619064807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477364987134933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494520276784897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490045011043549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478856772184372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47811084985733</t>
   </si>
   <si>
     <t xml:space="preserve">0.468414425849915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481840252876282</t>
+    <t xml:space="preserve">0.481840282678604</t>
   </si>
   <si>
     <t xml:space="preserve">0.484077930450439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475127309560776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473635494709015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474381387233734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484823733568192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487061470746994</t>
+    <t xml:space="preserve">0.475127369165421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473635613918304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474381446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484823763370514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487061411142349</t>
   </si>
   <si>
     <t xml:space="preserve">0.48333203792572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50421667098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504962563514709</t>
+    <t xml:space="preserve">0.504216730594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504962682723999</t>
   </si>
   <si>
     <t xml:space="preserve">0.496757864952087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497503787279129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486315548419952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500487327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454242587089539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465430796146393</t>
+    <t xml:space="preserve">0.497503817081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48631551861763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500487387180328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454242646694183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46543088555336</t>
   </si>
   <si>
     <t xml:space="preserve">0.452004909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457226037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458717852830887</t>
+    <t xml:space="preserve">0.457226067781448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458717912435532</t>
   </si>
   <si>
     <t xml:space="preserve">0.462447285652161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455734342336655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457972049713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485727876424789</t>
+    <t xml:space="preserve">0.455734312534332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45797199010849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485727906227112</t>
   </si>
   <si>
     <t xml:space="preserve">0.484185934066772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474933922290802</t>
+    <t xml:space="preserve">0.474933952093124</t>
   </si>
   <si>
     <t xml:space="preserve">0.469536989927292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464911013841629</t>
+    <t xml:space="preserve">0.464910984039307</t>
   </si>
   <si>
     <t xml:space="preserve">0.461055934429169</t>
@@ -1427,28 +1427,28 @@
     <t xml:space="preserve">0.463369011878967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459513962268829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45797199010849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458743035793304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447949022054672</t>
+    <t xml:space="preserve">0.459514021873474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457971960306168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458743005990982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447949051856995</t>
   </si>
   <si>
     <t xml:space="preserve">0.451033025979996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454887986183167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.446407049894333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441781044006348</t>
+    <t xml:space="preserve">0.454888015985489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.446407079696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441781103610992</t>
   </si>
   <si>
     <t xml:space="preserve">0.443323075771332</t>
@@ -1457,55 +1457,55 @@
     <t xml:space="preserve">0.494208812713623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474162936210632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481101900339127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489582866430283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476475954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464139968156815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461826920509338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456430017948151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454117029905319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466453015804291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46722400188446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439468085765839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442552030086517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452575027942657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453346014022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4410100877285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437926054000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433300107717514</t>
+    <t xml:space="preserve">0.474162966012955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481101959943771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489582896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476475894451141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464139997959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461826950311661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456429988145828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454117059707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466452926397324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467223942279816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439468055963516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442552089691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45257505774498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45334604382515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441010117530823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437926113605499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433300137519836</t>
   </si>
   <si>
     <t xml:space="preserve">0.430987119674683</t>
@@ -1517,31 +1517,31 @@
     <t xml:space="preserve">0.435613095760345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444865107536316</t>
+    <t xml:space="preserve">0.444865047931671</t>
   </si>
   <si>
     <t xml:space="preserve">0.460285007953644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451804041862488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470307916402817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471849948167801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465681999921799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45720100402832</t>
+    <t xml:space="preserve">0.45180407166481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470307976007462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471849918365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465681970119476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457200974225998</t>
   </si>
   <si>
     <t xml:space="preserve">0.462597966194153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455659031867981</t>
+    <t xml:space="preserve">0.455658972263336</t>
   </si>
   <si>
     <t xml:space="preserve">0.450262039899826</t>
@@ -1550,37 +1550,37 @@
     <t xml:space="preserve">0.449491083621979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437155038118362</t>
+    <t xml:space="preserve">0.437155097723007</t>
   </si>
   <si>
     <t xml:space="preserve">0.440239042043686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426361083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427903175354004</t>
+    <t xml:space="preserve">0.426361113786697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427903145551682</t>
   </si>
   <si>
     <t xml:space="preserve">0.407086193561554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406315237283707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4101702272892</t>
+    <t xml:space="preserve">0.406315207481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410170197486877</t>
   </si>
   <si>
     <t xml:space="preserve">0.404002219438553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407857179641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41094121336937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40014722943306</t>
+    <t xml:space="preserve">0.407857209444046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410941183567047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400147259235382</t>
   </si>
   <si>
     <t xml:space="preserve">0.396292269229889</t>
@@ -1595,19 +1595,19 @@
     <t xml:space="preserve">0.381643325090408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383185356855392</t>
+    <t xml:space="preserve">0.38318532705307</t>
   </si>
   <si>
     <t xml:space="preserve">0.387811332941055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388582319021225</t>
+    <t xml:space="preserve">0.388582289218903</t>
   </si>
   <si>
     <t xml:space="preserve">0.39475029706955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397063285112381</t>
+    <t xml:space="preserve">0.397063255310059</t>
   </si>
   <si>
     <t xml:space="preserve">0.389353275299072</t>
@@ -1619,70 +1619,70 @@
     <t xml:space="preserve">0.385498285293579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375475376844406</t>
+    <t xml:space="preserve">0.375475347042084</t>
   </si>
   <si>
     <t xml:space="preserve">0.366223394870758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351188987493515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345406502485275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348875969648361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36699441075325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372391372919083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36776539683342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162388801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370078355073929</t>
+    <t xml:space="preserve">0.351188957691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345406532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348875910043716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366994380950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37239134311676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367765367031097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162358999252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370078384876251</t>
   </si>
   <si>
     <t xml:space="preserve">0.370463877916336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369692891836166</t>
+    <t xml:space="preserve">0.369692832231522</t>
   </si>
   <si>
     <t xml:space="preserve">0.365837901830673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371620327234268</t>
+    <t xml:space="preserve">0.371620357036591</t>
   </si>
   <si>
     <t xml:space="preserve">0.368536353111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368921875953674</t>
+    <t xml:space="preserve">0.368921905755997</t>
   </si>
   <si>
     <t xml:space="preserve">0.378944844007492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383570849895477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377017319202423</t>
+    <t xml:space="preserve">0.383570820093155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377017349004745</t>
   </si>
   <si>
     <t xml:space="preserve">0.3824143409729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39937624335289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416338175535202</t>
+    <t xml:space="preserve">0.399376273155212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416338235139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.424048155546188</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">0.422506153583527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421735107898712</t>
+    <t xml:space="preserve">0.421735167503357</t>
   </si>
   <si>
     <t xml:space="preserve">0.420964181423187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408628165721893</t>
+    <t xml:space="preserve">0.408628195524216</t>
   </si>
   <si>
     <t xml:space="preserve">0.400918245315552</t>
@@ -1712,19 +1712,19 @@
     <t xml:space="preserve">0.404773235321045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405544281005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411712199449539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412483215332031</t>
+    <t xml:space="preserve">0.405544251203537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411712169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412483245134354</t>
   </si>
   <si>
     <t xml:space="preserve">0.423277199268341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425590127706528</t>
+    <t xml:space="preserve">0.42559015750885</t>
   </si>
   <si>
     <t xml:space="preserve">0.419422209262848</t>
@@ -1742,22 +1742,22 @@
     <t xml:space="preserve">0.41479617357254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413254231214523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409399211406708</t>
+    <t xml:space="preserve">0.413254201412201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40939924120903</t>
   </si>
   <si>
     <t xml:space="preserve">0.395521283149719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393208295106888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392437309026718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391666293144226</t>
+    <t xml:space="preserve">0.393208265304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392437279224396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391666322946548</t>
   </si>
   <si>
     <t xml:space="preserve">0.393979251384735</t>
@@ -1769,55 +1769,55 @@
     <t xml:space="preserve">0.403231233358383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411275923252106</t>
+    <t xml:space="preserve">0.411275893449783</t>
   </si>
   <si>
     <t xml:space="preserve">0.410471081733704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409666270017624</t>
+    <t xml:space="preserve">0.409666240215302</t>
   </si>
   <si>
     <t xml:space="preserve">0.415300130844116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412885636091232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41208079457283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399203240871429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401215344667435</t>
+    <t xml:space="preserve">0.412885665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412080824375153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399203270673752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401215374469757</t>
   </si>
   <si>
     <t xml:space="preserve">0.404032289981842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397995978593826</t>
+    <t xml:space="preserve">0.397996008396149</t>
   </si>
   <si>
     <t xml:space="preserve">0.403227478265762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398398399353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400008141994476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402422606945038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400410562753677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395983874797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39960566163063</t>
+    <t xml:space="preserve">0.39839842915535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400008112192154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40242263674736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400410503149033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395983904600143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399605691432953</t>
   </si>
   <si>
     <t xml:space="preserve">0.418519526720047</t>
@@ -1826,16 +1826,16 @@
     <t xml:space="preserve">0.417714685201645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416909843683243</t>
+    <t xml:space="preserve">0.416909873485565</t>
   </si>
   <si>
     <t xml:space="preserve">0.404837191104889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401617795228958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40725165605545</t>
+    <t xml:space="preserve">0.401617825031281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407251685857773</t>
   </si>
   <si>
     <t xml:space="preserve">0.408056557178497</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">0.397593557834625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391154795885086</t>
+    <t xml:space="preserve">0.391154825687408</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446844339371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426567941904068</t>
+    <t xml:space="preserve">0.42656797170639</t>
   </si>
   <si>
     <t xml:space="preserve">0.433811604976654</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">0.429787367582321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420934081077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428982555866241</t>
+    <t xml:space="preserve">0.420934110879898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428982526063919</t>
   </si>
   <si>
     <t xml:space="preserve">0.437030971050262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434616446495056</t>
+    <t xml:space="preserve">0.434616476297379</t>
   </si>
   <si>
     <t xml:space="preserve">0.430592238903046</t>
@@ -1895,64 +1895,64 @@
     <t xml:space="preserve">0.442664921283722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458761811256409</t>
+    <t xml:space="preserve">0.458761781454086</t>
   </si>
   <si>
     <t xml:space="preserve">0.466810256242752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473249018192291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476468414068222</t>
+    <t xml:space="preserve">0.473249047994614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4764683842659</t>
   </si>
   <si>
     <t xml:space="preserve">0.478882938623428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47566357254982</t>
+    <t xml:space="preserve">0.475663542747498</t>
   </si>
   <si>
     <t xml:space="preserve">0.481297433376312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478078067302704</t>
+    <t xml:space="preserve">0.478078097105026</t>
   </si>
   <si>
     <t xml:space="preserve">0.474858701229095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471639364957809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472444176673889</t>
+    <t xml:space="preserve">0.471639394760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472444206476212</t>
   </si>
   <si>
     <t xml:space="preserve">0.486126571893692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480492651462555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494979828596115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511881530284882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513491332530975</t>
+    <t xml:space="preserve">0.480492621660233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49497988820076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511881649494171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513491272926331</t>
   </si>
   <si>
     <t xml:space="preserve">0.520734906196594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535222113132477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53441721200943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523149430751801</t>
+    <t xml:space="preserve">0.535222172737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534417271614075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523149371147156</t>
   </si>
   <si>
     <t xml:space="preserve">0.515100955963135</t>
@@ -1961,19 +1961,19 @@
     <t xml:space="preserve">0.516710698604584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522344589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556148052215576</t>
+    <t xml:space="preserve">0.522344529628754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556148111820221</t>
   </si>
   <si>
     <t xml:space="preserve">0.555343270301819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551319003105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557757794857025</t>
+    <t xml:space="preserve">0.551319062709808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55775773525238</t>
   </si>
   <si>
     <t xml:space="preserve">0.571440160274506</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">0.56178206205368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560977160930634</t>
+    <t xml:space="preserve">0.560977220535278</t>
   </si>
   <si>
     <t xml:space="preserve">0.552928686141968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554538428783417</t>
+    <t xml:space="preserve">0.554538488388062</t>
   </si>
   <si>
     <t xml:space="preserve">0.59236615896225</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">0.599609732627869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6116823554039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606853365898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602024257183075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614901781082153</t>
+    <t xml:space="preserve">0.611682415008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606853306293488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60202419757843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614901721477509</t>
   </si>
   <si>
     <t xml:space="preserve">0.600414574146271</t>
@@ -2024,97 +2024,97 @@
     <t xml:space="preserve">0.590756475925446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595585525035858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609267890453339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614096879959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60604852437973</t>
+    <t xml:space="preserve">0.595585584640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609267830848694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614096939563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606048464775085</t>
   </si>
   <si>
     <t xml:space="preserve">0.593171000480652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598804831504822</t>
+    <t xml:space="preserve">0.598804891109467</t>
   </si>
   <si>
     <t xml:space="preserve">0.601219415664673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594780683517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603633999824524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610072731971741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59799998998642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630193769931793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631803572177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.646290719509125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655948877334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65997314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689752399921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684118509292603</t>
+    <t xml:space="preserve">0.594780743122101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603633880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610072672367096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598000049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630193829536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631803512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64629065990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65594893693924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.659973084926605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689752340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684118390083313</t>
   </si>
   <si>
     <t xml:space="preserve">0.661582827568054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588341891765594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581098318099976</t>
+    <t xml:space="preserve">0.588341951370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581098258495331</t>
   </si>
   <si>
     <t xml:space="preserve">0.572245001792908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540855944156647</t>
+    <t xml:space="preserve">0.540856063365936</t>
   </si>
   <si>
     <t xml:space="preserve">0.543270587921143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518320322036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526368856430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490955591201782</t>
+    <t xml:space="preserve">0.518320381641388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526368796825409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490955650806427</t>
   </si>
   <si>
     <t xml:space="preserve">0.439445525407791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398800820112228</t>
+    <t xml:space="preserve">0.398800849914551</t>
   </si>
   <si>
     <t xml:space="preserve">0.381496667861938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323145359754562</t>
+    <t xml:space="preserve">0.32314532995224</t>
   </si>
   <si>
     <t xml:space="preserve">0.348095566034317</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">0.303829044103622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282500743865967</t>
+    <t xml:space="preserve">0.282500684261322</t>
   </si>
   <si>
     <t xml:space="preserve">0.288939476013184</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">0.29135400056839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304633945226669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308255732059479</t>
+    <t xml:space="preserve">0.304633915424347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308255702257156</t>
   </si>
   <si>
     <t xml:space="preserve">0.343668907880783</t>
@@ -2147,28 +2147,28 @@
     <t xml:space="preserve">0.37224093079567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355741620063782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373850613832474</t>
+    <t xml:space="preserve">0.355741590261459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373850643634796</t>
   </si>
   <si>
     <t xml:space="preserve">0.391959637403488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37908211350441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375057905912399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384716033935547</t>
+    <t xml:space="preserve">0.379082143306732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375057846307755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384716004133224</t>
   </si>
   <si>
     <t xml:space="preserve">0.386325716972351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374253034591675</t>
+    <t xml:space="preserve">0.374253064393997</t>
   </si>
   <si>
     <t xml:space="preserve">0.362180352210999</t>
@@ -2195,16 +2195,16 @@
     <t xml:space="preserve">0.339644700288773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341254413127899</t>
+    <t xml:space="preserve">0.341254353523254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346083462238312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350912541151047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348497956991196</t>
+    <t xml:space="preserve">0.350912511348724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348497986793518</t>
   </si>
   <si>
     <t xml:space="preserve">0.342864066362381</t>
@@ -2219,19 +2219,19 @@
     <t xml:space="preserve">0.324352622032166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329986572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326767176389694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321938127279282</t>
+    <t xml:space="preserve">0.329986542463303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326767146587372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321938097476959</t>
   </si>
   <si>
     <t xml:space="preserve">0.331596255302429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340449541807175</t>
+    <t xml:space="preserve">0.340449571609497</t>
   </si>
   <si>
     <t xml:space="preserve">0.347693145275116</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">0.35493677854538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369423985481262</t>
+    <t xml:space="preserve">0.36942395567894</t>
   </si>
   <si>
     <t xml:space="preserve">0.382301479578018</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">0.356546431779861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357351273298264</t>
+    <t xml:space="preserve">0.357351332902908</t>
   </si>
   <si>
     <t xml:space="preserve">0.350107699632645</t>
@@ -2273,46 +2273,46 @@
     <t xml:space="preserve">0.346888303756714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342059254646301</t>
+    <t xml:space="preserve">0.342059195041656</t>
   </si>
   <si>
     <t xml:space="preserve">0.337230145931244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328376829624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33562046289444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370228856801987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358156114816666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363790065050125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420129239559174</t>
+    <t xml:space="preserve">0.328376859426498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335620492696762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370228826999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358156144618988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363790035247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420129269361496</t>
   </si>
   <si>
     <t xml:space="preserve">0.424958288669586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437835842370987</t>
+    <t xml:space="preserve">0.437835872173309</t>
   </si>
   <si>
     <t xml:space="preserve">0.444274574518204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445884257555008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482907146215439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560172259807587</t>
+    <t xml:space="preserve">0.445884317159653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482907176017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560172319412231</t>
   </si>
   <si>
     <t xml:space="preserve">0.527978539466858</t>
@@ -2330,31 +2330,31 @@
     <t xml:space="preserve">0.507052540779114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500613689422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494175016880035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502223432064056</t>
+    <t xml:space="preserve">0.500613749027252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494175046682358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502223551273346</t>
   </si>
   <si>
     <t xml:space="preserve">0.537636637687683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52475917339325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510271906852722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49900409579277</t>
+    <t xml:space="preserve">0.524759113788605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510271966457367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499004065990448</t>
   </si>
   <si>
     <t xml:space="preserve">0.492565304040909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487736284732819</t>
+    <t xml:space="preserve">0.487736195325851</t>
   </si>
   <si>
     <t xml:space="preserve">0.484516859054565</t>
@@ -2381,13 +2381,13 @@
     <t xml:space="preserve">0.375862747430801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367009431123734</t>
+    <t xml:space="preserve">0.367009401321411</t>
   </si>
   <si>
     <t xml:space="preserve">0.359765827655792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376667559146881</t>
+    <t xml:space="preserve">0.376667588949203</t>
   </si>
   <si>
     <t xml:space="preserve">0.421738892793655</t>
@@ -2396,19 +2396,19 @@
     <t xml:space="preserve">0.423348635435104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441055208444595</t>
+    <t xml:space="preserve">0.441055178642273</t>
   </si>
   <si>
     <t xml:space="preserve">0.50544285774231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468419969081879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461981147527695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46520060300827</t>
+    <t xml:space="preserve">0.468419998884201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461981207132339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465200573205948</t>
   </si>
   <si>
     <t xml:space="preserve">0.45232304930687</t>
@@ -2417,16 +2417,16 @@
     <t xml:space="preserve">0.455542385578156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450713336467743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460371494293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457152098417282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453932762145996</t>
+    <t xml:space="preserve">0.450713366270065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460371524095535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457152158021927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453932732343674</t>
   </si>
   <si>
     <t xml:space="preserve">0.47968778014183</t>
@@ -2435,13 +2435,13 @@
     <t xml:space="preserve">0.495784670114517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4893459379673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547294855117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565001487731934</t>
+    <t xml:space="preserve">0.489345908164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547294795513153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565001368522644</t>
   </si>
   <si>
     <t xml:space="preserve">0.576269268989563</t>
@@ -2453,16 +2453,16 @@
     <t xml:space="preserve">0.569830477237701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549709320068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567415952682495</t>
+    <t xml:space="preserve">0.549709379673004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56741589307785</t>
   </si>
   <si>
     <t xml:space="preserve">0.545685112476349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558562636375427</t>
+    <t xml:space="preserve">0.558562576770782</t>
   </si>
   <si>
     <t xml:space="preserve">0.544075429439545</t>
@@ -2474,13 +2474,13 @@
     <t xml:space="preserve">0.559367418289185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573854684829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581903159618378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.579488575458527</t>
+    <t xml:space="preserve">0.573854625225067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581903100013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579488635063171</t>
   </si>
   <si>
     <t xml:space="preserve">0.544880270957947</t>
@@ -2489,28 +2489,28 @@
     <t xml:space="preserve">0.552123844623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5480996966362</t>
+    <t xml:space="preserve">0.548099637031555</t>
   </si>
   <si>
     <t xml:space="preserve">0.548904478549957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553733587265015</t>
+    <t xml:space="preserve">0.553733646869659</t>
   </si>
   <si>
     <t xml:space="preserve">0.582058250904083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581226766109467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573743164539337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567091047763824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574649333954</t>
+    <t xml:space="preserve">0.581226825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573743224143982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567091107368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574708938599</t>
   </si>
   <si>
     <t xml:space="preserve">0.57291167974472</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">0.557944476604462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558775961399078</t>
+    <t xml:space="preserve">0.558776021003723</t>
   </si>
   <si>
     <t xml:space="preserve">0.540482699871063</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">0.544640243053436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542977273464203</t>
+    <t xml:space="preserve">0.542977213859558</t>
   </si>
   <si>
     <t xml:space="preserve">0.530504584312439</t>
@@ -2540,70 +2540,70 @@
     <t xml:space="preserve">0.531336069107056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532167553901672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516368806362152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511379837989807</t>
+    <t xml:space="preserve">0.532167613506317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516368865966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511379778385162</t>
   </si>
   <si>
     <t xml:space="preserve">0.505559206008911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508885264396667</t>
+    <t xml:space="preserve">0.508885204792023</t>
   </si>
   <si>
     <t xml:space="preserve">0.502233147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515537321567535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498907148838043</t>
+    <t xml:space="preserve">0.51553738117218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498907119035721</t>
   </si>
   <si>
     <t xml:space="preserve">0.493918001651764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494749546051025</t>
+    <t xml:space="preserve">0.494749575853348</t>
   </si>
   <si>
     <t xml:space="preserve">0.500570118427277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48393988609314</t>
+    <t xml:space="preserve">0.483939945697784</t>
   </si>
   <si>
     <t xml:space="preserve">0.465646624565125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466478109359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461489111185074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46065753698349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473961770534515</t>
+    <t xml:space="preserve">0.466478139162064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461489081382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460657566785812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473961740732193</t>
   </si>
   <si>
     <t xml:space="preserve">0.473130285739899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486434400081635</t>
+    <t xml:space="preserve">0.486434429883957</t>
   </si>
   <si>
     <t xml:space="preserve">0.489760518074036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503064692020416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504727721214294</t>
+    <t xml:space="preserve">0.503064632415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50472766160965</t>
   </si>
   <si>
     <t xml:space="preserve">0.506390750408173</t>
@@ -2612,61 +2612,61 @@
     <t xml:space="preserve">0.510548293590546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503896236419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495581030845642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484771430492401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482276856899261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491423547267914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497244119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487265944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493086516857147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483108341693878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478119283914566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475624829530716</t>
+    <t xml:space="preserve">0.503896176815033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495581090450287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484771460294724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482276886701584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491423487663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497244030237198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487265974283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493086487054825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483108371496201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478119343519211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475624799728394</t>
   </si>
   <si>
     <t xml:space="preserve">0.476456314325333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529673039913177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523852407932281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528010010719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533830642700195</t>
+    <t xml:space="preserve">0.529673099517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523852527141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528010070323944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533830583095551</t>
   </si>
   <si>
     <t xml:space="preserve">0.527178525924683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547966361045837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528841495513916</t>
+    <t xml:space="preserve">0.547966241836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528841555118561</t>
   </si>
   <si>
     <t xml:space="preserve">0.525515496730804</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">0.554618418216705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588710427284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575406134128571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577069282531738</t>
+    <t xml:space="preserve">0.588710367679596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57540625333786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577069222927094</t>
   </si>
   <si>
     <t xml:space="preserve">0.570417106151581</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">0.585384368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577900767326355</t>
+    <t xml:space="preserve">0.57790070772171</t>
   </si>
   <si>
     <t xml:space="preserve">0.58039528131485</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">0.550460875034332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556281507015228</t>
+    <t xml:space="preserve">0.556281447410583</t>
   </si>
   <si>
     <t xml:space="preserve">0.545471787452698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567922592163086</t>
+    <t xml:space="preserve">0.567922651767731</t>
   </si>
   <si>
     <t xml:space="preserve">0.566259562969208</t>
@@ -2723,19 +2723,19 @@
     <t xml:space="preserve">0.56459653377533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549629390239716</t>
+    <t xml:space="preserve">0.549629330635071</t>
   </si>
   <si>
     <t xml:space="preserve">0.539651155471802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53632515668869</t>
+    <t xml:space="preserve">0.536325097084045</t>
   </si>
   <si>
     <t xml:space="preserve">0.532999098300934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524683952331543</t>
+    <t xml:space="preserve">0.524684011936188</t>
   </si>
   <si>
     <t xml:space="preserve">0.509716749191284</t>
@@ -2747,55 +2747,55 @@
     <t xml:space="preserve">0.521357893943787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513874351978302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522189438343048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513042867183685</t>
+    <t xml:space="preserve">0.513874292373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522189497947693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513042807579041</t>
   </si>
   <si>
     <t xml:space="preserve">0.52052640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523020923137665</t>
+    <t xml:space="preserve">0.52302098274231</t>
   </si>
   <si>
     <t xml:space="preserve">0.519694924354553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508053779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488097429275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488928973674774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492255032062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496412634849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490592002868652</t>
+    <t xml:space="preserve">0.508053719997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488097488880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488929003477097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492254972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496412575244904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49059197306633</t>
   </si>
   <si>
     <t xml:space="preserve">0.485602915287018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480613827705383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474793285131454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4540054500103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478950798511505</t>
+    <t xml:space="preserve">0.480613857507706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47479322552681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454005479812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478950828313828</t>
   </si>
   <si>
     <t xml:space="preserve">0.458163022994995</t>
@@ -2804,37 +2804,37 @@
     <t xml:space="preserve">0.44901642203331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43986976146698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439038246870041</t>
+    <t xml:space="preserve">0.439869731664658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439038217067719</t>
   </si>
   <si>
     <t xml:space="preserve">0.419913470745087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422408044338226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42407101392746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411598354578018</t>
+    <t xml:space="preserve">0.422408014535904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424071043729782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411598384380341</t>
   </si>
   <si>
     <t xml:space="preserve">0.41118261218071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395799666643143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377090632915497</t>
+    <t xml:space="preserve">0.395799607038498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377090603113174</t>
   </si>
   <si>
     <t xml:space="preserve">0.365033686161041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402035981416702</t>
+    <t xml:space="preserve">0.40203595161438</t>
   </si>
   <si>
     <t xml:space="preserve">0.413677155971527</t>
@@ -2843,16 +2843,16 @@
     <t xml:space="preserve">0.407440811395645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412429839372635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431554615497589</t>
+    <t xml:space="preserve">0.412429869174957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431554645299911</t>
   </si>
   <si>
     <t xml:space="preserve">0.429891616106033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432386130094528</t>
+    <t xml:space="preserve">0.432386159896851</t>
   </si>
   <si>
     <t xml:space="preserve">0.451510936021805</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">0.443195819854736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448184877634048</t>
+    <t xml:space="preserve">0.448184847831726</t>
   </si>
   <si>
     <t xml:space="preserve">0.446521878242493</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">0.440701246261597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434880673885345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424902558326721</t>
+    <t xml:space="preserve">0.434880703687668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424902528524399</t>
   </si>
   <si>
     <t xml:space="preserve">0.444858849048615</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">0.445690363645554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463152080774307</t>
+    <t xml:space="preserve">0.463152050971985</t>
   </si>
   <si>
     <t xml:space="preserve">0.481445372104645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477287799119949</t>
+    <t xml:space="preserve">0.477287828922272</t>
   </si>
   <si>
     <t xml:space="preserve">0.470635682344437</t>
@@ -2909,10 +2909,10 @@
     <t xml:space="preserve">0.429060101509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421576529741287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40993532538414</t>
+    <t xml:space="preserve">0.421576499938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409935355186462</t>
   </si>
   <si>
     <t xml:space="preserve">0.430723130702972</t>
@@ -2921,16 +2921,16 @@
     <t xml:space="preserve">0.427397072315216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415755897760391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43321767449379</t>
+    <t xml:space="preserve">0.415755927562714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433217704296112</t>
   </si>
   <si>
     <t xml:space="preserve">0.452196657657623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446109443902969</t>
+    <t xml:space="preserve">0.446109414100647</t>
   </si>
   <si>
     <t xml:space="preserve">0.439152538776398</t>
@@ -2939,34 +2939,34 @@
     <t xml:space="preserve">0.431326061487198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423499554395676</t>
+    <t xml:space="preserve">0.423499584197998</t>
   </si>
   <si>
     <t xml:space="preserve">0.406542211771011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403063774108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414368718862534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3939328789711</t>
+    <t xml:space="preserve">0.403063744306564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414368689060211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393932908773422</t>
   </si>
   <si>
     <t xml:space="preserve">0.391324043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38393235206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388715237379074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627934217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380888760089874</t>
+    <t xml:space="preserve">0.383932381868362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388715207576752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627964019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380888730287552</t>
   </si>
   <si>
     <t xml:space="preserve">0.387845635414124</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">0.384367167949677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378714740276337</t>
+    <t xml:space="preserve">0.378714710474014</t>
   </si>
   <si>
     <t xml:space="preserve">0.373931884765625</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">0.373062252998352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3782799243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370888203382492</t>
+    <t xml:space="preserve">0.378279894590378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370888233184814</t>
   </si>
   <si>
     <t xml:space="preserve">0.361322522163391</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">0.371323019266129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375671118497849</t>
+    <t xml:space="preserve">0.375671088695526</t>
   </si>
   <si>
     <t xml:space="preserve">0.374366670846939</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">0.367844611406326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366975009441376</t>
+    <t xml:space="preserve">0.366974979639053</t>
   </si>
   <si>
     <t xml:space="preserve">0.364366173744202</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">0.368714213371277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377410292625427</t>
+    <t xml:space="preserve">0.37741032242775</t>
   </si>
   <si>
     <t xml:space="preserve">0.36958384513855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377845138311386</t>
+    <t xml:space="preserve">0.377845108509064</t>
   </si>
   <si>
     <t xml:space="preserve">0.374801486730576</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">0.37523627281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372192621231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365235775709152</t>
+    <t xml:space="preserve">0.372192680835724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36523574590683</t>
   </si>
   <si>
     <t xml:space="preserve">0.376540690660477</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">0.386976003646851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397411286830902</t>
+    <t xml:space="preserve">0.397411316633224</t>
   </si>
   <si>
     <t xml:space="preserve">0.402628988027573</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">0.399150520563126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403498589992523</t>
+    <t xml:space="preserve">0.403498560190201</t>
   </si>
   <si>
     <t xml:space="preserve">0.396541684865952</t>
@@ -3107,13 +3107,13 @@
     <t xml:space="preserve">0.408716231584549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400020122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400889754295349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393063277006149</t>
+    <t xml:space="preserve">0.400020182132721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400889724493027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393063247203827</t>
   </si>
   <si>
     <t xml:space="preserve">0.380019158124924</t>
@@ -3125,28 +3125,28 @@
     <t xml:space="preserve">0.389150023460388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390889257192612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395672082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401324570178986</t>
+    <t xml:space="preserve">0.390889227390289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395672112703323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401324540376663</t>
   </si>
   <si>
     <t xml:space="preserve">0.396976500749588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400454968214035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390454441308975</t>
+    <t xml:space="preserve">0.400454938411713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390454411506653</t>
   </si>
   <si>
     <t xml:space="preserve">0.387410819530487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383497565984726</t>
+    <t xml:space="preserve">0.383497595787048</t>
   </si>
   <si>
     <t xml:space="preserve">0.382193148136139</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">0.381758362054825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371757835149765</t>
+    <t xml:space="preserve">0.371757864952087</t>
   </si>
   <si>
     <t xml:space="preserve">0.357844114303589</t>
@@ -3164,28 +3164,28 @@
     <t xml:space="preserve">0.366540193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360887736082077</t>
+    <t xml:space="preserve">0.360887706279755</t>
   </si>
   <si>
     <t xml:space="preserve">0.362626940011978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369149029254913</t>
+    <t xml:space="preserve">0.369148999452591</t>
   </si>
   <si>
     <t xml:space="preserve">0.379149526357651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386106371879578</t>
+    <t xml:space="preserve">0.3861064016819</t>
   </si>
   <si>
     <t xml:space="preserve">0.394367665052414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404368221759796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392628490924835</t>
+    <t xml:space="preserve">0.404368191957474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392628461122513</t>
   </si>
   <si>
     <t xml:space="preserve">0.391758888959885</t>
@@ -3194,13 +3194,13 @@
     <t xml:space="preserve">0.395237267017365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385671585798264</t>
+    <t xml:space="preserve">0.385671615600586</t>
   </si>
   <si>
     <t xml:space="preserve">0.39480248093605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388280421495438</t>
+    <t xml:space="preserve">0.388280391693115</t>
   </si>
   <si>
     <t xml:space="preserve">0.398373305797577</t>
@@ -3810,6 +3810,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.453999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462000012397766</t>
   </si>
 </sst>
 </file>
@@ -69200,7 +69203,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.691099537</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>61082</v>
@@ -69221,6 +69224,32 @@
         <v>1256</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6911111111</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>109289</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>0.462999999523163</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>0.458000004291534</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844841241837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323679059743881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980736494064</t>
+    <t xml:space="preserve">0.326844781637192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323679089546204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980766296387</t>
   </si>
   <si>
     <t xml:space="preserve">0.313056260347366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304966032505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29976013302803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309538811445236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302503794431686</t>
+    <t xml:space="preserve">0.304966062307358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299760192632675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309538781642914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302503824234009</t>
   </si>
   <si>
     <t xml:space="preserve">0.287097215652466</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">0.278655260801315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265288829803467</t>
+    <t xml:space="preserve">0.265288800001144</t>
   </si>
   <si>
     <t xml:space="preserve">0.260645747184753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270846426486969</t>
+    <t xml:space="preserve">0.270846396684647</t>
   </si>
   <si>
     <t xml:space="preserve">0.269087702035904</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">0.272956907749176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270142912864685</t>
+    <t xml:space="preserve">0.270142942667007</t>
   </si>
   <si>
     <t xml:space="preserve">0.265921920537949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290825754404068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288433820009232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294061839580536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276404082775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273167997598648</t>
+    <t xml:space="preserve">0.290825724601746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288433849811554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294061869382858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276404023170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273167967796326</t>
   </si>
   <si>
     <t xml:space="preserve">0.262545168399811</t>
@@ -119,43 +119,43 @@
     <t xml:space="preserve">0.260293990373611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246927499771118</t>
+    <t xml:space="preserve">0.246927514672279</t>
   </si>
   <si>
     <t xml:space="preserve">0.246224015951157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239751875400543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240103647112846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271549969911575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276122659444809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274645328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277881413698196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270987093448639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281539559364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277177929878235</t>
+    <t xml:space="preserve">0.239751890301704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240103602409363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271549940109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276122719049454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274645268917084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277881443500519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270987153053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281539589166641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27717787027359</t>
   </si>
   <si>
     <t xml:space="preserve">0.263318985700607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268032431602478</t>
+    <t xml:space="preserve">0.2680324614048</t>
   </si>
   <si>
     <t xml:space="preserve">0.28210237622261</t>
@@ -164,19 +164,19 @@
     <t xml:space="preserve">0.295468837022781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293358355760574</t>
+    <t xml:space="preserve">0.293358325958252</t>
   </si>
   <si>
     <t xml:space="preserve">0.291740298271179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288644880056381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504242897034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281469196081161</t>
+    <t xml:space="preserve">0.288644939661026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504183292389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281469255685806</t>
   </si>
   <si>
     <t xml:space="preserve">0.277248233556747</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">0.278373837471008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287026822566986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297368288040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295820593833923</t>
+    <t xml:space="preserve">0.287026882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297368258237839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295820564031601</t>
   </si>
   <si>
     <t xml:space="preserve">0.307217210531235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305669546127319</t>
+    <t xml:space="preserve">0.305669575929642</t>
   </si>
   <si>
     <t xml:space="preserve">0.313759744167328</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">0.320442974567413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317417949438095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316573709249496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306161999702454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310945779085159</t>
+    <t xml:space="preserve">0.317417979240417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316573768854141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306161969900131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310945749282837</t>
   </si>
   <si>
     <t xml:space="preserve">0.311438232660294</t>
@@ -224,16 +224,16 @@
     <t xml:space="preserve">0.30180025100708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288011759519577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288082122802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280554682016373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281328529119492</t>
+    <t xml:space="preserve">0.288011789321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288082093000412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280554711818695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281328558921814</t>
   </si>
   <si>
     <t xml:space="preserve">0.291880995035172</t>
@@ -242,43 +242,43 @@
     <t xml:space="preserve">0.301378220319748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311649262905121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31024232506752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311508566141129</t>
+    <t xml:space="preserve">0.311649292707443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310242295265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311508536338806</t>
   </si>
   <si>
     <t xml:space="preserve">0.314533621072769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316644102334976</t>
+    <t xml:space="preserve">0.316644132137299</t>
   </si>
   <si>
     <t xml:space="preserve">0.318684250116348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330573350191116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330643683671951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334161192178726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333528012037277</t>
+    <t xml:space="preserve">0.330573320388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330643713474274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334161162376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3335280418396</t>
   </si>
   <si>
     <t xml:space="preserve">0.330432653427124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327126204967499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323538333177567</t>
+    <t xml:space="preserve">0.327126234769821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323538362979889</t>
   </si>
   <si>
     <t xml:space="preserve">0.318543553352356</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">0.319247007369995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323116272687912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321005761623383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324875026941299</t>
+    <t xml:space="preserve">0.323116302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321005791425705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324874997138977</t>
   </si>
   <si>
     <t xml:space="preserve">0.323749423027039</t>
@@ -314,115 +314,115 @@
     <t xml:space="preserve">0.344713628292084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342040330171585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338030427694321</t>
+    <t xml:space="preserve">0.34204038977623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338030457496643</t>
   </si>
   <si>
     <t xml:space="preserve">0.352100372314453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354914307594299</t>
+    <t xml:space="preserve">0.354914337396622</t>
   </si>
   <si>
     <t xml:space="preserve">0.351678252220154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350341647863388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343306660652161</t>
+    <t xml:space="preserve">0.350341618061066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343306630849838</t>
   </si>
   <si>
     <t xml:space="preserve">0.343165963888168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341196119785309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340211272239685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33704549074173</t>
+    <t xml:space="preserve">0.341196179389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340211242437363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337045520544052</t>
   </si>
   <si>
     <t xml:space="preserve">0.323537766933441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309325844049454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312153726816177</t>
+    <t xml:space="preserve">0.309325903654099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3121537566185</t>
   </si>
   <si>
     <t xml:space="preserve">0.308890819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31193619966507</t>
+    <t xml:space="preserve">0.311936259269714</t>
   </si>
   <si>
     <t xml:space="preserve">0.325277984142303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322232604026794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318607062101364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324190348386765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307223081588745</t>
+    <t xml:space="preserve">0.322232633829117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318607121706009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324190378189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30722314119339</t>
   </si>
   <si>
     <t xml:space="preserve">0.299102008342743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299464583396912</t>
+    <t xml:space="preserve">0.299464553594589</t>
   </si>
   <si>
     <t xml:space="preserve">0.313096404075623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320854872465134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31802698969841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319042205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318317055702209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309543430805206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311791181564331</t>
+    <t xml:space="preserve">0.320854961872101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318027019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319042146205902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318317115306854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309543401002884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311791241168976</t>
   </si>
   <si>
     <t xml:space="preserve">0.310558527708054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311066061258316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322087556123734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31976729631424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318172097206116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309978455305099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306715577840805</t>
+    <t xml:space="preserve">0.311066091060638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322087585926056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319767266511917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318172067403793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309978514909744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306715548038483</t>
   </si>
   <si>
     <t xml:space="preserve">0.305627882480621</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">0.301784873008728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300914734601974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298739463090897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298014372587204</t>
+    <t xml:space="preserve">0.300914764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298739492893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298014402389526</t>
   </si>
   <si>
     <t xml:space="preserve">0.291488528251648</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">0.294316381216049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304467707872391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301204770803452</t>
+    <t xml:space="preserve">0.304467737674713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301204800605774</t>
   </si>
   <si>
     <t xml:space="preserve">0.302727520465851</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">0.30381515622139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30062472820282</t>
+    <t xml:space="preserve">0.300624758005142</t>
   </si>
   <si>
     <t xml:space="preserve">0.29743430018425</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">0.301929891109467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301712334156036</t>
+    <t xml:space="preserve">0.301712363958359</t>
   </si>
   <si>
     <t xml:space="preserve">0.302364975214005</t>
@@ -485,91 +485,91 @@
     <t xml:space="preserve">0.29714423418045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295621544122696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293663769960403</t>
+    <t xml:space="preserve">0.295621573925018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293663829565048</t>
   </si>
   <si>
     <t xml:space="preserve">0.297289252281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291706055402756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292358636856079</t>
+    <t xml:space="preserve">0.291706025600433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292358607053757</t>
   </si>
   <si>
     <t xml:space="preserve">0.290038347244263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287500500679016</t>
+    <t xml:space="preserve">0.287500470876694</t>
   </si>
   <si>
     <t xml:space="preserve">0.292648673057556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287645488977432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295041531324387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291561007499695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294533878564835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289313226938248</t>
+    <t xml:space="preserve">0.287645548582077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295041471719742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29156106710434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294533938169479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289313167333603</t>
   </si>
   <si>
     <t xml:space="preserve">0.287935554981232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283004909753799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287427991628647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282859861850739</t>
+    <t xml:space="preserve">0.283004879951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287428021430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282859891653061</t>
   </si>
   <si>
     <t xml:space="preserve">0.275826454162598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279161900281906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269735664129257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273288637399673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279524445533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282062262296677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283802509307861</t>
+    <t xml:space="preserve">0.279161870479584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26973569393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273288607597351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27952441573143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282062292098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283802479505539</t>
   </si>
   <si>
     <t xml:space="preserve">0.282134741544724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28713795542717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292866170406342</t>
+    <t xml:space="preserve">0.287137985229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292866200208664</t>
   </si>
   <si>
     <t xml:space="preserve">0.301422327756882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295839041471481</t>
+    <t xml:space="preserve">0.295839101076126</t>
   </si>
   <si>
     <t xml:space="preserve">0.296564191579819</t>
@@ -578,22 +578,22 @@
     <t xml:space="preserve">0.300262153148651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297071754932404</t>
+    <t xml:space="preserve">0.297071784734726</t>
   </si>
   <si>
     <t xml:space="preserve">0.292938739061356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298811972141266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296056628227234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310195952653885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306425482034683</t>
+    <t xml:space="preserve">0.298812031745911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296056658029556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31019601225853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306425541639328</t>
   </si>
   <si>
     <t xml:space="preserve">0.302509963512421</t>
@@ -608,13 +608,13 @@
     <t xml:space="preserve">0.301639884710312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294098854064941</t>
+    <t xml:space="preserve">0.294098883867264</t>
   </si>
   <si>
     <t xml:space="preserve">0.283077418804169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287863075733185</t>
+    <t xml:space="preserve">0.287863045930862</t>
   </si>
   <si>
     <t xml:space="preserve">0.289603292942047</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">0.288805663585663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293736338615417</t>
+    <t xml:space="preserve">0.293736308813095</t>
   </si>
   <si>
     <t xml:space="preserve">0.290835946798325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28351241350174</t>
+    <t xml:space="preserve">0.283512502908707</t>
   </si>
   <si>
     <t xml:space="preserve">0.281409680843353</t>
@@ -644,22 +644,22 @@
     <t xml:space="preserve">0.280684620141983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279016882181168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273796170949936</t>
+    <t xml:space="preserve">0.279016822576523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273796230554581</t>
   </si>
   <si>
     <t xml:space="preserve">0.291415989398956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295114010572433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290545910596848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288588106632233</t>
+    <t xml:space="preserve">0.295114040374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290545880794525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288588166236877</t>
   </si>
   <si>
     <t xml:space="preserve">0.292213618755341</t>
@@ -671,31 +671,31 @@
     <t xml:space="preserve">0.294388890266418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299392074346542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296491652727127</t>
+    <t xml:space="preserve">0.299392014741898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296491682529449</t>
   </si>
   <si>
     <t xml:space="preserve">0.303597629070282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309615880250931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307440608739853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319187164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331513792276382</t>
+    <t xml:space="preserve">0.309615910053253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307440638542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319187194108963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331513822078705</t>
   </si>
   <si>
     <t xml:space="preserve">0.331368774175644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345000594854355</t>
+    <t xml:space="preserve">0.345000624656677</t>
   </si>
   <si>
     <t xml:space="preserve">0.349786221981049</t>
@@ -704,100 +704,100 @@
     <t xml:space="preserve">0.358342379331589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354209303855896</t>
+    <t xml:space="preserve">0.354209333658218</t>
   </si>
   <si>
     <t xml:space="preserve">0.34964120388031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352396547794342</t>
+    <t xml:space="preserve">0.352396577596664</t>
   </si>
   <si>
     <t xml:space="preserve">0.355296939611435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35943004488945</t>
+    <t xml:space="preserve">0.359429985284805</t>
   </si>
   <si>
     <t xml:space="preserve">0.352686613798141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346885859966278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343187838792801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346160769462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346595793962479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346450805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344348013401031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350221246480942</t>
+    <t xml:space="preserve">0.346885830163956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343187868595123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346160739660263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346595823764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346450746059418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344347983598709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350221276283264</t>
   </si>
   <si>
     <t xml:space="preserve">0.350946366786957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388288766145706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397715061903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379950225353241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382125496864319</t>
+    <t xml:space="preserve">0.388288795948029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397715091705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379950255155563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382125526666641</t>
   </si>
   <si>
     <t xml:space="preserve">0.37487456202507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373424381017685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377412378787994</t>
+    <t xml:space="preserve">0.37342432141304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377412408590317</t>
   </si>
   <si>
     <t xml:space="preserve">0.373061835765839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369798868894577</t>
+    <t xml:space="preserve">0.369798898696899</t>
   </si>
   <si>
     <t xml:space="preserve">0.383575677871704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369436323642731</t>
+    <t xml:space="preserve">0.369436353445053</t>
   </si>
   <si>
     <t xml:space="preserve">0.369073778390884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35819736123085</t>
+    <t xml:space="preserve">0.358197331428528</t>
   </si>
   <si>
     <t xml:space="preserve">0.358052313327789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377049803733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412579566240311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382488042116165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40061542391777</t>
+    <t xml:space="preserve">0.377049833536148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412579536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382488012313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400615453720093</t>
   </si>
   <si>
     <t xml:space="preserve">0.394452184438705</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">0.385750949382782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39372706413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390464097261429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384300738573074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39155176281929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387563705444336</t>
+    <t xml:space="preserve">0.393727004528046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390464067459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384300768375397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391551792621613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387563765048981</t>
   </si>
   <si>
     <t xml:space="preserve">0.390826612710953</t>
@@ -827,46 +827,46 @@
     <t xml:space="preserve">0.395177274942398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393364489078522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397352516651154</t>
+    <t xml:space="preserve">0.393364459276199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397352486848831</t>
   </si>
   <si>
     <t xml:space="preserve">0.398802727460861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395539730787277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396627426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39844012260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395902335643768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393001973628998</t>
+    <t xml:space="preserve">0.395539790391922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396627396345139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398440152406693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395902305841446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393001914024353</t>
   </si>
   <si>
     <t xml:space="preserve">0.398077636957169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401703089475632</t>
+    <t xml:space="preserve">0.401703119277954</t>
   </si>
   <si>
     <t xml:space="preserve">0.392276853322983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387201189994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386476069688797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382850587368011</t>
+    <t xml:space="preserve">0.38720116019249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386476039886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382850557565689</t>
   </si>
   <si>
     <t xml:space="preserve">0.394089579582214</t>
@@ -875,28 +875,28 @@
     <t xml:space="preserve">0.38937646150589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38176292181015</t>
+    <t xml:space="preserve">0.381762951612473</t>
   </si>
   <si>
     <t xml:space="preserve">0.38103786110878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386838614940643</t>
+    <t xml:space="preserve">0.386838644742966</t>
   </si>
   <si>
     <t xml:space="preserve">0.38865140080452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385025888681412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391189187765121</t>
+    <t xml:space="preserve">0.385025948286057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391189217567444</t>
   </si>
   <si>
     <t xml:space="preserve">0.392639368772507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425631284713745</t>
+    <t xml:space="preserve">0.425631254911423</t>
   </si>
   <si>
     <t xml:space="preserve">0.419105410575867</t>
@@ -905,64 +905,64 @@
     <t xml:space="preserve">0.445208817720413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435057491064072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442308485507965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432612001895905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413591921329498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408370792865753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406878978013992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402776688337326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399047285318375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400539040565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395317792892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396809607744217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39606374502182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393080204725266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388604938983917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387859016656876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379654318094254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38114607334137</t>
+    <t xml:space="preserve">0.435057520866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442308455705643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43261194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413591980934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408370822668076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406879037618637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402776718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399047315120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400539010763168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395317852497101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396809577941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396063774824142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393080234527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38860496878624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387858986854553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379654347896576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381146043539047</t>
   </si>
   <si>
     <t xml:space="preserve">0.383010774850845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387486129999161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384875476360321</t>
+    <t xml:space="preserve">0.387486100196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384875446557999</t>
   </si>
   <si>
     <t xml:space="preserve">0.383756697177887</t>
@@ -971,40 +971,40 @@
     <t xml:space="preserve">0.386740207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390096664428711</t>
+    <t xml:space="preserve">0.390096694231033</t>
   </si>
   <si>
     <t xml:space="preserve">0.394944906234741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403522551059723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410235524177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407252013683319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407624959945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40874370932579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4065061211586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400911957025528</t>
+    <t xml:space="preserve">0.403522580862045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410235494375229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407251954078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407624930143356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408743739128113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406506150960922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40091198682785</t>
   </si>
   <si>
     <t xml:space="preserve">0.394199043512344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39867427945137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39084255695343</t>
+    <t xml:space="preserve">0.398674339056015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390842586755753</t>
   </si>
   <si>
     <t xml:space="preserve">0.392334342002869</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">0.388231962919235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387113153934479</t>
+    <t xml:space="preserve">0.387113124132156</t>
   </si>
   <si>
     <t xml:space="preserve">0.391588419675827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389350801706314</t>
+    <t xml:space="preserve">0.389350771903992</t>
   </si>
   <si>
     <t xml:space="preserve">0.38562136888504</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">0.385248422622681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383383750915527</t>
+    <t xml:space="preserve">0.383383721113205</t>
   </si>
   <si>
     <t xml:space="preserve">0.397928446531296</t>
@@ -1040,88 +1040,88 @@
     <t xml:space="preserve">0.409489661455154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410981416702271</t>
+    <t xml:space="preserve">0.410981327295303</t>
   </si>
   <si>
     <t xml:space="preserve">0.414337813854218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415083736181259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416575521230698</t>
+    <t xml:space="preserve">0.415083706378937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41657555103302</t>
   </si>
   <si>
     <t xml:space="preserve">0.415829598903656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424034297466278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439324975013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866139173508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428882569074631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420304894447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421796709299088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428509622812271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454988539218903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445291996002197</t>
+    <t xml:space="preserve">0.4240343272686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439324945211411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866109371185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428882628679276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420304924249649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421796679496765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428509652614594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454988479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44529202580452</t>
   </si>
   <si>
     <t xml:space="preserve">0.4445461332798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440443724393845</t>
+    <t xml:space="preserve">0.440443813800812</t>
   </si>
   <si>
     <t xml:space="preserve">0.449767291545868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459463775157928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460955500602722</t>
+    <t xml:space="preserve">0.459463745355606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460955530405045</t>
   </si>
   <si>
     <t xml:space="preserve">0.469533145427704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466549664735794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474008470773697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474754363298416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348497629166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485942602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482586085796356</t>
+    <t xml:space="preserve">0.466549694538116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474008500576019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474754393100739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480348527431488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485942542552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482586145401001</t>
   </si>
   <si>
     <t xml:space="preserve">0.485569685697556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50943797826767</t>
+    <t xml:space="preserve">0.509437918663025</t>
   </si>
   <si>
     <t xml:space="preserve">0.511302590370178</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">0.521745026111603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512794375419617</t>
+    <t xml:space="preserve">0.512794435024261</t>
   </si>
   <si>
     <t xml:space="preserve">0.5195072889328</t>
@@ -1151,37 +1151,37 @@
     <t xml:space="preserve">0.495266169309616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491536676883698</t>
+    <t xml:space="preserve">0.49153670668602</t>
   </si>
   <si>
     <t xml:space="preserve">0.477737903594971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478483825922012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481094270944595</t>
+    <t xml:space="preserve">0.478483766317368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48109433054924</t>
   </si>
   <si>
     <t xml:space="preserve">0.492282629013062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499741464853287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493774443864822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495639085769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507946074008942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500114262104034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493028432130814</t>
+    <t xml:space="preserve">0.499741494655609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4937744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495638996362686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507946133613586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500114321708679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493028491735458</t>
   </si>
   <si>
     <t xml:space="preserve">0.50869208574295</t>
@@ -1193,25 +1193,25 @@
     <t xml:space="preserve">0.508319139480591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507200300693512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510183870792389</t>
+    <t xml:space="preserve">0.507200181484222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510183811187744</t>
   </si>
   <si>
     <t xml:space="preserve">0.513167381286621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500860273838043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503097891807556</t>
+    <t xml:space="preserve">0.500860333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503097951412201</t>
   </si>
   <si>
     <t xml:space="preserve">0.502724945545197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501606166362762</t>
+    <t xml:space="preserve">0.501606225967407</t>
   </si>
   <si>
     <t xml:space="preserve">0.498249650001526</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">0.531068563461304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557920217514038</t>
+    <t xml:space="preserve">0.557920336723328</t>
   </si>
   <si>
     <t xml:space="preserve">0.554936766624451</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">0.593722641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574329733848572</t>
+    <t xml:space="preserve">0.574329674243927</t>
   </si>
   <si>
     <t xml:space="preserve">0.576567351818085</t>
@@ -1247,49 +1247,49 @@
     <t xml:space="preserve">0.577313244342804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583280205726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591485023498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585518002510071</t>
+    <t xml:space="preserve">0.583280384540558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59148496389389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585517942905426</t>
   </si>
   <si>
     <t xml:space="preserve">0.575075566768646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61236971616745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556428492069244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551953315734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548223793506622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534797966480255</t>
+    <t xml:space="preserve">0.612369656562805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556428551673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551953256130219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548223853111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53479790687561</t>
   </si>
   <si>
     <t xml:space="preserve">0.521372020244598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505708575248718</t>
+    <t xml:space="preserve">0.505708456039429</t>
   </si>
   <si>
     <t xml:space="preserve">0.528084933757782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545240342617035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522863686084747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517642557621002</t>
+    <t xml:space="preserve">0.54524028301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522863805294037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517642736434937</t>
   </si>
   <si>
     <t xml:space="preserve">0.532560288906097</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">0.531814396381378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523609697818756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516150891780853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512421488761902</t>
+    <t xml:space="preserve">0.523609638214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516150832176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512421429157257</t>
   </si>
   <si>
     <t xml:space="preserve">0.519134402275085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498995631933212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463193207979202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469906181097031</t>
+    <t xml:space="preserve">0.498995572328568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46319317817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469906091690063</t>
   </si>
   <si>
     <t xml:space="preserve">0.476619064807892</t>
@@ -1328,91 +1328,91 @@
     <t xml:space="preserve">0.494520276784897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490045011043549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478856772184372</t>
+    <t xml:space="preserve">0.490044951438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478856712579727</t>
   </si>
   <si>
     <t xml:space="preserve">0.47811084985733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468414425849915</t>
+    <t xml:space="preserve">0.468414396047592</t>
   </si>
   <si>
     <t xml:space="preserve">0.481840282678604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484077930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475127369165421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473635613918304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474381446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484823763370514</t>
+    <t xml:space="preserve">0.484077870845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475127309560776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473635524511337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474381357431412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484823822975159</t>
   </si>
   <si>
     <t xml:space="preserve">0.487061411142349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48333203792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504216730594635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504962682723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496757864952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497503817081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48631551861763</t>
+    <t xml:space="preserve">0.483332008123398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50421679019928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504962563514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49675789475441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497503757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486315548419952</t>
   </si>
   <si>
     <t xml:space="preserve">0.500487387180328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454242646694183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46543088555336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452004909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457226067781448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458717912435532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462447285652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455734312534332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45797199010849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485727906227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484185934066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474933952093124</t>
+    <t xml:space="preserve">0.454242616891861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465430825948715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452004939317703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457226097583771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458717852830887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462447315454483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455734342336655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457972019910812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485727846622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48418590426445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474933922290802</t>
   </si>
   <si>
     <t xml:space="preserve">0.469536989927292</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">0.464910984039307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461055934429169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463369011878967</t>
+    <t xml:space="preserve">0.461055964231491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463368952274323</t>
   </si>
   <si>
     <t xml:space="preserve">0.459514021873474</t>
@@ -1436,52 +1436,52 @@
     <t xml:space="preserve">0.458743005990982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447949051856995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451033025979996</t>
+    <t xml:space="preserve">0.447949022054672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451032996177673</t>
   </si>
   <si>
     <t xml:space="preserve">0.454888015985489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446407079696655</t>
+    <t xml:space="preserve">0.446407049894333</t>
   </si>
   <si>
     <t xml:space="preserve">0.441781103610992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443323075771332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494208812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474162966012955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481101959943771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489582896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476475894451141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464139997959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461826950311661</t>
+    <t xml:space="preserve">0.443323105573654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494208872318268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474162876605988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481101870536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489582866430283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476475924253464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464139968156815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461827009916306</t>
   </si>
   <si>
     <t xml:space="preserve">0.456429988145828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454117059707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466452926397324</t>
+    <t xml:space="preserve">0.454117000102997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466452896595001</t>
   </si>
   <si>
     <t xml:space="preserve">0.467223942279816</t>
@@ -1493,22 +1493,22 @@
     <t xml:space="preserve">0.442552089691162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45257505774498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45334604382515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441010117530823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437926113605499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433300137519836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430987119674683</t>
+    <t xml:space="preserve">0.452575027942657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453345984220505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4410100877285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437926143407822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433300077915192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430987149477005</t>
   </si>
   <si>
     <t xml:space="preserve">0.431758105754852</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">0.435613095760345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444865047931671</t>
+    <t xml:space="preserve">0.444865137338638</t>
   </si>
   <si>
     <t xml:space="preserve">0.460285007953644</t>
@@ -1526,52 +1526,52 @@
     <t xml:space="preserve">0.45180407166481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470307976007462</t>
+    <t xml:space="preserve">0.470307946205139</t>
   </si>
   <si>
     <t xml:space="preserve">0.471849918365479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465681970119476</t>
+    <t xml:space="preserve">0.465681940317154</t>
   </si>
   <si>
     <t xml:space="preserve">0.457200974225998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462597966194153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455658972263336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450262039899826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449491083621979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437155097723007</t>
+    <t xml:space="preserve">0.46259805560112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455659031867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450261980295181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449490994215012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437155067920685</t>
   </si>
   <si>
     <t xml:space="preserve">0.440239042043686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426361113786697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427903145551682</t>
+    <t xml:space="preserve">0.42636114358902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427903115749359</t>
   </si>
   <si>
     <t xml:space="preserve">0.407086193561554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406315207481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410170197486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404002219438553</t>
+    <t xml:space="preserve">0.406315237283707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410170167684555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404002249240875</t>
   </si>
   <si>
     <t xml:space="preserve">0.407857209444046</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">0.410941183567047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400147259235382</t>
+    <t xml:space="preserve">0.40014722943306</t>
   </si>
   <si>
     <t xml:space="preserve">0.396292269229889</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">0.388582289218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39475029706955</t>
+    <t xml:space="preserve">0.394750326871872</t>
   </si>
   <si>
     <t xml:space="preserve">0.397063255310059</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">0.389353275299072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387040287256241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385498285293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375475347042084</t>
+    <t xml:space="preserve">0.387040317058563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385498315095901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375475376844406</t>
   </si>
   <si>
     <t xml:space="preserve">0.366223394870758</t>
@@ -1628,19 +1628,19 @@
     <t xml:space="preserve">0.351188957691193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345406532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348875910043716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366994380950928</t>
+    <t xml:space="preserve">0.345406502485275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348875969648361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366994440555573</t>
   </si>
   <si>
     <t xml:space="preserve">0.37239134311676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367765367031097</t>
+    <t xml:space="preserve">0.36776539683342</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162358999252</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">0.370078384876251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370463877916336</t>
+    <t xml:space="preserve">0.370463937520981</t>
   </si>
   <si>
     <t xml:space="preserve">0.369692832231522</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">0.365837901830673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371620357036591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368536353111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368921905755997</t>
+    <t xml:space="preserve">0.371620386838913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368536382913589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368921875953674</t>
   </si>
   <si>
     <t xml:space="preserve">0.378944844007492</t>
@@ -1676,31 +1676,31 @@
     <t xml:space="preserve">0.377017349004745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3824143409729</t>
+    <t xml:space="preserve">0.382414311170578</t>
   </si>
   <si>
     <t xml:space="preserve">0.399376273155212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416338235139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424048155546188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424819141626358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417109161615372</t>
+    <t xml:space="preserve">0.416338205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424048125743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424819111824036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417109191417694</t>
   </si>
   <si>
     <t xml:space="preserve">0.422506153583527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421735167503357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420964181423187</t>
+    <t xml:space="preserve">0.421735137701035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420964151620865</t>
   </si>
   <si>
     <t xml:space="preserve">0.408628195524216</t>
@@ -1709,31 +1709,31 @@
     <t xml:space="preserve">0.400918245315552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404773235321045</t>
+    <t xml:space="preserve">0.404773205518723</t>
   </si>
   <si>
     <t xml:space="preserve">0.405544251203537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411712169647217</t>
+    <t xml:space="preserve">0.411712199449539</t>
   </si>
   <si>
     <t xml:space="preserve">0.412483245134354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423277199268341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42559015750885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419422209262848</t>
+    <t xml:space="preserve">0.423277169466019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425590068101883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419422179460526</t>
   </si>
   <si>
     <t xml:space="preserve">0.430216133594513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427132129669189</t>
+    <t xml:space="preserve">0.427132189273834</t>
   </si>
   <si>
     <t xml:space="preserve">0.414025187492371</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">0.41479617357254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413254201412201</t>
+    <t xml:space="preserve">0.413254231214523</t>
   </si>
   <si>
     <t xml:space="preserve">0.40939924120903</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">0.393208265304565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392437279224396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391666322946548</t>
+    <t xml:space="preserve">0.392437309026718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391666293144226</t>
   </si>
   <si>
     <t xml:space="preserve">0.393979251384735</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">0.39860525727272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403231233358383</t>
+    <t xml:space="preserve">0.403231263160706</t>
   </si>
   <si>
     <t xml:space="preserve">0.411275893449783</t>
@@ -1775,34 +1775,34 @@
     <t xml:space="preserve">0.410471081733704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409666240215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415300130844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412885665893555</t>
+    <t xml:space="preserve">0.409666270017624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415300101041794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412885636091232</t>
   </si>
   <si>
     <t xml:space="preserve">0.412080824375153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399203270673752</t>
+    <t xml:space="preserve">0.399203240871429</t>
   </si>
   <si>
     <t xml:space="preserve">0.401215374469757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404032289981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397996008396149</t>
+    <t xml:space="preserve">0.404032319784164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397995978593826</t>
   </si>
   <si>
     <t xml:space="preserve">0.403227478265762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39839842915535</t>
+    <t xml:space="preserve">0.398398399353027</t>
   </si>
   <si>
     <t xml:space="preserve">0.400008112192154</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">0.40242263674736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400410503149033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395983904600143</t>
+    <t xml:space="preserve">0.400410532951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395983844995499</t>
   </si>
   <si>
     <t xml:space="preserve">0.399605691432953</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">0.404837191104889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401617825031281</t>
+    <t xml:space="preserve">0.401617795228958</t>
   </si>
   <si>
     <t xml:space="preserve">0.407251685857773</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">0.397593557834625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391154825687408</t>
+    <t xml:space="preserve">0.391154795885086</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446844339371</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">0.424153476953506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43220192193985</t>
+    <t xml:space="preserve">0.432201892137527</t>
   </si>
   <si>
     <t xml:space="preserve">0.425763130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428177684545517</t>
+    <t xml:space="preserve">0.428177654743195</t>
   </si>
   <si>
     <t xml:space="preserve">0.43300673365593</t>
@@ -1880,28 +1880,28 @@
     <t xml:space="preserve">0.420934110879898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428982526063919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437030971050262</t>
+    <t xml:space="preserve">0.428982496261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43703094124794</t>
   </si>
   <si>
     <t xml:space="preserve">0.434616476297379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430592238903046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442664921283722</t>
+    <t xml:space="preserve">0.430592268705368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4426648914814</t>
   </si>
   <si>
     <t xml:space="preserve">0.458761781454086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466810256242752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473249047994614</t>
+    <t xml:space="preserve">0.466810196638107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473248988389969</t>
   </si>
   <si>
     <t xml:space="preserve">0.4764683842659</t>
@@ -1910,34 +1910,34 @@
     <t xml:space="preserve">0.478882938623428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475663542747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481297433376312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478078097105026</t>
+    <t xml:space="preserve">0.47566357254982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481297463178635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478078037500381</t>
   </si>
   <si>
     <t xml:space="preserve">0.474858701229095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471639394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472444206476212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486126571893692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480492621660233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49497988820076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511881649494171</t>
+    <t xml:space="preserve">0.471639364957809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472444176673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486126512289047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480492651462555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494979798793793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511881530284882</t>
   </si>
   <si>
     <t xml:space="preserve">0.513491272926331</t>
@@ -1946,40 +1946,40 @@
     <t xml:space="preserve">0.520734906196594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535222172737122</t>
+    <t xml:space="preserve">0.535222113132477</t>
   </si>
   <si>
     <t xml:space="preserve">0.534417271614075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523149371147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515100955963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516710698604584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522344529628754</t>
+    <t xml:space="preserve">0.523149430751801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51510101556778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516710638999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522344589233398</t>
   </si>
   <si>
     <t xml:space="preserve">0.556148111820221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555343270301819</t>
+    <t xml:space="preserve">0.555343210697174</t>
   </si>
   <si>
     <t xml:space="preserve">0.551319062709808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55775773525238</t>
+    <t xml:space="preserve">0.557757794857025</t>
   </si>
   <si>
     <t xml:space="preserve">0.571440160274506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56178206205368</t>
+    <t xml:space="preserve">0.561782002449036</t>
   </si>
   <si>
     <t xml:space="preserve">0.560977220535278</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">0.552928686141968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554538488388062</t>
+    <t xml:space="preserve">0.554538369178772</t>
   </si>
   <si>
     <t xml:space="preserve">0.59236615896225</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">0.599609732627869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611682415008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606853306293488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60202419757843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614901721477509</t>
+    <t xml:space="preserve">0.61168247461319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606853365898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60202431678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614901840686798</t>
   </si>
   <si>
     <t xml:space="preserve">0.600414574146271</t>
@@ -2018,19 +2018,19 @@
     <t xml:space="preserve">0.608462989330292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593975841999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590756475925446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595585584640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609267830848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614096939563751</t>
+    <t xml:space="preserve">0.593975782394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590756416320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595585525035858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609267950057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614096999168396</t>
   </si>
   <si>
     <t xml:space="preserve">0.606048464775085</t>
@@ -2042,28 +2042,28 @@
     <t xml:space="preserve">0.598804891109467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601219415664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594780743122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603633880615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610072672367096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598000049591064</t>
+    <t xml:space="preserve">0.601219356060028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594780683517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603633940219879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610072731971741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59799998998642</t>
   </si>
   <si>
     <t xml:space="preserve">0.630193829536438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631803512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64629065990448</t>
+    <t xml:space="preserve">0.631803572177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646290719509125</t>
   </si>
   <si>
     <t xml:space="preserve">0.65594893693924</t>
@@ -2072,28 +2072,28 @@
     <t xml:space="preserve">0.659973084926605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689752340316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684118390083313</t>
+    <t xml:space="preserve">0.689752399921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684118509292603</t>
   </si>
   <si>
     <t xml:space="preserve">0.661582827568054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588341951370239</t>
+    <t xml:space="preserve">0.588341891765594</t>
   </si>
   <si>
     <t xml:space="preserve">0.581098258495331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572245001792908</t>
+    <t xml:space="preserve">0.572244942188263</t>
   </si>
   <si>
     <t xml:space="preserve">0.540856063365936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543270587921143</t>
+    <t xml:space="preserve">0.543270528316498</t>
   </si>
   <si>
     <t xml:space="preserve">0.518320381641388</t>
@@ -2102,46 +2102,46 @@
     <t xml:space="preserve">0.526368796825409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490955650806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439445525407791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398800849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381496667861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32314532995224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348095566034317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303829044103622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282500684261322</t>
+    <t xml:space="preserve">0.490955621004105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439445495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398800820112228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381496638059616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323145359754562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348095595836639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303829073905945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282500654459</t>
   </si>
   <si>
     <t xml:space="preserve">0.288939476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29135400056839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304633915424347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308255702257156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343668907880783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35896098613739</t>
+    <t xml:space="preserve">0.291353970766068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304633975028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308255732059479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343668937683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358961015939713</t>
   </si>
   <si>
     <t xml:space="preserve">0.37224093079567</t>
@@ -2150,19 +2150,19 @@
     <t xml:space="preserve">0.355741590261459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373850643634796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391959637403488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379082143306732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375057846307755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384716004133224</t>
+    <t xml:space="preserve">0.373850673437119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391959667205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37908211350441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375057905912399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384716033935547</t>
   </si>
   <si>
     <t xml:space="preserve">0.386325716972351</t>
@@ -2177,16 +2177,16 @@
     <t xml:space="preserve">0.351717382669449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353327065706253</t>
+    <t xml:space="preserve">0.353327095508575</t>
   </si>
   <si>
     <t xml:space="preserve">0.34930282831192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344473779201508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323547780513763</t>
+    <t xml:space="preserve">0.34447380900383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323547810316086</t>
   </si>
   <si>
     <t xml:space="preserve">0.338034987449646</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">0.339644700288773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341254353523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346083462238312</t>
+    <t xml:space="preserve">0.341254383325577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346083492040634</t>
   </si>
   <si>
     <t xml:space="preserve">0.350912511348724</t>
@@ -2210,10 +2210,10 @@
     <t xml:space="preserve">0.342864066362381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345278590917587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336425334215164</t>
+    <t xml:space="preserve">0.34527862071991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336425364017487</t>
   </si>
   <si>
     <t xml:space="preserve">0.324352622032166</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">0.329986542463303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326767146587372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321938097476959</t>
+    <t xml:space="preserve">0.326767176389694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321938127279282</t>
   </si>
   <si>
     <t xml:space="preserve">0.331596255302429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340449571609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347693145275116</t>
+    <t xml:space="preserve">0.340449541807175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347693175077438</t>
   </si>
   <si>
     <t xml:space="preserve">0.352522224187851</t>
@@ -2246,79 +2246,79 @@
     <t xml:space="preserve">0.36942395567894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382301479578018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379886984825134</t>
+    <t xml:space="preserve">0.382301509380341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379886955022812</t>
   </si>
   <si>
     <t xml:space="preserve">0.371838539838791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354131907224655</t>
+    <t xml:space="preserve">0.354131937026978</t>
   </si>
   <si>
     <t xml:space="preserve">0.330791413784027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356546431779861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357351332902908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350107699632645</t>
+    <t xml:space="preserve">0.356546491384506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357351303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350107669830322</t>
   </si>
   <si>
     <t xml:space="preserve">0.346888303756714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342059195041656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337230145931244</t>
+    <t xml:space="preserve">0.342059254646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337230175733566</t>
   </si>
   <si>
     <t xml:space="preserve">0.328376859426498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335620492696762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370228826999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358156144618988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363790035247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420129269361496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424958288669586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437835872173309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444274574518204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445884317159653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482907176017761</t>
+    <t xml:space="preserve">0.33562046289444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370228856801987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358156114816666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363790065050125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420129209756851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424958258867264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437835842370987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444274514913559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445884346961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482907235622406</t>
   </si>
   <si>
     <t xml:space="preserve">0.560172319412231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527978539466858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521539688110352</t>
+    <t xml:space="preserve">0.527978479862213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521539747714996</t>
   </si>
   <si>
     <t xml:space="preserve">0.529588162899017</t>
@@ -2327,16 +2327,16 @@
     <t xml:space="preserve">0.519930064678192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507052540779114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500613749027252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494175046682358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502223551273346</t>
+    <t xml:space="preserve">0.507052481174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500613808631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494175016880035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502223432064056</t>
   </si>
   <si>
     <t xml:space="preserve">0.537636637687683</t>
@@ -2345,16 +2345,16 @@
     <t xml:space="preserve">0.524759113788605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510271966457367</t>
+    <t xml:space="preserve">0.510271906852722</t>
   </si>
   <si>
     <t xml:space="preserve">0.499004065990448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492565304040909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487736195325851</t>
+    <t xml:space="preserve">0.492565274238586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487736225128174</t>
   </si>
   <si>
     <t xml:space="preserve">0.484516859054565</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">0.447493970394135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431397080421448</t>
+    <t xml:space="preserve">0.43139711022377</t>
   </si>
   <si>
     <t xml:space="preserve">0.449103683233261</t>
@@ -2384,40 +2384,40 @@
     <t xml:space="preserve">0.367009401321411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359765827655792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376667588949203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421738892793655</t>
+    <t xml:space="preserve">0.35976579785347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376667559146881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4217389523983</t>
   </si>
   <si>
     <t xml:space="preserve">0.423348635435104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441055178642273</t>
+    <t xml:space="preserve">0.441055208444595</t>
   </si>
   <si>
     <t xml:space="preserve">0.50544285774231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468419998884201</t>
+    <t xml:space="preserve">0.468419939279556</t>
   </si>
   <si>
     <t xml:space="preserve">0.461981207132339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465200573205948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45232304930687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455542385578156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450713366270065</t>
+    <t xml:space="preserve">0.46520060300827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452323019504547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455542415380478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450713336467743</t>
   </si>
   <si>
     <t xml:space="preserve">0.460371524095535</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">0.453932732343674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47968778014183</t>
+    <t xml:space="preserve">0.479687809944153</t>
   </si>
   <si>
     <t xml:space="preserve">0.495784670114517</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">0.489345908164978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547294795513153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565001368522644</t>
+    <t xml:space="preserve">0.547294735908508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565001308917999</t>
   </si>
   <si>
     <t xml:space="preserve">0.576269268989563</t>
@@ -2450,19 +2450,19 @@
     <t xml:space="preserve">0.575464367866516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569830477237701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549709379673004</t>
+    <t xml:space="preserve">0.569830417633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549709320068359</t>
   </si>
   <si>
     <t xml:space="preserve">0.56741589307785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545685112476349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558562576770782</t>
+    <t xml:space="preserve">0.545685052871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558562695980072</t>
   </si>
   <si>
     <t xml:space="preserve">0.544075429439545</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">0.531197905540466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559367418289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573854625225067</t>
+    <t xml:space="preserve">0.559367537498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573854684829712</t>
   </si>
   <si>
     <t xml:space="preserve">0.581903100013733</t>
@@ -2483,46 +2483,46 @@
     <t xml:space="preserve">0.579488635063171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544880270957947</t>
+    <t xml:space="preserve">0.544880211353302</t>
   </si>
   <si>
     <t xml:space="preserve">0.552123844623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548099637031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548904478549957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553733646869659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582058250904083</t>
+    <t xml:space="preserve">0.54809957742691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548904538154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553733587265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582058310508728</t>
   </si>
   <si>
     <t xml:space="preserve">0.581226825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573743224143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567091107368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574708938599</t>
+    <t xml:space="preserve">0.573743164539337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567091047763824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574649333954</t>
   </si>
   <si>
     <t xml:space="preserve">0.57291167974472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561270534992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557944476604462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558776021003723</t>
+    <t xml:space="preserve">0.561270475387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557944416999817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558775961399078</t>
   </si>
   <si>
     <t xml:space="preserve">0.540482699871063</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">0.544640243053436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542977213859558</t>
+    <t xml:space="preserve">0.542977273464203</t>
   </si>
   <si>
     <t xml:space="preserve">0.530504584312439</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">0.531336069107056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532167613506317</t>
+    <t xml:space="preserve">0.532167553901672</t>
   </si>
   <si>
     <t xml:space="preserve">0.516368865966797</t>
@@ -2558,22 +2558,22 @@
     <t xml:space="preserve">0.502233147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51553738117218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498907119035721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493918001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494749575853348</t>
+    <t xml:space="preserve">0.515537321567535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498907178640366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493918031454086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494749546051025</t>
   </si>
   <si>
     <t xml:space="preserve">0.500570118427277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483939945697784</t>
+    <t xml:space="preserve">0.483939915895462</t>
   </si>
   <si>
     <t xml:space="preserve">0.465646624565125</t>
@@ -2591,16 +2591,16 @@
     <t xml:space="preserve">0.473961740732193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473130285739899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486434429883957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489760518074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503064632415771</t>
+    <t xml:space="preserve">0.473130226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486434459686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489760458469391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503064692020416</t>
   </si>
   <si>
     <t xml:space="preserve">0.50472766160965</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">0.510548293590546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503896176815033</t>
+    <t xml:space="preserve">0.503896117210388</t>
   </si>
   <si>
     <t xml:space="preserve">0.495581090450287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484771460294724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482276886701584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491423487663269</t>
+    <t xml:space="preserve">0.484771370887756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482276827096939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491423547267914</t>
   </si>
   <si>
     <t xml:space="preserve">0.497244030237198</t>
@@ -2639,19 +2639,19 @@
     <t xml:space="preserve">0.483108371496201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478119343519211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475624799728394</t>
+    <t xml:space="preserve">0.478119283914566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475624829530716</t>
   </si>
   <si>
     <t xml:space="preserve">0.476456314325333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529673099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523852527141571</t>
+    <t xml:space="preserve">0.529672980308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523852467536926</t>
   </si>
   <si>
     <t xml:space="preserve">0.528010070323944</t>
@@ -2663,25 +2663,25 @@
     <t xml:space="preserve">0.527178525924683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547966241836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528841555118561</t>
+    <t xml:space="preserve">0.547966301441193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528841495513916</t>
   </si>
   <si>
     <t xml:space="preserve">0.525515496730804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526347041130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554618418216705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588710367679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57540625333786</t>
+    <t xml:space="preserve">0.526346981525421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554618358612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588710427284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575406134128571</t>
   </si>
   <si>
     <t xml:space="preserve">0.577069222927094</t>
@@ -2693,34 +2693,34 @@
     <t xml:space="preserve">0.583721339702606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585384368896484</t>
+    <t xml:space="preserve">0.58538430929184</t>
   </si>
   <si>
     <t xml:space="preserve">0.57790070772171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58039528131485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550460875034332</t>
+    <t xml:space="preserve">0.580395221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550460815429688</t>
   </si>
   <si>
     <t xml:space="preserve">0.556281447410583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545471787452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567922651767731</t>
+    <t xml:space="preserve">0.545471727848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567922592163086</t>
   </si>
   <si>
     <t xml:space="preserve">0.566259562969208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557112991809845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56459653377533</t>
+    <t xml:space="preserve">0.5571129322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564596474170685</t>
   </si>
   <si>
     <t xml:space="preserve">0.549629330635071</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">0.532999098300934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524684011936188</t>
+    <t xml:space="preserve">0.524683952331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.509716749191284</t>
@@ -2744,61 +2744,61 @@
     <t xml:space="preserve">0.507222235202789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521357893943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513874292373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522189497947693</t>
+    <t xml:space="preserve">0.521357953548431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513874232769012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522189438343048</t>
   </si>
   <si>
     <t xml:space="preserve">0.513042807579041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52052640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52302098274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519694924354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508053719997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488097488880157</t>
+    <t xml:space="preserve">0.520526349544525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523020923137665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519694864749908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508053779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48809739947319</t>
   </si>
   <si>
     <t xml:space="preserve">0.488929003477097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492254972457886</t>
+    <t xml:space="preserve">0.492255002260208</t>
   </si>
   <si>
     <t xml:space="preserve">0.496412575244904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49059197306633</t>
+    <t xml:space="preserve">0.490591943264008</t>
   </si>
   <si>
     <t xml:space="preserve">0.485602915287018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480613857507706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47479322552681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454005479812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478950828313828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458163022994995</t>
+    <t xml:space="preserve">0.480613827705383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474793255329132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4540054500103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478950768709183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458162993192673</t>
   </si>
   <si>
     <t xml:space="preserve">0.44901642203331</t>
@@ -2810,34 +2810,34 @@
     <t xml:space="preserve">0.439038217067719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419913470745087</t>
+    <t xml:space="preserve">0.419913500547409</t>
   </si>
   <si>
     <t xml:space="preserve">0.422408014535904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424071043729782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411598384380341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41118261218071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395799607038498</t>
+    <t xml:space="preserve">0.42407101392746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411598354578018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411182582378387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395799666643143</t>
   </si>
   <si>
     <t xml:space="preserve">0.377090603113174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365033686161041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40203595161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413677155971527</t>
+    <t xml:space="preserve">0.365033715963364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402035981416702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413677126169205</t>
   </si>
   <si>
     <t xml:space="preserve">0.407440811395645</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">0.431554645299911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429891616106033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432386159896851</t>
+    <t xml:space="preserve">0.429891645908356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432386130094528</t>
   </si>
   <si>
     <t xml:space="preserve">0.451510936021805</t>
@@ -2861,22 +2861,22 @@
     <t xml:space="preserve">0.444027304649353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436543703079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443195819854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448184847831726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.446521878242493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440701246261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434880703687668</t>
+    <t xml:space="preserve">0.436543673276901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443195790052414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448184877634048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44652184844017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440701276063919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434880673885345</t>
   </si>
   <si>
     <t xml:space="preserve">0.424902528524399</t>
@@ -2885,37 +2885,37 @@
     <t xml:space="preserve">0.444858849048615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447353363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445690363645554</t>
+    <t xml:space="preserve">0.447353333234787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445690393447876</t>
   </si>
   <si>
     <t xml:space="preserve">0.463152050971985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481445372104645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477287828922272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470635682344437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437375247478485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429060101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421576499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409935355186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430723130702972</t>
+    <t xml:space="preserve">0.4814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477287799119949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470635712146759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437375277280807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429060071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421576529741287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40993532538414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430723160505295</t>
   </si>
   <si>
     <t xml:space="preserve">0.427397072315216</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">0.446109414100647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439152538776398</t>
+    <t xml:space="preserve">0.43915256857872</t>
   </si>
   <si>
     <t xml:space="preserve">0.431326061487198</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">0.406542211771011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403063744306564</t>
+    <t xml:space="preserve">0.403063774108887</t>
   </si>
   <si>
     <t xml:space="preserve">0.414368689060211</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">0.391324043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383932381868362</t>
+    <t xml:space="preserve">0.383932411670685</t>
   </si>
   <si>
     <t xml:space="preserve">0.388715207576752</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">0.384367167949677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378714710474014</t>
+    <t xml:space="preserve">0.378714680671692</t>
   </si>
   <si>
     <t xml:space="preserve">0.373931884765625</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">0.371323019266129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375671088695526</t>
+    <t xml:space="preserve">0.375671118497849</t>
   </si>
   <si>
     <t xml:space="preserve">0.374366670846939</t>
@@ -3026,22 +3026,22 @@
     <t xml:space="preserve">0.364366173744202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36175736784935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368714213371277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37741032242775</t>
+    <t xml:space="preserve">0.361757338047028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368714183568954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377410292625427</t>
   </si>
   <si>
     <t xml:space="preserve">0.36958384513855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377845108509064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374801486730576</t>
+    <t xml:space="preserve">0.377845138311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374801456928253</t>
   </si>
   <si>
     <t xml:space="preserve">0.37523627281189</t>
@@ -3062,25 +3062,25 @@
     <t xml:space="preserve">0.367409825325012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376975506544113</t>
+    <t xml:space="preserve">0.376975476741791</t>
   </si>
   <si>
     <t xml:space="preserve">0.364800959825516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386976003646851</t>
+    <t xml:space="preserve">0.386975973844528</t>
   </si>
   <si>
     <t xml:space="preserve">0.397411316633224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402628988027573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407846629619598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389584869146347</t>
+    <t xml:space="preserve">0.40262895822525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407846659421921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389584839344025</t>
   </si>
   <si>
     <t xml:space="preserve">0.396106898784637</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">0.40393340587616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408716231584549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400020182132721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400889724493027</t>
+    <t xml:space="preserve">0.408716201782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400020152330399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400889754295349</t>
   </si>
   <si>
     <t xml:space="preserve">0.393063247203827</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">0.389150023460388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390889227390289</t>
+    <t xml:space="preserve">0.390889257192612</t>
   </si>
   <si>
     <t xml:space="preserve">0.395672112703323</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">0.400454938411713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390454411506653</t>
+    <t xml:space="preserve">0.390454441308975</t>
   </si>
   <si>
     <t xml:space="preserve">0.387410819530487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383497595787048</t>
+    <t xml:space="preserve">0.383497565984726</t>
   </si>
   <si>
     <t xml:space="preserve">0.382193148136139</t>
@@ -3161,22 +3161,22 @@
     <t xml:space="preserve">0.357844114303589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366540193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360887706279755</t>
+    <t xml:space="preserve">0.366540163755417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360887736082077</t>
   </si>
   <si>
     <t xml:space="preserve">0.362626940011978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369148999452591</t>
+    <t xml:space="preserve">0.369149029254913</t>
   </si>
   <si>
     <t xml:space="preserve">0.379149526357651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3861064016819</t>
+    <t xml:space="preserve">0.386106431484222</t>
   </si>
   <si>
     <t xml:space="preserve">0.394367665052414</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">0.392628461122513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391758888959885</t>
+    <t xml:space="preserve">0.391758859157562</t>
   </si>
   <si>
     <t xml:space="preserve">0.395237267017365</t>
@@ -3215,13 +3215,13 @@
     <t xml:space="preserve">0.403868108987808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406615495681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407531291246414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40936291217804</t>
+    <t xml:space="preserve">0.406615525484085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407531321048737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409362882375717</t>
   </si>
   <si>
     <t xml:space="preserve">0.408447116613388</t>
@@ -3239,16 +3239,16 @@
     <t xml:space="preserve">0.402952283620834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402036517858505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393794298171997</t>
+    <t xml:space="preserve">0.402036488056183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393794327974319</t>
   </si>
   <si>
     <t xml:space="preserve">0.39104688167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391962677240372</t>
+    <t xml:space="preserve">0.391962707042694</t>
   </si>
   <si>
     <t xml:space="preserve">0.390131086111069</t>
@@ -3257,22 +3257,22 @@
     <t xml:space="preserve">0.394710093736649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395625919103622</t>
+    <t xml:space="preserve">0.3956258893013</t>
   </si>
   <si>
     <t xml:space="preserve">0.397457480430603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392878472805023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388299494981766</t>
+    <t xml:space="preserve">0.392878502607346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388299465179443</t>
   </si>
   <si>
     <t xml:space="preserve">0.384636282920837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38921532034874</t>
+    <t xml:space="preserve">0.389215290546417</t>
   </si>
   <si>
     <t xml:space="preserve">0.386467903852463</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">0.380973100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375478297472</t>
+    <t xml:space="preserve">0.375478267669678</t>
   </si>
   <si>
     <t xml:space="preserve">0.373646676540375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371815085411072</t>
+    <t xml:space="preserve">0.371815055608749</t>
   </si>
   <si>
     <t xml:space="preserve">0.369067668914795</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">0.369983494281769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376394122838974</t>
+    <t xml:space="preserve">0.376394093036652</t>
   </si>
   <si>
     <t xml:space="preserve">0.374562501907349</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">0.37089928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378225654363632</t>
+    <t xml:space="preserve">0.378225684165955</t>
   </si>
   <si>
     <t xml:space="preserve">0.385552108287811</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">0.420352518558502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421268314123154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425847351551056</t>
+    <t xml:space="preserve">0.421268343925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425847321748734</t>
   </si>
   <si>
     <t xml:space="preserve">0.416689306497574</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">0.415773510932922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410278737545013</t>
+    <t xml:space="preserve">0.410278707742691</t>
   </si>
   <si>
     <t xml:space="preserve">0.422184109687805</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">0.456068724393845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445994913578033</t>
+    <t xml:space="preserve">0.445994943380356</t>
   </si>
   <si>
     <t xml:space="preserve">0.494532406330109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487206012010574</t>
+    <t xml:space="preserve">0.48720595240593</t>
   </si>
   <si>
     <t xml:space="preserve">0.492700755596161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481711179018021</t>
+    <t xml:space="preserve">0.481711208820343</t>
   </si>
   <si>
     <t xml:space="preserve">0.489037543535233</t>
@@ -3413,16 +3413,16 @@
     <t xml:space="preserve">0.496363997459412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485374361276627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483542770147324</t>
+    <t xml:space="preserve">0.485374301671982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483542799949646</t>
   </si>
   <si>
     <t xml:space="preserve">0.454237133264542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463395148515701</t>
+    <t xml:space="preserve">0.463395118713379</t>
   </si>
   <si>
     <t xml:space="preserve">0.476216346025467</t>
@@ -69229,7 +69229,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6911111111</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>109289</v>
@@ -69250,6 +69250,32 @@
         <v>1266</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6910763889</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>85774</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>0.465000003576279</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>0.456999987363815</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32635235786438</t>
+    <t xml:space="preserve">0.326352328062057</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844781637192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323679089546204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980766296387</t>
+    <t xml:space="preserve">0.326844841241837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323679059743881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980736494064</t>
   </si>
   <si>
     <t xml:space="preserve">0.313056260347366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304966062307358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299760192632675</t>
+    <t xml:space="preserve">0.304966032505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299760162830353</t>
   </si>
   <si>
     <t xml:space="preserve">0.309538781642914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302503824234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287097215652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274363905191422</t>
+    <t xml:space="preserve">0.302503794431686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287097245454788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274363934993744</t>
   </si>
   <si>
     <t xml:space="preserve">0.278655260801315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265288800001144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260645747184753</t>
+    <t xml:space="preserve">0.265288829803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260645717382431</t>
   </si>
   <si>
     <t xml:space="preserve">0.270846396684647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269087702035904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272956907749176</t>
+    <t xml:space="preserve">0.269087672233582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272956937551498</t>
   </si>
   <si>
     <t xml:space="preserve">0.270142942667007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265921920537949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290825724601746</t>
+    <t xml:space="preserve">0.265921950340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290825754404068</t>
   </si>
   <si>
     <t xml:space="preserve">0.288433849811554</t>
@@ -116,103 +116,103 @@
     <t xml:space="preserve">0.262545168399811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260293990373611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246927514672279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246224015951157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239751890301704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240103602409363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271549940109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276122719049454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274645268917084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277881443500519</t>
+    <t xml:space="preserve">0.260293960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246927559375763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24622406065464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239751860499382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240103587508202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271549910306931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276122689247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274645298719406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277881413698196</t>
   </si>
   <si>
     <t xml:space="preserve">0.270987153053284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281539589166641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27717787027359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263318985700607</t>
+    <t xml:space="preserve">0.281539618968964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277177900075912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263319045305252</t>
   </si>
   <si>
     <t xml:space="preserve">0.2680324614048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28210237622261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295468837022781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293358325958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291740298271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288644939661026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504183292389</t>
+    <t xml:space="preserve">0.282102406024933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295468807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293358355760574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291740328073502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288644880056381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504242897034</t>
   </si>
   <si>
     <t xml:space="preserve">0.281469255685806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277248233556747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278373837471008</t>
+    <t xml:space="preserve">0.27724826335907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278373867273331</t>
   </si>
   <si>
     <t xml:space="preserve">0.287026882171631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297368258237839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295820564031601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307217210531235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305669575929642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313759744167328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320442974567413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317417979240417</t>
+    <t xml:space="preserve">0.297368288040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295820593833923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307217240333557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305669516324997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31375977396965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320443004369736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317417949438095</t>
   </si>
   <si>
     <t xml:space="preserve">0.316573768854141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306161969900131</t>
+    <t xml:space="preserve">0.306161999702454</t>
   </si>
   <si>
     <t xml:space="preserve">0.310945749282837</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">0.311438232660294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30180025100708</t>
+    <t xml:space="preserve">0.301800280809402</t>
   </si>
   <si>
     <t xml:space="preserve">0.288011789321899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288082093000412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280554711818695</t>
+    <t xml:space="preserve">0.288082122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28055465221405</t>
   </si>
   <si>
     <t xml:space="preserve">0.281328558921814</t>
@@ -239,64 +239,64 @@
     <t xml:space="preserve">0.291880995035172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301378220319748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311649292707443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310242295265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311508536338806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314533621072769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316644132137299</t>
+    <t xml:space="preserve">0.30137825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311649262905121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310242265462875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311508566141129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314533591270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316644102334976</t>
   </si>
   <si>
     <t xml:space="preserve">0.318684250116348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330573320388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330643713474274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334161162376404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3335280418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330432653427124</t>
+    <t xml:space="preserve">0.330573350191116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330643683671951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334161221981049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333528012037277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330432623624802</t>
   </si>
   <si>
     <t xml:space="preserve">0.327126234769821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323538362979889</t>
+    <t xml:space="preserve">0.323538392782211</t>
   </si>
   <si>
     <t xml:space="preserve">0.318543553352356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319247007369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323116302490234</t>
+    <t xml:space="preserve">0.31924706697464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323116332292557</t>
   </si>
   <si>
     <t xml:space="preserve">0.321005791425705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324874997138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323749423027039</t>
+    <t xml:space="preserve">0.324875026941299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323749393224716</t>
   </si>
   <si>
     <t xml:space="preserve">0.325015723705292</t>
@@ -308,16 +308,16 @@
     <t xml:space="preserve">0.326774477958679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33176925778389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344713628292084</t>
+    <t xml:space="preserve">0.331769287586212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344713658094406</t>
   </si>
   <si>
     <t xml:space="preserve">0.34204038977623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338030457496643</t>
+    <t xml:space="preserve">0.338030397891998</t>
   </si>
   <si>
     <t xml:space="preserve">0.352100372314453</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">0.354914337396622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351678252220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350341618061066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343306630849838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343165963888168</t>
+    <t xml:space="preserve">0.351678282022476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350341588258743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343306660652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343165934085846</t>
   </si>
   <si>
     <t xml:space="preserve">0.341196179389954</t>
@@ -347,61 +347,61 @@
     <t xml:space="preserve">0.337045520544052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323537766933441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309325903654099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3121537566185</t>
+    <t xml:space="preserve">0.323537796735764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309325873851776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312153726816177</t>
   </si>
   <si>
     <t xml:space="preserve">0.308890819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311936259269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325277984142303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322232633829117</t>
+    <t xml:space="preserve">0.311936289072037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325278013944626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322232604026794</t>
   </si>
   <si>
     <t xml:space="preserve">0.318607121706009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324190378189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30722314119339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299102008342743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299464553594589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313096404075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320854961872101</t>
+    <t xml:space="preserve">0.324190407991409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307223111391068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299101978540421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299464613199234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3130963742733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320854872465134</t>
   </si>
   <si>
     <t xml:space="preserve">0.318027019500732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319042146205902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318317115306854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309543401002884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311791241168976</t>
+    <t xml:space="preserve">0.319042176008224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318317085504532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309543371200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311791181564331</t>
   </si>
   <si>
     <t xml:space="preserve">0.310558527708054</t>
@@ -410,28 +410,28 @@
     <t xml:space="preserve">0.311066091060638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322087585926056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319767266511917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318172067403793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309978514909744</t>
+    <t xml:space="preserve">0.322087615728378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319767326116562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318172037601471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309978485107422</t>
   </si>
   <si>
     <t xml:space="preserve">0.306715548038483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305627882480621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301784873008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300914764404297</t>
+    <t xml:space="preserve">0.305627912282944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30178490281105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300914734601974</t>
   </si>
   <si>
     <t xml:space="preserve">0.298739492893219</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">0.291488528251648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294316381216049</t>
+    <t xml:space="preserve">0.294316411018372</t>
   </si>
   <si>
     <t xml:space="preserve">0.304467737674713</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">0.301204800605774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302727520465851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30381515622139</t>
+    <t xml:space="preserve">0.302727490663528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303815186023712</t>
   </si>
   <si>
     <t xml:space="preserve">0.300624758005142</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">0.29743430018425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299682080745697</t>
+    <t xml:space="preserve">0.299682110548019</t>
   </si>
   <si>
     <t xml:space="preserve">0.301929891109467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301712363958359</t>
+    <t xml:space="preserve">0.301712393760681</t>
   </si>
   <si>
     <t xml:space="preserve">0.302364975214005</t>
@@ -482,22 +482,22 @@
     <t xml:space="preserve">0.302219927310944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29714423418045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295621573925018</t>
+    <t xml:space="preserve">0.297144263982773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295621603727341</t>
   </si>
   <si>
     <t xml:space="preserve">0.293663829565048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297289252281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291706025600433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292358607053757</t>
+    <t xml:space="preserve">0.297289282083511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291706055402756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292358636856079</t>
   </si>
   <si>
     <t xml:space="preserve">0.290038347244263</t>
@@ -509,31 +509,31 @@
     <t xml:space="preserve">0.292648673057556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287645548582077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295041471719742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29156106710434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294533938169479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289313167333603</t>
+    <t xml:space="preserve">0.287645518779755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295041531324387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291561007499695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294533908367157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289313226938248</t>
   </si>
   <si>
     <t xml:space="preserve">0.287935554981232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283004879951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287428021430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282859891653061</t>
+    <t xml:space="preserve">0.283004939556122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287427991628647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282859832048416</t>
   </si>
   <si>
     <t xml:space="preserve">0.275826454162598</t>
@@ -542,100 +542,100 @@
     <t xml:space="preserve">0.279161870479584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26973569393158</t>
+    <t xml:space="preserve">0.269735664129257</t>
   </si>
   <si>
     <t xml:space="preserve">0.273288607597351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27952441573143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282062292098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283802479505539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282134741544724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287137985229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292866200208664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301422327756882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295839101076126</t>
+    <t xml:space="preserve">0.279524475336075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282062262296677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283802568912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282134801149368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287137895822525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292866170406342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301422297954559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295839130878448</t>
   </si>
   <si>
     <t xml:space="preserve">0.296564191579819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300262153148651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297071784734726</t>
+    <t xml:space="preserve">0.300262212753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297071754932404</t>
   </si>
   <si>
     <t xml:space="preserve">0.292938739061356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298812031745911</t>
+    <t xml:space="preserve">0.298812001943588</t>
   </si>
   <si>
     <t xml:space="preserve">0.296056658029556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31019601225853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306425541639328</t>
+    <t xml:space="preserve">0.310195982456207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306425452232361</t>
   </si>
   <si>
     <t xml:space="preserve">0.302509963512421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306062936782837</t>
+    <t xml:space="preserve">0.306062996387482</t>
   </si>
   <si>
     <t xml:space="preserve">0.307078093290329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301639884710312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294098883867264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283077418804169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287863045930862</t>
+    <t xml:space="preserve">0.301639825105667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294098854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283077389001846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28786301612854</t>
   </si>
   <si>
     <t xml:space="preserve">0.289603292942047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285615235567093</t>
+    <t xml:space="preserve">0.285615265369415</t>
   </si>
   <si>
     <t xml:space="preserve">0.2839475274086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288805663585663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293736308813095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290835946798325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283512502908707</t>
+    <t xml:space="preserve">0.288805693387985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293736279010773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290835976600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283512443304062</t>
   </si>
   <si>
     <t xml:space="preserve">0.281409680843353</t>
@@ -644,34 +644,34 @@
     <t xml:space="preserve">0.280684620141983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279016822576523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273796230554581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291415989398956</t>
+    <t xml:space="preserve">0.279016882181168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273796200752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291416019201279</t>
   </si>
   <si>
     <t xml:space="preserve">0.295114040374756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290545880794525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288588166236877</t>
+    <t xml:space="preserve">0.290545910596848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288588106632233</t>
   </si>
   <si>
     <t xml:space="preserve">0.292213618755341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292141139507294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294388890266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299392014741898</t>
+    <t xml:space="preserve">0.292141109704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294388920068741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299392104148865</t>
   </si>
   <si>
     <t xml:space="preserve">0.296491682529449</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">0.303597629070282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309615910053253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307440638542175</t>
+    <t xml:space="preserve">0.309615939855576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307440608739853</t>
   </si>
   <si>
     <t xml:space="preserve">0.319187194108963</t>
@@ -695,10 +695,10 @@
     <t xml:space="preserve">0.331368774175644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345000624656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349786221981049</t>
+    <t xml:space="preserve">0.345000594854355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349786251783371</t>
   </si>
   <si>
     <t xml:space="preserve">0.358342379331589</t>
@@ -710,49 +710,49 @@
     <t xml:space="preserve">0.34964120388031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352396577596664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355296939611435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359429985284805</t>
+    <t xml:space="preserve">0.352396547794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355296969413757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35943004488945</t>
   </si>
   <si>
     <t xml:space="preserve">0.352686613798141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346885830163956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343187868595123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346160739660263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346595823764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346450746059418</t>
+    <t xml:space="preserve">0.346885859966278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343187838792801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346160769462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346595793962479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346450805664062</t>
   </si>
   <si>
     <t xml:space="preserve">0.344347983598709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350221276283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350946366786957</t>
+    <t xml:space="preserve">0.350221246480942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350946336984634</t>
   </si>
   <si>
     <t xml:space="preserve">0.388288795948029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397715091705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379950255155563</t>
+    <t xml:space="preserve">0.397715061903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379950225353241</t>
   </si>
   <si>
     <t xml:space="preserve">0.382125526666641</t>
@@ -761,34 +761,34 @@
     <t xml:space="preserve">0.37487456202507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37342432141304</t>
+    <t xml:space="preserve">0.373424351215363</t>
   </si>
   <si>
     <t xml:space="preserve">0.377412408590317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373061835765839</t>
+    <t xml:space="preserve">0.373061805963516</t>
   </si>
   <si>
     <t xml:space="preserve">0.369798898696899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383575677871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369436353445053</t>
+    <t xml:space="preserve">0.383575648069382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369436323642731</t>
   </si>
   <si>
     <t xml:space="preserve">0.369073778390884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358197331428528</t>
+    <t xml:space="preserve">0.35819736123085</t>
   </si>
   <si>
     <t xml:space="preserve">0.358052313327789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377049833536148</t>
+    <t xml:space="preserve">0.377049803733826</t>
   </si>
   <si>
     <t xml:space="preserve">0.412579536437988</t>
@@ -797,28 +797,28 @@
     <t xml:space="preserve">0.382488012313843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400615453720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394452184438705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385750949382782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393727004528046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390464067459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384300768375397</t>
+    <t xml:space="preserve">0.400615483522415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394452124834061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385750979185104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393727034330368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390464097261429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384300798177719</t>
   </si>
   <si>
     <t xml:space="preserve">0.391551792621613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387563765048981</t>
+    <t xml:space="preserve">0.387563705444336</t>
   </si>
   <si>
     <t xml:space="preserve">0.390826612710953</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.395177274942398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393364459276199</t>
+    <t xml:space="preserve">0.393364518880844</t>
   </si>
   <si>
     <t xml:space="preserve">0.397352486848831</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">0.395539790391922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396627396345139</t>
+    <t xml:space="preserve">0.396627455949783</t>
   </si>
   <si>
     <t xml:space="preserve">0.398440152406693</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">0.393001914024353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398077636957169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401703119277954</t>
+    <t xml:space="preserve">0.398077607154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401703059673309</t>
   </si>
   <si>
     <t xml:space="preserve">0.392276853322983</t>
@@ -863,37 +863,37 @@
     <t xml:space="preserve">0.38720116019249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386476039886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382850557565689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394089579582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38937646150589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381762951612473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38103786110878</t>
+    <t xml:space="preserve">0.386476099491119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382850646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394089639186859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389376431703568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38176292181015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381037890911102</t>
   </si>
   <si>
     <t xml:space="preserve">0.386838644742966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38865140080452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385025948286057</t>
+    <t xml:space="preserve">0.388651371002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385025918483734</t>
   </si>
   <si>
     <t xml:space="preserve">0.391189217567444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392639368772507</t>
+    <t xml:space="preserve">0.392639398574829</t>
   </si>
   <si>
     <t xml:space="preserve">0.425631254911423</t>
@@ -902,31 +902,31 @@
     <t xml:space="preserve">0.419105410575867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445208817720413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435057520866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442308455705643</t>
+    <t xml:space="preserve">0.44520890712738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435057580471039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44230854511261</t>
   </si>
   <si>
     <t xml:space="preserve">0.43261194229126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413591980934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408370822668076</t>
+    <t xml:space="preserve">0.413591951131821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408370792865753</t>
   </si>
   <si>
     <t xml:space="preserve">0.406879037618637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402776718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399047315120697</t>
+    <t xml:space="preserve">0.402776747941971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399047285318375</t>
   </si>
   <si>
     <t xml:space="preserve">0.400539010763168</t>
@@ -935,25 +935,25 @@
     <t xml:space="preserve">0.395317852497101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396809577941895</t>
+    <t xml:space="preserve">0.396809607744217</t>
   </si>
   <si>
     <t xml:space="preserve">0.396063774824142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393080234527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38860496878624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387858986854553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379654347896576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381146043539047</t>
+    <t xml:space="preserve">0.393080204725266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388604909181595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387859016656876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379654288291931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38114607334137</t>
   </si>
   <si>
     <t xml:space="preserve">0.383010774850845</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">0.383756697177887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386740207672119</t>
+    <t xml:space="preserve">0.386740177869797</t>
   </si>
   <si>
     <t xml:space="preserve">0.390096694231033</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">0.394944906234741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403522580862045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410235494375229</t>
+    <t xml:space="preserve">0.403522551059723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410235553979874</t>
   </si>
   <si>
     <t xml:space="preserve">0.407251954078674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407624930143356</t>
+    <t xml:space="preserve">0.407624959945679</t>
   </si>
   <si>
     <t xml:space="preserve">0.408743739128113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406506150960922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40091198682785</t>
+    <t xml:space="preserve">0.4065061211586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400912016630173</t>
   </si>
   <si>
     <t xml:space="preserve">0.394199043512344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398674339056015</t>
+    <t xml:space="preserve">0.39867427945137</t>
   </si>
   <si>
     <t xml:space="preserve">0.390842586755753</t>
@@ -1010,37 +1010,37 @@
     <t xml:space="preserve">0.392334342002869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388231962919235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387113124132156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391588419675827</t>
+    <t xml:space="preserve">0.388231992721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387113153934479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391588389873505</t>
   </si>
   <si>
     <t xml:space="preserve">0.389350771903992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38562136888504</t>
+    <t xml:space="preserve">0.385621398687363</t>
   </si>
   <si>
     <t xml:space="preserve">0.380773156881332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385248422622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383383721113205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397928446531296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409489661455154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410981327295303</t>
+    <t xml:space="preserve">0.385248392820358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383383750915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397928476333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409489631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410981386899948</t>
   </si>
   <si>
     <t xml:space="preserve">0.414337813854218</t>
@@ -1052,70 +1052,70 @@
     <t xml:space="preserve">0.41657555103302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415829598903656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4240343272686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439324945211411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866109371185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428882628679276</t>
+    <t xml:space="preserve">0.415829628705978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424034297466278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439324915409088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866139173508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428882539272308</t>
   </si>
   <si>
     <t xml:space="preserve">0.420304924249649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421796679496765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428509652614594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454988479614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44529202580452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4445461332798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440443813800812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449767291545868</t>
+    <t xml:space="preserve">0.42179673910141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428509622812271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454988539218903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445291996002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444546103477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440443783998489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44976732134819</t>
   </si>
   <si>
     <t xml:space="preserve">0.459463745355606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460955530405045</t>
+    <t xml:space="preserve">0.4609554708004</t>
   </si>
   <si>
     <t xml:space="preserve">0.469533145427704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466549694538116</t>
+    <t xml:space="preserve">0.466549664735794</t>
   </si>
   <si>
     <t xml:space="preserve">0.474008500576019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474754393100739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348527431488</t>
+    <t xml:space="preserve">0.474754422903061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480348438024521</t>
   </si>
   <si>
     <t xml:space="preserve">0.485942542552948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482586145401001</t>
+    <t xml:space="preserve">0.482586085796356</t>
   </si>
   <si>
     <t xml:space="preserve">0.485569685697556</t>
@@ -1127,52 +1127,52 @@
     <t xml:space="preserve">0.511302590370178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521745026111603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512794435024261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5195072889328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511675536632538</t>
+    <t xml:space="preserve">0.521744966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512794375419617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519507348537445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511675477027893</t>
   </si>
   <si>
     <t xml:space="preserve">0.506081402301788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501233220100403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502351999282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495266169309616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49153670668602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477737903594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478483766317368</t>
+    <t xml:space="preserve">0.501233160495758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502352058887482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495266109704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491536736488342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477737873792648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478483825922012</t>
   </si>
   <si>
     <t xml:space="preserve">0.48109433054924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492282629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499741494655609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4937744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495638996362686</t>
+    <t xml:space="preserve">0.492282658815384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499741464853287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493774324655533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495639026165009</t>
   </si>
   <si>
     <t xml:space="preserve">0.507946133613586</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">0.493028491735458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50869208574295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503470838069916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508319139480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507200181484222</t>
+    <t xml:space="preserve">0.508692026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503470897674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508319020271301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507200241088867</t>
   </si>
   <si>
     <t xml:space="preserve">0.510183811187744</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">0.498249650001526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510929703712463</t>
+    <t xml:space="preserve">0.510929644107819</t>
   </si>
   <si>
     <t xml:space="preserve">0.531068563461304</t>
@@ -1241,64 +1241,64 @@
     <t xml:space="preserve">0.574329674243927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576567351818085</t>
+    <t xml:space="preserve">0.576567411422729</t>
   </si>
   <si>
     <t xml:space="preserve">0.577313244342804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583280384540558</t>
+    <t xml:space="preserve">0.583280265331268</t>
   </si>
   <si>
     <t xml:space="preserve">0.59148496389389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585517942905426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575075566768646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612369656562805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556428551673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551953256130219</t>
+    <t xml:space="preserve">0.585518002510071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575075626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61236971616745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556428492069244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551953196525574</t>
   </si>
   <si>
     <t xml:space="preserve">0.548223853111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53479790687561</t>
+    <t xml:space="preserve">0.534797847270966</t>
   </si>
   <si>
     <t xml:space="preserve">0.521372020244598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505708456039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528084933757782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54524028301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522863805294037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517642736434937</t>
+    <t xml:space="preserve">0.505708515644073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528084993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545240342617035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522863745689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517642676830292</t>
   </si>
   <si>
     <t xml:space="preserve">0.532560288906097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531814396381378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523609638214111</t>
+    <t xml:space="preserve">0.531814455986023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523609697818756</t>
   </si>
   <si>
     <t xml:space="preserve">0.516150832176208</t>
@@ -1313,31 +1313,31 @@
     <t xml:space="preserve">0.498995572328568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46319317817688</t>
+    <t xml:space="preserve">0.463193148374557</t>
   </si>
   <si>
     <t xml:space="preserve">0.469906091690063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476619064807892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477364987134933</t>
+    <t xml:space="preserve">0.476619124412537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477364927530289</t>
   </si>
   <si>
     <t xml:space="preserve">0.494520276784897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490044951438904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478856712579727</t>
+    <t xml:space="preserve">0.490045011043549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478856772184372</t>
   </si>
   <si>
     <t xml:space="preserve">0.47811084985733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468414396047592</t>
+    <t xml:space="preserve">0.46841436624527</t>
   </si>
   <si>
     <t xml:space="preserve">0.481840282678604</t>
@@ -1352,40 +1352,40 @@
     <t xml:space="preserve">0.473635524511337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474381357431412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484823822975159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487061411142349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483332008123398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50421679019928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504962563514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49675789475441</t>
+    <t xml:space="preserve">0.474381446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484823763370514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487061470746994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483331978321075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504216730594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504962682723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496757864952087</t>
   </si>
   <si>
     <t xml:space="preserve">0.497503757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486315548419952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500487387180328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454242616891861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465430825948715</t>
+    <t xml:space="preserve">0.486315578222275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500487327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454242557287216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465430915355682</t>
   </si>
   <si>
     <t xml:space="preserve">0.452004939317703</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">0.457226097583771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458717852830887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462447315454483</t>
+    <t xml:space="preserve">0.458717912435532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462447226047516</t>
   </si>
   <si>
     <t xml:space="preserve">0.455734342336655</t>
@@ -1409,25 +1409,25 @@
     <t xml:space="preserve">0.485727846622467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48418590426445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474933922290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469536989927292</t>
+    <t xml:space="preserve">0.484185874462128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47493389248848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469536900520325</t>
   </si>
   <si>
     <t xml:space="preserve">0.464910984039307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461055964231491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463368952274323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459514021873474</t>
+    <t xml:space="preserve">0.461056023836136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463368922472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459513962268829</t>
   </si>
   <si>
     <t xml:space="preserve">0.457971960306168</t>
@@ -1436,43 +1436,43 @@
     <t xml:space="preserve">0.458743005990982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447949022054672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451032996177673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454888015985489</t>
+    <t xml:space="preserve">0.447949051856995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451032966375351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454887986183167</t>
   </si>
   <si>
     <t xml:space="preserve">0.446407049894333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441781103610992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443323105573654</t>
+    <t xml:space="preserve">0.441781044006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443323045969009</t>
   </si>
   <si>
     <t xml:space="preserve">0.494208872318268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474162876605988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481101870536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489582866430283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476475924253464</t>
+    <t xml:space="preserve">0.474162936210632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481101959943771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489582896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476475894451141</t>
   </si>
   <si>
     <t xml:space="preserve">0.464139968156815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461827009916306</t>
+    <t xml:space="preserve">0.461826950311661</t>
   </si>
   <si>
     <t xml:space="preserve">0.456429988145828</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">0.454117000102997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466452896595001</t>
+    <t xml:space="preserve">0.466453045606613</t>
   </si>
   <si>
     <t xml:space="preserve">0.467223942279816</t>
@@ -1493,91 +1493,91 @@
     <t xml:space="preserve">0.442552089691162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452575027942657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453345984220505</t>
+    <t xml:space="preserve">0.452574968338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453346073627472</t>
   </si>
   <si>
     <t xml:space="preserve">0.4410100877285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437926143407822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433300077915192</t>
+    <t xml:space="preserve">0.437926054000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433300107717514</t>
   </si>
   <si>
     <t xml:space="preserve">0.430987149477005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431758105754852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435613095760345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444865137338638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460285007953644</t>
+    <t xml:space="preserve">0.431758135557175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435613036155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444865077733994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284978151321</t>
   </si>
   <si>
     <t xml:space="preserve">0.45180407166481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470307946205139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471849918365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465681940317154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457200974225998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46259805560112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455659031867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450261980295181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449490994215012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437155067920685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440239042043686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42636114358902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427903115749359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407086193561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406315237283707</t>
+    <t xml:space="preserve">0.470308005809784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471849948167801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465681910514832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457201033830643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462597995996475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455659061670303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450262039899826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449491083621979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43715512752533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440239101648331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426361113786697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427903175354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407086223363876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406315207481384</t>
   </si>
   <si>
     <t xml:space="preserve">0.410170167684555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404002249240875</t>
+    <t xml:space="preserve">0.404002219438553</t>
   </si>
   <si>
     <t xml:space="preserve">0.407857209444046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410941183567047</t>
+    <t xml:space="preserve">0.410941243171692</t>
   </si>
   <si>
     <t xml:space="preserve">0.40014722943306</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">0.396292269229889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390895307064056</t>
+    <t xml:space="preserve">0.390895336866379</t>
   </si>
   <si>
     <t xml:space="preserve">0.390124261379242</t>
@@ -1604,115 +1604,115 @@
     <t xml:space="preserve">0.388582289218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394750326871872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397063255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389353275299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387040317058563</t>
+    <t xml:space="preserve">0.39475029706955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397063285112381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389353305101395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387040287256241</t>
   </si>
   <si>
     <t xml:space="preserve">0.385498315095901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375475376844406</t>
+    <t xml:space="preserve">0.375475317239761</t>
   </si>
   <si>
     <t xml:space="preserve">0.366223394870758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351188957691193</t>
+    <t xml:space="preserve">0.351188987493515</t>
   </si>
   <si>
     <t xml:space="preserve">0.345406502485275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348875969648361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366994440555573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37239134311676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36776539683342</t>
+    <t xml:space="preserve">0.348875999450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36699441075325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372391372919083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367765367031097</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162358999252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370078384876251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370463937520981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369692832231522</t>
+    <t xml:space="preserve">0.370078355073929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370463877916336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369692862033844</t>
   </si>
   <si>
     <t xml:space="preserve">0.365837901830673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371620386838913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368536382913589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368921875953674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378944844007492</t>
+    <t xml:space="preserve">0.371620357036591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368536353111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368921905755997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37894481420517</t>
   </si>
   <si>
     <t xml:space="preserve">0.383570820093155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377017349004745</t>
+    <t xml:space="preserve">0.377017378807068</t>
   </si>
   <si>
     <t xml:space="preserve">0.382414311170578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399376273155212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416338205337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424048125743866</t>
+    <t xml:space="preserve">0.39937624335289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416338235139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424048155546188</t>
   </si>
   <si>
     <t xml:space="preserve">0.424819111824036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417109191417694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422506153583527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421735137701035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420964151620865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408628195524216</t>
+    <t xml:space="preserve">0.417109161615372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422506183385849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421735167503357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420964121818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40862825512886</t>
   </si>
   <si>
     <t xml:space="preserve">0.400918245315552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404773205518723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405544251203537</t>
+    <t xml:space="preserve">0.4047731757164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405544281005859</t>
   </si>
   <si>
     <t xml:space="preserve">0.411712199449539</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">0.423277169466019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425590068101883</t>
+    <t xml:space="preserve">0.425590187311172</t>
   </si>
   <si>
     <t xml:space="preserve">0.419422179460526</t>
@@ -1733,37 +1733,37 @@
     <t xml:space="preserve">0.430216133594513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427132189273834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414025187492371</t>
+    <t xml:space="preserve">0.427132129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414025157690048</t>
   </si>
   <si>
     <t xml:space="preserve">0.41479617357254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413254231214523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40939924120903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395521283149719</t>
+    <t xml:space="preserve">0.413254201412201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409399211406708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395521253347397</t>
   </si>
   <si>
     <t xml:space="preserve">0.393208265304565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392437309026718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391666293144226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393979251384735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39860525727272</t>
+    <t xml:space="preserve">0.392437249422073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391666322946548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393979281187057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398605287075043</t>
   </si>
   <si>
     <t xml:space="preserve">0.403231263160706</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">0.410471081733704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409666270017624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415300101041794</t>
+    <t xml:space="preserve">0.409666240215302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415300160646439</t>
   </si>
   <si>
     <t xml:space="preserve">0.412885636091232</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">0.412080824375153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399203240871429</t>
+    <t xml:space="preserve">0.399203211069107</t>
   </si>
   <si>
     <t xml:space="preserve">0.401215374469757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404032319784164</t>
+    <t xml:space="preserve">0.404032289981842</t>
   </si>
   <si>
     <t xml:space="preserve">0.397995978593826</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">0.403227478265762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398398399353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400008112192154</t>
+    <t xml:space="preserve">0.39839842915535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400008082389832</t>
   </si>
   <si>
     <t xml:space="preserve">0.40242263674736</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">0.400410532951355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395983844995499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399605691432953</t>
+    <t xml:space="preserve">0.395983874797821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39960566163063</t>
   </si>
   <si>
     <t xml:space="preserve">0.418519526720047</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">0.417714685201645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416909873485565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404837191104889</t>
+    <t xml:space="preserve">0.416909843683243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404837220907211</t>
   </si>
   <si>
     <t xml:space="preserve">0.401617795228958</t>
@@ -1838,22 +1838,22 @@
     <t xml:space="preserve">0.407251685857773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408056557178497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405642002820969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397593557834625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391154795885086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406446844339371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42656797170639</t>
+    <t xml:space="preserve">0.408056527376175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405642062425613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397593587636948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391154766082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406446874141693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426567941904068</t>
   </si>
   <si>
     <t xml:space="preserve">0.433811604976654</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">0.424153476953506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432201892137527</t>
+    <t xml:space="preserve">0.43220192193985</t>
   </si>
   <si>
     <t xml:space="preserve">0.425763130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428177654743195</t>
+    <t xml:space="preserve">0.428177684545517</t>
   </si>
   <si>
     <t xml:space="preserve">0.43300673365593</t>
@@ -1877,13 +1877,13 @@
     <t xml:space="preserve">0.429787367582321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420934110879898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428982496261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43703094124794</t>
+    <t xml:space="preserve">0.420934081077576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428982526063919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437030971050262</t>
   </si>
   <si>
     <t xml:space="preserve">0.434616476297379</t>
@@ -1892,25 +1892,25 @@
     <t xml:space="preserve">0.430592268705368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4426648914814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458761781454086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466810196638107</t>
+    <t xml:space="preserve">0.442664921283722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458761751651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466810256242752</t>
   </si>
   <si>
     <t xml:space="preserve">0.473248988389969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4764683842659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478882938623428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47566357254982</t>
+    <t xml:space="preserve">0.476468354463577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478882998228073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475663542747498</t>
   </si>
   <si>
     <t xml:space="preserve">0.481297463178635</t>
@@ -1919,58 +1919,58 @@
     <t xml:space="preserve">0.478078037500381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474858701229095</t>
+    <t xml:space="preserve">0.474858641624451</t>
   </si>
   <si>
     <t xml:space="preserve">0.471639364957809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472444176673889</t>
+    <t xml:space="preserve">0.472444236278534</t>
   </si>
   <si>
     <t xml:space="preserve">0.486126512289047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480492651462555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494979798793793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511881530284882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513491272926331</t>
+    <t xml:space="preserve">0.480492621660233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494979828596115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511881589889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513491213321686</t>
   </si>
   <si>
     <t xml:space="preserve">0.520734906196594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535222113132477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534417271614075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523149430751801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51510101556778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516710638999939</t>
+    <t xml:space="preserve">0.535222053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53441721200943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523149371147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51510089635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516710698604584</t>
   </si>
   <si>
     <t xml:space="preserve">0.522344589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556148111820221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555343210697174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551319062709808</t>
+    <t xml:space="preserve">0.556148052215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555343270301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551319003105164</t>
   </si>
   <si>
     <t xml:space="preserve">0.557757794857025</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">0.571440160274506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561782002449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560977220535278</t>
+    <t xml:space="preserve">0.56178206205368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560977280139923</t>
   </si>
   <si>
     <t xml:space="preserve">0.552928686141968</t>
@@ -2000,46 +2000,46 @@
     <t xml:space="preserve">0.599609732627869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61168247461319</t>
+    <t xml:space="preserve">0.611682415008545</t>
   </si>
   <si>
     <t xml:space="preserve">0.606853365898132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60202431678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614901840686798</t>
+    <t xml:space="preserve">0.602024257183075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614901781082153</t>
   </si>
   <si>
     <t xml:space="preserve">0.600414574146271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608462989330292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593975782394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590756416320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595585525035858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609267950057983</t>
+    <t xml:space="preserve">0.608463048934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593975722789764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59075653553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595585465431213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609267890453339</t>
   </si>
   <si>
     <t xml:space="preserve">0.614096999168396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606048464775085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593171000480652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598804891109467</t>
+    <t xml:space="preserve">0.60604852437973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593170940876007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598804950714111</t>
   </si>
   <si>
     <t xml:space="preserve">0.601219356060028</t>
@@ -2048,34 +2048,34 @@
     <t xml:space="preserve">0.594780683517456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603633940219879</t>
+    <t xml:space="preserve">0.603633880615234</t>
   </si>
   <si>
     <t xml:space="preserve">0.610072731971741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.59799998998642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630193829536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631803572177887</t>
+    <t xml:space="preserve">0.598000049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630193889141083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631803631782532</t>
   </si>
   <si>
     <t xml:space="preserve">0.646290719509125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65594893693924</t>
+    <t xml:space="preserve">0.655948877334595</t>
   </si>
   <si>
     <t xml:space="preserve">0.659973084926605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689752399921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684118509292603</t>
+    <t xml:space="preserve">0.689752340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684118449687958</t>
   </si>
   <si>
     <t xml:space="preserve">0.661582827568054</t>
@@ -2084,16 +2084,16 @@
     <t xml:space="preserve">0.588341891765594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581098258495331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572244942188263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540856063365936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543270528316498</t>
+    <t xml:space="preserve">0.581098318099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572245001792908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540856003761292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543270587921143</t>
   </si>
   <si>
     <t xml:space="preserve">0.518320381641388</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">0.526368796825409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490955621004105</t>
+    <t xml:space="preserve">0.490955650806427</t>
   </si>
   <si>
     <t xml:space="preserve">0.439445495605469</t>
@@ -2117,22 +2117,22 @@
     <t xml:space="preserve">0.323145359754562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348095595836639</t>
+    <t xml:space="preserve">0.348095566034317</t>
   </si>
   <si>
     <t xml:space="preserve">0.303829073905945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282500654459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288939476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291353970766068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304633975028992</t>
+    <t xml:space="preserve">0.282500684261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288939446210861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29135400056839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304633945226669</t>
   </si>
   <si>
     <t xml:space="preserve">0.308255732059479</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">0.343668937683105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358961015939713</t>
+    <t xml:space="preserve">0.35896098613739</t>
   </si>
   <si>
     <t xml:space="preserve">0.37224093079567</t>
@@ -2150,16 +2150,16 @@
     <t xml:space="preserve">0.355741590261459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373850673437119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391959667205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37908211350441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375057905912399</t>
+    <t xml:space="preserve">0.373850643634796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391959607601166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379082143306732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375057876110077</t>
   </si>
   <si>
     <t xml:space="preserve">0.384716033935547</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">0.386325716972351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374253064393997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362180352210999</t>
+    <t xml:space="preserve">0.374253034591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362180382013321</t>
   </si>
   <si>
     <t xml:space="preserve">0.351717382669449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353327095508575</t>
+    <t xml:space="preserve">0.353327065706253</t>
   </si>
   <si>
     <t xml:space="preserve">0.34930282831192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34447380900383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323547810316086</t>
+    <t xml:space="preserve">0.344473779201508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323547780513763</t>
   </si>
   <si>
     <t xml:space="preserve">0.338034987449646</t>
@@ -2201,40 +2201,40 @@
     <t xml:space="preserve">0.346083492040634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350912511348724</t>
+    <t xml:space="preserve">0.350912541151047</t>
   </si>
   <si>
     <t xml:space="preserve">0.348497986793518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342864066362381</t>
+    <t xml:space="preserve">0.342864096164703</t>
   </si>
   <si>
     <t xml:space="preserve">0.34527862071991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336425364017487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324352622032166</t>
+    <t xml:space="preserve">0.336425334215164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324352651834488</t>
   </si>
   <si>
     <t xml:space="preserve">0.329986542463303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326767176389694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321938127279282</t>
+    <t xml:space="preserve">0.326767146587372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321938097476959</t>
   </si>
   <si>
     <t xml:space="preserve">0.331596255302429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340449541807175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347693175077438</t>
+    <t xml:space="preserve">0.340449571609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347693145275116</t>
   </si>
   <si>
     <t xml:space="preserve">0.352522224187851</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">0.35493677854538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36942395567894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382301509380341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379886955022812</t>
+    <t xml:space="preserve">0.369423985481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382301449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379887014627457</t>
   </si>
   <si>
     <t xml:space="preserve">0.371838539838791</t>
@@ -2261,52 +2261,52 @@
     <t xml:space="preserve">0.330791413784027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356546491384506</t>
+    <t xml:space="preserve">0.356546401977539</t>
   </si>
   <si>
     <t xml:space="preserve">0.357351303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350107669830322</t>
+    <t xml:space="preserve">0.350107699632645</t>
   </si>
   <si>
     <t xml:space="preserve">0.346888303756714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342059254646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337230175733566</t>
+    <t xml:space="preserve">0.342059224843979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337230145931244</t>
   </si>
   <si>
     <t xml:space="preserve">0.328376859426498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33562046289444</t>
+    <t xml:space="preserve">0.335620492696762</t>
   </si>
   <si>
     <t xml:space="preserve">0.370228856801987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358156114816666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363790065050125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420129209756851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424958258867264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437835842370987</t>
+    <t xml:space="preserve">0.358156144618988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363790035247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420129299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424958288669586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437835872173309</t>
   </si>
   <si>
     <t xml:space="preserve">0.444274514913559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445884346961975</t>
+    <t xml:space="preserve">0.44588428735733</t>
   </si>
   <si>
     <t xml:space="preserve">0.482907235622406</t>
@@ -2324,19 +2324,19 @@
     <t xml:space="preserve">0.529588162899017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519930064678192</t>
+    <t xml:space="preserve">0.519930124282837</t>
   </si>
   <si>
     <t xml:space="preserve">0.507052481174469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500613808631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494175016880035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502223432064056</t>
+    <t xml:space="preserve">0.500613749027252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494174987077713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502223551273346</t>
   </si>
   <si>
     <t xml:space="preserve">0.537636637687683</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">0.499004065990448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492565274238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487736225128174</t>
+    <t xml:space="preserve">0.492565304040909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487736254930496</t>
   </si>
   <si>
     <t xml:space="preserve">0.484516859054565</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">0.447493970394135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43139711022377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449103683233261</t>
+    <t xml:space="preserve">0.431397080421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449103713035583</t>
   </si>
   <si>
     <t xml:space="preserve">0.43622612953186</t>
@@ -2378,79 +2378,79 @@
     <t xml:space="preserve">0.378277271986008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375862747430801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367009401321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35976579785347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376667559146881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4217389523983</t>
+    <t xml:space="preserve">0.375862777233124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367009431123734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359765827655792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376667588949203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421738862991333</t>
   </si>
   <si>
     <t xml:space="preserve">0.423348635435104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441055208444595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50544285774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468419939279556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461981207132339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46520060300827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452323019504547</t>
+    <t xml:space="preserve">0.441055178642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505442798137665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468419998884201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461981177330017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465200573205948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452323079109192</t>
   </si>
   <si>
     <t xml:space="preserve">0.455542415380478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450713336467743</t>
+    <t xml:space="preserve">0.450713366270065</t>
   </si>
   <si>
     <t xml:space="preserve">0.460371524095535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457152158021927</t>
+    <t xml:space="preserve">0.457152098417282</t>
   </si>
   <si>
     <t xml:space="preserve">0.453932732343674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479687809944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495784670114517</t>
+    <t xml:space="preserve">0.47968778014183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495784640312195</t>
   </si>
   <si>
     <t xml:space="preserve">0.489345908164978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547294735908508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565001308917999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576269268989563</t>
+    <t xml:space="preserve">0.547294795513153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565001368522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576269209384918</t>
   </si>
   <si>
     <t xml:space="preserve">0.575464367866516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569830417633057</t>
+    <t xml:space="preserve">0.569830477237701</t>
   </si>
   <si>
     <t xml:space="preserve">0.549709320068359</t>
@@ -2459,22 +2459,22 @@
     <t xml:space="preserve">0.56741589307785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545685052871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558562695980072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544075429439545</t>
+    <t xml:space="preserve">0.545685112476349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558562576770782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5440753698349</t>
   </si>
   <si>
     <t xml:space="preserve">0.531197905540466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559367537498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573854684829712</t>
+    <t xml:space="preserve">0.559367477893829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573854625225067</t>
   </si>
   <si>
     <t xml:space="preserve">0.581903100013733</t>
@@ -2489,34 +2489,34 @@
     <t xml:space="preserve">0.552123844623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54809957742691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548904538154602</t>
+    <t xml:space="preserve">0.548099637031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548904418945312</t>
   </si>
   <si>
     <t xml:space="preserve">0.553733587265015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582058310508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581226825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573743164539337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567091047763824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574649333954</t>
+    <t xml:space="preserve">0.582058250904083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581226766109467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573743224143982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567091107368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574708938599</t>
   </si>
   <si>
     <t xml:space="preserve">0.57291167974472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561270475387573</t>
+    <t xml:space="preserve">0.561270534992218</t>
   </si>
   <si>
     <t xml:space="preserve">0.557944416999817</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">0.544640243053436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542977273464203</t>
+    <t xml:space="preserve">0.542977213859558</t>
   </si>
   <si>
     <t xml:space="preserve">0.530504584312439</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">0.531336069107056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532167553901672</t>
+    <t xml:space="preserve">0.532167613506317</t>
   </si>
   <si>
     <t xml:space="preserve">0.516368865966797</t>
@@ -2558,31 +2558,31 @@
     <t xml:space="preserve">0.502233147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515537321567535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498907178640366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493918031454086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494749546051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500570118427277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483939915895462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465646624565125</t>
+    <t xml:space="preserve">0.51553738117218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498907119035721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493918001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494749575853348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500570058822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483939945697784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46564656496048</t>
   </si>
   <si>
     <t xml:space="preserve">0.466478139162064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461489081382751</t>
+    <t xml:space="preserve">0.461489021778107</t>
   </si>
   <si>
     <t xml:space="preserve">0.460657566785812</t>
@@ -2594,13 +2594,13 @@
     <t xml:space="preserve">0.473130226135254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486434459686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489760458469391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503064692020416</t>
+    <t xml:space="preserve">0.486434429883957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489760518074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503064632415771</t>
   </si>
   <si>
     <t xml:space="preserve">0.50472766160965</t>
@@ -2612,16 +2612,16 @@
     <t xml:space="preserve">0.510548293590546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503896117210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495581090450287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484771370887756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482276827096939</t>
+    <t xml:space="preserve">0.503896176815033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495581030845642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484771400690079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482276886701584</t>
   </si>
   <si>
     <t xml:space="preserve">0.491423547267914</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">0.483108371496201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478119283914566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475624829530716</t>
+    <t xml:space="preserve">0.478119343519211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475624799728394</t>
   </si>
   <si>
     <t xml:space="preserve">0.476456314325333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529672980308533</t>
+    <t xml:space="preserve">0.529673039913177</t>
   </si>
   <si>
     <t xml:space="preserve">0.523852467536926</t>
@@ -2663,25 +2663,25 @@
     <t xml:space="preserve">0.527178525924683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547966301441193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528841495513916</t>
+    <t xml:space="preserve">0.547966241836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528841555118561</t>
   </si>
   <si>
     <t xml:space="preserve">0.525515496730804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526346981525421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554618358612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588710427284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575406134128571</t>
+    <t xml:space="preserve">0.526347041130066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554618418216705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588710367679596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575406193733215</t>
   </si>
   <si>
     <t xml:space="preserve">0.577069222927094</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">0.570417106151581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583721339702606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58538430929184</t>
+    <t xml:space="preserve">0.583721280097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585384368896484</t>
   </si>
   <si>
     <t xml:space="preserve">0.57790070772171</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">0.580395221710205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550460815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556281447410583</t>
+    <t xml:space="preserve">0.550460875034332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556281387805939</t>
   </si>
   <si>
     <t xml:space="preserve">0.545471727848053</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">0.5571129322052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564596474170685</t>
+    <t xml:space="preserve">0.56459653377533</t>
   </si>
   <si>
     <t xml:space="preserve">0.549629330635071</t>
@@ -2741,64 +2741,64 @@
     <t xml:space="preserve">0.509716749191284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507222235202789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521357953548431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513874232769012</t>
+    <t xml:space="preserve">0.507222175598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521357893943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513874351978302</t>
   </si>
   <si>
     <t xml:space="preserve">0.522189438343048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513042807579041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520526349544525</t>
+    <t xml:space="preserve">0.513042747974396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52052640914917</t>
   </si>
   <si>
     <t xml:space="preserve">0.523020923137665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519694864749908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508053779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48809739947319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488929003477097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492255002260208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496412575244904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490591943264008</t>
+    <t xml:space="preserve">0.519694924354553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508053719997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488097429275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488928943872452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492254972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496412515640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49059197306633</t>
   </si>
   <si>
     <t xml:space="preserve">0.485602915287018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480613827705383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474793255329132</t>
+    <t xml:space="preserve">0.480613857507706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47479322552681</t>
   </si>
   <si>
     <t xml:space="preserve">0.4540054500103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478950768709183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458162993192673</t>
+    <t xml:space="preserve">0.478950828313828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458163022994995</t>
   </si>
   <si>
     <t xml:space="preserve">0.44901642203331</t>
@@ -2810,22 +2810,22 @@
     <t xml:space="preserve">0.439038217067719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419913500547409</t>
+    <t xml:space="preserve">0.419913470745087</t>
   </si>
   <si>
     <t xml:space="preserve">0.422408014535904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42407101392746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411598354578018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411182582378387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395799666643143</t>
+    <t xml:space="preserve">0.424071043729782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411598384380341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41118261218071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395799607038498</t>
   </si>
   <si>
     <t xml:space="preserve">0.377090603113174</t>
@@ -2834,10 +2834,10 @@
     <t xml:space="preserve">0.365033715963364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402035981416702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413677126169205</t>
+    <t xml:space="preserve">0.40203595161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413677155971527</t>
   </si>
   <si>
     <t xml:space="preserve">0.407440811395645</t>
@@ -2858,25 +2858,25 @@
     <t xml:space="preserve">0.451510936021805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444027304649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436543673276901</t>
+    <t xml:space="preserve">0.444027274847031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436543703079224</t>
   </si>
   <si>
     <t xml:space="preserve">0.443195790052414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448184877634048</t>
+    <t xml:space="preserve">0.448184847831726</t>
   </si>
   <si>
     <t xml:space="preserve">0.44652184844017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440701276063919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434880673885345</t>
+    <t xml:space="preserve">0.440701246261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434880703687668</t>
   </si>
   <si>
     <t xml:space="preserve">0.424902528524399</t>
@@ -2885,37 +2885,37 @@
     <t xml:space="preserve">0.444858849048615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447353333234787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445690393447876</t>
+    <t xml:space="preserve">0.447353363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445690363645554</t>
   </si>
   <si>
     <t xml:space="preserve">0.463152050971985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477287799119949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470635712146759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437375277280807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429060071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421576529741287</t>
+    <t xml:space="preserve">0.481445372104645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477287769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470635682344437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437375247478485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429060101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421576499938965</t>
   </si>
   <si>
     <t xml:space="preserve">0.40993532538414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430723160505295</t>
+    <t xml:space="preserve">0.430723130702972</t>
   </si>
   <si>
     <t xml:space="preserve">0.427397072315216</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">0.446109414100647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43915256857872</t>
+    <t xml:space="preserve">0.439152538776398</t>
   </si>
   <si>
     <t xml:space="preserve">0.431326061487198</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">0.406542211771011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403063774108887</t>
+    <t xml:space="preserve">0.403063744306564</t>
   </si>
   <si>
     <t xml:space="preserve">0.414368689060211</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">0.391324043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383932411670685</t>
+    <t xml:space="preserve">0.383932381868362</t>
   </si>
   <si>
     <t xml:space="preserve">0.388715207576752</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">0.384367167949677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378714680671692</t>
+    <t xml:space="preserve">0.378714710474014</t>
   </si>
   <si>
     <t xml:space="preserve">0.373931884765625</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">0.371323019266129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375671118497849</t>
+    <t xml:space="preserve">0.375671088695526</t>
   </si>
   <si>
     <t xml:space="preserve">0.374366670846939</t>
@@ -3026,22 +3026,22 @@
     <t xml:space="preserve">0.364366173744202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361757338047028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368714183568954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377410292625427</t>
+    <t xml:space="preserve">0.36175736784935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368714213371277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37741032242775</t>
   </si>
   <si>
     <t xml:space="preserve">0.36958384513855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377845138311386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374801456928253</t>
+    <t xml:space="preserve">0.377845108509064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374801486730576</t>
   </si>
   <si>
     <t xml:space="preserve">0.37523627281189</t>
@@ -3062,25 +3062,25 @@
     <t xml:space="preserve">0.367409825325012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376975476741791</t>
+    <t xml:space="preserve">0.376975506544113</t>
   </si>
   <si>
     <t xml:space="preserve">0.364800959825516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386975973844528</t>
+    <t xml:space="preserve">0.386976003646851</t>
   </si>
   <si>
     <t xml:space="preserve">0.397411316633224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40262895822525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407846659421921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389584839344025</t>
+    <t xml:space="preserve">0.402628988027573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407846629619598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389584869146347</t>
   </si>
   <si>
     <t xml:space="preserve">0.396106898784637</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">0.40393340587616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408716201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400020152330399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400889754295349</t>
+    <t xml:space="preserve">0.408716231584549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400020182132721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400889724493027</t>
   </si>
   <si>
     <t xml:space="preserve">0.393063247203827</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">0.389150023460388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390889257192612</t>
+    <t xml:space="preserve">0.390889227390289</t>
   </si>
   <si>
     <t xml:space="preserve">0.395672112703323</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">0.400454938411713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390454441308975</t>
+    <t xml:space="preserve">0.390454411506653</t>
   </si>
   <si>
     <t xml:space="preserve">0.387410819530487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383497565984726</t>
+    <t xml:space="preserve">0.383497595787048</t>
   </si>
   <si>
     <t xml:space="preserve">0.382193148136139</t>
@@ -3161,22 +3161,22 @@
     <t xml:space="preserve">0.357844114303589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366540163755417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360887736082077</t>
+    <t xml:space="preserve">0.366540193557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360887706279755</t>
   </si>
   <si>
     <t xml:space="preserve">0.362626940011978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369149029254913</t>
+    <t xml:space="preserve">0.369148999452591</t>
   </si>
   <si>
     <t xml:space="preserve">0.379149526357651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386106431484222</t>
+    <t xml:space="preserve">0.3861064016819</t>
   </si>
   <si>
     <t xml:space="preserve">0.394367665052414</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">0.392628461122513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391758859157562</t>
+    <t xml:space="preserve">0.391758888959885</t>
   </si>
   <si>
     <t xml:space="preserve">0.395237267017365</t>
@@ -3215,13 +3215,13 @@
     <t xml:space="preserve">0.403868108987808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406615525484085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407531321048737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409362882375717</t>
+    <t xml:space="preserve">0.406615495681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407531291246414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40936291217804</t>
   </si>
   <si>
     <t xml:space="preserve">0.408447116613388</t>
@@ -3239,16 +3239,16 @@
     <t xml:space="preserve">0.402952283620834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402036488056183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393794327974319</t>
+    <t xml:space="preserve">0.402036517858505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393794298171997</t>
   </si>
   <si>
     <t xml:space="preserve">0.39104688167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391962707042694</t>
+    <t xml:space="preserve">0.391962677240372</t>
   </si>
   <si>
     <t xml:space="preserve">0.390131086111069</t>
@@ -3257,22 +3257,22 @@
     <t xml:space="preserve">0.394710093736649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3956258893013</t>
+    <t xml:space="preserve">0.395625919103622</t>
   </si>
   <si>
     <t xml:space="preserve">0.397457480430603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392878502607346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388299465179443</t>
+    <t xml:space="preserve">0.392878472805023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388299494981766</t>
   </si>
   <si>
     <t xml:space="preserve">0.384636282920837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389215290546417</t>
+    <t xml:space="preserve">0.38921532034874</t>
   </si>
   <si>
     <t xml:space="preserve">0.386467903852463</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">0.380973100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375478267669678</t>
+    <t xml:space="preserve">0.375478297472</t>
   </si>
   <si>
     <t xml:space="preserve">0.373646676540375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371815055608749</t>
+    <t xml:space="preserve">0.371815085411072</t>
   </si>
   <si>
     <t xml:space="preserve">0.369067668914795</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">0.369983494281769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376394093036652</t>
+    <t xml:space="preserve">0.376394122838974</t>
   </si>
   <si>
     <t xml:space="preserve">0.374562501907349</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">0.37089928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378225684165955</t>
+    <t xml:space="preserve">0.378225654363632</t>
   </si>
   <si>
     <t xml:space="preserve">0.385552108287811</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">0.420352518558502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421268343925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425847321748734</t>
+    <t xml:space="preserve">0.421268314123154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425847351551056</t>
   </si>
   <si>
     <t xml:space="preserve">0.416689306497574</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">0.415773510932922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410278707742691</t>
+    <t xml:space="preserve">0.410278737545013</t>
   </si>
   <si>
     <t xml:space="preserve">0.422184109687805</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">0.456068724393845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445994943380356</t>
+    <t xml:space="preserve">0.445994913578033</t>
   </si>
   <si>
     <t xml:space="preserve">0.494532406330109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48720595240593</t>
+    <t xml:space="preserve">0.487206012010574</t>
   </si>
   <si>
     <t xml:space="preserve">0.492700755596161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481711208820343</t>
+    <t xml:space="preserve">0.481711179018021</t>
   </si>
   <si>
     <t xml:space="preserve">0.489037543535233</t>
@@ -3413,16 +3413,16 @@
     <t xml:space="preserve">0.496363997459412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485374301671982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483542799949646</t>
+    <t xml:space="preserve">0.485374361276627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483542770147324</t>
   </si>
   <si>
     <t xml:space="preserve">0.454237133264542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463395118713379</t>
+    <t xml:space="preserve">0.463395148515701</t>
   </si>
   <si>
     <t xml:space="preserve">0.476216346025467</t>
@@ -69255,19 +69255,19 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6910763889</v>
+        <v>45967.6909722222</v>
       </c>
       <c r="B2505" t="n">
-        <v>85774</v>
+        <v>88005</v>
       </c>
       <c r="C2505" t="n">
-        <v>0.465000003576279</v>
+        <v>0.462999999523163</v>
       </c>
       <c r="D2505" t="n">
         <v>0.456999987363815</v>
       </c>
       <c r="E2505" t="n">
-        <v>0.462000012397766</v>
+        <v>0.462999999523163</v>
       </c>
       <c r="F2505" t="n">
         <v>0.462000012397766</v>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32635235786438</t>
+    <t xml:space="preserve">0.326352328062057</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844811439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323679059743881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980766296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313056260347366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304966032505035</t>
+    <t xml:space="preserve">0.326844781637192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323679089546204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980706691742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313056290149689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304966062307358</t>
   </si>
   <si>
     <t xml:space="preserve">0.299760162830353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309538781642914</t>
+    <t xml:space="preserve">0.309538751840591</t>
   </si>
   <si>
     <t xml:space="preserve">0.302503854036331</t>
@@ -71,40 +71,40 @@
     <t xml:space="preserve">0.287097245454788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274363875389099</t>
+    <t xml:space="preserve">0.274363905191422</t>
   </si>
   <si>
     <t xml:space="preserve">0.278655230998993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265288770198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260645687580109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270846426486969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269087702035904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272956937551498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270142942667007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265921950340271</t>
+    <t xml:space="preserve">0.265288800001144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260645717382431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270846366882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269087672233582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272956907749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270142912864685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265921920537949</t>
   </si>
   <si>
     <t xml:space="preserve">0.290825754404068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288433849811554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294061839580536</t>
+    <t xml:space="preserve">0.288433820009232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294061869382858</t>
   </si>
   <si>
     <t xml:space="preserve">0.276404082775116</t>
@@ -116,31 +116,31 @@
     <t xml:space="preserve">0.262545168399811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260293930768967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246927529573441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246224030852318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23975183069706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240103602409363</t>
+    <t xml:space="preserve">0.260293990373611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246927499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246224001049995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239751860499382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.240103587508202</t>
   </si>
   <si>
     <t xml:space="preserve">0.271549940109253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276122689247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274645358324051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277881443500519</t>
+    <t xml:space="preserve">0.276122659444809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274645328521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277881383895874</t>
   </si>
   <si>
     <t xml:space="preserve">0.270987153053284</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">0.277177900075912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263318985700607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2680324614048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282102406024933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295468866825104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29335829615593</t>
+    <t xml:space="preserve">0.26331901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268032491207123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282102465629578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295468837022781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293358325958252</t>
   </si>
   <si>
     <t xml:space="preserve">0.291740298271179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288644880056381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504183292389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281469225883484</t>
+    <t xml:space="preserve">0.288644909858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504242897034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281469255685806</t>
   </si>
   <si>
     <t xml:space="preserve">0.27724826335907</t>
@@ -185,31 +185,31 @@
     <t xml:space="preserve">0.278373837471008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287026822566986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297368258237839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295820593833923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30721727013588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305669546127319</t>
+    <t xml:space="preserve">0.287026852369308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297368288040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295820623636246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307217299938202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305669575929642</t>
   </si>
   <si>
     <t xml:space="preserve">0.31375977396965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320442974567413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317417949438095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316573739051819</t>
+    <t xml:space="preserve">0.320443004369736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317417919635773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316573768854141</t>
   </si>
   <si>
     <t xml:space="preserve">0.306161999702454</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">0.310945779085159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311438202857971</t>
+    <t xml:space="preserve">0.311438262462616</t>
   </si>
   <si>
     <t xml:space="preserve">0.301800280809402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288011729717255</t>
+    <t xml:space="preserve">0.288011759519577</t>
   </si>
   <si>
     <t xml:space="preserve">0.288082093000412</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">0.280554682016373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281328529119492</t>
+    <t xml:space="preserve">0.281328499317169</t>
   </si>
   <si>
     <t xml:space="preserve">0.291880965232849</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">0.30137825012207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311649262905121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310242265462875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311508595943451</t>
+    <t xml:space="preserve">0.311649233102798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310242295265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311508536338806</t>
   </si>
   <si>
     <t xml:space="preserve">0.314533621072769</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">0.330573350191116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330643743276596</t>
+    <t xml:space="preserve">0.330643713474274</t>
   </si>
   <si>
     <t xml:space="preserve">0.334161162376404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333528012037277</t>
+    <t xml:space="preserve">0.3335280418396</t>
   </si>
   <si>
     <t xml:space="preserve">0.330432653427124</t>
@@ -278,25 +278,25 @@
     <t xml:space="preserve">0.327126234769821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323538362979889</t>
+    <t xml:space="preserve">0.323538392782211</t>
   </si>
   <si>
     <t xml:space="preserve">0.318543523550034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31924706697464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323116272687912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321005821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324874997138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323749452829361</t>
+    <t xml:space="preserve">0.319247037172318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32311624288559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32100573182106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324875026941299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323749393224716</t>
   </si>
   <si>
     <t xml:space="preserve">0.325015723705292</t>
@@ -305,31 +305,31 @@
     <t xml:space="preserve">0.32107612490654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326774448156357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331769287586212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344713687896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342040359973907</t>
+    <t xml:space="preserve">0.326774477958679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331769317388535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344713658094406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342040330171585</t>
   </si>
   <si>
     <t xml:space="preserve">0.338030427694321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352100372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354914367198944</t>
+    <t xml:space="preserve">0.352100342512131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354914337396622</t>
   </si>
   <si>
     <t xml:space="preserve">0.351678282022476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350341618061066</t>
+    <t xml:space="preserve">0.350341558456421</t>
   </si>
   <si>
     <t xml:space="preserve">0.343306630849838</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">0.343165934085846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341196149587631</t>
+    <t xml:space="preserve">0.341196179389954</t>
   </si>
   <si>
     <t xml:space="preserve">0.340211242437363</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">0.323537766933441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309325933456421</t>
+    <t xml:space="preserve">0.309325873851776</t>
   </si>
   <si>
     <t xml:space="preserve">0.3121537566185</t>
@@ -359,55 +359,55 @@
     <t xml:space="preserve">0.308890819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31193619966507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325277984142303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322232633829117</t>
+    <t xml:space="preserve">0.311936229467392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325278013944626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322232663631439</t>
   </si>
   <si>
     <t xml:space="preserve">0.318607091903687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324190378189087</t>
+    <t xml:space="preserve">0.324190348386765</t>
   </si>
   <si>
     <t xml:space="preserve">0.307223111391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299102038145065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299464553594589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313096404075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320854872465134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318027049303055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319042176008224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318317085504532</t>
+    <t xml:space="preserve">0.299101978540421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299464583396912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3130963742733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320854902267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318027019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319042146205902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318317055702209</t>
   </si>
   <si>
     <t xml:space="preserve">0.309543401002884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311791211366653</t>
+    <t xml:space="preserve">0.311791181564331</t>
   </si>
   <si>
     <t xml:space="preserve">0.310558527708054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311066091060638</t>
+    <t xml:space="preserve">0.311066061258316</t>
   </si>
   <si>
     <t xml:space="preserve">0.322087556123734</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">0.31976729631424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318172067403793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309978455305099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306715548038483</t>
+    <t xml:space="preserve">0.318172037601471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309978514909744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30671551823616</t>
   </si>
   <si>
     <t xml:space="preserve">0.305627882480621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30178490281105</t>
+    <t xml:space="preserve">0.301784873008728</t>
   </si>
   <si>
     <t xml:space="preserve">0.300914764404297</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">0.298739463090897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298014402389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29148855805397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294316381216049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304467767477036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301204830408096</t>
+    <t xml:space="preserve">0.298014372587204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291488528251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294316411018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304467737674713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301204770803452</t>
   </si>
   <si>
     <t xml:space="preserve">0.302727520465851</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">0.30381515622139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30062472820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29743430018425</t>
+    <t xml:space="preserve">0.300624758005142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297434359788895</t>
   </si>
   <si>
     <t xml:space="preserve">0.299682110548019</t>
@@ -470,55 +470,55 @@
     <t xml:space="preserve">0.301929891109467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301712334156036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302364975214005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300117135047913</t>
+    <t xml:space="preserve">0.301712393760681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302364945411682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30011710524559</t>
   </si>
   <si>
     <t xml:space="preserve">0.302219927310944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297144293785095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295621603727341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293663859367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297289282083511</t>
+    <t xml:space="preserve">0.297144263982773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295621544122696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293663829565048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297289252281189</t>
   </si>
   <si>
     <t xml:space="preserve">0.291706055402756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292358607053757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290038347244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287500441074371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292648673057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287645518779755</t>
+    <t xml:space="preserve">0.292358666658401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290038377046585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287500470876694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292648643255234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287645548582077</t>
   </si>
   <si>
     <t xml:space="preserve">0.295041501522064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29156106710434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294533938169479</t>
+    <t xml:space="preserve">0.291561037302017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294533908367157</t>
   </si>
   <si>
     <t xml:space="preserve">0.289313226938248</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">0.287427991628647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282859891653061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275826454162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279161870479584</t>
+    <t xml:space="preserve">0.282859861850739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275826424360275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279161840677261</t>
   </si>
   <si>
     <t xml:space="preserve">0.269735664129257</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">0.273288607597351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279524475336075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282062262296677</t>
+    <t xml:space="preserve">0.279524445533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282062292098999</t>
   </si>
   <si>
     <t xml:space="preserve">0.283802539110184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282134741544724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28713795542717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292866170406342</t>
+    <t xml:space="preserve">0.282134801149368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287137925624847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292866200208664</t>
   </si>
   <si>
     <t xml:space="preserve">0.301422297954559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295839071273804</t>
+    <t xml:space="preserve">0.295839101076126</t>
   </si>
   <si>
     <t xml:space="preserve">0.296564191579819</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">0.300262212753296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297071814537048</t>
+    <t xml:space="preserve">0.297071784734726</t>
   </si>
   <si>
     <t xml:space="preserve">0.292938709259033</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">0.298811972141266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296056658029556</t>
+    <t xml:space="preserve">0.296056598424911</t>
   </si>
   <si>
     <t xml:space="preserve">0.31019601225853</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">0.306425482034683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302509993314743</t>
+    <t xml:space="preserve">0.302509963512421</t>
   </si>
   <si>
     <t xml:space="preserve">0.306062966585159</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">0.294098883867264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283077389001846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287863075733185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289603233337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285615265369415</t>
+    <t xml:space="preserve">0.283077418804169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28786301612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289603263139725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285615235567093</t>
   </si>
   <si>
     <t xml:space="preserve">0.2839475274086</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">0.288805663585663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293736338615417</t>
+    <t xml:space="preserve">0.293736308813095</t>
   </si>
   <si>
     <t xml:space="preserve">0.290835946798325</t>
@@ -638,67 +638,67 @@
     <t xml:space="preserve">0.283512473106384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281409710645676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280684560537338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279016882181168</t>
+    <t xml:space="preserve">0.281409680843353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280684620141983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27901691198349</t>
   </si>
   <si>
     <t xml:space="preserve">0.273796170949936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291415989398956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295113980770111</t>
+    <t xml:space="preserve">0.291415959596634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295114010572433</t>
   </si>
   <si>
     <t xml:space="preserve">0.290545910596848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288588136434555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292213648557663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292141139507294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294388890266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299392074346542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296491682529449</t>
+    <t xml:space="preserve">0.288588106632233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292213618755341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292141079902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294388920068741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29939204454422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296491712331772</t>
   </si>
   <si>
     <t xml:space="preserve">0.303597629070282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309615910053253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307440608739853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319187194108963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331513792276382</t>
+    <t xml:space="preserve">0.309615939855576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307440638542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319187223911285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331513822078705</t>
   </si>
   <si>
     <t xml:space="preserve">0.331368803977966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345000624656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349786221981049</t>
+    <t xml:space="preserve">0.345000594854355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349786192178726</t>
   </si>
   <si>
     <t xml:space="preserve">0.358342349529266</t>
@@ -707,31 +707,31 @@
     <t xml:space="preserve">0.354209333658218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34964120388031</t>
+    <t xml:space="preserve">0.349641174077988</t>
   </si>
   <si>
     <t xml:space="preserve">0.352396577596664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355296969413757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359430015087128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352686613798141</t>
+    <t xml:space="preserve">0.355296939611435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359429985284805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352686583995819</t>
   </si>
   <si>
     <t xml:space="preserve">0.346885859966278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343187898397446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346160739660263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346595823764801</t>
+    <t xml:space="preserve">0.343187868595123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346160769462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346595764160156</t>
   </si>
   <si>
     <t xml:space="preserve">0.346450805664062</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">0.350221306085587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350946336984634</t>
+    <t xml:space="preserve">0.350946366786957</t>
   </si>
   <si>
     <t xml:space="preserve">0.388288795948029</t>
@@ -752,22 +752,22 @@
     <t xml:space="preserve">0.397715061903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379950255155563</t>
+    <t xml:space="preserve">0.379950225353241</t>
   </si>
   <si>
     <t xml:space="preserve">0.382125526666641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374874532222748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37342432141304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377412348985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373061835765839</t>
+    <t xml:space="preserve">0.37487456202507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373424351215363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377412408590317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373061865568161</t>
   </si>
   <si>
     <t xml:space="preserve">0.369798868894577</t>
@@ -776,37 +776,37 @@
     <t xml:space="preserve">0.383575677871704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369436353445053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369073778390884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358197331428528</t>
+    <t xml:space="preserve">0.369436383247375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369073748588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35819736123085</t>
   </si>
   <si>
     <t xml:space="preserve">0.358052313327789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377049803733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412579536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382488012313843</t>
+    <t xml:space="preserve">0.377049833536148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412579476833344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382488042116165</t>
   </si>
   <si>
     <t xml:space="preserve">0.400615453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394452154636383</t>
+    <t xml:space="preserve">0.394452184438705</t>
   </si>
   <si>
     <t xml:space="preserve">0.385751008987427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393727004528046</t>
+    <t xml:space="preserve">0.393727034330368</t>
   </si>
   <si>
     <t xml:space="preserve">0.390464097261429</t>
@@ -815,46 +815,46 @@
     <t xml:space="preserve">0.384300768375397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391551733016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387563765048981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39082658290863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395177245140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393364518880844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397352516651154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398802667856216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3955397605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396627426147461</t>
+    <t xml:space="preserve">0.391551792621613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387563675642014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390826642513275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395177215337753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393364489078522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397352486848831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398802697658539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395539790391922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396627396345139</t>
   </si>
   <si>
     <t xml:space="preserve">0.398440152406693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395902335643768</t>
+    <t xml:space="preserve">0.395902305841446</t>
   </si>
   <si>
     <t xml:space="preserve">0.393001973628998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398077666759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401703059673309</t>
+    <t xml:space="preserve">0.398077636957169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401703089475632</t>
   </si>
   <si>
     <t xml:space="preserve">0.392276853322983</t>
@@ -863,34 +863,34 @@
     <t xml:space="preserve">0.38720116019249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386476099491119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382850617170334</t>
+    <t xml:space="preserve">0.386476069688797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382850557565689</t>
   </si>
   <si>
     <t xml:space="preserve">0.394089609384537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389376431703568</t>
+    <t xml:space="preserve">0.389376491308212</t>
   </si>
   <si>
     <t xml:space="preserve">0.381762951612473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38103786110878</t>
+    <t xml:space="preserve">0.381037831306458</t>
   </si>
   <si>
     <t xml:space="preserve">0.386838644742966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388651371002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385025918483734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391189157962799</t>
+    <t xml:space="preserve">0.38865140080452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385025888681412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391189187765121</t>
   </si>
   <si>
     <t xml:space="preserve">0.392639368772507</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">0.425631254911423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419105350971222</t>
+    <t xml:space="preserve">0.419105380773544</t>
   </si>
   <si>
     <t xml:space="preserve">0.445208847522736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435057580471039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44230842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432611972093582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413591980934143</t>
+    <t xml:space="preserve">0.435057520866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442308485507965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43261194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413591951131821</t>
   </si>
   <si>
     <t xml:space="preserve">0.408370792865753</t>
@@ -929,28 +929,28 @@
     <t xml:space="preserve">0.399047255516052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400539010763168</t>
+    <t xml:space="preserve">0.400539070367813</t>
   </si>
   <si>
     <t xml:space="preserve">0.395317822694778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396809667348862</t>
+    <t xml:space="preserve">0.396809637546539</t>
   </si>
   <si>
     <t xml:space="preserve">0.39606374502182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393080234527588</t>
+    <t xml:space="preserve">0.393080204725266</t>
   </si>
   <si>
     <t xml:space="preserve">0.388604909181595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387859016656876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379654318094254</t>
+    <t xml:space="preserve">0.387859046459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379654288291931</t>
   </si>
   <si>
     <t xml:space="preserve">0.381146103143692</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">0.383010774850845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387486129999161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384875476360321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383756697177887</t>
+    <t xml:space="preserve">0.387486100196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384875446557999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383756726980209</t>
   </si>
   <si>
     <t xml:space="preserve">0.386740177869797</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">0.394944906234741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403522551059723</t>
+    <t xml:space="preserve">0.403522580862045</t>
   </si>
   <si>
     <t xml:space="preserve">0.410235494375229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407252013683319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407624930143356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408743768930435</t>
+    <t xml:space="preserve">0.407251954078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407624959945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40874370932579</t>
   </si>
   <si>
     <t xml:space="preserve">0.406506061553955</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.394199043512344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398674339056015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390842586755753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392334342002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388231962919235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387113124132156</t>
+    <t xml:space="preserve">0.39867427945137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39084255695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392334312200546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388231992721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387113153934479</t>
   </si>
   <si>
     <t xml:space="preserve">0.391588419675827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389350831508636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38562136888504</t>
+    <t xml:space="preserve">0.389350801706314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385621398687363</t>
   </si>
   <si>
     <t xml:space="preserve">0.380773156881332</t>
@@ -1031,49 +1031,49 @@
     <t xml:space="preserve">0.385248422622681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383383721113205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397928446531296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409489661455154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410981416702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41433784365654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415083765983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416575521230698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415829598903656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4240343272686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439324915409088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866079568863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428882598876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420304894447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421796649694443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428509652614594</t>
+    <t xml:space="preserve">0.383383750915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397928476333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409489631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410981386899948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414337813854218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415083736181259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41657555103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415829628705978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424034297466278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439324975013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866109371185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428882539272308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420304924249649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42179673910141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428509622812271</t>
   </si>
   <si>
     <t xml:space="preserve">0.45498850941658</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">0.445291996002197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444546192884445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440443694591522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449767231941223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459463715553284</t>
+    <t xml:space="preserve">0.444546103477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440443724393845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449767291545868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459463775157928</t>
   </si>
   <si>
     <t xml:space="preserve">0.4609554708004</t>
@@ -1100,19 +1100,19 @@
     <t xml:space="preserve">0.469533145427704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466549634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474008470773697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474754393100739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348497629166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485942542552948</t>
+    <t xml:space="preserve">0.466549664735794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474008500576019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474754363298416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480348438024521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485942602157593</t>
   </si>
   <si>
     <t xml:space="preserve">0.482586145401001</t>
@@ -1121,70 +1121,70 @@
     <t xml:space="preserve">0.485569685697556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50943785905838</t>
+    <t xml:space="preserve">0.509437918663025</t>
   </si>
   <si>
     <t xml:space="preserve">0.511302590370178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521745026111603</t>
+    <t xml:space="preserve">0.521744966506958</t>
   </si>
   <si>
     <t xml:space="preserve">0.512794375419617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5195072889328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511675596237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506081461906433</t>
+    <t xml:space="preserve">0.519507348537445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511675477027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506081402301788</t>
   </si>
   <si>
     <t xml:space="preserve">0.501233160495758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502351999282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495266109704971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491536796092987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477737843990326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478483766317368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481094390153885</t>
+    <t xml:space="preserve">0.502352058887482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495266169309616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491536676883698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477737873792648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478483825922012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48109433054924</t>
   </si>
   <si>
     <t xml:space="preserve">0.492282629013062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499741464853287</t>
+    <t xml:space="preserve">0.499741405248642</t>
   </si>
   <si>
     <t xml:space="preserve">0.493774324655533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495639085769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507946074008942</t>
+    <t xml:space="preserve">0.495639026165009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507946133613586</t>
   </si>
   <si>
     <t xml:space="preserve">0.500114321708679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493028551340103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508692026138306</t>
+    <t xml:space="preserve">0.493028491735458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508691966533661</t>
   </si>
   <si>
     <t xml:space="preserve">0.503470897674561</t>
@@ -1193,28 +1193,28 @@
     <t xml:space="preserve">0.508319079875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507200300693512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510183811187744</t>
+    <t xml:space="preserve">0.507200241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510183691978455</t>
   </si>
   <si>
     <t xml:space="preserve">0.513167381286621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500860214233398</t>
+    <t xml:space="preserve">0.500860273838043</t>
   </si>
   <si>
     <t xml:space="preserve">0.503097951412201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502724945545197</t>
+    <t xml:space="preserve">0.502725005149841</t>
   </si>
   <si>
     <t xml:space="preserve">0.501606225967407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498249590396881</t>
+    <t xml:space="preserve">0.498249709606171</t>
   </si>
   <si>
     <t xml:space="preserve">0.510929644107819</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">0.531068563461304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557920277118683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554936826229095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559412121772766</t>
+    <t xml:space="preserve">0.557920336723328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554936766624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559412062168121</t>
   </si>
   <si>
     <t xml:space="preserve">0.56537914276123</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">0.593722641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574329674243927</t>
+    <t xml:space="preserve">0.574329614639282</t>
   </si>
   <si>
     <t xml:space="preserve">0.576567351818085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577313184738159</t>
+    <t xml:space="preserve">0.577313303947449</t>
   </si>
   <si>
     <t xml:space="preserve">0.583280324935913</t>
@@ -1253,31 +1253,31 @@
     <t xml:space="preserve">0.59148496389389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585517942905426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575075626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612369775772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556428551673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551953315734863</t>
+    <t xml:space="preserve">0.585518002510071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575075566768646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612369656562805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556428492069244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551953256130219</t>
   </si>
   <si>
     <t xml:space="preserve">0.548223793506622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53479790687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521371960639954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505708396434784</t>
+    <t xml:space="preserve">0.534797847270966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521372020244598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505708575248718</t>
   </si>
   <si>
     <t xml:space="preserve">0.528084933757782</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">0.545240342617035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522863745689392</t>
+    <t xml:space="preserve">0.522863686084747</t>
   </si>
   <si>
     <t xml:space="preserve">0.517642676830292</t>
@@ -1295,19 +1295,19 @@
     <t xml:space="preserve">0.532560288906097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531814336776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523609757423401</t>
+    <t xml:space="preserve">0.531814396381378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523609697818756</t>
   </si>
   <si>
     <t xml:space="preserve">0.516150891780853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512421429157257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51913446187973</t>
+    <t xml:space="preserve">0.512421369552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519134402275085</t>
   </si>
   <si>
     <t xml:space="preserve">0.498995572328568</t>
@@ -1316,40 +1316,40 @@
     <t xml:space="preserve">0.463193148374557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469906091690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476619124412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477364957332611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494520276784897</t>
+    <t xml:space="preserve">0.469906151294708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476619064807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477364987134933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494520157575607</t>
   </si>
   <si>
     <t xml:space="preserve">0.490045011043549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478856712579727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478110790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468414396047592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481840282678604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484077930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475127339363098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473635524511337</t>
+    <t xml:space="preserve">0.478856772184372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47811084985733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46841436624527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481840223073959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484077870845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475127309560776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473635464906693</t>
   </si>
   <si>
     <t xml:space="preserve">0.474381387233734</t>
@@ -1361,22 +1361,22 @@
     <t xml:space="preserve">0.487061411142349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48333203792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504216730594635</t>
+    <t xml:space="preserve">0.483331978321075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50421679019928</t>
   </si>
   <si>
     <t xml:space="preserve">0.504962623119354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496757864952087</t>
+    <t xml:space="preserve">0.496757924556732</t>
   </si>
   <si>
     <t xml:space="preserve">0.497503817081451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48631551861763</t>
+    <t xml:space="preserve">0.486315578222275</t>
   </si>
   <si>
     <t xml:space="preserve">0.500487387180328</t>
@@ -1385,130 +1385,130 @@
     <t xml:space="preserve">0.454242616891861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465430825948715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452004909515381</t>
+    <t xml:space="preserve">0.465430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452004939317703</t>
   </si>
   <si>
     <t xml:space="preserve">0.457226097583771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458717942237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462447315454483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455734342336655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45797199010849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485727846622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484185874462128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474933862686157</t>
+    <t xml:space="preserve">0.458717882633209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462447285652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455734401941299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457972019910812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485727906227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484185934066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47493389248848</t>
   </si>
   <si>
     <t xml:space="preserve">0.469536960124969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464910924434662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461055994033813</t>
+    <t xml:space="preserve">0.464910984039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461055964231491</t>
   </si>
   <si>
     <t xml:space="preserve">0.463368922472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459513992071152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457971930503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458743035793304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447949022054672</t>
+    <t xml:space="preserve">0.459513962268829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457971960306168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458743005990982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447949051856995</t>
   </si>
   <si>
     <t xml:space="preserve">0.451033025979996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454887956380844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.446406990289688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44178107380867</t>
+    <t xml:space="preserve">0.454887986183167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.446407049894333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441781044006348</t>
   </si>
   <si>
     <t xml:space="preserve">0.443323045969009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494208782911301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47416290640831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481101959943771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48958283662796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476475864648819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464139997959137</t>
+    <t xml:space="preserve">0.494208812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474162876605988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481101900339127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489582896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476475894451141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464140027761459</t>
   </si>
   <si>
     <t xml:space="preserve">0.461826950311661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456429958343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454117029905319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466452986001968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467223972082138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439468026161194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44255205988884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452575087547302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453345984220505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441010117530823</t>
+    <t xml:space="preserve">0.456429988145828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454117059707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466453045606613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46722400188446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439468055963516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442552030086517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452575027942657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453346073627472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4410100877285</t>
   </si>
   <si>
     <t xml:space="preserve">0.437926054000854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433300137519836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430987119674683</t>
+    <t xml:space="preserve">0.433300107717514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430987149477005</t>
   </si>
   <si>
     <t xml:space="preserve">0.431758135557175</t>
@@ -1517,46 +1517,46 @@
     <t xml:space="preserve">0.435613095760345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444865018129349</t>
+    <t xml:space="preserve">0.444865077733994</t>
   </si>
   <si>
     <t xml:space="preserve">0.460284978151321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451804041862488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470307976007462</t>
+    <t xml:space="preserve">0.45180407166481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470308005809784</t>
   </si>
   <si>
     <t xml:space="preserve">0.471849918365479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465681940317154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45720100402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462598025798798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455658972263336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450262069702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449491053819656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437155097723007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440239071846008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426361083984375</t>
+    <t xml:space="preserve">0.465681970119476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457200974225998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46259793639183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455659002065659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450262039899826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449491083621979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43715512752533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440239042043686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426361113786697</t>
   </si>
   <si>
     <t xml:space="preserve">0.427903115749359</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">0.407086193561554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406315237283707</t>
+    <t xml:space="preserve">0.406315207481384</t>
   </si>
   <si>
     <t xml:space="preserve">0.410170197486877</t>
@@ -1580,16 +1580,16 @@
     <t xml:space="preserve">0.41094121336937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40014722943306</t>
+    <t xml:space="preserve">0.400147259235382</t>
   </si>
   <si>
     <t xml:space="preserve">0.396292269229889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390895277261734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390124291181564</t>
+    <t xml:space="preserve">0.390895336866379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390124261379242</t>
   </si>
   <si>
     <t xml:space="preserve">0.381643325090408</t>
@@ -1598,16 +1598,16 @@
     <t xml:space="preserve">0.38318532705307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387811362743378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388582319021225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394750326871872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397063285112381</t>
+    <t xml:space="preserve">0.387811332941055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388582289218903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39475029706955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397063255310059</t>
   </si>
   <si>
     <t xml:space="preserve">0.389353305101395</t>
@@ -1622,28 +1622,28 @@
     <t xml:space="preserve">0.375475317239761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366223365068436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351188957691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345406532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348875939846039</t>
+    <t xml:space="preserve">0.366223394870758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351188987493515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345406502485275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348875969648361</t>
   </si>
   <si>
     <t xml:space="preserve">0.36699441075325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372391402721405</t>
+    <t xml:space="preserve">0.372391372919083</t>
   </si>
   <si>
     <t xml:space="preserve">0.367765367031097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162388801575</t>
+    <t xml:space="preserve">0.373162358999252</t>
   </si>
   <si>
     <t xml:space="preserve">0.370078355073929</t>
@@ -1655,55 +1655,55 @@
     <t xml:space="preserve">0.369692862033844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365837872028351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371620386838913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368536382913589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368921935558319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378944844007492</t>
+    <t xml:space="preserve">0.365837901830673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371620357036591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368536353111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368921905755997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37894481420517</t>
   </si>
   <si>
     <t xml:space="preserve">0.383570820093155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377017349004745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382414281368256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39937624335289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416338205337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424048155546188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424819141626358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417109191417694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422506153583527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421735137701035</t>
+    <t xml:space="preserve">0.377017378807068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382414311170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399376273155212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416338235139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424048095941544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424819111824036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417109221220016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422506123781204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421735107898712</t>
   </si>
   <si>
     <t xml:space="preserve">0.420964121818542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408628165721893</t>
+    <t xml:space="preserve">0.408628225326538</t>
   </si>
   <si>
     <t xml:space="preserve">0.400918245315552</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">0.411712199449539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412483245134354</t>
+    <t xml:space="preserve">0.412483215332031</t>
   </si>
   <si>
     <t xml:space="preserve">0.423277169466019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425590068101883</t>
+    <t xml:space="preserve">0.425590127706528</t>
   </si>
   <si>
     <t xml:space="preserve">0.41942223906517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430216163396835</t>
+    <t xml:space="preserve">0.430216193199158</t>
   </si>
   <si>
     <t xml:space="preserve">0.427132129669189</t>
@@ -1754,19 +1754,19 @@
     <t xml:space="preserve">0.393208265304565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392437279224396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391666293144226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393979251384735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398605287075043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403231233358383</t>
+    <t xml:space="preserve">0.392437249422073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391666322946548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393979281187057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398605316877365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403231203556061</t>
   </si>
   <si>
     <t xml:space="preserve">0.411275893449783</t>
@@ -69336,7 +69336,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6910300926</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>182295</v>
@@ -69357,6 +69357,32 @@
         <v>1267</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.69125</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>167607</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>0.465999990701675</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>0.456999987363815</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>0.460999995470047</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>0.467000007629395</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="1268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1269">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326352328062057</t>
+    <t xml:space="preserve">0.32635235786438</t>
   </si>
   <si>
     <t xml:space="preserve">FNM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326844781637192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323679089546204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317980706691742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313056290149689</t>
+    <t xml:space="preserve">0.326844811439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323679029941559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317980736494064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313056260347366</t>
   </si>
   <si>
     <t xml:space="preserve">0.304966062307358</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">0.299760162830353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309538751840591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302503854036331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287097245454788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274363905191422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278655230998993</t>
+    <t xml:space="preserve">0.309538781642914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302503794431686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287097215652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274363875389099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278655260801315</t>
   </si>
   <si>
     <t xml:space="preserve">0.265288800001144</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.260645717382431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270846366882324</t>
+    <t xml:space="preserve">0.270846396684647</t>
   </si>
   <si>
     <t xml:space="preserve">0.269087672233582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272956907749176</t>
+    <t xml:space="preserve">0.272956997156143</t>
   </si>
   <si>
     <t xml:space="preserve">0.270142912864685</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">0.265921920537949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290825754404068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288433820009232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294061869382858</t>
+    <t xml:space="preserve">0.290825724601746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288433879613876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294061839580536</t>
   </si>
   <si>
     <t xml:space="preserve">0.276404082775116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273167967796326</t>
+    <t xml:space="preserve">0.273167937994003</t>
   </si>
   <si>
     <t xml:space="preserve">0.262545168399811</t>
@@ -119,61 +119,61 @@
     <t xml:space="preserve">0.260293990373611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246927499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246224001049995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239751860499382</t>
+    <t xml:space="preserve">0.246927559375763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246223986148834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239751845598221</t>
   </si>
   <si>
     <t xml:space="preserve">0.240103587508202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271549940109253</t>
+    <t xml:space="preserve">0.271549910306931</t>
   </si>
   <si>
     <t xml:space="preserve">0.276122659444809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274645328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277881383895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270987153053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281539618968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277177900075912</t>
+    <t xml:space="preserve">0.274645298719406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277881413698196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270987182855606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281539589166641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277177929878235</t>
   </si>
   <si>
     <t xml:space="preserve">0.26331901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268032491207123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282102465629578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295468837022781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293358325958252</t>
+    <t xml:space="preserve">0.2680324614048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28210237622261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295468807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293358355760574</t>
   </si>
   <si>
     <t xml:space="preserve">0.291740298271179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288644909858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288504242897034</t>
+    <t xml:space="preserve">0.288644880056381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288504213094711</t>
   </si>
   <si>
     <t xml:space="preserve">0.281469255685806</t>
@@ -185,40 +185,40 @@
     <t xml:space="preserve">0.278373837471008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287026852369308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297368288040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295820623636246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307217299938202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305669575929642</t>
+    <t xml:space="preserve">0.287026882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297368258237839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295820564031601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307217240333557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305669516324997</t>
   </si>
   <si>
     <t xml:space="preserve">0.31375977396965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320443004369736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317417919635773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316573768854141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306161999702454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310945779085159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311438262462616</t>
+    <t xml:space="preserve">0.320443034172058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317417949438095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316573709249496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306161940097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310945749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311438232660294</t>
   </si>
   <si>
     <t xml:space="preserve">0.301800280809402</t>
@@ -227,28 +227,28 @@
     <t xml:space="preserve">0.288011759519577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288082093000412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280554682016373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281328499317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291880965232849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30137825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311649233102798</t>
+    <t xml:space="preserve">0.288082122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28055465221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281328558921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291881024837494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301378220319748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311649292707443</t>
   </si>
   <si>
     <t xml:space="preserve">0.310242295265198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311508536338806</t>
+    <t xml:space="preserve">0.311508506536484</t>
   </si>
   <si>
     <t xml:space="preserve">0.314533621072769</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">0.330573350191116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330643713474274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334161162376404</t>
+    <t xml:space="preserve">0.330643683671951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334161192178726</t>
   </si>
   <si>
     <t xml:space="preserve">0.3335280418396</t>
@@ -278,58 +278,58 @@
     <t xml:space="preserve">0.327126234769821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323538392782211</t>
+    <t xml:space="preserve">0.323538333177567</t>
   </si>
   <si>
     <t xml:space="preserve">0.318543523550034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319247037172318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32311624288559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32100573182106</t>
+    <t xml:space="preserve">0.319247007369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323116302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321005791425705</t>
   </si>
   <si>
     <t xml:space="preserve">0.324875026941299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323749393224716</t>
+    <t xml:space="preserve">0.323749452829361</t>
   </si>
   <si>
     <t xml:space="preserve">0.325015723705292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32107612490654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326774477958679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331769317388535</t>
+    <t xml:space="preserve">0.321076184511185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326774507761002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331769287586212</t>
   </si>
   <si>
     <t xml:space="preserve">0.344713658094406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342040330171585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338030427694321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352100342512131</t>
+    <t xml:space="preserve">0.342040359973907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338030397891998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352100372314453</t>
   </si>
   <si>
     <t xml:space="preserve">0.354914337396622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351678282022476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350341558456421</t>
+    <t xml:space="preserve">0.351678252220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350341647863388</t>
   </si>
   <si>
     <t xml:space="preserve">0.343306630849838</t>
@@ -338,79 +338,79 @@
     <t xml:space="preserve">0.343165934085846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341196179389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340211242437363</t>
+    <t xml:space="preserve">0.341196149587631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34021121263504</t>
   </si>
   <si>
     <t xml:space="preserve">0.337045520544052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323537766933441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309325873851776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3121537566185</t>
+    <t xml:space="preserve">0.323537737131119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309325903654099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312153786420822</t>
   </si>
   <si>
     <t xml:space="preserve">0.308890819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311936229467392</t>
+    <t xml:space="preserve">0.311936259269714</t>
   </si>
   <si>
     <t xml:space="preserve">0.325278013944626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322232663631439</t>
+    <t xml:space="preserve">0.322232604026794</t>
   </si>
   <si>
     <t xml:space="preserve">0.318607091903687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324190348386765</t>
+    <t xml:space="preserve">0.324190378189087</t>
   </si>
   <si>
     <t xml:space="preserve">0.307223111391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299101978540421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299464583396912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3130963742733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320854902267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318027019500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319042146205902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318317055702209</t>
+    <t xml:space="preserve">0.299102067947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299464553594589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313096344470978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320854872465134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318027049303055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319042176008224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318317085504532</t>
   </si>
   <si>
     <t xml:space="preserve">0.309543401002884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311791181564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310558527708054</t>
+    <t xml:space="preserve">0.311791211366653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310558557510376</t>
   </si>
   <si>
     <t xml:space="preserve">0.311066061258316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322087556123734</t>
+    <t xml:space="preserve">0.322087585926056</t>
   </si>
   <si>
     <t xml:space="preserve">0.31976729631424</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">0.318172037601471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309978514909744</t>
+    <t xml:space="preserve">0.309978455305099</t>
   </si>
   <si>
     <t xml:space="preserve">0.30671551823616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305627882480621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301784873008728</t>
+    <t xml:space="preserve">0.305627912282944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301784932613373</t>
   </si>
   <si>
     <t xml:space="preserve">0.300914764404297</t>
@@ -437,49 +437,49 @@
     <t xml:space="preserve">0.298739463090897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298014372587204</t>
+    <t xml:space="preserve">0.298014402389526</t>
   </si>
   <si>
     <t xml:space="preserve">0.291488528251648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294316411018372</t>
+    <t xml:space="preserve">0.294316381216049</t>
   </si>
   <si>
     <t xml:space="preserve">0.304467737674713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301204770803452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302727520465851</t>
+    <t xml:space="preserve">0.301204800605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302727490663528</t>
   </si>
   <si>
     <t xml:space="preserve">0.30381515622139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300624758005142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297434359788895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299682110548019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301929891109467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301712393760681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302364945411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30011710524559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302219927310944</t>
+    <t xml:space="preserve">0.30062472820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297434329986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299682080745697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301929861307144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301712334156036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302364975214005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300117164850235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302219897508621</t>
   </si>
   <si>
     <t xml:space="preserve">0.297144263982773</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">0.295621544122696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293663829565048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297289252281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291706055402756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292358666658401</t>
+    <t xml:space="preserve">0.293663799762726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297289311885834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291706115007401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292358636856079</t>
   </si>
   <si>
     <t xml:space="preserve">0.290038377046585</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">0.287500470876694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292648643255234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287645548582077</t>
+    <t xml:space="preserve">0.292648673057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287645518779755</t>
   </si>
   <si>
     <t xml:space="preserve">0.295041501522064</t>
@@ -521,10 +521,10 @@
     <t xml:space="preserve">0.294533908367157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289313226938248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287935554981232</t>
+    <t xml:space="preserve">0.28931325674057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287935525178909</t>
   </si>
   <si>
     <t xml:space="preserve">0.283004879951477</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">0.282859861850739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275826424360275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279161840677261</t>
+    <t xml:space="preserve">0.275826454162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279161900281906</t>
   </si>
   <si>
     <t xml:space="preserve">0.269735664129257</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">0.279524445533752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282062292098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283802539110184</t>
+    <t xml:space="preserve">0.282062262296677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283802509307861</t>
   </si>
   <si>
     <t xml:space="preserve">0.282134801149368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287137925624847</t>
+    <t xml:space="preserve">0.287137895822525</t>
   </si>
   <si>
     <t xml:space="preserve">0.292866200208664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301422297954559</t>
+    <t xml:space="preserve">0.301422327756882</t>
   </si>
   <si>
     <t xml:space="preserve">0.295839101076126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296564191579819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300262212753296</t>
+    <t xml:space="preserve">0.296564221382141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300262153148651</t>
   </si>
   <si>
     <t xml:space="preserve">0.297071784734726</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">0.298811972141266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296056598424911</t>
+    <t xml:space="preserve">0.296056658029556</t>
   </si>
   <si>
     <t xml:space="preserve">0.31019601225853</t>
@@ -599,28 +599,28 @@
     <t xml:space="preserve">0.302509963512421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306062966585159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307078093290329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30163985490799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294098883867264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283077418804169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28786301612854</t>
+    <t xml:space="preserve">0.306062936782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307078063488007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301639884710312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294098854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283077389001846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287863075733185</t>
   </si>
   <si>
     <t xml:space="preserve">0.289603263139725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285615235567093</t>
+    <t xml:space="preserve">0.285615295171738</t>
   </si>
   <si>
     <t xml:space="preserve">0.2839475274086</t>
@@ -638,58 +638,58 @@
     <t xml:space="preserve">0.283512473106384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281409680843353</t>
+    <t xml:space="preserve">0.281409710645676</t>
   </si>
   <si>
     <t xml:space="preserve">0.280684620141983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27901691198349</t>
+    <t xml:space="preserve">0.279016882181168</t>
   </si>
   <si>
     <t xml:space="preserve">0.273796170949936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291415959596634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295114010572433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290545910596848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288588106632233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292213618755341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292141079902649</t>
+    <t xml:space="preserve">0.291416019201279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295113950967789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290545880794525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288588136434555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292213648557663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292141109704971</t>
   </si>
   <si>
     <t xml:space="preserve">0.294388920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29939204454422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296491712331772</t>
+    <t xml:space="preserve">0.299392074346542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296491652727127</t>
   </si>
   <si>
     <t xml:space="preserve">0.303597629070282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309615939855576</t>
+    <t xml:space="preserve">0.309615910053253</t>
   </si>
   <si>
     <t xml:space="preserve">0.307440638542175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319187223911285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331513822078705</t>
+    <t xml:space="preserve">0.319187164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331513792276382</t>
   </si>
   <si>
     <t xml:space="preserve">0.331368803977966</t>
@@ -698,34 +698,34 @@
     <t xml:space="preserve">0.345000594854355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349786192178726</t>
+    <t xml:space="preserve">0.349786221981049</t>
   </si>
   <si>
     <t xml:space="preserve">0.358342349529266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354209333658218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349641174077988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352396577596664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355296939611435</t>
+    <t xml:space="preserve">0.354209303855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349641263484955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352396547794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355296969413757</t>
   </si>
   <si>
     <t xml:space="preserve">0.359429985284805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352686583995819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346885859966278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343187868595123</t>
+    <t xml:space="preserve">0.352686613798141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346885830163956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343187838792801</t>
   </si>
   <si>
     <t xml:space="preserve">0.346160769462585</t>
@@ -740,58 +740,58 @@
     <t xml:space="preserve">0.344348013401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350221306085587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350946366786957</t>
+    <t xml:space="preserve">0.350221335887909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350946396589279</t>
   </si>
   <si>
     <t xml:space="preserve">0.388288795948029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397715061903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379950225353241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382125526666641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37487456202507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373424351215363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377412408590317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373061865568161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369798868894577</t>
+    <t xml:space="preserve">0.397715091705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379950165748596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382125467061996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374874591827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37342432141304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377412378787994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373061805963516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369798839092255</t>
   </si>
   <si>
     <t xml:space="preserve">0.383575677871704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369436383247375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369073748588562</t>
+    <t xml:space="preserve">0.369436353445053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369073808193207</t>
   </si>
   <si>
     <t xml:space="preserve">0.35819736123085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358052313327789</t>
+    <t xml:space="preserve">0.358052343130112</t>
   </si>
   <si>
     <t xml:space="preserve">0.377049833536148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412579476833344</t>
+    <t xml:space="preserve">0.412579536437988</t>
   </si>
   <si>
     <t xml:space="preserve">0.382488042116165</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">0.400615453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394452184438705</t>
+    <t xml:space="preserve">0.394452095031738</t>
   </si>
   <si>
     <t xml:space="preserve">0.385751008987427</t>
@@ -815,19 +815,19 @@
     <t xml:space="preserve">0.384300768375397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391551792621613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387563675642014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390826642513275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395177215337753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393364489078522</t>
+    <t xml:space="preserve">0.391551822423935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387563735246658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390826612710953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395177185535431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393364518880844</t>
   </si>
   <si>
     <t xml:space="preserve">0.397352486848831</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">0.398802697658539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395539790391922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396627396345139</t>
+    <t xml:space="preserve">0.3955397605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396627426147461</t>
   </si>
   <si>
     <t xml:space="preserve">0.398440152406693</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">0.395902305841446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393001973628998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398077636957169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401703089475632</t>
+    <t xml:space="preserve">0.393001943826675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398077607154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401703119277954</t>
   </si>
   <si>
     <t xml:space="preserve">0.392276853322983</t>
@@ -866,55 +866,55 @@
     <t xml:space="preserve">0.386476069688797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382850557565689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394089609384537</t>
+    <t xml:space="preserve">0.382850587368011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394089549779892</t>
   </si>
   <si>
     <t xml:space="preserve">0.389376491308212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381762951612473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381037831306458</t>
+    <t xml:space="preserve">0.38176292181015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381037890911102</t>
   </si>
   <si>
     <t xml:space="preserve">0.386838644742966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38865140080452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385025888681412</t>
+    <t xml:space="preserve">0.388651341199875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385025918483734</t>
   </si>
   <si>
     <t xml:space="preserve">0.391189187765121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392639368772507</t>
+    <t xml:space="preserve">0.392639338970184</t>
   </si>
   <si>
     <t xml:space="preserve">0.425631254911423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419105380773544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445208847522736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435057520866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442308485507965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43261194229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413591951131821</t>
+    <t xml:space="preserve">0.419105410575867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445208817720413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435057580471039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44230842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432611912488937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413591980934143</t>
   </si>
   <si>
     <t xml:space="preserve">0.408370792865753</t>
@@ -923,40 +923,40 @@
     <t xml:space="preserve">0.406879037618637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402776718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399047255516052</t>
+    <t xml:space="preserve">0.402776747941971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399047315120697</t>
   </si>
   <si>
     <t xml:space="preserve">0.400539070367813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395317822694778</t>
+    <t xml:space="preserve">0.395317852497101</t>
   </si>
   <si>
     <t xml:space="preserve">0.396809637546539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39606374502182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393080204725266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388604909181595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387859046459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379654288291931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381146103143692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383010774850845</t>
+    <t xml:space="preserve">0.396063774824142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393080174922943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388604938983917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387859016656876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379654347896576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381146043539047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383010745048523</t>
   </si>
   <si>
     <t xml:space="preserve">0.387486100196838</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">0.384875446557999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383756726980209</t>
+    <t xml:space="preserve">0.383756667375565</t>
   </si>
   <si>
     <t xml:space="preserve">0.386740177869797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390096664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394944906234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403522580862045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410235494375229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407251954078674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407624959945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40874370932579</t>
+    <t xml:space="preserve">0.390096694231033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394944936037064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403522551059723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410235464572906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407251983880997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407624900341034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408743768930435</t>
   </si>
   <si>
     <t xml:space="preserve">0.406506061553955</t>
@@ -998,58 +998,58 @@
     <t xml:space="preserve">0.40091198682785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394199043512344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39867427945137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39084255695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392334312200546</t>
+    <t xml:space="preserve">0.394199073314667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398674339056015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390842527151108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392334342002869</t>
   </si>
   <si>
     <t xml:space="preserve">0.388231992721558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387113153934479</t>
+    <t xml:space="preserve">0.387113094329834</t>
   </si>
   <si>
     <t xml:space="preserve">0.391588419675827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389350801706314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385621398687363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380773156881332</t>
+    <t xml:space="preserve">0.389350771903992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385621428489685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380773186683655</t>
   </si>
   <si>
     <t xml:space="preserve">0.385248422622681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383383750915527</t>
+    <t xml:space="preserve">0.383383721113205</t>
   </si>
   <si>
     <t xml:space="preserve">0.397928476333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409489631652832</t>
+    <t xml:space="preserve">0.40948960185051</t>
   </si>
   <si>
     <t xml:space="preserve">0.410981386899948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414337813854218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415083736181259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41657555103302</t>
+    <t xml:space="preserve">0.41433784365654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415083765983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416575491428375</t>
   </si>
   <si>
     <t xml:space="preserve">0.415829628705978</t>
@@ -1058,31 +1058,31 @@
     <t xml:space="preserve">0.424034297466278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439324975013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431866109371185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428882539272308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420304924249649</t>
+    <t xml:space="preserve">0.439324915409088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431866139173508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428882569074631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420304864645004</t>
   </si>
   <si>
     <t xml:space="preserve">0.42179673910141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428509622812271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45498850941658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445291996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444546103477478</t>
+    <t xml:space="preserve">0.428509682416916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454988449811935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445291966199875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4445461332798</t>
   </si>
   <si>
     <t xml:space="preserve">0.440443724393845</t>
@@ -1094,22 +1094,22 @@
     <t xml:space="preserve">0.459463775157928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4609554708004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469533145427704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466549664735794</t>
+    <t xml:space="preserve">0.460955530405045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469533115625381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466549634933472</t>
   </si>
   <si>
     <t xml:space="preserve">0.474008500576019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474754363298416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480348438024521</t>
+    <t xml:space="preserve">0.474754333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480348497629166</t>
   </si>
   <si>
     <t xml:space="preserve">0.485942602157593</t>
@@ -1118,58 +1118,58 @@
     <t xml:space="preserve">0.482586145401001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485569685697556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509437918663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511302590370178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521744966506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512794375419617</t>
+    <t xml:space="preserve">0.485569626092911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50943797826767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511302649974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521745026111603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512794315814972</t>
   </si>
   <si>
     <t xml:space="preserve">0.519507348537445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511675477027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506081402301788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501233160495758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502352058887482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495266169309616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491536676883698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477737873792648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478483825922012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48109433054924</t>
+    <t xml:space="preserve">0.511675536632538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506081521511078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501233220100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502351999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495266109704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491536766290665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477737903594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47848379611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481094300746918</t>
   </si>
   <si>
     <t xml:space="preserve">0.492282629013062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499741405248642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493774324655533</t>
+    <t xml:space="preserve">0.499741435050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493774384260178</t>
   </si>
   <si>
     <t xml:space="preserve">0.495639026165009</t>
@@ -1178,25 +1178,25 @@
     <t xml:space="preserve">0.507946133613586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500114321708679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493028491735458</t>
+    <t xml:space="preserve">0.500114381313324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493028551340103</t>
   </si>
   <si>
     <t xml:space="preserve">0.508691966533661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503470897674561</t>
+    <t xml:space="preserve">0.503470838069916</t>
   </si>
   <si>
     <t xml:space="preserve">0.508319079875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507200241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510183691978455</t>
+    <t xml:space="preserve">0.507200300693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510183751583099</t>
   </si>
   <si>
     <t xml:space="preserve">0.513167381286621</t>
@@ -1208,22 +1208,22 @@
     <t xml:space="preserve">0.503097951412201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502725005149841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501606225967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498249709606171</t>
+    <t xml:space="preserve">0.502724945545197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501606166362762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498249590396881</t>
   </si>
   <si>
     <t xml:space="preserve">0.510929644107819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531068563461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557920336723328</t>
+    <t xml:space="preserve">0.531068503856659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557920277118683</t>
   </si>
   <si>
     <t xml:space="preserve">0.554936766624451</t>
@@ -1232,64 +1232,64 @@
     <t xml:space="preserve">0.559412062168121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56537914276123</t>
+    <t xml:space="preserve">0.565379083156586</t>
   </si>
   <si>
     <t xml:space="preserve">0.593722641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574329614639282</t>
+    <t xml:space="preserve">0.574329674243927</t>
   </si>
   <si>
     <t xml:space="preserve">0.576567351818085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577313303947449</t>
+    <t xml:space="preserve">0.577313244342804</t>
   </si>
   <si>
     <t xml:space="preserve">0.583280324935913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.59148496389389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585518002510071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575075566768646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612369656562805</t>
+    <t xml:space="preserve">0.591485023498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585517942905426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575075626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61236971616745</t>
   </si>
   <si>
     <t xml:space="preserve">0.556428492069244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551953256130219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548223793506622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534797847270966</t>
+    <t xml:space="preserve">0.551953196525574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548223853111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53479790687561</t>
   </si>
   <si>
     <t xml:space="preserve">0.521372020244598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505708575248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528084933757782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545240342617035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522863686084747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517642676830292</t>
+    <t xml:space="preserve">0.505708515644073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528084993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54524028301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522863745689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517642617225647</t>
   </si>
   <si>
     <t xml:space="preserve">0.532560288906097</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">0.523609697818756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516150891780853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512421369552612</t>
+    <t xml:space="preserve">0.516150832176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512421429157257</t>
   </si>
   <si>
     <t xml:space="preserve">0.519134402275085</t>
@@ -1313,34 +1313,34 @@
     <t xml:space="preserve">0.498995572328568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463193148374557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469906151294708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476619064807892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477364987134933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494520157575607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490045011043549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478856772184372</t>
+    <t xml:space="preserve">0.46319317817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469906061887741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476619094610214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477364927530289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49452018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490044951438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47885674238205</t>
   </si>
   <si>
     <t xml:space="preserve">0.47811084985733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46841436624527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481840223073959</t>
+    <t xml:space="preserve">0.468414396047592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481840252876282</t>
   </si>
   <si>
     <t xml:space="preserve">0.484077870845795</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">0.473635464906693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474381387233734</t>
+    <t xml:space="preserve">0.474381446838379</t>
   </si>
   <si>
     <t xml:space="preserve">0.484823822975159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487061411142349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483331978321075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50421679019928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504962623119354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496757924556732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497503817081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486315578222275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500487387180328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454242616891861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452004939317703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457226097583771</t>
+    <t xml:space="preserve">0.487061470746994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48333203792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504216730594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504962682723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496757954359055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497503727674484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486315548419952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500487327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454242646694183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465430825948715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452004998922348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457226127386093</t>
   </si>
   <si>
     <t xml:space="preserve">0.458717882633209</t>
@@ -1400,106 +1400,106 @@
     <t xml:space="preserve">0.462447285652161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455734401941299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457972019910812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485727906227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484185934066772</t>
+    <t xml:space="preserve">0.455734342336655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457972049713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485727876424789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48418590426445</t>
   </si>
   <si>
     <t xml:space="preserve">0.47493389248848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469536960124969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464910984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461055964231491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463368922472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459513962268829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457971960306168</t>
+    <t xml:space="preserve">0.469536989927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464910924434662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461055934429169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463368982076645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459514021873474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45797199010849</t>
   </si>
   <si>
     <t xml:space="preserve">0.458743005990982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447949051856995</t>
+    <t xml:space="preserve">0.447949022054672</t>
   </si>
   <si>
     <t xml:space="preserve">0.451033025979996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454887986183167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.446407049894333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441781044006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443323045969009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494208812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474162876605988</t>
+    <t xml:space="preserve">0.454887926578522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.446407079696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44178107380867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443323016166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494208842515945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47416290640831</t>
   </si>
   <si>
     <t xml:space="preserve">0.481101900339127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489582896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476475894451141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464140027761459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461826950311661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456429988145828</t>
+    <t xml:space="preserve">0.489582866430283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476475954055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464139938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461827009916306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456430017948151</t>
   </si>
   <si>
     <t xml:space="preserve">0.454117059707642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466453045606613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46722400188446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439468055963516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442552030086517</t>
+    <t xml:space="preserve">0.466452926397324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467223972082138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439468085765839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442552119493484</t>
   </si>
   <si>
     <t xml:space="preserve">0.452575027942657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453346073627472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4410100877285</t>
+    <t xml:space="preserve">0.453345984220505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441010117530823</t>
   </si>
   <si>
     <t xml:space="preserve">0.437926054000854</t>
@@ -1508,28 +1508,28 @@
     <t xml:space="preserve">0.433300107717514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430987149477005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431758135557175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435613095760345</t>
+    <t xml:space="preserve">0.430987179279327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43175807595253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435613065958023</t>
   </si>
   <si>
     <t xml:space="preserve">0.444865077733994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460284978151321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45180407166481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470308005809784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471849918365479</t>
+    <t xml:space="preserve">0.460284948348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451804041862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470307886600494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471849948167801</t>
   </si>
   <si>
     <t xml:space="preserve">0.465681970119476</t>
@@ -1538,22 +1538,22 @@
     <t xml:space="preserve">0.457200974225998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46259793639183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455659002065659</t>
+    <t xml:space="preserve">0.462597995996475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455659061670303</t>
   </si>
   <si>
     <t xml:space="preserve">0.450262039899826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449491083621979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43715512752533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440239042043686</t>
+    <t xml:space="preserve">0.449491024017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437155067920685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440239012241364</t>
   </si>
   <si>
     <t xml:space="preserve">0.426361113786697</t>
@@ -1562,25 +1562,25 @@
     <t xml:space="preserve">0.427903115749359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407086193561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406315207481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410170197486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40400218963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407857209444046</t>
+    <t xml:space="preserve">0.407086223363876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406315237283707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410170257091522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404002219438553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407857179641724</t>
   </si>
   <si>
     <t xml:space="preserve">0.41094121336937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400147259235382</t>
+    <t xml:space="preserve">0.40014722943306</t>
   </si>
   <si>
     <t xml:space="preserve">0.396292269229889</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">0.390895336866379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390124261379242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381643325090408</t>
+    <t xml:space="preserve">0.390124291181564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381643354892731</t>
   </si>
   <si>
     <t xml:space="preserve">0.38318532705307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387811332941055</t>
+    <t xml:space="preserve">0.387811303138733</t>
   </si>
   <si>
     <t xml:space="preserve">0.388582289218903</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">0.389353305101395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387040287256241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385498315095901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375475317239761</t>
+    <t xml:space="preserve">0.387040257453918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385498344898224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375475347042084</t>
   </si>
   <si>
     <t xml:space="preserve">0.366223394870758</t>
@@ -1631,31 +1631,31 @@
     <t xml:space="preserve">0.345406502485275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348875969648361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36699441075325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372391372919083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367765367031097</t>
+    <t xml:space="preserve">0.348875939846039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366994351148605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37239134311676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36776539683342</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162358999252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370078355073929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370463877916336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369692862033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365837901830673</t>
+    <t xml:space="preserve">0.370078384876251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370463907718658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369692832231522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365837872028351</t>
   </si>
   <si>
     <t xml:space="preserve">0.371620357036591</t>
@@ -1664,115 +1664,115 @@
     <t xml:space="preserve">0.368536353111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368921905755997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37894481420517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383570820093155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377017378807068</t>
+    <t xml:space="preserve">0.368921875953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378944844007492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383570849895477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377017319202423</t>
   </si>
   <si>
     <t xml:space="preserve">0.382414311170578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399376273155212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416338235139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424048095941544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424819111824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417109221220016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422506123781204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421735107898712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420964121818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408628225326538</t>
+    <t xml:space="preserve">0.39937624335289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416338205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424048155546188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424819141626358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417109191417694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422506153583527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421735197305679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420964151620865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408628195524216</t>
   </si>
   <si>
     <t xml:space="preserve">0.400918245315552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4047731757164</t>
+    <t xml:space="preserve">0.404773205518723</t>
   </si>
   <si>
     <t xml:space="preserve">0.405544251203537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411712199449539</t>
+    <t xml:space="preserve">0.411712169647217</t>
   </si>
   <si>
     <t xml:space="preserve">0.412483215332031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423277169466019</t>
+    <t xml:space="preserve">0.423277139663696</t>
   </si>
   <si>
     <t xml:space="preserve">0.425590127706528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41942223906517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430216193199158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427132129669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414025187492371</t>
+    <t xml:space="preserve">0.419422149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430216163396835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427132159471512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414025247097015</t>
   </si>
   <si>
     <t xml:space="preserve">0.41479617357254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413254201412201</t>
+    <t xml:space="preserve">0.413254171609879</t>
   </si>
   <si>
     <t xml:space="preserve">0.409399211406708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395521253347397</t>
+    <t xml:space="preserve">0.395521283149719</t>
   </si>
   <si>
     <t xml:space="preserve">0.393208265304565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392437249422073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391666322946548</t>
+    <t xml:space="preserve">0.392437279224396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391666293144226</t>
   </si>
   <si>
     <t xml:space="preserve">0.393979281187057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398605316877365</t>
+    <t xml:space="preserve">0.39860525727272</t>
   </si>
   <si>
     <t xml:space="preserve">0.403231203556061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411275893449783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410471081733704</t>
+    <t xml:space="preserve">0.411275953054428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410471051931381</t>
   </si>
   <si>
     <t xml:space="preserve">0.409666240215302</t>
@@ -1784,19 +1784,19 @@
     <t xml:space="preserve">0.412885636091232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412080824375153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399203211069107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401215374469757</t>
+    <t xml:space="preserve">0.41208079457283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399203240871429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401215344667435</t>
   </si>
   <si>
     <t xml:space="preserve">0.404032289981842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397995978593826</t>
+    <t xml:space="preserve">0.397996008396149</t>
   </si>
   <si>
     <t xml:space="preserve">0.403227478265762</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">0.39839842915535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400008082389832</t>
+    <t xml:space="preserve">0.400008112192154</t>
   </si>
   <si>
     <t xml:space="preserve">0.40242263674736</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">0.400410532951355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395983874797821</t>
+    <t xml:space="preserve">0.395983844995499</t>
   </si>
   <si>
     <t xml:space="preserve">0.39960566163063</t>
@@ -1823,67 +1823,67 @@
     <t xml:space="preserve">0.418519526720047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417714685201645</t>
+    <t xml:space="preserve">0.417714655399323</t>
   </si>
   <si>
     <t xml:space="preserve">0.416909843683243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404837220907211</t>
+    <t xml:space="preserve">0.404837191104889</t>
   </si>
   <si>
     <t xml:space="preserve">0.401617795228958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407251685857773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408056527376175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405642062425613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397593587636948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391154766082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406446874141693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426567941904068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433811604976654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424153476953506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43220192193985</t>
+    <t xml:space="preserve">0.407251715660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40805658698082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405642002820969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397593557834625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391154795885086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406446844339371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426568001508713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433811545372009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424153447151184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432201951742172</t>
   </si>
   <si>
     <t xml:space="preserve">0.425763130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428177684545517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43300673365593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429787367582321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420934081077576</t>
+    <t xml:space="preserve">0.428177714347839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433006763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429787337779999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420934051275253</t>
   </si>
   <si>
     <t xml:space="preserve">0.428982526063919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437030971050262</t>
+    <t xml:space="preserve">0.437031000852585</t>
   </si>
   <si>
     <t xml:space="preserve">0.434616476297379</t>
@@ -1895,79 +1895,79 @@
     <t xml:space="preserve">0.442664921283722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458761751651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466810256242752</t>
+    <t xml:space="preserve">0.458761811256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466810286045074</t>
   </si>
   <si>
     <t xml:space="preserve">0.473248988389969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476468354463577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478882998228073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475663542747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481297463178635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478078037500381</t>
+    <t xml:space="preserve">0.476468414068222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478882968425751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475663602352142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481297433376312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478078067302704</t>
   </si>
   <si>
     <t xml:space="preserve">0.474858641624451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471639364957809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472444236278534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486126512289047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480492621660233</t>
+    <t xml:space="preserve">0.471639335155487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472444146871567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48612654209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480492562055588</t>
   </si>
   <si>
     <t xml:space="preserve">0.494979828596115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511881589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513491213321686</t>
+    <t xml:space="preserve">0.511881530284882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513491332530975</t>
   </si>
   <si>
     <t xml:space="preserve">0.520734906196594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535222053527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53441721200943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523149371147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51510089635849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516710698604584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522344589233398</t>
+    <t xml:space="preserve">0.535222113132477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534417271614075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523149430751801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515100955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516710638999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522344529628754</t>
   </si>
   <si>
     <t xml:space="preserve">0.556148052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555343270301819</t>
+    <t xml:space="preserve">0.555343210697174</t>
   </si>
   <si>
     <t xml:space="preserve">0.551319003105164</t>
@@ -1976,19 +1976,19 @@
     <t xml:space="preserve">0.557757794857025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571440160274506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56178206205368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560977280139923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552928686141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554538369178772</t>
+    <t xml:space="preserve">0.571440100669861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561782002449036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560977220535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552928745746613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554538428783417</t>
   </si>
   <si>
     <t xml:space="preserve">0.59236615896225</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">0.59639036655426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599609732627869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611682415008545</t>
+    <t xml:space="preserve">0.599609673023224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6116823554039</t>
   </si>
   <si>
     <t xml:space="preserve">0.606853365898132</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">0.608463048934937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593975722789764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59075653553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595585465431213</t>
+    <t xml:space="preserve">0.593975782394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590756475925446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595585525035858</t>
   </si>
   <si>
     <t xml:space="preserve">0.609267890453339</t>
@@ -2039,70 +2039,70 @@
     <t xml:space="preserve">0.593170940876007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598804950714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601219356060028</t>
+    <t xml:space="preserve">0.598804891109467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601219415664673</t>
   </si>
   <si>
     <t xml:space="preserve">0.594780683517456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603633880615234</t>
+    <t xml:space="preserve">0.603633940219879</t>
   </si>
   <si>
     <t xml:space="preserve">0.610072731971741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598000049591064</t>
+    <t xml:space="preserve">0.59799998998642</t>
   </si>
   <si>
     <t xml:space="preserve">0.630193889141083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631803631782532</t>
+    <t xml:space="preserve">0.631803512573242</t>
   </si>
   <si>
     <t xml:space="preserve">0.646290719509125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655948877334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659973084926605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689752340316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684118449687958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661582827568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588341891765594</t>
+    <t xml:space="preserve">0.65594893693924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65997314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689752399921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684118509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661582887172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588341951370239</t>
   </si>
   <si>
     <t xml:space="preserve">0.581098318099976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572245001792908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540856003761292</t>
+    <t xml:space="preserve">0.572244942188263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540856063365936</t>
   </si>
   <si>
     <t xml:space="preserve">0.543270587921143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518320381641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526368796825409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490955650806427</t>
+    <t xml:space="preserve">0.518320322036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526368737220764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49095556139946</t>
   </si>
   <si>
     <t xml:space="preserve">0.439445495605469</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">0.398800820112228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381496638059616</t>
+    <t xml:space="preserve">0.381496697664261</t>
   </si>
   <si>
     <t xml:space="preserve">0.323145359754562</t>
@@ -2123,10 +2123,10 @@
     <t xml:space="preserve">0.303829073905945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282500684261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288939446210861</t>
+    <t xml:space="preserve">0.282500743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288939416408539</t>
   </si>
   <si>
     <t xml:space="preserve">0.29135400056839</t>
@@ -2135,10 +2135,10 @@
     <t xml:space="preserve">0.304633945226669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308255732059479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343668937683105</t>
+    <t xml:space="preserve">0.308255761861801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343668907880783</t>
   </si>
   <si>
     <t xml:space="preserve">0.35896098613739</t>
@@ -2147,31 +2147,31 @@
     <t xml:space="preserve">0.37224093079567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355741590261459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373850643634796</t>
+    <t xml:space="preserve">0.355741620063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373850613832474</t>
   </si>
   <si>
     <t xml:space="preserve">0.391959607601166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379082143306732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375057876110077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384716033935547</t>
+    <t xml:space="preserve">0.379082083702087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375057905912399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384716004133224</t>
   </si>
   <si>
     <t xml:space="preserve">0.386325716972351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374253034591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362180382013321</t>
+    <t xml:space="preserve">0.374253064393997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362180322408676</t>
   </si>
   <si>
     <t xml:space="preserve">0.351717382669449</t>
@@ -2183,25 +2183,25 @@
     <t xml:space="preserve">0.34930282831192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344473779201508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323547780513763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338034987449646</t>
+    <t xml:space="preserve">0.344473749399185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323547810316086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338035017251968</t>
   </si>
   <si>
     <t xml:space="preserve">0.339644700288773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341254383325577</t>
+    <t xml:space="preserve">0.341254413127899</t>
   </si>
   <si>
     <t xml:space="preserve">0.346083492040634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350912541151047</t>
+    <t xml:space="preserve">0.350912511348724</t>
   </si>
   <si>
     <t xml:space="preserve">0.348497986793518</t>
@@ -2210,31 +2210,31 @@
     <t xml:space="preserve">0.342864096164703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34527862071991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336425334215164</t>
+    <t xml:space="preserve">0.345278590917587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336425304412842</t>
   </si>
   <si>
     <t xml:space="preserve">0.324352651834488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329986542463303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326767146587372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321938097476959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331596255302429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340449571609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347693145275116</t>
+    <t xml:space="preserve">0.329986572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326767176389694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321938127279282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331596225500107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340449512004852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347693175077438</t>
   </si>
   <si>
     <t xml:space="preserve">0.352522224187851</t>
@@ -2243,28 +2243,28 @@
     <t xml:space="preserve">0.35493677854538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369423985481262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382301449775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379887014627457</t>
+    <t xml:space="preserve">0.36942395567894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382301509380341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379886955022812</t>
   </si>
   <si>
     <t xml:space="preserve">0.371838539838791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354131937026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330791413784027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356546401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357351303100586</t>
+    <t xml:space="preserve">0.354131907224655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330791443586349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356546461582184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357351273298264</t>
   </si>
   <si>
     <t xml:space="preserve">0.350107699632645</t>
@@ -2273,49 +2273,49 @@
     <t xml:space="preserve">0.346888303756714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342059224843979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337230145931244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328376859426498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335620492696762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370228856801987</t>
+    <t xml:space="preserve">0.342059254646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337230175733566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328376829624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33562046289444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370228797197342</t>
   </si>
   <si>
     <t xml:space="preserve">0.358156144618988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363790035247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420129299163818</t>
+    <t xml:space="preserve">0.363790065050125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420129239559174</t>
   </si>
   <si>
     <t xml:space="preserve">0.424958288669586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437835872173309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444274514913559</t>
+    <t xml:space="preserve">0.437835812568665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444274574518204</t>
   </si>
   <si>
     <t xml:space="preserve">0.44588428735733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482907235622406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560172319412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527978479862213</t>
+    <t xml:space="preserve">0.482907176017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560172259807587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527978539466858</t>
   </si>
   <si>
     <t xml:space="preserve">0.521539747714996</t>
@@ -2324,19 +2324,19 @@
     <t xml:space="preserve">0.529588162899017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519930124282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507052481174469</t>
+    <t xml:space="preserve">0.519930064678192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507052540779114</t>
   </si>
   <si>
     <t xml:space="preserve">0.500613749027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494174987077713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502223551273346</t>
+    <t xml:space="preserve">0.494175016880035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502223432064056</t>
   </si>
   <si>
     <t xml:space="preserve">0.537636637687683</t>
@@ -2348,22 +2348,22 @@
     <t xml:space="preserve">0.510271906852722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499004065990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492565304040909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487736254930496</t>
+    <t xml:space="preserve">0.499004036188126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492565333843231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487736225128174</t>
   </si>
   <si>
     <t xml:space="preserve">0.484516859054565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447493970394135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431397080421448</t>
+    <t xml:space="preserve">0.44749391078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431397050619125</t>
   </si>
   <si>
     <t xml:space="preserve">0.449103713035583</t>
@@ -2378,46 +2378,46 @@
     <t xml:space="preserve">0.378277271986008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375862777233124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367009431123734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359765827655792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376667588949203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421738862991333</t>
+    <t xml:space="preserve">0.375862747430801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367009460926056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359765857458115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376667559146881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421738892793655</t>
   </si>
   <si>
     <t xml:space="preserve">0.423348635435104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441055178642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505442798137665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468419998884201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461981177330017</t>
+    <t xml:space="preserve">0.441055238246918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505442917346954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468419939279556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461981236934662</t>
   </si>
   <si>
     <t xml:space="preserve">0.465200573205948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452323079109192</t>
+    <t xml:space="preserve">0.45232304930687</t>
   </si>
   <si>
     <t xml:space="preserve">0.455542415380478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450713366270065</t>
+    <t xml:space="preserve">0.450713306665421</t>
   </si>
   <si>
     <t xml:space="preserve">0.460371524095535</t>
@@ -2426,22 +2426,22 @@
     <t xml:space="preserve">0.457152098417282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453932732343674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47968778014183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495784640312195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489345908164978</t>
+    <t xml:space="preserve">0.453932762145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479687809944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495784670114517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4893459379673</t>
   </si>
   <si>
     <t xml:space="preserve">0.547294795513153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565001368522644</t>
+    <t xml:space="preserve">0.565001487731934</t>
   </si>
   <si>
     <t xml:space="preserve">0.576269209384918</t>
@@ -2450,34 +2450,34 @@
     <t xml:space="preserve">0.575464367866516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569830477237701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549709320068359</t>
+    <t xml:space="preserve">0.569830417633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549709379673004</t>
   </si>
   <si>
     <t xml:space="preserve">0.56741589307785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545685112476349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558562576770782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5440753698349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531197905540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559367477893829</t>
+    <t xml:space="preserve">0.545685052871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558562636375427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544075429439545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531197965145111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559367418289185</t>
   </si>
   <si>
     <t xml:space="preserve">0.573854625225067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581903100013733</t>
+    <t xml:space="preserve">0.581903040409088</t>
   </si>
   <si>
     <t xml:space="preserve">0.579488635063171</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">0.552123844623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548099637031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548904418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553733587265015</t>
+    <t xml:space="preserve">0.54809957742691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548904478549957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55373352766037</t>
   </si>
   <si>
     <t xml:space="preserve">0.582058250904083</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">0.581226766109467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573743224143982</t>
+    <t xml:space="preserve">0.573743164539337</t>
   </si>
   <si>
     <t xml:space="preserve">0.567091107368469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574574708938599</t>
+    <t xml:space="preserve">0.574574649333954</t>
   </si>
   <si>
     <t xml:space="preserve">0.57291167974472</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">0.557944416999817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558775961399078</t>
+    <t xml:space="preserve">0.558776021003723</t>
   </si>
   <si>
     <t xml:space="preserve">0.540482699871063</t>
@@ -2531,16 +2531,16 @@
     <t xml:space="preserve">0.544640243053436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542977213859558</t>
+    <t xml:space="preserve">0.542977273464203</t>
   </si>
   <si>
     <t xml:space="preserve">0.530504584312439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531336069107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532167613506317</t>
+    <t xml:space="preserve">0.531336009502411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532167553901672</t>
   </si>
   <si>
     <t xml:space="preserve">0.516368865966797</t>
@@ -2552,13 +2552,13 @@
     <t xml:space="preserve">0.505559206008911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508885204792023</t>
+    <t xml:space="preserve">0.508885264396667</t>
   </si>
   <si>
     <t xml:space="preserve">0.502233147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51553738117218</t>
+    <t xml:space="preserve">0.515537321567535</t>
   </si>
   <si>
     <t xml:space="preserve">0.498907119035721</t>
@@ -2570,28 +2570,28 @@
     <t xml:space="preserve">0.494749575853348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500570058822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483939945697784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46564656496048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466478139162064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461489021778107</t>
+    <t xml:space="preserve">0.500570118427277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48393988609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465646594762802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466478109359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461489081382751</t>
   </si>
   <si>
     <t xml:space="preserve">0.460657566785812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473961740732193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473130226135254</t>
+    <t xml:space="preserve">0.473961770534515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473130285739899</t>
   </si>
   <si>
     <t xml:space="preserve">0.486434429883957</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">0.503896176815033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495581030845642</t>
+    <t xml:space="preserve">0.495581090450287</t>
   </si>
   <si>
     <t xml:space="preserve">0.484771400690079</t>
@@ -2630,22 +2630,22 @@
     <t xml:space="preserve">0.497244030237198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487265974283218</t>
+    <t xml:space="preserve">0.487265944480896</t>
   </si>
   <si>
     <t xml:space="preserve">0.493086487054825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483108371496201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478119343519211</t>
+    <t xml:space="preserve">0.483108341693878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478119283914566</t>
   </si>
   <si>
     <t xml:space="preserve">0.475624799728394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476456314325333</t>
+    <t xml:space="preserve">0.47645628452301</t>
   </si>
   <si>
     <t xml:space="preserve">0.529673039913177</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">0.523852467536926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528010070323944</t>
+    <t xml:space="preserve">0.528010010719299</t>
   </si>
   <si>
     <t xml:space="preserve">0.533830583095551</t>
@@ -2666,10 +2666,10 @@
     <t xml:space="preserve">0.547966241836548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528841555118561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525515496730804</t>
+    <t xml:space="preserve">0.528841495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52551543712616</t>
   </si>
   <si>
     <t xml:space="preserve">0.526347041130066</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">0.570417106151581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583721280097961</t>
+    <t xml:space="preserve">0.583721399307251</t>
   </si>
   <si>
     <t xml:space="preserve">0.585384368896484</t>
@@ -2699,37 +2699,37 @@
     <t xml:space="preserve">0.57790070772171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580395221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550460875034332</t>
+    <t xml:space="preserve">0.58039528131485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550460815429688</t>
   </si>
   <si>
     <t xml:space="preserve">0.556281387805939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545471727848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567922592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566259562969208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5571129322052</t>
+    <t xml:space="preserve">0.545471787452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567922651767731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566259503364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557112991809845</t>
   </si>
   <si>
     <t xml:space="preserve">0.56459653377533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549629330635071</t>
+    <t xml:space="preserve">0.549629271030426</t>
   </si>
   <si>
     <t xml:space="preserve">0.539651155471802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536325097084045</t>
+    <t xml:space="preserve">0.53632515668869</t>
   </si>
   <si>
     <t xml:space="preserve">0.532999098300934</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">0.513874351978302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522189438343048</t>
+    <t xml:space="preserve">0.522189497947693</t>
   </si>
   <si>
     <t xml:space="preserve">0.513042747974396</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">0.519694924354553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508053719997406</t>
+    <t xml:space="preserve">0.508053779602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.488097429275513</t>
@@ -2774,13 +2774,13 @@
     <t xml:space="preserve">0.488928943872452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492254972457886</t>
+    <t xml:space="preserve">0.492255032062531</t>
   </si>
   <si>
     <t xml:space="preserve">0.496412515640259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49059197306633</t>
+    <t xml:space="preserve">0.490591913461685</t>
   </si>
   <si>
     <t xml:space="preserve">0.485602915287018</t>
@@ -2789,13 +2789,13 @@
     <t xml:space="preserve">0.480613857507706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47479322552681</t>
+    <t xml:space="preserve">0.474793195724487</t>
   </si>
   <si>
     <t xml:space="preserve">0.4540054500103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478950828313828</t>
+    <t xml:space="preserve">0.478950768709183</t>
   </si>
   <si>
     <t xml:space="preserve">0.458163022994995</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">0.439869731664658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439038217067719</t>
+    <t xml:space="preserve">0.439038246870041</t>
   </si>
   <si>
     <t xml:space="preserve">0.419913470745087</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">0.422408014535904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424071043729782</t>
+    <t xml:space="preserve">0.42407101392746</t>
   </si>
   <si>
     <t xml:space="preserve">0.411598384380341</t>
@@ -2831,25 +2831,25 @@
     <t xml:space="preserve">0.377090603113174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365033715963364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40203595161438</t>
+    <t xml:space="preserve">0.365033686161041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402035981416702</t>
   </si>
   <si>
     <t xml:space="preserve">0.413677155971527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407440811395645</t>
+    <t xml:space="preserve">0.407440841197968</t>
   </si>
   <si>
     <t xml:space="preserve">0.412429869174957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431554645299911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429891645908356</t>
+    <t xml:space="preserve">0.431554615497589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429891616106033</t>
   </si>
   <si>
     <t xml:space="preserve">0.432386130094528</t>
@@ -2864,40 +2864,40 @@
     <t xml:space="preserve">0.436543703079224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443195790052414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448184847831726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44652184844017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440701246261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434880703687668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424902528524399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444858849048615</t>
+    <t xml:space="preserve">0.443195819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448184818029404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.446521908044815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440701276063919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434880673885345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424902558326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444858878850937</t>
   </si>
   <si>
     <t xml:space="preserve">0.447353363037109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445690363645554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463152050971985</t>
+    <t xml:space="preserve">0.445690333843231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463152080774307</t>
   </si>
   <si>
     <t xml:space="preserve">0.481445372104645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477287769317627</t>
+    <t xml:space="preserve">0.477287858724594</t>
   </si>
   <si>
     <t xml:space="preserve">0.470635682344437</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">0.429060101509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421576499938965</t>
+    <t xml:space="preserve">0.421576529741287</t>
   </si>
   <si>
     <t xml:space="preserve">0.40993532538414</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">0.415755927562714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433217704296112</t>
+    <t xml:space="preserve">0.43321767449379</t>
   </si>
   <si>
     <t xml:space="preserve">0.452196657657623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446109414100647</t>
+    <t xml:space="preserve">0.446109443902969</t>
   </si>
   <si>
     <t xml:space="preserve">0.439152538776398</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">0.431326061487198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423499584197998</t>
+    <t xml:space="preserve">0.423499554395676</t>
   </si>
   <si>
     <t xml:space="preserve">0.406542211771011</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">0.383932381868362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388715207576752</t>
+    <t xml:space="preserve">0.388715237379074</t>
   </si>
   <si>
     <t xml:space="preserve">0.382627964019775</t>
@@ -2969,19 +2969,19 @@
     <t xml:space="preserve">0.380888730287552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387845635414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393498063087463</t>
+    <t xml:space="preserve">0.387845605611801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393498033285141</t>
   </si>
   <si>
     <t xml:space="preserve">0.379584342241287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384367167949677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378714710474014</t>
+    <t xml:space="preserve">0.384367197751999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378714740276337</t>
   </si>
   <si>
     <t xml:space="preserve">0.373931884765625</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">0.372627437114716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373062252998352</t>
+    <t xml:space="preserve">0.37306222319603</t>
   </si>
   <si>
     <t xml:space="preserve">0.378279894590378</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">0.366105407476425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371323019266129</t>
+    <t xml:space="preserve">0.371323049068451</t>
   </si>
   <si>
     <t xml:space="preserve">0.375671088695526</t>
@@ -3017,10 +3017,10 @@
     <t xml:space="preserve">0.370018631219864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367844611406326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366974979639053</t>
+    <t xml:space="preserve">0.367844581604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366975009441376</t>
   </si>
   <si>
     <t xml:space="preserve">0.364366173744202</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">0.368714213371277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37741032242775</t>
+    <t xml:space="preserve">0.377410292625427</t>
   </si>
   <si>
     <t xml:space="preserve">0.36958384513855</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">0.374801486730576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37523627281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372192680835724</t>
+    <t xml:space="preserve">0.375236243009567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372192651033401</t>
   </si>
   <si>
     <t xml:space="preserve">0.36523574590683</t>
@@ -3086,157 +3086,160 @@
     <t xml:space="preserve">0.396106898784637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399150520563126</t>
+    <t xml:space="preserve">0.399150550365448</t>
   </si>
   <si>
     <t xml:space="preserve">0.403498560190201</t>
   </si>
   <si>
+    <t xml:space="preserve">0.396541714668274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392193675041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401759386062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403933376073837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408716231584549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400020152330399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400889724493027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393063247203827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380019158124924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385236769914627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389150023460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390889227390289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395672082901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401324540376663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39697653055191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400454938411713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390454411506653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387410819530487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383497565984726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382193177938461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381758362054825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371757864952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357844114303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366540193557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360887736082077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362626940011978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369149029254913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379149526357651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3861064016819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394367694854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404368221759796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392628461122513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391758888959885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395237267017365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385671585798264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394802510738373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388280391693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398373305797577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399289101362228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400204926729202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403868108987808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406615495681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407531291246414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40936291217804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408447116613388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40478390455246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405699700117111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401120722293854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402952283620834</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.396541684865952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392193675041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401759386062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40393340587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408716231584549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400020182132721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400889724493027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393063247203827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380019158124924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385236769914627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389150023460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390889227390289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395672112703323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401324540376663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396976500749588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400454938411713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390454411506653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387410819530487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383497595787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382193148136139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381758362054825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371757864952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357844114303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366540193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360887706279755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362626940011978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369148999452591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379149526357651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3861064016819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394367665052414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404368191957474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392628461122513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391758888959885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395237267017365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385671615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39480248093605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388280391693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398373305797577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399289101362228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400204926729202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403868108987808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406615495681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407531291246414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40936291217804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408447116613388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40478390455246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405699700117111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401120722293854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402952283620834</t>
   </si>
   <si>
     <t xml:space="preserve">0.402036517858505</t>
@@ -53806,7 +53809,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1910" t="s">
-        <v>1026</v>
+        <v>1075</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53832,7 +53835,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1911" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53884,7 +53887,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1913" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53910,7 +53913,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1914" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53936,7 +53939,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1915" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53962,7 +53965,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1916" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53988,7 +53991,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1917" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54014,7 +54017,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1918" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54040,7 +54043,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1919" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54066,7 +54069,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1920" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54092,7 +54095,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1921" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54118,7 +54121,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1922" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54144,7 +54147,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1923" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54170,7 +54173,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1924" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54196,7 +54199,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1925" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54222,7 +54225,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1926" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54248,7 +54251,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1927" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54300,7 +54303,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1929" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54326,7 +54329,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1930" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54352,7 +54355,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1931" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54378,7 +54381,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1932" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54404,7 +54407,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1933" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54430,7 +54433,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1934" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54456,7 +54459,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1935" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54482,7 +54485,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1936" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54508,7 +54511,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1937" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54534,7 +54537,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1938" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54560,7 +54563,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1939" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54586,7 +54589,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1940" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54612,7 +54615,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1941" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54638,7 +54641,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1942" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54664,7 +54667,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1943" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54690,7 +54693,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1944" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54716,7 +54719,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1945" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54742,7 +54745,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1946" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54768,7 +54771,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1947" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54794,7 +54797,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1948" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54820,7 +54823,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1949" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54976,7 +54979,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1955" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55132,7 +55135,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1961" t="s">
-        <v>1026</v>
+        <v>1075</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55210,7 +55213,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1964" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55236,7 +55239,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1965" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55262,7 +55265,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1966" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55288,7 +55291,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1967" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55314,7 +55317,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1968" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55340,7 +55343,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1969" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55366,7 +55369,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1970" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55392,7 +55395,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -55418,7 +55421,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1972" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55444,7 +55447,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1973" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55470,7 +55473,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1974" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55496,7 +55499,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1975" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55522,7 +55525,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1976" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55548,7 +55551,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1977" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55574,7 +55577,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1978" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55600,7 +55603,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1979" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55626,7 +55629,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1980" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55652,7 +55655,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1981" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55678,7 +55681,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1982" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55704,7 +55707,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1983" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55730,7 +55733,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1984" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55756,7 +55759,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1985" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55782,7 +55785,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1986" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55808,7 +55811,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1987" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55834,7 +55837,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1988" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55860,7 +55863,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1989" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55886,7 +55889,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G1990" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55912,7 +55915,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1991" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55938,7 +55941,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1992" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55964,7 +55967,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1993" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55990,7 +55993,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1994" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56016,7 +56019,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1995" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56042,7 +56045,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1996" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56068,7 +56071,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1997" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56094,7 +56097,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1998" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56120,7 +56123,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1999" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56146,7 +56149,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G2000" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56172,7 +56175,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G2001" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56198,7 +56201,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2002" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56224,7 +56227,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2003" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56250,7 +56253,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2004" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56276,7 +56279,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2005" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56302,7 +56305,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2006" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56328,7 +56331,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2007" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56354,7 +56357,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2008" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56380,7 +56383,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2009" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56406,7 +56409,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2010" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56432,7 +56435,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2011" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56458,7 +56461,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2012" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56484,7 +56487,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56510,7 +56513,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G2014" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56536,7 +56539,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2015" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56562,7 +56565,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2016" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56588,7 +56591,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56640,7 +56643,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56666,7 +56669,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2020" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56692,7 +56695,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2021" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56718,7 +56721,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2022" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56744,7 +56747,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2023" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56770,7 +56773,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2024" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56796,7 +56799,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G2025" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56822,7 +56825,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2026" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56848,7 +56851,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2027" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56874,7 +56877,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2028" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56900,7 +56903,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G2029" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56926,7 +56929,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2030" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56952,7 +56955,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2031" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56978,7 +56981,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2032" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57004,7 +57007,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2033" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57030,7 +57033,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2034" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57056,7 +57059,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2035" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57082,7 +57085,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2036" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57108,7 +57111,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2037" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57134,7 +57137,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2038" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57160,7 +57163,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2039" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57186,7 +57189,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2040" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57212,7 +57215,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57238,7 +57241,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2042" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57264,7 +57267,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2043" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57316,7 +57319,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2045" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57524,7 +57527,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2053" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57550,7 +57553,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2054" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57758,7 +57761,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2062" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57810,7 +57813,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2064" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57836,7 +57839,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2065" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57862,7 +57865,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2066" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57888,7 +57891,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2067" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57940,7 +57943,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2069" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58226,7 +58229,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2080" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58278,7 +58281,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2082" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58304,7 +58307,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G2083" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -58330,7 +58333,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2084" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58356,7 +58359,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2085" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58382,7 +58385,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2086" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58408,7 +58411,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2087" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -58434,7 +58437,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2088" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58590,7 +58593,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2094" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58616,7 +58619,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2095" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58642,7 +58645,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2096" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58668,7 +58671,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2097" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58694,7 +58697,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2098" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58824,7 +58827,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2103" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58850,7 +58853,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2104" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58876,7 +58879,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2105" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58902,7 +58905,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2106" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58928,7 +58931,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2107" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59214,7 +59217,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2118" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59240,7 +59243,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2119" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59266,7 +59269,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G2120" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59292,7 +59295,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G2121" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59318,7 +59321,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2122" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59344,7 +59347,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G2123" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59370,7 +59373,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2124" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59396,7 +59399,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2125" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59422,7 +59425,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2126" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59448,7 +59451,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2127" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59474,7 +59477,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2128" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59500,7 +59503,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2129" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59526,7 +59529,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2130" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59552,7 +59555,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2131" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59578,7 +59581,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2132" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59604,7 +59607,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2133" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59630,7 +59633,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2134" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59656,7 +59659,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2135" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59682,7 +59685,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2136" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59708,7 +59711,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2137" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59734,7 +59737,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2138" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59760,7 +59763,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2139" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59786,7 +59789,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2140" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59812,7 +59815,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2141" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59838,7 +59841,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2142" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59864,7 +59867,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2143" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59890,7 +59893,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2144" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59916,7 +59919,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2145" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59942,7 +59945,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2146" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59968,7 +59971,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2147" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59994,7 +59997,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2148" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60020,7 +60023,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2149" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60046,7 +60049,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2150" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60072,7 +60075,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G2151" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60098,7 +60101,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G2152" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60124,7 +60127,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2153" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60150,7 +60153,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2154" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60176,7 +60179,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2155" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60202,7 +60205,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60228,7 +60231,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60254,7 +60257,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2158" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60280,7 +60283,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2159" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60306,7 +60309,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2160" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60332,7 +60335,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2161" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60358,7 +60361,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2162" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60384,7 +60387,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2163" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60410,7 +60413,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2164" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60436,7 +60439,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2165" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60462,7 +60465,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2166" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60488,7 +60491,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2167" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60514,7 +60517,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2168" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60540,7 +60543,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2169" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60566,7 +60569,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2170" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60592,7 +60595,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G2171" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60618,7 +60621,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G2172" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60644,7 +60647,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2173" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60670,7 +60673,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2174" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60696,7 +60699,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2175" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60722,7 +60725,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2176" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60748,7 +60751,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2177" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60774,7 +60777,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2178" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60800,7 +60803,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2179" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60826,7 +60829,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2180" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60852,7 +60855,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2181" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60878,7 +60881,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2182" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60904,7 +60907,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2183" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60930,7 +60933,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2184" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60956,7 +60959,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2185" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60982,7 +60985,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2186" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61008,7 +61011,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2187" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61034,7 +61037,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2188" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61060,7 +61063,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2189" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61086,7 +61089,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2190" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61112,7 +61115,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2191" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61138,7 +61141,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2192" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61164,7 +61167,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2193" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61190,7 +61193,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2194" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61216,7 +61219,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2195" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61242,7 +61245,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2196" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61268,7 +61271,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2197" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61294,7 +61297,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2198" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61320,7 +61323,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2199" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61346,7 +61349,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2200" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61372,7 +61375,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2201" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61398,7 +61401,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2202" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61424,7 +61427,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2203" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61450,7 +61453,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2204" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61476,7 +61479,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2205" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61502,7 +61505,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2206" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61528,7 +61531,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2207" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61554,7 +61557,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2208" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61580,7 +61583,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2209" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61606,7 +61609,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2210" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61632,7 +61635,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2211" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61658,7 +61661,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2212" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61684,7 +61687,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2213" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61710,7 +61713,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2214" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61736,7 +61739,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61762,7 +61765,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2216" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61788,7 +61791,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2217" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61814,7 +61817,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2218" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61840,7 +61843,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2219" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61866,7 +61869,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2220" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61892,7 +61895,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2221" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61918,7 +61921,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2222" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61944,7 +61947,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2223" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61970,7 +61973,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2224" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61996,7 +61999,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2225" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62022,7 +62025,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2226" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62048,7 +62051,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2227" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62074,7 +62077,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2228" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62100,7 +62103,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2229" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62126,7 +62129,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2230" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62152,7 +62155,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2231" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62178,7 +62181,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2232" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62204,7 +62207,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2233" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62230,7 +62233,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2234" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62256,7 +62259,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2235" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62282,7 +62285,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2236" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62308,7 +62311,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2237" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62334,7 +62337,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2238" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62360,7 +62363,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2239" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62386,7 +62389,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2240" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62412,7 +62415,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2241" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62438,7 +62441,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2242" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62464,7 +62467,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2243" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62490,7 +62493,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2244" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62516,7 +62519,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2245" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62542,7 +62545,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2246" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62568,7 +62571,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62594,7 +62597,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62620,7 +62623,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2249" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62646,7 +62649,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2250" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62672,7 +62675,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2251" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62698,7 +62701,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G2252" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62724,7 +62727,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G2253" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62750,7 +62753,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2254" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62776,7 +62779,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2255" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62802,7 +62805,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2256" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62828,7 +62831,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2257" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62854,7 +62857,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2258" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62880,7 +62883,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2259" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62906,7 +62909,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2260" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62932,7 +62935,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2261" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62958,7 +62961,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2262" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62984,7 +62987,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2263" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63010,7 +63013,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2264" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63036,7 +63039,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2265" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63062,7 +63065,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2266" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63088,7 +63091,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2267" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63114,7 +63117,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2268" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63140,7 +63143,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2269" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63166,7 +63169,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63192,7 +63195,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2271" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63218,7 +63221,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2272" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63244,7 +63247,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2273" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63270,7 +63273,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2274" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63296,7 +63299,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2275" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63322,7 +63325,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2276" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63348,7 +63351,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2277" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63374,7 +63377,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2278" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63400,7 +63403,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G2279" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63426,7 +63429,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2280" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63452,7 +63455,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2281" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63478,7 +63481,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2282" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63504,7 +63507,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2283" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63530,7 +63533,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2284" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63556,7 +63559,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2285" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63582,7 +63585,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2286" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63608,7 +63611,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2287" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63634,7 +63637,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2288" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63660,7 +63663,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2289" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63686,7 +63689,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G2290" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63712,7 +63715,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63738,7 +63741,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G2292" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63764,7 +63767,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G2293" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63790,7 +63793,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2294" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63816,7 +63819,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2295" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63842,7 +63845,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2296" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63868,7 +63871,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2297" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63894,7 +63897,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2298" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63920,7 +63923,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2299" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63946,7 +63949,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2300" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63972,7 +63975,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2301" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63998,7 +64001,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2302" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64024,7 +64027,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2303" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64050,7 +64053,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2304" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64076,7 +64079,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G2305" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64102,7 +64105,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2306" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64128,7 +64131,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2307" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64154,7 +64157,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G2308" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64180,7 +64183,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2309" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64206,7 +64209,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G2310" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64232,7 +64235,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2311" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64258,7 +64261,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2312" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64284,7 +64287,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2313" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64310,7 +64313,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2314" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64336,7 +64339,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2315" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64362,7 +64365,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2316" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64388,7 +64391,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2317" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64414,7 +64417,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2318" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64440,7 +64443,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2319" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64466,7 +64469,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2320" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64492,7 +64495,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2321" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64518,7 +64521,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2322" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64544,7 +64547,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2323" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64570,7 +64573,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2324" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64596,7 +64599,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G2325" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64622,7 +64625,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64648,7 +64651,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2327" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64674,7 +64677,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2328" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64700,7 +64703,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2329" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64726,7 +64729,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G2330" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64752,7 +64755,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G2331" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64778,7 +64781,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G2332" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64804,7 +64807,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2333" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64830,7 +64833,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2334" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64856,7 +64859,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2335" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64882,7 +64885,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G2336" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64908,7 +64911,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2337" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64934,7 +64937,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2338" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64960,7 +64963,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G2339" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64986,7 +64989,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2340" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65012,7 +65015,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G2341" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65038,7 +65041,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G2342" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65064,7 +65067,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G2343" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65090,7 +65093,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G2344" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65116,7 +65119,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2345" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65142,7 +65145,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G2346" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65168,7 +65171,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G2347" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65194,7 +65197,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2348" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65220,7 +65223,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G2349" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65246,7 +65249,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2350" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65272,7 +65275,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2351" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65298,7 +65301,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2352" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65324,7 +65327,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2353" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65350,7 +65353,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2354" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65376,7 +65379,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G2355" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65402,7 +65405,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2356" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65428,7 +65431,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2357" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65454,7 +65457,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2358" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65480,7 +65483,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G2359" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65506,7 +65509,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G2360" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65532,7 +65535,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G2361" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65558,7 +6556